--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -615,10 +615,10 @@
         <v>6.25</v>
       </c>
       <c r="C2" t="n">
-        <v>0.021182</v>
+        <v>0.021256</v>
       </c>
       <c r="D2" t="n">
-        <v>0.021182</v>
+        <v>0.021256</v>
       </c>
       <c r="E2" t="n">
         <v>1.16</v>
@@ -773,10 +773,10 @@
         <v>1.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.003062</v>
+        <v>0.002988</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.003062</v>
+        <v>0.002988</v>
       </c>
       <c r="AH3" t="n">
         <v>-0.01</v>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -615,10 +615,10 @@
         <v>6.25</v>
       </c>
       <c r="C2" t="n">
-        <v>0.021256</v>
+        <v>0.021339</v>
       </c>
       <c r="D2" t="n">
-        <v>0.021256</v>
+        <v>0.021339</v>
       </c>
       <c r="E2" t="n">
         <v>1.16</v>
@@ -773,10 +773,10 @@
         <v>1.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.002988</v>
+        <v>0.002905</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.002988</v>
+        <v>0.002905</v>
       </c>
       <c r="AH3" t="n">
         <v>-0.01</v>
@@ -7203,7 +7203,9 @@
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
+      <c r="S61" t="n">
+        <v>372616</v>
+      </c>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="n">
@@ -7215,7 +7217,9 @@
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
-      <c r="AA61" t="inlineStr"/>
+      <c r="AA61" t="n">
+        <v>0.777299</v>
+      </c>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
         <v>2.178243</v>
@@ -7254,10 +7258,10 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>5.1253</v>
+        <v>5.0856</v>
       </c>
       <c r="K62" t="n">
-        <v>5.1247</v>
+        <v>5.085</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -7270,10 +7274,10 @@
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="n">
-        <v>-1.086537</v>
+        <v>-1.85271</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.086663</v>
+        <v>-1.852924</v>
       </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -615,10 +615,10 @@
         <v>6.25</v>
       </c>
       <c r="C2" t="n">
-        <v>0.021339</v>
+        <v>0.021433</v>
       </c>
       <c r="D2" t="n">
-        <v>0.021339</v>
+        <v>0.021433</v>
       </c>
       <c r="E2" t="n">
         <v>1.16</v>
@@ -773,10 +773,10 @@
         <v>1.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.002905</v>
+        <v>0.002811</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.002905</v>
+        <v>0.002811</v>
       </c>
       <c r="AH3" t="n">
         <v>-0.01</v>
@@ -7258,10 +7258,10 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>5.0856</v>
+        <v>5.0979</v>
       </c>
       <c r="K62" t="n">
-        <v>5.085</v>
+        <v>5.0973</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -7274,10 +7274,10 @@
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="n">
-        <v>-1.85271</v>
+        <v>-1.615331</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.852924</v>
+        <v>-1.615518</v>
       </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -615,10 +615,10 @@
         <v>6.25</v>
       </c>
       <c r="C2" t="n">
-        <v>0.021433</v>
+        <v>0.02154</v>
       </c>
       <c r="D2" t="n">
-        <v>0.021433</v>
+        <v>0.02154</v>
       </c>
       <c r="E2" t="n">
         <v>1.16</v>
@@ -773,10 +773,10 @@
         <v>1.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.002811</v>
+        <v>0.002704</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.002811</v>
+        <v>0.002704</v>
       </c>
       <c r="AH3" t="n">
         <v>-0.01</v>
@@ -7183,11 +7183,15 @@
       <c r="D61" t="n">
         <v>0.051784</v>
       </c>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="n">
+        <v>-0.32</v>
+      </c>
       <c r="F61" t="n">
         <v>-0.22</v>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="n">
+        <v>-0.32</v>
+      </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="n">
@@ -7220,11 +7224,15 @@
       <c r="AA61" t="n">
         <v>0.777299</v>
       </c>
-      <c r="AB61" t="inlineStr"/>
+      <c r="AB61" t="n">
+        <v>4.223453</v>
+      </c>
       <c r="AC61" t="n">
         <v>2.178243</v>
       </c>
-      <c r="AD61" t="inlineStr"/>
+      <c r="AD61" t="n">
+        <v>3.983297</v>
+      </c>
       <c r="AE61" t="n">
         <v>-0.25</v>
       </c>
@@ -7258,10 +7266,10 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>5.0979</v>
+        <v>5.1149</v>
       </c>
       <c r="K62" t="n">
-        <v>5.0973</v>
+        <v>5.1143</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -7274,10 +7282,10 @@
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="n">
-        <v>-1.615331</v>
+        <v>-1.287247</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.615518</v>
+        <v>-1.287396</v>
       </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK62"/>
+  <dimension ref="A1:AG62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,145 +463,125 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>ibc_br</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
           <t>cambio_venda_usd</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>cambio_compra_usd</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>saldo_credito_total</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>saldo_credito_pj</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>saldo_credito_pf</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inadimplencia_total</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>inadimplencia_pj</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inadimplencia_pf</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>var_pct_ibc_br</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ipca_acum_12m</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>inpc_acum_12m</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>dif_selic_over</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>dif_cdi</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pj</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -633,38 +613,34 @@
         <v>96.95313</v>
       </c>
       <c r="I2" t="n">
-        <v>97.10569</v>
+        <v>5.4394</v>
       </c>
       <c r="J2" t="n">
-        <v>5.4394</v>
+        <v>5.4388</v>
       </c>
       <c r="K2" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="L2" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="M2" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="N2" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="O2" t="n">
-        <v>2.34</v>
+        <v>3.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.43</v>
+        <v>21.42</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="R2" t="n">
-        <v>21.42</v>
-      </c>
-      <c r="S2" t="n">
         <v>368886</v>
       </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -679,10 +655,6 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -710,84 +682,72 @@
         <v>97.47790999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>96.52863000000001</v>
+        <v>5.643</v>
       </c>
       <c r="J3" t="n">
-        <v>5.643</v>
+        <v>5.6424</v>
       </c>
       <c r="K3" t="n">
-        <v>5.6424</v>
+        <v>4511956</v>
       </c>
       <c r="L3" t="n">
-        <v>4511956</v>
+        <v>1910940</v>
       </c>
       <c r="M3" t="n">
-        <v>1910940</v>
+        <v>2601017</v>
       </c>
       <c r="N3" t="n">
-        <v>2601017</v>
+        <v>2.33</v>
       </c>
       <c r="O3" t="n">
-        <v>2.33</v>
+        <v>2.99</v>
       </c>
       <c r="P3" t="n">
-        <v>1.43</v>
+        <v>22.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.99</v>
+        <v>367927</v>
       </c>
       <c r="R3" t="n">
-        <v>22.89</v>
+        <v>0.541272</v>
       </c>
       <c r="S3" t="n">
-        <v>367927</v>
+        <v>3.74306</v>
       </c>
       <c r="T3" t="n">
-        <v>0.541272</v>
+        <v>3.743473</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.59426</v>
+        <v>1.596467</v>
       </c>
       <c r="V3" t="n">
-        <v>3.74306</v>
+        <v>0.888065</v>
       </c>
       <c r="W3" t="n">
-        <v>3.743473</v>
+        <v>2.123375</v>
       </c>
       <c r="X3" t="n">
-        <v>1.596467</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.888065</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.123375</v>
-      </c>
-      <c r="AA3" t="n">
         <v>-0.259972</v>
       </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.002704</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.002704</v>
+      </c>
       <c r="AE3" t="n">
-        <v>1.5</v>
+        <v>-0.01</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.002704</v>
+        <v>-0.02</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.002704</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AK3" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -817,84 +777,72 @@
         <v>99.05295</v>
       </c>
       <c r="I4" t="n">
-        <v>97.85433</v>
+        <v>5.6199</v>
       </c>
       <c r="J4" t="n">
-        <v>5.6199</v>
+        <v>5.6193</v>
       </c>
       <c r="K4" t="n">
-        <v>5.6193</v>
+        <v>4597507</v>
       </c>
       <c r="L4" t="n">
-        <v>4597507</v>
+        <v>1933111</v>
       </c>
       <c r="M4" t="n">
-        <v>1933111</v>
+        <v>2664395</v>
       </c>
       <c r="N4" t="n">
-        <v>2664395</v>
+        <v>2.36</v>
       </c>
       <c r="O4" t="n">
-        <v>2.36</v>
+        <v>3.01</v>
       </c>
       <c r="P4" t="n">
-        <v>1.46</v>
+        <v>23.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.01</v>
+        <v>367772</v>
       </c>
       <c r="R4" t="n">
-        <v>23.91</v>
+        <v>1.615792</v>
       </c>
       <c r="S4" t="n">
-        <v>367772</v>
+        <v>-0.409357</v>
       </c>
       <c r="T4" t="n">
-        <v>1.615792</v>
+        <v>-0.4094</v>
       </c>
       <c r="U4" t="n">
-        <v>1.373375</v>
+        <v>1.896096</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.409357</v>
+        <v>1.160214</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.4094</v>
+        <v>2.436662</v>
       </c>
       <c r="X4" t="n">
-        <v>1.896096</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.160214</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.436662</v>
-      </c>
-      <c r="AA4" t="n">
         <v>-0.042128</v>
       </c>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.005012</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.005012</v>
+      </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.005012</v>
+        <v>0.02</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.005012</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK4" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -924,84 +872,72 @@
         <v>99.36759000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>99.32245</v>
+        <v>5.5805</v>
       </c>
       <c r="J5" t="n">
-        <v>5.5805</v>
+        <v>5.5799</v>
       </c>
       <c r="K5" t="n">
-        <v>5.5799</v>
+        <v>4682852</v>
       </c>
       <c r="L5" t="n">
-        <v>4682852</v>
+        <v>1974391</v>
       </c>
       <c r="M5" t="n">
-        <v>1974391</v>
+        <v>2708461</v>
       </c>
       <c r="N5" t="n">
-        <v>2708461</v>
+        <v>2.35</v>
       </c>
       <c r="O5" t="n">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="P5" t="n">
-        <v>1.4</v>
+        <v>24.21</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.05</v>
+        <v>362204</v>
       </c>
       <c r="R5" t="n">
-        <v>24.21</v>
+        <v>0.317648</v>
       </c>
       <c r="S5" t="n">
-        <v>362204</v>
+        <v>-0.70108</v>
       </c>
       <c r="T5" t="n">
-        <v>0.317648</v>
+        <v>-0.701155</v>
       </c>
       <c r="U5" t="n">
-        <v>1.500312</v>
+        <v>1.856332</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.70108</v>
+        <v>2.135418</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.701155</v>
+        <v>1.653884</v>
       </c>
       <c r="X5" t="n">
-        <v>1.856332</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.135418</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.653884</v>
-      </c>
-      <c r="AA5" t="n">
         <v>-1.513981</v>
       </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.00406</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.00406</v>
+      </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>-0.01</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.00406</v>
+        <v>0.04</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.00406</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK5" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1031,84 +967,72 @@
         <v>97.41759</v>
       </c>
       <c r="I6" t="n">
-        <v>91.67452</v>
+        <v>5.3574</v>
       </c>
       <c r="J6" t="n">
-        <v>5.3574</v>
+        <v>5.3568</v>
       </c>
       <c r="K6" t="n">
-        <v>5.3568</v>
+        <v>4682131</v>
       </c>
       <c r="L6" t="n">
-        <v>4682131</v>
+        <v>1947035</v>
       </c>
       <c r="M6" t="n">
-        <v>1947035</v>
+        <v>2735096</v>
       </c>
       <c r="N6" t="n">
-        <v>2735096</v>
+        <v>2.51</v>
       </c>
       <c r="O6" t="n">
-        <v>2.51</v>
+        <v>3.26</v>
       </c>
       <c r="P6" t="n">
-        <v>1.46</v>
+        <v>25.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.26</v>
+        <v>358398</v>
       </c>
       <c r="R6" t="n">
-        <v>25.23</v>
+        <v>-1.96241</v>
       </c>
       <c r="S6" t="n">
-        <v>358398</v>
+        <v>-3.99785</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.96241</v>
+        <v>-3.99828</v>
       </c>
       <c r="U6" t="n">
-        <v>-7.700102</v>
+        <v>-0.015397</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.99785</v>
+        <v>-1.385541</v>
       </c>
       <c r="W6" t="n">
-        <v>-3.99828</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.015397</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-1.385541</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.9834000000000001</v>
-      </c>
-      <c r="AA6" t="n">
         <v>-1.050789</v>
       </c>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.001433</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.001433</v>
+      </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.001433</v>
+        <v>0.21</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.001433</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AK6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1138,84 +1062,72 @@
         <v>98.48287000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>95.64045</v>
+        <v>5.1394</v>
       </c>
       <c r="J7" t="n">
-        <v>5.1394</v>
+        <v>5.1388</v>
       </c>
       <c r="K7" t="n">
-        <v>5.1388</v>
+        <v>4727818</v>
       </c>
       <c r="L7" t="n">
-        <v>4727818</v>
+        <v>1971524</v>
       </c>
       <c r="M7" t="n">
-        <v>1971524</v>
+        <v>2756295</v>
       </c>
       <c r="N7" t="n">
-        <v>2756295</v>
+        <v>2.57</v>
       </c>
       <c r="O7" t="n">
-        <v>2.57</v>
+        <v>3.38</v>
       </c>
       <c r="P7" t="n">
-        <v>1.44</v>
+        <v>25.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.38</v>
+        <v>357740</v>
       </c>
       <c r="R7" t="n">
-        <v>25.63</v>
+        <v>1.093519</v>
       </c>
       <c r="S7" t="n">
-        <v>357740</v>
+        <v>-4.069138</v>
       </c>
       <c r="T7" t="n">
-        <v>1.093519</v>
+        <v>-4.069594</v>
       </c>
       <c r="U7" t="n">
-        <v>4.326098</v>
+        <v>0.975774</v>
       </c>
       <c r="V7" t="n">
-        <v>-4.069138</v>
+        <v>1.257759</v>
       </c>
       <c r="W7" t="n">
-        <v>-4.069594</v>
+        <v>0.775073</v>
       </c>
       <c r="X7" t="n">
-        <v>0.975774</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.257759</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.775073</v>
-      </c>
-      <c r="AA7" t="n">
         <v>-0.183595</v>
       </c>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.004849</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.004849</v>
+      </c>
       <c r="AE7" t="n">
-        <v>1.5</v>
+        <v>0.06</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.004849</v>
+        <v>0.12</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.004849</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AK7" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1245,84 +1157,72 @@
         <v>99.54331000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>104.53224</v>
+        <v>4.7378</v>
       </c>
       <c r="J8" t="n">
-        <v>4.7378</v>
+        <v>4.7372</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7372</v>
+        <v>4794583</v>
       </c>
       <c r="L8" t="n">
-        <v>4794583</v>
+        <v>1994119</v>
       </c>
       <c r="M8" t="n">
-        <v>1994119</v>
+        <v>2800464</v>
       </c>
       <c r="N8" t="n">
-        <v>2800464</v>
+        <v>2.66</v>
       </c>
       <c r="O8" t="n">
-        <v>2.66</v>
+        <v>3.45</v>
       </c>
       <c r="P8" t="n">
-        <v>1.55</v>
+        <v>26.54</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.45</v>
+        <v>353169</v>
       </c>
       <c r="R8" t="n">
-        <v>26.54</v>
+        <v>1.076776</v>
       </c>
       <c r="S8" t="n">
-        <v>353169</v>
+        <v>-7.814142</v>
       </c>
       <c r="T8" t="n">
-        <v>1.076776</v>
+        <v>-7.815054</v>
       </c>
       <c r="U8" t="n">
-        <v>9.297102000000001</v>
+        <v>1.412174</v>
       </c>
       <c r="V8" t="n">
-        <v>-7.814142</v>
+        <v>1.146068</v>
       </c>
       <c r="W8" t="n">
-        <v>-7.815054</v>
+        <v>1.602477</v>
       </c>
       <c r="X8" t="n">
-        <v>1.412174</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.146068</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.602477</v>
-      </c>
-      <c r="AA8" t="n">
         <v>-1.277744</v>
       </c>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.002356</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.002356</v>
+      </c>
       <c r="AE8" t="n">
-        <v>1</v>
+        <v>0.09</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.002356</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.002356</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK8" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1352,84 +1252,72 @@
         <v>99.44726</v>
       </c>
       <c r="I9" t="n">
-        <v>100.22451</v>
+        <v>4.9191</v>
       </c>
       <c r="J9" t="n">
-        <v>4.9191</v>
+        <v>4.9185</v>
       </c>
       <c r="K9" t="n">
-        <v>4.9185</v>
+        <v>4833732</v>
       </c>
       <c r="L9" t="n">
-        <v>4833732</v>
+        <v>2003312</v>
       </c>
       <c r="M9" t="n">
-        <v>2003312</v>
+        <v>2830420</v>
       </c>
       <c r="N9" t="n">
-        <v>2830420</v>
+        <v>2.72</v>
       </c>
       <c r="O9" t="n">
-        <v>2.72</v>
+        <v>3.54</v>
       </c>
       <c r="P9" t="n">
-        <v>1.57</v>
+        <v>27.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.54</v>
+        <v>345097</v>
       </c>
       <c r="R9" t="n">
-        <v>27.46</v>
+        <v>-0.09649099999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>345097</v>
+        <v>3.826671</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.09649099999999999</v>
+        <v>3.827155</v>
       </c>
       <c r="U9" t="n">
-        <v>-4.120958</v>
+        <v>0.816526</v>
       </c>
       <c r="V9" t="n">
-        <v>3.826671</v>
+        <v>0.461006</v>
       </c>
       <c r="W9" t="n">
-        <v>3.827155</v>
+        <v>1.06968</v>
       </c>
       <c r="X9" t="n">
-        <v>0.816526</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.461006</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.06968</v>
-      </c>
-      <c r="AA9" t="n">
         <v>-2.285591</v>
       </c>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.001785</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.001785</v>
+      </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.001785</v>
+        <v>0.09</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001785</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK9" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1459,84 +1347,72 @@
         <v>99.65249</v>
       </c>
       <c r="I10" t="n">
-        <v>99.74639000000001</v>
+        <v>4.7289</v>
       </c>
       <c r="J10" t="n">
-        <v>4.7289</v>
+        <v>4.7283</v>
       </c>
       <c r="K10" t="n">
-        <v>4.7283</v>
+        <v>4889397</v>
       </c>
       <c r="L10" t="n">
-        <v>4889397</v>
+        <v>2013726</v>
       </c>
       <c r="M10" t="n">
-        <v>2013726</v>
+        <v>2875671</v>
       </c>
       <c r="N10" t="n">
-        <v>2875671</v>
+        <v>2.79</v>
       </c>
       <c r="O10" t="n">
-        <v>2.79</v>
+        <v>3.65</v>
       </c>
       <c r="P10" t="n">
-        <v>1.57</v>
+        <v>27.42</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.65</v>
+        <v>346415</v>
       </c>
       <c r="R10" t="n">
-        <v>27.42</v>
+        <v>0.206371</v>
       </c>
       <c r="S10" t="n">
-        <v>346415</v>
+        <v>-3.866561</v>
       </c>
       <c r="T10" t="n">
-        <v>0.206371</v>
+        <v>-3.867033</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.477049</v>
+        <v>1.151595</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.866561</v>
+        <v>0.5198390000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>-3.867033</v>
+        <v>1.598738</v>
       </c>
       <c r="X10" t="n">
-        <v>1.151595</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.5198390000000001</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.598738</v>
-      </c>
-      <c r="AA10" t="n">
         <v>0.381922</v>
       </c>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.003057</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.003057</v>
+      </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.003057</v>
+        <v>0.11</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.003057</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK10" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1566,84 +1442,72 @@
         <v>99.53077999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>99.32053000000001</v>
+        <v>5.238</v>
       </c>
       <c r="J11" t="n">
-        <v>5.238</v>
+        <v>5.2374</v>
       </c>
       <c r="K11" t="n">
-        <v>5.2374</v>
+        <v>4965603</v>
       </c>
       <c r="L11" t="n">
-        <v>4965603</v>
+        <v>2052569</v>
       </c>
       <c r="M11" t="n">
-        <v>2052569</v>
+        <v>2913035</v>
       </c>
       <c r="N11" t="n">
-        <v>2913035</v>
+        <v>2.73</v>
       </c>
       <c r="O11" t="n">
-        <v>2.73</v>
+        <v>3.57</v>
       </c>
       <c r="P11" t="n">
-        <v>1.52</v>
+        <v>27.88</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.57</v>
+        <v>341958</v>
       </c>
       <c r="R11" t="n">
-        <v>27.88</v>
+        <v>-0.122134</v>
       </c>
       <c r="S11" t="n">
-        <v>341958</v>
+        <v>10.765717</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.122134</v>
+        <v>10.767083</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.426943</v>
+        <v>1.558597</v>
       </c>
       <c r="V11" t="n">
-        <v>10.765717</v>
+        <v>1.928912</v>
       </c>
       <c r="W11" t="n">
-        <v>10.767083</v>
+        <v>1.299314</v>
       </c>
       <c r="X11" t="n">
-        <v>1.558597</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.928912</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.299314</v>
-      </c>
-      <c r="AA11" t="n">
         <v>-1.286607</v>
       </c>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.00132</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.00132</v>
+      </c>
       <c r="AE11" t="n">
-        <v>0.5</v>
+        <v>-0.06</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.00132</v>
+        <v>-0.08</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.00132</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AK11" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1673,84 +1537,72 @@
         <v>101.43252</v>
       </c>
       <c r="I12" t="n">
-        <v>103.95413</v>
+        <v>5.1884</v>
       </c>
       <c r="J12" t="n">
-        <v>5.1884</v>
+        <v>5.1878</v>
       </c>
       <c r="K12" t="n">
-        <v>5.1878</v>
+        <v>4999244</v>
       </c>
       <c r="L12" t="n">
-        <v>4999244</v>
+        <v>2047038</v>
       </c>
       <c r="M12" t="n">
-        <v>2047038</v>
+        <v>2952207</v>
       </c>
       <c r="N12" t="n">
-        <v>2952207</v>
+        <v>2.84</v>
       </c>
       <c r="O12" t="n">
-        <v>2.84</v>
+        <v>3.71</v>
       </c>
       <c r="P12" t="n">
-        <v>1.6</v>
+        <v>29.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.71</v>
+        <v>346403</v>
       </c>
       <c r="R12" t="n">
-        <v>29.24</v>
+        <v>1.910705</v>
       </c>
       <c r="S12" t="n">
-        <v>346403</v>
+        <v>-0.946926</v>
       </c>
       <c r="T12" t="n">
-        <v>1.910705</v>
+        <v>-0.947035</v>
       </c>
       <c r="U12" t="n">
-        <v>4.665299</v>
+        <v>0.677481</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.946926</v>
+        <v>-0.269467</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.947035</v>
+        <v>1.344714</v>
       </c>
       <c r="X12" t="n">
-        <v>0.677481</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>-0.269467</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.344714</v>
-      </c>
-      <c r="AA12" t="n">
         <v>1.299867</v>
       </c>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.0009210000000000001</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.0009210000000000001</v>
+      </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.0009210000000000001</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AK12" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -1780,90 +1632,78 @@
         <v>101.09886</v>
       </c>
       <c r="I13" t="n">
-        <v>104.51426</v>
+        <v>5.179</v>
       </c>
       <c r="J13" t="n">
-        <v>5.179</v>
+        <v>5.1784</v>
       </c>
       <c r="K13" t="n">
-        <v>5.1784</v>
+        <v>5072711</v>
       </c>
       <c r="L13" t="n">
-        <v>5072711</v>
+        <v>2064183</v>
       </c>
       <c r="M13" t="n">
-        <v>2064183</v>
+        <v>3008528</v>
       </c>
       <c r="N13" t="n">
-        <v>3008528</v>
+        <v>2.9</v>
       </c>
       <c r="O13" t="n">
-        <v>2.9</v>
+        <v>3.78</v>
       </c>
       <c r="P13" t="n">
-        <v>1.62</v>
+        <v>28.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.78</v>
+        <v>339664</v>
       </c>
       <c r="R13" t="n">
-        <v>28.6</v>
+        <v>-0.328948</v>
       </c>
       <c r="S13" t="n">
-        <v>339664</v>
+        <v>-0.181173</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.328948</v>
+        <v>-0.181194</v>
       </c>
       <c r="U13" t="n">
-        <v>0.538824</v>
+        <v>1.469562</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.181173</v>
+        <v>0.837552</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.181194</v>
+        <v>1.907759</v>
       </c>
       <c r="X13" t="n">
-        <v>1.469562</v>
+        <v>-1.945422</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.837552</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.907759</v>
+        <v>8.58755</v>
       </c>
       <c r="AA13" t="n">
-        <v>-1.945422</v>
+        <v>8.825751</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.727061000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.58755</v>
+        <v>0.001523</v>
       </c>
       <c r="AD13" t="n">
-        <v>8.825751</v>
+        <v>0.001523</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.5</v>
+        <v>0.06</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.001523</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.001523</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK13" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -1893,90 +1733,78 @@
         <v>101.15209</v>
       </c>
       <c r="I14" t="n">
-        <v>101.19157</v>
+        <v>5.4066</v>
       </c>
       <c r="J14" t="n">
-        <v>5.4066</v>
+        <v>5.406</v>
       </c>
       <c r="K14" t="n">
-        <v>5.406</v>
+        <v>5164775</v>
       </c>
       <c r="L14" t="n">
-        <v>5164775</v>
+        <v>2109806</v>
       </c>
       <c r="M14" t="n">
-        <v>2109806</v>
+        <v>3054969</v>
       </c>
       <c r="N14" t="n">
-        <v>3054969</v>
+        <v>2.92</v>
       </c>
       <c r="O14" t="n">
-        <v>2.92</v>
+        <v>3.8</v>
       </c>
       <c r="P14" t="n">
-        <v>1.65</v>
+        <v>28.57</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.8</v>
+        <v>327580</v>
       </c>
       <c r="R14" t="n">
-        <v>28.57</v>
+        <v>0.052651</v>
       </c>
       <c r="S14" t="n">
-        <v>327580</v>
+        <v>4.394671</v>
       </c>
       <c r="T14" t="n">
-        <v>0.052651</v>
+        <v>4.39518</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.179174</v>
+        <v>1.814888</v>
       </c>
       <c r="V14" t="n">
-        <v>4.394671</v>
+        <v>2.210221</v>
       </c>
       <c r="W14" t="n">
-        <v>4.39518</v>
+        <v>1.543645</v>
       </c>
       <c r="X14" t="n">
-        <v>1.814888</v>
+        <v>-3.557633</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.210221</v>
+        <v>7.168596</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.543645</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="AA14" t="n">
-        <v>-3.557633</v>
+        <v>7.191214</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.168596</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.248760000000001</v>
+        <v>0.000228</v>
       </c>
       <c r="AD14" t="n">
-        <v>7.191214</v>
+        <v>0.000228</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.000228</v>
+        <v>0.02</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.000228</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK14" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -2006,90 +1834,78 @@
         <v>101.43094</v>
       </c>
       <c r="I15" t="n">
-        <v>100.07474</v>
+        <v>5.257</v>
       </c>
       <c r="J15" t="n">
-        <v>5.257</v>
+        <v>5.2564</v>
       </c>
       <c r="K15" t="n">
-        <v>5.2564</v>
+        <v>5215990</v>
       </c>
       <c r="L15" t="n">
-        <v>5215990</v>
+        <v>2105856</v>
       </c>
       <c r="M15" t="n">
-        <v>2105856</v>
+        <v>3110134</v>
       </c>
       <c r="N15" t="n">
-        <v>3110134</v>
+        <v>3.04</v>
       </c>
       <c r="O15" t="n">
-        <v>3.04</v>
+        <v>3.89</v>
       </c>
       <c r="P15" t="n">
-        <v>1.77</v>
+        <v>29.68</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.89</v>
+        <v>325546</v>
       </c>
       <c r="R15" t="n">
-        <v>29.68</v>
+        <v>0.275674</v>
       </c>
       <c r="S15" t="n">
-        <v>325546</v>
+        <v>-2.766988</v>
       </c>
       <c r="T15" t="n">
-        <v>0.275674</v>
+        <v>-2.767296</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.103679</v>
+        <v>0.991621</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.766988</v>
+        <v>-0.187221</v>
       </c>
       <c r="W15" t="n">
-        <v>-2.767296</v>
+        <v>1.805747</v>
       </c>
       <c r="X15" t="n">
-        <v>0.991621</v>
+        <v>-0.6209170000000001</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.187221</v>
+        <v>6.470016</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.805747</v>
+        <v>6.517038</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.6209170000000001</v>
+        <v>6.460076</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.470016</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>6.517038</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.460076</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK15" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -2119,90 +1935,78 @@
         <v>100.7113</v>
       </c>
       <c r="I16" t="n">
-        <v>99.15328</v>
+        <v>5.2941</v>
       </c>
       <c r="J16" t="n">
-        <v>5.2941</v>
+        <v>5.2935</v>
       </c>
       <c r="K16" t="n">
-        <v>5.2935</v>
+        <v>5285657</v>
       </c>
       <c r="L16" t="n">
-        <v>5285657</v>
+        <v>2130312</v>
       </c>
       <c r="M16" t="n">
-        <v>2130312</v>
+        <v>3155345</v>
       </c>
       <c r="N16" t="n">
-        <v>3155345</v>
+        <v>3.07</v>
       </c>
       <c r="O16" t="n">
-        <v>3.07</v>
+        <v>3.92</v>
       </c>
       <c r="P16" t="n">
-        <v>1.81</v>
+        <v>30.52</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.92</v>
+        <v>331505</v>
       </c>
       <c r="R16" t="n">
-        <v>30.52</v>
+        <v>-0.709488</v>
       </c>
       <c r="S16" t="n">
-        <v>331505</v>
+        <v>0.705726</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.709488</v>
+        <v>0.705806</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.920772</v>
+        <v>1.335643</v>
       </c>
       <c r="V16" t="n">
-        <v>0.705726</v>
+        <v>1.161333</v>
       </c>
       <c r="W16" t="n">
-        <v>0.705806</v>
+        <v>1.453667</v>
       </c>
       <c r="X16" t="n">
-        <v>1.335643</v>
+        <v>1.830463</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.161333</v>
+        <v>5.900488</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.453667</v>
+        <v>5.899363</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.830463</v>
+        <v>5.974439</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.900488</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>5.899363</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>5.974439</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AK16" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2232,90 +2036,78 @@
         <v>100.58566</v>
       </c>
       <c r="I17" t="n">
-        <v>99.97338999999999</v>
+        <v>5.2177</v>
       </c>
       <c r="J17" t="n">
-        <v>5.2177</v>
+        <v>5.2171</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2171</v>
+        <v>5366069</v>
       </c>
       <c r="L17" t="n">
-        <v>5366069</v>
+        <v>2178236</v>
       </c>
       <c r="M17" t="n">
-        <v>2178236</v>
+        <v>3187833</v>
       </c>
       <c r="N17" t="n">
-        <v>3187833</v>
+        <v>3.07</v>
       </c>
       <c r="O17" t="n">
-        <v>3.07</v>
+        <v>3.94</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8</v>
+        <v>29.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.94</v>
+        <v>324703</v>
       </c>
       <c r="R17" t="n">
-        <v>29.64</v>
+        <v>-0.124753</v>
       </c>
       <c r="S17" t="n">
-        <v>324703</v>
+        <v>-1.443116</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.124753</v>
+        <v>-1.443279</v>
       </c>
       <c r="U17" t="n">
-        <v>0.827113</v>
+        <v>1.521325</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.443116</v>
+        <v>2.249624</v>
       </c>
       <c r="W17" t="n">
-        <v>-1.443279</v>
+        <v>1.029618</v>
       </c>
       <c r="X17" t="n">
-        <v>1.521325</v>
+        <v>-2.051854</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.249624</v>
+        <v>5.784842</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.029618</v>
+        <v>5.458422</v>
       </c>
       <c r="AA17" t="n">
-        <v>-2.051854</v>
+        <v>5.932356</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.784842</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.458422</v>
+        <v>-0</v>
       </c>
       <c r="AD17" t="n">
-        <v>5.932356</v>
+        <v>-0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0</v>
+        <v>0.02</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK17" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -2345,90 +2137,78 @@
         <v>100.10937</v>
       </c>
       <c r="I18" t="n">
-        <v>95.09372999999999</v>
+        <v>5.0993</v>
       </c>
       <c r="J18" t="n">
-        <v>5.0993</v>
+        <v>5.0987</v>
       </c>
       <c r="K18" t="n">
-        <v>5.0987</v>
+        <v>5373231</v>
       </c>
       <c r="L18" t="n">
-        <v>5373231</v>
+        <v>2151399</v>
       </c>
       <c r="M18" t="n">
-        <v>2151399</v>
+        <v>3221831</v>
       </c>
       <c r="N18" t="n">
-        <v>3221831</v>
+        <v>3.24</v>
       </c>
       <c r="O18" t="n">
-        <v>3.24</v>
+        <v>4.11</v>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>30.54</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.11</v>
+        <v>331122</v>
       </c>
       <c r="R18" t="n">
-        <v>30.54</v>
+        <v>-0.473517</v>
       </c>
       <c r="S18" t="n">
-        <v>331122</v>
+        <v>-2.269199</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.473517</v>
+        <v>-2.26946</v>
       </c>
       <c r="U18" t="n">
-        <v>-4.880959</v>
+        <v>0.133468</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.269199</v>
+        <v>-1.232052</v>
       </c>
       <c r="W18" t="n">
-        <v>-2.26946</v>
+        <v>1.066493</v>
       </c>
       <c r="X18" t="n">
-        <v>0.133468</v>
+        <v>1.976883</v>
       </c>
       <c r="Y18" t="n">
-        <v>-1.232052</v>
+        <v>5.77432</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.066493</v>
+        <v>3.79089</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.976883</v>
+        <v>5.711379</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.77432</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.79089</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>5.711379</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AK18" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2458,90 +2238,78 @@
         <v>103.08344</v>
       </c>
       <c r="I19" t="n">
-        <v>98.65015</v>
+        <v>5.2078</v>
       </c>
       <c r="J19" t="n">
-        <v>5.2078</v>
+        <v>5.2072</v>
       </c>
       <c r="K19" t="n">
-        <v>5.2072</v>
+        <v>5370950</v>
       </c>
       <c r="L19" t="n">
-        <v>5370950</v>
+        <v>2136105</v>
       </c>
       <c r="M19" t="n">
-        <v>2136105</v>
+        <v>3234845</v>
       </c>
       <c r="N19" t="n">
-        <v>3234845</v>
+        <v>3.36</v>
       </c>
       <c r="O19" t="n">
-        <v>3.36</v>
+        <v>4.16</v>
       </c>
       <c r="P19" t="n">
-        <v>2.17</v>
+        <v>30.48</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.16</v>
+        <v>328098</v>
       </c>
       <c r="R19" t="n">
-        <v>30.48</v>
+        <v>2.970821</v>
       </c>
       <c r="S19" t="n">
-        <v>328098</v>
+        <v>2.127743</v>
       </c>
       <c r="T19" t="n">
-        <v>2.970821</v>
+        <v>2.127993</v>
       </c>
       <c r="U19" t="n">
-        <v>3.73991</v>
+        <v>-0.042451</v>
       </c>
       <c r="V19" t="n">
-        <v>2.127743</v>
+        <v>-0.710886</v>
       </c>
       <c r="W19" t="n">
-        <v>2.127993</v>
+        <v>0.403932</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.042451</v>
+        <v>-0.913259</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.710886</v>
+        <v>5.596302</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.403932</v>
+        <v>1.864495</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.913259</v>
+        <v>5.47065</v>
       </c>
       <c r="AB19" t="n">
-        <v>5.596302</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.864495</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>5.47065</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK19" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2571,90 +2339,78 @@
         <v>103.08526</v>
       </c>
       <c r="I20" t="n">
-        <v>110.62045</v>
+        <v>5.0804</v>
       </c>
       <c r="J20" t="n">
-        <v>5.0804</v>
+        <v>5.0798</v>
       </c>
       <c r="K20" t="n">
-        <v>5.0798</v>
+        <v>5424811</v>
       </c>
       <c r="L20" t="n">
-        <v>5424811</v>
+        <v>2154900</v>
       </c>
       <c r="M20" t="n">
-        <v>2154900</v>
+        <v>3269910</v>
       </c>
       <c r="N20" t="n">
-        <v>3269910</v>
+        <v>3.35</v>
       </c>
       <c r="O20" t="n">
-        <v>3.35</v>
+        <v>4.11</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>30.99</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.11</v>
+        <v>341158</v>
       </c>
       <c r="R20" t="n">
-        <v>30.99</v>
+        <v>0.001766</v>
       </c>
       <c r="S20" t="n">
-        <v>341158</v>
+        <v>-2.446331</v>
       </c>
       <c r="T20" t="n">
-        <v>0.001766</v>
+        <v>-2.446612</v>
       </c>
       <c r="U20" t="n">
-        <v>12.134092</v>
+        <v>1.002821</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.446331</v>
+        <v>0.879872</v>
       </c>
       <c r="W20" t="n">
-        <v>-2.446612</v>
+        <v>1.083978</v>
       </c>
       <c r="X20" t="n">
-        <v>1.002821</v>
+        <v>3.980518</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.879872</v>
+        <v>4.650694</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.083978</v>
+        <v>0.172427</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.980518</v>
+        <v>4.361088</v>
       </c>
       <c r="AB20" t="n">
-        <v>4.650694</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.172427</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.361088</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AK20" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2684,90 +2440,78 @@
         <v>103.96006</v>
       </c>
       <c r="I21" t="n">
-        <v>104.03539</v>
+        <v>5.0007</v>
       </c>
       <c r="J21" t="n">
-        <v>5.0007</v>
+        <v>5.0001</v>
       </c>
       <c r="K21" t="n">
-        <v>5.0001</v>
+        <v>5426307</v>
       </c>
       <c r="L21" t="n">
-        <v>5426307</v>
+        <v>2145000</v>
       </c>
       <c r="M21" t="n">
-        <v>2145000</v>
+        <v>3281308</v>
       </c>
       <c r="N21" t="n">
-        <v>3281308</v>
+        <v>3.54</v>
       </c>
       <c r="O21" t="n">
-        <v>3.54</v>
+        <v>4.26</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>31.62</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.26</v>
+        <v>345725</v>
       </c>
       <c r="R21" t="n">
-        <v>31.62</v>
+        <v>0.848618</v>
       </c>
       <c r="S21" t="n">
-        <v>345725</v>
+        <v>-1.568774</v>
       </c>
       <c r="T21" t="n">
-        <v>0.848618</v>
+        <v>-1.568959</v>
       </c>
       <c r="U21" t="n">
-        <v>-5.952841</v>
+        <v>0.027577</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.568774</v>
+        <v>-0.459418</v>
       </c>
       <c r="W21" t="n">
-        <v>-1.568959</v>
+        <v>0.348572</v>
       </c>
       <c r="X21" t="n">
-        <v>0.027577</v>
+        <v>1.338676</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.459418</v>
+        <v>4.184706</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.348572</v>
+        <v>-2.158772</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.338676</v>
+        <v>3.834324</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.184706</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.158772</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.834324</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AK21" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -2797,90 +2541,78 @@
         <v>102.40467</v>
       </c>
       <c r="I22" t="n">
-        <v>102.71665</v>
+        <v>5.0959</v>
       </c>
       <c r="J22" t="n">
-        <v>5.0959</v>
+        <v>5.0953</v>
       </c>
       <c r="K22" t="n">
-        <v>5.0953</v>
+        <v>5453708</v>
       </c>
       <c r="L22" t="n">
-        <v>5453708</v>
+        <v>2145530</v>
       </c>
       <c r="M22" t="n">
-        <v>2145530</v>
+        <v>3308178</v>
       </c>
       <c r="N22" t="n">
-        <v>3308178</v>
+        <v>3.65</v>
       </c>
       <c r="O22" t="n">
-        <v>3.65</v>
+        <v>4.35</v>
       </c>
       <c r="P22" t="n">
-        <v>2.58</v>
+        <v>31.63</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.35</v>
+        <v>343489</v>
       </c>
       <c r="R22" t="n">
-        <v>31.63</v>
+        <v>-1.496142</v>
       </c>
       <c r="S22" t="n">
-        <v>343489</v>
+        <v>1.903733</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.496142</v>
+        <v>1.903962</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.267588</v>
+        <v>0.504966</v>
       </c>
       <c r="V22" t="n">
-        <v>1.903733</v>
+        <v>0.024709</v>
       </c>
       <c r="W22" t="n">
-        <v>1.903962</v>
+        <v>0.818881</v>
       </c>
       <c r="X22" t="n">
-        <v>0.504966</v>
+        <v>-0.646757</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.024709</v>
+        <v>3.935832</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.818881</v>
+        <v>-4.45588</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0.646757</v>
+        <v>3.741292</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.935832</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>-4.45588</v>
+        <v>-0</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.741292</v>
+        <v>-0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0</v>
+        <v>0.09</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK22" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -2910,90 +2642,78 @@
         <v>102.4398</v>
       </c>
       <c r="I23" t="n">
-        <v>102.285</v>
+        <v>4.8192</v>
       </c>
       <c r="J23" t="n">
-        <v>4.8192</v>
+        <v>4.8186</v>
       </c>
       <c r="K23" t="n">
-        <v>4.8186</v>
+        <v>5479459</v>
       </c>
       <c r="L23" t="n">
-        <v>5479459</v>
+        <v>2169613</v>
       </c>
       <c r="M23" t="n">
-        <v>2169613</v>
+        <v>3309846</v>
       </c>
       <c r="N23" t="n">
-        <v>3309846</v>
+        <v>3.61</v>
       </c>
       <c r="O23" t="n">
-        <v>3.61</v>
+        <v>4.25</v>
       </c>
       <c r="P23" t="n">
-        <v>2.63</v>
+        <v>30.85</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.25</v>
+        <v>343620</v>
       </c>
       <c r="R23" t="n">
-        <v>30.85</v>
+        <v>0.034305</v>
       </c>
       <c r="S23" t="n">
-        <v>343620</v>
+        <v>-5.429855</v>
       </c>
       <c r="T23" t="n">
-        <v>0.034305</v>
+        <v>-5.430495</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.420234</v>
+        <v>0.472174</v>
       </c>
       <c r="V23" t="n">
-        <v>-5.429855</v>
+        <v>1.122473</v>
       </c>
       <c r="W23" t="n">
-        <v>-5.430495</v>
+        <v>0.050421</v>
       </c>
       <c r="X23" t="n">
-        <v>0.472174</v>
+        <v>0.038138</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.122473</v>
+        <v>3.161501</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.050421</v>
+        <v>-6.84947</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.038138</v>
+        <v>2.998957</v>
       </c>
       <c r="AB23" t="n">
-        <v>3.161501</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6.84947</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.998957</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AK23" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -3023,90 +2743,78 @@
         <v>102.89895</v>
       </c>
       <c r="I24" t="n">
-        <v>105.33914</v>
+        <v>4.7415</v>
       </c>
       <c r="J24" t="n">
-        <v>4.7415</v>
+        <v>4.7409</v>
       </c>
       <c r="K24" t="n">
-        <v>4.7409</v>
+        <v>5484871</v>
       </c>
       <c r="L24" t="n">
-        <v>5484871</v>
+        <v>2153541</v>
       </c>
       <c r="M24" t="n">
-        <v>2153541</v>
+        <v>3331330</v>
       </c>
       <c r="N24" t="n">
-        <v>3331330</v>
+        <v>3.63</v>
       </c>
       <c r="O24" t="n">
-        <v>3.63</v>
+        <v>4.22</v>
       </c>
       <c r="P24" t="n">
-        <v>2.73</v>
+        <v>30.43</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.22</v>
+        <v>345476</v>
       </c>
       <c r="R24" t="n">
-        <v>30.43</v>
+        <v>0.448214</v>
       </c>
       <c r="S24" t="n">
-        <v>345476</v>
+        <v>-1.612301</v>
       </c>
       <c r="T24" t="n">
-        <v>0.448214</v>
+        <v>-1.612502</v>
       </c>
       <c r="U24" t="n">
-        <v>2.985912</v>
+        <v>0.098769</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.612301</v>
+        <v>-0.740777</v>
       </c>
       <c r="W24" t="n">
-        <v>-1.612502</v>
+        <v>0.6490939999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>0.098769</v>
+        <v>0.5401319999999999</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.740777</v>
+        <v>3.992444</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.6490939999999999</v>
+        <v>-7.713954</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.5401319999999999</v>
+        <v>3.527423</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.992444</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>-7.713954</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.527423</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK24" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3136,90 +2844,78 @@
         <v>102.48797</v>
       </c>
       <c r="I25" t="n">
-        <v>106.05945</v>
+        <v>4.9219</v>
       </c>
       <c r="J25" t="n">
-        <v>4.9219</v>
+        <v>4.9213</v>
       </c>
       <c r="K25" t="n">
-        <v>4.9213</v>
+        <v>5559063</v>
       </c>
       <c r="L25" t="n">
-        <v>5559063</v>
+        <v>2172658</v>
       </c>
       <c r="M25" t="n">
-        <v>2172658</v>
+        <v>3386405</v>
       </c>
       <c r="N25" t="n">
-        <v>3386405</v>
+        <v>3.61</v>
       </c>
       <c r="O25" t="n">
-        <v>3.61</v>
+        <v>4.12</v>
       </c>
       <c r="P25" t="n">
-        <v>2.82</v>
+        <v>29.92</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.12</v>
+        <v>344177</v>
       </c>
       <c r="R25" t="n">
-        <v>29.92</v>
+        <v>-0.399402</v>
       </c>
       <c r="S25" t="n">
-        <v>344177</v>
+        <v>3.804703</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.399402</v>
+        <v>3.805185</v>
       </c>
       <c r="U25" t="n">
-        <v>0.683801</v>
+        <v>1.352666</v>
       </c>
       <c r="V25" t="n">
-        <v>3.804703</v>
+        <v>0.887701</v>
       </c>
       <c r="W25" t="n">
-        <v>3.805185</v>
+        <v>1.653244</v>
       </c>
       <c r="X25" t="n">
-        <v>1.352666</v>
+        <v>-0.376003</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.887701</v>
+        <v>4.608216</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.653244</v>
+        <v>-7.193509</v>
       </c>
       <c r="AA25" t="n">
-        <v>-0.376003</v>
+        <v>4.057054</v>
       </c>
       <c r="AB25" t="n">
-        <v>4.608216</v>
+        <v>-0.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>-7.193509</v>
+        <v>-0.001599</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.057054</v>
+        <v>-0.001599</v>
       </c>
       <c r="AE25" t="n">
-        <v>-0.5</v>
+        <v>-0.02</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.001599</v>
+        <v>-0.1</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.001599</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AK25" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -3249,90 +2945,78 @@
         <v>102.50227</v>
       </c>
       <c r="I26" t="n">
-        <v>101.76242</v>
+        <v>5.0076</v>
       </c>
       <c r="J26" t="n">
-        <v>5.0076</v>
+        <v>5.007</v>
       </c>
       <c r="K26" t="n">
-        <v>5.007</v>
+        <v>5625945</v>
       </c>
       <c r="L26" t="n">
-        <v>5625945</v>
+        <v>2215175</v>
       </c>
       <c r="M26" t="n">
-        <v>2215175</v>
+        <v>3410769</v>
       </c>
       <c r="N26" t="n">
-        <v>3410769</v>
+        <v>3.54</v>
       </c>
       <c r="O26" t="n">
-        <v>3.54</v>
+        <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.82</v>
+        <v>29.66</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>340324</v>
       </c>
       <c r="R26" t="n">
-        <v>29.66</v>
+        <v>0.013953</v>
       </c>
       <c r="S26" t="n">
-        <v>340324</v>
+        <v>1.741198</v>
       </c>
       <c r="T26" t="n">
-        <v>0.013953</v>
+        <v>1.74141</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.05153</v>
+        <v>1.203116</v>
       </c>
       <c r="V26" t="n">
-        <v>1.741198</v>
+        <v>1.956912</v>
       </c>
       <c r="W26" t="n">
-        <v>1.74141</v>
+        <v>0.719465</v>
       </c>
       <c r="X26" t="n">
-        <v>1.203116</v>
+        <v>-1.119482</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.956912</v>
+        <v>5.185235</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.719465</v>
+        <v>-5.956714</v>
       </c>
       <c r="AA26" t="n">
-        <v>-1.119482</v>
+        <v>4.505936</v>
       </c>
       <c r="AB26" t="n">
-        <v>5.185235</v>
+        <v>-0.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>-5.956714</v>
+        <v>-0.000768</v>
       </c>
       <c r="AD26" t="n">
-        <v>4.505936</v>
+        <v>-0.000768</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.5</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.000768</v>
+        <v>-0.12</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.000768</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK26" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -3362,90 +3046,78 @@
         <v>102.83037</v>
       </c>
       <c r="I27" t="n">
-        <v>101.92849</v>
+        <v>5.0575</v>
       </c>
       <c r="J27" t="n">
-        <v>5.0575</v>
+        <v>5.0569</v>
       </c>
       <c r="K27" t="n">
-        <v>5.0569</v>
+        <v>5653808</v>
       </c>
       <c r="L27" t="n">
-        <v>5653808</v>
+        <v>2204808</v>
       </c>
       <c r="M27" t="n">
-        <v>2204808</v>
+        <v>3449000</v>
       </c>
       <c r="N27" t="n">
-        <v>3449000</v>
+        <v>3.56</v>
       </c>
       <c r="O27" t="n">
-        <v>3.56</v>
+        <v>3.97</v>
       </c>
       <c r="P27" t="n">
-        <v>2.92</v>
+        <v>29.24</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.97</v>
+        <v>340247</v>
       </c>
       <c r="R27" t="n">
-        <v>29.24</v>
+        <v>0.32009</v>
       </c>
       <c r="S27" t="n">
-        <v>340247</v>
+        <v>0.996485</v>
       </c>
       <c r="T27" t="n">
-        <v>0.32009</v>
+        <v>0.996605</v>
       </c>
       <c r="U27" t="n">
-        <v>0.163194</v>
+        <v>0.495259</v>
       </c>
       <c r="V27" t="n">
-        <v>0.996485</v>
+        <v>-0.467999</v>
       </c>
       <c r="W27" t="n">
-        <v>0.996605</v>
+        <v>1.120891</v>
       </c>
       <c r="X27" t="n">
-        <v>0.495259</v>
+        <v>-0.022625</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.467999</v>
+        <v>4.819246</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.120891</v>
+        <v>-4.560737</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.022625</v>
+        <v>4.141877</v>
       </c>
       <c r="AB27" t="n">
-        <v>4.819246</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4.560737</v>
+        <v>-0.001143</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.141877</v>
+        <v>-0.001143</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.001143</v>
+        <v>-0.03</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.001143</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK27" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3475,90 +3147,78 @@
         <v>103.58799</v>
       </c>
       <c r="I28" t="n">
-        <v>101.68208</v>
+        <v>4.9355</v>
       </c>
       <c r="J28" t="n">
-        <v>4.9355</v>
+        <v>4.9349</v>
       </c>
       <c r="K28" t="n">
-        <v>4.9349</v>
+        <v>5711103</v>
       </c>
       <c r="L28" t="n">
-        <v>5711103</v>
+        <v>2220766</v>
       </c>
       <c r="M28" t="n">
-        <v>2220766</v>
+        <v>3490337</v>
       </c>
       <c r="N28" t="n">
-        <v>3490337</v>
+        <v>3.53</v>
       </c>
       <c r="O28" t="n">
-        <v>3.53</v>
+        <v>3.88</v>
       </c>
       <c r="P28" t="n">
-        <v>2.99</v>
+        <v>29.01</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.88</v>
+        <v>348406</v>
       </c>
       <c r="R28" t="n">
-        <v>29.01</v>
+        <v>0.7367669999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>348406</v>
+        <v>-2.412259</v>
       </c>
       <c r="T28" t="n">
-        <v>0.7367669999999999</v>
+        <v>-2.412545</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.241748</v>
+        <v>1.013388</v>
       </c>
       <c r="V28" t="n">
-        <v>-2.412259</v>
+        <v>0.723782</v>
       </c>
       <c r="W28" t="n">
-        <v>-2.412545</v>
+        <v>1.198521</v>
       </c>
       <c r="X28" t="n">
-        <v>1.013388</v>
+        <v>2.397964</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.723782</v>
+        <v>4.683537</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.198521</v>
+        <v>-3.457004</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.397964</v>
+        <v>3.851383</v>
       </c>
       <c r="AB28" t="n">
-        <v>4.683537</v>
+        <v>-0.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>-3.457004</v>
+        <v>-0.001678</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.851383</v>
+        <v>-0.001678</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.5</v>
+        <v>-0.03</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.001678</v>
+        <v>-0.09</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.001678</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="AK28" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -3588,90 +3248,78 @@
         <v>104.88262</v>
       </c>
       <c r="I29" t="n">
-        <v>101.68652</v>
+        <v>4.8413</v>
       </c>
       <c r="J29" t="n">
-        <v>4.8413</v>
+        <v>4.8407</v>
       </c>
       <c r="K29" t="n">
-        <v>4.8407</v>
+        <v>5805157</v>
       </c>
       <c r="L29" t="n">
-        <v>5805157</v>
+        <v>2283485</v>
       </c>
       <c r="M29" t="n">
-        <v>2283485</v>
+        <v>3521672</v>
       </c>
       <c r="N29" t="n">
-        <v>3521672</v>
+        <v>3.29</v>
       </c>
       <c r="O29" t="n">
-        <v>3.29</v>
+        <v>3.75</v>
       </c>
       <c r="P29" t="n">
-        <v>2.59</v>
+        <v>28.14</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.75</v>
+        <v>355034</v>
       </c>
       <c r="R29" t="n">
-        <v>28.14</v>
+        <v>1.249788</v>
       </c>
       <c r="S29" t="n">
-        <v>355034</v>
+        <v>-1.908621</v>
       </c>
       <c r="T29" t="n">
-        <v>1.249788</v>
+        <v>-1.908853</v>
       </c>
       <c r="U29" t="n">
-        <v>0.004367</v>
+        <v>1.646862</v>
       </c>
       <c r="V29" t="n">
-        <v>-1.908621</v>
+        <v>2.824206</v>
       </c>
       <c r="W29" t="n">
-        <v>-1.908853</v>
+        <v>0.897764</v>
       </c>
       <c r="X29" t="n">
-        <v>1.646862</v>
+        <v>1.902378</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.824206</v>
+        <v>4.621114</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.897764</v>
+        <v>-3.178284</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.902378</v>
+        <v>3.706988</v>
       </c>
       <c r="AB29" t="n">
-        <v>4.621114</v>
+        <v>-0.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.178284</v>
+        <v>-0.001064</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.706988</v>
+        <v>-0.001064</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.5</v>
+        <v>-0.24</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.001064</v>
+        <v>-0.13</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.001064</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="AK29" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3701,90 +3349,78 @@
         <v>104.47589</v>
       </c>
       <c r="I30" t="n">
-        <v>99.29136</v>
+        <v>4.9535</v>
       </c>
       <c r="J30" t="n">
-        <v>4.9535</v>
+        <v>4.9529</v>
       </c>
       <c r="K30" t="n">
-        <v>4.9529</v>
+        <v>5794707</v>
       </c>
       <c r="L30" t="n">
-        <v>5794707</v>
+        <v>2234362</v>
       </c>
       <c r="M30" t="n">
-        <v>2234362</v>
+        <v>3560345</v>
       </c>
       <c r="N30" t="n">
-        <v>3560345</v>
+        <v>3.38</v>
       </c>
       <c r="O30" t="n">
-        <v>3.38</v>
+        <v>3.76</v>
       </c>
       <c r="P30" t="n">
-        <v>2.77</v>
+        <v>28</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.76</v>
+        <v>355066</v>
       </c>
       <c r="R30" t="n">
-        <v>28</v>
+        <v>-0.387795</v>
       </c>
       <c r="S30" t="n">
-        <v>355066</v>
+        <v>2.317559</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.387795</v>
+        <v>2.317847</v>
       </c>
       <c r="U30" t="n">
-        <v>-2.355435</v>
+        <v>-0.180012</v>
       </c>
       <c r="V30" t="n">
-        <v>2.317559</v>
+        <v>-2.151229</v>
       </c>
       <c r="W30" t="n">
-        <v>2.317847</v>
+        <v>1.098143</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.180012</v>
+        <v>0.009013</v>
       </c>
       <c r="Y30" t="n">
-        <v>-2.151229</v>
+        <v>4.506637</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.098143</v>
+        <v>-3.31355</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.009013</v>
+        <v>3.820543</v>
       </c>
       <c r="AB30" t="n">
-        <v>4.506637</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>-3.31355</v>
+        <v>-0.000798</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.820543</v>
+        <v>-0.000798</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.000798</v>
+        <v>0.01</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.000798</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK30" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -3814,90 +3450,78 @@
         <v>104.67291</v>
       </c>
       <c r="I31" t="n">
-        <v>102.15158</v>
+        <v>4.9833</v>
       </c>
       <c r="J31" t="n">
-        <v>4.9833</v>
+        <v>4.9827</v>
       </c>
       <c r="K31" t="n">
-        <v>4.9827</v>
+        <v>5815954</v>
       </c>
       <c r="L31" t="n">
-        <v>5815954</v>
+        <v>2235302</v>
       </c>
       <c r="M31" t="n">
-        <v>2235302</v>
+        <v>3580652</v>
       </c>
       <c r="N31" t="n">
-        <v>3580652</v>
+        <v>3.38</v>
       </c>
       <c r="O31" t="n">
-        <v>3.38</v>
+        <v>3.76</v>
       </c>
       <c r="P31" t="n">
-        <v>2.76</v>
+        <v>27.85</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.76</v>
+        <v>352705</v>
       </c>
       <c r="R31" t="n">
-        <v>27.85</v>
+        <v>0.188579</v>
       </c>
       <c r="S31" t="n">
-        <v>352705</v>
+        <v>0.601595</v>
       </c>
       <c r="T31" t="n">
-        <v>0.188579</v>
+        <v>0.601668</v>
       </c>
       <c r="U31" t="n">
-        <v>2.880633</v>
+        <v>0.366662</v>
       </c>
       <c r="V31" t="n">
-        <v>0.601595</v>
+        <v>0.04207</v>
       </c>
       <c r="W31" t="n">
-        <v>0.601668</v>
+        <v>0.570366</v>
       </c>
       <c r="X31" t="n">
-        <v>0.366662</v>
+        <v>-0.664947</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.04207</v>
+        <v>4.496274</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.570366</v>
+        <v>-3.758575</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.664947</v>
+        <v>3.861754</v>
       </c>
       <c r="AB31" t="n">
-        <v>4.496274</v>
+        <v>-0.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>-3.758575</v>
+        <v>-0.001782</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.861754</v>
+        <v>-0.001782</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.001782</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.001782</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -3927,90 +3551,78 @@
         <v>104.68779</v>
       </c>
       <c r="I32" t="n">
-        <v>109.57244</v>
+        <v>4.9962</v>
       </c>
       <c r="J32" t="n">
-        <v>4.9962</v>
+        <v>4.9956</v>
       </c>
       <c r="K32" t="n">
-        <v>4.9956</v>
+        <v>5899742</v>
       </c>
       <c r="L32" t="n">
-        <v>5899742</v>
+        <v>2285775</v>
       </c>
       <c r="M32" t="n">
-        <v>2285775</v>
+        <v>3613967</v>
       </c>
       <c r="N32" t="n">
-        <v>3613967</v>
+        <v>3.33</v>
       </c>
       <c r="O32" t="n">
-        <v>3.33</v>
+        <v>3.71</v>
       </c>
       <c r="P32" t="n">
-        <v>2.71</v>
+        <v>28.14</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.71</v>
+        <v>355008</v>
       </c>
       <c r="R32" t="n">
-        <v>28.14</v>
+        <v>0.014216</v>
       </c>
       <c r="S32" t="n">
-        <v>355008</v>
+        <v>0.258865</v>
       </c>
       <c r="T32" t="n">
-        <v>0.014216</v>
+        <v>0.258896</v>
       </c>
       <c r="U32" t="n">
-        <v>7.264557</v>
+        <v>1.440658</v>
       </c>
       <c r="V32" t="n">
-        <v>0.258865</v>
+        <v>2.257995</v>
       </c>
       <c r="W32" t="n">
-        <v>0.258896</v>
+        <v>0.930417</v>
       </c>
       <c r="X32" t="n">
-        <v>1.440658</v>
+        <v>0.652954</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.257995</v>
+        <v>3.925596</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.930417</v>
+        <v>-4.25878</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.652954</v>
+        <v>3.397348</v>
       </c>
       <c r="AB32" t="n">
-        <v>3.925596</v>
+        <v>-0.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>-4.25878</v>
+        <v>-0.000537</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.397348</v>
+        <v>-0.000537</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.5</v>
+        <v>-0.05</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.000537</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AK32" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -4040,90 +3652,78 @@
         <v>104.6751</v>
       </c>
       <c r="I33" t="n">
-        <v>109.25226</v>
+        <v>5.1718</v>
       </c>
       <c r="J33" t="n">
-        <v>5.1718</v>
+        <v>5.1712</v>
       </c>
       <c r="K33" t="n">
-        <v>5.1712</v>
+        <v>5915538</v>
       </c>
       <c r="L33" t="n">
-        <v>5915538</v>
+        <v>2268879</v>
       </c>
       <c r="M33" t="n">
-        <v>2268879</v>
+        <v>3646659</v>
       </c>
       <c r="N33" t="n">
-        <v>3646659</v>
+        <v>3.37</v>
       </c>
       <c r="O33" t="n">
-        <v>3.37</v>
+        <v>3.75</v>
       </c>
       <c r="P33" t="n">
-        <v>2.76</v>
+        <v>27.86</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.75</v>
+        <v>351599</v>
       </c>
       <c r="R33" t="n">
-        <v>27.86</v>
+        <v>-0.012122</v>
       </c>
       <c r="S33" t="n">
-        <v>351599</v>
+        <v>3.514671</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.012122</v>
+        <v>3.515093</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.292209</v>
+        <v>0.267741</v>
       </c>
       <c r="V33" t="n">
-        <v>3.514671</v>
+        <v>-0.7391799999999999</v>
       </c>
       <c r="W33" t="n">
-        <v>3.515093</v>
+        <v>0.904602</v>
       </c>
       <c r="X33" t="n">
-        <v>0.267741</v>
+        <v>-0.96026</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.7391799999999999</v>
+        <v>3.688016</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.904602</v>
+        <v>-3.040871</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.96026</v>
+        <v>3.232784</v>
       </c>
       <c r="AB33" t="n">
-        <v>3.688016</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>-3.040871</v>
+        <v>-0.001252</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.232784</v>
+        <v>-0.001252</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.001252</v>
+        <v>0.04</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.001252</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK33" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -4153,90 +3753,78 @@
         <v>105.5521</v>
       </c>
       <c r="I34" t="n">
-        <v>104.71219</v>
+        <v>5.2416</v>
       </c>
       <c r="J34" t="n">
-        <v>5.2416</v>
+        <v>5.241</v>
       </c>
       <c r="K34" t="n">
-        <v>5.241</v>
+        <v>5953960</v>
       </c>
       <c r="L34" t="n">
-        <v>5953960</v>
+        <v>2278309</v>
       </c>
       <c r="M34" t="n">
-        <v>2278309</v>
+        <v>3675652</v>
       </c>
       <c r="N34" t="n">
-        <v>3675652</v>
+        <v>3.43</v>
       </c>
       <c r="O34" t="n">
-        <v>3.43</v>
+        <v>3.82</v>
       </c>
       <c r="P34" t="n">
-        <v>2.8</v>
+        <v>27.75</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.82</v>
+        <v>355560</v>
       </c>
       <c r="R34" t="n">
-        <v>27.75</v>
+        <v>0.837831</v>
       </c>
       <c r="S34" t="n">
-        <v>355560</v>
+        <v>1.349627</v>
       </c>
       <c r="T34" t="n">
-        <v>0.837831</v>
+        <v>1.349783</v>
       </c>
       <c r="U34" t="n">
-        <v>-4.155585</v>
+        <v>0.64951</v>
       </c>
       <c r="V34" t="n">
-        <v>1.349627</v>
+        <v>0.415624</v>
       </c>
       <c r="W34" t="n">
-        <v>1.349783</v>
+        <v>0.795057</v>
       </c>
       <c r="X34" t="n">
-        <v>0.64951</v>
+        <v>1.126567</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.415624</v>
+        <v>3.925952</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.795057</v>
+        <v>-0.344269</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.126567</v>
+        <v>3.335647</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.925952</v>
+        <v>-0.25</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.344269</v>
+        <v>-0.000684</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.335647</v>
+        <v>-0.000684</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.25</v>
+        <v>0.06</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.000684</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.000684</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK34" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -4266,90 +3854,78 @@
         <v>106.65779</v>
       </c>
       <c r="I35" t="n">
-        <v>105.87342</v>
+        <v>5.5589</v>
       </c>
       <c r="J35" t="n">
-        <v>5.5589</v>
+        <v>5.5583</v>
       </c>
       <c r="K35" t="n">
-        <v>5.5583</v>
+        <v>6041898</v>
       </c>
       <c r="L35" t="n">
-        <v>6041898</v>
+        <v>2336858</v>
       </c>
       <c r="M35" t="n">
-        <v>2336858</v>
+        <v>3705041</v>
       </c>
       <c r="N35" t="n">
-        <v>3705041</v>
+        <v>3.29</v>
       </c>
       <c r="O35" t="n">
-        <v>3.29</v>
+        <v>3.71</v>
       </c>
       <c r="P35" t="n">
-        <v>2.64</v>
+        <v>27.81</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.71</v>
+        <v>357827</v>
       </c>
       <c r="R35" t="n">
-        <v>27.81</v>
+        <v>1.04753</v>
       </c>
       <c r="S35" t="n">
-        <v>357827</v>
+        <v>6.053495</v>
       </c>
       <c r="T35" t="n">
-        <v>1.04753</v>
+        <v>6.054188</v>
       </c>
       <c r="U35" t="n">
-        <v>1.108973</v>
+        <v>1.476967</v>
       </c>
       <c r="V35" t="n">
-        <v>6.053495</v>
+        <v>2.569845</v>
       </c>
       <c r="W35" t="n">
-        <v>6.054188</v>
+        <v>0.799559</v>
       </c>
       <c r="X35" t="n">
-        <v>1.476967</v>
+        <v>0.637586</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.569845</v>
+        <v>4.227578</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.799559</v>
+        <v>2.440035</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.637586</v>
+        <v>3.697684</v>
       </c>
       <c r="AB35" t="n">
-        <v>4.227578</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.440035</v>
+        <v>-0.000214</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.697684</v>
+        <v>-0.000214</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.000214</v>
+        <v>-0.11</v>
       </c>
       <c r="AG35" t="n">
-        <v>-0.000214</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="AK35" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -4379,90 +3955,78 @@
         <v>107.01873</v>
       </c>
       <c r="I36" t="n">
-        <v>111.50432</v>
+        <v>5.6621</v>
       </c>
       <c r="J36" t="n">
-        <v>5.6621</v>
+        <v>5.6615</v>
       </c>
       <c r="K36" t="n">
-        <v>5.6615</v>
+        <v>6069205</v>
       </c>
       <c r="L36" t="n">
-        <v>6069205</v>
+        <v>2323362</v>
       </c>
       <c r="M36" t="n">
-        <v>2323362</v>
+        <v>3745844</v>
       </c>
       <c r="N36" t="n">
-        <v>3745844</v>
+        <v>3.3</v>
       </c>
       <c r="O36" t="n">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="P36" t="n">
-        <v>2.52</v>
+        <v>27.74</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.78</v>
+        <v>363282</v>
       </c>
       <c r="R36" t="n">
-        <v>27.74</v>
+        <v>0.338409</v>
       </c>
       <c r="S36" t="n">
-        <v>363282</v>
+        <v>1.856482</v>
       </c>
       <c r="T36" t="n">
-        <v>0.338409</v>
+        <v>1.856683</v>
       </c>
       <c r="U36" t="n">
-        <v>5.318521</v>
+        <v>0.451961</v>
       </c>
       <c r="V36" t="n">
-        <v>1.856482</v>
+        <v>-0.577528</v>
       </c>
       <c r="W36" t="n">
-        <v>1.856683</v>
+        <v>1.101283</v>
       </c>
       <c r="X36" t="n">
-        <v>0.451961</v>
+        <v>1.52448</v>
       </c>
       <c r="Y36" t="n">
-        <v>-0.577528</v>
+        <v>4.498245</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.101283</v>
+        <v>3.812368</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.52448</v>
+        <v>4.060953</v>
       </c>
       <c r="AB36" t="n">
-        <v>4.498245</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.812368</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>4.060953</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK36" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -4492,90 +4056,78 @@
         <v>107.16697</v>
       </c>
       <c r="I37" t="n">
-        <v>110.06264</v>
+        <v>5.6562</v>
       </c>
       <c r="J37" t="n">
-        <v>5.6562</v>
+        <v>5.6556</v>
       </c>
       <c r="K37" t="n">
-        <v>5.6556</v>
+        <v>6135298</v>
       </c>
       <c r="L37" t="n">
-        <v>6135298</v>
+        <v>2344397</v>
       </c>
       <c r="M37" t="n">
-        <v>2344397</v>
+        <v>3790900</v>
       </c>
       <c r="N37" t="n">
-        <v>3790900</v>
+        <v>3.33</v>
       </c>
       <c r="O37" t="n">
-        <v>3.33</v>
+        <v>3.82</v>
       </c>
       <c r="P37" t="n">
-        <v>2.55</v>
+        <v>27.59</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.82</v>
+        <v>369214</v>
       </c>
       <c r="R37" t="n">
-        <v>27.59</v>
+        <v>0.138518</v>
       </c>
       <c r="S37" t="n">
-        <v>369214</v>
+        <v>-0.104202</v>
       </c>
       <c r="T37" t="n">
-        <v>0.138518</v>
+        <v>-0.104213</v>
       </c>
       <c r="U37" t="n">
-        <v>-1.292936</v>
+        <v>1.088989</v>
       </c>
       <c r="V37" t="n">
-        <v>-0.104202</v>
+        <v>0.905369</v>
       </c>
       <c r="W37" t="n">
-        <v>-0.104213</v>
+        <v>1.202826</v>
       </c>
       <c r="X37" t="n">
-        <v>1.088989</v>
+        <v>1.632891</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.905369</v>
+        <v>4.237599</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.202826</v>
+        <v>4.259387</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.632891</v>
+        <v>3.707852</v>
       </c>
       <c r="AB37" t="n">
-        <v>4.237599</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>4.259387</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.707852</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK37" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4605,90 +4157,78 @@
         <v>108.02415</v>
       </c>
       <c r="I38" t="n">
-        <v>107.08272</v>
+        <v>5.4481</v>
       </c>
       <c r="J38" t="n">
-        <v>5.4481</v>
+        <v>5.4475</v>
       </c>
       <c r="K38" t="n">
-        <v>5.4475</v>
+        <v>6216528</v>
       </c>
       <c r="L38" t="n">
-        <v>6216528</v>
+        <v>2384828</v>
       </c>
       <c r="M38" t="n">
-        <v>2384828</v>
+        <v>3831700</v>
       </c>
       <c r="N38" t="n">
-        <v>3831700</v>
+        <v>3.34</v>
       </c>
       <c r="O38" t="n">
-        <v>3.34</v>
+        <v>3.83</v>
       </c>
       <c r="P38" t="n">
-        <v>2.56</v>
+        <v>27.49</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.83</v>
+        <v>372016</v>
       </c>
       <c r="R38" t="n">
-        <v>27.49</v>
+        <v>0.799855</v>
       </c>
       <c r="S38" t="n">
-        <v>372016</v>
+        <v>-3.679149</v>
       </c>
       <c r="T38" t="n">
-        <v>0.799855</v>
+        <v>-3.679539</v>
       </c>
       <c r="U38" t="n">
-        <v>-2.707476</v>
+        <v>1.323978</v>
       </c>
       <c r="V38" t="n">
-        <v>-3.679149</v>
+        <v>1.72458</v>
       </c>
       <c r="W38" t="n">
-        <v>-3.679539</v>
+        <v>1.076262</v>
       </c>
       <c r="X38" t="n">
-        <v>1.323978</v>
+        <v>0.7589089999999999</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.72458</v>
+        <v>4.42474</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.076262</v>
+        <v>4.519075</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.7589089999999999</v>
+        <v>4.091149</v>
       </c>
       <c r="AB38" t="n">
-        <v>4.42474</v>
+        <v>0.25</v>
       </c>
       <c r="AC38" t="n">
-        <v>4.519075</v>
+        <v>0.000342</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.091149</v>
+        <v>0.000342</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.25</v>
+        <v>0.01</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.000342</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK38" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -4718,90 +4258,78 @@
         <v>108.23273</v>
       </c>
       <c r="I39" t="n">
-        <v>109.17883</v>
+        <v>5.7779</v>
       </c>
       <c r="J39" t="n">
-        <v>5.7779</v>
+        <v>5.7773</v>
       </c>
       <c r="K39" t="n">
-        <v>5.7773</v>
+        <v>6275117</v>
       </c>
       <c r="L39" t="n">
-        <v>6275117</v>
+        <v>2397533</v>
       </c>
       <c r="M39" t="n">
-        <v>2397533</v>
+        <v>3877584</v>
       </c>
       <c r="N39" t="n">
-        <v>3877584</v>
+        <v>3.3</v>
       </c>
       <c r="O39" t="n">
-        <v>3.3</v>
+        <v>3.79</v>
       </c>
       <c r="P39" t="n">
-        <v>2.52</v>
+        <v>27.94</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.79</v>
+        <v>366096</v>
       </c>
       <c r="R39" t="n">
-        <v>27.94</v>
+        <v>0.193086</v>
       </c>
       <c r="S39" t="n">
-        <v>366096</v>
+        <v>6.053487</v>
       </c>
       <c r="T39" t="n">
-        <v>0.193086</v>
+        <v>6.054153</v>
       </c>
       <c r="U39" t="n">
-        <v>1.957468</v>
+        <v>0.9424709999999999</v>
       </c>
       <c r="V39" t="n">
-        <v>6.053487</v>
+        <v>0.532743</v>
       </c>
       <c r="W39" t="n">
-        <v>6.054153</v>
+        <v>1.197484</v>
       </c>
       <c r="X39" t="n">
-        <v>0.9424709999999999</v>
+        <v>-1.591329</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.532743</v>
+        <v>4.758099</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.197484</v>
+        <v>5.579866</v>
       </c>
       <c r="AA39" t="n">
-        <v>-1.591329</v>
+        <v>4.600584</v>
       </c>
       <c r="AB39" t="n">
-        <v>4.758099</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>5.579866</v>
+        <v>0.000556</v>
       </c>
       <c r="AD39" t="n">
-        <v>4.600584</v>
+        <v>0.000556</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.000556</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AK39" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -4831,90 +4359,78 @@
         <v>107.99539</v>
       </c>
       <c r="I40" t="n">
-        <v>105.48993</v>
+        <v>6.0535</v>
       </c>
       <c r="J40" t="n">
-        <v>6.0535</v>
+        <v>6.0529</v>
       </c>
       <c r="K40" t="n">
-        <v>6.0529</v>
+        <v>6365690</v>
       </c>
       <c r="L40" t="n">
-        <v>6365690</v>
+        <v>2436022</v>
       </c>
       <c r="M40" t="n">
-        <v>2436022</v>
+        <v>3929668</v>
       </c>
       <c r="N40" t="n">
-        <v>3929668</v>
+        <v>3.27</v>
       </c>
       <c r="O40" t="n">
-        <v>3.27</v>
+        <v>3.75</v>
       </c>
       <c r="P40" t="n">
-        <v>2.5</v>
+        <v>28.45</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.75</v>
+        <v>363003</v>
       </c>
       <c r="R40" t="n">
-        <v>28.45</v>
+        <v>-0.219287</v>
       </c>
       <c r="S40" t="n">
-        <v>363003</v>
+        <v>4.769899</v>
       </c>
       <c r="T40" t="n">
-        <v>-0.219287</v>
+        <v>4.770394</v>
       </c>
       <c r="U40" t="n">
-        <v>-3.378769</v>
+        <v>1.443368</v>
       </c>
       <c r="V40" t="n">
-        <v>4.769899</v>
+        <v>1.605359</v>
       </c>
       <c r="W40" t="n">
-        <v>4.770394</v>
+        <v>1.343208</v>
       </c>
       <c r="X40" t="n">
-        <v>1.443368</v>
+        <v>-0.8448600000000001</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.605359</v>
+        <v>4.873011</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.343208</v>
+        <v>6.325086</v>
       </c>
       <c r="AA40" t="n">
-        <v>-0.8448600000000001</v>
+        <v>4.840925</v>
       </c>
       <c r="AB40" t="n">
-        <v>4.873011</v>
+        <v>0.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>6.325086</v>
+        <v>0.001412</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.840925</v>
+        <v>0.001412</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.5</v>
+        <v>-0.03</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.001412</v>
+        <v>-0.04</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.001412</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AK40" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4944,90 +4460,78 @@
         <v>107.3722</v>
       </c>
       <c r="I41" t="n">
-        <v>104.15749</v>
+        <v>6.1923</v>
       </c>
       <c r="J41" t="n">
-        <v>6.1923</v>
+        <v>6.1917</v>
       </c>
       <c r="K41" t="n">
-        <v>6.1917</v>
+        <v>6464602</v>
       </c>
       <c r="L41" t="n">
-        <v>6464602</v>
+        <v>2499177</v>
       </c>
       <c r="M41" t="n">
-        <v>2499177</v>
+        <v>3965425</v>
       </c>
       <c r="N41" t="n">
-        <v>3965425</v>
+        <v>3.08</v>
       </c>
       <c r="O41" t="n">
-        <v>3.08</v>
+        <v>3.63</v>
       </c>
       <c r="P41" t="n">
-        <v>2.21</v>
+        <v>28.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.63</v>
+        <v>329730</v>
       </c>
       <c r="R41" t="n">
-        <v>28.5</v>
+        <v>-0.577052</v>
       </c>
       <c r="S41" t="n">
-        <v>329730</v>
+        <v>2.292888</v>
       </c>
       <c r="T41" t="n">
-        <v>-0.577052</v>
+        <v>2.293116</v>
       </c>
       <c r="U41" t="n">
-        <v>-1.263097</v>
+        <v>1.55383</v>
       </c>
       <c r="V41" t="n">
-        <v>2.292888</v>
+        <v>2.592546</v>
       </c>
       <c r="W41" t="n">
-        <v>2.293116</v>
+        <v>0.909924</v>
       </c>
       <c r="X41" t="n">
-        <v>1.55383</v>
+        <v>-9.166040000000001</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.592546</v>
+        <v>4.831296</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.909924</v>
+        <v>6.536174</v>
       </c>
       <c r="AA41" t="n">
-        <v>-9.166040000000001</v>
+        <v>4.767938</v>
       </c>
       <c r="AB41" t="n">
-        <v>4.831296</v>
+        <v>1</v>
       </c>
       <c r="AC41" t="n">
-        <v>6.536174</v>
+        <v>0.002578</v>
       </c>
       <c r="AD41" t="n">
-        <v>4.767938</v>
+        <v>0.002578</v>
       </c>
       <c r="AE41" t="n">
-        <v>1</v>
+        <v>-0.19</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.002578</v>
+        <v>-0.12</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.002578</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK41" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -5057,90 +4561,78 @@
         <v>108.10202</v>
       </c>
       <c r="I42" t="n">
-        <v>102.62361</v>
+        <v>5.8301</v>
       </c>
       <c r="J42" t="n">
-        <v>5.8301</v>
+        <v>5.8295</v>
       </c>
       <c r="K42" t="n">
-        <v>5.8295</v>
+        <v>6465016</v>
       </c>
       <c r="L42" t="n">
-        <v>6465016</v>
+        <v>2451957</v>
       </c>
       <c r="M42" t="n">
-        <v>2451957</v>
+        <v>4013059</v>
       </c>
       <c r="N42" t="n">
-        <v>4013059</v>
+        <v>3.34</v>
       </c>
       <c r="O42" t="n">
-        <v>3.34</v>
+        <v>3.89</v>
       </c>
       <c r="P42" t="n">
-        <v>2.43</v>
+        <v>29.88</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.89</v>
+        <v>328303</v>
       </c>
       <c r="R42" t="n">
-        <v>29.88</v>
+        <v>0.67971</v>
       </c>
       <c r="S42" t="n">
-        <v>328303</v>
+        <v>-5.8492</v>
       </c>
       <c r="T42" t="n">
-        <v>0.67971</v>
+        <v>-5.849767</v>
       </c>
       <c r="U42" t="n">
-        <v>-1.472655</v>
+        <v>0.006404</v>
       </c>
       <c r="V42" t="n">
-        <v>-5.8492</v>
+        <v>-1.889422</v>
       </c>
       <c r="W42" t="n">
-        <v>-5.849767</v>
+        <v>1.201233</v>
       </c>
       <c r="X42" t="n">
-        <v>0.006404</v>
+        <v>-0.432778</v>
       </c>
       <c r="Y42" t="n">
-        <v>-1.889422</v>
+        <v>4.559874</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.201233</v>
+        <v>6.749097</v>
       </c>
       <c r="AA42" t="n">
-        <v>-0.432778</v>
+        <v>4.174145</v>
       </c>
       <c r="AB42" t="n">
-        <v>4.559874</v>
+        <v>1</v>
       </c>
       <c r="AC42" t="n">
-        <v>6.749097</v>
+        <v>0.001675</v>
       </c>
       <c r="AD42" t="n">
-        <v>4.174145</v>
+        <v>0.001675</v>
       </c>
       <c r="AE42" t="n">
-        <v>1</v>
+        <v>0.26</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.001675</v>
+        <v>0.26</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.001675</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK42" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -5170,90 +4662,78 @@
         <v>108.64347</v>
       </c>
       <c r="I43" t="n">
-        <v>106.82695</v>
+        <v>5.8488</v>
       </c>
       <c r="J43" t="n">
-        <v>5.8488</v>
+        <v>5.8482</v>
       </c>
       <c r="K43" t="n">
-        <v>5.8482</v>
+        <v>6511444</v>
       </c>
       <c r="L43" t="n">
-        <v>6511444</v>
+        <v>2477151</v>
       </c>
       <c r="M43" t="n">
-        <v>2477151</v>
+        <v>4034293</v>
       </c>
       <c r="N43" t="n">
-        <v>4034293</v>
+        <v>3.41</v>
       </c>
       <c r="O43" t="n">
-        <v>3.41</v>
+        <v>3.96</v>
       </c>
       <c r="P43" t="n">
-        <v>2.52</v>
+        <v>30.53</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.96</v>
+        <v>332508</v>
       </c>
       <c r="R43" t="n">
-        <v>30.53</v>
+        <v>0.500869</v>
       </c>
       <c r="S43" t="n">
-        <v>332508</v>
+        <v>0.320749</v>
       </c>
       <c r="T43" t="n">
-        <v>0.500869</v>
+        <v>0.320782</v>
       </c>
       <c r="U43" t="n">
-        <v>4.09588</v>
+        <v>0.7181419999999999</v>
       </c>
       <c r="V43" t="n">
-        <v>0.320749</v>
+        <v>1.027506</v>
       </c>
       <c r="W43" t="n">
-        <v>0.320782</v>
+        <v>0.529123</v>
       </c>
       <c r="X43" t="n">
-        <v>0.7181419999999999</v>
+        <v>1.280829</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.027506</v>
+        <v>5.05763</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.529123</v>
+        <v>8.444549</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.280829</v>
+        <v>4.866504</v>
       </c>
       <c r="AB43" t="n">
-        <v>5.05763</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.444549</v>
+        <v>0.003204</v>
       </c>
       <c r="AD43" t="n">
-        <v>4.866504</v>
+        <v>0.003204</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.003204</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.003204</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK43" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -5283,90 +4763,78 @@
         <v>110.0586</v>
       </c>
       <c r="I44" t="n">
-        <v>114.02633</v>
+        <v>5.7422</v>
       </c>
       <c r="J44" t="n">
-        <v>5.7422</v>
+        <v>5.7416</v>
       </c>
       <c r="K44" t="n">
-        <v>5.7416</v>
+        <v>6576464</v>
       </c>
       <c r="L44" t="n">
-        <v>6576464</v>
+        <v>2498262</v>
       </c>
       <c r="M44" t="n">
-        <v>2498262</v>
+        <v>4078202</v>
       </c>
       <c r="N44" t="n">
-        <v>4078202</v>
+        <v>3.44</v>
       </c>
       <c r="O44" t="n">
-        <v>3.44</v>
+        <v>4.03</v>
       </c>
       <c r="P44" t="n">
-        <v>2.49</v>
+        <v>31.34</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.03</v>
+        <v>336157</v>
       </c>
       <c r="R44" t="n">
-        <v>31.34</v>
+        <v>1.302545</v>
       </c>
       <c r="S44" t="n">
-        <v>336157</v>
+        <v>-1.822596</v>
       </c>
       <c r="T44" t="n">
-        <v>1.302545</v>
+        <v>-1.822783</v>
       </c>
       <c r="U44" t="n">
-        <v>6.739292</v>
+        <v>0.99855</v>
       </c>
       <c r="V44" t="n">
-        <v>-1.822596</v>
+        <v>0.852229</v>
       </c>
       <c r="W44" t="n">
-        <v>-1.822783</v>
+        <v>1.088394</v>
       </c>
       <c r="X44" t="n">
-        <v>0.99855</v>
+        <v>1.097417</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.852229</v>
+        <v>5.47719</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.088394</v>
+        <v>8.586193</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.097417</v>
+        <v>5.201441</v>
       </c>
       <c r="AB44" t="n">
-        <v>5.47719</v>
+        <v>1</v>
       </c>
       <c r="AC44" t="n">
-        <v>8.586193</v>
+        <v>0.001471</v>
       </c>
       <c r="AD44" t="n">
-        <v>5.201441</v>
+        <v>0.001471</v>
       </c>
       <c r="AE44" t="n">
-        <v>1</v>
+        <v>0.03</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.001471</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.001471</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK44" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -5396,90 +4864,78 @@
         <v>109.59971</v>
       </c>
       <c r="I45" t="n">
-        <v>112.58856</v>
+        <v>5.6608</v>
       </c>
       <c r="J45" t="n">
-        <v>5.6608</v>
+        <v>5.6602</v>
       </c>
       <c r="K45" t="n">
-        <v>5.6602</v>
+        <v>6623948</v>
       </c>
       <c r="L45" t="n">
-        <v>6623948</v>
+        <v>2512426</v>
       </c>
       <c r="M45" t="n">
-        <v>2512426</v>
+        <v>4111522</v>
       </c>
       <c r="N45" t="n">
-        <v>4111522</v>
+        <v>3.67</v>
       </c>
       <c r="O45" t="n">
-        <v>3.67</v>
+        <v>4.25</v>
       </c>
       <c r="P45" t="n">
-        <v>2.72</v>
+        <v>31.63</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.25</v>
+        <v>340789</v>
       </c>
       <c r="R45" t="n">
-        <v>31.63</v>
+        <v>-0.416951</v>
       </c>
       <c r="S45" t="n">
-        <v>340789</v>
+        <v>-1.417575</v>
       </c>
       <c r="T45" t="n">
-        <v>-0.416951</v>
+        <v>-1.417723</v>
       </c>
       <c r="U45" t="n">
-        <v>-1.260911</v>
+        <v>0.722029</v>
       </c>
       <c r="V45" t="n">
-        <v>-1.417575</v>
+        <v>0.566954</v>
       </c>
       <c r="W45" t="n">
-        <v>-1.417723</v>
+        <v>0.8170269999999999</v>
       </c>
       <c r="X45" t="n">
-        <v>0.722029</v>
+        <v>1.377928</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.566954</v>
+        <v>5.529729</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.8170269999999999</v>
+        <v>8.510418</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.377928</v>
+        <v>5.316736</v>
       </c>
       <c r="AB45" t="n">
-        <v>5.529729</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.510418</v>
+        <v>0.002023</v>
       </c>
       <c r="AD45" t="n">
-        <v>5.316736</v>
+        <v>0.002023</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.002023</v>
+        <v>0.22</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AK45" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -5509,90 +4965,78 @@
         <v>108.80425</v>
       </c>
       <c r="I46" t="n">
-        <v>108.55662</v>
+        <v>5.7087</v>
       </c>
       <c r="J46" t="n">
-        <v>5.7087</v>
+        <v>5.7081</v>
       </c>
       <c r="K46" t="n">
-        <v>5.7081</v>
+        <v>6666287</v>
       </c>
       <c r="L46" t="n">
-        <v>6666287</v>
+        <v>2532708</v>
       </c>
       <c r="M46" t="n">
-        <v>2532708</v>
+        <v>4133579</v>
       </c>
       <c r="N46" t="n">
-        <v>4133579</v>
+        <v>3.72</v>
       </c>
       <c r="O46" t="n">
-        <v>3.72</v>
+        <v>4.36</v>
       </c>
       <c r="P46" t="n">
-        <v>2.67</v>
+        <v>31.7</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.36</v>
+        <v>341459</v>
       </c>
       <c r="R46" t="n">
-        <v>31.7</v>
+        <v>-0.725787</v>
       </c>
       <c r="S46" t="n">
-        <v>341459</v>
+        <v>0.84617</v>
       </c>
       <c r="T46" t="n">
-        <v>-0.725787</v>
+        <v>0.84626</v>
       </c>
       <c r="U46" t="n">
-        <v>-3.581128</v>
+        <v>0.639181</v>
       </c>
       <c r="V46" t="n">
-        <v>0.84617</v>
+        <v>0.807268</v>
       </c>
       <c r="W46" t="n">
-        <v>0.84626</v>
+        <v>0.5364679999999999</v>
       </c>
       <c r="X46" t="n">
-        <v>0.639181</v>
+        <v>0.196603</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.807268</v>
+        <v>5.319636</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.5364679999999999</v>
+        <v>7.026183</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.196603</v>
+        <v>5.201418</v>
       </c>
       <c r="AB46" t="n">
-        <v>5.319636</v>
+        <v>0.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>7.026183</v>
+        <v>0.001405</v>
       </c>
       <c r="AD46" t="n">
-        <v>5.201418</v>
+        <v>0.001405</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.001405</v>
+        <v>0.11</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.001405</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK46" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5622,90 +5066,78 @@
         <v>108.90168</v>
       </c>
       <c r="I47" t="n">
-        <v>107.36878</v>
+        <v>5.4571</v>
       </c>
       <c r="J47" t="n">
-        <v>5.4571</v>
+        <v>5.4565</v>
       </c>
       <c r="K47" t="n">
-        <v>5.4565</v>
+        <v>6703663</v>
       </c>
       <c r="L47" t="n">
-        <v>6703663</v>
+        <v>2547693</v>
       </c>
       <c r="M47" t="n">
-        <v>2547693</v>
+        <v>4155970</v>
       </c>
       <c r="N47" t="n">
-        <v>4155970</v>
+        <v>3.75</v>
       </c>
       <c r="O47" t="n">
-        <v>3.75</v>
+        <v>4.41</v>
       </c>
       <c r="P47" t="n">
-        <v>2.67</v>
+        <v>31.85</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.41</v>
+        <v>344440</v>
       </c>
       <c r="R47" t="n">
-        <v>31.85</v>
+        <v>0.089546</v>
       </c>
       <c r="S47" t="n">
-        <v>344440</v>
+        <v>-4.407308</v>
       </c>
       <c r="T47" t="n">
-        <v>0.089546</v>
+        <v>-4.407771</v>
       </c>
       <c r="U47" t="n">
-        <v>-1.094212</v>
+        <v>0.5606719999999999</v>
       </c>
       <c r="V47" t="n">
-        <v>-4.407308</v>
+        <v>0.591659</v>
       </c>
       <c r="W47" t="n">
-        <v>-4.407771</v>
+        <v>0.541686</v>
       </c>
       <c r="X47" t="n">
-        <v>0.5606719999999999</v>
+        <v>0.873018</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.591659</v>
+        <v>5.351165</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.541686</v>
+        <v>4.393261</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.873018</v>
+        <v>5.18043</v>
       </c>
       <c r="AB47" t="n">
-        <v>5.351165</v>
+        <v>0.25</v>
       </c>
       <c r="AC47" t="n">
-        <v>4.393261</v>
+        <v>0.000633</v>
       </c>
       <c r="AD47" t="n">
-        <v>5.18043</v>
+        <v>0.000633</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.25</v>
+        <v>0.03</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.000633</v>
+        <v>0.05</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.000633</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK47" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5735,90 +5167,78 @@
         <v>108.39998</v>
       </c>
       <c r="I48" t="n">
-        <v>113.10359</v>
+        <v>5.6021</v>
       </c>
       <c r="J48" t="n">
-        <v>5.6021</v>
+        <v>5.6015</v>
       </c>
       <c r="K48" t="n">
-        <v>5.6015</v>
+        <v>6733209</v>
       </c>
       <c r="L48" t="n">
-        <v>6733209</v>
+        <v>2544400</v>
       </c>
       <c r="M48" t="n">
-        <v>2544400</v>
+        <v>4188808</v>
       </c>
       <c r="N48" t="n">
-        <v>4188808</v>
+        <v>3.96</v>
       </c>
       <c r="O48" t="n">
-        <v>3.96</v>
+        <v>4.66</v>
       </c>
       <c r="P48" t="n">
-        <v>2.79</v>
+        <v>31.75</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.66</v>
+        <v>345111</v>
       </c>
       <c r="R48" t="n">
-        <v>31.75</v>
+        <v>-0.460691</v>
       </c>
       <c r="S48" t="n">
-        <v>345111</v>
+        <v>2.657089</v>
       </c>
       <c r="T48" t="n">
-        <v>-0.460691</v>
+        <v>2.657381</v>
       </c>
       <c r="U48" t="n">
-        <v>5.341227</v>
+        <v>0.440744</v>
       </c>
       <c r="V48" t="n">
-        <v>2.657089</v>
+        <v>-0.129254</v>
       </c>
       <c r="W48" t="n">
-        <v>2.657381</v>
+        <v>0.79014</v>
       </c>
       <c r="X48" t="n">
-        <v>0.440744</v>
+        <v>0.194809</v>
       </c>
       <c r="Y48" t="n">
-        <v>-0.129254</v>
+        <v>5.225222</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.79014</v>
+        <v>2.961368</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.194809</v>
+        <v>5.127976</v>
       </c>
       <c r="AB48" t="n">
-        <v>5.225222</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.961368</v>
+        <v>0.000562</v>
       </c>
       <c r="AD48" t="n">
-        <v>5.127976</v>
+        <v>0.000562</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.000562</v>
+        <v>0.25</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.000562</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK48" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -5848,90 +5268,78 @@
         <v>108.79892</v>
       </c>
       <c r="I49" t="n">
-        <v>110.38013</v>
+        <v>5.4264</v>
       </c>
       <c r="J49" t="n">
-        <v>5.4264</v>
+        <v>5.4258</v>
       </c>
       <c r="K49" t="n">
-        <v>5.4258</v>
+        <v>6774436</v>
       </c>
       <c r="L49" t="n">
-        <v>6774436</v>
+        <v>2546265</v>
       </c>
       <c r="M49" t="n">
-        <v>2546265</v>
+        <v>4228171</v>
       </c>
       <c r="N49" t="n">
-        <v>4228171</v>
+        <v>4.14</v>
       </c>
       <c r="O49" t="n">
-        <v>4.14</v>
+        <v>4.92</v>
       </c>
       <c r="P49" t="n">
-        <v>2.85</v>
+        <v>31.87</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.92</v>
+        <v>350767</v>
       </c>
       <c r="R49" t="n">
-        <v>31.87</v>
+        <v>0.368026</v>
       </c>
       <c r="S49" t="n">
-        <v>350767</v>
+        <v>-3.136324</v>
       </c>
       <c r="T49" t="n">
-        <v>0.368026</v>
+        <v>-3.13666</v>
       </c>
       <c r="U49" t="n">
-        <v>-2.407934</v>
+        <v>0.612293</v>
       </c>
       <c r="V49" t="n">
-        <v>-3.136324</v>
+        <v>0.073298</v>
       </c>
       <c r="W49" t="n">
-        <v>-3.13666</v>
+        <v>0.9397180000000001</v>
       </c>
       <c r="X49" t="n">
-        <v>0.612293</v>
+        <v>1.638893</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.073298</v>
+        <v>5.130501</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.9397180000000001</v>
+        <v>3.033233</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.638893</v>
+        <v>5.054283</v>
       </c>
       <c r="AB49" t="n">
-        <v>5.130501</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.033233</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>5.054283</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK49" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5961,90 +5369,78 @@
         <v>108.7209</v>
       </c>
       <c r="I50" t="n">
-        <v>109.48882</v>
+        <v>5.3186</v>
       </c>
       <c r="J50" t="n">
-        <v>5.3186</v>
+        <v>5.318</v>
       </c>
       <c r="K50" t="n">
-        <v>5.318</v>
+        <v>6852705</v>
       </c>
       <c r="L50" t="n">
-        <v>6852705</v>
+        <v>2589817</v>
       </c>
       <c r="M50" t="n">
-        <v>2589817</v>
+        <v>4262888</v>
       </c>
       <c r="N50" t="n">
-        <v>4262888</v>
+        <v>4.09</v>
       </c>
       <c r="O50" t="n">
-        <v>4.09</v>
+        <v>4.89</v>
       </c>
       <c r="P50" t="n">
-        <v>2.77</v>
+        <v>31.47</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.89</v>
+        <v>356582</v>
       </c>
       <c r="R50" t="n">
-        <v>31.47</v>
+        <v>-0.07171</v>
       </c>
       <c r="S50" t="n">
-        <v>356582</v>
+        <v>-1.986584</v>
       </c>
       <c r="T50" t="n">
-        <v>-0.07171</v>
+        <v>-1.986804</v>
       </c>
       <c r="U50" t="n">
-        <v>-0.807491</v>
+        <v>1.155358</v>
       </c>
       <c r="V50" t="n">
-        <v>-1.986584</v>
+        <v>1.710427</v>
       </c>
       <c r="W50" t="n">
-        <v>-1.986804</v>
+        <v>0.821088</v>
       </c>
       <c r="X50" t="n">
-        <v>1.155358</v>
+        <v>1.657796</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.710427</v>
+        <v>5.172369</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.821088</v>
+        <v>2.828436</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.657796</v>
+        <v>5.096104</v>
       </c>
       <c r="AB50" t="n">
-        <v>5.172369</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.828436</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>5.096104</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK50" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -6074,90 +5470,78 @@
         <v>108.73364</v>
       </c>
       <c r="I51" t="n">
-        <v>110.06407</v>
+        <v>5.3843</v>
       </c>
       <c r="J51" t="n">
-        <v>5.3843</v>
+        <v>5.3837</v>
       </c>
       <c r="K51" t="n">
-        <v>5.3837</v>
+        <v>6923886</v>
       </c>
       <c r="L51" t="n">
-        <v>6923886</v>
+        <v>2597630</v>
       </c>
       <c r="M51" t="n">
-        <v>2597630</v>
+        <v>4326256</v>
       </c>
       <c r="N51" t="n">
-        <v>4326256</v>
+        <v>4.18</v>
       </c>
       <c r="O51" t="n">
-        <v>4.18</v>
+        <v>4.99</v>
       </c>
       <c r="P51" t="n">
-        <v>2.82</v>
+        <v>32.04</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.99</v>
+        <v>357103</v>
       </c>
       <c r="R51" t="n">
-        <v>32.04</v>
+        <v>0.011718</v>
       </c>
       <c r="S51" t="n">
-        <v>357103</v>
+        <v>1.235287</v>
       </c>
       <c r="T51" t="n">
-        <v>0.011718</v>
+        <v>1.235427</v>
       </c>
       <c r="U51" t="n">
-        <v>0.525396</v>
+        <v>1.038729</v>
       </c>
       <c r="V51" t="n">
-        <v>1.235287</v>
+        <v>0.301682</v>
       </c>
       <c r="W51" t="n">
-        <v>1.235427</v>
+        <v>1.486504</v>
       </c>
       <c r="X51" t="n">
-        <v>1.038729</v>
+        <v>0.146109</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.301682</v>
+        <v>4.680811</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.486504</v>
+        <v>0.924206</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.146109</v>
+        <v>4.490243</v>
       </c>
       <c r="AB51" t="n">
-        <v>4.680811</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.924206</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>4.490243</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK51" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -6187,90 +5571,78 @@
         <v>109.24151</v>
       </c>
       <c r="I52" t="n">
-        <v>106.59541</v>
+        <v>5.3338</v>
       </c>
       <c r="J52" t="n">
-        <v>5.3338</v>
+        <v>5.3332</v>
       </c>
       <c r="K52" t="n">
-        <v>5.3332</v>
+        <v>7004223</v>
       </c>
       <c r="L52" t="n">
-        <v>7004223</v>
+        <v>2616902</v>
       </c>
       <c r="M52" t="n">
-        <v>2616902</v>
+        <v>4387321</v>
       </c>
       <c r="N52" t="n">
-        <v>4387321</v>
+        <v>4.24</v>
       </c>
       <c r="O52" t="n">
-        <v>4.24</v>
+        <v>5.12</v>
       </c>
       <c r="P52" t="n">
-        <v>2.75</v>
+        <v>32.2</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.12</v>
+        <v>360578</v>
       </c>
       <c r="R52" t="n">
-        <v>32.2</v>
+        <v>0.467077</v>
       </c>
       <c r="S52" t="n">
-        <v>360578</v>
+        <v>-0.937912</v>
       </c>
       <c r="T52" t="n">
-        <v>0.467077</v>
+        <v>-0.938017</v>
       </c>
       <c r="U52" t="n">
-        <v>-3.151492</v>
+        <v>1.160288</v>
       </c>
       <c r="V52" t="n">
-        <v>-0.937912</v>
+        <v>0.741907</v>
       </c>
       <c r="W52" t="n">
-        <v>-0.938017</v>
+        <v>1.411498</v>
       </c>
       <c r="X52" t="n">
-        <v>1.160288</v>
+        <v>0.973109</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.741907</v>
+        <v>4.461836</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.411498</v>
+        <v>-0.101973</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.973109</v>
+        <v>4.177803</v>
       </c>
       <c r="AB52" t="n">
-        <v>4.461836</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>-0.101973</v>
+        <v>-0</v>
       </c>
       <c r="AD52" t="n">
-        <v>4.177803</v>
+        <v>-0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AF52" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="AG52" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AK52" t="n">
         <v>0.16</v>
       </c>
     </row>
@@ -6300,90 +5672,78 @@
         <v>109.46142</v>
       </c>
       <c r="I53" t="n">
-        <v>107.19319</v>
+        <v>5.5024</v>
       </c>
       <c r="J53" t="n">
-        <v>5.5024</v>
+        <v>5.5018</v>
       </c>
       <c r="K53" t="n">
-        <v>5.5018</v>
+        <v>7137252</v>
       </c>
       <c r="L53" t="n">
-        <v>7137252</v>
+        <v>2701735</v>
       </c>
       <c r="M53" t="n">
-        <v>2701735</v>
+        <v>4435517</v>
       </c>
       <c r="N53" t="n">
-        <v>4435517</v>
+        <v>4.2</v>
       </c>
       <c r="O53" t="n">
-        <v>4.2</v>
+        <v>5.12</v>
       </c>
       <c r="P53" t="n">
-        <v>2.7</v>
+        <v>31.87</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.12</v>
+        <v>358234</v>
       </c>
       <c r="R53" t="n">
-        <v>31.87</v>
+        <v>0.201306</v>
       </c>
       <c r="S53" t="n">
-        <v>358234</v>
+        <v>3.160973</v>
       </c>
       <c r="T53" t="n">
-        <v>0.201306</v>
+        <v>3.161329</v>
       </c>
       <c r="U53" t="n">
-        <v>0.560793</v>
+        <v>1.899268</v>
       </c>
       <c r="V53" t="n">
-        <v>3.160973</v>
+        <v>3.241734</v>
       </c>
       <c r="W53" t="n">
-        <v>3.161329</v>
+        <v>1.098529</v>
       </c>
       <c r="X53" t="n">
-        <v>1.899268</v>
+        <v>-0.650067</v>
       </c>
       <c r="Y53" t="n">
-        <v>3.241734</v>
+        <v>4.264385</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.098529</v>
+        <v>-1.042167</v>
       </c>
       <c r="AA53" t="n">
-        <v>-0.650067</v>
+        <v>3.897866</v>
       </c>
       <c r="AB53" t="n">
-        <v>4.264385</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>-1.042167</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>3.897866</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="AF53" t="n">
         <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -6413,90 +5773,78 @@
         <v>110.07661</v>
       </c>
       <c r="I54" t="n">
-        <v>103.78191</v>
+        <v>5.2301</v>
       </c>
       <c r="J54" t="n">
-        <v>5.2301</v>
+        <v>5.2295</v>
       </c>
       <c r="K54" t="n">
-        <v>5.2295</v>
+        <v>7130762</v>
       </c>
       <c r="L54" t="n">
-        <v>7130762</v>
+        <v>2654220</v>
       </c>
       <c r="M54" t="n">
-        <v>2654220</v>
+        <v>4476542</v>
       </c>
       <c r="N54" t="n">
-        <v>4476542</v>
+        <v>4.44</v>
       </c>
       <c r="O54" t="n">
-        <v>4.44</v>
+        <v>5.38</v>
       </c>
       <c r="P54" t="n">
-        <v>2.87</v>
+        <v>32.45</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.38</v>
+        <v>364367</v>
       </c>
       <c r="R54" t="n">
-        <v>32.45</v>
+        <v>0.562015</v>
       </c>
       <c r="S54" t="n">
-        <v>364367</v>
+        <v>-4.94875</v>
       </c>
       <c r="T54" t="n">
-        <v>0.562015</v>
+        <v>-4.949289</v>
       </c>
       <c r="U54" t="n">
-        <v>-3.182366</v>
+        <v>-0.090931</v>
       </c>
       <c r="V54" t="n">
-        <v>-4.94875</v>
+        <v>-1.758685</v>
       </c>
       <c r="W54" t="n">
-        <v>-4.949289</v>
+        <v>0.92492</v>
       </c>
       <c r="X54" t="n">
-        <v>-0.090931</v>
+        <v>1.712009</v>
       </c>
       <c r="Y54" t="n">
-        <v>-1.758685</v>
+        <v>4.441351</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.92492</v>
+        <v>-0.903999</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.712009</v>
+        <v>4.303068</v>
       </c>
       <c r="AB54" t="n">
-        <v>4.441351</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>-0.903999</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>4.303068</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK54" t="n">
         <v>0.58</v>
       </c>
     </row>
@@ -6526,90 +5874,78 @@
         <v>110.77581</v>
       </c>
       <c r="I55" t="n">
-        <v>106.77083</v>
+        <v>5.1495</v>
       </c>
       <c r="J55" t="n">
-        <v>5.1495</v>
+        <v>5.1489</v>
       </c>
       <c r="K55" t="n">
-        <v>5.1489</v>
+        <v>7157783</v>
       </c>
       <c r="L55" t="n">
-        <v>7157783</v>
+        <v>2656484</v>
       </c>
       <c r="M55" t="n">
-        <v>2656484</v>
+        <v>4501299</v>
       </c>
       <c r="N55" t="n">
-        <v>4501299</v>
+        <v>4.64</v>
       </c>
       <c r="O55" t="n">
-        <v>4.64</v>
+        <v>5.56</v>
       </c>
       <c r="P55" t="n">
-        <v>3.07</v>
+        <v>32.63</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.56</v>
+        <v>371074</v>
       </c>
       <c r="R55" t="n">
-        <v>32.63</v>
+        <v>0.635194</v>
       </c>
       <c r="S55" t="n">
-        <v>371074</v>
+        <v>-1.54108</v>
       </c>
       <c r="T55" t="n">
-        <v>0.635194</v>
+        <v>-1.541256</v>
       </c>
       <c r="U55" t="n">
-        <v>2.880001</v>
+        <v>0.378936</v>
       </c>
       <c r="V55" t="n">
-        <v>-1.54108</v>
+        <v>0.085298</v>
       </c>
       <c r="W55" t="n">
-        <v>-1.541256</v>
+        <v>0.553038</v>
       </c>
       <c r="X55" t="n">
-        <v>0.378936</v>
+        <v>1.840727</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.085298</v>
+        <v>3.812497</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.553038</v>
+        <v>-2.659212</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.840727</v>
+        <v>3.357475</v>
       </c>
       <c r="AB55" t="n">
-        <v>3.812497</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>-2.659212</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.357475</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AK55" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -6639,90 +5975,78 @@
         <v>110.60765</v>
       </c>
       <c r="I56" t="n">
-        <v>118.00063</v>
+        <v>5.2194</v>
       </c>
       <c r="J56" t="n">
-        <v>5.2194</v>
+        <v>5.2188</v>
       </c>
       <c r="K56" t="n">
-        <v>5.2188</v>
+        <v>7240557</v>
       </c>
       <c r="L56" t="n">
-        <v>7240557</v>
+        <v>2687535</v>
       </c>
       <c r="M56" t="n">
-        <v>2687535</v>
+        <v>4553022</v>
       </c>
       <c r="N56" t="n">
-        <v>4553022</v>
+        <v>4.52</v>
       </c>
       <c r="O56" t="n">
-        <v>4.52</v>
+        <v>5.39</v>
       </c>
       <c r="P56" t="n">
-        <v>3.06</v>
+        <v>32.84</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.39</v>
+        <v>362002</v>
       </c>
       <c r="R56" t="n">
-        <v>32.84</v>
+        <v>-0.151802</v>
       </c>
       <c r="S56" t="n">
-        <v>362002</v>
+        <v>1.357413</v>
       </c>
       <c r="T56" t="n">
-        <v>-0.151802</v>
+        <v>1.357572</v>
       </c>
       <c r="U56" t="n">
-        <v>10.517667</v>
+        <v>1.15642</v>
       </c>
       <c r="V56" t="n">
-        <v>1.357413</v>
+        <v>1.168876</v>
       </c>
       <c r="W56" t="n">
-        <v>1.357572</v>
+        <v>1.149068</v>
       </c>
       <c r="X56" t="n">
-        <v>1.15642</v>
+        <v>-2.444795</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.168876</v>
+        <v>4.142847</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.149068</v>
+        <v>-1.819225</v>
       </c>
       <c r="AA56" t="n">
-        <v>-2.444795</v>
+        <v>3.768807</v>
       </c>
       <c r="AB56" t="n">
-        <v>4.142847</v>
+        <v>-0.25</v>
       </c>
       <c r="AC56" t="n">
-        <v>-1.819225</v>
+        <v>-0.000354</v>
       </c>
       <c r="AD56" t="n">
-        <v>3.768807</v>
+        <v>-0.000354</v>
       </c>
       <c r="AE56" t="n">
-        <v>-0.25</v>
+        <v>-0.12</v>
       </c>
       <c r="AF56" t="n">
-        <v>-0.000354</v>
+        <v>-0.17</v>
       </c>
       <c r="AG56" t="n">
-        <v>-0.000354</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="AK56" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -6752,90 +6076,78 @@
         <v>110.90086</v>
       </c>
       <c r="I57" t="n">
-        <v>113.89942</v>
+        <v>4.9886</v>
       </c>
       <c r="J57" t="n">
-        <v>4.9886</v>
+        <v>4.988</v>
       </c>
       <c r="K57" t="n">
-        <v>4.988</v>
+        <v>7259766</v>
       </c>
       <c r="L57" t="n">
-        <v>7259766</v>
+        <v>2685397</v>
       </c>
       <c r="M57" t="n">
-        <v>2685397</v>
+        <v>4574368</v>
       </c>
       <c r="N57" t="n">
-        <v>4574368</v>
+        <v>4.64</v>
       </c>
       <c r="O57" t="n">
-        <v>4.64</v>
+        <v>5.51</v>
       </c>
       <c r="P57" t="n">
-        <v>3.15</v>
+        <v>33.36</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.51</v>
+        <v>366913</v>
       </c>
       <c r="R57" t="n">
-        <v>33.36</v>
+        <v>0.26509</v>
       </c>
       <c r="S57" t="n">
-        <v>366913</v>
+        <v>-4.421964</v>
       </c>
       <c r="T57" t="n">
-        <v>0.26509</v>
+        <v>-4.422473</v>
       </c>
       <c r="U57" t="n">
-        <v>-3.475583</v>
+        <v>0.265297</v>
       </c>
       <c r="V57" t="n">
-        <v>-4.421964</v>
+        <v>-0.079552</v>
       </c>
       <c r="W57" t="n">
-        <v>-4.422473</v>
+        <v>0.468831</v>
       </c>
       <c r="X57" t="n">
-        <v>0.265297</v>
+        <v>1.356622</v>
       </c>
       <c r="Y57" t="n">
-        <v>-0.079552</v>
+        <v>4.39172</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.468831</v>
+        <v>0.619623</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.356622</v>
+        <v>4.109608</v>
       </c>
       <c r="AB57" t="n">
-        <v>4.39172</v>
+        <v>-0.25</v>
       </c>
       <c r="AC57" t="n">
-        <v>0.619623</v>
+        <v>-0.000554</v>
       </c>
       <c r="AD57" t="n">
-        <v>4.109608</v>
+        <v>-0.000554</v>
       </c>
       <c r="AE57" t="n">
-        <v>-0.25</v>
+        <v>0.12</v>
       </c>
       <c r="AF57" t="n">
-        <v>-0.000554</v>
+        <v>0.12</v>
       </c>
       <c r="AG57" t="n">
-        <v>-0.000554</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AK57" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -6865,90 +6177,78 @@
         <v>110.93102</v>
       </c>
       <c r="I58" t="n">
-        <v>109.53002</v>
+        <v>5.0569</v>
       </c>
       <c r="J58" t="n">
-        <v>5.0569</v>
+        <v>5.0563</v>
       </c>
       <c r="K58" t="n">
-        <v>5.0563</v>
+        <v>7305306</v>
       </c>
       <c r="L58" t="n">
-        <v>7305306</v>
+        <v>2708154</v>
       </c>
       <c r="M58" t="n">
-        <v>2708154</v>
+        <v>4597152</v>
       </c>
       <c r="N58" t="n">
-        <v>4597152</v>
+        <v>4.74</v>
       </c>
       <c r="O58" t="n">
-        <v>4.74</v>
+        <v>5.62</v>
       </c>
       <c r="P58" t="n">
-        <v>3.25</v>
+        <v>33.1</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.62</v>
+        <v>371137</v>
       </c>
       <c r="R58" t="n">
-        <v>33.1</v>
+        <v>0.027195</v>
       </c>
       <c r="S58" t="n">
-        <v>371137</v>
+        <v>1.369122</v>
       </c>
       <c r="T58" t="n">
-        <v>0.027195</v>
+        <v>1.369286</v>
       </c>
       <c r="U58" t="n">
-        <v>-3.836192</v>
+        <v>0.627293</v>
       </c>
       <c r="V58" t="n">
-        <v>1.369122</v>
+        <v>0.847435</v>
       </c>
       <c r="W58" t="n">
-        <v>1.369286</v>
+        <v>0.49808</v>
       </c>
       <c r="X58" t="n">
-        <v>0.627293</v>
+        <v>1.151227</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.847435</v>
+        <v>4.724907</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.49808</v>
+        <v>1.964454</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.151227</v>
+        <v>4.420848</v>
       </c>
       <c r="AB58" t="n">
-        <v>4.724907</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.964454</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="AD58" t="n">
-        <v>4.420848</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AF58" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="AG58" t="n">
-        <v>-0.0008229999999999999</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK58" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -6978,90 +6278,78 @@
         <v>110.22154</v>
       </c>
       <c r="I59" t="n">
-        <v>109.89427</v>
+        <v>5.1766</v>
       </c>
       <c r="J59" t="n">
-        <v>5.1766</v>
+        <v>5.176</v>
       </c>
       <c r="K59" t="n">
-        <v>5.176</v>
+        <v>7353293</v>
       </c>
       <c r="L59" t="n">
-        <v>7353293</v>
+        <v>2750625</v>
       </c>
       <c r="M59" t="n">
-        <v>2750625</v>
+        <v>4602668</v>
       </c>
       <c r="N59" t="n">
-        <v>4602668</v>
+        <v>4.58</v>
       </c>
       <c r="O59" t="n">
-        <v>4.58</v>
+        <v>5.42</v>
       </c>
       <c r="P59" t="n">
-        <v>3.18</v>
+        <v>33.33</v>
       </c>
       <c r="Q59" t="n">
-        <v>5.42</v>
+        <v>367558</v>
       </c>
       <c r="R59" t="n">
-        <v>33.33</v>
+        <v>-0.6395690000000001</v>
       </c>
       <c r="S59" t="n">
-        <v>367558</v>
+        <v>2.367063</v>
       </c>
       <c r="T59" t="n">
-        <v>-0.6395690000000001</v>
+        <v>2.367344</v>
       </c>
       <c r="U59" t="n">
-        <v>0.332557</v>
+        <v>0.656879</v>
       </c>
       <c r="V59" t="n">
-        <v>2.367063</v>
+        <v>1.568264</v>
       </c>
       <c r="W59" t="n">
-        <v>2.367344</v>
+        <v>0.119987</v>
       </c>
       <c r="X59" t="n">
-        <v>0.656879</v>
+        <v>-0.964334</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.568264</v>
+        <v>4.641328</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.119987</v>
+        <v>3.177699</v>
       </c>
       <c r="AA59" t="n">
-        <v>-0.964334</v>
+        <v>4.327084</v>
       </c>
       <c r="AB59" t="n">
-        <v>4.641328</v>
+        <v>-0.25</v>
       </c>
       <c r="AC59" t="n">
-        <v>3.177699</v>
+        <v>-0.000372</v>
       </c>
       <c r="AD59" t="n">
-        <v>4.327084</v>
+        <v>-0.000372</v>
       </c>
       <c r="AE59" t="n">
-        <v>-0.25</v>
+        <v>-0.16</v>
       </c>
       <c r="AF59" t="n">
-        <v>-0.000372</v>
+        <v>-0.2</v>
       </c>
       <c r="AG59" t="n">
-        <v>-0.000372</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AK59" t="n">
         <v>0.23</v>
       </c>
     </row>
@@ -7088,85 +6376,77 @@
         <v>-0.01</v>
       </c>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="n">
+        <v>5.0773</v>
+      </c>
       <c r="J60" t="n">
-        <v>5.0773</v>
+        <v>5.0767</v>
       </c>
       <c r="K60" t="n">
-        <v>5.0767</v>
+        <v>7372243</v>
       </c>
       <c r="L60" t="n">
-        <v>7372243</v>
+        <v>2731513</v>
       </c>
       <c r="M60" t="n">
-        <v>2731513</v>
+        <v>4640730</v>
       </c>
       <c r="N60" t="n">
-        <v>4640730</v>
+        <v>4.88</v>
       </c>
       <c r="O60" t="n">
-        <v>4.88</v>
+        <v>5.81</v>
       </c>
       <c r="P60" t="n">
-        <v>3.31</v>
+        <v>32.08</v>
       </c>
       <c r="Q60" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="R60" t="n">
-        <v>32.08</v>
-      </c>
+        <v>369742</v>
+      </c>
+      <c r="R60" t="inlineStr"/>
       <c r="S60" t="n">
-        <v>369742</v>
-      </c>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
+        <v>-1.918247</v>
+      </c>
+      <c r="T60" t="n">
+        <v>-1.91847</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0.257708</v>
+      </c>
       <c r="V60" t="n">
-        <v>-1.918247</v>
+        <v>-0.694824</v>
       </c>
       <c r="W60" t="n">
-        <v>-1.91847</v>
+        <v>0.826955</v>
       </c>
       <c r="X60" t="n">
-        <v>0.257708</v>
+        <v>0.5941920000000001</v>
       </c>
       <c r="Y60" t="n">
-        <v>-0.694824</v>
+        <v>4.443025</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.826955</v>
+        <v>2.772183</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.5941920000000001</v>
+        <v>4.098046</v>
       </c>
       <c r="AB60" t="n">
-        <v>4.443025</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.772183</v>
+        <v>-0.000497</v>
       </c>
       <c r="AD60" t="n">
-        <v>4.098046</v>
+        <v>-0.000497</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AF60" t="n">
-        <v>-0.000497</v>
+        <v>0.39</v>
       </c>
       <c r="AG60" t="n">
-        <v>-0.000497</v>
-      </c>
-      <c r="AH60" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="AK60" t="n">
         <v>-1.25</v>
       </c>
     </row>
@@ -7193,59 +6473,55 @@
         <v>-0.32</v>
       </c>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="n">
+        <v>5.1816</v>
+      </c>
       <c r="J61" t="n">
-        <v>5.1816</v>
-      </c>
-      <c r="K61" t="n">
         <v>5.181</v>
       </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
+      <c r="Q61" t="n">
+        <v>372616</v>
+      </c>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="n">
-        <v>372616</v>
-      </c>
-      <c r="T61" t="inlineStr"/>
+        <v>2.054241</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2.054484</v>
+      </c>
       <c r="U61" t="inlineStr"/>
-      <c r="V61" t="n">
-        <v>2.054241</v>
-      </c>
-      <c r="W61" t="n">
-        <v>2.054484</v>
-      </c>
-      <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="n">
+        <v>0.777299</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>4.223453</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>2.178243</v>
+      </c>
       <c r="AA61" t="n">
-        <v>0.777299</v>
+        <v>3.983297</v>
       </c>
       <c r="AB61" t="n">
-        <v>4.223453</v>
+        <v>-0.25</v>
       </c>
       <c r="AC61" t="n">
-        <v>2.178243</v>
+        <v>-0.0007470000000000001</v>
       </c>
       <c r="AD61" t="n">
-        <v>3.983297</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AF61" t="n">
         <v>-0.0007470000000000001</v>
       </c>
-      <c r="AG61" t="n">
-        <v>-0.0007470000000000001</v>
-      </c>
-      <c r="AH61" t="inlineStr"/>
-      <c r="AI61" t="inlineStr"/>
-      <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -7264,13 +6540,13 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="n">
+        <v>5.1149</v>
+      </c>
       <c r="J62" t="n">
-        <v>5.1149</v>
-      </c>
-      <c r="K62" t="n">
         <v>5.1143</v>
       </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -7278,35 +6554,31 @@
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
+      <c r="S62" t="n">
+        <v>-1.287247</v>
+      </c>
+      <c r="T62" t="n">
+        <v>-1.287396</v>
+      </c>
       <c r="U62" t="inlineStr"/>
-      <c r="V62" t="n">
-        <v>-1.287247</v>
-      </c>
-      <c r="W62" t="n">
-        <v>-1.287396</v>
-      </c>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
-      <c r="AB62" t="inlineStr"/>
-      <c r="AC62" t="inlineStr"/>
-      <c r="AD62" t="inlineStr"/>
-      <c r="AE62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="n">
+      <c r="AB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" t="n">
         <v>-0.000124</v>
       </c>
-      <c r="AG62" t="n">
+      <c r="AD62" t="n">
         <v>-0.000124</v>
       </c>
-      <c r="AH62" t="inlineStr"/>
-      <c r="AI62" t="inlineStr"/>
-      <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AK62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,125 +463,145 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>ibc_br</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>cambio_venda_usd</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>cambio_compra_usd</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>saldo_credito_total</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>saldo_credito_pj</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>saldo_credito_pf</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inadimplencia_total</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>inadimplencia_pj</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inadimplencia_pf</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>var_pct_ibc_br</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ipca_acum_12m</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>inpc_acum_12m</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>dif_selic_over</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>dif_cdi</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pj</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -613,34 +633,38 @@
         <v>96.95313</v>
       </c>
       <c r="I2" t="n">
+        <v>97.10569</v>
+      </c>
+      <c r="J2" t="n">
         <v>5.4394</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>5.4388</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>4441056</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>1894119</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>2546936</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>2.34</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q2" t="n">
         <v>3.01</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>21.42</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>368886</v>
       </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -655,6 +679,10 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -682,72 +710,84 @@
         <v>97.47790999999999</v>
       </c>
       <c r="I3" t="n">
+        <v>96.52863000000001</v>
+      </c>
+      <c r="J3" t="n">
         <v>5.643</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>5.6424</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>4511956</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>1910940</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>2601017</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>2.33</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q3" t="n">
         <v>2.99</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>22.89</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>367927</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>0.541272</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
+        <v>-0.59426</v>
+      </c>
+      <c r="V3" t="n">
         <v>3.74306</v>
       </c>
-      <c r="T3" t="n">
+      <c r="W3" t="n">
         <v>3.743473</v>
       </c>
-      <c r="U3" t="n">
+      <c r="X3" t="n">
         <v>1.596467</v>
       </c>
-      <c r="V3" t="n">
+      <c r="Y3" t="n">
         <v>0.888065</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Z3" t="n">
         <v>2.123375</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AA3" t="n">
         <v>-0.259972</v>
       </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="n">
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="n">
         <v>1.5</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AF3" t="n">
         <v>0.002704</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AG3" t="n">
         <v>0.002704</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AH3" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AK3" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -777,72 +817,84 @@
         <v>99.05295</v>
       </c>
       <c r="I4" t="n">
+        <v>97.85433</v>
+      </c>
+      <c r="J4" t="n">
         <v>5.6199</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>5.6193</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>4597507</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>1933111</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2664395</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>2.36</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3.01</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>23.91</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>367772</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>1.615792</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
+        <v>1.373375</v>
+      </c>
+      <c r="V4" t="n">
         <v>-0.409357</v>
       </c>
-      <c r="T4" t="n">
+      <c r="W4" t="n">
         <v>-0.4094</v>
       </c>
-      <c r="U4" t="n">
+      <c r="X4" t="n">
         <v>1.896096</v>
       </c>
-      <c r="V4" t="n">
+      <c r="Y4" t="n">
         <v>1.160214</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Z4" t="n">
         <v>2.436662</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AA4" t="n">
         <v>-0.042128</v>
       </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
         <v>0.005012</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AG4" t="n">
         <v>0.005012</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AH4" t="n">
         <v>0.03</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AI4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AK4" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -872,72 +924,84 @@
         <v>99.36759000000001</v>
       </c>
       <c r="I5" t="n">
+        <v>99.32245</v>
+      </c>
+      <c r="J5" t="n">
         <v>5.5805</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>5.5799</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>4682852</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>1974391</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>2708461</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>2.35</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q5" t="n">
         <v>3.05</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>24.21</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>362204</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>0.317648</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
+        <v>1.500312</v>
+      </c>
+      <c r="V5" t="n">
         <v>-0.70108</v>
       </c>
-      <c r="T5" t="n">
+      <c r="W5" t="n">
         <v>-0.701155</v>
       </c>
-      <c r="U5" t="n">
+      <c r="X5" t="n">
         <v>1.856332</v>
       </c>
-      <c r="V5" t="n">
+      <c r="Y5" t="n">
         <v>2.135418</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Z5" t="n">
         <v>1.653884</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AA5" t="n">
         <v>-1.513981</v>
       </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="n">
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
         <v>1.5</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AF5" t="n">
         <v>0.00406</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AG5" t="n">
         <v>0.00406</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AH5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AI5" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>0.04</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AK5" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -967,72 +1031,84 @@
         <v>97.41759</v>
       </c>
       <c r="I6" t="n">
+        <v>91.67452</v>
+      </c>
+      <c r="J6" t="n">
         <v>5.3574</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>5.3568</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>4682131</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>1947035</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>2735096</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>2.51</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3.26</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>25.23</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>358398</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>-1.96241</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
+        <v>-7.700102</v>
+      </c>
+      <c r="V6" t="n">
         <v>-3.99785</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>-3.99828</v>
       </c>
-      <c r="U6" t="n">
+      <c r="X6" t="n">
         <v>-0.015397</v>
       </c>
-      <c r="V6" t="n">
+      <c r="Y6" t="n">
         <v>-1.385541</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Z6" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AA6" t="n">
         <v>-1.050789</v>
       </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
         <v>0.001433</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AG6" t="n">
         <v>0.001433</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AH6" t="n">
         <v>0.16</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AI6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>0.21</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AK6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1062,72 +1138,84 @@
         <v>98.48287000000001</v>
       </c>
       <c r="I7" t="n">
+        <v>95.64045</v>
+      </c>
+      <c r="J7" t="n">
         <v>5.1394</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>5.1388</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>4727818</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>1971524</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>2756295</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>2.57</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q7" t="n">
         <v>3.38</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>25.63</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>357740</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>1.093519</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
+        <v>4.326098</v>
+      </c>
+      <c r="V7" t="n">
         <v>-4.069138</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>-4.069594</v>
       </c>
-      <c r="U7" t="n">
+      <c r="X7" t="n">
         <v>0.975774</v>
       </c>
-      <c r="V7" t="n">
+      <c r="Y7" t="n">
         <v>1.257759</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Z7" t="n">
         <v>0.775073</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AA7" t="n">
         <v>-0.183595</v>
       </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="n">
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="n">
         <v>1.5</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AF7" t="n">
         <v>0.004849</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AG7" t="n">
         <v>0.004849</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AH7" t="n">
         <v>0.06</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AI7" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>0.12</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AK7" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1157,72 +1245,84 @@
         <v>99.54331000000001</v>
       </c>
       <c r="I8" t="n">
+        <v>104.53224</v>
+      </c>
+      <c r="J8" t="n">
         <v>4.7378</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>4.7372</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>4794583</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>1994119</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>2800464</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>2.66</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q8" t="n">
         <v>3.45</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>26.54</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>353169</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>1.076776</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
+        <v>9.297102000000001</v>
+      </c>
+      <c r="V8" t="n">
         <v>-7.814142</v>
       </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
         <v>-7.815054</v>
       </c>
-      <c r="U8" t="n">
+      <c r="X8" t="n">
         <v>1.412174</v>
       </c>
-      <c r="V8" t="n">
+      <c r="Y8" t="n">
         <v>1.146068</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Z8" t="n">
         <v>1.602477</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AA8" t="n">
         <v>-1.277744</v>
       </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="n">
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="n">
         <v>1</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AF8" t="n">
         <v>0.002356</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AG8" t="n">
         <v>0.002356</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AH8" t="n">
         <v>0.09</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AI8" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AK8" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1252,72 +1352,84 @@
         <v>99.44726</v>
       </c>
       <c r="I9" t="n">
+        <v>100.22451</v>
+      </c>
+      <c r="J9" t="n">
         <v>4.9191</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>4.9185</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>4833732</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>2003312</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>2830420</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>2.72</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q9" t="n">
         <v>3.54</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>27.46</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>345097</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>-0.09649099999999999</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
+        <v>-4.120958</v>
+      </c>
+      <c r="V9" t="n">
         <v>3.826671</v>
       </c>
-      <c r="T9" t="n">
+      <c r="W9" t="n">
         <v>3.827155</v>
       </c>
-      <c r="U9" t="n">
+      <c r="X9" t="n">
         <v>0.816526</v>
       </c>
-      <c r="V9" t="n">
+      <c r="Y9" t="n">
         <v>0.461006</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Z9" t="n">
         <v>1.06968</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AA9" t="n">
         <v>-2.285591</v>
       </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
         <v>0.001785</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AG9" t="n">
         <v>0.001785</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AH9" t="n">
         <v>0.06</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AI9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AK9" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1347,72 +1459,84 @@
         <v>99.65249</v>
       </c>
       <c r="I10" t="n">
+        <v>99.74639000000001</v>
+      </c>
+      <c r="J10" t="n">
         <v>4.7289</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>4.7283</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4889397</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>2013726</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>2875671</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>2.79</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q10" t="n">
         <v>3.65</v>
       </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
         <v>27.42</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>346415</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>0.206371</v>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
+        <v>-0.477049</v>
+      </c>
+      <c r="V10" t="n">
         <v>-3.866561</v>
       </c>
-      <c r="T10" t="n">
+      <c r="W10" t="n">
         <v>-3.867033</v>
       </c>
-      <c r="U10" t="n">
+      <c r="X10" t="n">
         <v>1.151595</v>
       </c>
-      <c r="V10" t="n">
+      <c r="Y10" t="n">
         <v>0.5198390000000001</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Z10" t="n">
         <v>1.598738</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AA10" t="n">
         <v>0.381922</v>
       </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="n">
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="n">
         <v>1</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AF10" t="n">
         <v>0.003057</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AG10" t="n">
         <v>0.003057</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AH10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>0.11</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AK10" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1442,72 +1566,84 @@
         <v>99.53077999999999</v>
       </c>
       <c r="I11" t="n">
+        <v>99.32053000000001</v>
+      </c>
+      <c r="J11" t="n">
         <v>5.238</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>5.2374</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>4965603</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>2052569</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>2913035</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>2.73</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3.57</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>27.88</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
         <v>341958</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>-0.122134</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
+        <v>-0.426943</v>
+      </c>
+      <c r="V11" t="n">
         <v>10.765717</v>
       </c>
-      <c r="T11" t="n">
+      <c r="W11" t="n">
         <v>10.767083</v>
       </c>
-      <c r="U11" t="n">
+      <c r="X11" t="n">
         <v>1.558597</v>
       </c>
-      <c r="V11" t="n">
+      <c r="Y11" t="n">
         <v>1.928912</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Z11" t="n">
         <v>1.299314</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AA11" t="n">
         <v>-1.286607</v>
       </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="n">
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AF11" t="n">
         <v>0.00132</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AG11" t="n">
         <v>0.00132</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AH11" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AI11" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AK11" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1537,72 +1673,84 @@
         <v>101.43252</v>
       </c>
       <c r="I12" t="n">
+        <v>103.95413</v>
+      </c>
+      <c r="J12" t="n">
         <v>5.1884</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>5.1878</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>4999244</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>2047038</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>2952207</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>2.84</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q12" t="n">
         <v>3.71</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>29.24</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>346403</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>1.910705</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
+        <v>4.665299</v>
+      </c>
+      <c r="V12" t="n">
         <v>-0.946926</v>
       </c>
-      <c r="T12" t="n">
+      <c r="W12" t="n">
         <v>-0.947035</v>
       </c>
-      <c r="U12" t="n">
+      <c r="X12" t="n">
         <v>0.677481</v>
       </c>
-      <c r="V12" t="n">
+      <c r="Y12" t="n">
         <v>-0.269467</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Z12" t="n">
         <v>1.344714</v>
       </c>
-      <c r="X12" t="n">
+      <c r="AA12" t="n">
         <v>1.299867</v>
       </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AG12" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AH12" t="n">
         <v>0.11</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AI12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>0.14</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AK12" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -1632,78 +1780,90 @@
         <v>101.09886</v>
       </c>
       <c r="I13" t="n">
+        <v>104.51426</v>
+      </c>
+      <c r="J13" t="n">
         <v>5.179</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>5.1784</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>5072711</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>2064183</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>3008528</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>2.9</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q13" t="n">
         <v>3.78</v>
       </c>
-      <c r="P13" t="n">
+      <c r="R13" t="n">
         <v>28.6</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>339664</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>-0.328948</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
+        <v>0.538824</v>
+      </c>
+      <c r="V13" t="n">
         <v>-0.181173</v>
       </c>
-      <c r="T13" t="n">
+      <c r="W13" t="n">
         <v>-0.181194</v>
       </c>
-      <c r="U13" t="n">
+      <c r="X13" t="n">
         <v>1.469562</v>
       </c>
-      <c r="V13" t="n">
+      <c r="Y13" t="n">
         <v>0.837552</v>
       </c>
-      <c r="W13" t="n">
+      <c r="Z13" t="n">
         <v>1.907759</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AA13" t="n">
         <v>-1.945422</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AB13" t="n">
         <v>8.727061000000001</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AC13" t="n">
         <v>8.58755</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AD13" t="n">
         <v>8.825751</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AE13" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AF13" t="n">
         <v>0.001523</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AG13" t="n">
         <v>0.001523</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AH13" t="n">
         <v>0.06</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AI13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AK13" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -1733,78 +1893,90 @@
         <v>101.15209</v>
       </c>
       <c r="I14" t="n">
+        <v>101.19157</v>
+      </c>
+      <c r="J14" t="n">
         <v>5.4066</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>5.406</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>5164775</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>2109806</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3054969</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>2.92</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3.8</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>28.57</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>327580</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>0.052651</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
+        <v>-3.179174</v>
+      </c>
+      <c r="V14" t="n">
         <v>4.394671</v>
       </c>
-      <c r="T14" t="n">
+      <c r="W14" t="n">
         <v>4.39518</v>
       </c>
-      <c r="U14" t="n">
+      <c r="X14" t="n">
         <v>1.814888</v>
       </c>
-      <c r="V14" t="n">
+      <c r="Y14" t="n">
         <v>2.210221</v>
       </c>
-      <c r="W14" t="n">
+      <c r="Z14" t="n">
         <v>1.543645</v>
       </c>
-      <c r="X14" t="n">
+      <c r="AA14" t="n">
         <v>-3.557633</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AB14" t="n">
         <v>7.168596</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AC14" t="n">
         <v>8.248760000000001</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AD14" t="n">
         <v>7.191214</v>
       </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
         <v>0.000228</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AG14" t="n">
         <v>0.000228</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AH14" t="n">
         <v>0.02</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AI14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AK14" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -1834,78 +2006,90 @@
         <v>101.43094</v>
       </c>
       <c r="I15" t="n">
+        <v>100.07474</v>
+      </c>
+      <c r="J15" t="n">
         <v>5.257</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>5.2564</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>5215990</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>2105856</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>3110134</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>3.04</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q15" t="n">
         <v>3.89</v>
       </c>
-      <c r="P15" t="n">
+      <c r="R15" t="n">
         <v>29.68</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>325546</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>0.275674</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
+        <v>-1.103679</v>
+      </c>
+      <c r="V15" t="n">
         <v>-2.766988</v>
       </c>
-      <c r="T15" t="n">
+      <c r="W15" t="n">
         <v>-2.767296</v>
       </c>
-      <c r="U15" t="n">
+      <c r="X15" t="n">
         <v>0.991621</v>
       </c>
-      <c r="V15" t="n">
+      <c r="Y15" t="n">
         <v>-0.187221</v>
       </c>
-      <c r="W15" t="n">
+      <c r="Z15" t="n">
         <v>1.805747</v>
       </c>
-      <c r="X15" t="n">
+      <c r="AA15" t="n">
         <v>-0.6209170000000001</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AB15" t="n">
         <v>6.470016</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AC15" t="n">
         <v>6.517038</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AD15" t="n">
         <v>6.460076</v>
       </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
       <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
         <v>0.12</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AI15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AK15" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -1935,78 +2119,90 @@
         <v>100.7113</v>
       </c>
       <c r="I16" t="n">
+        <v>99.15328</v>
+      </c>
+      <c r="J16" t="n">
         <v>5.2941</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>5.2935</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>5285657</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>2130312</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>3155345</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>3.07</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q16" t="n">
         <v>3.92</v>
       </c>
-      <c r="P16" t="n">
+      <c r="R16" t="n">
         <v>30.52</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>331505</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>-0.709488</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
+        <v>-0.920772</v>
+      </c>
+      <c r="V16" t="n">
         <v>0.705726</v>
       </c>
-      <c r="T16" t="n">
+      <c r="W16" t="n">
         <v>0.705806</v>
       </c>
-      <c r="U16" t="n">
+      <c r="X16" t="n">
         <v>1.335643</v>
       </c>
-      <c r="V16" t="n">
+      <c r="Y16" t="n">
         <v>1.161333</v>
       </c>
-      <c r="W16" t="n">
+      <c r="Z16" t="n">
         <v>1.453667</v>
       </c>
-      <c r="X16" t="n">
+      <c r="AA16" t="n">
         <v>1.830463</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AB16" t="n">
         <v>5.900488</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AC16" t="n">
         <v>5.899363</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AD16" t="n">
         <v>5.974439</v>
       </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
       <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
         <v>0.03</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AI16" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AK16" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2036,78 +2232,90 @@
         <v>100.58566</v>
       </c>
       <c r="I17" t="n">
+        <v>99.97338999999999</v>
+      </c>
+      <c r="J17" t="n">
         <v>5.2177</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>5.2171</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>5366069</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>2178236</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>3187833</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>3.07</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q17" t="n">
         <v>3.94</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>29.64</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>324703</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>-0.124753</v>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
+        <v>0.827113</v>
+      </c>
+      <c r="V17" t="n">
         <v>-1.443116</v>
       </c>
-      <c r="T17" t="n">
+      <c r="W17" t="n">
         <v>-1.443279</v>
       </c>
-      <c r="U17" t="n">
+      <c r="X17" t="n">
         <v>1.521325</v>
       </c>
-      <c r="V17" t="n">
+      <c r="Y17" t="n">
         <v>2.249624</v>
       </c>
-      <c r="W17" t="n">
+      <c r="Z17" t="n">
         <v>1.029618</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AA17" t="n">
         <v>-2.051854</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AB17" t="n">
         <v>5.784842</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AC17" t="n">
         <v>5.458422</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AD17" t="n">
         <v>5.932356</v>
       </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
         <v>-0</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AG17" t="n">
         <v>-0</v>
       </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AK17" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -2137,78 +2345,90 @@
         <v>100.10937</v>
       </c>
       <c r="I18" t="n">
+        <v>95.09372999999999</v>
+      </c>
+      <c r="J18" t="n">
         <v>5.0993</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>5.0987</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>5373231</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>2151399</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>3221831</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>3.24</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q18" t="n">
         <v>4.11</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>30.54</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>331122</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>-0.473517</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
+        <v>-4.880959</v>
+      </c>
+      <c r="V18" t="n">
         <v>-2.269199</v>
       </c>
-      <c r="T18" t="n">
+      <c r="W18" t="n">
         <v>-2.26946</v>
       </c>
-      <c r="U18" t="n">
+      <c r="X18" t="n">
         <v>0.133468</v>
       </c>
-      <c r="V18" t="n">
+      <c r="Y18" t="n">
         <v>-1.232052</v>
       </c>
-      <c r="W18" t="n">
+      <c r="Z18" t="n">
         <v>1.066493</v>
       </c>
-      <c r="X18" t="n">
+      <c r="AA18" t="n">
         <v>1.976883</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AB18" t="n">
         <v>5.77432</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AC18" t="n">
         <v>3.79089</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AD18" t="n">
         <v>5.711379</v>
       </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
       <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
         <v>0.17</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AI18" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>0.17</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AK18" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2238,78 +2458,90 @@
         <v>103.08344</v>
       </c>
       <c r="I19" t="n">
+        <v>98.65015</v>
+      </c>
+      <c r="J19" t="n">
         <v>5.2078</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>5.2072</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>5370950</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>2136105</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>3234845</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>3.36</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q19" t="n">
         <v>4.16</v>
       </c>
-      <c r="P19" t="n">
+      <c r="R19" t="n">
         <v>30.48</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="S19" t="n">
         <v>328098</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>2.970821</v>
       </c>
-      <c r="S19" t="n">
+      <c r="U19" t="n">
+        <v>3.73991</v>
+      </c>
+      <c r="V19" t="n">
         <v>2.127743</v>
       </c>
-      <c r="T19" t="n">
+      <c r="W19" t="n">
         <v>2.127993</v>
       </c>
-      <c r="U19" t="n">
+      <c r="X19" t="n">
         <v>-0.042451</v>
       </c>
-      <c r="V19" t="n">
+      <c r="Y19" t="n">
         <v>-0.710886</v>
       </c>
-      <c r="W19" t="n">
+      <c r="Z19" t="n">
         <v>0.403932</v>
       </c>
-      <c r="X19" t="n">
+      <c r="AA19" t="n">
         <v>-0.913259</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AB19" t="n">
         <v>5.596302</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AC19" t="n">
         <v>1.864495</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AD19" t="n">
         <v>5.47065</v>
       </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
       <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
         <v>0.12</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="AI19" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>0.05</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AK19" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2339,78 +2571,90 @@
         <v>103.08526</v>
       </c>
       <c r="I20" t="n">
+        <v>110.62045</v>
+      </c>
+      <c r="J20" t="n">
         <v>5.0804</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>5.0798</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>5424811</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>2154900</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>3269910</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>3.35</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q20" t="n">
         <v>4.11</v>
       </c>
-      <c r="P20" t="n">
+      <c r="R20" t="n">
         <v>30.99</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="S20" t="n">
         <v>341158</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>0.001766</v>
       </c>
-      <c r="S20" t="n">
+      <c r="U20" t="n">
+        <v>12.134092</v>
+      </c>
+      <c r="V20" t="n">
         <v>-2.446331</v>
       </c>
-      <c r="T20" t="n">
+      <c r="W20" t="n">
         <v>-2.446612</v>
       </c>
-      <c r="U20" t="n">
+      <c r="X20" t="n">
         <v>1.002821</v>
       </c>
-      <c r="V20" t="n">
+      <c r="Y20" t="n">
         <v>0.879872</v>
       </c>
-      <c r="W20" t="n">
+      <c r="Z20" t="n">
         <v>1.083978</v>
       </c>
-      <c r="X20" t="n">
+      <c r="AA20" t="n">
         <v>3.980518</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AB20" t="n">
         <v>4.650694</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AC20" t="n">
         <v>0.172427</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AD20" t="n">
         <v>4.361088</v>
       </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
       <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AI20" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AK20" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2440,78 +2684,90 @@
         <v>103.96006</v>
       </c>
       <c r="I21" t="n">
+        <v>104.03539</v>
+      </c>
+      <c r="J21" t="n">
         <v>5.0007</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>5.0001</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>5426307</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>2145000</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>3281308</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>3.54</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q21" t="n">
         <v>4.26</v>
       </c>
-      <c r="P21" t="n">
+      <c r="R21" t="n">
         <v>31.62</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="S21" t="n">
         <v>345725</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>0.848618</v>
       </c>
-      <c r="S21" t="n">
+      <c r="U21" t="n">
+        <v>-5.952841</v>
+      </c>
+      <c r="V21" t="n">
         <v>-1.568774</v>
       </c>
-      <c r="T21" t="n">
+      <c r="W21" t="n">
         <v>-1.568959</v>
       </c>
-      <c r="U21" t="n">
+      <c r="X21" t="n">
         <v>0.027577</v>
       </c>
-      <c r="V21" t="n">
+      <c r="Y21" t="n">
         <v>-0.459418</v>
       </c>
-      <c r="W21" t="n">
+      <c r="Z21" t="n">
         <v>0.348572</v>
       </c>
-      <c r="X21" t="n">
+      <c r="AA21" t="n">
         <v>1.338676</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AB21" t="n">
         <v>4.184706</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AC21" t="n">
         <v>-2.158772</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AD21" t="n">
         <v>3.834324</v>
       </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
       <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
         <v>0.19</v>
       </c>
-      <c r="AF21" t="n">
+      <c r="AI21" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>0.15</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AK21" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -2541,78 +2797,90 @@
         <v>102.40467</v>
       </c>
       <c r="I22" t="n">
+        <v>102.71665</v>
+      </c>
+      <c r="J22" t="n">
         <v>5.0959</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>5.0953</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>5453708</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>2145530</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>3308178</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>3.65</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q22" t="n">
         <v>4.35</v>
       </c>
-      <c r="P22" t="n">
+      <c r="R22" t="n">
         <v>31.63</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
         <v>343489</v>
       </c>
-      <c r="R22" t="n">
+      <c r="T22" t="n">
         <v>-1.496142</v>
       </c>
-      <c r="S22" t="n">
+      <c r="U22" t="n">
+        <v>-1.267588</v>
+      </c>
+      <c r="V22" t="n">
         <v>1.903733</v>
       </c>
-      <c r="T22" t="n">
+      <c r="W22" t="n">
         <v>1.903962</v>
       </c>
-      <c r="U22" t="n">
+      <c r="X22" t="n">
         <v>0.504966</v>
       </c>
-      <c r="V22" t="n">
+      <c r="Y22" t="n">
         <v>0.024709</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Z22" t="n">
         <v>0.818881</v>
       </c>
-      <c r="X22" t="n">
+      <c r="AA22" t="n">
         <v>-0.646757</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AB22" t="n">
         <v>3.935832</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AC22" t="n">
         <v>-4.45588</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AD22" t="n">
         <v>3.741292</v>
       </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
         <v>-0</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AG22" t="n">
         <v>-0</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AH22" t="n">
         <v>0.11</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AI22" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AK22" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -2642,78 +2910,90 @@
         <v>102.4398</v>
       </c>
       <c r="I23" t="n">
+        <v>102.285</v>
+      </c>
+      <c r="J23" t="n">
         <v>4.8192</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>4.8186</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>5479459</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>2169613</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>3309846</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>3.61</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q23" t="n">
         <v>4.25</v>
       </c>
-      <c r="P23" t="n">
+      <c r="R23" t="n">
         <v>30.85</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
         <v>343620</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>0.034305</v>
       </c>
-      <c r="S23" t="n">
+      <c r="U23" t="n">
+        <v>-0.420234</v>
+      </c>
+      <c r="V23" t="n">
         <v>-5.429855</v>
       </c>
-      <c r="T23" t="n">
+      <c r="W23" t="n">
         <v>-5.430495</v>
       </c>
-      <c r="U23" t="n">
+      <c r="X23" t="n">
         <v>0.472174</v>
       </c>
-      <c r="V23" t="n">
+      <c r="Y23" t="n">
         <v>1.122473</v>
       </c>
-      <c r="W23" t="n">
+      <c r="Z23" t="n">
         <v>0.050421</v>
       </c>
-      <c r="X23" t="n">
+      <c r="AA23" t="n">
         <v>0.038138</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AB23" t="n">
         <v>3.161501</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AC23" t="n">
         <v>-6.84947</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AD23" t="n">
         <v>2.998957</v>
       </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
       <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AF23" t="n">
+      <c r="AI23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AK23" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -2743,78 +3023,90 @@
         <v>102.89895</v>
       </c>
       <c r="I24" t="n">
+        <v>105.33914</v>
+      </c>
+      <c r="J24" t="n">
         <v>4.7415</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>4.7409</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>5484871</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>2153541</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>3331330</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>3.63</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Q24" t="n">
         <v>4.22</v>
       </c>
-      <c r="P24" t="n">
+      <c r="R24" t="n">
         <v>30.43</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
         <v>345476</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>0.448214</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
+        <v>2.985912</v>
+      </c>
+      <c r="V24" t="n">
         <v>-1.612301</v>
       </c>
-      <c r="T24" t="n">
+      <c r="W24" t="n">
         <v>-1.612502</v>
       </c>
-      <c r="U24" t="n">
+      <c r="X24" t="n">
         <v>0.098769</v>
       </c>
-      <c r="V24" t="n">
+      <c r="Y24" t="n">
         <v>-0.740777</v>
       </c>
-      <c r="W24" t="n">
+      <c r="Z24" t="n">
         <v>0.6490939999999999</v>
       </c>
-      <c r="X24" t="n">
+      <c r="AA24" t="n">
         <v>0.5401319999999999</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AB24" t="n">
         <v>3.992444</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AC24" t="n">
         <v>-7.713954</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AD24" t="n">
         <v>3.527423</v>
       </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
       <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
         <v>0.02</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AI24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AK24" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -2844,78 +3136,90 @@
         <v>102.48797</v>
       </c>
       <c r="I25" t="n">
+        <v>106.05945</v>
+      </c>
+      <c r="J25" t="n">
         <v>4.9219</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>4.9213</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5559063</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>2172658</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>3386405</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>3.61</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Q25" t="n">
         <v>4.12</v>
       </c>
-      <c r="P25" t="n">
+      <c r="R25" t="n">
         <v>29.92</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
         <v>344177</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>-0.399402</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
+        <v>0.683801</v>
+      </c>
+      <c r="V25" t="n">
         <v>3.804703</v>
       </c>
-      <c r="T25" t="n">
+      <c r="W25" t="n">
         <v>3.805185</v>
       </c>
-      <c r="U25" t="n">
+      <c r="X25" t="n">
         <v>1.352666</v>
       </c>
-      <c r="V25" t="n">
+      <c r="Y25" t="n">
         <v>0.887701</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Z25" t="n">
         <v>1.653244</v>
       </c>
-      <c r="X25" t="n">
+      <c r="AA25" t="n">
         <v>-0.376003</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AB25" t="n">
         <v>4.608216</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AC25" t="n">
         <v>-7.193509</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AD25" t="n">
         <v>4.057054</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AE25" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AF25" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AG25" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AH25" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AI25" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AK25" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -2945,78 +3249,90 @@
         <v>102.50227</v>
       </c>
       <c r="I26" t="n">
+        <v>101.76242</v>
+      </c>
+      <c r="J26" t="n">
         <v>5.0076</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>5.007</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>5625945</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>2215175</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>3410769</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>3.54</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Q26" t="n">
         <v>4</v>
       </c>
-      <c r="P26" t="n">
+      <c r="R26" t="n">
         <v>29.66</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
         <v>340324</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>0.013953</v>
       </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
+        <v>-4.05153</v>
+      </c>
+      <c r="V26" t="n">
         <v>1.741198</v>
       </c>
-      <c r="T26" t="n">
+      <c r="W26" t="n">
         <v>1.74141</v>
       </c>
-      <c r="U26" t="n">
+      <c r="X26" t="n">
         <v>1.203116</v>
       </c>
-      <c r="V26" t="n">
+      <c r="Y26" t="n">
         <v>1.956912</v>
       </c>
-      <c r="W26" t="n">
+      <c r="Z26" t="n">
         <v>0.719465</v>
       </c>
-      <c r="X26" t="n">
+      <c r="AA26" t="n">
         <v>-1.119482</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AB26" t="n">
         <v>5.185235</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AC26" t="n">
         <v>-5.956714</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AD26" t="n">
         <v>4.505936</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AE26" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AF26" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AG26" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AH26" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AF26" t="n">
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AK26" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -3046,78 +3362,90 @@
         <v>102.83037</v>
       </c>
       <c r="I27" t="n">
+        <v>101.92849</v>
+      </c>
+      <c r="J27" t="n">
         <v>5.0575</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>5.0569</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>5653808</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>2204808</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>3449000</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>3.56</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Q27" t="n">
         <v>3.97</v>
       </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
         <v>29.24</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
         <v>340247</v>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>0.32009</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
+        <v>0.163194</v>
+      </c>
+      <c r="V27" t="n">
         <v>0.996485</v>
       </c>
-      <c r="T27" t="n">
+      <c r="W27" t="n">
         <v>0.996605</v>
       </c>
-      <c r="U27" t="n">
+      <c r="X27" t="n">
         <v>0.495259</v>
       </c>
-      <c r="V27" t="n">
+      <c r="Y27" t="n">
         <v>-0.467999</v>
       </c>
-      <c r="W27" t="n">
+      <c r="Z27" t="n">
         <v>1.120891</v>
       </c>
-      <c r="X27" t="n">
+      <c r="AA27" t="n">
         <v>-0.022625</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AB27" t="n">
         <v>4.819246</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AC27" t="n">
         <v>-4.560737</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AD27" t="n">
         <v>4.141877</v>
       </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AG27" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AH27" t="n">
         <v>0.02</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AI27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AK27" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3147,78 +3475,90 @@
         <v>103.58799</v>
       </c>
       <c r="I28" t="n">
+        <v>101.68208</v>
+      </c>
+      <c r="J28" t="n">
         <v>4.9355</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>4.9349</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>5711103</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>2220766</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>3490337</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>3.53</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Q28" t="n">
         <v>3.88</v>
       </c>
-      <c r="P28" t="n">
+      <c r="R28" t="n">
         <v>29.01</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
         <v>348406</v>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>0.7367669999999999</v>
       </c>
-      <c r="S28" t="n">
+      <c r="U28" t="n">
+        <v>-0.241748</v>
+      </c>
+      <c r="V28" t="n">
         <v>-2.412259</v>
       </c>
-      <c r="T28" t="n">
+      <c r="W28" t="n">
         <v>-2.412545</v>
       </c>
-      <c r="U28" t="n">
+      <c r="X28" t="n">
         <v>1.013388</v>
       </c>
-      <c r="V28" t="n">
+      <c r="Y28" t="n">
         <v>0.723782</v>
       </c>
-      <c r="W28" t="n">
+      <c r="Z28" t="n">
         <v>1.198521</v>
       </c>
-      <c r="X28" t="n">
+      <c r="AA28" t="n">
         <v>2.397964</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AB28" t="n">
         <v>4.683537</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AC28" t="n">
         <v>-3.457004</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AD28" t="n">
         <v>3.851383</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AE28" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AF28" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AG28" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AH28" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AI28" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>-0.09</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AK28" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -3248,78 +3588,90 @@
         <v>104.88262</v>
       </c>
       <c r="I29" t="n">
+        <v>101.68652</v>
+      </c>
+      <c r="J29" t="n">
         <v>4.8413</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>4.8407</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>5805157</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>2283485</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>3521672</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>3.29</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Q29" t="n">
         <v>3.75</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>28.14</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
         <v>355034</v>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>1.249788</v>
       </c>
-      <c r="S29" t="n">
+      <c r="U29" t="n">
+        <v>0.004367</v>
+      </c>
+      <c r="V29" t="n">
         <v>-1.908621</v>
       </c>
-      <c r="T29" t="n">
+      <c r="W29" t="n">
         <v>-1.908853</v>
       </c>
-      <c r="U29" t="n">
+      <c r="X29" t="n">
         <v>1.646862</v>
       </c>
-      <c r="V29" t="n">
+      <c r="Y29" t="n">
         <v>2.824206</v>
       </c>
-      <c r="W29" t="n">
+      <c r="Z29" t="n">
         <v>0.897764</v>
       </c>
-      <c r="X29" t="n">
+      <c r="AA29" t="n">
         <v>1.902378</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AB29" t="n">
         <v>4.621114</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AC29" t="n">
         <v>-3.178284</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AD29" t="n">
         <v>3.706988</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AE29" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AF29" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AG29" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AH29" t="n">
         <v>-0.24</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AI29" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>-0.13</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AK29" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3349,78 +3701,90 @@
         <v>104.47589</v>
       </c>
       <c r="I30" t="n">
+        <v>99.29136</v>
+      </c>
+      <c r="J30" t="n">
         <v>4.9535</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>4.9529</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>5794707</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>2234362</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3560345</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>3.38</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Q30" t="n">
         <v>3.76</v>
       </c>
-      <c r="P30" t="n">
+      <c r="R30" t="n">
         <v>28</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
         <v>355066</v>
       </c>
-      <c r="R30" t="n">
+      <c r="T30" t="n">
         <v>-0.387795</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
+        <v>-2.355435</v>
+      </c>
+      <c r="V30" t="n">
         <v>2.317559</v>
       </c>
-      <c r="T30" t="n">
+      <c r="W30" t="n">
         <v>2.317847</v>
       </c>
-      <c r="U30" t="n">
+      <c r="X30" t="n">
         <v>-0.180012</v>
       </c>
-      <c r="V30" t="n">
+      <c r="Y30" t="n">
         <v>-2.151229</v>
       </c>
-      <c r="W30" t="n">
+      <c r="Z30" t="n">
         <v>1.098143</v>
       </c>
-      <c r="X30" t="n">
+      <c r="AA30" t="n">
         <v>0.009013</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AB30" t="n">
         <v>4.506637</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AC30" t="n">
         <v>-3.31355</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AD30" t="n">
         <v>3.820543</v>
       </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AG30" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AH30" t="n">
         <v>0.09</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AI30" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AJ30" t="n">
         <v>0.01</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AK30" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -3450,78 +3814,90 @@
         <v>104.67291</v>
       </c>
       <c r="I31" t="n">
+        <v>102.15158</v>
+      </c>
+      <c r="J31" t="n">
         <v>4.9833</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>4.9827</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>5815954</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>2235302</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>3580652</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>3.38</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="Q31" t="n">
         <v>3.76</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
         <v>27.85</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="S31" t="n">
         <v>352705</v>
       </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
         <v>0.188579</v>
       </c>
-      <c r="S31" t="n">
+      <c r="U31" t="n">
+        <v>2.880633</v>
+      </c>
+      <c r="V31" t="n">
         <v>0.601595</v>
       </c>
-      <c r="T31" t="n">
+      <c r="W31" t="n">
         <v>0.601668</v>
       </c>
-      <c r="U31" t="n">
+      <c r="X31" t="n">
         <v>0.366662</v>
       </c>
-      <c r="V31" t="n">
+      <c r="Y31" t="n">
         <v>0.04207</v>
       </c>
-      <c r="W31" t="n">
+      <c r="Z31" t="n">
         <v>0.570366</v>
       </c>
-      <c r="X31" t="n">
+      <c r="AA31" t="n">
         <v>-0.664947</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AB31" t="n">
         <v>4.496274</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AC31" t="n">
         <v>-3.758575</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AD31" t="n">
         <v>3.861754</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AE31" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AF31" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AG31" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -3551,78 +3927,90 @@
         <v>104.68779</v>
       </c>
       <c r="I32" t="n">
+        <v>109.57244</v>
+      </c>
+      <c r="J32" t="n">
         <v>4.9962</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>4.9956</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>5899742</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>2285775</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>3613967</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>3.33</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="Q32" t="n">
         <v>3.71</v>
       </c>
-      <c r="P32" t="n">
+      <c r="R32" t="n">
         <v>28.14</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
         <v>355008</v>
       </c>
-      <c r="R32" t="n">
+      <c r="T32" t="n">
         <v>0.014216</v>
       </c>
-      <c r="S32" t="n">
+      <c r="U32" t="n">
+        <v>7.264557</v>
+      </c>
+      <c r="V32" t="n">
         <v>0.258865</v>
       </c>
-      <c r="T32" t="n">
+      <c r="W32" t="n">
         <v>0.258896</v>
       </c>
-      <c r="U32" t="n">
+      <c r="X32" t="n">
         <v>1.440658</v>
       </c>
-      <c r="V32" t="n">
+      <c r="Y32" t="n">
         <v>2.257995</v>
       </c>
-      <c r="W32" t="n">
+      <c r="Z32" t="n">
         <v>0.930417</v>
       </c>
-      <c r="X32" t="n">
+      <c r="AA32" t="n">
         <v>0.652954</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AB32" t="n">
         <v>3.925596</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AC32" t="n">
         <v>-4.25878</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AD32" t="n">
         <v>3.397348</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AE32" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AF32" t="n">
         <v>-0.000537</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AG32" t="n">
         <v>-0.000537</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AH32" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="AI32" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AJ32" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK32" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -3652,78 +4040,90 @@
         <v>104.6751</v>
       </c>
       <c r="I33" t="n">
+        <v>109.25226</v>
+      </c>
+      <c r="J33" t="n">
         <v>5.1718</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>5.1712</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5915538</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>2268879</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3646659</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>3.37</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="Q33" t="n">
         <v>3.75</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>27.86</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
         <v>351599</v>
       </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
         <v>-0.012122</v>
       </c>
-      <c r="S33" t="n">
+      <c r="U33" t="n">
+        <v>-0.292209</v>
+      </c>
+      <c r="V33" t="n">
         <v>3.514671</v>
       </c>
-      <c r="T33" t="n">
+      <c r="W33" t="n">
         <v>3.515093</v>
       </c>
-      <c r="U33" t="n">
+      <c r="X33" t="n">
         <v>0.267741</v>
       </c>
-      <c r="V33" t="n">
+      <c r="Y33" t="n">
         <v>-0.7391799999999999</v>
       </c>
-      <c r="W33" t="n">
+      <c r="Z33" t="n">
         <v>0.904602</v>
       </c>
-      <c r="X33" t="n">
+      <c r="AA33" t="n">
         <v>-0.96026</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AB33" t="n">
         <v>3.688016</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AC33" t="n">
         <v>-3.040871</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AD33" t="n">
         <v>3.232784</v>
       </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
         <v>-0.001252</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AG33" t="n">
         <v>-0.001252</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AH33" t="n">
         <v>0.04</v>
       </c>
-      <c r="AF33" t="n">
+      <c r="AI33" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AJ33" t="n">
         <v>0.04</v>
       </c>
-      <c r="AG33" t="n">
+      <c r="AK33" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -3753,78 +4153,90 @@
         <v>105.5521</v>
       </c>
       <c r="I34" t="n">
+        <v>104.71219</v>
+      </c>
+      <c r="J34" t="n">
         <v>5.2416</v>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>5.241</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>5953960</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>2278309</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>3675652</v>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>3.43</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q34" t="n">
         <v>3.82</v>
       </c>
-      <c r="P34" t="n">
+      <c r="R34" t="n">
         <v>27.75</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="S34" t="n">
         <v>355560</v>
       </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
         <v>0.837831</v>
       </c>
-      <c r="S34" t="n">
+      <c r="U34" t="n">
+        <v>-4.155585</v>
+      </c>
+      <c r="V34" t="n">
         <v>1.349627</v>
       </c>
-      <c r="T34" t="n">
+      <c r="W34" t="n">
         <v>1.349783</v>
       </c>
-      <c r="U34" t="n">
+      <c r="X34" t="n">
         <v>0.64951</v>
       </c>
-      <c r="V34" t="n">
+      <c r="Y34" t="n">
         <v>0.415624</v>
       </c>
-      <c r="W34" t="n">
+      <c r="Z34" t="n">
         <v>0.795057</v>
       </c>
-      <c r="X34" t="n">
+      <c r="AA34" t="n">
         <v>1.126567</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="AB34" t="n">
         <v>3.925952</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AC34" t="n">
         <v>-0.344269</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AD34" t="n">
         <v>3.335647</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AE34" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AF34" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AG34" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="AE34" t="n">
+      <c r="AH34" t="n">
         <v>0.06</v>
       </c>
-      <c r="AF34" t="n">
+      <c r="AI34" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AJ34" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AG34" t="n">
+      <c r="AK34" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -3854,78 +4266,90 @@
         <v>106.65779</v>
       </c>
       <c r="I35" t="n">
+        <v>105.87342</v>
+      </c>
+      <c r="J35" t="n">
         <v>5.5589</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>5.5583</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>6041898</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>2336858</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>3705041</v>
       </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>3.29</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q35" t="n">
         <v>3.71</v>
       </c>
-      <c r="P35" t="n">
+      <c r="R35" t="n">
         <v>27.81</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="S35" t="n">
         <v>357827</v>
       </c>
-      <c r="R35" t="n">
+      <c r="T35" t="n">
         <v>1.04753</v>
       </c>
-      <c r="S35" t="n">
+      <c r="U35" t="n">
+        <v>1.108973</v>
+      </c>
+      <c r="V35" t="n">
         <v>6.053495</v>
       </c>
-      <c r="T35" t="n">
+      <c r="W35" t="n">
         <v>6.054188</v>
       </c>
-      <c r="U35" t="n">
+      <c r="X35" t="n">
         <v>1.476967</v>
       </c>
-      <c r="V35" t="n">
+      <c r="Y35" t="n">
         <v>2.569845</v>
       </c>
-      <c r="W35" t="n">
+      <c r="Z35" t="n">
         <v>0.799559</v>
       </c>
-      <c r="X35" t="n">
+      <c r="AA35" t="n">
         <v>0.637586</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="AB35" t="n">
         <v>4.227578</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AC35" t="n">
         <v>2.440035</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AD35" t="n">
         <v>3.697684</v>
       </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="AD35" t="n">
+      <c r="AG35" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="AE35" t="n">
+      <c r="AH35" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AF35" t="n">
+      <c r="AI35" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="AJ35" t="n">
         <v>-0.11</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AK35" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -3955,78 +4379,90 @@
         <v>107.01873</v>
       </c>
       <c r="I36" t="n">
+        <v>111.50432</v>
+      </c>
+      <c r="J36" t="n">
         <v>5.6621</v>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>5.6615</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>6069205</v>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>2323362</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>3745844</v>
       </c>
-      <c r="N36" t="n">
+      <c r="O36" t="n">
         <v>3.3</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q36" t="n">
         <v>3.78</v>
       </c>
-      <c r="P36" t="n">
+      <c r="R36" t="n">
         <v>27.74</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="S36" t="n">
         <v>363282</v>
       </c>
-      <c r="R36" t="n">
+      <c r="T36" t="n">
         <v>0.338409</v>
       </c>
-      <c r="S36" t="n">
+      <c r="U36" t="n">
+        <v>5.318521</v>
+      </c>
+      <c r="V36" t="n">
         <v>1.856482</v>
       </c>
-      <c r="T36" t="n">
+      <c r="W36" t="n">
         <v>1.856683</v>
       </c>
-      <c r="U36" t="n">
+      <c r="X36" t="n">
         <v>0.451961</v>
       </c>
-      <c r="V36" t="n">
+      <c r="Y36" t="n">
         <v>-0.577528</v>
       </c>
-      <c r="W36" t="n">
+      <c r="Z36" t="n">
         <v>1.101283</v>
       </c>
-      <c r="X36" t="n">
+      <c r="AA36" t="n">
         <v>1.52448</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="AB36" t="n">
         <v>4.498245</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AC36" t="n">
         <v>3.812368</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AD36" t="n">
         <v>4.060953</v>
       </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
       <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
         <v>0.01</v>
       </c>
-      <c r="AF36" t="n">
+      <c r="AI36" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AK36" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -4056,78 +4492,90 @@
         <v>107.16697</v>
       </c>
       <c r="I37" t="n">
+        <v>110.06264</v>
+      </c>
+      <c r="J37" t="n">
         <v>5.6562</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>5.6556</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6135298</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>2344397</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>3790900</v>
       </c>
-      <c r="N37" t="n">
+      <c r="O37" t="n">
         <v>3.33</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q37" t="n">
         <v>3.82</v>
       </c>
-      <c r="P37" t="n">
+      <c r="R37" t="n">
         <v>27.59</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="S37" t="n">
         <v>369214</v>
       </c>
-      <c r="R37" t="n">
+      <c r="T37" t="n">
         <v>0.138518</v>
       </c>
-      <c r="S37" t="n">
+      <c r="U37" t="n">
+        <v>-1.292936</v>
+      </c>
+      <c r="V37" t="n">
         <v>-0.104202</v>
       </c>
-      <c r="T37" t="n">
+      <c r="W37" t="n">
         <v>-0.104213</v>
       </c>
-      <c r="U37" t="n">
+      <c r="X37" t="n">
         <v>1.088989</v>
       </c>
-      <c r="V37" t="n">
+      <c r="Y37" t="n">
         <v>0.905369</v>
       </c>
-      <c r="W37" t="n">
+      <c r="Z37" t="n">
         <v>1.202826</v>
       </c>
-      <c r="X37" t="n">
+      <c r="AA37" t="n">
         <v>1.632891</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="AB37" t="n">
         <v>4.237599</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AC37" t="n">
         <v>4.259387</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AD37" t="n">
         <v>3.707852</v>
       </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
       <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
         <v>0.03</v>
       </c>
-      <c r="AF37" t="n">
+      <c r="AI37" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AJ37" t="n">
         <v>0.04</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AK37" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4157,78 +4605,90 @@
         <v>108.02415</v>
       </c>
       <c r="I38" t="n">
+        <v>107.08272</v>
+      </c>
+      <c r="J38" t="n">
         <v>5.4481</v>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>5.4475</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>6216528</v>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>2384828</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>3831700</v>
       </c>
-      <c r="N38" t="n">
+      <c r="O38" t="n">
         <v>3.34</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q38" t="n">
         <v>3.83</v>
       </c>
-      <c r="P38" t="n">
+      <c r="R38" t="n">
         <v>27.49</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="S38" t="n">
         <v>372016</v>
       </c>
-      <c r="R38" t="n">
+      <c r="T38" t="n">
         <v>0.799855</v>
       </c>
-      <c r="S38" t="n">
+      <c r="U38" t="n">
+        <v>-2.707476</v>
+      </c>
+      <c r="V38" t="n">
         <v>-3.679149</v>
       </c>
-      <c r="T38" t="n">
+      <c r="W38" t="n">
         <v>-3.679539</v>
       </c>
-      <c r="U38" t="n">
+      <c r="X38" t="n">
         <v>1.323978</v>
       </c>
-      <c r="V38" t="n">
+      <c r="Y38" t="n">
         <v>1.72458</v>
       </c>
-      <c r="W38" t="n">
+      <c r="Z38" t="n">
         <v>1.076262</v>
       </c>
-      <c r="X38" t="n">
+      <c r="AA38" t="n">
         <v>0.7589089999999999</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="AB38" t="n">
         <v>4.42474</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AC38" t="n">
         <v>4.519075</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AD38" t="n">
         <v>4.091149</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AE38" t="n">
         <v>0.25</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AF38" t="n">
         <v>0.000342</v>
       </c>
-      <c r="AD38" t="n">
+      <c r="AG38" t="n">
         <v>0.000342</v>
       </c>
-      <c r="AE38" t="n">
+      <c r="AH38" t="n">
         <v>0.01</v>
       </c>
-      <c r="AF38" t="n">
+      <c r="AI38" t="n">
         <v>0.01</v>
       </c>
-      <c r="AG38" t="n">
+      <c r="AJ38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AK38" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -4258,78 +4718,90 @@
         <v>108.23273</v>
       </c>
       <c r="I39" t="n">
+        <v>109.17883</v>
+      </c>
+      <c r="J39" t="n">
         <v>5.7779</v>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>5.7773</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>6275117</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>2397533</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>3877584</v>
       </c>
-      <c r="N39" t="n">
+      <c r="O39" t="n">
         <v>3.3</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q39" t="n">
         <v>3.79</v>
       </c>
-      <c r="P39" t="n">
+      <c r="R39" t="n">
         <v>27.94</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="S39" t="n">
         <v>366096</v>
       </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
         <v>0.193086</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
+        <v>1.957468</v>
+      </c>
+      <c r="V39" t="n">
         <v>6.053487</v>
       </c>
-      <c r="T39" t="n">
+      <c r="W39" t="n">
         <v>6.054153</v>
       </c>
-      <c r="U39" t="n">
+      <c r="X39" t="n">
         <v>0.9424709999999999</v>
       </c>
-      <c r="V39" t="n">
+      <c r="Y39" t="n">
         <v>0.532743</v>
       </c>
-      <c r="W39" t="n">
+      <c r="Z39" t="n">
         <v>1.197484</v>
       </c>
-      <c r="X39" t="n">
+      <c r="AA39" t="n">
         <v>-1.591329</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="AB39" t="n">
         <v>4.758099</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AC39" t="n">
         <v>5.579866</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AD39" t="n">
         <v>4.600584</v>
       </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
         <v>0.000556</v>
       </c>
-      <c r="AD39" t="n">
+      <c r="AG39" t="n">
         <v>0.000556</v>
       </c>
-      <c r="AE39" t="n">
+      <c r="AH39" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AF39" t="n">
+      <c r="AI39" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AG39" t="n">
+      <c r="AJ39" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AK39" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -4359,78 +4831,90 @@
         <v>107.99539</v>
       </c>
       <c r="I40" t="n">
+        <v>105.48993</v>
+      </c>
+      <c r="J40" t="n">
         <v>6.0535</v>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>6.0529</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>6365690</v>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
         <v>2436022</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>3929668</v>
       </c>
-      <c r="N40" t="n">
+      <c r="O40" t="n">
         <v>3.27</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q40" t="n">
         <v>3.75</v>
       </c>
-      <c r="P40" t="n">
+      <c r="R40" t="n">
         <v>28.45</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="S40" t="n">
         <v>363003</v>
       </c>
-      <c r="R40" t="n">
+      <c r="T40" t="n">
         <v>-0.219287</v>
       </c>
-      <c r="S40" t="n">
+      <c r="U40" t="n">
+        <v>-3.378769</v>
+      </c>
+      <c r="V40" t="n">
         <v>4.769899</v>
       </c>
-      <c r="T40" t="n">
+      <c r="W40" t="n">
         <v>4.770394</v>
       </c>
-      <c r="U40" t="n">
+      <c r="X40" t="n">
         <v>1.443368</v>
       </c>
-      <c r="V40" t="n">
+      <c r="Y40" t="n">
         <v>1.605359</v>
       </c>
-      <c r="W40" t="n">
+      <c r="Z40" t="n">
         <v>1.343208</v>
       </c>
-      <c r="X40" t="n">
+      <c r="AA40" t="n">
         <v>-0.8448600000000001</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="AB40" t="n">
         <v>4.873011</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AC40" t="n">
         <v>6.325086</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AD40" t="n">
         <v>4.840925</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AE40" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AF40" t="n">
         <v>0.001412</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AG40" t="n">
         <v>0.001412</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AH40" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AF40" t="n">
+      <c r="AI40" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AJ40" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AG40" t="n">
+      <c r="AK40" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4460,78 +4944,90 @@
         <v>107.3722</v>
       </c>
       <c r="I41" t="n">
+        <v>104.15749</v>
+      </c>
+      <c r="J41" t="n">
         <v>6.1923</v>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>6.1917</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>6464602</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>2499177</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>3965425</v>
       </c>
-      <c r="N41" t="n">
+      <c r="O41" t="n">
         <v>3.08</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q41" t="n">
         <v>3.63</v>
       </c>
-      <c r="P41" t="n">
+      <c r="R41" t="n">
         <v>28.5</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="S41" t="n">
         <v>329730</v>
       </c>
-      <c r="R41" t="n">
+      <c r="T41" t="n">
         <v>-0.577052</v>
       </c>
-      <c r="S41" t="n">
+      <c r="U41" t="n">
+        <v>-1.263097</v>
+      </c>
+      <c r="V41" t="n">
         <v>2.292888</v>
       </c>
-      <c r="T41" t="n">
+      <c r="W41" t="n">
         <v>2.293116</v>
       </c>
-      <c r="U41" t="n">
+      <c r="X41" t="n">
         <v>1.55383</v>
       </c>
-      <c r="V41" t="n">
+      <c r="Y41" t="n">
         <v>2.592546</v>
       </c>
-      <c r="W41" t="n">
+      <c r="Z41" t="n">
         <v>0.909924</v>
       </c>
-      <c r="X41" t="n">
+      <c r="AA41" t="n">
         <v>-9.166040000000001</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="AB41" t="n">
         <v>4.831296</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AC41" t="n">
         <v>6.536174</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AD41" t="n">
         <v>4.767938</v>
       </c>
-      <c r="AB41" t="n">
+      <c r="AE41" t="n">
         <v>1</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AF41" t="n">
         <v>0.002578</v>
       </c>
-      <c r="AD41" t="n">
+      <c r="AG41" t="n">
         <v>0.002578</v>
       </c>
-      <c r="AE41" t="n">
+      <c r="AH41" t="n">
         <v>-0.19</v>
       </c>
-      <c r="AF41" t="n">
+      <c r="AI41" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="AJ41" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AG41" t="n">
+      <c r="AK41" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -4561,78 +5057,90 @@
         <v>108.10202</v>
       </c>
       <c r="I42" t="n">
+        <v>102.62361</v>
+      </c>
+      <c r="J42" t="n">
         <v>5.8301</v>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>5.8295</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>6465016</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>2451957</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>4013059</v>
       </c>
-      <c r="N42" t="n">
+      <c r="O42" t="n">
         <v>3.34</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q42" t="n">
         <v>3.89</v>
       </c>
-      <c r="P42" t="n">
+      <c r="R42" t="n">
         <v>29.88</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="S42" t="n">
         <v>328303</v>
       </c>
-      <c r="R42" t="n">
+      <c r="T42" t="n">
         <v>0.67971</v>
       </c>
-      <c r="S42" t="n">
+      <c r="U42" t="n">
+        <v>-1.472655</v>
+      </c>
+      <c r="V42" t="n">
         <v>-5.8492</v>
       </c>
-      <c r="T42" t="n">
+      <c r="W42" t="n">
         <v>-5.849767</v>
       </c>
-      <c r="U42" t="n">
+      <c r="X42" t="n">
         <v>0.006404</v>
       </c>
-      <c r="V42" t="n">
+      <c r="Y42" t="n">
         <v>-1.889422</v>
       </c>
-      <c r="W42" t="n">
+      <c r="Z42" t="n">
         <v>1.201233</v>
       </c>
-      <c r="X42" t="n">
+      <c r="AA42" t="n">
         <v>-0.432778</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="AB42" t="n">
         <v>4.559874</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AC42" t="n">
         <v>6.749097</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AD42" t="n">
         <v>4.174145</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AE42" t="n">
         <v>1</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AF42" t="n">
         <v>0.001675</v>
       </c>
-      <c r="AD42" t="n">
+      <c r="AG42" t="n">
         <v>0.001675</v>
       </c>
-      <c r="AE42" t="n">
+      <c r="AH42" t="n">
         <v>0.26</v>
       </c>
-      <c r="AF42" t="n">
+      <c r="AI42" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AJ42" t="n">
         <v>0.26</v>
       </c>
-      <c r="AG42" t="n">
+      <c r="AK42" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -4662,78 +5170,90 @@
         <v>108.64347</v>
       </c>
       <c r="I43" t="n">
+        <v>106.82695</v>
+      </c>
+      <c r="J43" t="n">
         <v>5.8488</v>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
         <v>5.8482</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>6511444</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>2477151</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>4034293</v>
       </c>
-      <c r="N43" t="n">
+      <c r="O43" t="n">
         <v>3.41</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q43" t="n">
         <v>3.96</v>
       </c>
-      <c r="P43" t="n">
+      <c r="R43" t="n">
         <v>30.53</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="S43" t="n">
         <v>332508</v>
       </c>
-      <c r="R43" t="n">
+      <c r="T43" t="n">
         <v>0.500869</v>
       </c>
-      <c r="S43" t="n">
+      <c r="U43" t="n">
+        <v>4.09588</v>
+      </c>
+      <c r="V43" t="n">
         <v>0.320749</v>
       </c>
-      <c r="T43" t="n">
+      <c r="W43" t="n">
         <v>0.320782</v>
       </c>
-      <c r="U43" t="n">
+      <c r="X43" t="n">
         <v>0.7181419999999999</v>
       </c>
-      <c r="V43" t="n">
+      <c r="Y43" t="n">
         <v>1.027506</v>
       </c>
-      <c r="W43" t="n">
+      <c r="Z43" t="n">
         <v>0.529123</v>
       </c>
-      <c r="X43" t="n">
+      <c r="AA43" t="n">
         <v>1.280829</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="AB43" t="n">
         <v>5.05763</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="AC43" t="n">
         <v>8.444549</v>
       </c>
-      <c r="AA43" t="n">
+      <c r="AD43" t="n">
         <v>4.866504</v>
       </c>
-      <c r="AB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC43" t="n">
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
         <v>0.003204</v>
       </c>
-      <c r="AD43" t="n">
+      <c r="AG43" t="n">
         <v>0.003204</v>
       </c>
-      <c r="AE43" t="n">
+      <c r="AH43" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AF43" t="n">
+      <c r="AI43" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AJ43" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AG43" t="n">
+      <c r="AK43" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -4763,78 +5283,90 @@
         <v>110.0586</v>
       </c>
       <c r="I44" t="n">
+        <v>114.02633</v>
+      </c>
+      <c r="J44" t="n">
         <v>5.7422</v>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>5.7416</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>6576464</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>2498262</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>4078202</v>
       </c>
-      <c r="N44" t="n">
+      <c r="O44" t="n">
         <v>3.44</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Q44" t="n">
         <v>4.03</v>
       </c>
-      <c r="P44" t="n">
+      <c r="R44" t="n">
         <v>31.34</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="S44" t="n">
         <v>336157</v>
       </c>
-      <c r="R44" t="n">
+      <c r="T44" t="n">
         <v>1.302545</v>
       </c>
-      <c r="S44" t="n">
+      <c r="U44" t="n">
+        <v>6.739292</v>
+      </c>
+      <c r="V44" t="n">
         <v>-1.822596</v>
       </c>
-      <c r="T44" t="n">
+      <c r="W44" t="n">
         <v>-1.822783</v>
       </c>
-      <c r="U44" t="n">
+      <c r="X44" t="n">
         <v>0.99855</v>
       </c>
-      <c r="V44" t="n">
+      <c r="Y44" t="n">
         <v>0.852229</v>
       </c>
-      <c r="W44" t="n">
+      <c r="Z44" t="n">
         <v>1.088394</v>
       </c>
-      <c r="X44" t="n">
+      <c r="AA44" t="n">
         <v>1.097417</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="AB44" t="n">
         <v>5.47719</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AC44" t="n">
         <v>8.586193</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AD44" t="n">
         <v>5.201441</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="AE44" t="n">
         <v>1</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AF44" t="n">
         <v>0.001471</v>
       </c>
-      <c r="AD44" t="n">
+      <c r="AG44" t="n">
         <v>0.001471</v>
       </c>
-      <c r="AE44" t="n">
+      <c r="AH44" t="n">
         <v>0.03</v>
       </c>
-      <c r="AF44" t="n">
+      <c r="AI44" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AJ44" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AG44" t="n">
+      <c r="AK44" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -4864,78 +5396,90 @@
         <v>109.59971</v>
       </c>
       <c r="I45" t="n">
+        <v>112.58856</v>
+      </c>
+      <c r="J45" t="n">
         <v>5.6608</v>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>5.6602</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>6623948</v>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" t="n">
         <v>2512426</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>4111522</v>
       </c>
-      <c r="N45" t="n">
+      <c r="O45" t="n">
         <v>3.67</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Q45" t="n">
         <v>4.25</v>
       </c>
-      <c r="P45" t="n">
+      <c r="R45" t="n">
         <v>31.63</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="S45" t="n">
         <v>340789</v>
       </c>
-      <c r="R45" t="n">
+      <c r="T45" t="n">
         <v>-0.416951</v>
       </c>
-      <c r="S45" t="n">
+      <c r="U45" t="n">
+        <v>-1.260911</v>
+      </c>
+      <c r="V45" t="n">
         <v>-1.417575</v>
       </c>
-      <c r="T45" t="n">
+      <c r="W45" t="n">
         <v>-1.417723</v>
       </c>
-      <c r="U45" t="n">
+      <c r="X45" t="n">
         <v>0.722029</v>
       </c>
-      <c r="V45" t="n">
+      <c r="Y45" t="n">
         <v>0.566954</v>
       </c>
-      <c r="W45" t="n">
+      <c r="Z45" t="n">
         <v>0.8170269999999999</v>
       </c>
-      <c r="X45" t="n">
+      <c r="AA45" t="n">
         <v>1.377928</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="AB45" t="n">
         <v>5.529729</v>
       </c>
-      <c r="Z45" t="n">
+      <c r="AC45" t="n">
         <v>8.510418</v>
       </c>
-      <c r="AA45" t="n">
+      <c r="AD45" t="n">
         <v>5.316736</v>
       </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" t="n">
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
         <v>0.002023</v>
       </c>
-      <c r="AD45" t="n">
+      <c r="AG45" t="n">
         <v>0.002023</v>
       </c>
-      <c r="AE45" t="n">
+      <c r="AH45" t="n">
         <v>0.23</v>
       </c>
-      <c r="AF45" t="n">
+      <c r="AI45" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AJ45" t="n">
         <v>0.22</v>
       </c>
-      <c r="AG45" t="n">
+      <c r="AK45" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -4965,78 +5509,90 @@
         <v>108.80425</v>
       </c>
       <c r="I46" t="n">
+        <v>108.55662</v>
+      </c>
+      <c r="J46" t="n">
         <v>5.7087</v>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>5.7081</v>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
         <v>6666287</v>
       </c>
-      <c r="L46" t="n">
+      <c r="M46" t="n">
         <v>2532708</v>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
         <v>4133579</v>
       </c>
-      <c r="N46" t="n">
+      <c r="O46" t="n">
         <v>3.72</v>
       </c>
-      <c r="O46" t="n">
+      <c r="P46" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Q46" t="n">
         <v>4.36</v>
       </c>
-      <c r="P46" t="n">
+      <c r="R46" t="n">
         <v>31.7</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="S46" t="n">
         <v>341459</v>
       </c>
-      <c r="R46" t="n">
+      <c r="T46" t="n">
         <v>-0.725787</v>
       </c>
-      <c r="S46" t="n">
+      <c r="U46" t="n">
+        <v>-3.581128</v>
+      </c>
+      <c r="V46" t="n">
         <v>0.84617</v>
       </c>
-      <c r="T46" t="n">
+      <c r="W46" t="n">
         <v>0.84626</v>
       </c>
-      <c r="U46" t="n">
+      <c r="X46" t="n">
         <v>0.639181</v>
       </c>
-      <c r="V46" t="n">
+      <c r="Y46" t="n">
         <v>0.807268</v>
       </c>
-      <c r="W46" t="n">
+      <c r="Z46" t="n">
         <v>0.5364679999999999</v>
       </c>
-      <c r="X46" t="n">
+      <c r="AA46" t="n">
         <v>0.196603</v>
       </c>
-      <c r="Y46" t="n">
+      <c r="AB46" t="n">
         <v>5.319636</v>
       </c>
-      <c r="Z46" t="n">
+      <c r="AC46" t="n">
         <v>7.026183</v>
       </c>
-      <c r="AA46" t="n">
+      <c r="AD46" t="n">
         <v>5.201418</v>
       </c>
-      <c r="AB46" t="n">
+      <c r="AE46" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC46" t="n">
+      <c r="AF46" t="n">
         <v>0.001405</v>
       </c>
-      <c r="AD46" t="n">
+      <c r="AG46" t="n">
         <v>0.001405</v>
       </c>
-      <c r="AE46" t="n">
+      <c r="AH46" t="n">
         <v>0.05</v>
       </c>
-      <c r="AF46" t="n">
+      <c r="AI46" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ46" t="n">
         <v>0.11</v>
       </c>
-      <c r="AG46" t="n">
+      <c r="AK46" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5066,78 +5622,90 @@
         <v>108.90168</v>
       </c>
       <c r="I47" t="n">
+        <v>107.36878</v>
+      </c>
+      <c r="J47" t="n">
         <v>5.4571</v>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>5.4565</v>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>6703663</v>
       </c>
-      <c r="L47" t="n">
+      <c r="M47" t="n">
         <v>2547693</v>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
         <v>4155970</v>
       </c>
-      <c r="N47" t="n">
+      <c r="O47" t="n">
         <v>3.75</v>
       </c>
-      <c r="O47" t="n">
+      <c r="P47" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Q47" t="n">
         <v>4.41</v>
       </c>
-      <c r="P47" t="n">
+      <c r="R47" t="n">
         <v>31.85</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="S47" t="n">
         <v>344440</v>
       </c>
-      <c r="R47" t="n">
+      <c r="T47" t="n">
         <v>0.089546</v>
       </c>
-      <c r="S47" t="n">
+      <c r="U47" t="n">
+        <v>-1.094212</v>
+      </c>
+      <c r="V47" t="n">
         <v>-4.407308</v>
       </c>
-      <c r="T47" t="n">
+      <c r="W47" t="n">
         <v>-4.407771</v>
       </c>
-      <c r="U47" t="n">
+      <c r="X47" t="n">
         <v>0.5606719999999999</v>
       </c>
-      <c r="V47" t="n">
+      <c r="Y47" t="n">
         <v>0.591659</v>
       </c>
-      <c r="W47" t="n">
+      <c r="Z47" t="n">
         <v>0.541686</v>
       </c>
-      <c r="X47" t="n">
+      <c r="AA47" t="n">
         <v>0.873018</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="AB47" t="n">
         <v>5.351165</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="AC47" t="n">
         <v>4.393261</v>
       </c>
-      <c r="AA47" t="n">
+      <c r="AD47" t="n">
         <v>5.18043</v>
       </c>
-      <c r="AB47" t="n">
+      <c r="AE47" t="n">
         <v>0.25</v>
       </c>
-      <c r="AC47" t="n">
+      <c r="AF47" t="n">
         <v>0.000633</v>
       </c>
-      <c r="AD47" t="n">
+      <c r="AG47" t="n">
         <v>0.000633</v>
       </c>
-      <c r="AE47" t="n">
+      <c r="AH47" t="n">
         <v>0.03</v>
       </c>
-      <c r="AF47" t="n">
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
         <v>0.05</v>
       </c>
-      <c r="AG47" t="n">
+      <c r="AK47" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5167,78 +5735,90 @@
         <v>108.39998</v>
       </c>
       <c r="I48" t="n">
+        <v>113.10359</v>
+      </c>
+      <c r="J48" t="n">
         <v>5.6021</v>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
         <v>5.6015</v>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" t="n">
         <v>6733209</v>
       </c>
-      <c r="L48" t="n">
+      <c r="M48" t="n">
         <v>2544400</v>
       </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
         <v>4188808</v>
       </c>
-      <c r="N48" t="n">
+      <c r="O48" t="n">
         <v>3.96</v>
       </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Q48" t="n">
         <v>4.66</v>
       </c>
-      <c r="P48" t="n">
+      <c r="R48" t="n">
         <v>31.75</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="S48" t="n">
         <v>345111</v>
       </c>
-      <c r="R48" t="n">
+      <c r="T48" t="n">
         <v>-0.460691</v>
       </c>
-      <c r="S48" t="n">
+      <c r="U48" t="n">
+        <v>5.341227</v>
+      </c>
+      <c r="V48" t="n">
         <v>2.657089</v>
       </c>
-      <c r="T48" t="n">
+      <c r="W48" t="n">
         <v>2.657381</v>
       </c>
-      <c r="U48" t="n">
+      <c r="X48" t="n">
         <v>0.440744</v>
       </c>
-      <c r="V48" t="n">
+      <c r="Y48" t="n">
         <v>-0.129254</v>
       </c>
-      <c r="W48" t="n">
+      <c r="Z48" t="n">
         <v>0.79014</v>
       </c>
-      <c r="X48" t="n">
+      <c r="AA48" t="n">
         <v>0.194809</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="AB48" t="n">
         <v>5.225222</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="AC48" t="n">
         <v>2.961368</v>
       </c>
-      <c r="AA48" t="n">
+      <c r="AD48" t="n">
         <v>5.127976</v>
       </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="n">
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
         <v>0.000562</v>
       </c>
-      <c r="AD48" t="n">
+      <c r="AG48" t="n">
         <v>0.000562</v>
       </c>
-      <c r="AE48" t="n">
+      <c r="AH48" t="n">
         <v>0.21</v>
       </c>
-      <c r="AF48" t="n">
+      <c r="AI48" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AJ48" t="n">
         <v>0.25</v>
       </c>
-      <c r="AG48" t="n">
+      <c r="AK48" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -5268,78 +5848,90 @@
         <v>108.79892</v>
       </c>
       <c r="I49" t="n">
+        <v>110.38013</v>
+      </c>
+      <c r="J49" t="n">
         <v>5.4264</v>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
         <v>5.4258</v>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
         <v>6774436</v>
       </c>
-      <c r="L49" t="n">
+      <c r="M49" t="n">
         <v>2546265</v>
       </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
         <v>4228171</v>
       </c>
-      <c r="N49" t="n">
+      <c r="O49" t="n">
         <v>4.14</v>
       </c>
-      <c r="O49" t="n">
+      <c r="P49" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q49" t="n">
         <v>4.92</v>
       </c>
-      <c r="P49" t="n">
+      <c r="R49" t="n">
         <v>31.87</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="S49" t="n">
         <v>350767</v>
       </c>
-      <c r="R49" t="n">
+      <c r="T49" t="n">
         <v>0.368026</v>
       </c>
-      <c r="S49" t="n">
+      <c r="U49" t="n">
+        <v>-2.407934</v>
+      </c>
+      <c r="V49" t="n">
         <v>-3.136324</v>
       </c>
-      <c r="T49" t="n">
+      <c r="W49" t="n">
         <v>-3.13666</v>
       </c>
-      <c r="U49" t="n">
+      <c r="X49" t="n">
         <v>0.612293</v>
       </c>
-      <c r="V49" t="n">
+      <c r="Y49" t="n">
         <v>0.073298</v>
       </c>
-      <c r="W49" t="n">
+      <c r="Z49" t="n">
         <v>0.9397180000000001</v>
       </c>
-      <c r="X49" t="n">
+      <c r="AA49" t="n">
         <v>1.638893</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="AB49" t="n">
         <v>5.130501</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="AC49" t="n">
         <v>3.033233</v>
       </c>
-      <c r="AA49" t="n">
+      <c r="AD49" t="n">
         <v>5.054283</v>
       </c>
-      <c r="AB49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
       <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
         <v>0.18</v>
       </c>
-      <c r="AF49" t="n">
+      <c r="AI49" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AJ49" t="n">
         <v>0.26</v>
       </c>
-      <c r="AG49" t="n">
+      <c r="AK49" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5369,78 +5961,90 @@
         <v>108.7209</v>
       </c>
       <c r="I50" t="n">
+        <v>109.48882</v>
+      </c>
+      <c r="J50" t="n">
         <v>5.3186</v>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
         <v>5.318</v>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" t="n">
         <v>6852705</v>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" t="n">
         <v>2589817</v>
       </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
         <v>4262888</v>
       </c>
-      <c r="N50" t="n">
+      <c r="O50" t="n">
         <v>4.09</v>
       </c>
-      <c r="O50" t="n">
+      <c r="P50" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Q50" t="n">
         <v>4.89</v>
       </c>
-      <c r="P50" t="n">
+      <c r="R50" t="n">
         <v>31.47</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="S50" t="n">
         <v>356582</v>
       </c>
-      <c r="R50" t="n">
+      <c r="T50" t="n">
         <v>-0.07171</v>
       </c>
-      <c r="S50" t="n">
+      <c r="U50" t="n">
+        <v>-0.807491</v>
+      </c>
+      <c r="V50" t="n">
         <v>-1.986584</v>
       </c>
-      <c r="T50" t="n">
+      <c r="W50" t="n">
         <v>-1.986804</v>
       </c>
-      <c r="U50" t="n">
+      <c r="X50" t="n">
         <v>1.155358</v>
       </c>
-      <c r="V50" t="n">
+      <c r="Y50" t="n">
         <v>1.710427</v>
       </c>
-      <c r="W50" t="n">
+      <c r="Z50" t="n">
         <v>0.821088</v>
       </c>
-      <c r="X50" t="n">
+      <c r="AA50" t="n">
         <v>1.657796</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="AB50" t="n">
         <v>5.172369</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="AC50" t="n">
         <v>2.828436</v>
       </c>
-      <c r="AA50" t="n">
+      <c r="AD50" t="n">
         <v>5.096104</v>
       </c>
-      <c r="AB50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
       <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AF50" t="n">
+      <c r="AI50" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AJ50" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG50" t="n">
+      <c r="AK50" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -5470,78 +6074,90 @@
         <v>108.73364</v>
       </c>
       <c r="I51" t="n">
+        <v>110.06407</v>
+      </c>
+      <c r="J51" t="n">
         <v>5.3843</v>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
         <v>5.3837</v>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
         <v>6923886</v>
       </c>
-      <c r="L51" t="n">
+      <c r="M51" t="n">
         <v>2597630</v>
       </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
         <v>4326256</v>
       </c>
-      <c r="N51" t="n">
+      <c r="O51" t="n">
         <v>4.18</v>
       </c>
-      <c r="O51" t="n">
+      <c r="P51" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Q51" t="n">
         <v>4.99</v>
       </c>
-      <c r="P51" t="n">
+      <c r="R51" t="n">
         <v>32.04</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="S51" t="n">
         <v>357103</v>
       </c>
-      <c r="R51" t="n">
+      <c r="T51" t="n">
         <v>0.011718</v>
       </c>
-      <c r="S51" t="n">
+      <c r="U51" t="n">
+        <v>0.525396</v>
+      </c>
+      <c r="V51" t="n">
         <v>1.235287</v>
       </c>
-      <c r="T51" t="n">
+      <c r="W51" t="n">
         <v>1.235427</v>
       </c>
-      <c r="U51" t="n">
+      <c r="X51" t="n">
         <v>1.038729</v>
       </c>
-      <c r="V51" t="n">
+      <c r="Y51" t="n">
         <v>0.301682</v>
       </c>
-      <c r="W51" t="n">
+      <c r="Z51" t="n">
         <v>1.486504</v>
       </c>
-      <c r="X51" t="n">
+      <c r="AA51" t="n">
         <v>0.146109</v>
       </c>
-      <c r="Y51" t="n">
+      <c r="AB51" t="n">
         <v>4.680811</v>
       </c>
-      <c r="Z51" t="n">
+      <c r="AC51" t="n">
         <v>0.924206</v>
       </c>
-      <c r="AA51" t="n">
+      <c r="AD51" t="n">
         <v>4.490243</v>
       </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
       <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
         <v>0.09</v>
       </c>
-      <c r="AF51" t="n">
+      <c r="AI51" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AJ51" t="n">
         <v>0.1</v>
       </c>
-      <c r="AG51" t="n">
+      <c r="AK51" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -5571,78 +6187,90 @@
         <v>109.24151</v>
       </c>
       <c r="I52" t="n">
+        <v>106.59541</v>
+      </c>
+      <c r="J52" t="n">
         <v>5.3338</v>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
         <v>5.3332</v>
       </c>
-      <c r="K52" t="n">
+      <c r="L52" t="n">
         <v>7004223</v>
       </c>
-      <c r="L52" t="n">
+      <c r="M52" t="n">
         <v>2616902</v>
       </c>
-      <c r="M52" t="n">
+      <c r="N52" t="n">
         <v>4387321</v>
       </c>
-      <c r="N52" t="n">
+      <c r="O52" t="n">
         <v>4.24</v>
       </c>
-      <c r="O52" t="n">
+      <c r="P52" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q52" t="n">
         <v>5.12</v>
       </c>
-      <c r="P52" t="n">
+      <c r="R52" t="n">
         <v>32.2</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="S52" t="n">
         <v>360578</v>
       </c>
-      <c r="R52" t="n">
+      <c r="T52" t="n">
         <v>0.467077</v>
       </c>
-      <c r="S52" t="n">
+      <c r="U52" t="n">
+        <v>-3.151492</v>
+      </c>
+      <c r="V52" t="n">
         <v>-0.937912</v>
       </c>
-      <c r="T52" t="n">
+      <c r="W52" t="n">
         <v>-0.938017</v>
       </c>
-      <c r="U52" t="n">
+      <c r="X52" t="n">
         <v>1.160288</v>
       </c>
-      <c r="V52" t="n">
+      <c r="Y52" t="n">
         <v>0.741907</v>
       </c>
-      <c r="W52" t="n">
+      <c r="Z52" t="n">
         <v>1.411498</v>
       </c>
-      <c r="X52" t="n">
+      <c r="AA52" t="n">
         <v>0.973109</v>
       </c>
-      <c r="Y52" t="n">
+      <c r="AB52" t="n">
         <v>4.461836</v>
       </c>
-      <c r="Z52" t="n">
+      <c r="AC52" t="n">
         <v>-0.101973</v>
       </c>
-      <c r="AA52" t="n">
+      <c r="AD52" t="n">
         <v>4.177803</v>
       </c>
-      <c r="AB52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC52" t="n">
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="n">
         <v>-0</v>
       </c>
-      <c r="AD52" t="n">
+      <c r="AG52" t="n">
         <v>-0</v>
       </c>
-      <c r="AE52" t="n">
+      <c r="AH52" t="n">
         <v>0.06</v>
       </c>
-      <c r="AF52" t="n">
+      <c r="AI52" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AJ52" t="n">
         <v>0.13</v>
       </c>
-      <c r="AG52" t="n">
+      <c r="AK52" t="n">
         <v>0.16</v>
       </c>
     </row>
@@ -5672,78 +6300,90 @@
         <v>109.46142</v>
       </c>
       <c r="I53" t="n">
+        <v>107.19319</v>
+      </c>
+      <c r="J53" t="n">
         <v>5.5024</v>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>5.5018</v>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" t="n">
         <v>7137252</v>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" t="n">
         <v>2701735</v>
       </c>
-      <c r="M53" t="n">
+      <c r="N53" t="n">
         <v>4435517</v>
       </c>
-      <c r="N53" t="n">
+      <c r="O53" t="n">
         <v>4.2</v>
       </c>
-      <c r="O53" t="n">
+      <c r="P53" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q53" t="n">
         <v>5.12</v>
       </c>
-      <c r="P53" t="n">
+      <c r="R53" t="n">
         <v>31.87</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="S53" t="n">
         <v>358234</v>
       </c>
-      <c r="R53" t="n">
+      <c r="T53" t="n">
         <v>0.201306</v>
       </c>
-      <c r="S53" t="n">
+      <c r="U53" t="n">
+        <v>0.560793</v>
+      </c>
+      <c r="V53" t="n">
         <v>3.160973</v>
       </c>
-      <c r="T53" t="n">
+      <c r="W53" t="n">
         <v>3.161329</v>
       </c>
-      <c r="U53" t="n">
+      <c r="X53" t="n">
         <v>1.899268</v>
       </c>
-      <c r="V53" t="n">
+      <c r="Y53" t="n">
         <v>3.241734</v>
       </c>
-      <c r="W53" t="n">
+      <c r="Z53" t="n">
         <v>1.098529</v>
       </c>
-      <c r="X53" t="n">
+      <c r="AA53" t="n">
         <v>-0.650067</v>
       </c>
-      <c r="Y53" t="n">
+      <c r="AB53" t="n">
         <v>4.264385</v>
       </c>
-      <c r="Z53" t="n">
+      <c r="AC53" t="n">
         <v>-1.042167</v>
       </c>
-      <c r="AA53" t="n">
+      <c r="AD53" t="n">
         <v>3.897866</v>
       </c>
-      <c r="AB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
       <c r="AE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="n">
+      <c r="AI53" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -5773,78 +6413,90 @@
         <v>110.07661</v>
       </c>
       <c r="I54" t="n">
+        <v>103.78191</v>
+      </c>
+      <c r="J54" t="n">
         <v>5.2301</v>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
         <v>5.2295</v>
       </c>
-      <c r="K54" t="n">
+      <c r="L54" t="n">
         <v>7130762</v>
       </c>
-      <c r="L54" t="n">
+      <c r="M54" t="n">
         <v>2654220</v>
       </c>
-      <c r="M54" t="n">
+      <c r="N54" t="n">
         <v>4476542</v>
       </c>
-      <c r="N54" t="n">
+      <c r="O54" t="n">
         <v>4.44</v>
       </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q54" t="n">
         <v>5.38</v>
       </c>
-      <c r="P54" t="n">
+      <c r="R54" t="n">
         <v>32.45</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="S54" t="n">
         <v>364367</v>
       </c>
-      <c r="R54" t="n">
+      <c r="T54" t="n">
         <v>0.562015</v>
       </c>
-      <c r="S54" t="n">
+      <c r="U54" t="n">
+        <v>-3.182366</v>
+      </c>
+      <c r="V54" t="n">
         <v>-4.94875</v>
       </c>
-      <c r="T54" t="n">
+      <c r="W54" t="n">
         <v>-4.949289</v>
       </c>
-      <c r="U54" t="n">
+      <c r="X54" t="n">
         <v>-0.090931</v>
       </c>
-      <c r="V54" t="n">
+      <c r="Y54" t="n">
         <v>-1.758685</v>
       </c>
-      <c r="W54" t="n">
+      <c r="Z54" t="n">
         <v>0.92492</v>
       </c>
-      <c r="X54" t="n">
+      <c r="AA54" t="n">
         <v>1.712009</v>
       </c>
-      <c r="Y54" t="n">
+      <c r="AB54" t="n">
         <v>4.441351</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="AC54" t="n">
         <v>-0.903999</v>
       </c>
-      <c r="AA54" t="n">
+      <c r="AD54" t="n">
         <v>4.303068</v>
       </c>
-      <c r="AB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>0</v>
-      </c>
       <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
         <v>0.24</v>
       </c>
-      <c r="AF54" t="n">
+      <c r="AI54" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AJ54" t="n">
         <v>0.26</v>
       </c>
-      <c r="AG54" t="n">
+      <c r="AK54" t="n">
         <v>0.58</v>
       </c>
     </row>
@@ -5874,78 +6526,90 @@
         <v>110.77581</v>
       </c>
       <c r="I55" t="n">
+        <v>106.77083</v>
+      </c>
+      <c r="J55" t="n">
         <v>5.1495</v>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>5.1489</v>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" t="n">
         <v>7157783</v>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" t="n">
         <v>2656484</v>
       </c>
-      <c r="M55" t="n">
+      <c r="N55" t="n">
         <v>4501299</v>
       </c>
-      <c r="N55" t="n">
+      <c r="O55" t="n">
         <v>4.64</v>
       </c>
-      <c r="O55" t="n">
+      <c r="P55" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="Q55" t="n">
         <v>5.56</v>
       </c>
-      <c r="P55" t="n">
+      <c r="R55" t="n">
         <v>32.63</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="S55" t="n">
         <v>371074</v>
       </c>
-      <c r="R55" t="n">
+      <c r="T55" t="n">
         <v>0.635194</v>
       </c>
-      <c r="S55" t="n">
+      <c r="U55" t="n">
+        <v>2.880001</v>
+      </c>
+      <c r="V55" t="n">
         <v>-1.54108</v>
       </c>
-      <c r="T55" t="n">
+      <c r="W55" t="n">
         <v>-1.541256</v>
       </c>
-      <c r="U55" t="n">
+      <c r="X55" t="n">
         <v>0.378936</v>
       </c>
-      <c r="V55" t="n">
+      <c r="Y55" t="n">
         <v>0.085298</v>
       </c>
-      <c r="W55" t="n">
+      <c r="Z55" t="n">
         <v>0.553038</v>
       </c>
-      <c r="X55" t="n">
+      <c r="AA55" t="n">
         <v>1.840727</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="AB55" t="n">
         <v>3.812497</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="AC55" t="n">
         <v>-2.659212</v>
       </c>
-      <c r="AA55" t="n">
+      <c r="AD55" t="n">
         <v>3.357475</v>
       </c>
-      <c r="AB55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
       <c r="AE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
         <v>0.2</v>
       </c>
-      <c r="AF55" t="n">
+      <c r="AI55" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AJ55" t="n">
         <v>0.18</v>
       </c>
-      <c r="AG55" t="n">
+      <c r="AK55" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -5975,78 +6639,90 @@
         <v>110.60765</v>
       </c>
       <c r="I56" t="n">
+        <v>118.00063</v>
+      </c>
+      <c r="J56" t="n">
         <v>5.2194</v>
       </c>
-      <c r="J56" t="n">
+      <c r="K56" t="n">
         <v>5.2188</v>
       </c>
-      <c r="K56" t="n">
+      <c r="L56" t="n">
         <v>7240557</v>
       </c>
-      <c r="L56" t="n">
+      <c r="M56" t="n">
         <v>2687535</v>
       </c>
-      <c r="M56" t="n">
+      <c r="N56" t="n">
         <v>4553022</v>
       </c>
-      <c r="N56" t="n">
+      <c r="O56" t="n">
         <v>4.52</v>
       </c>
-      <c r="O56" t="n">
+      <c r="P56" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="Q56" t="n">
         <v>5.39</v>
       </c>
-      <c r="P56" t="n">
+      <c r="R56" t="n">
         <v>32.84</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="S56" t="n">
         <v>362002</v>
       </c>
-      <c r="R56" t="n">
+      <c r="T56" t="n">
         <v>-0.151802</v>
       </c>
-      <c r="S56" t="n">
+      <c r="U56" t="n">
+        <v>10.517667</v>
+      </c>
+      <c r="V56" t="n">
         <v>1.357413</v>
       </c>
-      <c r="T56" t="n">
+      <c r="W56" t="n">
         <v>1.357572</v>
       </c>
-      <c r="U56" t="n">
+      <c r="X56" t="n">
         <v>1.15642</v>
       </c>
-      <c r="V56" t="n">
+      <c r="Y56" t="n">
         <v>1.168876</v>
       </c>
-      <c r="W56" t="n">
+      <c r="Z56" t="n">
         <v>1.149068</v>
       </c>
-      <c r="X56" t="n">
+      <c r="AA56" t="n">
         <v>-2.444795</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="AB56" t="n">
         <v>4.142847</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="AC56" t="n">
         <v>-1.819225</v>
       </c>
-      <c r="AA56" t="n">
+      <c r="AD56" t="n">
         <v>3.768807</v>
       </c>
-      <c r="AB56" t="n">
+      <c r="AE56" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AC56" t="n">
+      <c r="AF56" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="AD56" t="n">
+      <c r="AG56" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="AE56" t="n">
+      <c r="AH56" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AF56" t="n">
+      <c r="AI56" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AJ56" t="n">
         <v>-0.17</v>
       </c>
-      <c r="AG56" t="n">
+      <c r="AK56" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -6076,78 +6752,90 @@
         <v>110.90086</v>
       </c>
       <c r="I57" t="n">
+        <v>113.89942</v>
+      </c>
+      <c r="J57" t="n">
         <v>4.9886</v>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
         <v>4.988</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
         <v>7259766</v>
       </c>
-      <c r="L57" t="n">
+      <c r="M57" t="n">
         <v>2685397</v>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
         <v>4574368</v>
       </c>
-      <c r="N57" t="n">
+      <c r="O57" t="n">
         <v>4.64</v>
       </c>
-      <c r="O57" t="n">
+      <c r="P57" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q57" t="n">
         <v>5.51</v>
       </c>
-      <c r="P57" t="n">
+      <c r="R57" t="n">
         <v>33.36</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="S57" t="n">
         <v>366913</v>
       </c>
-      <c r="R57" t="n">
+      <c r="T57" t="n">
         <v>0.26509</v>
       </c>
-      <c r="S57" t="n">
+      <c r="U57" t="n">
+        <v>-3.475583</v>
+      </c>
+      <c r="V57" t="n">
         <v>-4.421964</v>
       </c>
-      <c r="T57" t="n">
+      <c r="W57" t="n">
         <v>-4.422473</v>
       </c>
-      <c r="U57" t="n">
+      <c r="X57" t="n">
         <v>0.265297</v>
       </c>
-      <c r="V57" t="n">
+      <c r="Y57" t="n">
         <v>-0.079552</v>
       </c>
-      <c r="W57" t="n">
+      <c r="Z57" t="n">
         <v>0.468831</v>
       </c>
-      <c r="X57" t="n">
+      <c r="AA57" t="n">
         <v>1.356622</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="AB57" t="n">
         <v>4.39172</v>
       </c>
-      <c r="Z57" t="n">
+      <c r="AC57" t="n">
         <v>0.619623</v>
       </c>
-      <c r="AA57" t="n">
+      <c r="AD57" t="n">
         <v>4.109608</v>
       </c>
-      <c r="AB57" t="n">
+      <c r="AE57" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AC57" t="n">
+      <c r="AF57" t="n">
         <v>-0.000554</v>
       </c>
-      <c r="AD57" t="n">
+      <c r="AG57" t="n">
         <v>-0.000554</v>
       </c>
-      <c r="AE57" t="n">
+      <c r="AH57" t="n">
         <v>0.12</v>
       </c>
-      <c r="AF57" t="n">
+      <c r="AI57" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AJ57" t="n">
         <v>0.12</v>
       </c>
-      <c r="AG57" t="n">
+      <c r="AK57" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -6177,78 +6865,90 @@
         <v>110.93102</v>
       </c>
       <c r="I58" t="n">
+        <v>109.53002</v>
+      </c>
+      <c r="J58" t="n">
         <v>5.0569</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>5.0563</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>7305306</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>2708154</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>4597152</v>
       </c>
-      <c r="N58" t="n">
+      <c r="O58" t="n">
         <v>4.74</v>
       </c>
-      <c r="O58" t="n">
+      <c r="P58" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q58" t="n">
         <v>5.62</v>
       </c>
-      <c r="P58" t="n">
+      <c r="R58" t="n">
         <v>33.1</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="S58" t="n">
         <v>371137</v>
       </c>
-      <c r="R58" t="n">
+      <c r="T58" t="n">
         <v>0.027195</v>
       </c>
-      <c r="S58" t="n">
+      <c r="U58" t="n">
+        <v>-3.836192</v>
+      </c>
+      <c r="V58" t="n">
         <v>1.369122</v>
       </c>
-      <c r="T58" t="n">
+      <c r="W58" t="n">
         <v>1.369286</v>
       </c>
-      <c r="U58" t="n">
+      <c r="X58" t="n">
         <v>0.627293</v>
       </c>
-      <c r="V58" t="n">
+      <c r="Y58" t="n">
         <v>0.847435</v>
       </c>
-      <c r="W58" t="n">
+      <c r="Z58" t="n">
         <v>0.49808</v>
       </c>
-      <c r="X58" t="n">
+      <c r="AA58" t="n">
         <v>1.151227</v>
       </c>
-      <c r="Y58" t="n">
+      <c r="AB58" t="n">
         <v>4.724907</v>
       </c>
-      <c r="Z58" t="n">
+      <c r="AC58" t="n">
         <v>1.964454</v>
       </c>
-      <c r="AA58" t="n">
+      <c r="AD58" t="n">
         <v>4.420848</v>
       </c>
-      <c r="AB58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC58" t="n">
+      <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="n">
         <v>-0.0008229999999999999</v>
       </c>
-      <c r="AD58" t="n">
+      <c r="AG58" t="n">
         <v>-0.0008229999999999999</v>
       </c>
-      <c r="AE58" t="n">
+      <c r="AH58" t="n">
         <v>0.1</v>
       </c>
-      <c r="AF58" t="n">
+      <c r="AI58" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AJ58" t="n">
         <v>0.11</v>
       </c>
-      <c r="AG58" t="n">
+      <c r="AK58" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -6278,78 +6978,90 @@
         <v>110.22154</v>
       </c>
       <c r="I59" t="n">
+        <v>109.89427</v>
+      </c>
+      <c r="J59" t="n">
         <v>5.1766</v>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
         <v>5.176</v>
       </c>
-      <c r="K59" t="n">
+      <c r="L59" t="n">
         <v>7353293</v>
       </c>
-      <c r="L59" t="n">
+      <c r="M59" t="n">
         <v>2750625</v>
       </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
         <v>4602668</v>
       </c>
-      <c r="N59" t="n">
+      <c r="O59" t="n">
         <v>4.58</v>
       </c>
-      <c r="O59" t="n">
+      <c r="P59" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="Q59" t="n">
         <v>5.42</v>
       </c>
-      <c r="P59" t="n">
+      <c r="R59" t="n">
         <v>33.33</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="S59" t="n">
         <v>367558</v>
       </c>
-      <c r="R59" t="n">
+      <c r="T59" t="n">
         <v>-0.6395690000000001</v>
       </c>
-      <c r="S59" t="n">
+      <c r="U59" t="n">
+        <v>0.332557</v>
+      </c>
+      <c r="V59" t="n">
         <v>2.367063</v>
       </c>
-      <c r="T59" t="n">
+      <c r="W59" t="n">
         <v>2.367344</v>
       </c>
-      <c r="U59" t="n">
+      <c r="X59" t="n">
         <v>0.656879</v>
       </c>
-      <c r="V59" t="n">
+      <c r="Y59" t="n">
         <v>1.568264</v>
       </c>
-      <c r="W59" t="n">
+      <c r="Z59" t="n">
         <v>0.119987</v>
       </c>
-      <c r="X59" t="n">
+      <c r="AA59" t="n">
         <v>-0.964334</v>
       </c>
-      <c r="Y59" t="n">
+      <c r="AB59" t="n">
         <v>4.641328</v>
       </c>
-      <c r="Z59" t="n">
+      <c r="AC59" t="n">
         <v>3.177699</v>
       </c>
-      <c r="AA59" t="n">
+      <c r="AD59" t="n">
         <v>4.327084</v>
       </c>
-      <c r="AB59" t="n">
+      <c r="AE59" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AC59" t="n">
+      <c r="AF59" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AD59" t="n">
+      <c r="AG59" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AE59" t="n">
+      <c r="AH59" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AF59" t="n">
+      <c r="AI59" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AJ59" t="n">
         <v>-0.2</v>
       </c>
-      <c r="AG59" t="n">
+      <c r="AK59" t="n">
         <v>0.23</v>
       </c>
     </row>
@@ -6376,77 +7088,85 @@
         <v>-0.01</v>
       </c>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="n">
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="n">
         <v>5.0773</v>
       </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
         <v>5.0767</v>
       </c>
-      <c r="K60" t="n">
+      <c r="L60" t="n">
         <v>7372243</v>
       </c>
-      <c r="L60" t="n">
+      <c r="M60" t="n">
         <v>2731513</v>
       </c>
-      <c r="M60" t="n">
+      <c r="N60" t="n">
         <v>4640730</v>
       </c>
-      <c r="N60" t="n">
+      <c r="O60" t="n">
         <v>4.88</v>
       </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="Q60" t="n">
         <v>5.81</v>
       </c>
-      <c r="P60" t="n">
+      <c r="R60" t="n">
         <v>32.08</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="S60" t="n">
         <v>369742</v>
       </c>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="n">
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="n">
         <v>-1.918247</v>
       </c>
-      <c r="T60" t="n">
+      <c r="W60" t="n">
         <v>-1.91847</v>
       </c>
-      <c r="U60" t="n">
+      <c r="X60" t="n">
         <v>0.257708</v>
       </c>
-      <c r="V60" t="n">
+      <c r="Y60" t="n">
         <v>-0.694824</v>
       </c>
-      <c r="W60" t="n">
+      <c r="Z60" t="n">
         <v>0.826955</v>
       </c>
-      <c r="X60" t="n">
+      <c r="AA60" t="n">
         <v>0.5941920000000001</v>
       </c>
-      <c r="Y60" t="n">
+      <c r="AB60" t="n">
         <v>4.443025</v>
       </c>
-      <c r="Z60" t="n">
+      <c r="AC60" t="n">
         <v>2.772183</v>
       </c>
-      <c r="AA60" t="n">
+      <c r="AD60" t="n">
         <v>4.098046</v>
       </c>
-      <c r="AB60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC60" t="n">
+      <c r="AE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="AD60" t="n">
+      <c r="AG60" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="AE60" t="n">
+      <c r="AH60" t="n">
         <v>0.3</v>
       </c>
-      <c r="AF60" t="n">
+      <c r="AI60" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AJ60" t="n">
         <v>0.39</v>
       </c>
-      <c r="AG60" t="n">
+      <c r="AK60" t="n">
         <v>-1.25</v>
       </c>
     </row>
@@ -6473,55 +7193,59 @@
         <v>-0.32</v>
       </c>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="n">
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="n">
         <v>5.1816</v>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
         <v>5.181</v>
       </c>
-      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="n">
-        <v>372616</v>
-      </c>
+      <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="n">
+        <v>372616</v>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="n">
         <v>2.054241</v>
       </c>
-      <c r="T61" t="n">
+      <c r="W61" t="n">
         <v>2.054484</v>
       </c>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
-      <c r="X61" t="n">
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="n">
         <v>0.777299</v>
       </c>
-      <c r="Y61" t="n">
+      <c r="AB61" t="n">
         <v>4.223453</v>
       </c>
-      <c r="Z61" t="n">
+      <c r="AC61" t="n">
         <v>2.178243</v>
       </c>
-      <c r="AA61" t="n">
+      <c r="AD61" t="n">
         <v>3.983297</v>
       </c>
-      <c r="AB61" t="n">
+      <c r="AE61" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AC61" t="n">
+      <c r="AF61" t="n">
         <v>-0.0007470000000000001</v>
       </c>
-      <c r="AD61" t="n">
+      <c r="AG61" t="n">
         <v>-0.0007470000000000001</v>
       </c>
-      <c r="AE61" t="inlineStr"/>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -6540,13 +7264,13 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="n">
-        <v>5.1149</v>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>5.1143</v>
-      </c>
-      <c r="K62" t="inlineStr"/>
+        <v>5.0918</v>
+      </c>
+      <c r="K62" t="n">
+        <v>5.0912</v>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -6554,31 +7278,35 @@
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
-      <c r="S62" t="n">
-        <v>-1.287247</v>
-      </c>
-      <c r="T62" t="n">
-        <v>-1.287396</v>
-      </c>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
+      <c r="V62" t="n">
+        <v>-1.733055</v>
+      </c>
+      <c r="W62" t="n">
+        <v>-1.733256</v>
+      </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
-      <c r="AB62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC62" t="n">
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="n">
         <v>-0.000124</v>
       </c>
-      <c r="AD62" t="n">
+      <c r="AG62" t="n">
         <v>-0.000124</v>
       </c>
-      <c r="AE62" t="inlineStr"/>
-      <c r="AF62" t="inlineStr"/>
-      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK62"/>
+  <dimension ref="A1:AI62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,165 +443,155 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>ipca</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
           <t>igp_m</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>inpc</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ibc_br_sa</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ibc_br</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>cambio_venda_usd</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>cambio_compra_usd</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>saldo_credito_total</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>saldo_credito_pj</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>saldo_credito_pf</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inadimplencia_total</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inadimplencia_pj</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inadimplencia_pf</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>ipca_acum_12m</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>inpc_acum_12m</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>dif_selic_over</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dif_cdi</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -621,50 +611,48 @@
         <v>0.02154</v>
       </c>
       <c r="E2" t="n">
-        <v>1.16</v>
+        <v>-0.64</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.64</v>
+        <v>1.2</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2</v>
+        <v>96.95313</v>
       </c>
       <c r="H2" t="n">
-        <v>96.95313</v>
+        <v>97.10569</v>
       </c>
       <c r="I2" t="n">
-        <v>97.10569</v>
+        <v>5.4394</v>
       </c>
       <c r="J2" t="n">
-        <v>5.4394</v>
+        <v>5.4388</v>
       </c>
       <c r="K2" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="L2" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="M2" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="N2" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="O2" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="P2" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="R2" t="n">
-        <v>21.42</v>
-      </c>
-      <c r="S2" t="n">
         <v>368886</v>
       </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -681,8 +669,6 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -698,96 +684,92 @@
         <v>0.024244</v>
       </c>
       <c r="E3" t="n">
-        <v>1.25</v>
+        <v>0.64</v>
       </c>
       <c r="F3" t="n">
-        <v>0.64</v>
+        <v>1.16</v>
       </c>
       <c r="G3" t="n">
-        <v>1.16</v>
+        <v>97.47790999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>97.47790999999999</v>
+        <v>96.52863000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>96.52863000000001</v>
+        <v>5.643</v>
       </c>
       <c r="J3" t="n">
-        <v>5.643</v>
+        <v>5.6424</v>
       </c>
       <c r="K3" t="n">
-        <v>5.6424</v>
+        <v>4511956</v>
       </c>
       <c r="L3" t="n">
-        <v>4511956</v>
+        <v>1910940</v>
       </c>
       <c r="M3" t="n">
-        <v>1910940</v>
+        <v>2601017</v>
       </c>
       <c r="N3" t="n">
-        <v>2601017</v>
+        <v>2.33</v>
       </c>
       <c r="O3" t="n">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="R3" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="S3" t="n">
-        <v>367927</v>
+        <v>0.541272</v>
       </c>
       <c r="T3" t="n">
-        <v>0.541272</v>
+        <v>-0.59426</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.59426</v>
+        <v>3.74306</v>
       </c>
       <c r="V3" t="n">
-        <v>3.74306</v>
+        <v>3.743473</v>
       </c>
       <c r="W3" t="n">
-        <v>3.743473</v>
+        <v>1.596467</v>
       </c>
       <c r="X3" t="n">
-        <v>1.596467</v>
+        <v>0.888065</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.888065</v>
+        <v>2.123375</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.123375</v>
-      </c>
-      <c r="AA3" t="n">
         <v>-0.259972</v>
       </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.002704</v>
+      </c>
       <c r="AE3" t="n">
-        <v>1.5</v>
+        <v>0.002704</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.002704</v>
+        <v>-0.01</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.002704</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AK3" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -805,96 +787,92 @@
         <v>0.029256</v>
       </c>
       <c r="E4" t="n">
-        <v>0.95</v>
+        <v>0.02</v>
       </c>
       <c r="F4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G4" t="n">
+        <v>99.05295</v>
+      </c>
+      <c r="H4" t="n">
+        <v>97.85433</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5.6199</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5.6193</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4597507</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1933111</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2664395</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>23.91</v>
+      </c>
+      <c r="R4" t="n">
+        <v>367772</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.615792</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.373375</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0.409357</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0.4094</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.896096</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.160214</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.436662</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0.042128</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.005012</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.005012</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AH4" t="n">
         <v>0.02</v>
       </c>
-      <c r="G4" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="H4" t="n">
-        <v>99.05295</v>
-      </c>
-      <c r="I4" t="n">
-        <v>97.85433</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5.6199</v>
-      </c>
-      <c r="K4" t="n">
-        <v>5.6193</v>
-      </c>
-      <c r="L4" t="n">
-        <v>4597507</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1933111</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2664395</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="R4" t="n">
-        <v>23.91</v>
-      </c>
-      <c r="S4" t="n">
-        <v>367772</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.615792</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.373375</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-0.409357</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-0.4094</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.896096</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.160214</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.436662</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-0.042128</v>
-      </c>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.005012</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.005012</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.03</v>
-      </c>
       <c r="AI4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK4" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -912,96 +890,92 @@
         <v>0.033316</v>
       </c>
       <c r="E5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F5" t="n">
         <v>0.73</v>
       </c>
-      <c r="F5" t="n">
-        <v>0.87</v>
-      </c>
       <c r="G5" t="n">
-        <v>0.73</v>
+        <v>99.36759000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>99.36759000000001</v>
+        <v>99.32245</v>
       </c>
       <c r="I5" t="n">
-        <v>99.32245</v>
+        <v>5.5805</v>
       </c>
       <c r="J5" t="n">
-        <v>5.5805</v>
+        <v>5.5799</v>
       </c>
       <c r="K5" t="n">
-        <v>5.5799</v>
+        <v>4682852</v>
       </c>
       <c r="L5" t="n">
-        <v>4682852</v>
+        <v>1974391</v>
       </c>
       <c r="M5" t="n">
-        <v>1974391</v>
+        <v>2708461</v>
       </c>
       <c r="N5" t="n">
-        <v>2708461</v>
+        <v>2.35</v>
       </c>
       <c r="O5" t="n">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="P5" t="n">
-        <v>1.4</v>
+        <v>3.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.05</v>
+        <v>24.21</v>
       </c>
       <c r="R5" t="n">
-        <v>24.21</v>
+        <v>362204</v>
       </c>
       <c r="S5" t="n">
-        <v>362204</v>
+        <v>0.317648</v>
       </c>
       <c r="T5" t="n">
-        <v>0.317648</v>
+        <v>1.500312</v>
       </c>
       <c r="U5" t="n">
-        <v>1.500312</v>
+        <v>-0.70108</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.70108</v>
+        <v>-0.701155</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.701155</v>
+        <v>1.856332</v>
       </c>
       <c r="X5" t="n">
-        <v>1.856332</v>
+        <v>2.135418</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.135418</v>
+        <v>1.653884</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.653884</v>
-      </c>
-      <c r="AA5" t="n">
         <v>-1.513981</v>
       </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.00406</v>
+      </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>0.00406</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.00406</v>
+        <v>-0.01</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.00406</v>
+        <v>-0.06</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK5" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1019,96 +993,92 @@
         <v>0.034749</v>
       </c>
       <c r="E6" t="n">
-        <v>0.54</v>
+        <v>1.82</v>
       </c>
       <c r="F6" t="n">
-        <v>1.82</v>
+        <v>0.67</v>
       </c>
       <c r="G6" t="n">
-        <v>0.67</v>
+        <v>97.41759</v>
       </c>
       <c r="H6" t="n">
-        <v>97.41759</v>
+        <v>91.67452</v>
       </c>
       <c r="I6" t="n">
-        <v>91.67452</v>
+        <v>5.3574</v>
       </c>
       <c r="J6" t="n">
-        <v>5.3574</v>
+        <v>5.3568</v>
       </c>
       <c r="K6" t="n">
-        <v>5.3568</v>
+        <v>4682131</v>
       </c>
       <c r="L6" t="n">
-        <v>4682131</v>
+        <v>1947035</v>
       </c>
       <c r="M6" t="n">
-        <v>1947035</v>
+        <v>2735096</v>
       </c>
       <c r="N6" t="n">
-        <v>2735096</v>
+        <v>2.51</v>
       </c>
       <c r="O6" t="n">
-        <v>2.51</v>
+        <v>1.46</v>
       </c>
       <c r="P6" t="n">
-        <v>1.46</v>
+        <v>3.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.26</v>
+        <v>25.23</v>
       </c>
       <c r="R6" t="n">
-        <v>25.23</v>
+        <v>358398</v>
       </c>
       <c r="S6" t="n">
-        <v>358398</v>
+        <v>-1.96241</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.96241</v>
+        <v>-7.700102</v>
       </c>
       <c r="U6" t="n">
-        <v>-7.700102</v>
+        <v>-3.99785</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.99785</v>
+        <v>-3.99828</v>
       </c>
       <c r="W6" t="n">
-        <v>-3.99828</v>
+        <v>-0.015397</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.015397</v>
+        <v>-1.385541</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.385541</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.9834000000000001</v>
-      </c>
-      <c r="AA6" t="n">
         <v>-1.050789</v>
       </c>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.001433</v>
+      </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>0.001433</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.001433</v>
+        <v>0.16</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.001433</v>
+        <v>0.06</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AK6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1126,96 +1096,92 @@
         <v>0.039598</v>
       </c>
       <c r="E7" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="F7" t="n">
-        <v>1.83</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>98.48287000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>98.48287000000001</v>
+        <v>95.64045</v>
       </c>
       <c r="I7" t="n">
-        <v>95.64045</v>
+        <v>5.1394</v>
       </c>
       <c r="J7" t="n">
-        <v>5.1394</v>
+        <v>5.1388</v>
       </c>
       <c r="K7" t="n">
-        <v>5.1388</v>
+        <v>4727818</v>
       </c>
       <c r="L7" t="n">
-        <v>4727818</v>
+        <v>1971524</v>
       </c>
       <c r="M7" t="n">
-        <v>1971524</v>
+        <v>2756295</v>
       </c>
       <c r="N7" t="n">
-        <v>2756295</v>
+        <v>2.57</v>
       </c>
       <c r="O7" t="n">
-        <v>2.57</v>
+        <v>1.44</v>
       </c>
       <c r="P7" t="n">
-        <v>1.44</v>
+        <v>3.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.38</v>
+        <v>25.63</v>
       </c>
       <c r="R7" t="n">
-        <v>25.63</v>
+        <v>357740</v>
       </c>
       <c r="S7" t="n">
-        <v>357740</v>
+        <v>1.093519</v>
       </c>
       <c r="T7" t="n">
-        <v>1.093519</v>
+        <v>4.326098</v>
       </c>
       <c r="U7" t="n">
-        <v>4.326098</v>
+        <v>-4.069138</v>
       </c>
       <c r="V7" t="n">
-        <v>-4.069138</v>
+        <v>-4.069594</v>
       </c>
       <c r="W7" t="n">
-        <v>-4.069594</v>
+        <v>0.975774</v>
       </c>
       <c r="X7" t="n">
-        <v>0.975774</v>
+        <v>1.257759</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.257759</v>
+        <v>0.775073</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.775073</v>
-      </c>
-      <c r="AA7" t="n">
         <v>-0.183595</v>
       </c>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.004849</v>
+      </c>
       <c r="AE7" t="n">
-        <v>1.5</v>
+        <v>0.004849</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.004849</v>
+        <v>0.06</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.004849</v>
+        <v>-0.02</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AK7" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1233,96 +1199,92 @@
         <v>0.041954</v>
       </c>
       <c r="E8" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="F8" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="G8" t="n">
-        <v>1.71</v>
+        <v>99.54331000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>99.54331000000001</v>
+        <v>104.53224</v>
       </c>
       <c r="I8" t="n">
-        <v>104.53224</v>
+        <v>4.7378</v>
       </c>
       <c r="J8" t="n">
-        <v>4.7378</v>
+        <v>4.7372</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7372</v>
+        <v>4794583</v>
       </c>
       <c r="L8" t="n">
-        <v>4794583</v>
+        <v>1994119</v>
       </c>
       <c r="M8" t="n">
-        <v>1994119</v>
+        <v>2800464</v>
       </c>
       <c r="N8" t="n">
-        <v>2800464</v>
+        <v>2.66</v>
       </c>
       <c r="O8" t="n">
-        <v>2.66</v>
+        <v>1.55</v>
       </c>
       <c r="P8" t="n">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.45</v>
+        <v>26.54</v>
       </c>
       <c r="R8" t="n">
-        <v>26.54</v>
+        <v>353169</v>
       </c>
       <c r="S8" t="n">
-        <v>353169</v>
+        <v>1.076776</v>
       </c>
       <c r="T8" t="n">
-        <v>1.076776</v>
+        <v>9.297102000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>9.297102000000001</v>
+        <v>-7.814142</v>
       </c>
       <c r="V8" t="n">
-        <v>-7.814142</v>
+        <v>-7.815054</v>
       </c>
       <c r="W8" t="n">
-        <v>-7.815054</v>
+        <v>1.412174</v>
       </c>
       <c r="X8" t="n">
-        <v>1.412174</v>
+        <v>1.146068</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.146068</v>
+        <v>1.602477</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.602477</v>
-      </c>
-      <c r="AA8" t="n">
         <v>-1.277744</v>
       </c>
+      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.002356</v>
+      </c>
       <c r="AE8" t="n">
-        <v>1</v>
+        <v>0.002356</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.002356</v>
+        <v>0.09</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.002356</v>
+        <v>0.11</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK8" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1340,96 +1302,92 @@
         <v>0.043739</v>
       </c>
       <c r="E9" t="n">
-        <v>1.06</v>
+        <v>1.41</v>
       </c>
       <c r="F9" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>1.04</v>
+        <v>99.44726</v>
       </c>
       <c r="H9" t="n">
-        <v>99.44726</v>
+        <v>100.22451</v>
       </c>
       <c r="I9" t="n">
-        <v>100.22451</v>
+        <v>4.9191</v>
       </c>
       <c r="J9" t="n">
-        <v>4.9191</v>
+        <v>4.9185</v>
       </c>
       <c r="K9" t="n">
-        <v>4.9185</v>
+        <v>4833732</v>
       </c>
       <c r="L9" t="n">
-        <v>4833732</v>
+        <v>2003312</v>
       </c>
       <c r="M9" t="n">
-        <v>2003312</v>
+        <v>2830420</v>
       </c>
       <c r="N9" t="n">
-        <v>2830420</v>
+        <v>2.72</v>
       </c>
       <c r="O9" t="n">
-        <v>2.72</v>
+        <v>1.57</v>
       </c>
       <c r="P9" t="n">
-        <v>1.57</v>
+        <v>3.54</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.54</v>
+        <v>27.46</v>
       </c>
       <c r="R9" t="n">
-        <v>27.46</v>
+        <v>345097</v>
       </c>
       <c r="S9" t="n">
-        <v>345097</v>
+        <v>-0.09649099999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.09649099999999999</v>
+        <v>-4.120958</v>
       </c>
       <c r="U9" t="n">
-        <v>-4.120958</v>
+        <v>3.826671</v>
       </c>
       <c r="V9" t="n">
-        <v>3.826671</v>
+        <v>3.827155</v>
       </c>
       <c r="W9" t="n">
-        <v>3.827155</v>
+        <v>0.816526</v>
       </c>
       <c r="X9" t="n">
-        <v>0.816526</v>
+        <v>0.461006</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.461006</v>
+        <v>1.06968</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.06968</v>
-      </c>
-      <c r="AA9" t="n">
         <v>-2.285591</v>
       </c>
+      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.001785</v>
+      </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>0.001785</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.001785</v>
+        <v>0.06</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001785</v>
+        <v>0.02</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK9" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1447,96 +1405,92 @@
         <v>0.046796</v>
       </c>
       <c r="E10" t="n">
-        <v>0.47</v>
+        <v>0.52</v>
       </c>
       <c r="F10" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="G10" t="n">
-        <v>0.45</v>
+        <v>99.65249</v>
       </c>
       <c r="H10" t="n">
-        <v>99.65249</v>
+        <v>99.74639000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>99.74639000000001</v>
+        <v>4.7289</v>
       </c>
       <c r="J10" t="n">
-        <v>4.7289</v>
+        <v>4.7283</v>
       </c>
       <c r="K10" t="n">
-        <v>4.7283</v>
+        <v>4889397</v>
       </c>
       <c r="L10" t="n">
-        <v>4889397</v>
+        <v>2013726</v>
       </c>
       <c r="M10" t="n">
-        <v>2013726</v>
+        <v>2875671</v>
       </c>
       <c r="N10" t="n">
-        <v>2875671</v>
+        <v>2.79</v>
       </c>
       <c r="O10" t="n">
-        <v>2.79</v>
+        <v>1.57</v>
       </c>
       <c r="P10" t="n">
-        <v>1.57</v>
+        <v>3.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.65</v>
+        <v>27.42</v>
       </c>
       <c r="R10" t="n">
-        <v>27.42</v>
+        <v>346415</v>
       </c>
       <c r="S10" t="n">
-        <v>346415</v>
+        <v>0.206371</v>
       </c>
       <c r="T10" t="n">
-        <v>0.206371</v>
+        <v>-0.477049</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.477049</v>
+        <v>-3.866561</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.866561</v>
+        <v>-3.867033</v>
       </c>
       <c r="W10" t="n">
-        <v>-3.867033</v>
+        <v>1.151595</v>
       </c>
       <c r="X10" t="n">
-        <v>1.151595</v>
+        <v>0.5198390000000001</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5198390000000001</v>
+        <v>1.598738</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.598738</v>
-      </c>
-      <c r="AA10" t="n">
         <v>0.381922</v>
       </c>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.003057</v>
+      </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>0.003057</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.003057</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.003057</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK10" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1554,96 +1508,92 @@
         <v>0.048116</v>
       </c>
       <c r="E11" t="n">
-        <v>0.67</v>
+        <v>0.59</v>
       </c>
       <c r="F11" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="G11" t="n">
-        <v>0.62</v>
+        <v>99.53077999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>99.53077999999999</v>
+        <v>99.32053000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>99.32053000000001</v>
+        <v>5.238</v>
       </c>
       <c r="J11" t="n">
-        <v>5.238</v>
+        <v>5.2374</v>
       </c>
       <c r="K11" t="n">
-        <v>5.2374</v>
+        <v>4965603</v>
       </c>
       <c r="L11" t="n">
-        <v>4965603</v>
+        <v>2052569</v>
       </c>
       <c r="M11" t="n">
-        <v>2052569</v>
+        <v>2913035</v>
       </c>
       <c r="N11" t="n">
-        <v>2913035</v>
+        <v>2.73</v>
       </c>
       <c r="O11" t="n">
-        <v>2.73</v>
+        <v>1.52</v>
       </c>
       <c r="P11" t="n">
-        <v>1.52</v>
+        <v>3.57</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.57</v>
+        <v>27.88</v>
       </c>
       <c r="R11" t="n">
-        <v>27.88</v>
+        <v>341958</v>
       </c>
       <c r="S11" t="n">
-        <v>341958</v>
+        <v>-0.122134</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.122134</v>
+        <v>-0.426943</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.426943</v>
+        <v>10.765717</v>
       </c>
       <c r="V11" t="n">
-        <v>10.765717</v>
+        <v>10.767083</v>
       </c>
       <c r="W11" t="n">
-        <v>10.767083</v>
+        <v>1.558597</v>
       </c>
       <c r="X11" t="n">
-        <v>1.558597</v>
+        <v>1.928912</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.928912</v>
+        <v>1.299314</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.299314</v>
-      </c>
-      <c r="AA11" t="n">
         <v>-1.286607</v>
       </c>
+      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.00132</v>
+      </c>
       <c r="AE11" t="n">
-        <v>0.5</v>
+        <v>0.00132</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.00132</v>
+        <v>-0.06</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.00132</v>
+        <v>-0.05</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AK11" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1661,96 +1611,92 @@
         <v>0.049037</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.68</v>
+        <v>0.21</v>
       </c>
       <c r="F12" t="n">
-        <v>0.21</v>
+        <v>-0.6</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6</v>
+        <v>101.43252</v>
       </c>
       <c r="H12" t="n">
-        <v>101.43252</v>
+        <v>103.95413</v>
       </c>
       <c r="I12" t="n">
-        <v>103.95413</v>
+        <v>5.1884</v>
       </c>
       <c r="J12" t="n">
-        <v>5.1884</v>
+        <v>5.1878</v>
       </c>
       <c r="K12" t="n">
-        <v>5.1878</v>
+        <v>4999244</v>
       </c>
       <c r="L12" t="n">
-        <v>4999244</v>
+        <v>2047038</v>
       </c>
       <c r="M12" t="n">
-        <v>2047038</v>
+        <v>2952207</v>
       </c>
       <c r="N12" t="n">
-        <v>2952207</v>
+        <v>2.84</v>
       </c>
       <c r="O12" t="n">
-        <v>2.84</v>
+        <v>1.6</v>
       </c>
       <c r="P12" t="n">
-        <v>1.6</v>
+        <v>3.71</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.71</v>
+        <v>29.24</v>
       </c>
       <c r="R12" t="n">
-        <v>29.24</v>
+        <v>346403</v>
       </c>
       <c r="S12" t="n">
-        <v>346403</v>
+        <v>1.910705</v>
       </c>
       <c r="T12" t="n">
-        <v>1.910705</v>
+        <v>4.665299</v>
       </c>
       <c r="U12" t="n">
-        <v>4.665299</v>
+        <v>-0.946926</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.946926</v>
+        <v>-0.947035</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.947035</v>
+        <v>0.677481</v>
       </c>
       <c r="X12" t="n">
-        <v>0.677481</v>
+        <v>-0.269467</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.269467</v>
+        <v>1.344714</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.344714</v>
-      </c>
-      <c r="AA12" t="n">
         <v>1.299867</v>
       </c>
+      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.0009210000000000001</v>
+      </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AK12" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -1768,102 +1714,96 @@
         <v>0.05056</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.36</v>
+        <v>-0.7</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7</v>
+        <v>-0.31</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.31</v>
+        <v>101.09886</v>
       </c>
       <c r="H13" t="n">
-        <v>101.09886</v>
+        <v>104.51426</v>
       </c>
       <c r="I13" t="n">
-        <v>104.51426</v>
+        <v>5.179</v>
       </c>
       <c r="J13" t="n">
-        <v>5.179</v>
+        <v>5.1784</v>
       </c>
       <c r="K13" t="n">
-        <v>5.1784</v>
+        <v>5072711</v>
       </c>
       <c r="L13" t="n">
-        <v>5072711</v>
+        <v>2064183</v>
       </c>
       <c r="M13" t="n">
-        <v>2064183</v>
+        <v>3008528</v>
       </c>
       <c r="N13" t="n">
-        <v>3008528</v>
+        <v>2.9</v>
       </c>
       <c r="O13" t="n">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="P13" t="n">
-        <v>1.62</v>
+        <v>3.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.78</v>
+        <v>28.6</v>
       </c>
       <c r="R13" t="n">
-        <v>28.6</v>
+        <v>339664</v>
       </c>
       <c r="S13" t="n">
-        <v>339664</v>
+        <v>-0.328948</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.328948</v>
+        <v>0.538824</v>
       </c>
       <c r="U13" t="n">
-        <v>0.538824</v>
+        <v>-0.181173</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.181173</v>
+        <v>-0.181194</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.181194</v>
+        <v>1.469562</v>
       </c>
       <c r="X13" t="n">
-        <v>1.469562</v>
+        <v>0.837552</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.837552</v>
+        <v>1.907759</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.907759</v>
+        <v>-1.945422</v>
       </c>
       <c r="AA13" t="n">
-        <v>-1.945422</v>
+        <v>8.58755</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.727061000000001</v>
+        <v>8.825751</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.58755</v>
+        <v>0.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>8.825751</v>
+        <v>0.001523</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.5</v>
+        <v>0.001523</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.001523</v>
+        <v>0.06</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.001523</v>
+        <v>0.02</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK13" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -1881,102 +1821,96 @@
         <v>0.050788</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.29</v>
+        <v>-0.95</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.95</v>
+        <v>-0.32</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.32</v>
+        <v>101.15209</v>
       </c>
       <c r="H14" t="n">
-        <v>101.15209</v>
+        <v>101.19157</v>
       </c>
       <c r="I14" t="n">
-        <v>101.19157</v>
+        <v>5.4066</v>
       </c>
       <c r="J14" t="n">
-        <v>5.4066</v>
+        <v>5.406</v>
       </c>
       <c r="K14" t="n">
-        <v>5.406</v>
+        <v>5164775</v>
       </c>
       <c r="L14" t="n">
-        <v>5164775</v>
+        <v>2109806</v>
       </c>
       <c r="M14" t="n">
-        <v>2109806</v>
+        <v>3054969</v>
       </c>
       <c r="N14" t="n">
-        <v>3054969</v>
+        <v>2.92</v>
       </c>
       <c r="O14" t="n">
-        <v>2.92</v>
+        <v>1.65</v>
       </c>
       <c r="P14" t="n">
-        <v>1.65</v>
+        <v>3.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.8</v>
+        <v>28.57</v>
       </c>
       <c r="R14" t="n">
-        <v>28.57</v>
+        <v>327580</v>
       </c>
       <c r="S14" t="n">
-        <v>327580</v>
+        <v>0.052651</v>
       </c>
       <c r="T14" t="n">
-        <v>0.052651</v>
+        <v>-3.179174</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.179174</v>
+        <v>4.394671</v>
       </c>
       <c r="V14" t="n">
-        <v>4.394671</v>
+        <v>4.39518</v>
       </c>
       <c r="W14" t="n">
-        <v>4.39518</v>
+        <v>1.814888</v>
       </c>
       <c r="X14" t="n">
-        <v>1.814888</v>
+        <v>2.210221</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.210221</v>
+        <v>1.543645</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.543645</v>
+        <v>-3.557633</v>
       </c>
       <c r="AA14" t="n">
-        <v>-3.557633</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.168596</v>
+        <v>7.191214</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.248760000000001</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>7.191214</v>
+        <v>0.000228</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>0.000228</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.000228</v>
+        <v>0.02</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.000228</v>
+        <v>0.03</v>
       </c>
       <c r="AH14" t="n">
         <v>0.02</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK14" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -1994,102 +1928,96 @@
         <v>0.050788</v>
       </c>
       <c r="E15" t="n">
-        <v>0.59</v>
+        <v>-0.97</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.97</v>
+        <v>0.47</v>
       </c>
       <c r="G15" t="n">
-        <v>0.47</v>
+        <v>101.43094</v>
       </c>
       <c r="H15" t="n">
-        <v>101.43094</v>
+        <v>100.07474</v>
       </c>
       <c r="I15" t="n">
-        <v>100.07474</v>
+        <v>5.257</v>
       </c>
       <c r="J15" t="n">
-        <v>5.257</v>
+        <v>5.2564</v>
       </c>
       <c r="K15" t="n">
-        <v>5.2564</v>
+        <v>5215990</v>
       </c>
       <c r="L15" t="n">
-        <v>5215990</v>
+        <v>2105856</v>
       </c>
       <c r="M15" t="n">
-        <v>2105856</v>
+        <v>3110134</v>
       </c>
       <c r="N15" t="n">
-        <v>3110134</v>
+        <v>3.04</v>
       </c>
       <c r="O15" t="n">
-        <v>3.04</v>
+        <v>1.77</v>
       </c>
       <c r="P15" t="n">
-        <v>1.77</v>
+        <v>3.89</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.89</v>
+        <v>29.68</v>
       </c>
       <c r="R15" t="n">
-        <v>29.68</v>
+        <v>325546</v>
       </c>
       <c r="S15" t="n">
-        <v>325546</v>
+        <v>0.275674</v>
       </c>
       <c r="T15" t="n">
-        <v>0.275674</v>
+        <v>-1.103679</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.103679</v>
+        <v>-2.766988</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.766988</v>
+        <v>-2.767296</v>
       </c>
       <c r="W15" t="n">
-        <v>-2.767296</v>
+        <v>0.991621</v>
       </c>
       <c r="X15" t="n">
-        <v>0.991621</v>
+        <v>-0.187221</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.187221</v>
+        <v>1.805747</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.805747</v>
+        <v>-0.6209170000000001</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.6209170000000001</v>
+        <v>6.517038</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.470016</v>
+        <v>6.460076</v>
       </c>
       <c r="AC15" t="n">
-        <v>6.517038</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.460076</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK15" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -2107,102 +2035,96 @@
         <v>0.050788</v>
       </c>
       <c r="E16" t="n">
-        <v>0.41</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="G16" t="n">
-        <v>0.38</v>
+        <v>100.7113</v>
       </c>
       <c r="H16" t="n">
-        <v>100.7113</v>
+        <v>99.15328</v>
       </c>
       <c r="I16" t="n">
-        <v>99.15328</v>
+        <v>5.2941</v>
       </c>
       <c r="J16" t="n">
-        <v>5.2941</v>
+        <v>5.2935</v>
       </c>
       <c r="K16" t="n">
-        <v>5.2935</v>
+        <v>5285657</v>
       </c>
       <c r="L16" t="n">
-        <v>5285657</v>
+        <v>2130312</v>
       </c>
       <c r="M16" t="n">
-        <v>2130312</v>
+        <v>3155345</v>
       </c>
       <c r="N16" t="n">
-        <v>3155345</v>
+        <v>3.07</v>
       </c>
       <c r="O16" t="n">
-        <v>3.07</v>
+        <v>1.81</v>
       </c>
       <c r="P16" t="n">
-        <v>1.81</v>
+        <v>3.92</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.92</v>
+        <v>30.52</v>
       </c>
       <c r="R16" t="n">
-        <v>30.52</v>
+        <v>331505</v>
       </c>
       <c r="S16" t="n">
-        <v>331505</v>
+        <v>-0.709488</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.709488</v>
+        <v>-0.920772</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.920772</v>
+        <v>0.705726</v>
       </c>
       <c r="V16" t="n">
-        <v>0.705726</v>
+        <v>0.705806</v>
       </c>
       <c r="W16" t="n">
-        <v>0.705806</v>
+        <v>1.335643</v>
       </c>
       <c r="X16" t="n">
-        <v>1.335643</v>
+        <v>1.161333</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.161333</v>
+        <v>1.453667</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.453667</v>
+        <v>1.830463</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.830463</v>
+        <v>5.899363</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.900488</v>
+        <v>5.974439</v>
       </c>
       <c r="AC16" t="n">
-        <v>5.899363</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>5.974439</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AH16" t="n">
         <v>0.03</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AK16" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2220,102 +2142,96 @@
         <v>0.050788</v>
       </c>
       <c r="E17" t="n">
-        <v>0.62</v>
+        <v>0.45</v>
       </c>
       <c r="F17" t="n">
-        <v>0.45</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6899999999999999</v>
+        <v>100.58566</v>
       </c>
       <c r="H17" t="n">
-        <v>100.58566</v>
+        <v>99.97338999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>99.97338999999999</v>
+        <v>5.2177</v>
       </c>
       <c r="J17" t="n">
-        <v>5.2177</v>
+        <v>5.2171</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2171</v>
+        <v>5366069</v>
       </c>
       <c r="L17" t="n">
-        <v>5366069</v>
+        <v>2178236</v>
       </c>
       <c r="M17" t="n">
-        <v>2178236</v>
+        <v>3187833</v>
       </c>
       <c r="N17" t="n">
-        <v>3187833</v>
+        <v>3.07</v>
       </c>
       <c r="O17" t="n">
-        <v>3.07</v>
+        <v>1.8</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8</v>
+        <v>3.94</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.94</v>
+        <v>29.64</v>
       </c>
       <c r="R17" t="n">
-        <v>29.64</v>
+        <v>324703</v>
       </c>
       <c r="S17" t="n">
-        <v>324703</v>
+        <v>-0.124753</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.124753</v>
+        <v>0.827113</v>
       </c>
       <c r="U17" t="n">
-        <v>0.827113</v>
+        <v>-1.443116</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.443116</v>
+        <v>-1.443279</v>
       </c>
       <c r="W17" t="n">
-        <v>-1.443279</v>
+        <v>1.521325</v>
       </c>
       <c r="X17" t="n">
-        <v>1.521325</v>
+        <v>2.249624</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.249624</v>
+        <v>1.029618</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.029618</v>
+        <v>-2.051854</v>
       </c>
       <c r="AA17" t="n">
-        <v>-2.051854</v>
+        <v>5.458422</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.784842</v>
+        <v>5.932356</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.458422</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>5.932356</v>
+        <v>-0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AI17" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK17" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -2333,102 +2249,96 @@
         <v>0.050788</v>
       </c>
       <c r="E18" t="n">
-        <v>0.53</v>
+        <v>0.21</v>
       </c>
       <c r="F18" t="n">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
       <c r="G18" t="n">
-        <v>0.46</v>
+        <v>100.10937</v>
       </c>
       <c r="H18" t="n">
-        <v>100.10937</v>
+        <v>95.09372999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>95.09372999999999</v>
+        <v>5.0993</v>
       </c>
       <c r="J18" t="n">
-        <v>5.0993</v>
+        <v>5.0987</v>
       </c>
       <c r="K18" t="n">
-        <v>5.0987</v>
+        <v>5373231</v>
       </c>
       <c r="L18" t="n">
-        <v>5373231</v>
+        <v>2151399</v>
       </c>
       <c r="M18" t="n">
-        <v>2151399</v>
+        <v>3221831</v>
       </c>
       <c r="N18" t="n">
-        <v>3221831</v>
+        <v>3.24</v>
       </c>
       <c r="O18" t="n">
-        <v>3.24</v>
+        <v>1.94</v>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>4.11</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.11</v>
+        <v>30.54</v>
       </c>
       <c r="R18" t="n">
-        <v>30.54</v>
+        <v>331122</v>
       </c>
       <c r="S18" t="n">
-        <v>331122</v>
+        <v>-0.473517</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.473517</v>
+        <v>-4.880959</v>
       </c>
       <c r="U18" t="n">
-        <v>-4.880959</v>
+        <v>-2.269199</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.269199</v>
+        <v>-2.26946</v>
       </c>
       <c r="W18" t="n">
-        <v>-2.26946</v>
+        <v>0.133468</v>
       </c>
       <c r="X18" t="n">
-        <v>0.133468</v>
+        <v>-1.232052</v>
       </c>
       <c r="Y18" t="n">
-        <v>-1.232052</v>
+        <v>1.066493</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.066493</v>
+        <v>1.976883</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.976883</v>
+        <v>3.79089</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.77432</v>
+        <v>5.711379</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.79089</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>5.711379</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AH18" t="n">
         <v>0.17</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AK18" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2446,102 +2356,96 @@
         <v>0.050788</v>
       </c>
       <c r="E19" t="n">
-        <v>0.84</v>
+        <v>-0.06</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.06</v>
+        <v>0.77</v>
       </c>
       <c r="G19" t="n">
-        <v>0.77</v>
+        <v>103.08344</v>
       </c>
       <c r="H19" t="n">
-        <v>103.08344</v>
+        <v>98.65015</v>
       </c>
       <c r="I19" t="n">
-        <v>98.65015</v>
+        <v>5.2078</v>
       </c>
       <c r="J19" t="n">
-        <v>5.2078</v>
+        <v>5.2072</v>
       </c>
       <c r="K19" t="n">
-        <v>5.2072</v>
+        <v>5370950</v>
       </c>
       <c r="L19" t="n">
-        <v>5370950</v>
+        <v>2136105</v>
       </c>
       <c r="M19" t="n">
-        <v>2136105</v>
+        <v>3234845</v>
       </c>
       <c r="N19" t="n">
-        <v>3234845</v>
+        <v>3.36</v>
       </c>
       <c r="O19" t="n">
-        <v>3.36</v>
+        <v>2.17</v>
       </c>
       <c r="P19" t="n">
-        <v>2.17</v>
+        <v>4.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.16</v>
+        <v>30.48</v>
       </c>
       <c r="R19" t="n">
-        <v>30.48</v>
+        <v>328098</v>
       </c>
       <c r="S19" t="n">
-        <v>328098</v>
+        <v>2.970821</v>
       </c>
       <c r="T19" t="n">
-        <v>2.970821</v>
+        <v>3.73991</v>
       </c>
       <c r="U19" t="n">
-        <v>3.73991</v>
+        <v>2.127743</v>
       </c>
       <c r="V19" t="n">
-        <v>2.127743</v>
+        <v>2.127993</v>
       </c>
       <c r="W19" t="n">
-        <v>2.127993</v>
+        <v>-0.042451</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.042451</v>
+        <v>-0.710886</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.710886</v>
+        <v>0.403932</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.403932</v>
+        <v>-0.913259</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.913259</v>
+        <v>1.864495</v>
       </c>
       <c r="AB19" t="n">
-        <v>5.596302</v>
+        <v>5.47065</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.864495</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>5.47065</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK19" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2559,102 +2463,96 @@
         <v>0.050788</v>
       </c>
       <c r="E20" t="n">
-        <v>0.71</v>
+        <v>0.05</v>
       </c>
       <c r="F20" t="n">
-        <v>0.05</v>
+        <v>0.64</v>
       </c>
       <c r="G20" t="n">
-        <v>0.64</v>
+        <v>103.08526</v>
       </c>
       <c r="H20" t="n">
-        <v>103.08526</v>
+        <v>110.62045</v>
       </c>
       <c r="I20" t="n">
-        <v>110.62045</v>
+        <v>5.0804</v>
       </c>
       <c r="J20" t="n">
-        <v>5.0804</v>
+        <v>5.0798</v>
       </c>
       <c r="K20" t="n">
-        <v>5.0798</v>
+        <v>5424811</v>
       </c>
       <c r="L20" t="n">
-        <v>5424811</v>
+        <v>2154900</v>
       </c>
       <c r="M20" t="n">
-        <v>2154900</v>
+        <v>3269910</v>
       </c>
       <c r="N20" t="n">
-        <v>3269910</v>
+        <v>3.35</v>
       </c>
       <c r="O20" t="n">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>4.11</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.11</v>
+        <v>30.99</v>
       </c>
       <c r="R20" t="n">
-        <v>30.99</v>
+        <v>341158</v>
       </c>
       <c r="S20" t="n">
-        <v>341158</v>
+        <v>0.001766</v>
       </c>
       <c r="T20" t="n">
-        <v>0.001766</v>
+        <v>12.134092</v>
       </c>
       <c r="U20" t="n">
-        <v>12.134092</v>
+        <v>-2.446331</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.446331</v>
+        <v>-2.446612</v>
       </c>
       <c r="W20" t="n">
-        <v>-2.446612</v>
+        <v>1.002821</v>
       </c>
       <c r="X20" t="n">
-        <v>1.002821</v>
+        <v>0.879872</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.879872</v>
+        <v>1.083978</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.083978</v>
+        <v>3.980518</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.980518</v>
+        <v>0.172427</v>
       </c>
       <c r="AB20" t="n">
-        <v>4.650694</v>
+        <v>4.361088</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.172427</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.361088</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AK20" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2672,102 +2570,96 @@
         <v>0.050788</v>
       </c>
       <c r="E21" t="n">
-        <v>0.61</v>
+        <v>-0.95</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.95</v>
+        <v>0.53</v>
       </c>
       <c r="G21" t="n">
-        <v>0.53</v>
+        <v>103.96006</v>
       </c>
       <c r="H21" t="n">
-        <v>103.96006</v>
+        <v>104.03539</v>
       </c>
       <c r="I21" t="n">
-        <v>104.03539</v>
+        <v>5.0007</v>
       </c>
       <c r="J21" t="n">
-        <v>5.0007</v>
+        <v>5.0001</v>
       </c>
       <c r="K21" t="n">
-        <v>5.0001</v>
+        <v>5426307</v>
       </c>
       <c r="L21" t="n">
-        <v>5426307</v>
+        <v>2145000</v>
       </c>
       <c r="M21" t="n">
-        <v>2145000</v>
+        <v>3281308</v>
       </c>
       <c r="N21" t="n">
-        <v>3281308</v>
+        <v>3.54</v>
       </c>
       <c r="O21" t="n">
-        <v>3.54</v>
+        <v>2.45</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>4.26</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.26</v>
+        <v>31.62</v>
       </c>
       <c r="R21" t="n">
-        <v>31.62</v>
+        <v>345725</v>
       </c>
       <c r="S21" t="n">
-        <v>345725</v>
+        <v>0.848618</v>
       </c>
       <c r="T21" t="n">
-        <v>0.848618</v>
+        <v>-5.952841</v>
       </c>
       <c r="U21" t="n">
-        <v>-5.952841</v>
+        <v>-1.568774</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.568774</v>
+        <v>-1.568959</v>
       </c>
       <c r="W21" t="n">
-        <v>-1.568959</v>
+        <v>0.027577</v>
       </c>
       <c r="X21" t="n">
-        <v>0.027577</v>
+        <v>-0.459418</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.459418</v>
+        <v>0.348572</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.348572</v>
+        <v>1.338676</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.338676</v>
+        <v>-2.158772</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.184706</v>
+        <v>3.834324</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.158772</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.834324</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AK21" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -2785,102 +2677,96 @@
         <v>0.050788</v>
       </c>
       <c r="E22" t="n">
-        <v>0.23</v>
+        <v>-1.84</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.84</v>
+        <v>0.36</v>
       </c>
       <c r="G22" t="n">
-        <v>0.36</v>
+        <v>102.40467</v>
       </c>
       <c r="H22" t="n">
-        <v>102.40467</v>
+        <v>102.71665</v>
       </c>
       <c r="I22" t="n">
-        <v>102.71665</v>
+        <v>5.0959</v>
       </c>
       <c r="J22" t="n">
-        <v>5.0959</v>
+        <v>5.0953</v>
       </c>
       <c r="K22" t="n">
-        <v>5.0953</v>
+        <v>5453708</v>
       </c>
       <c r="L22" t="n">
-        <v>5453708</v>
+        <v>2145530</v>
       </c>
       <c r="M22" t="n">
-        <v>2145530</v>
+        <v>3308178</v>
       </c>
       <c r="N22" t="n">
-        <v>3308178</v>
+        <v>3.65</v>
       </c>
       <c r="O22" t="n">
-        <v>3.65</v>
+        <v>2.58</v>
       </c>
       <c r="P22" t="n">
-        <v>2.58</v>
+        <v>4.35</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.35</v>
+        <v>31.63</v>
       </c>
       <c r="R22" t="n">
-        <v>31.63</v>
+        <v>343489</v>
       </c>
       <c r="S22" t="n">
-        <v>343489</v>
+        <v>-1.496142</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.496142</v>
+        <v>-1.267588</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.267588</v>
+        <v>1.903733</v>
       </c>
       <c r="V22" t="n">
-        <v>1.903733</v>
+        <v>1.903962</v>
       </c>
       <c r="W22" t="n">
-        <v>1.903962</v>
+        <v>0.504966</v>
       </c>
       <c r="X22" t="n">
-        <v>0.504966</v>
+        <v>0.024709</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.024709</v>
+        <v>0.818881</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.818881</v>
+        <v>-0.646757</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0.646757</v>
+        <v>-4.45588</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.935832</v>
+        <v>3.741292</v>
       </c>
       <c r="AC22" t="n">
-        <v>-4.45588</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.741292</v>
+        <v>-0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0</v>
+        <v>0.11</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK22" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -2898,102 +2784,96 @@
         <v>0.050788</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.08</v>
+        <v>-1.93</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.93</v>
+        <v>-0.1</v>
       </c>
       <c r="G23" t="n">
+        <v>102.4398</v>
+      </c>
+      <c r="H23" t="n">
+        <v>102.285</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4.8192</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4.8186</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5479459</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2169613</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3309846</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P23" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>30.85</v>
+      </c>
+      <c r="R23" t="n">
+        <v>343620</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.034305</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.420234</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-5.429855</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-5.430495</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.472174</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.122473</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.050421</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.038138</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-6.84947</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.998957</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AH23" t="n">
         <v>-0.1</v>
       </c>
-      <c r="H23" t="n">
-        <v>102.4398</v>
-      </c>
-      <c r="I23" t="n">
-        <v>102.285</v>
-      </c>
-      <c r="J23" t="n">
-        <v>4.8192</v>
-      </c>
-      <c r="K23" t="n">
-        <v>4.8186</v>
-      </c>
-      <c r="L23" t="n">
-        <v>5479459</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2169613</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3309846</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="R23" t="n">
-        <v>30.85</v>
-      </c>
-      <c r="S23" t="n">
-        <v>343620</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0.034305</v>
-      </c>
-      <c r="U23" t="n">
-        <v>-0.420234</v>
-      </c>
-      <c r="V23" t="n">
-        <v>-5.429855</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-5.430495</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0.472174</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.122473</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0.050421</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.038138</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>3.161501</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>-6.84947</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.998957</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>-0.04</v>
-      </c>
       <c r="AI23" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AK23" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -3011,102 +2891,96 @@
         <v>0.050788</v>
       </c>
       <c r="E24" t="n">
-        <v>0.12</v>
+        <v>-0.72</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.72</v>
+        <v>-0.09</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.09</v>
+        <v>102.89895</v>
       </c>
       <c r="H24" t="n">
-        <v>102.89895</v>
+        <v>105.33914</v>
       </c>
       <c r="I24" t="n">
-        <v>105.33914</v>
+        <v>4.7415</v>
       </c>
       <c r="J24" t="n">
-        <v>4.7415</v>
+        <v>4.7409</v>
       </c>
       <c r="K24" t="n">
-        <v>4.7409</v>
+        <v>5484871</v>
       </c>
       <c r="L24" t="n">
-        <v>5484871</v>
+        <v>2153541</v>
       </c>
       <c r="M24" t="n">
-        <v>2153541</v>
+        <v>3331330</v>
       </c>
       <c r="N24" t="n">
-        <v>3331330</v>
+        <v>3.63</v>
       </c>
       <c r="O24" t="n">
-        <v>3.63</v>
+        <v>2.73</v>
       </c>
       <c r="P24" t="n">
-        <v>2.73</v>
+        <v>4.22</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.22</v>
+        <v>30.43</v>
       </c>
       <c r="R24" t="n">
-        <v>30.43</v>
+        <v>345476</v>
       </c>
       <c r="S24" t="n">
-        <v>345476</v>
+        <v>0.448214</v>
       </c>
       <c r="T24" t="n">
-        <v>0.448214</v>
+        <v>2.985912</v>
       </c>
       <c r="U24" t="n">
-        <v>2.985912</v>
+        <v>-1.612301</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.612301</v>
+        <v>-1.612502</v>
       </c>
       <c r="W24" t="n">
-        <v>-1.612502</v>
+        <v>0.098769</v>
       </c>
       <c r="X24" t="n">
-        <v>0.098769</v>
+        <v>-0.740777</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.740777</v>
+        <v>0.6490939999999999</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.6490939999999999</v>
+        <v>0.5401319999999999</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.5401319999999999</v>
+        <v>-7.713954</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.992444</v>
+        <v>3.527423</v>
       </c>
       <c r="AC24" t="n">
-        <v>-7.713954</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.527423</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK24" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3124,102 +2998,96 @@
         <v>0.049189</v>
       </c>
       <c r="E25" t="n">
-        <v>0.23</v>
+        <v>-0.14</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.14</v>
+        <v>0.2</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2</v>
+        <v>102.48797</v>
       </c>
       <c r="H25" t="n">
-        <v>102.48797</v>
+        <v>106.05945</v>
       </c>
       <c r="I25" t="n">
-        <v>106.05945</v>
+        <v>4.9219</v>
       </c>
       <c r="J25" t="n">
-        <v>4.9219</v>
+        <v>4.9213</v>
       </c>
       <c r="K25" t="n">
-        <v>4.9213</v>
+        <v>5559063</v>
       </c>
       <c r="L25" t="n">
-        <v>5559063</v>
+        <v>2172658</v>
       </c>
       <c r="M25" t="n">
-        <v>2172658</v>
+        <v>3386405</v>
       </c>
       <c r="N25" t="n">
-        <v>3386405</v>
+        <v>3.61</v>
       </c>
       <c r="O25" t="n">
-        <v>3.61</v>
+        <v>2.82</v>
       </c>
       <c r="P25" t="n">
-        <v>2.82</v>
+        <v>4.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.12</v>
+        <v>29.92</v>
       </c>
       <c r="R25" t="n">
-        <v>29.92</v>
+        <v>344177</v>
       </c>
       <c r="S25" t="n">
-        <v>344177</v>
+        <v>-0.399402</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.399402</v>
+        <v>0.683801</v>
       </c>
       <c r="U25" t="n">
-        <v>0.683801</v>
+        <v>3.804703</v>
       </c>
       <c r="V25" t="n">
-        <v>3.804703</v>
+        <v>3.805185</v>
       </c>
       <c r="W25" t="n">
-        <v>3.805185</v>
+        <v>1.352666</v>
       </c>
       <c r="X25" t="n">
-        <v>1.352666</v>
+        <v>0.887701</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.887701</v>
+        <v>1.653244</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.653244</v>
+        <v>-0.376003</v>
       </c>
       <c r="AA25" t="n">
-        <v>-0.376003</v>
+        <v>-7.193509</v>
       </c>
       <c r="AB25" t="n">
-        <v>4.608216</v>
+        <v>4.057054</v>
       </c>
       <c r="AC25" t="n">
-        <v>-7.193509</v>
+        <v>-0.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.057054</v>
+        <v>-0.001599</v>
       </c>
       <c r="AE25" t="n">
-        <v>-0.5</v>
+        <v>-0.001599</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.001599</v>
+        <v>-0.02</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.001599</v>
+        <v>0.09</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AK25" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -3237,102 +3105,96 @@
         <v>0.048422</v>
       </c>
       <c r="E26" t="n">
-        <v>0.26</v>
+        <v>0.37</v>
       </c>
       <c r="F26" t="n">
-        <v>0.37</v>
+        <v>0.11</v>
       </c>
       <c r="G26" t="n">
-        <v>0.11</v>
+        <v>102.50227</v>
       </c>
       <c r="H26" t="n">
-        <v>102.50227</v>
+        <v>101.76242</v>
       </c>
       <c r="I26" t="n">
-        <v>101.76242</v>
+        <v>5.0076</v>
       </c>
       <c r="J26" t="n">
-        <v>5.0076</v>
+        <v>5.007</v>
       </c>
       <c r="K26" t="n">
-        <v>5.007</v>
+        <v>5625945</v>
       </c>
       <c r="L26" t="n">
-        <v>5625945</v>
+        <v>2215175</v>
       </c>
       <c r="M26" t="n">
-        <v>2215175</v>
+        <v>3410769</v>
       </c>
       <c r="N26" t="n">
-        <v>3410769</v>
+        <v>3.54</v>
       </c>
       <c r="O26" t="n">
-        <v>3.54</v>
+        <v>2.82</v>
       </c>
       <c r="P26" t="n">
-        <v>2.82</v>
+        <v>4</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>29.66</v>
       </c>
       <c r="R26" t="n">
-        <v>29.66</v>
+        <v>340324</v>
       </c>
       <c r="S26" t="n">
-        <v>340324</v>
+        <v>0.013953</v>
       </c>
       <c r="T26" t="n">
-        <v>0.013953</v>
+        <v>-4.05153</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.05153</v>
+        <v>1.741198</v>
       </c>
       <c r="V26" t="n">
-        <v>1.741198</v>
+        <v>1.74141</v>
       </c>
       <c r="W26" t="n">
-        <v>1.74141</v>
+        <v>1.203116</v>
       </c>
       <c r="X26" t="n">
-        <v>1.203116</v>
+        <v>1.956912</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.956912</v>
+        <v>0.719465</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.719465</v>
+        <v>-1.119482</v>
       </c>
       <c r="AA26" t="n">
-        <v>-1.119482</v>
+        <v>-5.956714</v>
       </c>
       <c r="AB26" t="n">
-        <v>5.185235</v>
+        <v>4.505936</v>
       </c>
       <c r="AC26" t="n">
-        <v>-5.956714</v>
+        <v>-0.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>4.505936</v>
+        <v>-0.000768</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.5</v>
+        <v>-0.000768</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.000768</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.000768</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK26" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -3350,102 +3212,96 @@
         <v>0.047279</v>
       </c>
       <c r="E27" t="n">
-        <v>0.24</v>
+        <v>0.5</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="G27" t="n">
-        <v>0.12</v>
+        <v>102.83037</v>
       </c>
       <c r="H27" t="n">
-        <v>102.83037</v>
+        <v>101.92849</v>
       </c>
       <c r="I27" t="n">
-        <v>101.92849</v>
+        <v>5.0575</v>
       </c>
       <c r="J27" t="n">
-        <v>5.0575</v>
+        <v>5.0569</v>
       </c>
       <c r="K27" t="n">
-        <v>5.0569</v>
+        <v>5653808</v>
       </c>
       <c r="L27" t="n">
-        <v>5653808</v>
+        <v>2204808</v>
       </c>
       <c r="M27" t="n">
-        <v>2204808</v>
+        <v>3449000</v>
       </c>
       <c r="N27" t="n">
-        <v>3449000</v>
+        <v>3.56</v>
       </c>
       <c r="O27" t="n">
-        <v>3.56</v>
+        <v>2.92</v>
       </c>
       <c r="P27" t="n">
-        <v>2.92</v>
+        <v>3.97</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.97</v>
+        <v>29.24</v>
       </c>
       <c r="R27" t="n">
-        <v>29.24</v>
+        <v>340247</v>
       </c>
       <c r="S27" t="n">
-        <v>340247</v>
+        <v>0.32009</v>
       </c>
       <c r="T27" t="n">
-        <v>0.32009</v>
+        <v>0.163194</v>
       </c>
       <c r="U27" t="n">
-        <v>0.163194</v>
+        <v>0.996485</v>
       </c>
       <c r="V27" t="n">
-        <v>0.996485</v>
+        <v>0.996605</v>
       </c>
       <c r="W27" t="n">
-        <v>0.996605</v>
+        <v>0.495259</v>
       </c>
       <c r="X27" t="n">
-        <v>0.495259</v>
+        <v>-0.467999</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.467999</v>
+        <v>1.120891</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.120891</v>
+        <v>-0.022625</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.022625</v>
+        <v>-4.560737</v>
       </c>
       <c r="AB27" t="n">
-        <v>4.819246</v>
+        <v>4.141877</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4.560737</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.141877</v>
+        <v>-0.001143</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>-0.001143</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.001143</v>
+        <v>0.02</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.001143</v>
+        <v>0.1</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK27" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3463,102 +3319,96 @@
         <v>0.045601</v>
       </c>
       <c r="E28" t="n">
-        <v>0.28</v>
+        <v>0.59</v>
       </c>
       <c r="F28" t="n">
-        <v>0.59</v>
+        <v>0.1</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1</v>
+        <v>103.58799</v>
       </c>
       <c r="H28" t="n">
-        <v>103.58799</v>
+        <v>101.68208</v>
       </c>
       <c r="I28" t="n">
-        <v>101.68208</v>
+        <v>4.9355</v>
       </c>
       <c r="J28" t="n">
-        <v>4.9355</v>
+        <v>4.9349</v>
       </c>
       <c r="K28" t="n">
-        <v>4.9349</v>
+        <v>5711103</v>
       </c>
       <c r="L28" t="n">
-        <v>5711103</v>
+        <v>2220766</v>
       </c>
       <c r="M28" t="n">
-        <v>2220766</v>
+        <v>3490337</v>
       </c>
       <c r="N28" t="n">
-        <v>3490337</v>
+        <v>3.53</v>
       </c>
       <c r="O28" t="n">
-        <v>3.53</v>
+        <v>2.99</v>
       </c>
       <c r="P28" t="n">
-        <v>2.99</v>
+        <v>3.88</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.88</v>
+        <v>29.01</v>
       </c>
       <c r="R28" t="n">
-        <v>29.01</v>
+        <v>348406</v>
       </c>
       <c r="S28" t="n">
-        <v>348406</v>
+        <v>0.7367669999999999</v>
       </c>
       <c r="T28" t="n">
-        <v>0.7367669999999999</v>
+        <v>-0.241748</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.241748</v>
+        <v>-2.412259</v>
       </c>
       <c r="V28" t="n">
-        <v>-2.412259</v>
+        <v>-2.412545</v>
       </c>
       <c r="W28" t="n">
-        <v>-2.412545</v>
+        <v>1.013388</v>
       </c>
       <c r="X28" t="n">
-        <v>1.013388</v>
+        <v>0.723782</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.723782</v>
+        <v>1.198521</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.198521</v>
+        <v>2.397964</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.397964</v>
+        <v>-3.457004</v>
       </c>
       <c r="AB28" t="n">
-        <v>4.683537</v>
+        <v>3.851383</v>
       </c>
       <c r="AC28" t="n">
-        <v>-3.457004</v>
+        <v>-0.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.851383</v>
+        <v>-0.001678</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.5</v>
+        <v>-0.001678</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.001678</v>
+        <v>-0.03</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.001678</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AH28" t="n">
-        <v>-0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="AK28" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -3576,102 +3426,96 @@
         <v>0.044537</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="F29" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="G29" t="n">
-        <v>0.55</v>
+        <v>104.88262</v>
       </c>
       <c r="H29" t="n">
-        <v>104.88262</v>
+        <v>101.68652</v>
       </c>
       <c r="I29" t="n">
-        <v>101.68652</v>
+        <v>4.8413</v>
       </c>
       <c r="J29" t="n">
-        <v>4.8413</v>
+        <v>4.8407</v>
       </c>
       <c r="K29" t="n">
-        <v>4.8407</v>
+        <v>5805157</v>
       </c>
       <c r="L29" t="n">
-        <v>5805157</v>
+        <v>2283485</v>
       </c>
       <c r="M29" t="n">
-        <v>2283485</v>
+        <v>3521672</v>
       </c>
       <c r="N29" t="n">
-        <v>3521672</v>
+        <v>3.29</v>
       </c>
       <c r="O29" t="n">
-        <v>3.29</v>
+        <v>2.59</v>
       </c>
       <c r="P29" t="n">
-        <v>2.59</v>
+        <v>3.75</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.75</v>
+        <v>28.14</v>
       </c>
       <c r="R29" t="n">
-        <v>28.14</v>
+        <v>355034</v>
       </c>
       <c r="S29" t="n">
-        <v>355034</v>
+        <v>1.249788</v>
       </c>
       <c r="T29" t="n">
-        <v>1.249788</v>
+        <v>0.004367</v>
       </c>
       <c r="U29" t="n">
-        <v>0.004367</v>
+        <v>-1.908621</v>
       </c>
       <c r="V29" t="n">
-        <v>-1.908621</v>
+        <v>-1.908853</v>
       </c>
       <c r="W29" t="n">
-        <v>-1.908853</v>
+        <v>1.646862</v>
       </c>
       <c r="X29" t="n">
-        <v>1.646862</v>
+        <v>2.824206</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.824206</v>
+        <v>0.897764</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.897764</v>
+        <v>1.902378</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.902378</v>
+        <v>-3.178284</v>
       </c>
       <c r="AB29" t="n">
-        <v>4.621114</v>
+        <v>3.706988</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.178284</v>
+        <v>-0.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.706988</v>
+        <v>-0.001064</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.5</v>
+        <v>-0.001064</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.001064</v>
+        <v>-0.24</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.001064</v>
+        <v>-0.4</v>
       </c>
       <c r="AH29" t="n">
-        <v>-0.24</v>
+        <v>-0.13</v>
       </c>
       <c r="AI29" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="AK29" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3689,102 +3533,96 @@
         <v>0.043739</v>
       </c>
       <c r="E30" t="n">
-        <v>0.42</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="G30" t="n">
-        <v>0.57</v>
+        <v>104.47589</v>
       </c>
       <c r="H30" t="n">
-        <v>104.47589</v>
+        <v>99.29136</v>
       </c>
       <c r="I30" t="n">
-        <v>99.29136</v>
+        <v>4.9535</v>
       </c>
       <c r="J30" t="n">
-        <v>4.9535</v>
+        <v>4.9529</v>
       </c>
       <c r="K30" t="n">
-        <v>4.9529</v>
+        <v>5794707</v>
       </c>
       <c r="L30" t="n">
-        <v>5794707</v>
+        <v>2234362</v>
       </c>
       <c r="M30" t="n">
-        <v>2234362</v>
+        <v>3560345</v>
       </c>
       <c r="N30" t="n">
-        <v>3560345</v>
+        <v>3.38</v>
       </c>
       <c r="O30" t="n">
-        <v>3.38</v>
+        <v>2.77</v>
       </c>
       <c r="P30" t="n">
-        <v>2.77</v>
+        <v>3.76</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.76</v>
+        <v>28</v>
       </c>
       <c r="R30" t="n">
-        <v>28</v>
+        <v>355066</v>
       </c>
       <c r="S30" t="n">
-        <v>355066</v>
+        <v>-0.387795</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.387795</v>
+        <v>-2.355435</v>
       </c>
       <c r="U30" t="n">
-        <v>-2.355435</v>
+        <v>2.317559</v>
       </c>
       <c r="V30" t="n">
-        <v>2.317559</v>
+        <v>2.317847</v>
       </c>
       <c r="W30" t="n">
-        <v>2.317847</v>
+        <v>-0.180012</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.180012</v>
+        <v>-2.151229</v>
       </c>
       <c r="Y30" t="n">
-        <v>-2.151229</v>
+        <v>1.098143</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.098143</v>
+        <v>0.009013</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.009013</v>
+        <v>-3.31355</v>
       </c>
       <c r="AB30" t="n">
-        <v>4.506637</v>
+        <v>3.820543</v>
       </c>
       <c r="AC30" t="n">
-        <v>-3.31355</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.820543</v>
+        <v>-0.000798</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>-0.000798</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.000798</v>
+        <v>0.09</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.000798</v>
+        <v>0.18</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK30" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -3802,102 +3640,96 @@
         <v>0.041957</v>
       </c>
       <c r="E31" t="n">
-        <v>0.83</v>
+        <v>-0.52</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.52</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>0.8100000000000001</v>
+        <v>104.67291</v>
       </c>
       <c r="H31" t="n">
-        <v>104.67291</v>
+        <v>102.15158</v>
       </c>
       <c r="I31" t="n">
-        <v>102.15158</v>
+        <v>4.9833</v>
       </c>
       <c r="J31" t="n">
-        <v>4.9833</v>
+        <v>4.9827</v>
       </c>
       <c r="K31" t="n">
-        <v>4.9827</v>
+        <v>5815954</v>
       </c>
       <c r="L31" t="n">
-        <v>5815954</v>
+        <v>2235302</v>
       </c>
       <c r="M31" t="n">
-        <v>2235302</v>
+        <v>3580652</v>
       </c>
       <c r="N31" t="n">
-        <v>3580652</v>
+        <v>3.38</v>
       </c>
       <c r="O31" t="n">
-        <v>3.38</v>
+        <v>2.76</v>
       </c>
       <c r="P31" t="n">
-        <v>2.76</v>
+        <v>3.76</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.76</v>
+        <v>27.85</v>
       </c>
       <c r="R31" t="n">
-        <v>27.85</v>
+        <v>352705</v>
       </c>
       <c r="S31" t="n">
-        <v>352705</v>
+        <v>0.188579</v>
       </c>
       <c r="T31" t="n">
-        <v>0.188579</v>
+        <v>2.880633</v>
       </c>
       <c r="U31" t="n">
-        <v>2.880633</v>
+        <v>0.601595</v>
       </c>
       <c r="V31" t="n">
-        <v>0.601595</v>
+        <v>0.601668</v>
       </c>
       <c r="W31" t="n">
-        <v>0.601668</v>
+        <v>0.366662</v>
       </c>
       <c r="X31" t="n">
-        <v>0.366662</v>
+        <v>0.04207</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.04207</v>
+        <v>0.570366</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.570366</v>
+        <v>-0.664947</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.664947</v>
+        <v>-3.758575</v>
       </c>
       <c r="AB31" t="n">
-        <v>4.496274</v>
+        <v>3.861754</v>
       </c>
       <c r="AC31" t="n">
-        <v>-3.758575</v>
+        <v>-0.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.861754</v>
+        <v>-0.001782</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.5</v>
+        <v>-0.001782</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.001782</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.001782</v>
+        <v>-0.01</v>
       </c>
       <c r="AH31" t="n">
         <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -3915,102 +3747,96 @@
         <v>0.04142</v>
       </c>
       <c r="E32" t="n">
-        <v>0.16</v>
+        <v>-0.47</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.47</v>
+        <v>0.19</v>
       </c>
       <c r="G32" t="n">
-        <v>0.19</v>
+        <v>104.68779</v>
       </c>
       <c r="H32" t="n">
-        <v>104.68779</v>
+        <v>109.57244</v>
       </c>
       <c r="I32" t="n">
-        <v>109.57244</v>
+        <v>4.9962</v>
       </c>
       <c r="J32" t="n">
-        <v>4.9962</v>
+        <v>4.9956</v>
       </c>
       <c r="K32" t="n">
-        <v>4.9956</v>
+        <v>5899742</v>
       </c>
       <c r="L32" t="n">
-        <v>5899742</v>
+        <v>2285775</v>
       </c>
       <c r="M32" t="n">
-        <v>2285775</v>
+        <v>3613967</v>
       </c>
       <c r="N32" t="n">
-        <v>3613967</v>
+        <v>3.33</v>
       </c>
       <c r="O32" t="n">
-        <v>3.33</v>
+        <v>2.71</v>
       </c>
       <c r="P32" t="n">
-        <v>2.71</v>
+        <v>3.71</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.71</v>
+        <v>28.14</v>
       </c>
       <c r="R32" t="n">
-        <v>28.14</v>
+        <v>355008</v>
       </c>
       <c r="S32" t="n">
-        <v>355008</v>
+        <v>0.014216</v>
       </c>
       <c r="T32" t="n">
-        <v>0.014216</v>
+        <v>7.264557</v>
       </c>
       <c r="U32" t="n">
-        <v>7.264557</v>
+        <v>0.258865</v>
       </c>
       <c r="V32" t="n">
-        <v>0.258865</v>
+        <v>0.258896</v>
       </c>
       <c r="W32" t="n">
-        <v>0.258896</v>
+        <v>1.440658</v>
       </c>
       <c r="X32" t="n">
-        <v>1.440658</v>
+        <v>2.257995</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.257995</v>
+        <v>0.930417</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.930417</v>
+        <v>0.652954</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.652954</v>
+        <v>-4.25878</v>
       </c>
       <c r="AB32" t="n">
-        <v>3.925596</v>
+        <v>3.397348</v>
       </c>
       <c r="AC32" t="n">
-        <v>-4.25878</v>
+        <v>-0.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.397348</v>
+        <v>-0.000537</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.5</v>
+        <v>-0.000537</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="AH32" t="n">
         <v>-0.05</v>
       </c>
       <c r="AI32" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AK32" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -4028,102 +3854,96 @@
         <v>0.040168</v>
       </c>
       <c r="E33" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="F33" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
       <c r="G33" t="n">
-        <v>0.37</v>
+        <v>104.6751</v>
       </c>
       <c r="H33" t="n">
-        <v>104.6751</v>
+        <v>109.25226</v>
       </c>
       <c r="I33" t="n">
-        <v>109.25226</v>
+        <v>5.1718</v>
       </c>
       <c r="J33" t="n">
-        <v>5.1718</v>
+        <v>5.1712</v>
       </c>
       <c r="K33" t="n">
-        <v>5.1712</v>
+        <v>5915538</v>
       </c>
       <c r="L33" t="n">
-        <v>5915538</v>
+        <v>2268879</v>
       </c>
       <c r="M33" t="n">
-        <v>2268879</v>
+        <v>3646659</v>
       </c>
       <c r="N33" t="n">
-        <v>3646659</v>
+        <v>3.37</v>
       </c>
       <c r="O33" t="n">
-        <v>3.37</v>
+        <v>2.76</v>
       </c>
       <c r="P33" t="n">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.75</v>
+        <v>27.86</v>
       </c>
       <c r="R33" t="n">
-        <v>27.86</v>
+        <v>351599</v>
       </c>
       <c r="S33" t="n">
-        <v>351599</v>
+        <v>-0.012122</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.012122</v>
+        <v>-0.292209</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.292209</v>
+        <v>3.514671</v>
       </c>
       <c r="V33" t="n">
-        <v>3.514671</v>
+        <v>3.515093</v>
       </c>
       <c r="W33" t="n">
-        <v>3.515093</v>
+        <v>0.267741</v>
       </c>
       <c r="X33" t="n">
-        <v>0.267741</v>
+        <v>-0.7391799999999999</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.7391799999999999</v>
+        <v>0.904602</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.904602</v>
+        <v>-0.96026</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.96026</v>
+        <v>-3.040871</v>
       </c>
       <c r="AB33" t="n">
-        <v>3.688016</v>
+        <v>3.232784</v>
       </c>
       <c r="AC33" t="n">
-        <v>-3.040871</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.232784</v>
+        <v>-0.001252</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>-0.001252</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.001252</v>
+        <v>0.04</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.001252</v>
+        <v>0.05</v>
       </c>
       <c r="AH33" t="n">
         <v>0.04</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK33" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -4141,102 +3961,96 @@
         <v>0.039484</v>
       </c>
       <c r="E34" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F34" t="n">
         <v>0.46</v>
       </c>
-      <c r="F34" t="n">
-        <v>0.89</v>
-      </c>
       <c r="G34" t="n">
-        <v>0.46</v>
+        <v>105.5521</v>
       </c>
       <c r="H34" t="n">
-        <v>105.5521</v>
+        <v>104.71219</v>
       </c>
       <c r="I34" t="n">
-        <v>104.71219</v>
+        <v>5.2416</v>
       </c>
       <c r="J34" t="n">
-        <v>5.2416</v>
+        <v>5.241</v>
       </c>
       <c r="K34" t="n">
-        <v>5.241</v>
+        <v>5953960</v>
       </c>
       <c r="L34" t="n">
-        <v>5953960</v>
+        <v>2278309</v>
       </c>
       <c r="M34" t="n">
-        <v>2278309</v>
+        <v>3675652</v>
       </c>
       <c r="N34" t="n">
-        <v>3675652</v>
+        <v>3.43</v>
       </c>
       <c r="O34" t="n">
-        <v>3.43</v>
+        <v>2.8</v>
       </c>
       <c r="P34" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.82</v>
+        <v>27.75</v>
       </c>
       <c r="R34" t="n">
-        <v>27.75</v>
+        <v>355560</v>
       </c>
       <c r="S34" t="n">
-        <v>355560</v>
+        <v>0.837831</v>
       </c>
       <c r="T34" t="n">
-        <v>0.837831</v>
+        <v>-4.155585</v>
       </c>
       <c r="U34" t="n">
-        <v>-4.155585</v>
+        <v>1.349627</v>
       </c>
       <c r="V34" t="n">
-        <v>1.349627</v>
+        <v>1.349783</v>
       </c>
       <c r="W34" t="n">
-        <v>1.349783</v>
+        <v>0.64951</v>
       </c>
       <c r="X34" t="n">
-        <v>0.64951</v>
+        <v>0.415624</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.415624</v>
+        <v>0.795057</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.795057</v>
+        <v>1.126567</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.126567</v>
+        <v>-0.344269</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.925952</v>
+        <v>3.335647</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.344269</v>
+        <v>-0.25</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.335647</v>
+        <v>-0.000684</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.25</v>
+        <v>-0.000684</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.000684</v>
+        <v>0.06</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.000684</v>
+        <v>0.04</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK34" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -4254,102 +4068,96 @@
         <v>0.03927</v>
       </c>
       <c r="E35" t="n">
-        <v>0.21</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="G35" t="n">
-        <v>0.25</v>
+        <v>106.65779</v>
       </c>
       <c r="H35" t="n">
-        <v>106.65779</v>
+        <v>105.87342</v>
       </c>
       <c r="I35" t="n">
-        <v>105.87342</v>
+        <v>5.5589</v>
       </c>
       <c r="J35" t="n">
-        <v>5.5589</v>
+        <v>5.5583</v>
       </c>
       <c r="K35" t="n">
-        <v>5.5583</v>
+        <v>6041898</v>
       </c>
       <c r="L35" t="n">
-        <v>6041898</v>
+        <v>2336858</v>
       </c>
       <c r="M35" t="n">
-        <v>2336858</v>
+        <v>3705041</v>
       </c>
       <c r="N35" t="n">
-        <v>3705041</v>
+        <v>3.29</v>
       </c>
       <c r="O35" t="n">
-        <v>3.29</v>
+        <v>2.64</v>
       </c>
       <c r="P35" t="n">
-        <v>2.64</v>
+        <v>3.71</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.71</v>
+        <v>27.81</v>
       </c>
       <c r="R35" t="n">
-        <v>27.81</v>
+        <v>357827</v>
       </c>
       <c r="S35" t="n">
-        <v>357827</v>
+        <v>1.04753</v>
       </c>
       <c r="T35" t="n">
-        <v>1.04753</v>
+        <v>1.108973</v>
       </c>
       <c r="U35" t="n">
-        <v>1.108973</v>
+        <v>6.053495</v>
       </c>
       <c r="V35" t="n">
-        <v>6.053495</v>
+        <v>6.054188</v>
       </c>
       <c r="W35" t="n">
-        <v>6.054188</v>
+        <v>1.476967</v>
       </c>
       <c r="X35" t="n">
-        <v>1.476967</v>
+        <v>2.569845</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.569845</v>
+        <v>0.799559</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.799559</v>
+        <v>0.637586</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.637586</v>
+        <v>2.440035</v>
       </c>
       <c r="AB35" t="n">
-        <v>4.227578</v>
+        <v>3.697684</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.440035</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.697684</v>
+        <v>-0.000214</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>-0.000214</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.000214</v>
+        <v>-0.14</v>
       </c>
       <c r="AG35" t="n">
-        <v>-0.000214</v>
+        <v>-0.16</v>
       </c>
       <c r="AH35" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="AI35" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="AK35" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -4367,102 +4175,96 @@
         <v>0.03927</v>
       </c>
       <c r="E36" t="n">
-        <v>0.38</v>
+        <v>0.61</v>
       </c>
       <c r="F36" t="n">
-        <v>0.61</v>
+        <v>0.26</v>
       </c>
       <c r="G36" t="n">
-        <v>0.26</v>
+        <v>107.01873</v>
       </c>
       <c r="H36" t="n">
-        <v>107.01873</v>
+        <v>111.50432</v>
       </c>
       <c r="I36" t="n">
-        <v>111.50432</v>
+        <v>5.6621</v>
       </c>
       <c r="J36" t="n">
-        <v>5.6621</v>
+        <v>5.6615</v>
       </c>
       <c r="K36" t="n">
-        <v>5.6615</v>
+        <v>6069205</v>
       </c>
       <c r="L36" t="n">
-        <v>6069205</v>
+        <v>2323362</v>
       </c>
       <c r="M36" t="n">
-        <v>2323362</v>
+        <v>3745844</v>
       </c>
       <c r="N36" t="n">
-        <v>3745844</v>
+        <v>3.3</v>
       </c>
       <c r="O36" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="P36" t="n">
-        <v>2.52</v>
+        <v>3.78</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.78</v>
+        <v>27.74</v>
       </c>
       <c r="R36" t="n">
-        <v>27.74</v>
+        <v>363282</v>
       </c>
       <c r="S36" t="n">
-        <v>363282</v>
+        <v>0.338409</v>
       </c>
       <c r="T36" t="n">
-        <v>0.338409</v>
+        <v>5.318521</v>
       </c>
       <c r="U36" t="n">
-        <v>5.318521</v>
+        <v>1.856482</v>
       </c>
       <c r="V36" t="n">
-        <v>1.856482</v>
+        <v>1.856683</v>
       </c>
       <c r="W36" t="n">
-        <v>1.856683</v>
+        <v>0.451961</v>
       </c>
       <c r="X36" t="n">
-        <v>0.451961</v>
+        <v>-0.577528</v>
       </c>
       <c r="Y36" t="n">
-        <v>-0.577528</v>
+        <v>1.101283</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.101283</v>
+        <v>1.52448</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.52448</v>
+        <v>3.812368</v>
       </c>
       <c r="AB36" t="n">
-        <v>4.498245</v>
+        <v>4.060953</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.812368</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>4.060953</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI36" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK36" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -4480,102 +4282,96 @@
         <v>0.03927</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.02</v>
+        <v>0.29</v>
       </c>
       <c r="F37" t="n">
-        <v>0.29</v>
+        <v>-0.14</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.14</v>
+        <v>107.16697</v>
       </c>
       <c r="H37" t="n">
-        <v>107.16697</v>
+        <v>110.06264</v>
       </c>
       <c r="I37" t="n">
-        <v>110.06264</v>
+        <v>5.6562</v>
       </c>
       <c r="J37" t="n">
-        <v>5.6562</v>
+        <v>5.6556</v>
       </c>
       <c r="K37" t="n">
-        <v>5.6556</v>
+        <v>6135298</v>
       </c>
       <c r="L37" t="n">
-        <v>6135298</v>
+        <v>2344397</v>
       </c>
       <c r="M37" t="n">
-        <v>2344397</v>
+        <v>3790900</v>
       </c>
       <c r="N37" t="n">
-        <v>3790900</v>
+        <v>3.33</v>
       </c>
       <c r="O37" t="n">
-        <v>3.33</v>
+        <v>2.55</v>
       </c>
       <c r="P37" t="n">
-        <v>2.55</v>
+        <v>3.82</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.82</v>
+        <v>27.59</v>
       </c>
       <c r="R37" t="n">
-        <v>27.59</v>
+        <v>369214</v>
       </c>
       <c r="S37" t="n">
-        <v>369214</v>
+        <v>0.138518</v>
       </c>
       <c r="T37" t="n">
-        <v>0.138518</v>
+        <v>-1.292936</v>
       </c>
       <c r="U37" t="n">
-        <v>-1.292936</v>
+        <v>-0.104202</v>
       </c>
       <c r="V37" t="n">
-        <v>-0.104202</v>
+        <v>-0.104213</v>
       </c>
       <c r="W37" t="n">
-        <v>-0.104213</v>
+        <v>1.088989</v>
       </c>
       <c r="X37" t="n">
-        <v>1.088989</v>
+        <v>0.905369</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.905369</v>
+        <v>1.202826</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.202826</v>
+        <v>1.632891</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.632891</v>
+        <v>4.259387</v>
       </c>
       <c r="AB37" t="n">
-        <v>4.237599</v>
+        <v>3.707852</v>
       </c>
       <c r="AC37" t="n">
-        <v>4.259387</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.707852</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK37" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4593,102 +4389,96 @@
         <v>0.039612</v>
       </c>
       <c r="E38" t="n">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="F38" t="n">
-        <v>0.62</v>
+        <v>0.48</v>
       </c>
       <c r="G38" t="n">
-        <v>0.48</v>
+        <v>108.02415</v>
       </c>
       <c r="H38" t="n">
-        <v>108.02415</v>
+        <v>107.08272</v>
       </c>
       <c r="I38" t="n">
-        <v>107.08272</v>
+        <v>5.4481</v>
       </c>
       <c r="J38" t="n">
-        <v>5.4481</v>
+        <v>5.4475</v>
       </c>
       <c r="K38" t="n">
-        <v>5.4475</v>
+        <v>6216528</v>
       </c>
       <c r="L38" t="n">
-        <v>6216528</v>
+        <v>2384828</v>
       </c>
       <c r="M38" t="n">
-        <v>2384828</v>
+        <v>3831700</v>
       </c>
       <c r="N38" t="n">
-        <v>3831700</v>
+        <v>3.34</v>
       </c>
       <c r="O38" t="n">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="P38" t="n">
-        <v>2.56</v>
+        <v>3.83</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.83</v>
+        <v>27.49</v>
       </c>
       <c r="R38" t="n">
-        <v>27.49</v>
+        <v>372016</v>
       </c>
       <c r="S38" t="n">
-        <v>372016</v>
+        <v>0.799855</v>
       </c>
       <c r="T38" t="n">
-        <v>0.799855</v>
+        <v>-2.707476</v>
       </c>
       <c r="U38" t="n">
-        <v>-2.707476</v>
+        <v>-3.679149</v>
       </c>
       <c r="V38" t="n">
-        <v>-3.679149</v>
+        <v>-3.679539</v>
       </c>
       <c r="W38" t="n">
-        <v>-3.679539</v>
+        <v>1.323978</v>
       </c>
       <c r="X38" t="n">
-        <v>1.323978</v>
+        <v>1.72458</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.72458</v>
+        <v>1.076262</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.076262</v>
+        <v>0.7589089999999999</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.7589089999999999</v>
+        <v>4.519075</v>
       </c>
       <c r="AB38" t="n">
-        <v>4.42474</v>
+        <v>4.091149</v>
       </c>
       <c r="AC38" t="n">
-        <v>4.519075</v>
+        <v>0.25</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.091149</v>
+        <v>0.000342</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.25</v>
+        <v>0.000342</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="AH38" t="n">
         <v>0.01</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK38" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -4706,102 +4496,96 @@
         <v>0.040168</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.52</v>
       </c>
       <c r="F39" t="n">
-        <v>1.52</v>
+        <v>0.61</v>
       </c>
       <c r="G39" t="n">
-        <v>0.61</v>
+        <v>108.23273</v>
       </c>
       <c r="H39" t="n">
-        <v>108.23273</v>
+        <v>109.17883</v>
       </c>
       <c r="I39" t="n">
-        <v>109.17883</v>
+        <v>5.7779</v>
       </c>
       <c r="J39" t="n">
-        <v>5.7779</v>
+        <v>5.7773</v>
       </c>
       <c r="K39" t="n">
-        <v>5.7773</v>
+        <v>6275117</v>
       </c>
       <c r="L39" t="n">
-        <v>6275117</v>
+        <v>2397533</v>
       </c>
       <c r="M39" t="n">
-        <v>2397533</v>
+        <v>3877584</v>
       </c>
       <c r="N39" t="n">
-        <v>3877584</v>
+        <v>3.3</v>
       </c>
       <c r="O39" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="P39" t="n">
-        <v>2.52</v>
+        <v>3.79</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.79</v>
+        <v>27.94</v>
       </c>
       <c r="R39" t="n">
-        <v>27.94</v>
+        <v>366096</v>
       </c>
       <c r="S39" t="n">
-        <v>366096</v>
+        <v>0.193086</v>
       </c>
       <c r="T39" t="n">
-        <v>0.193086</v>
+        <v>1.957468</v>
       </c>
       <c r="U39" t="n">
-        <v>1.957468</v>
+        <v>6.053487</v>
       </c>
       <c r="V39" t="n">
-        <v>6.053487</v>
+        <v>6.054153</v>
       </c>
       <c r="W39" t="n">
-        <v>6.054153</v>
+        <v>0.9424709999999999</v>
       </c>
       <c r="X39" t="n">
-        <v>0.9424709999999999</v>
+        <v>0.532743</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.532743</v>
+        <v>1.197484</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.197484</v>
+        <v>-1.591329</v>
       </c>
       <c r="AA39" t="n">
-        <v>-1.591329</v>
+        <v>5.579866</v>
       </c>
       <c r="AB39" t="n">
-        <v>4.758099</v>
+        <v>4.600584</v>
       </c>
       <c r="AC39" t="n">
-        <v>5.579866</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>4.600584</v>
+        <v>0.000556</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>0.000556</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="AH39" t="n">
         <v>-0.04</v>
       </c>
       <c r="AI39" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AK39" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -4819,102 +4603,96 @@
         <v>0.04158</v>
       </c>
       <c r="E40" t="n">
-        <v>0.39</v>
+        <v>1.3</v>
       </c>
       <c r="F40" t="n">
-        <v>1.3</v>
+        <v>0.33</v>
       </c>
       <c r="G40" t="n">
-        <v>0.33</v>
+        <v>107.99539</v>
       </c>
       <c r="H40" t="n">
-        <v>107.99539</v>
+        <v>105.48993</v>
       </c>
       <c r="I40" t="n">
-        <v>105.48993</v>
+        <v>6.0535</v>
       </c>
       <c r="J40" t="n">
-        <v>6.0535</v>
+        <v>6.0529</v>
       </c>
       <c r="K40" t="n">
-        <v>6.0529</v>
+        <v>6365690</v>
       </c>
       <c r="L40" t="n">
-        <v>6365690</v>
+        <v>2436022</v>
       </c>
       <c r="M40" t="n">
-        <v>2436022</v>
+        <v>3929668</v>
       </c>
       <c r="N40" t="n">
-        <v>3929668</v>
+        <v>3.27</v>
       </c>
       <c r="O40" t="n">
-        <v>3.27</v>
+        <v>2.5</v>
       </c>
       <c r="P40" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.75</v>
+        <v>28.45</v>
       </c>
       <c r="R40" t="n">
-        <v>28.45</v>
+        <v>363003</v>
       </c>
       <c r="S40" t="n">
-        <v>363003</v>
+        <v>-0.219287</v>
       </c>
       <c r="T40" t="n">
-        <v>-0.219287</v>
+        <v>-3.378769</v>
       </c>
       <c r="U40" t="n">
-        <v>-3.378769</v>
+        <v>4.769899</v>
       </c>
       <c r="V40" t="n">
-        <v>4.769899</v>
+        <v>4.770394</v>
       </c>
       <c r="W40" t="n">
-        <v>4.770394</v>
+        <v>1.443368</v>
       </c>
       <c r="X40" t="n">
-        <v>1.443368</v>
+        <v>1.605359</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.605359</v>
+        <v>1.343208</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.343208</v>
+        <v>-0.8448600000000001</v>
       </c>
       <c r="AA40" t="n">
-        <v>-0.8448600000000001</v>
+        <v>6.325086</v>
       </c>
       <c r="AB40" t="n">
-        <v>4.873011</v>
+        <v>4.840925</v>
       </c>
       <c r="AC40" t="n">
-        <v>6.325086</v>
+        <v>0.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.840925</v>
+        <v>0.001412</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.5</v>
+        <v>0.001412</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.001412</v>
+        <v>-0.03</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.001412</v>
+        <v>-0.02</v>
       </c>
       <c r="AH40" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="AI40" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AK40" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4932,102 +4710,96 @@
         <v>0.044158</v>
       </c>
       <c r="E41" t="n">
-        <v>0.52</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="G41" t="n">
-        <v>0.48</v>
+        <v>107.3722</v>
       </c>
       <c r="H41" t="n">
-        <v>107.3722</v>
+        <v>104.15749</v>
       </c>
       <c r="I41" t="n">
-        <v>104.15749</v>
+        <v>6.1923</v>
       </c>
       <c r="J41" t="n">
-        <v>6.1923</v>
+        <v>6.1917</v>
       </c>
       <c r="K41" t="n">
-        <v>6.1917</v>
+        <v>6464602</v>
       </c>
       <c r="L41" t="n">
-        <v>6464602</v>
+        <v>2499177</v>
       </c>
       <c r="M41" t="n">
-        <v>2499177</v>
+        <v>3965425</v>
       </c>
       <c r="N41" t="n">
-        <v>3965425</v>
+        <v>3.08</v>
       </c>
       <c r="O41" t="n">
-        <v>3.08</v>
+        <v>2.21</v>
       </c>
       <c r="P41" t="n">
-        <v>2.21</v>
+        <v>3.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.63</v>
+        <v>28.5</v>
       </c>
       <c r="R41" t="n">
-        <v>28.5</v>
+        <v>329730</v>
       </c>
       <c r="S41" t="n">
-        <v>329730</v>
+        <v>-0.577052</v>
       </c>
       <c r="T41" t="n">
-        <v>-0.577052</v>
+        <v>-1.263097</v>
       </c>
       <c r="U41" t="n">
-        <v>-1.263097</v>
+        <v>2.292888</v>
       </c>
       <c r="V41" t="n">
-        <v>2.292888</v>
+        <v>2.293116</v>
       </c>
       <c r="W41" t="n">
-        <v>2.293116</v>
+        <v>1.55383</v>
       </c>
       <c r="X41" t="n">
-        <v>1.55383</v>
+        <v>2.592546</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.592546</v>
+        <v>0.909924</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.909924</v>
+        <v>-9.166040000000001</v>
       </c>
       <c r="AA41" t="n">
-        <v>-9.166040000000001</v>
+        <v>6.536174</v>
       </c>
       <c r="AB41" t="n">
-        <v>4.831296</v>
+        <v>4.767938</v>
       </c>
       <c r="AC41" t="n">
-        <v>6.536174</v>
+        <v>1</v>
       </c>
       <c r="AD41" t="n">
-        <v>4.767938</v>
+        <v>0.002578</v>
       </c>
       <c r="AE41" t="n">
-        <v>1</v>
+        <v>0.002578</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.002578</v>
+        <v>-0.19</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.002578</v>
+        <v>-0.29</v>
       </c>
       <c r="AH41" t="n">
-        <v>-0.19</v>
+        <v>-0.12</v>
       </c>
       <c r="AI41" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK41" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -5045,102 +4817,96 @@
         <v>0.045833</v>
       </c>
       <c r="E42" t="n">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="F42" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>108.10202</v>
       </c>
       <c r="H42" t="n">
-        <v>108.10202</v>
+        <v>102.62361</v>
       </c>
       <c r="I42" t="n">
-        <v>102.62361</v>
+        <v>5.8301</v>
       </c>
       <c r="J42" t="n">
-        <v>5.8301</v>
+        <v>5.8295</v>
       </c>
       <c r="K42" t="n">
-        <v>5.8295</v>
+        <v>6465016</v>
       </c>
       <c r="L42" t="n">
-        <v>6465016</v>
+        <v>2451957</v>
       </c>
       <c r="M42" t="n">
-        <v>2451957</v>
+        <v>4013059</v>
       </c>
       <c r="N42" t="n">
-        <v>4013059</v>
+        <v>3.34</v>
       </c>
       <c r="O42" t="n">
-        <v>3.34</v>
+        <v>2.43</v>
       </c>
       <c r="P42" t="n">
-        <v>2.43</v>
+        <v>3.89</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.89</v>
+        <v>29.88</v>
       </c>
       <c r="R42" t="n">
-        <v>29.88</v>
+        <v>328303</v>
       </c>
       <c r="S42" t="n">
-        <v>328303</v>
+        <v>0.67971</v>
       </c>
       <c r="T42" t="n">
-        <v>0.67971</v>
+        <v>-1.472655</v>
       </c>
       <c r="U42" t="n">
-        <v>-1.472655</v>
+        <v>-5.8492</v>
       </c>
       <c r="V42" t="n">
-        <v>-5.8492</v>
+        <v>-5.849767</v>
       </c>
       <c r="W42" t="n">
-        <v>-5.849767</v>
+        <v>0.006404</v>
       </c>
       <c r="X42" t="n">
-        <v>0.006404</v>
+        <v>-1.889422</v>
       </c>
       <c r="Y42" t="n">
-        <v>-1.889422</v>
+        <v>1.201233</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.201233</v>
+        <v>-0.432778</v>
       </c>
       <c r="AA42" t="n">
-        <v>-0.432778</v>
+        <v>6.749097</v>
       </c>
       <c r="AB42" t="n">
-        <v>4.559874</v>
+        <v>4.174145</v>
       </c>
       <c r="AC42" t="n">
-        <v>6.749097</v>
+        <v>1</v>
       </c>
       <c r="AD42" t="n">
-        <v>4.174145</v>
+        <v>0.001675</v>
       </c>
       <c r="AE42" t="n">
-        <v>1</v>
+        <v>0.001675</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.001675</v>
+        <v>0.26</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.001675</v>
+        <v>0.22</v>
       </c>
       <c r="AH42" t="n">
         <v>0.26</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK42" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -5158,102 +4924,96 @@
         <v>0.049037</v>
       </c>
       <c r="E43" t="n">
-        <v>1.31</v>
+        <v>1.06</v>
       </c>
       <c r="F43" t="n">
-        <v>1.06</v>
+        <v>1.48</v>
       </c>
       <c r="G43" t="n">
-        <v>1.48</v>
+        <v>108.64347</v>
       </c>
       <c r="H43" t="n">
-        <v>108.64347</v>
+        <v>106.82695</v>
       </c>
       <c r="I43" t="n">
-        <v>106.82695</v>
+        <v>5.8488</v>
       </c>
       <c r="J43" t="n">
-        <v>5.8488</v>
+        <v>5.8482</v>
       </c>
       <c r="K43" t="n">
-        <v>5.8482</v>
+        <v>6511444</v>
       </c>
       <c r="L43" t="n">
-        <v>6511444</v>
+        <v>2477151</v>
       </c>
       <c r="M43" t="n">
-        <v>2477151</v>
+        <v>4034293</v>
       </c>
       <c r="N43" t="n">
-        <v>4034293</v>
+        <v>3.41</v>
       </c>
       <c r="O43" t="n">
-        <v>3.41</v>
+        <v>2.52</v>
       </c>
       <c r="P43" t="n">
-        <v>2.52</v>
+        <v>3.96</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.96</v>
+        <v>30.53</v>
       </c>
       <c r="R43" t="n">
-        <v>30.53</v>
+        <v>332508</v>
       </c>
       <c r="S43" t="n">
-        <v>332508</v>
+        <v>0.500869</v>
       </c>
       <c r="T43" t="n">
-        <v>0.500869</v>
+        <v>4.09588</v>
       </c>
       <c r="U43" t="n">
-        <v>4.09588</v>
+        <v>0.320749</v>
       </c>
       <c r="V43" t="n">
-        <v>0.320749</v>
+        <v>0.320782</v>
       </c>
       <c r="W43" t="n">
-        <v>0.320782</v>
+        <v>0.7181419999999999</v>
       </c>
       <c r="X43" t="n">
-        <v>0.7181419999999999</v>
+        <v>1.027506</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.027506</v>
+        <v>0.529123</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.529123</v>
+        <v>1.280829</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.280829</v>
+        <v>8.444549</v>
       </c>
       <c r="AB43" t="n">
-        <v>5.05763</v>
+        <v>4.866504</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.444549</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>4.866504</v>
+        <v>0.003204</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>0.003204</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.003204</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.003204</v>
+        <v>0.09</v>
       </c>
       <c r="AH43" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK43" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -5271,102 +5031,96 @@
         <v>0.050508</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.34</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.34</v>
+        <v>0.51</v>
       </c>
       <c r="G44" t="n">
-        <v>0.51</v>
+        <v>110.0586</v>
       </c>
       <c r="H44" t="n">
-        <v>110.0586</v>
+        <v>114.02633</v>
       </c>
       <c r="I44" t="n">
-        <v>114.02633</v>
+        <v>5.7422</v>
       </c>
       <c r="J44" t="n">
-        <v>5.7422</v>
+        <v>5.7416</v>
       </c>
       <c r="K44" t="n">
-        <v>5.7416</v>
+        <v>6576464</v>
       </c>
       <c r="L44" t="n">
-        <v>6576464</v>
+        <v>2498262</v>
       </c>
       <c r="M44" t="n">
-        <v>2498262</v>
+        <v>4078202</v>
       </c>
       <c r="N44" t="n">
-        <v>4078202</v>
+        <v>3.44</v>
       </c>
       <c r="O44" t="n">
-        <v>3.44</v>
+        <v>2.49</v>
       </c>
       <c r="P44" t="n">
-        <v>2.49</v>
+        <v>4.03</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.03</v>
+        <v>31.34</v>
       </c>
       <c r="R44" t="n">
-        <v>31.34</v>
+        <v>336157</v>
       </c>
       <c r="S44" t="n">
-        <v>336157</v>
+        <v>1.302545</v>
       </c>
       <c r="T44" t="n">
-        <v>1.302545</v>
+        <v>6.739292</v>
       </c>
       <c r="U44" t="n">
-        <v>6.739292</v>
+        <v>-1.822596</v>
       </c>
       <c r="V44" t="n">
-        <v>-1.822596</v>
+        <v>-1.822783</v>
       </c>
       <c r="W44" t="n">
-        <v>-1.822783</v>
+        <v>0.99855</v>
       </c>
       <c r="X44" t="n">
-        <v>0.99855</v>
+        <v>0.852229</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.852229</v>
+        <v>1.088394</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.088394</v>
+        <v>1.097417</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.097417</v>
+        <v>8.586193</v>
       </c>
       <c r="AB44" t="n">
-        <v>5.47719</v>
+        <v>5.201441</v>
       </c>
       <c r="AC44" t="n">
-        <v>8.586193</v>
+        <v>1</v>
       </c>
       <c r="AD44" t="n">
-        <v>5.201441</v>
+        <v>0.001471</v>
       </c>
       <c r="AE44" t="n">
-        <v>1</v>
+        <v>0.001471</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.001471</v>
+        <v>0.03</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.001471</v>
+        <v>-0.03</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI44" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK44" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -5384,102 +5138,96 @@
         <v>0.052531</v>
       </c>
       <c r="E45" t="n">
-        <v>0.43</v>
+        <v>0.24</v>
       </c>
       <c r="F45" t="n">
-        <v>0.24</v>
+        <v>0.48</v>
       </c>
       <c r="G45" t="n">
-        <v>0.48</v>
+        <v>109.59971</v>
       </c>
       <c r="H45" t="n">
-        <v>109.59971</v>
+        <v>112.58856</v>
       </c>
       <c r="I45" t="n">
-        <v>112.58856</v>
+        <v>5.6608</v>
       </c>
       <c r="J45" t="n">
-        <v>5.6608</v>
+        <v>5.6602</v>
       </c>
       <c r="K45" t="n">
-        <v>5.6602</v>
+        <v>6623948</v>
       </c>
       <c r="L45" t="n">
-        <v>6623948</v>
+        <v>2512426</v>
       </c>
       <c r="M45" t="n">
-        <v>2512426</v>
+        <v>4111522</v>
       </c>
       <c r="N45" t="n">
-        <v>4111522</v>
+        <v>3.67</v>
       </c>
       <c r="O45" t="n">
-        <v>3.67</v>
+        <v>2.72</v>
       </c>
       <c r="P45" t="n">
-        <v>2.72</v>
+        <v>4.25</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.25</v>
+        <v>31.63</v>
       </c>
       <c r="R45" t="n">
-        <v>31.63</v>
+        <v>340789</v>
       </c>
       <c r="S45" t="n">
-        <v>340789</v>
+        <v>-0.416951</v>
       </c>
       <c r="T45" t="n">
-        <v>-0.416951</v>
+        <v>-1.260911</v>
       </c>
       <c r="U45" t="n">
-        <v>-1.260911</v>
+        <v>-1.417575</v>
       </c>
       <c r="V45" t="n">
-        <v>-1.417575</v>
+        <v>-1.417723</v>
       </c>
       <c r="W45" t="n">
-        <v>-1.417723</v>
+        <v>0.722029</v>
       </c>
       <c r="X45" t="n">
-        <v>0.722029</v>
+        <v>0.566954</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.566954</v>
+        <v>0.8170269999999999</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.8170269999999999</v>
+        <v>1.377928</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.377928</v>
+        <v>8.510418</v>
       </c>
       <c r="AB45" t="n">
-        <v>5.529729</v>
+        <v>5.316736</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.510418</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>5.316736</v>
+        <v>0.002023</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>0.002023</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AK45" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -5497,102 +5245,96 @@
         <v>0.053936</v>
       </c>
       <c r="E46" t="n">
-        <v>0.26</v>
+        <v>-0.49</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.49</v>
+        <v>0.35</v>
       </c>
       <c r="G46" t="n">
-        <v>0.35</v>
+        <v>108.80425</v>
       </c>
       <c r="H46" t="n">
-        <v>108.80425</v>
+        <v>108.55662</v>
       </c>
       <c r="I46" t="n">
-        <v>108.55662</v>
+        <v>5.7087</v>
       </c>
       <c r="J46" t="n">
-        <v>5.7087</v>
+        <v>5.7081</v>
       </c>
       <c r="K46" t="n">
-        <v>5.7081</v>
+        <v>6666287</v>
       </c>
       <c r="L46" t="n">
-        <v>6666287</v>
+        <v>2532708</v>
       </c>
       <c r="M46" t="n">
-        <v>2532708</v>
+        <v>4133579</v>
       </c>
       <c r="N46" t="n">
-        <v>4133579</v>
+        <v>3.72</v>
       </c>
       <c r="O46" t="n">
-        <v>3.72</v>
+        <v>2.67</v>
       </c>
       <c r="P46" t="n">
-        <v>2.67</v>
+        <v>4.36</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.36</v>
+        <v>31.7</v>
       </c>
       <c r="R46" t="n">
-        <v>31.7</v>
+        <v>341459</v>
       </c>
       <c r="S46" t="n">
-        <v>341459</v>
+        <v>-0.725787</v>
       </c>
       <c r="T46" t="n">
-        <v>-0.725787</v>
+        <v>-3.581128</v>
       </c>
       <c r="U46" t="n">
-        <v>-3.581128</v>
+        <v>0.84617</v>
       </c>
       <c r="V46" t="n">
-        <v>0.84617</v>
+        <v>0.84626</v>
       </c>
       <c r="W46" t="n">
-        <v>0.84626</v>
+        <v>0.639181</v>
       </c>
       <c r="X46" t="n">
-        <v>0.639181</v>
+        <v>0.807268</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.807268</v>
+        <v>0.5364679999999999</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.5364679999999999</v>
+        <v>0.196603</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.196603</v>
+        <v>7.026183</v>
       </c>
       <c r="AB46" t="n">
-        <v>5.319636</v>
+        <v>5.201418</v>
       </c>
       <c r="AC46" t="n">
-        <v>7.026183</v>
+        <v>0.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>5.201418</v>
+        <v>0.001405</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.5</v>
+        <v>0.001405</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.001405</v>
+        <v>0.05</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.001405</v>
+        <v>-0.05</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="AI46" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK46" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5610,102 +5352,96 @@
         <v>0.054569</v>
       </c>
       <c r="E47" t="n">
-        <v>0.24</v>
+        <v>-1.67</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.67</v>
+        <v>0.23</v>
       </c>
       <c r="G47" t="n">
-        <v>0.23</v>
+        <v>108.90168</v>
       </c>
       <c r="H47" t="n">
-        <v>108.90168</v>
+        <v>107.36878</v>
       </c>
       <c r="I47" t="n">
-        <v>107.36878</v>
+        <v>5.4571</v>
       </c>
       <c r="J47" t="n">
-        <v>5.4571</v>
+        <v>5.4565</v>
       </c>
       <c r="K47" t="n">
-        <v>5.4565</v>
+        <v>6703663</v>
       </c>
       <c r="L47" t="n">
-        <v>6703663</v>
+        <v>2547693</v>
       </c>
       <c r="M47" t="n">
-        <v>2547693</v>
+        <v>4155970</v>
       </c>
       <c r="N47" t="n">
-        <v>4155970</v>
+        <v>3.75</v>
       </c>
       <c r="O47" t="n">
-        <v>3.75</v>
+        <v>2.67</v>
       </c>
       <c r="P47" t="n">
-        <v>2.67</v>
+        <v>4.41</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.41</v>
+        <v>31.85</v>
       </c>
       <c r="R47" t="n">
-        <v>31.85</v>
+        <v>344440</v>
       </c>
       <c r="S47" t="n">
-        <v>344440</v>
+        <v>0.089546</v>
       </c>
       <c r="T47" t="n">
-        <v>0.089546</v>
+        <v>-1.094212</v>
       </c>
       <c r="U47" t="n">
-        <v>-1.094212</v>
+        <v>-4.407308</v>
       </c>
       <c r="V47" t="n">
-        <v>-4.407308</v>
+        <v>-4.407771</v>
       </c>
       <c r="W47" t="n">
-        <v>-4.407771</v>
+        <v>0.5606719999999999</v>
       </c>
       <c r="X47" t="n">
-        <v>0.5606719999999999</v>
+        <v>0.591659</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.591659</v>
+        <v>0.541686</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.541686</v>
+        <v>0.873018</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.873018</v>
+        <v>4.393261</v>
       </c>
       <c r="AB47" t="n">
-        <v>5.351165</v>
+        <v>5.18043</v>
       </c>
       <c r="AC47" t="n">
-        <v>4.393261</v>
+        <v>0.25</v>
       </c>
       <c r="AD47" t="n">
-        <v>5.18043</v>
+        <v>0.000633</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.25</v>
+        <v>0.000633</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.000633</v>
+        <v>0.03</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.000633</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK47" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5723,102 +5459,96 @@
         <v>0.055131</v>
       </c>
       <c r="E48" t="n">
-        <v>0.26</v>
+        <v>-0.77</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.77</v>
+        <v>0.21</v>
       </c>
       <c r="G48" t="n">
+        <v>108.39998</v>
+      </c>
+      <c r="H48" t="n">
+        <v>113.10359</v>
+      </c>
+      <c r="I48" t="n">
+        <v>5.6021</v>
+      </c>
+      <c r="J48" t="n">
+        <v>5.6015</v>
+      </c>
+      <c r="K48" t="n">
+        <v>6733209</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2544400</v>
+      </c>
+      <c r="M48" t="n">
+        <v>4188808</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="O48" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="P48" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="R48" t="n">
+        <v>345111</v>
+      </c>
+      <c r="S48" t="n">
+        <v>-0.460691</v>
+      </c>
+      <c r="T48" t="n">
+        <v>5.341227</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2.657089</v>
+      </c>
+      <c r="V48" t="n">
+        <v>2.657381</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0.440744</v>
+      </c>
+      <c r="X48" t="n">
+        <v>-0.129254</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0.79014</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0.194809</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>2.961368</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>5.127976</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.000562</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0.000562</v>
+      </c>
+      <c r="AF48" t="n">
         <v>0.21</v>
       </c>
-      <c r="H48" t="n">
-        <v>108.39998</v>
-      </c>
-      <c r="I48" t="n">
-        <v>113.10359</v>
-      </c>
-      <c r="J48" t="n">
-        <v>5.6021</v>
-      </c>
-      <c r="K48" t="n">
-        <v>5.6015</v>
-      </c>
-      <c r="L48" t="n">
-        <v>6733209</v>
-      </c>
-      <c r="M48" t="n">
-        <v>2544400</v>
-      </c>
-      <c r="N48" t="n">
-        <v>4188808</v>
-      </c>
-      <c r="O48" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="R48" t="n">
-        <v>31.75</v>
-      </c>
-      <c r="S48" t="n">
-        <v>345111</v>
-      </c>
-      <c r="T48" t="n">
-        <v>-0.460691</v>
-      </c>
-      <c r="U48" t="n">
-        <v>5.341227</v>
-      </c>
-      <c r="V48" t="n">
-        <v>2.657089</v>
-      </c>
-      <c r="W48" t="n">
-        <v>2.657381</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0.440744</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>-0.129254</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0.79014</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0.194809</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>5.225222</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>2.961368</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>5.127976</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>0.000562</v>
-      </c>
       <c r="AG48" t="n">
-        <v>0.000562</v>
+        <v>0.12</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="AI48" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK48" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -5836,102 +5566,96 @@
         <v>0.055131</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.11</v>
+        <v>0.36</v>
       </c>
       <c r="F49" t="n">
-        <v>0.36</v>
+        <v>-0.21</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.21</v>
+        <v>108.79892</v>
       </c>
       <c r="H49" t="n">
-        <v>108.79892</v>
+        <v>110.38013</v>
       </c>
       <c r="I49" t="n">
-        <v>110.38013</v>
+        <v>5.4264</v>
       </c>
       <c r="J49" t="n">
-        <v>5.4264</v>
+        <v>5.4258</v>
       </c>
       <c r="K49" t="n">
-        <v>5.4258</v>
+        <v>6774436</v>
       </c>
       <c r="L49" t="n">
-        <v>6774436</v>
+        <v>2546265</v>
       </c>
       <c r="M49" t="n">
-        <v>2546265</v>
+        <v>4228171</v>
       </c>
       <c r="N49" t="n">
-        <v>4228171</v>
+        <v>4.14</v>
       </c>
       <c r="O49" t="n">
-        <v>4.14</v>
+        <v>2.85</v>
       </c>
       <c r="P49" t="n">
-        <v>2.85</v>
+        <v>4.92</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.92</v>
+        <v>31.87</v>
       </c>
       <c r="R49" t="n">
-        <v>31.87</v>
+        <v>350767</v>
       </c>
       <c r="S49" t="n">
-        <v>350767</v>
+        <v>0.368026</v>
       </c>
       <c r="T49" t="n">
-        <v>0.368026</v>
+        <v>-2.407934</v>
       </c>
       <c r="U49" t="n">
-        <v>-2.407934</v>
+        <v>-3.136324</v>
       </c>
       <c r="V49" t="n">
-        <v>-3.136324</v>
+        <v>-3.13666</v>
       </c>
       <c r="W49" t="n">
-        <v>-3.13666</v>
+        <v>0.612293</v>
       </c>
       <c r="X49" t="n">
-        <v>0.612293</v>
+        <v>0.073298</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.073298</v>
+        <v>0.9397180000000001</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.9397180000000001</v>
+        <v>1.638893</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.638893</v>
+        <v>3.033233</v>
       </c>
       <c r="AB49" t="n">
-        <v>5.130501</v>
+        <v>5.054283</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.033233</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>5.054283</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK49" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5949,102 +5673,96 @@
         <v>0.055131</v>
       </c>
       <c r="E50" t="n">
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
       <c r="F50" t="n">
-        <v>0.42</v>
+        <v>0.52</v>
       </c>
       <c r="G50" t="n">
-        <v>0.52</v>
+        <v>108.7209</v>
       </c>
       <c r="H50" t="n">
-        <v>108.7209</v>
+        <v>109.48882</v>
       </c>
       <c r="I50" t="n">
-        <v>109.48882</v>
+        <v>5.3186</v>
       </c>
       <c r="J50" t="n">
-        <v>5.3186</v>
+        <v>5.318</v>
       </c>
       <c r="K50" t="n">
-        <v>5.318</v>
+        <v>6852705</v>
       </c>
       <c r="L50" t="n">
-        <v>6852705</v>
+        <v>2589817</v>
       </c>
       <c r="M50" t="n">
-        <v>2589817</v>
+        <v>4262888</v>
       </c>
       <c r="N50" t="n">
-        <v>4262888</v>
+        <v>4.09</v>
       </c>
       <c r="O50" t="n">
-        <v>4.09</v>
+        <v>2.77</v>
       </c>
       <c r="P50" t="n">
-        <v>2.77</v>
+        <v>4.89</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.89</v>
+        <v>31.47</v>
       </c>
       <c r="R50" t="n">
-        <v>31.47</v>
+        <v>356582</v>
       </c>
       <c r="S50" t="n">
-        <v>356582</v>
+        <v>-0.07171</v>
       </c>
       <c r="T50" t="n">
-        <v>-0.07171</v>
+        <v>-0.807491</v>
       </c>
       <c r="U50" t="n">
-        <v>-0.807491</v>
+        <v>-1.986584</v>
       </c>
       <c r="V50" t="n">
-        <v>-1.986584</v>
+        <v>-1.986804</v>
       </c>
       <c r="W50" t="n">
-        <v>-1.986804</v>
+        <v>1.155358</v>
       </c>
       <c r="X50" t="n">
-        <v>1.155358</v>
+        <v>1.710427</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.710427</v>
+        <v>0.821088</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.821088</v>
+        <v>1.657796</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.657796</v>
+        <v>2.828436</v>
       </c>
       <c r="AB50" t="n">
-        <v>5.172369</v>
+        <v>5.096104</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.828436</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>5.096104</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="AH50" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="AI50" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK50" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -6062,102 +5780,96 @@
         <v>0.055131</v>
       </c>
       <c r="E51" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G51" t="n">
+        <v>108.73364</v>
+      </c>
+      <c r="H51" t="n">
+        <v>110.06407</v>
+      </c>
+      <c r="I51" t="n">
+        <v>5.3843</v>
+      </c>
+      <c r="J51" t="n">
+        <v>5.3837</v>
+      </c>
+      <c r="K51" t="n">
+        <v>6923886</v>
+      </c>
+      <c r="L51" t="n">
+        <v>2597630</v>
+      </c>
+      <c r="M51" t="n">
+        <v>4326256</v>
+      </c>
+      <c r="N51" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="O51" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="P51" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>32.04</v>
+      </c>
+      <c r="R51" t="n">
+        <v>357103</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0.011718</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.525396</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.235287</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.235427</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.038729</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0.301682</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.486504</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0.146109</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0.924206</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>4.490243</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
         <v>0.09</v>
       </c>
-      <c r="F51" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H51" t="n">
-        <v>108.73364</v>
-      </c>
-      <c r="I51" t="n">
-        <v>110.06407</v>
-      </c>
-      <c r="J51" t="n">
-        <v>5.3843</v>
-      </c>
-      <c r="K51" t="n">
-        <v>5.3837</v>
-      </c>
-      <c r="L51" t="n">
-        <v>6923886</v>
-      </c>
-      <c r="M51" t="n">
-        <v>2597630</v>
-      </c>
-      <c r="N51" t="n">
-        <v>4326256</v>
-      </c>
-      <c r="O51" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="P51" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="R51" t="n">
-        <v>32.04</v>
-      </c>
-      <c r="S51" t="n">
-        <v>357103</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0.011718</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0.525396</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.235287</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.235427</v>
-      </c>
-      <c r="X51" t="n">
-        <v>1.038729</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0.301682</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.486504</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0.146109</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>4.680811</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0.924206</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>4.490243</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0</v>
-      </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK51" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -6175,102 +5887,96 @@
         <v>0.055131</v>
       </c>
       <c r="E52" t="n">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="F52" t="n">
-        <v>0.27</v>
+        <v>0.03</v>
       </c>
       <c r="G52" t="n">
-        <v>0.03</v>
+        <v>109.24151</v>
       </c>
       <c r="H52" t="n">
-        <v>109.24151</v>
+        <v>106.59541</v>
       </c>
       <c r="I52" t="n">
-        <v>106.59541</v>
+        <v>5.3338</v>
       </c>
       <c r="J52" t="n">
-        <v>5.3338</v>
+        <v>5.3332</v>
       </c>
       <c r="K52" t="n">
-        <v>5.3332</v>
+        <v>7004223</v>
       </c>
       <c r="L52" t="n">
-        <v>7004223</v>
+        <v>2616902</v>
       </c>
       <c r="M52" t="n">
-        <v>2616902</v>
+        <v>4387321</v>
       </c>
       <c r="N52" t="n">
-        <v>4387321</v>
+        <v>4.24</v>
       </c>
       <c r="O52" t="n">
-        <v>4.24</v>
+        <v>2.75</v>
       </c>
       <c r="P52" t="n">
-        <v>2.75</v>
+        <v>5.12</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.12</v>
+        <v>32.2</v>
       </c>
       <c r="R52" t="n">
-        <v>32.2</v>
+        <v>360578</v>
       </c>
       <c r="S52" t="n">
-        <v>360578</v>
+        <v>0.467077</v>
       </c>
       <c r="T52" t="n">
-        <v>0.467077</v>
+        <v>-3.151492</v>
       </c>
       <c r="U52" t="n">
-        <v>-3.151492</v>
+        <v>-0.937912</v>
       </c>
       <c r="V52" t="n">
-        <v>-0.937912</v>
+        <v>-0.938017</v>
       </c>
       <c r="W52" t="n">
-        <v>-0.938017</v>
+        <v>1.160288</v>
       </c>
       <c r="X52" t="n">
-        <v>1.160288</v>
+        <v>0.741907</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.741907</v>
+        <v>1.411498</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.411498</v>
+        <v>0.973109</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.973109</v>
+        <v>-0.101973</v>
       </c>
       <c r="AB52" t="n">
-        <v>4.461836</v>
+        <v>4.177803</v>
       </c>
       <c r="AC52" t="n">
-        <v>-0.101973</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>4.177803</v>
+        <v>-0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF52" t="n">
-        <v>-0</v>
+        <v>0.06</v>
       </c>
       <c r="AG52" t="n">
-        <v>-0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AH52" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="AI52" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AK52" t="n">
         <v>0.16</v>
       </c>
     </row>
@@ -6288,102 +5994,96 @@
         <v>0.055131</v>
       </c>
       <c r="E53" t="n">
-        <v>0.33</v>
+        <v>-0.01</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.01</v>
+        <v>0.21</v>
       </c>
       <c r="G53" t="n">
-        <v>0.21</v>
+        <v>109.46142</v>
       </c>
       <c r="H53" t="n">
-        <v>109.46142</v>
+        <v>107.19319</v>
       </c>
       <c r="I53" t="n">
-        <v>107.19319</v>
+        <v>5.5024</v>
       </c>
       <c r="J53" t="n">
-        <v>5.5024</v>
+        <v>5.5018</v>
       </c>
       <c r="K53" t="n">
-        <v>5.5018</v>
+        <v>7137252</v>
       </c>
       <c r="L53" t="n">
-        <v>7137252</v>
+        <v>2701735</v>
       </c>
       <c r="M53" t="n">
-        <v>2701735</v>
+        <v>4435517</v>
       </c>
       <c r="N53" t="n">
-        <v>4435517</v>
+        <v>4.2</v>
       </c>
       <c r="O53" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="P53" t="n">
-        <v>2.7</v>
+        <v>5.12</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.12</v>
+        <v>31.87</v>
       </c>
       <c r="R53" t="n">
-        <v>31.87</v>
+        <v>358234</v>
       </c>
       <c r="S53" t="n">
-        <v>358234</v>
+        <v>0.201306</v>
       </c>
       <c r="T53" t="n">
-        <v>0.201306</v>
+        <v>0.560793</v>
       </c>
       <c r="U53" t="n">
-        <v>0.560793</v>
+        <v>3.160973</v>
       </c>
       <c r="V53" t="n">
-        <v>3.160973</v>
+        <v>3.161329</v>
       </c>
       <c r="W53" t="n">
-        <v>3.161329</v>
+        <v>1.899268</v>
       </c>
       <c r="X53" t="n">
-        <v>1.899268</v>
+        <v>3.241734</v>
       </c>
       <c r="Y53" t="n">
-        <v>3.241734</v>
+        <v>1.098529</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.098529</v>
+        <v>-0.650067</v>
       </c>
       <c r="AA53" t="n">
-        <v>-0.650067</v>
+        <v>-1.042167</v>
       </c>
       <c r="AB53" t="n">
-        <v>4.264385</v>
+        <v>3.897866</v>
       </c>
       <c r="AC53" t="n">
-        <v>-1.042167</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>3.897866</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AH53" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -6401,102 +6101,96 @@
         <v>0.055131</v>
       </c>
       <c r="E54" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="F54" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="G54" t="n">
-        <v>0.39</v>
+        <v>110.07661</v>
       </c>
       <c r="H54" t="n">
-        <v>110.07661</v>
+        <v>103.78191</v>
       </c>
       <c r="I54" t="n">
-        <v>103.78191</v>
+        <v>5.2301</v>
       </c>
       <c r="J54" t="n">
-        <v>5.2301</v>
+        <v>5.2295</v>
       </c>
       <c r="K54" t="n">
-        <v>5.2295</v>
+        <v>7130762</v>
       </c>
       <c r="L54" t="n">
-        <v>7130762</v>
+        <v>2654220</v>
       </c>
       <c r="M54" t="n">
-        <v>2654220</v>
+        <v>4476542</v>
       </c>
       <c r="N54" t="n">
-        <v>4476542</v>
+        <v>4.44</v>
       </c>
       <c r="O54" t="n">
-        <v>4.44</v>
+        <v>2.87</v>
       </c>
       <c r="P54" t="n">
-        <v>2.87</v>
+        <v>5.38</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.38</v>
+        <v>32.45</v>
       </c>
       <c r="R54" t="n">
-        <v>32.45</v>
+        <v>364367</v>
       </c>
       <c r="S54" t="n">
-        <v>364367</v>
+        <v>0.562015</v>
       </c>
       <c r="T54" t="n">
-        <v>0.562015</v>
+        <v>-3.182366</v>
       </c>
       <c r="U54" t="n">
-        <v>-3.182366</v>
+        <v>-4.94875</v>
       </c>
       <c r="V54" t="n">
-        <v>-4.94875</v>
+        <v>-4.949289</v>
       </c>
       <c r="W54" t="n">
-        <v>-4.949289</v>
+        <v>-0.090931</v>
       </c>
       <c r="X54" t="n">
-        <v>-0.090931</v>
+        <v>-1.758685</v>
       </c>
       <c r="Y54" t="n">
-        <v>-1.758685</v>
+        <v>0.92492</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.92492</v>
+        <v>1.712009</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.712009</v>
+        <v>-0.903999</v>
       </c>
       <c r="AB54" t="n">
-        <v>4.441351</v>
+        <v>4.303068</v>
       </c>
       <c r="AC54" t="n">
-        <v>-0.903999</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>4.303068</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
         <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AH54" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="AI54" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK54" t="n">
         <v>0.58</v>
       </c>
     </row>
@@ -6514,102 +6208,96 @@
         <v>0.055131</v>
       </c>
       <c r="E55" t="n">
-        <v>0.7</v>
+        <v>-0.73</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>0.5600000000000001</v>
+        <v>110.77581</v>
       </c>
       <c r="H55" t="n">
-        <v>110.77581</v>
+        <v>106.77083</v>
       </c>
       <c r="I55" t="n">
-        <v>106.77083</v>
+        <v>5.1495</v>
       </c>
       <c r="J55" t="n">
-        <v>5.1495</v>
+        <v>5.1489</v>
       </c>
       <c r="K55" t="n">
-        <v>5.1489</v>
+        <v>7157783</v>
       </c>
       <c r="L55" t="n">
-        <v>7157783</v>
+        <v>2656484</v>
       </c>
       <c r="M55" t="n">
-        <v>2656484</v>
+        <v>4501299</v>
       </c>
       <c r="N55" t="n">
-        <v>4501299</v>
+        <v>4.64</v>
       </c>
       <c r="O55" t="n">
-        <v>4.64</v>
+        <v>3.07</v>
       </c>
       <c r="P55" t="n">
-        <v>3.07</v>
+        <v>5.56</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.56</v>
+        <v>32.63</v>
       </c>
       <c r="R55" t="n">
-        <v>32.63</v>
+        <v>371074</v>
       </c>
       <c r="S55" t="n">
-        <v>371074</v>
+        <v>0.635194</v>
       </c>
       <c r="T55" t="n">
-        <v>0.635194</v>
+        <v>2.880001</v>
       </c>
       <c r="U55" t="n">
-        <v>2.880001</v>
+        <v>-1.54108</v>
       </c>
       <c r="V55" t="n">
-        <v>-1.54108</v>
+        <v>-1.541256</v>
       </c>
       <c r="W55" t="n">
-        <v>-1.541256</v>
+        <v>0.378936</v>
       </c>
       <c r="X55" t="n">
-        <v>0.378936</v>
+        <v>0.085298</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.085298</v>
+        <v>0.553038</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.553038</v>
+        <v>1.840727</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.840727</v>
+        <v>-2.659212</v>
       </c>
       <c r="AB55" t="n">
-        <v>3.812497</v>
+        <v>3.357475</v>
       </c>
       <c r="AC55" t="n">
-        <v>-2.659212</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.357475</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
         <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AH55" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AI55" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AK55" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -6627,102 +6315,96 @@
         <v>0.054777</v>
       </c>
       <c r="E56" t="n">
-        <v>0.88</v>
+        <v>0.52</v>
       </c>
       <c r="F56" t="n">
-        <v>0.52</v>
+        <v>0.91</v>
       </c>
       <c r="G56" t="n">
-        <v>0.91</v>
+        <v>110.60765</v>
       </c>
       <c r="H56" t="n">
-        <v>110.60765</v>
+        <v>118.00063</v>
       </c>
       <c r="I56" t="n">
-        <v>118.00063</v>
+        <v>5.2194</v>
       </c>
       <c r="J56" t="n">
-        <v>5.2194</v>
+        <v>5.2188</v>
       </c>
       <c r="K56" t="n">
-        <v>5.2188</v>
+        <v>7240557</v>
       </c>
       <c r="L56" t="n">
-        <v>7240557</v>
+        <v>2687535</v>
       </c>
       <c r="M56" t="n">
-        <v>2687535</v>
+        <v>4553022</v>
       </c>
       <c r="N56" t="n">
-        <v>4553022</v>
+        <v>4.52</v>
       </c>
       <c r="O56" t="n">
-        <v>4.52</v>
+        <v>3.06</v>
       </c>
       <c r="P56" t="n">
-        <v>3.06</v>
+        <v>5.39</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.39</v>
+        <v>32.84</v>
       </c>
       <c r="R56" t="n">
-        <v>32.84</v>
+        <v>362002</v>
       </c>
       <c r="S56" t="n">
-        <v>362002</v>
+        <v>-0.151802</v>
       </c>
       <c r="T56" t="n">
-        <v>-0.151802</v>
+        <v>10.517667</v>
       </c>
       <c r="U56" t="n">
-        <v>10.517667</v>
+        <v>1.357413</v>
       </c>
       <c r="V56" t="n">
-        <v>1.357413</v>
+        <v>1.357572</v>
       </c>
       <c r="W56" t="n">
-        <v>1.357572</v>
+        <v>1.15642</v>
       </c>
       <c r="X56" t="n">
-        <v>1.15642</v>
+        <v>1.168876</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.168876</v>
+        <v>1.149068</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.149068</v>
+        <v>-2.444795</v>
       </c>
       <c r="AA56" t="n">
-        <v>-2.444795</v>
+        <v>-1.819225</v>
       </c>
       <c r="AB56" t="n">
-        <v>4.142847</v>
+        <v>3.768807</v>
       </c>
       <c r="AC56" t="n">
-        <v>-1.819225</v>
+        <v>-0.25</v>
       </c>
       <c r="AD56" t="n">
-        <v>3.768807</v>
+        <v>-0.000354</v>
       </c>
       <c r="AE56" t="n">
-        <v>-0.25</v>
+        <v>-0.000354</v>
       </c>
       <c r="AF56" t="n">
-        <v>-0.000354</v>
+        <v>-0.12</v>
       </c>
       <c r="AG56" t="n">
-        <v>-0.000354</v>
+        <v>-0.01</v>
       </c>
       <c r="AH56" t="n">
-        <v>-0.12</v>
+        <v>-0.17</v>
       </c>
       <c r="AI56" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="AK56" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -6740,102 +6422,96 @@
         <v>0.054223</v>
       </c>
       <c r="E57" t="n">
-        <v>0.67</v>
+        <v>2.73</v>
       </c>
       <c r="F57" t="n">
-        <v>2.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>0.8100000000000001</v>
+        <v>110.90086</v>
       </c>
       <c r="H57" t="n">
-        <v>110.90086</v>
+        <v>113.89942</v>
       </c>
       <c r="I57" t="n">
-        <v>113.89942</v>
+        <v>4.9886</v>
       </c>
       <c r="J57" t="n">
-        <v>4.9886</v>
+        <v>4.988</v>
       </c>
       <c r="K57" t="n">
-        <v>4.988</v>
+        <v>7259766</v>
       </c>
       <c r="L57" t="n">
-        <v>7259766</v>
+        <v>2685397</v>
       </c>
       <c r="M57" t="n">
-        <v>2685397</v>
+        <v>4574368</v>
       </c>
       <c r="N57" t="n">
-        <v>4574368</v>
+        <v>4.64</v>
       </c>
       <c r="O57" t="n">
-        <v>4.64</v>
+        <v>3.15</v>
       </c>
       <c r="P57" t="n">
-        <v>3.15</v>
+        <v>5.51</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.51</v>
+        <v>33.36</v>
       </c>
       <c r="R57" t="n">
-        <v>33.36</v>
+        <v>366913</v>
       </c>
       <c r="S57" t="n">
-        <v>366913</v>
+        <v>0.26509</v>
       </c>
       <c r="T57" t="n">
-        <v>0.26509</v>
+        <v>-3.475583</v>
       </c>
       <c r="U57" t="n">
-        <v>-3.475583</v>
+        <v>-4.421964</v>
       </c>
       <c r="V57" t="n">
-        <v>-4.421964</v>
+        <v>-4.422473</v>
       </c>
       <c r="W57" t="n">
-        <v>-4.422473</v>
+        <v>0.265297</v>
       </c>
       <c r="X57" t="n">
-        <v>0.265297</v>
+        <v>-0.079552</v>
       </c>
       <c r="Y57" t="n">
-        <v>-0.079552</v>
+        <v>0.468831</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.468831</v>
+        <v>1.356622</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.356622</v>
+        <v>0.619623</v>
       </c>
       <c r="AB57" t="n">
-        <v>4.39172</v>
+        <v>4.109608</v>
       </c>
       <c r="AC57" t="n">
-        <v>0.619623</v>
+        <v>-0.25</v>
       </c>
       <c r="AD57" t="n">
-        <v>4.109608</v>
+        <v>-0.000554</v>
       </c>
       <c r="AE57" t="n">
-        <v>-0.25</v>
+        <v>-0.000554</v>
       </c>
       <c r="AF57" t="n">
-        <v>-0.000554</v>
+        <v>0.12</v>
       </c>
       <c r="AG57" t="n">
-        <v>-0.000554</v>
+        <v>0.09</v>
       </c>
       <c r="AH57" t="n">
         <v>0.12</v>
       </c>
       <c r="AI57" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AK57" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -6853,102 +6529,96 @@
         <v>0.0534</v>
       </c>
       <c r="E58" t="n">
-        <v>0.58</v>
+        <v>0.84</v>
       </c>
       <c r="F58" t="n">
-        <v>0.84</v>
+        <v>0.65</v>
       </c>
       <c r="G58" t="n">
-        <v>0.65</v>
+        <v>110.93102</v>
       </c>
       <c r="H58" t="n">
-        <v>110.93102</v>
+        <v>109.53002</v>
       </c>
       <c r="I58" t="n">
-        <v>109.53002</v>
+        <v>5.0569</v>
       </c>
       <c r="J58" t="n">
-        <v>5.0569</v>
+        <v>5.0563</v>
       </c>
       <c r="K58" t="n">
-        <v>5.0563</v>
+        <v>7305306</v>
       </c>
       <c r="L58" t="n">
-        <v>7305306</v>
+        <v>2708154</v>
       </c>
       <c r="M58" t="n">
-        <v>2708154</v>
+        <v>4597152</v>
       </c>
       <c r="N58" t="n">
-        <v>4597152</v>
+        <v>4.74</v>
       </c>
       <c r="O58" t="n">
-        <v>4.74</v>
+        <v>3.25</v>
       </c>
       <c r="P58" t="n">
-        <v>3.25</v>
+        <v>5.62</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.62</v>
+        <v>33.1</v>
       </c>
       <c r="R58" t="n">
-        <v>33.1</v>
+        <v>371137</v>
       </c>
       <c r="S58" t="n">
-        <v>371137</v>
+        <v>0.027195</v>
       </c>
       <c r="T58" t="n">
-        <v>0.027195</v>
+        <v>-3.836192</v>
       </c>
       <c r="U58" t="n">
-        <v>-3.836192</v>
+        <v>1.369122</v>
       </c>
       <c r="V58" t="n">
-        <v>1.369122</v>
+        <v>1.369286</v>
       </c>
       <c r="W58" t="n">
-        <v>1.369286</v>
+        <v>0.627293</v>
       </c>
       <c r="X58" t="n">
-        <v>0.627293</v>
+        <v>0.847435</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.847435</v>
+        <v>0.49808</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.49808</v>
+        <v>1.151227</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.151227</v>
+        <v>1.964454</v>
       </c>
       <c r="AB58" t="n">
-        <v>4.724907</v>
+        <v>4.420848</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.964454</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>4.420848</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="AF58" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="AG58" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="AH58" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="AI58" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK58" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -6966,102 +6636,96 @@
         <v>0.053028</v>
       </c>
       <c r="E59" t="n">
-        <v>0.16</v>
+        <v>-0.5</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.5</v>
+        <v>0.14</v>
       </c>
       <c r="G59" t="n">
-        <v>0.14</v>
+        <v>110.22154</v>
       </c>
       <c r="H59" t="n">
-        <v>110.22154</v>
+        <v>109.89427</v>
       </c>
       <c r="I59" t="n">
-        <v>109.89427</v>
+        <v>5.1766</v>
       </c>
       <c r="J59" t="n">
-        <v>5.1766</v>
+        <v>5.176</v>
       </c>
       <c r="K59" t="n">
-        <v>5.176</v>
+        <v>7353293</v>
       </c>
       <c r="L59" t="n">
-        <v>7353293</v>
+        <v>2750625</v>
       </c>
       <c r="M59" t="n">
-        <v>2750625</v>
+        <v>4602668</v>
       </c>
       <c r="N59" t="n">
-        <v>4602668</v>
+        <v>4.58</v>
       </c>
       <c r="O59" t="n">
-        <v>4.58</v>
+        <v>3.18</v>
       </c>
       <c r="P59" t="n">
-        <v>3.18</v>
+        <v>5.42</v>
       </c>
       <c r="Q59" t="n">
-        <v>5.42</v>
+        <v>33.33</v>
       </c>
       <c r="R59" t="n">
-        <v>33.33</v>
+        <v>367558</v>
       </c>
       <c r="S59" t="n">
-        <v>367558</v>
+        <v>-0.6395690000000001</v>
       </c>
       <c r="T59" t="n">
-        <v>-0.6395690000000001</v>
+        <v>0.332557</v>
       </c>
       <c r="U59" t="n">
-        <v>0.332557</v>
+        <v>2.367063</v>
       </c>
       <c r="V59" t="n">
-        <v>2.367063</v>
+        <v>2.367344</v>
       </c>
       <c r="W59" t="n">
-        <v>2.367344</v>
+        <v>0.656879</v>
       </c>
       <c r="X59" t="n">
-        <v>0.656879</v>
+        <v>1.568264</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.568264</v>
+        <v>0.119987</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.119987</v>
+        <v>-0.964334</v>
       </c>
       <c r="AA59" t="n">
-        <v>-0.964334</v>
+        <v>3.177699</v>
       </c>
       <c r="AB59" t="n">
-        <v>4.641328</v>
+        <v>4.327084</v>
       </c>
       <c r="AC59" t="n">
-        <v>3.177699</v>
+        <v>-0.25</v>
       </c>
       <c r="AD59" t="n">
-        <v>4.327084</v>
+        <v>-0.000372</v>
       </c>
       <c r="AE59" t="n">
-        <v>-0.25</v>
+        <v>-0.000372</v>
       </c>
       <c r="AF59" t="n">
-        <v>-0.000372</v>
+        <v>-0.16</v>
       </c>
       <c r="AG59" t="n">
-        <v>-0.000372</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AH59" t="n">
-        <v>-0.16</v>
+        <v>-0.2</v>
       </c>
       <c r="AI59" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AK59" t="n">
         <v>0.23</v>
       </c>
     </row>
@@ -7079,94 +6743,88 @@
         <v>0.052531</v>
       </c>
       <c r="E60" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.16</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="G60" t="n">
         <v>-0.01</v>
       </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="n">
+        <v>5.0773</v>
+      </c>
       <c r="J60" t="n">
-        <v>5.0773</v>
+        <v>5.0767</v>
       </c>
       <c r="K60" t="n">
-        <v>5.0767</v>
+        <v>7372243</v>
       </c>
       <c r="L60" t="n">
-        <v>7372243</v>
+        <v>2731513</v>
       </c>
       <c r="M60" t="n">
-        <v>2731513</v>
+        <v>4640730</v>
       </c>
       <c r="N60" t="n">
-        <v>4640730</v>
+        <v>4.88</v>
       </c>
       <c r="O60" t="n">
-        <v>4.88</v>
+        <v>3.31</v>
       </c>
       <c r="P60" t="n">
-        <v>3.31</v>
+        <v>5.81</v>
       </c>
       <c r="Q60" t="n">
-        <v>5.81</v>
+        <v>32.08</v>
       </c>
       <c r="R60" t="n">
-        <v>32.08</v>
-      </c>
-      <c r="S60" t="n">
         <v>369742</v>
       </c>
+      <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
+      <c r="U60" t="n">
+        <v>-1.918247</v>
+      </c>
       <c r="V60" t="n">
-        <v>-1.918247</v>
+        <v>-1.91847</v>
       </c>
       <c r="W60" t="n">
-        <v>-1.91847</v>
+        <v>0.257708</v>
       </c>
       <c r="X60" t="n">
-        <v>0.257708</v>
+        <v>-0.694824</v>
       </c>
       <c r="Y60" t="n">
-        <v>-0.694824</v>
+        <v>0.826955</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.826955</v>
+        <v>0.5941920000000001</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.5941920000000001</v>
+        <v>2.772183</v>
       </c>
       <c r="AB60" t="n">
-        <v>4.443025</v>
+        <v>4.098046</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.772183</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>4.098046</v>
+        <v>-0.000497</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>-0.000497</v>
       </c>
       <c r="AF60" t="n">
-        <v>-0.000497</v>
+        <v>0.3</v>
       </c>
       <c r="AG60" t="n">
-        <v>-0.000497</v>
+        <v>0.13</v>
       </c>
       <c r="AH60" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="AI60" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="AK60" t="n">
         <v>-1.25</v>
       </c>
     </row>
@@ -7184,68 +6842,62 @@
         <v>0.051784</v>
       </c>
       <c r="E61" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="F61" t="n">
         <v>-0.32</v>
       </c>
-      <c r="F61" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="G61" t="n">
-        <v>-0.32</v>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="n">
+        <v>5.1816</v>
+      </c>
       <c r="J61" t="n">
-        <v>5.1816</v>
-      </c>
-      <c r="K61" t="n">
         <v>5.181</v>
       </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="n">
+      <c r="R61" t="n">
         <v>372616</v>
       </c>
+      <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
+      <c r="U61" t="n">
+        <v>2.054241</v>
+      </c>
       <c r="V61" t="n">
-        <v>2.054241</v>
-      </c>
-      <c r="W61" t="n">
         <v>2.054484</v>
       </c>
+      <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
+      <c r="Z61" t="n">
+        <v>0.777299</v>
+      </c>
       <c r="AA61" t="n">
-        <v>0.777299</v>
+        <v>2.178243</v>
       </c>
       <c r="AB61" t="n">
-        <v>4.223453</v>
+        <v>3.983297</v>
       </c>
       <c r="AC61" t="n">
-        <v>2.178243</v>
+        <v>-0.25</v>
       </c>
       <c r="AD61" t="n">
-        <v>3.983297</v>
+        <v>-0.0007470000000000001</v>
       </c>
       <c r="AE61" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AF61" t="n">
         <v>-0.0007470000000000001</v>
       </c>
-      <c r="AG61" t="n">
-        <v>-0.0007470000000000001</v>
-      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="inlineStr"/>
-      <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -7264,13 +6916,13 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="n">
+        <v>5.0918</v>
+      </c>
       <c r="J62" t="n">
-        <v>5.0918</v>
-      </c>
-      <c r="K62" t="n">
         <v>5.0912</v>
       </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -7280,33 +6932,31 @@
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
+      <c r="U62" t="n">
+        <v>-1.733055</v>
+      </c>
       <c r="V62" t="n">
-        <v>-1.733055</v>
-      </c>
-      <c r="W62" t="n">
         <v>-1.733256</v>
       </c>
+      <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr"/>
-      <c r="AC62" t="inlineStr"/>
-      <c r="AD62" t="inlineStr"/>
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>-0.000124</v>
+      </c>
       <c r="AE62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="n">
         <v>-0.000124</v>
       </c>
-      <c r="AG62" t="n">
-        <v>-0.000124</v>
-      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
-      <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI62"/>
+  <dimension ref="A1:AK62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,155 +443,165 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>ipca</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>igp_m</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>inpc</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ibc_br_sa</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ibc_br</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>cambio_venda_usd</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>cambio_compra_usd</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>saldo_credito_total</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>saldo_credito_pj</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>saldo_credito_pf</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inadimplencia_total</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inadimplencia_pj</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inadimplencia_pf</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ipca_acum_12m</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
         <is>
           <t>igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>inpc_acum_12m</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>dif_selic_over</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>dif_cdi</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -605,54 +615,56 @@
         <v>6.25</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02154</v>
+        <v>0.021664</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02154</v>
+        <v>0.021664</v>
       </c>
       <c r="E2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F2" t="n">
         <v>-0.64</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>1.2</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>96.95313</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>97.10569</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>5.4394</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>5.4388</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>4441056</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>1894119</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>2546936</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>2.34</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1.43</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>3.01</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>21.42</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>368886</v>
       </c>
-      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -669,6 +681,8 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -684,92 +698,96 @@
         <v>0.024244</v>
       </c>
       <c r="E3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.64</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>1.16</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>97.47790999999999</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>96.52863000000001</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>5.643</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>5.6424</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>4511956</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>1910940</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>2601017</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>2.33</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>1.43</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>2.99</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>22.89</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>367927</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>0.541272</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>-0.59426</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>3.74306</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>3.743473</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>1.596467</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>0.888065</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>2.123375</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>-0.259972</v>
       </c>
-      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="n">
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD3" t="n">
-        <v>0.002704</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0.002704</v>
-      </c>
       <c r="AF3" t="n">
+        <v>0.00258</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.00258</v>
+      </c>
+      <c r="AH3" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AK3" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -787,92 +805,96 @@
         <v>0.029256</v>
       </c>
       <c r="E4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F4" t="n">
         <v>0.02</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.84</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>99.05295</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>97.85433</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>5.6199</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>5.6193</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>4597507</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>1933111</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2664395</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>2.36</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>1.46</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>3.01</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>23.91</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>367772</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>1.615792</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>1.373375</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>-0.409357</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>-0.4094</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>1.896096</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>1.160214</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>2.436662</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>-0.042128</v>
       </c>
-      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
         <v>0.005012</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AG4" t="n">
         <v>0.005012</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AH4" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AI4" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AJ4" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AK4" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -890,92 +912,96 @@
         <v>0.033316</v>
       </c>
       <c r="E5" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F5" t="n">
         <v>0.87</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.73</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>99.36759000000001</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>99.32245</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>5.5805</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>5.5799</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>4682852</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>1974391</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>2708461</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>2.35</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>1.4</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>3.05</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>24.21</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>362204</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>0.317648</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>1.500312</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>-0.70108</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>-0.701155</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>1.856332</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>2.135418</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>1.653884</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>-1.513981</v>
       </c>
-      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="n">
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AF5" t="n">
         <v>0.00406</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AG5" t="n">
         <v>0.00406</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AH5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AI5" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AJ5" t="n">
         <v>0.04</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AK5" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -993,92 +1019,96 @@
         <v>0.034749</v>
       </c>
       <c r="E6" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F6" t="n">
         <v>1.82</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.67</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>97.41759</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>91.67452</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>5.3574</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>5.3568</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>4682131</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>1947035</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>2735096</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>2.51</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>1.46</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>3.26</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>25.23</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>358398</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>-1.96241</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>-7.700102</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>-3.99785</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>-3.99828</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>-0.015397</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>-1.385541</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>-1.050789</v>
       </c>
-      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
         <v>0.001433</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AG6" t="n">
         <v>0.001433</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AH6" t="n">
         <v>0.16</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AI6" t="n">
         <v>0.06</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AJ6" t="n">
         <v>0.21</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AK6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1096,92 +1126,96 @@
         <v>0.039598</v>
       </c>
       <c r="E7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F7" t="n">
         <v>1.83</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>98.48287000000001</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>95.64045</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>5.1394</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>5.1388</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>4727818</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>1971524</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>2756295</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>2.57</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>1.44</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>3.38</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>25.63</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>357740</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>1.093519</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>4.326098</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>-4.069138</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>-4.069594</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>0.975774</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>1.257759</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>0.775073</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>-0.183595</v>
       </c>
-      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="n">
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AF7" t="n">
         <v>0.004849</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AG7" t="n">
         <v>0.004849</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AH7" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AI7" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AJ7" t="n">
         <v>0.12</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AK7" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1199,92 +1233,96 @@
         <v>0.041954</v>
       </c>
       <c r="E8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F8" t="n">
         <v>1.74</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>1.71</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>99.54331000000001</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>104.53224</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>4.7378</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>4.7372</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>4794583</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>1994119</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>2800464</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>2.66</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>1.55</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>3.45</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>26.54</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>353169</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>1.076776</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>9.297102000000001</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>-7.814142</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>-7.815054</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>1.412174</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>1.146068</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>1.602477</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>-1.277744</v>
       </c>
-      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="n">
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="n">
         <v>1</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AF8" t="n">
         <v>0.002356</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AG8" t="n">
         <v>0.002356</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AH8" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AI8" t="n">
         <v>0.11</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AJ8" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AK8" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1302,92 +1340,96 @@
         <v>0.043739</v>
       </c>
       <c r="E9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="F9" t="n">
         <v>1.41</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>1.04</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>99.44726</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>100.22451</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>4.9191</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>4.9185</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>4833732</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>2003312</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>2830420</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>2.72</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>1.57</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>3.54</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>27.46</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>345097</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>-0.09649099999999999</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>-4.120958</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>3.826671</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>3.827155</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>0.816526</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>0.461006</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>1.06968</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>-2.285591</v>
       </c>
-      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
         <v>0.001785</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AG9" t="n">
         <v>0.001785</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AH9" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AI9" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AJ9" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AK9" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1405,92 +1447,96 @@
         <v>0.046796</v>
       </c>
       <c r="E10" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F10" t="n">
         <v>0.52</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>0.45</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>99.65249</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>99.74639000000001</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>4.7289</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>4.7283</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4889397</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>2013726</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>2875671</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>2.79</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>1.57</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>27.42</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>346415</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>0.206371</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>-0.477049</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>-3.866561</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>-3.867033</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>1.151595</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
         <v>0.5198390000000001</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>1.598738</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
         <v>0.381922</v>
       </c>
-      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="n">
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="n">
         <v>1</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AF10" t="n">
         <v>0.003057</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AG10" t="n">
         <v>0.003057</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AH10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AK10" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1508,92 +1554,96 @@
         <v>0.048116</v>
       </c>
       <c r="E11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F11" t="n">
         <v>0.59</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>0.62</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>99.53077999999999</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>99.32053000000001</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>5.238</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>5.2374</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>4965603</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>2052569</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>2913035</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>2.73</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>1.52</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>3.57</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>27.88</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>341958</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>-0.122134</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>-0.426943</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>10.765717</v>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>10.767083</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>1.558597</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
         <v>1.928912</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>1.299314</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
         <v>-1.286607</v>
       </c>
-      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="n">
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AF11" t="n">
         <v>0.00132</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AG11" t="n">
         <v>0.00132</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AH11" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AI11" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AJ11" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AK11" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1611,92 +1661,96 @@
         <v>0.049037</v>
       </c>
       <c r="E12" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="F12" t="n">
         <v>0.21</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>101.43252</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>103.95413</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>5.1884</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>5.1878</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>4999244</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>2047038</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>2952207</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>2.84</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>1.6</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>29.24</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>346403</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>1.910705</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>4.665299</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>-0.946926</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>-0.947035</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>0.677481</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Y12" t="n">
         <v>-0.269467</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>1.344714</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="n">
         <v>1.299867</v>
       </c>
-      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AG12" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AH12" t="n">
         <v>0.11</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AI12" t="n">
         <v>0.08</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AJ12" t="n">
         <v>0.14</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AK12" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -1714,96 +1768,102 @@
         <v>0.05056</v>
       </c>
       <c r="E13" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="F13" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>-0.31</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>101.09886</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>104.51426</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>5.179</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>5.1784</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>5072711</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>2064183</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>3008528</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>2.9</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>1.62</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>3.78</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>28.6</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>339664</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>-0.328948</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>0.538824</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>-0.181173</v>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>-0.181194</v>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>1.469562</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Y13" t="n">
         <v>0.837552</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>1.907759</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AA13" t="n">
         <v>-1.945422</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AB13" t="n">
+        <v>8.727061000000001</v>
+      </c>
+      <c r="AC13" t="n">
         <v>8.58755</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AD13" t="n">
         <v>8.825751</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AE13" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AF13" t="n">
         <v>0.001523</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AG13" t="n">
         <v>0.001523</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AH13" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AI13" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AJ13" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AK13" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -1821,96 +1881,102 @@
         <v>0.050788</v>
       </c>
       <c r="E14" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="F14" t="n">
         <v>-0.95</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>-0.32</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>101.15209</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>101.19157</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>5.4066</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>5.406</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>5164775</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>2109806</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3054969</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>2.92</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>1.65</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>3.8</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>28.57</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>327580</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>0.052651</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>-3.179174</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>4.394671</v>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>4.39518</v>
       </c>
-      <c r="W14" t="n">
+      <c r="X14" t="n">
         <v>1.814888</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Y14" t="n">
         <v>2.210221</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Z14" t="n">
         <v>1.543645</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AA14" t="n">
         <v>-3.557633</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AB14" t="n">
+        <v>7.168596</v>
+      </c>
+      <c r="AC14" t="n">
         <v>8.248760000000001</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AD14" t="n">
         <v>7.191214</v>
       </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
         <v>0.000228</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AG14" t="n">
         <v>0.000228</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0.03</v>
       </c>
       <c r="AH14" t="n">
         <v>0.02</v>
       </c>
       <c r="AI14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AK14" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -1928,96 +1994,102 @@
         <v>0.050788</v>
       </c>
       <c r="E15" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F15" t="n">
         <v>-0.97</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>0.47</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>101.43094</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>100.07474</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>5.257</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>5.2564</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>5215990</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>2105856</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>3110134</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>3.04</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>1.77</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>3.89</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>29.68</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>325546</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>0.275674</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>-1.103679</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>-2.766988</v>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>-2.767296</v>
       </c>
-      <c r="W15" t="n">
+      <c r="X15" t="n">
         <v>0.991621</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Y15" t="n">
         <v>-0.187221</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Z15" t="n">
         <v>1.805747</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AA15" t="n">
         <v>-0.6209170000000001</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AB15" t="n">
+        <v>6.470016</v>
+      </c>
+      <c r="AC15" t="n">
         <v>6.517038</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AD15" t="n">
         <v>6.460076</v>
       </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
       <c r="AE15" t="n">
         <v>0</v>
       </c>
       <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
         <v>0.12</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AI15" t="n">
         <v>0.12</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AJ15" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AK15" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -2035,96 +2107,102 @@
         <v>0.050788</v>
       </c>
       <c r="E16" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F16" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>0.38</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>100.7113</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>99.15328</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>5.2941</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>5.2935</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>5285657</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>2130312</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>3155345</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>3.07</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>1.81</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>3.92</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>30.52</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>331505</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>-0.709488</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>-0.920772</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>0.705726</v>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
         <v>0.705806</v>
       </c>
-      <c r="W16" t="n">
+      <c r="X16" t="n">
         <v>1.335643</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Y16" t="n">
         <v>1.161333</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Z16" t="n">
         <v>1.453667</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AA16" t="n">
         <v>1.830463</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AB16" t="n">
+        <v>5.900488</v>
+      </c>
+      <c r="AC16" t="n">
         <v>5.899363</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AD16" t="n">
         <v>5.974439</v>
       </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
       <c r="AE16" t="n">
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
         <v>0.03</v>
       </c>
       <c r="AI16" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AK16" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2142,96 +2220,102 @@
         <v>0.050788</v>
       </c>
       <c r="E17" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F17" t="n">
         <v>0.45</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>100.58566</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>99.97338999999999</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>5.2177</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>5.2171</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>5366069</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>2178236</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>3187833</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>3.07</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>1.8</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>3.94</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>29.64</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>324703</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>-0.124753</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>0.827113</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>-1.443116</v>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
         <v>-1.443279</v>
       </c>
-      <c r="W17" t="n">
+      <c r="X17" t="n">
         <v>1.521325</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Y17" t="n">
         <v>2.249624</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Z17" t="n">
         <v>1.029618</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AA17" t="n">
         <v>-2.051854</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AB17" t="n">
+        <v>5.784842</v>
+      </c>
+      <c r="AC17" t="n">
         <v>5.458422</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AD17" t="n">
         <v>5.932356</v>
       </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
         <v>-0</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AG17" t="n">
         <v>-0</v>
       </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AJ17" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AK17" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -2249,96 +2333,102 @@
         <v>0.050788</v>
       </c>
       <c r="E18" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F18" t="n">
         <v>0.21</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>0.46</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>100.10937</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>95.09372999999999</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>5.0993</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>5.0987</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>5373231</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>2151399</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>3221831</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>3.24</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>1.94</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>4.11</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>30.54</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>331122</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>-0.473517</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>-4.880959</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>-2.269199</v>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>-2.26946</v>
       </c>
-      <c r="W18" t="n">
+      <c r="X18" t="n">
         <v>0.133468</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Y18" t="n">
         <v>-1.232052</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Z18" t="n">
         <v>1.066493</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AA18" t="n">
         <v>1.976883</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AB18" t="n">
+        <v>5.77432</v>
+      </c>
+      <c r="AC18" t="n">
         <v>3.79089</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AD18" t="n">
         <v>5.711379</v>
       </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
         <v>0.17</v>
       </c>
       <c r="AI18" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AK18" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2356,96 +2446,102 @@
         <v>0.050788</v>
       </c>
       <c r="E19" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F19" t="n">
         <v>-0.06</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>0.77</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>103.08344</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>98.65015</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>5.2078</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>5.2072</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>5370950</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>2136105</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>3234845</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>3.36</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>2.17</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>4.16</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>30.48</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>328098</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>2.970821</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>3.73991</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>2.127743</v>
       </c>
-      <c r="V19" t="n">
+      <c r="W19" t="n">
         <v>2.127993</v>
       </c>
-      <c r="W19" t="n">
+      <c r="X19" t="n">
         <v>-0.042451</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Y19" t="n">
         <v>-0.710886</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="Z19" t="n">
         <v>0.403932</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AA19" t="n">
         <v>-0.913259</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AB19" t="n">
+        <v>5.596302</v>
+      </c>
+      <c r="AC19" t="n">
         <v>1.864495</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AD19" t="n">
         <v>5.47065</v>
       </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
       <c r="AE19" t="n">
         <v>0</v>
       </c>
       <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
         <v>0.12</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AI19" t="n">
         <v>0.23</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AJ19" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AK19" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2463,96 +2559,102 @@
         <v>0.050788</v>
       </c>
       <c r="E20" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F20" t="n">
         <v>0.05</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>0.64</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>103.08526</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>110.62045</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>5.0804</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>5.0798</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>5424811</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>2154900</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>3269910</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>3.35</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>2.2</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>4.11</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>30.99</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>341158</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>0.001766</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>12.134092</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>-2.446331</v>
       </c>
-      <c r="V20" t="n">
+      <c r="W20" t="n">
         <v>-2.446612</v>
       </c>
-      <c r="W20" t="n">
+      <c r="X20" t="n">
         <v>1.002821</v>
       </c>
-      <c r="X20" t="n">
+      <c r="Y20" t="n">
         <v>0.879872</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="Z20" t="n">
         <v>1.083978</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AA20" t="n">
         <v>3.980518</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AB20" t="n">
+        <v>4.650694</v>
+      </c>
+      <c r="AC20" t="n">
         <v>0.172427</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AD20" t="n">
         <v>4.361088</v>
       </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
       <c r="AE20" t="n">
         <v>0</v>
       </c>
       <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AI20" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AJ20" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AK20" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2570,96 +2672,102 @@
         <v>0.050788</v>
       </c>
       <c r="E21" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="F21" t="n">
         <v>-0.95</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>0.53</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>103.96006</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>104.03539</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>5.0007</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>5.0001</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>5426307</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>2145000</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>3281308</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>3.54</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>2.45</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>4.26</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>31.62</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>345725</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>0.848618</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>-5.952841</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>-1.568774</v>
       </c>
-      <c r="V21" t="n">
+      <c r="W21" t="n">
         <v>-1.568959</v>
       </c>
-      <c r="W21" t="n">
+      <c r="X21" t="n">
         <v>0.027577</v>
       </c>
-      <c r="X21" t="n">
+      <c r="Y21" t="n">
         <v>-0.459418</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="Z21" t="n">
         <v>0.348572</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AA21" t="n">
         <v>1.338676</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AB21" t="n">
+        <v>4.184706</v>
+      </c>
+      <c r="AC21" t="n">
         <v>-2.158772</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AD21" t="n">
         <v>3.834324</v>
       </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
       <c r="AE21" t="n">
         <v>0</v>
       </c>
       <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
         <v>0.19</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AI21" t="n">
         <v>0.25</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AJ21" t="n">
         <v>0.15</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AK21" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -2677,96 +2785,102 @@
         <v>0.050788</v>
       </c>
       <c r="E22" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F22" t="n">
         <v>-1.84</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>0.36</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>102.40467</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>102.71665</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>5.0959</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>5.0953</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>5453708</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>2145530</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>3308178</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>3.65</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>2.58</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>4.35</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>31.63</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>343489</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>-1.496142</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>-1.267588</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>1.903733</v>
       </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
         <v>1.903962</v>
       </c>
-      <c r="W22" t="n">
+      <c r="X22" t="n">
         <v>0.504966</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Y22" t="n">
         <v>0.024709</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="Z22" t="n">
         <v>0.818881</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AA22" t="n">
         <v>-0.646757</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AB22" t="n">
+        <v>3.935832</v>
+      </c>
+      <c r="AC22" t="n">
         <v>-4.45588</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AD22" t="n">
         <v>3.741292</v>
       </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
         <v>-0</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AG22" t="n">
         <v>-0</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AH22" t="n">
         <v>0.11</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AI22" t="n">
         <v>0.13</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AJ22" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI22" t="n">
+      <c r="AK22" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -2784,96 +2898,102 @@
         <v>0.050788</v>
       </c>
       <c r="E23" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="F23" t="n">
         <v>-1.93</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>-0.1</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>102.4398</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>102.285</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>4.8192</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>4.8186</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>5479459</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>2169613</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>3309846</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>3.61</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>2.63</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>4.25</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>30.85</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>343620</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>0.034305</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>-0.420234</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>-5.429855</v>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
         <v>-5.430495</v>
       </c>
-      <c r="W23" t="n">
+      <c r="X23" t="n">
         <v>0.472174</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Y23" t="n">
         <v>1.122473</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="Z23" t="n">
         <v>0.050421</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AA23" t="n">
         <v>0.038138</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AB23" t="n">
+        <v>3.161501</v>
+      </c>
+      <c r="AC23" t="n">
         <v>-6.84947</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AD23" t="n">
         <v>2.998957</v>
       </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
       <c r="AE23" t="n">
         <v>0</v>
       </c>
       <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AI23" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AJ23" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AK23" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -2891,96 +3011,102 @@
         <v>0.050788</v>
       </c>
       <c r="E24" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F24" t="n">
         <v>-0.72</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>-0.09</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>102.89895</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>105.33914</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>4.7415</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>4.7409</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>5484871</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>2153541</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>3331330</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>3.63</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>2.73</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>4.22</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>30.43</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>345476</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>0.448214</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>2.985912</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>-1.612301</v>
       </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
         <v>-1.612502</v>
       </c>
-      <c r="W24" t="n">
+      <c r="X24" t="n">
         <v>0.098769</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Y24" t="n">
         <v>-0.740777</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="Z24" t="n">
         <v>0.6490939999999999</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AA24" t="n">
         <v>0.5401319999999999</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AB24" t="n">
+        <v>3.992444</v>
+      </c>
+      <c r="AC24" t="n">
         <v>-7.713954</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AD24" t="n">
         <v>3.527423</v>
       </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
       <c r="AE24" t="n">
         <v>0</v>
       </c>
       <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AI24" t="n">
         <v>0.1</v>
       </c>
-      <c r="AH24" t="n">
+      <c r="AJ24" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AK24" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -2998,96 +3124,102 @@
         <v>0.049189</v>
       </c>
       <c r="E25" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F25" t="n">
         <v>-0.14</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>0.2</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>102.48797</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>106.05945</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>4.9219</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>4.9213</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5559063</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>2172658</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>3386405</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>3.61</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>2.82</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>4.12</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>29.92</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>344177</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>-0.399402</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>0.683801</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>3.804703</v>
       </c>
-      <c r="V25" t="n">
+      <c r="W25" t="n">
         <v>3.805185</v>
       </c>
-      <c r="W25" t="n">
+      <c r="X25" t="n">
         <v>1.352666</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Y25" t="n">
         <v>0.887701</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="Z25" t="n">
         <v>1.653244</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AA25" t="n">
         <v>-0.376003</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AB25" t="n">
+        <v>4.608216</v>
+      </c>
+      <c r="AC25" t="n">
         <v>-7.193509</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AD25" t="n">
         <v>4.057054</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AE25" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AF25" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AG25" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AH25" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AI25" t="n">
         <v>0.09</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AJ25" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="AK25" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -3105,96 +3237,102 @@
         <v>0.048422</v>
       </c>
       <c r="E26" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F26" t="n">
         <v>0.37</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>0.11</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>102.50227</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>101.76242</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>5.0076</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>5.007</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>5625945</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>2215175</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>3410769</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>3.54</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>2.82</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>4</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>29.66</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>340324</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>0.013953</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>-4.05153</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>1.741198</v>
       </c>
-      <c r="V26" t="n">
+      <c r="W26" t="n">
         <v>1.74141</v>
       </c>
-      <c r="W26" t="n">
+      <c r="X26" t="n">
         <v>1.203116</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Y26" t="n">
         <v>1.956912</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="Z26" t="n">
         <v>0.719465</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AA26" t="n">
         <v>-1.119482</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AB26" t="n">
+        <v>5.185235</v>
+      </c>
+      <c r="AC26" t="n">
         <v>-5.956714</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AD26" t="n">
         <v>4.505936</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AE26" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AF26" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AG26" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="AF26" t="n">
+      <c r="AH26" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AK26" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -3212,96 +3350,102 @@
         <v>0.047279</v>
       </c>
       <c r="E27" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F27" t="n">
         <v>0.5</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>0.12</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>102.83037</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>101.92849</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>5.0575</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>5.0569</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>5653808</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>2204808</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>3449000</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>3.56</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>2.92</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>3.97</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>29.24</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>340247</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>0.32009</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>0.163194</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>0.996485</v>
       </c>
-      <c r="V27" t="n">
+      <c r="W27" t="n">
         <v>0.996605</v>
       </c>
-      <c r="W27" t="n">
+      <c r="X27" t="n">
         <v>0.495259</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Y27" t="n">
         <v>-0.467999</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="Z27" t="n">
         <v>1.120891</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AA27" t="n">
         <v>-0.022625</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AB27" t="n">
+        <v>4.819246</v>
+      </c>
+      <c r="AC27" t="n">
         <v>-4.560737</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AD27" t="n">
         <v>4.141877</v>
       </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AG27" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AH27" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AI27" t="n">
         <v>0.1</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="AJ27" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AK27" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3319,96 +3463,102 @@
         <v>0.045601</v>
       </c>
       <c r="E28" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F28" t="n">
         <v>0.59</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>0.1</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>103.58799</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>101.68208</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>4.9355</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>4.9349</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>5711103</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>2220766</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>3490337</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>3.53</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>2.99</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>3.88</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>29.01</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>348406</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>0.7367669999999999</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>-0.241748</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>-2.412259</v>
       </c>
-      <c r="V28" t="n">
+      <c r="W28" t="n">
         <v>-2.412545</v>
       </c>
-      <c r="W28" t="n">
+      <c r="X28" t="n">
         <v>1.013388</v>
       </c>
-      <c r="X28" t="n">
+      <c r="Y28" t="n">
         <v>0.723782</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="Z28" t="n">
         <v>1.198521</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AA28" t="n">
         <v>2.397964</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AB28" t="n">
+        <v>4.683537</v>
+      </c>
+      <c r="AC28" t="n">
         <v>-3.457004</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AD28" t="n">
         <v>3.851383</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AE28" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AF28" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AG28" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AH28" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AI28" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AH28" t="n">
+      <c r="AJ28" t="n">
         <v>-0.09</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AK28" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -3426,96 +3576,102 @@
         <v>0.044537</v>
       </c>
       <c r="E29" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F29" t="n">
         <v>0.74</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>0.55</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>104.88262</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>101.68652</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>4.8413</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>4.8407</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>5805157</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>2283485</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>3521672</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>3.29</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>2.59</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>28.14</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>355034</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>1.249788</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>0.004367</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>-1.908621</v>
       </c>
-      <c r="V29" t="n">
+      <c r="W29" t="n">
         <v>-1.908853</v>
       </c>
-      <c r="W29" t="n">
+      <c r="X29" t="n">
         <v>1.646862</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Y29" t="n">
         <v>2.824206</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="Z29" t="n">
         <v>0.897764</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AA29" t="n">
         <v>1.902378</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AB29" t="n">
+        <v>4.621114</v>
+      </c>
+      <c r="AC29" t="n">
         <v>-3.178284</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AD29" t="n">
         <v>3.706988</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AE29" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AF29" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AG29" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AH29" t="n">
         <v>-0.24</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AI29" t="n">
         <v>-0.4</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AJ29" t="n">
         <v>-0.13</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AK29" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3533,96 +3689,102 @@
         <v>0.043739</v>
       </c>
       <c r="E30" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F30" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>0.57</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>104.47589</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>99.29136</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>4.9535</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>4.9529</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>5794707</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>2234362</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3560345</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>3.38</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2.77</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>3.76</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>28</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>355066</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>-0.387795</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>-2.355435</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>2.317559</v>
       </c>
-      <c r="V30" t="n">
+      <c r="W30" t="n">
         <v>2.317847</v>
       </c>
-      <c r="W30" t="n">
+      <c r="X30" t="n">
         <v>-0.180012</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Y30" t="n">
         <v>-2.151229</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="Z30" t="n">
         <v>1.098143</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AA30" t="n">
         <v>0.009013</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AB30" t="n">
+        <v>4.506637</v>
+      </c>
+      <c r="AC30" t="n">
         <v>-3.31355</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AD30" t="n">
         <v>3.820543</v>
       </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AG30" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AH30" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AI30" t="n">
         <v>0.18</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AJ30" t="n">
         <v>0.01</v>
       </c>
-      <c r="AI30" t="n">
+      <c r="AK30" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -3640,96 +3802,102 @@
         <v>0.041957</v>
       </c>
       <c r="E31" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F31" t="n">
         <v>-0.52</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>104.67291</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>102.15158</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>4.9833</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>4.9827</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>5815954</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>2235302</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>3580652</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>3.38</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>2.76</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>3.76</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>27.85</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>352705</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>0.188579</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>2.880633</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>0.601595</v>
       </c>
-      <c r="V31" t="n">
+      <c r="W31" t="n">
         <v>0.601668</v>
       </c>
-      <c r="W31" t="n">
+      <c r="X31" t="n">
         <v>0.366662</v>
       </c>
-      <c r="X31" t="n">
+      <c r="Y31" t="n">
         <v>0.04207</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="Z31" t="n">
         <v>0.570366</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AA31" t="n">
         <v>-0.664947</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AB31" t="n">
+        <v>4.496274</v>
+      </c>
+      <c r="AC31" t="n">
         <v>-3.758575</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AD31" t="n">
         <v>3.861754</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AE31" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AF31" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AG31" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -3747,96 +3915,102 @@
         <v>0.04142</v>
       </c>
       <c r="E32" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F32" t="n">
         <v>-0.47</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>0.19</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>104.68779</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>109.57244</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>4.9962</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>4.9956</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>5899742</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>2285775</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>3613967</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>3.33</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>2.71</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>28.14</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>355008</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>0.014216</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>7.264557</v>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
         <v>0.258865</v>
       </c>
-      <c r="V32" t="n">
+      <c r="W32" t="n">
         <v>0.258896</v>
       </c>
-      <c r="W32" t="n">
+      <c r="X32" t="n">
         <v>1.440658</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Y32" t="n">
         <v>2.257995</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="Z32" t="n">
         <v>0.930417</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AA32" t="n">
         <v>0.652954</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AB32" t="n">
+        <v>3.925596</v>
+      </c>
+      <c r="AC32" t="n">
         <v>-4.25878</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AD32" t="n">
         <v>3.397348</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AE32" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AF32" t="n">
         <v>-0.000537</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AG32" t="n">
         <v>-0.000537</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>-0.05</v>
       </c>
       <c r="AH32" t="n">
         <v>-0.05</v>
       </c>
       <c r="AI32" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK32" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -3854,96 +4028,102 @@
         <v>0.040168</v>
       </c>
       <c r="E33" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F33" t="n">
         <v>0.31</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>0.37</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>104.6751</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>109.25226</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>5.1718</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>5.1712</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5915538</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>2268879</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3646659</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>3.37</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>2.76</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>27.86</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>351599</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>-0.012122</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
         <v>-0.292209</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>3.514671</v>
       </c>
-      <c r="V33" t="n">
+      <c r="W33" t="n">
         <v>3.515093</v>
       </c>
-      <c r="W33" t="n">
+      <c r="X33" t="n">
         <v>0.267741</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Y33" t="n">
         <v>-0.7391799999999999</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="Z33" t="n">
         <v>0.904602</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AA33" t="n">
         <v>-0.96026</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AB33" t="n">
+        <v>3.688016</v>
+      </c>
+      <c r="AC33" t="n">
         <v>-3.040871</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AD33" t="n">
         <v>3.232784</v>
       </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
         <v>-0.001252</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AG33" t="n">
         <v>-0.001252</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0.05</v>
       </c>
       <c r="AH33" t="n">
         <v>0.04</v>
       </c>
       <c r="AI33" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK33" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -3961,96 +4141,102 @@
         <v>0.039484</v>
       </c>
       <c r="E34" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F34" t="n">
         <v>0.89</v>
       </c>
-      <c r="F34" t="n">
+      <c r="G34" t="n">
         <v>0.46</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>105.5521</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>104.71219</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>5.2416</v>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>5.241</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>5953960</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>2278309</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>3675652</v>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>3.43</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>2.8</v>
       </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
         <v>3.82</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>27.75</v>
       </c>
-      <c r="R34" t="n">
+      <c r="S34" t="n">
         <v>355560</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>0.837831</v>
       </c>
-      <c r="T34" t="n">
+      <c r="U34" t="n">
         <v>-4.155585</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>1.349627</v>
       </c>
-      <c r="V34" t="n">
+      <c r="W34" t="n">
         <v>1.349783</v>
       </c>
-      <c r="W34" t="n">
+      <c r="X34" t="n">
         <v>0.64951</v>
       </c>
-      <c r="X34" t="n">
+      <c r="Y34" t="n">
         <v>0.415624</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="Z34" t="n">
         <v>0.795057</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AA34" t="n">
         <v>1.126567</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AB34" t="n">
+        <v>3.925952</v>
+      </c>
+      <c r="AC34" t="n">
         <v>-0.344269</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AD34" t="n">
         <v>3.335647</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AE34" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AF34" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="AE34" t="n">
+      <c r="AG34" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="AF34" t="n">
+      <c r="AH34" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG34" t="n">
+      <c r="AI34" t="n">
         <v>0.04</v>
       </c>
-      <c r="AH34" t="n">
+      <c r="AJ34" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI34" t="n">
+      <c r="AK34" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -4068,96 +4254,102 @@
         <v>0.03927</v>
       </c>
       <c r="E35" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F35" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="n">
         <v>0.25</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>106.65779</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>105.87342</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>5.5589</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>5.5583</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>6041898</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>2336858</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>3705041</v>
       </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>3.29</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>2.64</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>27.81</v>
       </c>
-      <c r="R35" t="n">
+      <c r="S35" t="n">
         <v>357827</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>1.04753</v>
       </c>
-      <c r="T35" t="n">
+      <c r="U35" t="n">
         <v>1.108973</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>6.053495</v>
       </c>
-      <c r="V35" t="n">
+      <c r="W35" t="n">
         <v>6.054188</v>
       </c>
-      <c r="W35" t="n">
+      <c r="X35" t="n">
         <v>1.476967</v>
       </c>
-      <c r="X35" t="n">
+      <c r="Y35" t="n">
         <v>2.569845</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="Z35" t="n">
         <v>0.799559</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AA35" t="n">
         <v>0.637586</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AB35" t="n">
+        <v>4.227578</v>
+      </c>
+      <c r="AC35" t="n">
         <v>2.440035</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AD35" t="n">
         <v>3.697684</v>
       </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="AE35" t="n">
+      <c r="AG35" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="AF35" t="n">
+      <c r="AH35" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AI35" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AH35" t="n">
+      <c r="AJ35" t="n">
         <v>-0.11</v>
       </c>
-      <c r="AI35" t="n">
+      <c r="AK35" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -4175,96 +4367,102 @@
         <v>0.03927</v>
       </c>
       <c r="E36" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F36" t="n">
         <v>0.61</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>0.26</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>107.01873</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>111.50432</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>5.6621</v>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>5.6615</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>6069205</v>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>2323362</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>3745844</v>
       </c>
-      <c r="N36" t="n">
+      <c r="O36" t="n">
         <v>3.3</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>2.52</v>
       </c>
-      <c r="P36" t="n">
+      <c r="Q36" t="n">
         <v>3.78</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>27.74</v>
       </c>
-      <c r="R36" t="n">
+      <c r="S36" t="n">
         <v>363282</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>0.338409</v>
       </c>
-      <c r="T36" t="n">
+      <c r="U36" t="n">
         <v>5.318521</v>
       </c>
-      <c r="U36" t="n">
+      <c r="V36" t="n">
         <v>1.856482</v>
       </c>
-      <c r="V36" t="n">
+      <c r="W36" t="n">
         <v>1.856683</v>
       </c>
-      <c r="W36" t="n">
+      <c r="X36" t="n">
         <v>0.451961</v>
       </c>
-      <c r="X36" t="n">
+      <c r="Y36" t="n">
         <v>-0.577528</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="Z36" t="n">
         <v>1.101283</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AA36" t="n">
         <v>1.52448</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AB36" t="n">
+        <v>4.498245</v>
+      </c>
+      <c r="AC36" t="n">
         <v>3.812368</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AD36" t="n">
         <v>4.060953</v>
       </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
       <c r="AE36" t="n">
         <v>0</v>
       </c>
       <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
         <v>0.01</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AI36" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AH36" t="n">
+      <c r="AJ36" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI36" t="n">
+      <c r="AK36" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -4282,96 +4480,102 @@
         <v>0.03927</v>
       </c>
       <c r="E37" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F37" t="n">
         <v>0.29</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>-0.14</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>107.16697</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>110.06264</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>5.6562</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>5.6556</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6135298</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>2344397</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>3790900</v>
       </c>
-      <c r="N37" t="n">
+      <c r="O37" t="n">
         <v>3.33</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>2.55</v>
       </c>
-      <c r="P37" t="n">
+      <c r="Q37" t="n">
         <v>3.82</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>27.59</v>
       </c>
-      <c r="R37" t="n">
+      <c r="S37" t="n">
         <v>369214</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>0.138518</v>
       </c>
-      <c r="T37" t="n">
+      <c r="U37" t="n">
         <v>-1.292936</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>-0.104202</v>
       </c>
-      <c r="V37" t="n">
+      <c r="W37" t="n">
         <v>-0.104213</v>
       </c>
-      <c r="W37" t="n">
+      <c r="X37" t="n">
         <v>1.088989</v>
       </c>
-      <c r="X37" t="n">
+      <c r="Y37" t="n">
         <v>0.905369</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="Z37" t="n">
         <v>1.202826</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AA37" t="n">
         <v>1.632891</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AB37" t="n">
+        <v>4.237599</v>
+      </c>
+      <c r="AC37" t="n">
         <v>4.259387</v>
       </c>
-      <c r="AB37" t="n">
+      <c r="AD37" t="n">
         <v>3.707852</v>
       </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
       <c r="AE37" t="n">
         <v>0</v>
       </c>
       <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AI37" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH37" t="n">
+      <c r="AJ37" t="n">
         <v>0.04</v>
       </c>
-      <c r="AI37" t="n">
+      <c r="AK37" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4389,96 +4593,102 @@
         <v>0.039612</v>
       </c>
       <c r="E38" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F38" t="n">
         <v>0.62</v>
       </c>
-      <c r="F38" t="n">
+      <c r="G38" t="n">
         <v>0.48</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>108.02415</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>107.08272</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>5.4481</v>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>5.4475</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>6216528</v>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>2384828</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>3831700</v>
       </c>
-      <c r="N38" t="n">
+      <c r="O38" t="n">
         <v>3.34</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>2.56</v>
       </c>
-      <c r="P38" t="n">
+      <c r="Q38" t="n">
         <v>3.83</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>27.49</v>
       </c>
-      <c r="R38" t="n">
+      <c r="S38" t="n">
         <v>372016</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>0.799855</v>
       </c>
-      <c r="T38" t="n">
+      <c r="U38" t="n">
         <v>-2.707476</v>
       </c>
-      <c r="U38" t="n">
+      <c r="V38" t="n">
         <v>-3.679149</v>
       </c>
-      <c r="V38" t="n">
+      <c r="W38" t="n">
         <v>-3.679539</v>
       </c>
-      <c r="W38" t="n">
+      <c r="X38" t="n">
         <v>1.323978</v>
       </c>
-      <c r="X38" t="n">
+      <c r="Y38" t="n">
         <v>1.72458</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="Z38" t="n">
         <v>1.076262</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AA38" t="n">
         <v>0.7589089999999999</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AB38" t="n">
+        <v>4.42474</v>
+      </c>
+      <c r="AC38" t="n">
         <v>4.519075</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AD38" t="n">
         <v>4.091149</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AE38" t="n">
         <v>0.25</v>
       </c>
-      <c r="AD38" t="n">
+      <c r="AF38" t="n">
         <v>0.000342</v>
       </c>
-      <c r="AE38" t="n">
+      <c r="AG38" t="n">
         <v>0.000342</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0.01</v>
       </c>
       <c r="AH38" t="n">
         <v>0.01</v>
       </c>
       <c r="AI38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AK38" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -4496,96 +4706,102 @@
         <v>0.040168</v>
       </c>
       <c r="E39" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F39" t="n">
         <v>1.52</v>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>0.61</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>108.23273</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>109.17883</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>5.7779</v>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>5.7773</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>6275117</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>2397533</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>3877584</v>
       </c>
-      <c r="N39" t="n">
+      <c r="O39" t="n">
         <v>3.3</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>2.52</v>
       </c>
-      <c r="P39" t="n">
+      <c r="Q39" t="n">
         <v>3.79</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>27.94</v>
       </c>
-      <c r="R39" t="n">
+      <c r="S39" t="n">
         <v>366096</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>0.193086</v>
       </c>
-      <c r="T39" t="n">
+      <c r="U39" t="n">
         <v>1.957468</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>6.053487</v>
       </c>
-      <c r="V39" t="n">
+      <c r="W39" t="n">
         <v>6.054153</v>
       </c>
-      <c r="W39" t="n">
+      <c r="X39" t="n">
         <v>0.9424709999999999</v>
       </c>
-      <c r="X39" t="n">
+      <c r="Y39" t="n">
         <v>0.532743</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="Z39" t="n">
         <v>1.197484</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AA39" t="n">
         <v>-1.591329</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AB39" t="n">
+        <v>4.758099</v>
+      </c>
+      <c r="AC39" t="n">
         <v>5.579866</v>
       </c>
-      <c r="AB39" t="n">
+      <c r="AD39" t="n">
         <v>4.600584</v>
       </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
         <v>0.000556</v>
       </c>
-      <c r="AE39" t="n">
+      <c r="AG39" t="n">
         <v>0.000556</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>-0.04</v>
       </c>
       <c r="AH39" t="n">
         <v>-0.04</v>
       </c>
       <c r="AI39" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AK39" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -4603,96 +4819,102 @@
         <v>0.04158</v>
       </c>
       <c r="E40" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F40" t="n">
         <v>1.3</v>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="n">
         <v>0.33</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>107.99539</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>105.48993</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>6.0535</v>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>6.0529</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>6365690</v>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
         <v>2436022</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>3929668</v>
       </c>
-      <c r="N40" t="n">
+      <c r="O40" t="n">
         <v>3.27</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>2.5</v>
       </c>
-      <c r="P40" t="n">
+      <c r="Q40" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>28.45</v>
       </c>
-      <c r="R40" t="n">
+      <c r="S40" t="n">
         <v>363003</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>-0.219287</v>
       </c>
-      <c r="T40" t="n">
+      <c r="U40" t="n">
         <v>-3.378769</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>4.769899</v>
       </c>
-      <c r="V40" t="n">
+      <c r="W40" t="n">
         <v>4.770394</v>
       </c>
-      <c r="W40" t="n">
+      <c r="X40" t="n">
         <v>1.443368</v>
       </c>
-      <c r="X40" t="n">
+      <c r="Y40" t="n">
         <v>1.605359</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="Z40" t="n">
         <v>1.343208</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AA40" t="n">
         <v>-0.8448600000000001</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AB40" t="n">
+        <v>4.873011</v>
+      </c>
+      <c r="AC40" t="n">
         <v>6.325086</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AD40" t="n">
         <v>4.840925</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AE40" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AF40" t="n">
         <v>0.001412</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AG40" t="n">
         <v>0.001412</v>
       </c>
-      <c r="AF40" t="n">
+      <c r="AH40" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG40" t="n">
+      <c r="AI40" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AH40" t="n">
+      <c r="AJ40" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AI40" t="n">
+      <c r="AK40" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4710,96 +4932,102 @@
         <v>0.044158</v>
       </c>
       <c r="E41" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F41" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>0.48</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>107.3722</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>104.15749</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>6.1923</v>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>6.1917</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>6464602</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>2499177</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>3965425</v>
       </c>
-      <c r="N41" t="n">
+      <c r="O41" t="n">
         <v>3.08</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>2.21</v>
       </c>
-      <c r="P41" t="n">
+      <c r="Q41" t="n">
         <v>3.63</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>28.5</v>
       </c>
-      <c r="R41" t="n">
+      <c r="S41" t="n">
         <v>329730</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>-0.577052</v>
       </c>
-      <c r="T41" t="n">
+      <c r="U41" t="n">
         <v>-1.263097</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>2.292888</v>
       </c>
-      <c r="V41" t="n">
+      <c r="W41" t="n">
         <v>2.293116</v>
       </c>
-      <c r="W41" t="n">
+      <c r="X41" t="n">
         <v>1.55383</v>
       </c>
-      <c r="X41" t="n">
+      <c r="Y41" t="n">
         <v>2.592546</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="Z41" t="n">
         <v>0.909924</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AA41" t="n">
         <v>-9.166040000000001</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AB41" t="n">
+        <v>4.831296</v>
+      </c>
+      <c r="AC41" t="n">
         <v>6.536174</v>
       </c>
-      <c r="AB41" t="n">
+      <c r="AD41" t="n">
         <v>4.767938</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AE41" t="n">
         <v>1</v>
       </c>
-      <c r="AD41" t="n">
+      <c r="AF41" t="n">
         <v>0.002578</v>
       </c>
-      <c r="AE41" t="n">
+      <c r="AG41" t="n">
         <v>0.002578</v>
       </c>
-      <c r="AF41" t="n">
+      <c r="AH41" t="n">
         <v>-0.19</v>
       </c>
-      <c r="AG41" t="n">
+      <c r="AI41" t="n">
         <v>-0.29</v>
       </c>
-      <c r="AH41" t="n">
+      <c r="AJ41" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AI41" t="n">
+      <c r="AK41" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -4817,96 +5045,102 @@
         <v>0.045833</v>
       </c>
       <c r="E42" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F42" t="n">
         <v>0.27</v>
       </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
       <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
         <v>108.10202</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>102.62361</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>5.8301</v>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>5.8295</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>6465016</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>2451957</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>4013059</v>
       </c>
-      <c r="N42" t="n">
+      <c r="O42" t="n">
         <v>3.34</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>2.43</v>
       </c>
-      <c r="P42" t="n">
+      <c r="Q42" t="n">
         <v>3.89</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>29.88</v>
       </c>
-      <c r="R42" t="n">
+      <c r="S42" t="n">
         <v>328303</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>0.67971</v>
       </c>
-      <c r="T42" t="n">
+      <c r="U42" t="n">
         <v>-1.472655</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>-5.8492</v>
       </c>
-      <c r="V42" t="n">
+      <c r="W42" t="n">
         <v>-5.849767</v>
       </c>
-      <c r="W42" t="n">
+      <c r="X42" t="n">
         <v>0.006404</v>
       </c>
-      <c r="X42" t="n">
+      <c r="Y42" t="n">
         <v>-1.889422</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="Z42" t="n">
         <v>1.201233</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AA42" t="n">
         <v>-0.432778</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AB42" t="n">
+        <v>4.559874</v>
+      </c>
+      <c r="AC42" t="n">
         <v>6.749097</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AD42" t="n">
         <v>4.174145</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AE42" t="n">
         <v>1</v>
       </c>
-      <c r="AD42" t="n">
+      <c r="AF42" t="n">
         <v>0.001675</v>
       </c>
-      <c r="AE42" t="n">
+      <c r="AG42" t="n">
         <v>0.001675</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0.22</v>
       </c>
       <c r="AH42" t="n">
         <v>0.26</v>
       </c>
       <c r="AI42" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AK42" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -4924,96 +5158,102 @@
         <v>0.049037</v>
       </c>
       <c r="E43" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="F43" t="n">
         <v>1.06</v>
       </c>
-      <c r="F43" t="n">
+      <c r="G43" t="n">
         <v>1.48</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>108.64347</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>106.82695</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>5.8488</v>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
         <v>5.8482</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>6511444</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>2477151</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>4034293</v>
       </c>
-      <c r="N43" t="n">
+      <c r="O43" t="n">
         <v>3.41</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2.52</v>
       </c>
-      <c r="P43" t="n">
+      <c r="Q43" t="n">
         <v>3.96</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>30.53</v>
       </c>
-      <c r="R43" t="n">
+      <c r="S43" t="n">
         <v>332508</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>0.500869</v>
       </c>
-      <c r="T43" t="n">
+      <c r="U43" t="n">
         <v>4.09588</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>0.320749</v>
       </c>
-      <c r="V43" t="n">
+      <c r="W43" t="n">
         <v>0.320782</v>
       </c>
-      <c r="W43" t="n">
+      <c r="X43" t="n">
         <v>0.7181419999999999</v>
       </c>
-      <c r="X43" t="n">
+      <c r="Y43" t="n">
         <v>1.027506</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="Z43" t="n">
         <v>0.529123</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="AA43" t="n">
         <v>1.280829</v>
       </c>
-      <c r="AA43" t="n">
+      <c r="AB43" t="n">
+        <v>5.05763</v>
+      </c>
+      <c r="AC43" t="n">
         <v>8.444549</v>
       </c>
-      <c r="AB43" t="n">
+      <c r="AD43" t="n">
         <v>4.866504</v>
       </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
         <v>0.003204</v>
       </c>
-      <c r="AE43" t="n">
+      <c r="AG43" t="n">
         <v>0.003204</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0.09</v>
       </c>
       <c r="AH43" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AI43" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AK43" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -5031,96 +5271,102 @@
         <v>0.050508</v>
       </c>
       <c r="E44" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F44" t="n">
         <v>-0.34</v>
       </c>
-      <c r="F44" t="n">
+      <c r="G44" t="n">
         <v>0.51</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>110.0586</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>114.02633</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>5.7422</v>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>5.7416</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>6576464</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>2498262</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>4078202</v>
       </c>
-      <c r="N44" t="n">
+      <c r="O44" t="n">
         <v>3.44</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>2.49</v>
       </c>
-      <c r="P44" t="n">
+      <c r="Q44" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>31.34</v>
       </c>
-      <c r="R44" t="n">
+      <c r="S44" t="n">
         <v>336157</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>1.302545</v>
       </c>
-      <c r="T44" t="n">
+      <c r="U44" t="n">
         <v>6.739292</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>-1.822596</v>
       </c>
-      <c r="V44" t="n">
+      <c r="W44" t="n">
         <v>-1.822783</v>
       </c>
-      <c r="W44" t="n">
+      <c r="X44" t="n">
         <v>0.99855</v>
       </c>
-      <c r="X44" t="n">
+      <c r="Y44" t="n">
         <v>0.852229</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="Z44" t="n">
         <v>1.088394</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AA44" t="n">
         <v>1.097417</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AB44" t="n">
+        <v>5.47719</v>
+      </c>
+      <c r="AC44" t="n">
         <v>8.586193</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="AD44" t="n">
         <v>5.201441</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AE44" t="n">
         <v>1</v>
       </c>
-      <c r="AD44" t="n">
+      <c r="AF44" t="n">
         <v>0.001471</v>
       </c>
-      <c r="AE44" t="n">
+      <c r="AG44" t="n">
         <v>0.001471</v>
       </c>
-      <c r="AF44" t="n">
+      <c r="AH44" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG44" t="n">
+      <c r="AI44" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AH44" t="n">
+      <c r="AJ44" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI44" t="n">
+      <c r="AK44" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -5138,96 +5384,102 @@
         <v>0.052531</v>
       </c>
       <c r="E45" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F45" t="n">
         <v>0.24</v>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
         <v>0.48</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>109.59971</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>112.58856</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>5.6608</v>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>5.6602</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>6623948</v>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" t="n">
         <v>2512426</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>4111522</v>
       </c>
-      <c r="N45" t="n">
+      <c r="O45" t="n">
         <v>3.67</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>2.72</v>
       </c>
-      <c r="P45" t="n">
+      <c r="Q45" t="n">
         <v>4.25</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>31.63</v>
       </c>
-      <c r="R45" t="n">
+      <c r="S45" t="n">
         <v>340789</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>-0.416951</v>
       </c>
-      <c r="T45" t="n">
+      <c r="U45" t="n">
         <v>-1.260911</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>-1.417575</v>
       </c>
-      <c r="V45" t="n">
+      <c r="W45" t="n">
         <v>-1.417723</v>
       </c>
-      <c r="W45" t="n">
+      <c r="X45" t="n">
         <v>0.722029</v>
       </c>
-      <c r="X45" t="n">
+      <c r="Y45" t="n">
         <v>0.566954</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="Z45" t="n">
         <v>0.8170269999999999</v>
       </c>
-      <c r="Z45" t="n">
+      <c r="AA45" t="n">
         <v>1.377928</v>
       </c>
-      <c r="AA45" t="n">
+      <c r="AB45" t="n">
+        <v>5.529729</v>
+      </c>
+      <c r="AC45" t="n">
         <v>8.510418</v>
       </c>
-      <c r="AB45" t="n">
+      <c r="AD45" t="n">
         <v>5.316736</v>
       </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
         <v>0.002023</v>
       </c>
-      <c r="AE45" t="n">
+      <c r="AG45" t="n">
         <v>0.002023</v>
       </c>
-      <c r="AF45" t="n">
+      <c r="AH45" t="n">
         <v>0.23</v>
       </c>
-      <c r="AG45" t="n">
+      <c r="AI45" t="n">
         <v>0.23</v>
       </c>
-      <c r="AH45" t="n">
+      <c r="AJ45" t="n">
         <v>0.22</v>
       </c>
-      <c r="AI45" t="n">
+      <c r="AK45" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -5245,96 +5497,102 @@
         <v>0.053936</v>
       </c>
       <c r="E46" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F46" t="n">
         <v>-0.49</v>
       </c>
-      <c r="F46" t="n">
+      <c r="G46" t="n">
         <v>0.35</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>108.80425</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>108.55662</v>
       </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
         <v>5.7087</v>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>5.7081</v>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
         <v>6666287</v>
       </c>
-      <c r="L46" t="n">
+      <c r="M46" t="n">
         <v>2532708</v>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
         <v>4133579</v>
       </c>
-      <c r="N46" t="n">
+      <c r="O46" t="n">
         <v>3.72</v>
       </c>
-      <c r="O46" t="n">
+      <c r="P46" t="n">
         <v>2.67</v>
       </c>
-      <c r="P46" t="n">
+      <c r="Q46" t="n">
         <v>4.36</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="R46" t="n">
         <v>31.7</v>
       </c>
-      <c r="R46" t="n">
+      <c r="S46" t="n">
         <v>341459</v>
       </c>
-      <c r="S46" t="n">
+      <c r="T46" t="n">
         <v>-0.725787</v>
       </c>
-      <c r="T46" t="n">
+      <c r="U46" t="n">
         <v>-3.581128</v>
       </c>
-      <c r="U46" t="n">
+      <c r="V46" t="n">
         <v>0.84617</v>
       </c>
-      <c r="V46" t="n">
+      <c r="W46" t="n">
         <v>0.84626</v>
       </c>
-      <c r="W46" t="n">
+      <c r="X46" t="n">
         <v>0.639181</v>
       </c>
-      <c r="X46" t="n">
+      <c r="Y46" t="n">
         <v>0.807268</v>
       </c>
-      <c r="Y46" t="n">
+      <c r="Z46" t="n">
         <v>0.5364679999999999</v>
       </c>
-      <c r="Z46" t="n">
+      <c r="AA46" t="n">
         <v>0.196603</v>
       </c>
-      <c r="AA46" t="n">
+      <c r="AB46" t="n">
+        <v>5.319636</v>
+      </c>
+      <c r="AC46" t="n">
         <v>7.026183</v>
       </c>
-      <c r="AB46" t="n">
+      <c r="AD46" t="n">
         <v>5.201418</v>
       </c>
-      <c r="AC46" t="n">
+      <c r="AE46" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD46" t="n">
+      <c r="AF46" t="n">
         <v>0.001405</v>
       </c>
-      <c r="AE46" t="n">
+      <c r="AG46" t="n">
         <v>0.001405</v>
       </c>
-      <c r="AF46" t="n">
+      <c r="AH46" t="n">
         <v>0.05</v>
       </c>
-      <c r="AG46" t="n">
+      <c r="AI46" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH46" t="n">
+      <c r="AJ46" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI46" t="n">
+      <c r="AK46" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5352,96 +5610,102 @@
         <v>0.054569</v>
       </c>
       <c r="E47" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F47" t="n">
         <v>-1.67</v>
       </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
         <v>0.23</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>108.90168</v>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>107.36878</v>
       </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
         <v>5.4571</v>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>5.4565</v>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>6703663</v>
       </c>
-      <c r="L47" t="n">
+      <c r="M47" t="n">
         <v>2547693</v>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
         <v>4155970</v>
       </c>
-      <c r="N47" t="n">
+      <c r="O47" t="n">
         <v>3.75</v>
       </c>
-      <c r="O47" t="n">
+      <c r="P47" t="n">
         <v>2.67</v>
       </c>
-      <c r="P47" t="n">
+      <c r="Q47" t="n">
         <v>4.41</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="R47" t="n">
         <v>31.85</v>
       </c>
-      <c r="R47" t="n">
+      <c r="S47" t="n">
         <v>344440</v>
       </c>
-      <c r="S47" t="n">
+      <c r="T47" t="n">
         <v>0.089546</v>
       </c>
-      <c r="T47" t="n">
+      <c r="U47" t="n">
         <v>-1.094212</v>
       </c>
-      <c r="U47" t="n">
+      <c r="V47" t="n">
         <v>-4.407308</v>
       </c>
-      <c r="V47" t="n">
+      <c r="W47" t="n">
         <v>-4.407771</v>
       </c>
-      <c r="W47" t="n">
+      <c r="X47" t="n">
         <v>0.5606719999999999</v>
       </c>
-      <c r="X47" t="n">
+      <c r="Y47" t="n">
         <v>0.591659</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="Z47" t="n">
         <v>0.541686</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="AA47" t="n">
         <v>0.873018</v>
       </c>
-      <c r="AA47" t="n">
+      <c r="AB47" t="n">
+        <v>5.351165</v>
+      </c>
+      <c r="AC47" t="n">
         <v>4.393261</v>
       </c>
-      <c r="AB47" t="n">
+      <c r="AD47" t="n">
         <v>5.18043</v>
       </c>
-      <c r="AC47" t="n">
+      <c r="AE47" t="n">
         <v>0.25</v>
       </c>
-      <c r="AD47" t="n">
+      <c r="AF47" t="n">
         <v>0.000633</v>
       </c>
-      <c r="AE47" t="n">
+      <c r="AG47" t="n">
         <v>0.000633</v>
       </c>
-      <c r="AF47" t="n">
+      <c r="AH47" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="n">
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI47" t="n">
+      <c r="AK47" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5459,96 +5723,102 @@
         <v>0.055131</v>
       </c>
       <c r="E48" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F48" t="n">
         <v>-0.77</v>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>0.21</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>108.39998</v>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>113.10359</v>
       </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
         <v>5.6021</v>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
         <v>5.6015</v>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" t="n">
         <v>6733209</v>
       </c>
-      <c r="L48" t="n">
+      <c r="M48" t="n">
         <v>2544400</v>
       </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
         <v>4188808</v>
       </c>
-      <c r="N48" t="n">
+      <c r="O48" t="n">
         <v>3.96</v>
       </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
         <v>2.79</v>
       </c>
-      <c r="P48" t="n">
+      <c r="Q48" t="n">
         <v>4.66</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="R48" t="n">
         <v>31.75</v>
       </c>
-      <c r="R48" t="n">
+      <c r="S48" t="n">
         <v>345111</v>
       </c>
-      <c r="S48" t="n">
+      <c r="T48" t="n">
         <v>-0.460691</v>
       </c>
-      <c r="T48" t="n">
+      <c r="U48" t="n">
         <v>5.341227</v>
       </c>
-      <c r="U48" t="n">
+      <c r="V48" t="n">
         <v>2.657089</v>
       </c>
-      <c r="V48" t="n">
+      <c r="W48" t="n">
         <v>2.657381</v>
       </c>
-      <c r="W48" t="n">
+      <c r="X48" t="n">
         <v>0.440744</v>
       </c>
-      <c r="X48" t="n">
+      <c r="Y48" t="n">
         <v>-0.129254</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="Z48" t="n">
         <v>0.79014</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="AA48" t="n">
         <v>0.194809</v>
       </c>
-      <c r="AA48" t="n">
+      <c r="AB48" t="n">
+        <v>5.225222</v>
+      </c>
+      <c r="AC48" t="n">
         <v>2.961368</v>
       </c>
-      <c r="AB48" t="n">
+      <c r="AD48" t="n">
         <v>5.127976</v>
       </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
         <v>0.000562</v>
       </c>
-      <c r="AE48" t="n">
+      <c r="AG48" t="n">
         <v>0.000562</v>
       </c>
-      <c r="AF48" t="n">
+      <c r="AH48" t="n">
         <v>0.21</v>
       </c>
-      <c r="AG48" t="n">
+      <c r="AI48" t="n">
         <v>0.12</v>
       </c>
-      <c r="AH48" t="n">
+      <c r="AJ48" t="n">
         <v>0.25</v>
       </c>
-      <c r="AI48" t="n">
+      <c r="AK48" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -5566,96 +5836,102 @@
         <v>0.055131</v>
       </c>
       <c r="E49" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="F49" t="n">
         <v>0.36</v>
       </c>
-      <c r="F49" t="n">
+      <c r="G49" t="n">
         <v>-0.21</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>108.79892</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>110.38013</v>
       </c>
-      <c r="I49" t="n">
+      <c r="J49" t="n">
         <v>5.4264</v>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
         <v>5.4258</v>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
         <v>6774436</v>
       </c>
-      <c r="L49" t="n">
+      <c r="M49" t="n">
         <v>2546265</v>
       </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
         <v>4228171</v>
       </c>
-      <c r="N49" t="n">
+      <c r="O49" t="n">
         <v>4.14</v>
       </c>
-      <c r="O49" t="n">
+      <c r="P49" t="n">
         <v>2.85</v>
       </c>
-      <c r="P49" t="n">
+      <c r="Q49" t="n">
         <v>4.92</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="R49" t="n">
         <v>31.87</v>
       </c>
-      <c r="R49" t="n">
+      <c r="S49" t="n">
         <v>350767</v>
       </c>
-      <c r="S49" t="n">
+      <c r="T49" t="n">
         <v>0.368026</v>
       </c>
-      <c r="T49" t="n">
+      <c r="U49" t="n">
         <v>-2.407934</v>
       </c>
-      <c r="U49" t="n">
+      <c r="V49" t="n">
         <v>-3.136324</v>
       </c>
-      <c r="V49" t="n">
+      <c r="W49" t="n">
         <v>-3.13666</v>
       </c>
-      <c r="W49" t="n">
+      <c r="X49" t="n">
         <v>0.612293</v>
       </c>
-      <c r="X49" t="n">
+      <c r="Y49" t="n">
         <v>0.073298</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="Z49" t="n">
         <v>0.9397180000000001</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="AA49" t="n">
         <v>1.638893</v>
       </c>
-      <c r="AA49" t="n">
+      <c r="AB49" t="n">
+        <v>5.130501</v>
+      </c>
+      <c r="AC49" t="n">
         <v>3.033233</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AD49" t="n">
         <v>5.054283</v>
       </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
       <c r="AE49" t="n">
         <v>0</v>
       </c>
       <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
         <v>0.18</v>
       </c>
-      <c r="AG49" t="n">
+      <c r="AI49" t="n">
         <v>0.06</v>
       </c>
-      <c r="AH49" t="n">
+      <c r="AJ49" t="n">
         <v>0.26</v>
       </c>
-      <c r="AI49" t="n">
+      <c r="AK49" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5673,96 +5949,102 @@
         <v>0.055131</v>
       </c>
       <c r="E50" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F50" t="n">
         <v>0.42</v>
       </c>
-      <c r="F50" t="n">
+      <c r="G50" t="n">
         <v>0.52</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>108.7209</v>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>109.48882</v>
       </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
         <v>5.3186</v>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
         <v>5.318</v>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" t="n">
         <v>6852705</v>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" t="n">
         <v>2589817</v>
       </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
         <v>4262888</v>
       </c>
-      <c r="N50" t="n">
+      <c r="O50" t="n">
         <v>4.09</v>
       </c>
-      <c r="O50" t="n">
+      <c r="P50" t="n">
         <v>2.77</v>
       </c>
-      <c r="P50" t="n">
+      <c r="Q50" t="n">
         <v>4.89</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="R50" t="n">
         <v>31.47</v>
       </c>
-      <c r="R50" t="n">
+      <c r="S50" t="n">
         <v>356582</v>
       </c>
-      <c r="S50" t="n">
+      <c r="T50" t="n">
         <v>-0.07171</v>
       </c>
-      <c r="T50" t="n">
+      <c r="U50" t="n">
         <v>-0.807491</v>
       </c>
-      <c r="U50" t="n">
+      <c r="V50" t="n">
         <v>-1.986584</v>
       </c>
-      <c r="V50" t="n">
+      <c r="W50" t="n">
         <v>-1.986804</v>
       </c>
-      <c r="W50" t="n">
+      <c r="X50" t="n">
         <v>1.155358</v>
       </c>
-      <c r="X50" t="n">
+      <c r="Y50" t="n">
         <v>1.710427</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="Z50" t="n">
         <v>0.821088</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="AA50" t="n">
         <v>1.657796</v>
       </c>
-      <c r="AA50" t="n">
+      <c r="AB50" t="n">
+        <v>5.172369</v>
+      </c>
+      <c r="AC50" t="n">
         <v>2.828436</v>
       </c>
-      <c r="AB50" t="n">
+      <c r="AD50" t="n">
         <v>5.096104</v>
       </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
       <c r="AE50" t="n">
         <v>0</v>
       </c>
       <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AG50" t="n">
+      <c r="AI50" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AH50" t="n">
+      <c r="AJ50" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI50" t="n">
+      <c r="AK50" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -5780,96 +6062,102 @@
         <v>0.055131</v>
       </c>
       <c r="E51" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F51" t="n">
         <v>-0.36</v>
       </c>
-      <c r="F51" t="n">
+      <c r="G51" t="n">
         <v>0.03</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>108.73364</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>110.06407</v>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
         <v>5.3843</v>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
         <v>5.3837</v>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
         <v>6923886</v>
       </c>
-      <c r="L51" t="n">
+      <c r="M51" t="n">
         <v>2597630</v>
       </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
         <v>4326256</v>
       </c>
-      <c r="N51" t="n">
+      <c r="O51" t="n">
         <v>4.18</v>
       </c>
-      <c r="O51" t="n">
+      <c r="P51" t="n">
         <v>2.82</v>
       </c>
-      <c r="P51" t="n">
+      <c r="Q51" t="n">
         <v>4.99</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="R51" t="n">
         <v>32.04</v>
       </c>
-      <c r="R51" t="n">
+      <c r="S51" t="n">
         <v>357103</v>
       </c>
-      <c r="S51" t="n">
+      <c r="T51" t="n">
         <v>0.011718</v>
       </c>
-      <c r="T51" t="n">
+      <c r="U51" t="n">
         <v>0.525396</v>
       </c>
-      <c r="U51" t="n">
+      <c r="V51" t="n">
         <v>1.235287</v>
       </c>
-      <c r="V51" t="n">
+      <c r="W51" t="n">
         <v>1.235427</v>
       </c>
-      <c r="W51" t="n">
+      <c r="X51" t="n">
         <v>1.038729</v>
       </c>
-      <c r="X51" t="n">
+      <c r="Y51" t="n">
         <v>0.301682</v>
       </c>
-      <c r="Y51" t="n">
+      <c r="Z51" t="n">
         <v>1.486504</v>
       </c>
-      <c r="Z51" t="n">
+      <c r="AA51" t="n">
         <v>0.146109</v>
       </c>
-      <c r="AA51" t="n">
+      <c r="AB51" t="n">
+        <v>4.680811</v>
+      </c>
+      <c r="AC51" t="n">
         <v>0.924206</v>
       </c>
-      <c r="AB51" t="n">
+      <c r="AD51" t="n">
         <v>4.490243</v>
       </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
       <c r="AE51" t="n">
         <v>0</v>
       </c>
       <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG51" t="n">
+      <c r="AI51" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH51" t="n">
+      <c r="AJ51" t="n">
         <v>0.1</v>
       </c>
-      <c r="AI51" t="n">
+      <c r="AK51" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -5887,96 +6175,102 @@
         <v>0.055131</v>
       </c>
       <c r="E52" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F52" t="n">
         <v>0.27</v>
       </c>
-      <c r="F52" t="n">
+      <c r="G52" t="n">
         <v>0.03</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>109.24151</v>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>106.59541</v>
       </c>
-      <c r="I52" t="n">
+      <c r="J52" t="n">
         <v>5.3338</v>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
         <v>5.3332</v>
       </c>
-      <c r="K52" t="n">
+      <c r="L52" t="n">
         <v>7004223</v>
       </c>
-      <c r="L52" t="n">
+      <c r="M52" t="n">
         <v>2616902</v>
       </c>
-      <c r="M52" t="n">
+      <c r="N52" t="n">
         <v>4387321</v>
       </c>
-      <c r="N52" t="n">
+      <c r="O52" t="n">
         <v>4.24</v>
       </c>
-      <c r="O52" t="n">
+      <c r="P52" t="n">
         <v>2.75</v>
       </c>
-      <c r="P52" t="n">
+      <c r="Q52" t="n">
         <v>5.12</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="R52" t="n">
         <v>32.2</v>
       </c>
-      <c r="R52" t="n">
+      <c r="S52" t="n">
         <v>360578</v>
       </c>
-      <c r="S52" t="n">
+      <c r="T52" t="n">
         <v>0.467077</v>
       </c>
-      <c r="T52" t="n">
+      <c r="U52" t="n">
         <v>-3.151492</v>
       </c>
-      <c r="U52" t="n">
+      <c r="V52" t="n">
         <v>-0.937912</v>
       </c>
-      <c r="V52" t="n">
+      <c r="W52" t="n">
         <v>-0.938017</v>
       </c>
-      <c r="W52" t="n">
+      <c r="X52" t="n">
         <v>1.160288</v>
       </c>
-      <c r="X52" t="n">
+      <c r="Y52" t="n">
         <v>0.741907</v>
       </c>
-      <c r="Y52" t="n">
+      <c r="Z52" t="n">
         <v>1.411498</v>
       </c>
-      <c r="Z52" t="n">
+      <c r="AA52" t="n">
         <v>0.973109</v>
       </c>
-      <c r="AA52" t="n">
+      <c r="AB52" t="n">
+        <v>4.461836</v>
+      </c>
+      <c r="AC52" t="n">
         <v>-0.101973</v>
       </c>
-      <c r="AB52" t="n">
+      <c r="AD52" t="n">
         <v>4.177803</v>
       </c>
-      <c r="AC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" t="n">
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="n">
         <v>-0</v>
       </c>
-      <c r="AE52" t="n">
+      <c r="AG52" t="n">
         <v>-0</v>
       </c>
-      <c r="AF52" t="n">
+      <c r="AH52" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG52" t="n">
+      <c r="AI52" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AH52" t="n">
+      <c r="AJ52" t="n">
         <v>0.13</v>
       </c>
-      <c r="AI52" t="n">
+      <c r="AK52" t="n">
         <v>0.16</v>
       </c>
     </row>
@@ -5994,96 +6288,102 @@
         <v>0.055131</v>
       </c>
       <c r="E53" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F53" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F53" t="n">
+      <c r="G53" t="n">
         <v>0.21</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>109.46142</v>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>107.19319</v>
       </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
         <v>5.5024</v>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>5.5018</v>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" t="n">
         <v>7137252</v>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" t="n">
         <v>2701735</v>
       </c>
-      <c r="M53" t="n">
+      <c r="N53" t="n">
         <v>4435517</v>
       </c>
-      <c r="N53" t="n">
+      <c r="O53" t="n">
         <v>4.2</v>
       </c>
-      <c r="O53" t="n">
+      <c r="P53" t="n">
         <v>2.7</v>
       </c>
-      <c r="P53" t="n">
+      <c r="Q53" t="n">
         <v>5.12</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="R53" t="n">
         <v>31.87</v>
       </c>
-      <c r="R53" t="n">
+      <c r="S53" t="n">
         <v>358234</v>
       </c>
-      <c r="S53" t="n">
+      <c r="T53" t="n">
         <v>0.201306</v>
       </c>
-      <c r="T53" t="n">
+      <c r="U53" t="n">
         <v>0.560793</v>
       </c>
-      <c r="U53" t="n">
+      <c r="V53" t="n">
         <v>3.160973</v>
       </c>
-      <c r="V53" t="n">
+      <c r="W53" t="n">
         <v>3.161329</v>
       </c>
-      <c r="W53" t="n">
+      <c r="X53" t="n">
         <v>1.899268</v>
       </c>
-      <c r="X53" t="n">
+      <c r="Y53" t="n">
         <v>3.241734</v>
       </c>
-      <c r="Y53" t="n">
+      <c r="Z53" t="n">
         <v>1.098529</v>
       </c>
-      <c r="Z53" t="n">
+      <c r="AA53" t="n">
         <v>-0.650067</v>
       </c>
-      <c r="AA53" t="n">
+      <c r="AB53" t="n">
+        <v>4.264385</v>
+      </c>
+      <c r="AC53" t="n">
         <v>-1.042167</v>
       </c>
-      <c r="AB53" t="n">
+      <c r="AD53" t="n">
         <v>3.897866</v>
       </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
       <c r="AE53" t="n">
         <v>0</v>
       </c>
       <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AG53" t="n">
+      <c r="AI53" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI53" t="n">
+      <c r="AJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -6101,96 +6401,102 @@
         <v>0.055131</v>
       </c>
       <c r="E54" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F54" t="n">
         <v>0.41</v>
       </c>
-      <c r="F54" t="n">
+      <c r="G54" t="n">
         <v>0.39</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>110.07661</v>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>103.78191</v>
       </c>
-      <c r="I54" t="n">
+      <c r="J54" t="n">
         <v>5.2301</v>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
         <v>5.2295</v>
       </c>
-      <c r="K54" t="n">
+      <c r="L54" t="n">
         <v>7130762</v>
       </c>
-      <c r="L54" t="n">
+      <c r="M54" t="n">
         <v>2654220</v>
       </c>
-      <c r="M54" t="n">
+      <c r="N54" t="n">
         <v>4476542</v>
       </c>
-      <c r="N54" t="n">
+      <c r="O54" t="n">
         <v>4.44</v>
       </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
         <v>2.87</v>
       </c>
-      <c r="P54" t="n">
+      <c r="Q54" t="n">
         <v>5.38</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="R54" t="n">
         <v>32.45</v>
       </c>
-      <c r="R54" t="n">
+      <c r="S54" t="n">
         <v>364367</v>
       </c>
-      <c r="S54" t="n">
+      <c r="T54" t="n">
         <v>0.562015</v>
       </c>
-      <c r="T54" t="n">
+      <c r="U54" t="n">
         <v>-3.182366</v>
       </c>
-      <c r="U54" t="n">
+      <c r="V54" t="n">
         <v>-4.94875</v>
       </c>
-      <c r="V54" t="n">
+      <c r="W54" t="n">
         <v>-4.949289</v>
       </c>
-      <c r="W54" t="n">
+      <c r="X54" t="n">
         <v>-0.090931</v>
       </c>
-      <c r="X54" t="n">
+      <c r="Y54" t="n">
         <v>-1.758685</v>
       </c>
-      <c r="Y54" t="n">
+      <c r="Z54" t="n">
         <v>0.92492</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="AA54" t="n">
         <v>1.712009</v>
       </c>
-      <c r="AA54" t="n">
+      <c r="AB54" t="n">
+        <v>4.441351</v>
+      </c>
+      <c r="AC54" t="n">
         <v>-0.903999</v>
       </c>
-      <c r="AB54" t="n">
+      <c r="AD54" t="n">
         <v>4.303068</v>
       </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>0</v>
-      </c>
       <c r="AE54" t="n">
         <v>0</v>
       </c>
       <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
         <v>0.24</v>
       </c>
-      <c r="AG54" t="n">
+      <c r="AI54" t="n">
         <v>0.17</v>
       </c>
-      <c r="AH54" t="n">
+      <c r="AJ54" t="n">
         <v>0.26</v>
       </c>
-      <c r="AI54" t="n">
+      <c r="AK54" t="n">
         <v>0.58</v>
       </c>
     </row>
@@ -6208,96 +6514,102 @@
         <v>0.055131</v>
       </c>
       <c r="E55" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F55" t="n">
         <v>-0.73</v>
       </c>
-      <c r="F55" t="n">
+      <c r="G55" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>110.77581</v>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>106.77083</v>
       </c>
-      <c r="I55" t="n">
+      <c r="J55" t="n">
         <v>5.1495</v>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>5.1489</v>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" t="n">
         <v>7157783</v>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" t="n">
         <v>2656484</v>
       </c>
-      <c r="M55" t="n">
+      <c r="N55" t="n">
         <v>4501299</v>
       </c>
-      <c r="N55" t="n">
+      <c r="O55" t="n">
         <v>4.64</v>
       </c>
-      <c r="O55" t="n">
+      <c r="P55" t="n">
         <v>3.07</v>
       </c>
-      <c r="P55" t="n">
+      <c r="Q55" t="n">
         <v>5.56</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="R55" t="n">
         <v>32.63</v>
       </c>
-      <c r="R55" t="n">
+      <c r="S55" t="n">
         <v>371074</v>
       </c>
-      <c r="S55" t="n">
+      <c r="T55" t="n">
         <v>0.635194</v>
       </c>
-      <c r="T55" t="n">
+      <c r="U55" t="n">
         <v>2.880001</v>
       </c>
-      <c r="U55" t="n">
+      <c r="V55" t="n">
         <v>-1.54108</v>
       </c>
-      <c r="V55" t="n">
+      <c r="W55" t="n">
         <v>-1.541256</v>
       </c>
-      <c r="W55" t="n">
+      <c r="X55" t="n">
         <v>0.378936</v>
       </c>
-      <c r="X55" t="n">
+      <c r="Y55" t="n">
         <v>0.085298</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="Z55" t="n">
         <v>0.553038</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="AA55" t="n">
         <v>1.840727</v>
       </c>
-      <c r="AA55" t="n">
+      <c r="AB55" t="n">
+        <v>3.812497</v>
+      </c>
+      <c r="AC55" t="n">
         <v>-2.659212</v>
       </c>
-      <c r="AB55" t="n">
+      <c r="AD55" t="n">
         <v>3.357475</v>
       </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
       <c r="AE55" t="n">
         <v>0</v>
       </c>
       <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
         <v>0.2</v>
       </c>
-      <c r="AG55" t="n">
+      <c r="AI55" t="n">
         <v>0.2</v>
       </c>
-      <c r="AH55" t="n">
+      <c r="AJ55" t="n">
         <v>0.18</v>
       </c>
-      <c r="AI55" t="n">
+      <c r="AK55" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -6315,96 +6627,102 @@
         <v>0.054777</v>
       </c>
       <c r="E56" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F56" t="n">
         <v>0.52</v>
       </c>
-      <c r="F56" t="n">
+      <c r="G56" t="n">
         <v>0.91</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>110.60765</v>
       </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
         <v>118.00063</v>
       </c>
-      <c r="I56" t="n">
+      <c r="J56" t="n">
         <v>5.2194</v>
       </c>
-      <c r="J56" t="n">
+      <c r="K56" t="n">
         <v>5.2188</v>
       </c>
-      <c r="K56" t="n">
+      <c r="L56" t="n">
         <v>7240557</v>
       </c>
-      <c r="L56" t="n">
+      <c r="M56" t="n">
         <v>2687535</v>
       </c>
-      <c r="M56" t="n">
+      <c r="N56" t="n">
         <v>4553022</v>
       </c>
-      <c r="N56" t="n">
+      <c r="O56" t="n">
         <v>4.52</v>
       </c>
-      <c r="O56" t="n">
+      <c r="P56" t="n">
         <v>3.06</v>
       </c>
-      <c r="P56" t="n">
+      <c r="Q56" t="n">
         <v>5.39</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="R56" t="n">
         <v>32.84</v>
       </c>
-      <c r="R56" t="n">
+      <c r="S56" t="n">
         <v>362002</v>
       </c>
-      <c r="S56" t="n">
+      <c r="T56" t="n">
         <v>-0.151802</v>
       </c>
-      <c r="T56" t="n">
+      <c r="U56" t="n">
         <v>10.517667</v>
       </c>
-      <c r="U56" t="n">
+      <c r="V56" t="n">
         <v>1.357413</v>
       </c>
-      <c r="V56" t="n">
+      <c r="W56" t="n">
         <v>1.357572</v>
       </c>
-      <c r="W56" t="n">
+      <c r="X56" t="n">
         <v>1.15642</v>
       </c>
-      <c r="X56" t="n">
+      <c r="Y56" t="n">
         <v>1.168876</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="Z56" t="n">
         <v>1.149068</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="AA56" t="n">
         <v>-2.444795</v>
       </c>
-      <c r="AA56" t="n">
+      <c r="AB56" t="n">
+        <v>4.142847</v>
+      </c>
+      <c r="AC56" t="n">
         <v>-1.819225</v>
       </c>
-      <c r="AB56" t="n">
+      <c r="AD56" t="n">
         <v>3.768807</v>
       </c>
-      <c r="AC56" t="n">
+      <c r="AE56" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD56" t="n">
+      <c r="AF56" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="AE56" t="n">
+      <c r="AG56" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="AF56" t="n">
+      <c r="AH56" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AG56" t="n">
+      <c r="AI56" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH56" t="n">
+      <c r="AJ56" t="n">
         <v>-0.17</v>
       </c>
-      <c r="AI56" t="n">
+      <c r="AK56" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -6422,96 +6740,102 @@
         <v>0.054223</v>
       </c>
       <c r="E57" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F57" t="n">
         <v>2.73</v>
       </c>
-      <c r="F57" t="n">
+      <c r="G57" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>110.90086</v>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>113.89942</v>
       </c>
-      <c r="I57" t="n">
+      <c r="J57" t="n">
         <v>4.9886</v>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
         <v>4.988</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
         <v>7259766</v>
       </c>
-      <c r="L57" t="n">
+      <c r="M57" t="n">
         <v>2685397</v>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
         <v>4574368</v>
       </c>
-      <c r="N57" t="n">
+      <c r="O57" t="n">
         <v>4.64</v>
       </c>
-      <c r="O57" t="n">
+      <c r="P57" t="n">
         <v>3.15</v>
       </c>
-      <c r="P57" t="n">
+      <c r="Q57" t="n">
         <v>5.51</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="R57" t="n">
         <v>33.36</v>
       </c>
-      <c r="R57" t="n">
+      <c r="S57" t="n">
         <v>366913</v>
       </c>
-      <c r="S57" t="n">
+      <c r="T57" t="n">
         <v>0.26509</v>
       </c>
-      <c r="T57" t="n">
+      <c r="U57" t="n">
         <v>-3.475583</v>
       </c>
-      <c r="U57" t="n">
+      <c r="V57" t="n">
         <v>-4.421964</v>
       </c>
-      <c r="V57" t="n">
+      <c r="W57" t="n">
         <v>-4.422473</v>
       </c>
-      <c r="W57" t="n">
+      <c r="X57" t="n">
         <v>0.265297</v>
       </c>
-      <c r="X57" t="n">
+      <c r="Y57" t="n">
         <v>-0.079552</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="Z57" t="n">
         <v>0.468831</v>
       </c>
-      <c r="Z57" t="n">
+      <c r="AA57" t="n">
         <v>1.356622</v>
       </c>
-      <c r="AA57" t="n">
+      <c r="AB57" t="n">
+        <v>4.39172</v>
+      </c>
+      <c r="AC57" t="n">
         <v>0.619623</v>
       </c>
-      <c r="AB57" t="n">
+      <c r="AD57" t="n">
         <v>4.109608</v>
       </c>
-      <c r="AC57" t="n">
+      <c r="AE57" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD57" t="n">
+      <c r="AF57" t="n">
         <v>-0.000554</v>
       </c>
-      <c r="AE57" t="n">
+      <c r="AG57" t="n">
         <v>-0.000554</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>0.09</v>
       </c>
       <c r="AH57" t="n">
         <v>0.12</v>
       </c>
       <c r="AI57" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AK57" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -6529,96 +6853,102 @@
         <v>0.0534</v>
       </c>
       <c r="E58" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F58" t="n">
         <v>0.84</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>0.65</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>110.93102</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>109.53002</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>5.0569</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>5.0563</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>7305306</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>2708154</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>4597152</v>
       </c>
-      <c r="N58" t="n">
+      <c r="O58" t="n">
         <v>4.74</v>
       </c>
-      <c r="O58" t="n">
+      <c r="P58" t="n">
         <v>3.25</v>
       </c>
-      <c r="P58" t="n">
+      <c r="Q58" t="n">
         <v>5.62</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="R58" t="n">
         <v>33.1</v>
       </c>
-      <c r="R58" t="n">
+      <c r="S58" t="n">
         <v>371137</v>
       </c>
-      <c r="S58" t="n">
+      <c r="T58" t="n">
         <v>0.027195</v>
       </c>
-      <c r="T58" t="n">
+      <c r="U58" t="n">
         <v>-3.836192</v>
       </c>
-      <c r="U58" t="n">
+      <c r="V58" t="n">
         <v>1.369122</v>
       </c>
-      <c r="V58" t="n">
+      <c r="W58" t="n">
         <v>1.369286</v>
       </c>
-      <c r="W58" t="n">
+      <c r="X58" t="n">
         <v>0.627293</v>
       </c>
-      <c r="X58" t="n">
+      <c r="Y58" t="n">
         <v>0.847435</v>
       </c>
-      <c r="Y58" t="n">
+      <c r="Z58" t="n">
         <v>0.49808</v>
       </c>
-      <c r="Z58" t="n">
+      <c r="AA58" t="n">
         <v>1.151227</v>
       </c>
-      <c r="AA58" t="n">
+      <c r="AB58" t="n">
+        <v>4.724907</v>
+      </c>
+      <c r="AC58" t="n">
         <v>1.964454</v>
       </c>
-      <c r="AB58" t="n">
+      <c r="AD58" t="n">
         <v>4.420848</v>
       </c>
-      <c r="AC58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD58" t="n">
+      <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="n">
         <v>-0.0008229999999999999</v>
       </c>
-      <c r="AE58" t="n">
+      <c r="AG58" t="n">
         <v>-0.0008229999999999999</v>
       </c>
-      <c r="AF58" t="n">
+      <c r="AH58" t="n">
         <v>0.1</v>
       </c>
-      <c r="AG58" t="n">
+      <c r="AI58" t="n">
         <v>0.1</v>
       </c>
-      <c r="AH58" t="n">
+      <c r="AJ58" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI58" t="n">
+      <c r="AK58" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -6636,96 +6966,102 @@
         <v>0.053028</v>
       </c>
       <c r="E59" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F59" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F59" t="n">
+      <c r="G59" t="n">
         <v>0.14</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>110.22154</v>
       </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
         <v>109.89427</v>
       </c>
-      <c r="I59" t="n">
+      <c r="J59" t="n">
         <v>5.1766</v>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
         <v>5.176</v>
       </c>
-      <c r="K59" t="n">
+      <c r="L59" t="n">
         <v>7353293</v>
       </c>
-      <c r="L59" t="n">
+      <c r="M59" t="n">
         <v>2750625</v>
       </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
         <v>4602668</v>
       </c>
-      <c r="N59" t="n">
+      <c r="O59" t="n">
         <v>4.58</v>
       </c>
-      <c r="O59" t="n">
+      <c r="P59" t="n">
         <v>3.18</v>
       </c>
-      <c r="P59" t="n">
+      <c r="Q59" t="n">
         <v>5.42</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="R59" t="n">
         <v>33.33</v>
       </c>
-      <c r="R59" t="n">
+      <c r="S59" t="n">
         <v>367558</v>
       </c>
-      <c r="S59" t="n">
+      <c r="T59" t="n">
         <v>-0.6395690000000001</v>
       </c>
-      <c r="T59" t="n">
+      <c r="U59" t="n">
         <v>0.332557</v>
       </c>
-      <c r="U59" t="n">
+      <c r="V59" t="n">
         <v>2.367063</v>
       </c>
-      <c r="V59" t="n">
+      <c r="W59" t="n">
         <v>2.367344</v>
       </c>
-      <c r="W59" t="n">
+      <c r="X59" t="n">
         <v>0.656879</v>
       </c>
-      <c r="X59" t="n">
+      <c r="Y59" t="n">
         <v>1.568264</v>
       </c>
-      <c r="Y59" t="n">
+      <c r="Z59" t="n">
         <v>0.119987</v>
       </c>
-      <c r="Z59" t="n">
+      <c r="AA59" t="n">
         <v>-0.964334</v>
       </c>
-      <c r="AA59" t="n">
+      <c r="AB59" t="n">
+        <v>4.641328</v>
+      </c>
+      <c r="AC59" t="n">
         <v>3.177699</v>
       </c>
-      <c r="AB59" t="n">
+      <c r="AD59" t="n">
         <v>4.327084</v>
       </c>
-      <c r="AC59" t="n">
+      <c r="AE59" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD59" t="n">
+      <c r="AF59" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AE59" t="n">
+      <c r="AG59" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AF59" t="n">
+      <c r="AH59" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AG59" t="n">
+      <c r="AI59" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AH59" t="n">
+      <c r="AJ59" t="n">
         <v>-0.2</v>
       </c>
-      <c r="AI59" t="n">
+      <c r="AK59" t="n">
         <v>0.23</v>
       </c>
     </row>
@@ -6743,88 +7079,94 @@
         <v>0.052531</v>
       </c>
       <c r="E60" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F60" t="n">
         <v>-1.16</v>
       </c>
-      <c r="F60" t="n">
+      <c r="G60" t="n">
         <v>-0.01</v>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="n">
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="n">
         <v>5.0773</v>
       </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
         <v>5.0767</v>
       </c>
-      <c r="K60" t="n">
+      <c r="L60" t="n">
         <v>7372243</v>
       </c>
-      <c r="L60" t="n">
+      <c r="M60" t="n">
         <v>2731513</v>
       </c>
-      <c r="M60" t="n">
+      <c r="N60" t="n">
         <v>4640730</v>
       </c>
-      <c r="N60" t="n">
+      <c r="O60" t="n">
         <v>4.88</v>
       </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
         <v>3.31</v>
       </c>
-      <c r="P60" t="n">
+      <c r="Q60" t="n">
         <v>5.81</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="R60" t="n">
         <v>32.08</v>
       </c>
-      <c r="R60" t="n">
+      <c r="S60" t="n">
         <v>369742</v>
       </c>
-      <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
-      <c r="U60" t="n">
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="n">
         <v>-1.918247</v>
       </c>
-      <c r="V60" t="n">
+      <c r="W60" t="n">
         <v>-1.91847</v>
       </c>
-      <c r="W60" t="n">
+      <c r="X60" t="n">
         <v>0.257708</v>
       </c>
-      <c r="X60" t="n">
+      <c r="Y60" t="n">
         <v>-0.694824</v>
       </c>
-      <c r="Y60" t="n">
+      <c r="Z60" t="n">
         <v>0.826955</v>
       </c>
-      <c r="Z60" t="n">
+      <c r="AA60" t="n">
         <v>0.5941920000000001</v>
       </c>
-      <c r="AA60" t="n">
+      <c r="AB60" t="n">
+        <v>4.443025</v>
+      </c>
+      <c r="AC60" t="n">
         <v>2.772183</v>
       </c>
-      <c r="AB60" t="n">
+      <c r="AD60" t="n">
         <v>4.098046</v>
       </c>
-      <c r="AC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" t="n">
+      <c r="AE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="AE60" t="n">
+      <c r="AG60" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="AF60" t="n">
+      <c r="AH60" t="n">
         <v>0.3</v>
       </c>
-      <c r="AG60" t="n">
+      <c r="AI60" t="n">
         <v>0.13</v>
       </c>
-      <c r="AH60" t="n">
+      <c r="AJ60" t="n">
         <v>0.39</v>
       </c>
-      <c r="AI60" t="n">
+      <c r="AK60" t="n">
         <v>-1.25</v>
       </c>
     </row>
@@ -6842,62 +7184,68 @@
         <v>0.051784</v>
       </c>
       <c r="E61" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="F61" t="n">
         <v>-0.22</v>
       </c>
-      <c r="F61" t="n">
+      <c r="G61" t="n">
         <v>-0.32</v>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="n">
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="n">
         <v>5.1816</v>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
         <v>5.181</v>
       </c>
-      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="n">
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="n">
         <v>372616</v>
       </c>
-      <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="n">
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="n">
         <v>2.054241</v>
       </c>
-      <c r="V61" t="n">
+      <c r="W61" t="n">
         <v>2.054484</v>
       </c>
-      <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="n">
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="n">
         <v>0.777299</v>
       </c>
-      <c r="AA61" t="n">
+      <c r="AB61" t="n">
+        <v>4.223453</v>
+      </c>
+      <c r="AC61" t="n">
         <v>2.178243</v>
       </c>
-      <c r="AB61" t="n">
+      <c r="AD61" t="n">
         <v>3.983297</v>
       </c>
-      <c r="AC61" t="n">
+      <c r="AE61" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD61" t="n">
+      <c r="AF61" t="n">
         <v>-0.0007470000000000001</v>
       </c>
-      <c r="AE61" t="n">
+      <c r="AG61" t="n">
         <v>-0.0007470000000000001</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -6916,13 +7264,13 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="n">
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="n">
         <v>5.0918</v>
       </c>
-      <c r="J62" t="n">
+      <c r="K62" t="n">
         <v>5.0912</v>
       </c>
-      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -6932,31 +7280,33 @@
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="n">
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="n">
         <v>-1.733055</v>
       </c>
-      <c r="V62" t="n">
+      <c r="W62" t="n">
         <v>-1.733256</v>
       </c>
-      <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr"/>
-      <c r="AC62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD62" t="n">
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="n">
         <v>-0.000124</v>
       </c>
-      <c r="AE62" t="n">
+      <c r="AG62" t="n">
         <v>-0.000124</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
-      <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -615,10 +615,10 @@
         <v>6.25</v>
       </c>
       <c r="C2" t="n">
-        <v>0.021664</v>
+        <v>0.021808</v>
       </c>
       <c r="D2" t="n">
-        <v>0.021664</v>
+        <v>0.021808</v>
       </c>
       <c r="E2" t="n">
         <v>1.16</v>
@@ -773,10 +773,10 @@
         <v>1.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.00258</v>
+        <v>0.002435</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.00258</v>
+        <v>0.002435</v>
       </c>
       <c r="AH3" t="n">
         <v>-0.01</v>
@@ -7266,10 +7266,10 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>5.0918</v>
+        <v>5.1696</v>
       </c>
       <c r="K62" t="n">
-        <v>5.0912</v>
+        <v>5.169</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -7282,10 +7282,10 @@
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="n">
-        <v>-1.733055</v>
+        <v>-0.231589</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.733256</v>
+        <v>-0.231616</v>
       </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -615,10 +615,10 @@
         <v>6.25</v>
       </c>
       <c r="C2" t="n">
-        <v>0.021808</v>
+        <v>0.021979</v>
       </c>
       <c r="D2" t="n">
-        <v>0.021808</v>
+        <v>0.021979</v>
       </c>
       <c r="E2" t="n">
         <v>1.16</v>
@@ -630,10 +630,10 @@
         <v>1.2</v>
       </c>
       <c r="H2" t="n">
-        <v>96.95313</v>
+        <v>96.96513</v>
       </c>
       <c r="I2" t="n">
-        <v>97.10569</v>
+        <v>97.10777</v>
       </c>
       <c r="J2" t="n">
         <v>5.4394</v>
@@ -707,10 +707,10 @@
         <v>1.16</v>
       </c>
       <c r="H3" t="n">
-        <v>97.47790999999999</v>
+        <v>97.48671</v>
       </c>
       <c r="I3" t="n">
-        <v>96.52863000000001</v>
+        <v>96.53041</v>
       </c>
       <c r="J3" t="n">
         <v>5.643</v>
@@ -743,10 +743,10 @@
         <v>367927</v>
       </c>
       <c r="T3" t="n">
-        <v>0.541272</v>
+        <v>0.537905</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.59426</v>
+        <v>-0.594556</v>
       </c>
       <c r="V3" t="n">
         <v>3.74306</v>
@@ -773,10 +773,10 @@
         <v>1.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.002435</v>
+        <v>0.002265</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.002435</v>
+        <v>0.002265</v>
       </c>
       <c r="AH3" t="n">
         <v>-0.01</v>
@@ -814,10 +814,10 @@
         <v>0.84</v>
       </c>
       <c r="H4" t="n">
-        <v>99.05295</v>
+        <v>99.05526</v>
       </c>
       <c r="I4" t="n">
-        <v>97.85433</v>
+        <v>97.85277000000001</v>
       </c>
       <c r="J4" t="n">
         <v>5.6199</v>
@@ -850,10 +850,10 @@
         <v>367772</v>
       </c>
       <c r="T4" t="n">
-        <v>1.615792</v>
+        <v>1.608989</v>
       </c>
       <c r="U4" t="n">
-        <v>1.373375</v>
+        <v>1.36989</v>
       </c>
       <c r="V4" t="n">
         <v>-0.409357</v>
@@ -921,10 +921,10 @@
         <v>0.73</v>
       </c>
       <c r="H5" t="n">
-        <v>99.36759000000001</v>
+        <v>99.37716</v>
       </c>
       <c r="I5" t="n">
-        <v>99.32245</v>
+        <v>99.32258</v>
       </c>
       <c r="J5" t="n">
         <v>5.5805</v>
@@ -957,10 +957,10 @@
         <v>362204</v>
       </c>
       <c r="T5" t="n">
-        <v>0.317648</v>
+        <v>0.32497</v>
       </c>
       <c r="U5" t="n">
-        <v>1.500312</v>
+        <v>1.502063</v>
       </c>
       <c r="V5" t="n">
         <v>-0.70108</v>
@@ -1028,10 +1028,10 @@
         <v>0.67</v>
       </c>
       <c r="H6" t="n">
-        <v>97.41759</v>
+        <v>97.4213</v>
       </c>
       <c r="I6" t="n">
-        <v>91.67452</v>
+        <v>91.67776000000001</v>
       </c>
       <c r="J6" t="n">
         <v>5.3574</v>
@@ -1064,10 +1064,10 @@
         <v>358398</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.96241</v>
+        <v>-1.968118</v>
       </c>
       <c r="U6" t="n">
-        <v>-7.700102</v>
+        <v>-7.696961</v>
       </c>
       <c r="V6" t="n">
         <v>-3.99785</v>
@@ -1135,10 +1135,10 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>98.48287000000001</v>
+        <v>98.4804</v>
       </c>
       <c r="I7" t="n">
-        <v>95.64045</v>
+        <v>95.63728999999999</v>
       </c>
       <c r="J7" t="n">
         <v>5.1394</v>
@@ -1171,10 +1171,10 @@
         <v>357740</v>
       </c>
       <c r="T7" t="n">
-        <v>1.093519</v>
+        <v>1.087134</v>
       </c>
       <c r="U7" t="n">
-        <v>4.326098</v>
+        <v>4.318965</v>
       </c>
       <c r="V7" t="n">
         <v>-4.069138</v>
@@ -1242,10 +1242,10 @@
         <v>1.71</v>
       </c>
       <c r="H8" t="n">
-        <v>99.54331000000001</v>
+        <v>99.54801999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>104.53224</v>
+        <v>104.53237</v>
       </c>
       <c r="J8" t="n">
         <v>4.7378</v>
@@ -1278,10 +1278,10 @@
         <v>353169</v>
       </c>
       <c r="T8" t="n">
-        <v>1.076776</v>
+        <v>1.084094</v>
       </c>
       <c r="U8" t="n">
-        <v>9.297102000000001</v>
+        <v>9.300848999999999</v>
       </c>
       <c r="V8" t="n">
         <v>-7.814142</v>
@@ -1349,10 +1349,10 @@
         <v>1.04</v>
       </c>
       <c r="H9" t="n">
-        <v>99.44726</v>
+        <v>99.44118</v>
       </c>
       <c r="I9" t="n">
-        <v>100.22451</v>
+        <v>100.22938</v>
       </c>
       <c r="J9" t="n">
         <v>4.9191</v>
@@ -1385,10 +1385,10 @@
         <v>345097</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.09649099999999999</v>
+        <v>-0.107325</v>
       </c>
       <c r="U9" t="n">
-        <v>-4.120958</v>
+        <v>-4.116419</v>
       </c>
       <c r="V9" t="n">
         <v>3.826671</v>
@@ -1456,10 +1456,10 @@
         <v>0.45</v>
       </c>
       <c r="H10" t="n">
-        <v>99.65249</v>
+        <v>99.6454</v>
       </c>
       <c r="I10" t="n">
-        <v>99.74639000000001</v>
+        <v>99.74383</v>
       </c>
       <c r="J10" t="n">
         <v>4.7289</v>
@@ -1492,10 +1492,10 @@
         <v>346415</v>
       </c>
       <c r="T10" t="n">
-        <v>0.206371</v>
+        <v>0.205368</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.477049</v>
+        <v>-0.484439</v>
       </c>
       <c r="V10" t="n">
         <v>-3.866561</v>
@@ -1563,10 +1563,10 @@
         <v>0.62</v>
       </c>
       <c r="H11" t="n">
-        <v>99.53077999999999</v>
+        <v>99.51048</v>
       </c>
       <c r="I11" t="n">
-        <v>99.32053000000001</v>
+        <v>99.31653</v>
       </c>
       <c r="J11" t="n">
         <v>5.238</v>
@@ -1599,10 +1599,10 @@
         <v>341958</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.122134</v>
+        <v>-0.1354</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.426943</v>
+        <v>-0.428397</v>
       </c>
       <c r="V11" t="n">
         <v>10.765717</v>
@@ -1670,10 +1670,10 @@
         <v>-0.6</v>
       </c>
       <c r="H12" t="n">
-        <v>101.43252</v>
+        <v>101.43172</v>
       </c>
       <c r="I12" t="n">
-        <v>103.95413</v>
+        <v>103.95991</v>
       </c>
       <c r="J12" t="n">
         <v>5.1884</v>
@@ -1706,10 +1706,10 @@
         <v>346403</v>
       </c>
       <c r="T12" t="n">
-        <v>1.910705</v>
+        <v>1.930691</v>
       </c>
       <c r="U12" t="n">
-        <v>4.665299</v>
+        <v>4.675335</v>
       </c>
       <c r="V12" t="n">
         <v>-0.946926</v>
@@ -1777,10 +1777,10 @@
         <v>-0.31</v>
       </c>
       <c r="H13" t="n">
-        <v>101.09886</v>
+        <v>101.10583</v>
       </c>
       <c r="I13" t="n">
-        <v>104.51426</v>
+        <v>104.51156</v>
       </c>
       <c r="J13" t="n">
         <v>5.179</v>
@@ -1813,10 +1813,10 @@
         <v>339664</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.328948</v>
+        <v>-0.32129</v>
       </c>
       <c r="U13" t="n">
-        <v>0.538824</v>
+        <v>0.530637</v>
       </c>
       <c r="V13" t="n">
         <v>-0.181173</v>
@@ -1890,10 +1890,10 @@
         <v>-0.32</v>
       </c>
       <c r="H14" t="n">
-        <v>101.15209</v>
+        <v>101.16034</v>
       </c>
       <c r="I14" t="n">
-        <v>101.19157</v>
+        <v>101.1889</v>
       </c>
       <c r="J14" t="n">
         <v>5.4066</v>
@@ -1926,10 +1926,10 @@
         <v>327580</v>
       </c>
       <c r="T14" t="n">
-        <v>0.052651</v>
+        <v>0.053914</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.179174</v>
+        <v>-3.179227</v>
       </c>
       <c r="V14" t="n">
         <v>4.394671</v>
@@ -2003,10 +2003,10 @@
         <v>0.47</v>
       </c>
       <c r="H15" t="n">
-        <v>101.43094</v>
+        <v>101.44171</v>
       </c>
       <c r="I15" t="n">
-        <v>100.07474</v>
+        <v>100.08177</v>
       </c>
       <c r="J15" t="n">
         <v>5.257</v>
@@ -2039,10 +2039,10 @@
         <v>325546</v>
       </c>
       <c r="T15" t="n">
-        <v>0.275674</v>
+        <v>0.278143</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.103679</v>
+        <v>-1.094122</v>
       </c>
       <c r="V15" t="n">
         <v>-2.766988</v>
@@ -2116,10 +2116,10 @@
         <v>0.38</v>
       </c>
       <c r="H16" t="n">
-        <v>100.7113</v>
+        <v>100.7146</v>
       </c>
       <c r="I16" t="n">
-        <v>99.15328</v>
+        <v>99.15031999999999</v>
       </c>
       <c r="J16" t="n">
         <v>5.2941</v>
@@ -2152,10 +2152,10 @@
         <v>331505</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.709488</v>
+        <v>-0.716776</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.920772</v>
+        <v>-0.930689</v>
       </c>
       <c r="V16" t="n">
         <v>0.705726</v>
@@ -2229,10 +2229,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>100.58566</v>
+        <v>100.58818</v>
       </c>
       <c r="I17" t="n">
-        <v>99.97338999999999</v>
+        <v>99.97037</v>
       </c>
       <c r="J17" t="n">
         <v>5.2177</v>
@@ -2265,10 +2265,10 @@
         <v>324703</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.124753</v>
+        <v>-0.125523</v>
       </c>
       <c r="U17" t="n">
-        <v>0.827113</v>
+        <v>0.827078</v>
       </c>
       <c r="V17" t="n">
         <v>-1.443116</v>
@@ -2342,10 +2342,10 @@
         <v>0.46</v>
       </c>
       <c r="H18" t="n">
-        <v>100.10937</v>
+        <v>100.10988</v>
       </c>
       <c r="I18" t="n">
-        <v>95.09372999999999</v>
+        <v>95.09953</v>
       </c>
       <c r="J18" t="n">
         <v>5.0993</v>
@@ -2378,10 +2378,10 @@
         <v>331122</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.473517</v>
+        <v>-0.475503</v>
       </c>
       <c r="U18" t="n">
-        <v>-4.880959</v>
+        <v>-4.872284</v>
       </c>
       <c r="V18" t="n">
         <v>-2.269199</v>
@@ -2455,10 +2455,10 @@
         <v>0.77</v>
       </c>
       <c r="H19" t="n">
-        <v>103.08344</v>
+        <v>103.07987</v>
       </c>
       <c r="I19" t="n">
-        <v>98.65015</v>
+        <v>98.64798</v>
       </c>
       <c r="J19" t="n">
         <v>5.2078</v>
@@ -2491,10 +2491,10 @@
         <v>328098</v>
       </c>
       <c r="T19" t="n">
-        <v>2.970821</v>
+        <v>2.96673</v>
       </c>
       <c r="U19" t="n">
-        <v>3.73991</v>
+        <v>3.731301</v>
       </c>
       <c r="V19" t="n">
         <v>2.127743</v>
@@ -2568,10 +2568,10 @@
         <v>0.64</v>
       </c>
       <c r="H20" t="n">
-        <v>103.08526</v>
+        <v>103.08494</v>
       </c>
       <c r="I20" t="n">
-        <v>110.62045</v>
+        <v>110.61922</v>
       </c>
       <c r="J20" t="n">
         <v>5.0804</v>
@@ -2604,10 +2604,10 @@
         <v>341158</v>
       </c>
       <c r="T20" t="n">
-        <v>0.001766</v>
+        <v>0.004919</v>
       </c>
       <c r="U20" t="n">
-        <v>12.134092</v>
+        <v>12.135312</v>
       </c>
       <c r="V20" t="n">
         <v>-2.446331</v>
@@ -2681,10 +2681,10 @@
         <v>0.53</v>
       </c>
       <c r="H21" t="n">
-        <v>103.96006</v>
+        <v>103.93573</v>
       </c>
       <c r="I21" t="n">
-        <v>104.03539</v>
+        <v>104.04095</v>
       </c>
       <c r="J21" t="n">
         <v>5.0007</v>
@@ -2717,10 +2717,10 @@
         <v>345725</v>
       </c>
       <c r="T21" t="n">
-        <v>0.848618</v>
+        <v>0.825329</v>
       </c>
       <c r="U21" t="n">
-        <v>-5.952841</v>
+        <v>-5.946769</v>
       </c>
       <c r="V21" t="n">
         <v>-1.568774</v>
@@ -2794,10 +2794,10 @@
         <v>0.36</v>
       </c>
       <c r="H22" t="n">
-        <v>102.40467</v>
+        <v>102.42973</v>
       </c>
       <c r="I22" t="n">
-        <v>102.71665</v>
+        <v>102.71375</v>
       </c>
       <c r="J22" t="n">
         <v>5.0959</v>
@@ -2830,10 +2830,10 @@
         <v>343489</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.496142</v>
+        <v>-1.448972</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.267588</v>
+        <v>-1.275652</v>
       </c>
       <c r="V22" t="n">
         <v>1.903733</v>
@@ -2907,10 +2907,10 @@
         <v>-0.1</v>
       </c>
       <c r="H23" t="n">
-        <v>102.4398</v>
+        <v>102.39935</v>
       </c>
       <c r="I23" t="n">
-        <v>102.285</v>
+        <v>102.28352</v>
       </c>
       <c r="J23" t="n">
         <v>4.8192</v>
@@ -2943,10 +2943,10 @@
         <v>343620</v>
       </c>
       <c r="T23" t="n">
-        <v>0.034305</v>
+        <v>-0.029659</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.420234</v>
+        <v>-0.418863</v>
       </c>
       <c r="V23" t="n">
         <v>-5.429855</v>
@@ -3020,10 +3020,10 @@
         <v>-0.09</v>
       </c>
       <c r="H24" t="n">
-        <v>102.89895</v>
+        <v>102.90686</v>
       </c>
       <c r="I24" t="n">
-        <v>105.33914</v>
+        <v>105.34474</v>
       </c>
       <c r="J24" t="n">
         <v>4.7415</v>
@@ -3056,10 +3056,10 @@
         <v>345476</v>
       </c>
       <c r="T24" t="n">
-        <v>0.448214</v>
+        <v>0.495618</v>
       </c>
       <c r="U24" t="n">
-        <v>2.985912</v>
+        <v>2.992877</v>
       </c>
       <c r="V24" t="n">
         <v>-1.612301</v>
@@ -3133,10 +3133,10 @@
         <v>0.2</v>
       </c>
       <c r="H25" t="n">
-        <v>102.48797</v>
+        <v>102.50239</v>
       </c>
       <c r="I25" t="n">
-        <v>106.05945</v>
+        <v>106.05687</v>
       </c>
       <c r="J25" t="n">
         <v>4.9219</v>
@@ -3169,10 +3169,10 @@
         <v>344177</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.399402</v>
+        <v>-0.393045</v>
       </c>
       <c r="U25" t="n">
-        <v>0.683801</v>
+        <v>0.676</v>
       </c>
       <c r="V25" t="n">
         <v>3.804703</v>
@@ -3246,10 +3246,10 @@
         <v>0.11</v>
       </c>
       <c r="H26" t="n">
-        <v>102.50227</v>
+        <v>102.5153</v>
       </c>
       <c r="I26" t="n">
-        <v>101.76242</v>
+        <v>101.75897</v>
       </c>
       <c r="J26" t="n">
         <v>5.0076</v>
@@ -3282,10 +3282,10 @@
         <v>340324</v>
       </c>
       <c r="T26" t="n">
-        <v>0.013953</v>
+        <v>0.012595</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.05153</v>
+        <v>-4.052448</v>
       </c>
       <c r="V26" t="n">
         <v>1.741198</v>
@@ -3359,10 +3359,10 @@
         <v>0.12</v>
       </c>
       <c r="H27" t="n">
-        <v>102.83037</v>
+        <v>102.83959</v>
       </c>
       <c r="I27" t="n">
-        <v>101.92849</v>
+        <v>101.9338</v>
       </c>
       <c r="J27" t="n">
         <v>5.0575</v>
@@ -3395,10 +3395,10 @@
         <v>340247</v>
       </c>
       <c r="T27" t="n">
-        <v>0.32009</v>
+        <v>0.316333</v>
       </c>
       <c r="U27" t="n">
-        <v>0.163194</v>
+        <v>0.171808</v>
       </c>
       <c r="V27" t="n">
         <v>0.996485</v>
@@ -3472,10 +3472,10 @@
         <v>0.1</v>
       </c>
       <c r="H28" t="n">
-        <v>103.58799</v>
+        <v>103.59456</v>
       </c>
       <c r="I28" t="n">
-        <v>101.68208</v>
+        <v>101.68042</v>
       </c>
       <c r="J28" t="n">
         <v>4.9355</v>
@@ -3508,10 +3508,10 @@
         <v>348406</v>
       </c>
       <c r="T28" t="n">
-        <v>0.7367669999999999</v>
+        <v>0.734124</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.241748</v>
+        <v>-0.248573</v>
       </c>
       <c r="V28" t="n">
         <v>-2.412259</v>
@@ -3585,10 +3585,10 @@
         <v>0.55</v>
       </c>
       <c r="H29" t="n">
-        <v>104.88262</v>
+        <v>104.88818</v>
       </c>
       <c r="I29" t="n">
-        <v>101.68652</v>
+        <v>101.68469</v>
       </c>
       <c r="J29" t="n">
         <v>4.8413</v>
@@ -3621,10 +3621,10 @@
         <v>355034</v>
       </c>
       <c r="T29" t="n">
-        <v>1.249788</v>
+        <v>1.248734</v>
       </c>
       <c r="U29" t="n">
-        <v>0.004367</v>
+        <v>0.004199</v>
       </c>
       <c r="V29" t="n">
         <v>-1.908621</v>
@@ -3698,10 +3698,10 @@
         <v>0.57</v>
       </c>
       <c r="H30" t="n">
-        <v>104.47589</v>
+        <v>104.473</v>
       </c>
       <c r="I30" t="n">
-        <v>99.29136</v>
+        <v>99.29718</v>
       </c>
       <c r="J30" t="n">
         <v>4.9535</v>
@@ -3734,10 +3734,10 @@
         <v>355066</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.387795</v>
+        <v>-0.395831</v>
       </c>
       <c r="U30" t="n">
-        <v>-2.355435</v>
+        <v>-2.347954</v>
       </c>
       <c r="V30" t="n">
         <v>2.317559</v>
@@ -3811,10 +3811,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>104.67291</v>
+        <v>104.65885</v>
       </c>
       <c r="I31" t="n">
-        <v>102.15158</v>
+        <v>102.15036</v>
       </c>
       <c r="J31" t="n">
         <v>4.9833</v>
@@ -3847,10 +3847,10 @@
         <v>352705</v>
       </c>
       <c r="T31" t="n">
-        <v>0.188579</v>
+        <v>0.177893</v>
       </c>
       <c r="U31" t="n">
-        <v>2.880633</v>
+        <v>2.873375</v>
       </c>
       <c r="V31" t="n">
         <v>0.601595</v>
@@ -3924,10 +3924,10 @@
         <v>0.19</v>
       </c>
       <c r="H32" t="n">
-        <v>104.68779</v>
+        <v>104.6738</v>
       </c>
       <c r="I32" t="n">
-        <v>109.57244</v>
+        <v>109.56901</v>
       </c>
       <c r="J32" t="n">
         <v>4.9962</v>
@@ -3960,10 +3960,10 @@
         <v>355008</v>
       </c>
       <c r="T32" t="n">
-        <v>0.014216</v>
+        <v>0.014285</v>
       </c>
       <c r="U32" t="n">
-        <v>7.264557</v>
+        <v>7.262481</v>
       </c>
       <c r="V32" t="n">
         <v>0.258865</v>
@@ -4037,10 +4037,10 @@
         <v>0.37</v>
       </c>
       <c r="H33" t="n">
-        <v>104.6751</v>
+        <v>104.62771</v>
       </c>
       <c r="I33" t="n">
-        <v>109.25226</v>
+        <v>109.2572</v>
       </c>
       <c r="J33" t="n">
         <v>5.1718</v>
@@ -4073,10 +4073,10 @@
         <v>351599</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.012122</v>
+        <v>-0.044032</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.292209</v>
+        <v>-0.284579</v>
       </c>
       <c r="V33" t="n">
         <v>3.514671</v>
@@ -4150,10 +4150,10 @@
         <v>0.46</v>
       </c>
       <c r="H34" t="n">
-        <v>105.5521</v>
+        <v>105.60427</v>
       </c>
       <c r="I34" t="n">
-        <v>104.71219</v>
+        <v>104.71213</v>
       </c>
       <c r="J34" t="n">
         <v>5.2416</v>
@@ -4186,10 +4186,10 @@
         <v>355560</v>
       </c>
       <c r="T34" t="n">
-        <v>0.837831</v>
+        <v>0.9333669999999999</v>
       </c>
       <c r="U34" t="n">
-        <v>-4.155585</v>
+        <v>-4.159973</v>
       </c>
       <c r="V34" t="n">
         <v>1.349627</v>
@@ -4263,10 +4263,10 @@
         <v>0.25</v>
       </c>
       <c r="H35" t="n">
-        <v>106.65779</v>
+        <v>106.5891</v>
       </c>
       <c r="I35" t="n">
-        <v>105.87342</v>
+        <v>105.86915</v>
       </c>
       <c r="J35" t="n">
         <v>5.5589</v>
@@ -4299,10 +4299,10 @@
         <v>357827</v>
       </c>
       <c r="T35" t="n">
-        <v>1.04753</v>
+        <v>0.932566</v>
       </c>
       <c r="U35" t="n">
-        <v>1.108973</v>
+        <v>1.104953</v>
       </c>
       <c r="V35" t="n">
         <v>6.053495</v>
@@ -4376,10 +4376,10 @@
         <v>0.26</v>
       </c>
       <c r="H36" t="n">
-        <v>107.01873</v>
+        <v>107.06237</v>
       </c>
       <c r="I36" t="n">
-        <v>111.50432</v>
+        <v>111.509</v>
       </c>
       <c r="J36" t="n">
         <v>5.6621</v>
@@ -4412,10 +4412,10 @@
         <v>363282</v>
       </c>
       <c r="T36" t="n">
-        <v>0.338409</v>
+        <v>0.444014</v>
       </c>
       <c r="U36" t="n">
-        <v>5.318521</v>
+        <v>5.327189</v>
       </c>
       <c r="V36" t="n">
         <v>1.856482</v>
@@ -4489,10 +4489,10 @@
         <v>-0.14</v>
       </c>
       <c r="H37" t="n">
-        <v>107.16697</v>
+        <v>107.19174</v>
       </c>
       <c r="I37" t="n">
-        <v>110.06264</v>
+        <v>110.06254</v>
       </c>
       <c r="J37" t="n">
         <v>5.6562</v>
@@ -4525,10 +4525,10 @@
         <v>369214</v>
       </c>
       <c r="T37" t="n">
-        <v>0.138518</v>
+        <v>0.120836</v>
       </c>
       <c r="U37" t="n">
-        <v>-1.292936</v>
+        <v>-1.297169</v>
       </c>
       <c r="V37" t="n">
         <v>-0.104202</v>
@@ -4602,10 +4602,10 @@
         <v>0.48</v>
       </c>
       <c r="H38" t="n">
-        <v>108.02415</v>
+        <v>108.04382</v>
       </c>
       <c r="I38" t="n">
-        <v>107.08272</v>
+        <v>107.07852</v>
       </c>
       <c r="J38" t="n">
         <v>5.4481</v>
@@ -4638,10 +4638,10 @@
         <v>372016</v>
       </c>
       <c r="T38" t="n">
-        <v>0.799855</v>
+        <v>0.794912</v>
       </c>
       <c r="U38" t="n">
-        <v>-2.707476</v>
+        <v>-2.711204</v>
       </c>
       <c r="V38" t="n">
         <v>-3.679149</v>
@@ -4715,10 +4715,10 @@
         <v>0.61</v>
       </c>
       <c r="H39" t="n">
-        <v>108.23273</v>
+        <v>108.2446</v>
       </c>
       <c r="I39" t="n">
-        <v>109.17883</v>
+        <v>109.18379</v>
       </c>
       <c r="J39" t="n">
         <v>5.7779</v>
@@ -4751,10 +4751,10 @@
         <v>366096</v>
       </c>
       <c r="T39" t="n">
-        <v>0.193086</v>
+        <v>0.185832</v>
       </c>
       <c r="U39" t="n">
-        <v>1.957468</v>
+        <v>1.966099</v>
       </c>
       <c r="V39" t="n">
         <v>6.053487</v>
@@ -4828,10 +4828,10 @@
         <v>0.33</v>
       </c>
       <c r="H40" t="n">
-        <v>107.99539</v>
+        <v>108.00109</v>
       </c>
       <c r="I40" t="n">
-        <v>105.48993</v>
+        <v>105.49006</v>
       </c>
       <c r="J40" t="n">
         <v>6.0535</v>
@@ -4864,10 +4864,10 @@
         <v>363003</v>
       </c>
       <c r="T40" t="n">
-        <v>-0.219287</v>
+        <v>-0.224963</v>
       </c>
       <c r="U40" t="n">
-        <v>-3.378769</v>
+        <v>-3.383039</v>
       </c>
       <c r="V40" t="n">
         <v>4.769899</v>
@@ -4941,10 +4941,10 @@
         <v>0.48</v>
       </c>
       <c r="H41" t="n">
-        <v>107.3722</v>
+        <v>107.37012</v>
       </c>
       <c r="I41" t="n">
-        <v>104.15749</v>
+        <v>104.15552</v>
       </c>
       <c r="J41" t="n">
         <v>6.1923</v>
@@ -4977,10 +4977,10 @@
         <v>329730</v>
       </c>
       <c r="T41" t="n">
-        <v>-0.577052</v>
+        <v>-0.584226</v>
       </c>
       <c r="U41" t="n">
-        <v>-1.263097</v>
+        <v>-1.265086</v>
       </c>
       <c r="V41" t="n">
         <v>2.292888</v>
@@ -5054,10 +5054,10 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>108.10202</v>
+        <v>108.09524</v>
       </c>
       <c r="I42" t="n">
-        <v>102.62361</v>
+        <v>102.62949</v>
       </c>
       <c r="J42" t="n">
         <v>5.8301</v>
@@ -5090,10 +5090,10 @@
         <v>328303</v>
       </c>
       <c r="T42" t="n">
-        <v>0.67971</v>
+        <v>0.675346</v>
       </c>
       <c r="U42" t="n">
-        <v>-1.472655</v>
+        <v>-1.465146</v>
       </c>
       <c r="V42" t="n">
         <v>-5.8492</v>
@@ -5167,10 +5167,10 @@
         <v>1.48</v>
       </c>
       <c r="H43" t="n">
-        <v>108.64347</v>
+        <v>108.62006</v>
       </c>
       <c r="I43" t="n">
-        <v>106.82695</v>
+        <v>106.82599</v>
       </c>
       <c r="J43" t="n">
         <v>5.8488</v>
@@ -5203,10 +5203,10 @@
         <v>332508</v>
       </c>
       <c r="T43" t="n">
-        <v>0.500869</v>
+        <v>0.485516</v>
       </c>
       <c r="U43" t="n">
-        <v>4.09588</v>
+        <v>4.088981</v>
       </c>
       <c r="V43" t="n">
         <v>0.320749</v>
@@ -5280,10 +5280,10 @@
         <v>0.51</v>
       </c>
       <c r="H44" t="n">
-        <v>110.0586</v>
+        <v>110.03287</v>
       </c>
       <c r="I44" t="n">
-        <v>114.02633</v>
+        <v>114.02067</v>
       </c>
       <c r="J44" t="n">
         <v>5.7422</v>
@@ -5316,10 +5316,10 @@
         <v>336157</v>
       </c>
       <c r="T44" t="n">
-        <v>1.302545</v>
+        <v>1.30069</v>
       </c>
       <c r="U44" t="n">
-        <v>6.739292</v>
+        <v>6.734953</v>
       </c>
       <c r="V44" t="n">
         <v>-1.822596</v>
@@ -5393,10 +5393,10 @@
         <v>0.48</v>
       </c>
       <c r="H45" t="n">
-        <v>109.59971</v>
+        <v>109.52766</v>
       </c>
       <c r="I45" t="n">
-        <v>112.58856</v>
+        <v>112.59512</v>
       </c>
       <c r="J45" t="n">
         <v>5.6608</v>
@@ -5429,10 +5429,10 @@
         <v>340789</v>
       </c>
       <c r="T45" t="n">
-        <v>-0.416951</v>
+        <v>-0.459145</v>
       </c>
       <c r="U45" t="n">
-        <v>-1.260911</v>
+        <v>-1.250256</v>
       </c>
       <c r="V45" t="n">
         <v>-1.417575</v>
@@ -5506,10 +5506,10 @@
         <v>0.35</v>
       </c>
       <c r="H46" t="n">
-        <v>108.80425</v>
+        <v>108.8862</v>
       </c>
       <c r="I46" t="n">
-        <v>108.55662</v>
+        <v>108.55704</v>
       </c>
       <c r="J46" t="n">
         <v>5.7087</v>
@@ -5542,10 +5542,10 @@
         <v>341459</v>
       </c>
       <c r="T46" t="n">
-        <v>-0.725787</v>
+        <v>-0.58566</v>
       </c>
       <c r="U46" t="n">
-        <v>-3.581128</v>
+        <v>-3.586372</v>
       </c>
       <c r="V46" t="n">
         <v>0.84617</v>
@@ -5619,10 +5619,10 @@
         <v>0.23</v>
       </c>
       <c r="H47" t="n">
-        <v>108.90168</v>
+        <v>108.80376</v>
       </c>
       <c r="I47" t="n">
-        <v>107.36878</v>
+        <v>107.36219</v>
       </c>
       <c r="J47" t="n">
         <v>5.4571</v>
@@ -5655,10 +5655,10 @@
         <v>344440</v>
       </c>
       <c r="T47" t="n">
-        <v>0.089546</v>
+        <v>-0.075712</v>
       </c>
       <c r="U47" t="n">
-        <v>-1.094212</v>
+        <v>-1.100666</v>
       </c>
       <c r="V47" t="n">
         <v>-4.407308</v>
@@ -5732,10 +5732,10 @@
         <v>0.21</v>
       </c>
       <c r="H48" t="n">
-        <v>108.39998</v>
+        <v>108.49869</v>
       </c>
       <c r="I48" t="n">
-        <v>113.10359</v>
+        <v>113.10928</v>
       </c>
       <c r="J48" t="n">
         <v>5.6021</v>
@@ -5768,10 +5768,10 @@
         <v>345111</v>
       </c>
       <c r="T48" t="n">
-        <v>-0.460691</v>
+        <v>-0.280386</v>
       </c>
       <c r="U48" t="n">
-        <v>5.341227</v>
+        <v>5.352993</v>
       </c>
       <c r="V48" t="n">
         <v>2.657089</v>
@@ -5845,10 +5845,10 @@
         <v>-0.21</v>
       </c>
       <c r="H49" t="n">
-        <v>108.79892</v>
+        <v>108.82893</v>
       </c>
       <c r="I49" t="n">
-        <v>110.38013</v>
+        <v>110.38054</v>
       </c>
       <c r="J49" t="n">
         <v>5.4264</v>
@@ -5881,10 +5881,10 @@
         <v>350767</v>
       </c>
       <c r="T49" t="n">
-        <v>0.368026</v>
+        <v>0.304372</v>
       </c>
       <c r="U49" t="n">
-        <v>-2.407934</v>
+        <v>-2.412481</v>
       </c>
       <c r="V49" t="n">
         <v>-3.136324</v>
@@ -5958,10 +5958,10 @@
         <v>0.52</v>
       </c>
       <c r="H50" t="n">
-        <v>108.7209</v>
+        <v>108.73548</v>
       </c>
       <c r="I50" t="n">
-        <v>109.48882</v>
+        <v>109.48375</v>
       </c>
       <c r="J50" t="n">
         <v>5.3186</v>
@@ -5994,10 +5994,10 @@
         <v>356582</v>
       </c>
       <c r="T50" t="n">
-        <v>-0.07171</v>
+        <v>-0.085869</v>
       </c>
       <c r="U50" t="n">
-        <v>-0.807491</v>
+        <v>-0.812453</v>
       </c>
       <c r="V50" t="n">
         <v>-1.986584</v>
@@ -6071,10 +6071,10 @@
         <v>0.03</v>
       </c>
       <c r="H51" t="n">
-        <v>108.73364</v>
+        <v>108.75326</v>
       </c>
       <c r="I51" t="n">
-        <v>110.06407</v>
+        <v>110.07682</v>
       </c>
       <c r="J51" t="n">
         <v>5.3843</v>
@@ -6107,10 +6107,10 @@
         <v>357103</v>
       </c>
       <c r="T51" t="n">
-        <v>0.011718</v>
+        <v>0.016352</v>
       </c>
       <c r="U51" t="n">
-        <v>0.525396</v>
+        <v>0.541697</v>
       </c>
       <c r="V51" t="n">
         <v>1.235287</v>
@@ -6184,10 +6184,10 @@
         <v>0.03</v>
       </c>
       <c r="H52" t="n">
-        <v>109.24151</v>
+        <v>109.25005</v>
       </c>
       <c r="I52" t="n">
-        <v>106.59541</v>
+        <v>106.59892</v>
       </c>
       <c r="J52" t="n">
         <v>5.3338</v>
@@ -6220,10 +6220,10 @@
         <v>360578</v>
       </c>
       <c r="T52" t="n">
-        <v>0.467077</v>
+        <v>0.456805</v>
       </c>
       <c r="U52" t="n">
-        <v>-3.151492</v>
+        <v>-3.159521</v>
       </c>
       <c r="V52" t="n">
         <v>-0.937912</v>
@@ -6297,10 +6297,10 @@
         <v>0.21</v>
       </c>
       <c r="H53" t="n">
-        <v>109.46142</v>
+        <v>109.4528</v>
       </c>
       <c r="I53" t="n">
-        <v>107.19319</v>
+        <v>107.18417</v>
       </c>
       <c r="J53" t="n">
         <v>5.5024</v>
@@ -6333,10 +6333,10 @@
         <v>358234</v>
       </c>
       <c r="T53" t="n">
-        <v>0.201306</v>
+        <v>0.185583</v>
       </c>
       <c r="U53" t="n">
-        <v>0.560793</v>
+        <v>0.549021</v>
       </c>
       <c r="V53" t="n">
         <v>3.160973</v>
@@ -6410,10 +6410,10 @@
         <v>0.39</v>
       </c>
       <c r="H54" t="n">
-        <v>110.07661</v>
+        <v>110.04992</v>
       </c>
       <c r="I54" t="n">
-        <v>103.78191</v>
+        <v>103.77761</v>
       </c>
       <c r="J54" t="n">
         <v>5.2301</v>
@@ -6446,10 +6446,10 @@
         <v>364367</v>
       </c>
       <c r="T54" t="n">
-        <v>0.562015</v>
+        <v>0.54555</v>
       </c>
       <c r="U54" t="n">
-        <v>-3.182366</v>
+        <v>-3.178231</v>
       </c>
       <c r="V54" t="n">
         <v>-4.94875</v>
@@ -6523,10 +6523,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="H55" t="n">
-        <v>110.77581</v>
+        <v>110.7366</v>
       </c>
       <c r="I55" t="n">
-        <v>106.77083</v>
+        <v>106.76075</v>
       </c>
       <c r="J55" t="n">
         <v>5.1495</v>
@@ -6559,10 +6559,10 @@
         <v>371074</v>
       </c>
       <c r="T55" t="n">
-        <v>0.635194</v>
+        <v>0.6239710000000001</v>
       </c>
       <c r="U55" t="n">
-        <v>2.880001</v>
+        <v>2.874551</v>
       </c>
       <c r="V55" t="n">
         <v>-1.54108</v>
@@ -6636,10 +6636,10 @@
         <v>0.91</v>
       </c>
       <c r="H56" t="n">
-        <v>110.60765</v>
+        <v>110.58808</v>
       </c>
       <c r="I56" t="n">
-        <v>118.00063</v>
+        <v>118.01719</v>
       </c>
       <c r="J56" t="n">
         <v>5.2194</v>
@@ -6672,10 +6672,10 @@
         <v>362002</v>
       </c>
       <c r="T56" t="n">
-        <v>-0.151802</v>
+        <v>-0.13412</v>
       </c>
       <c r="U56" t="n">
-        <v>10.517667</v>
+        <v>10.543613</v>
       </c>
       <c r="V56" t="n">
         <v>1.357413</v>
@@ -6749,10 +6749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>110.90086</v>
+        <v>110.90009</v>
       </c>
       <c r="I57" t="n">
-        <v>113.89942</v>
+        <v>113.99295</v>
       </c>
       <c r="J57" t="n">
         <v>4.9886</v>
@@ -6785,10 +6785,10 @@
         <v>366913</v>
       </c>
       <c r="T57" t="n">
-        <v>0.26509</v>
+        <v>0.282137</v>
       </c>
       <c r="U57" t="n">
-        <v>-3.475583</v>
+        <v>-3.409876</v>
       </c>
       <c r="V57" t="n">
         <v>-4.421964</v>
@@ -6862,10 +6862,10 @@
         <v>0.65</v>
       </c>
       <c r="H58" t="n">
-        <v>110.93102</v>
+        <v>111.13846</v>
       </c>
       <c r="I58" t="n">
-        <v>109.53002</v>
+        <v>109.65479</v>
       </c>
       <c r="J58" t="n">
         <v>5.0569</v>
@@ -6898,10 +6898,10 @@
         <v>371137</v>
       </c>
       <c r="T58" t="n">
-        <v>0.027195</v>
+        <v>0.214941</v>
       </c>
       <c r="U58" t="n">
-        <v>-3.836192</v>
+        <v>-3.805639</v>
       </c>
       <c r="V58" t="n">
         <v>1.369122</v>
@@ -6975,10 +6975,10 @@
         <v>0.14</v>
       </c>
       <c r="H59" t="n">
-        <v>110.22154</v>
+        <v>110.15775</v>
       </c>
       <c r="I59" t="n">
-        <v>109.89427</v>
+        <v>109.94156</v>
       </c>
       <c r="J59" t="n">
         <v>5.1766</v>
@@ -7011,10 +7011,10 @@
         <v>367558</v>
       </c>
       <c r="T59" t="n">
-        <v>-0.6395690000000001</v>
+        <v>-0.882422</v>
       </c>
       <c r="U59" t="n">
-        <v>0.332557</v>
+        <v>0.261521</v>
       </c>
       <c r="V59" t="n">
         <v>2.367063</v>
@@ -7087,8 +7087,12 @@
       <c r="G60" t="n">
         <v>-0.01</v>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+      <c r="H60" t="n">
+        <v>109.91611</v>
+      </c>
+      <c r="I60" t="n">
+        <v>114.40189</v>
+      </c>
       <c r="J60" t="n">
         <v>5.0773</v>
       </c>
@@ -7119,8 +7123,12 @@
       <c r="S60" t="n">
         <v>369742</v>
       </c>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
+      <c r="T60" t="n">
+        <v>-0.219358</v>
+      </c>
+      <c r="U60" t="n">
+        <v>4.057001</v>
+      </c>
       <c r="V60" t="n">
         <v>-1.918247</v>
       </c>
@@ -7266,10 +7274,10 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>5.1696</v>
+        <v>5.149</v>
       </c>
       <c r="K62" t="n">
-        <v>5.169</v>
+        <v>5.1484</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -7282,10 +7290,10 @@
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="n">
-        <v>-0.231589</v>
+        <v>-0.629149</v>
       </c>
       <c r="W62" t="n">
-        <v>-0.231616</v>
+        <v>-0.6292219999999999</v>
       </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -615,10 +615,10 @@
         <v>6.25</v>
       </c>
       <c r="C2" t="n">
-        <v>0.021979</v>
+        <v>0.022184</v>
       </c>
       <c r="D2" t="n">
-        <v>0.021979</v>
+        <v>0.022184</v>
       </c>
       <c r="E2" t="n">
         <v>1.16</v>
@@ -773,10 +773,10 @@
         <v>1.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.002265</v>
+        <v>0.00206</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.002265</v>
+        <v>0.00206</v>
       </c>
       <c r="AH3" t="n">
         <v>-0.01</v>
@@ -7260,7 +7260,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="C62" t="n">
         <v>0.05166</v>
@@ -7274,10 +7274,10 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>5.149</v>
+        <v>5.1527</v>
       </c>
       <c r="K62" t="n">
-        <v>5.1484</v>
+        <v>5.152</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -7290,10 +7290,10 @@
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="n">
-        <v>-0.629149</v>
+        <v>-0.557743</v>
       </c>
       <c r="W62" t="n">
-        <v>-0.6292219999999999</v>
+        <v>-0.559738</v>
       </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
@@ -7303,7 +7303,7 @@
       <c r="AC62" t="inlineStr"/>
       <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="AF62" t="n">
         <v>-0.000124</v>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK62"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -433,175 +433,135 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
           <t>cdi</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ipca</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>igp_m</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>inpc</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ibc_br_sa</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ibc_br</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>cambio_venda_usd</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>cambio_compra_usd</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>saldo_credito_total</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>saldo_credito_pj</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>saldo_credito_pf</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inadimplencia_total</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inadimplencia_pj</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>var_pct_saldo_credito_total</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>ipca_acum_12m</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>inpc_acum_12m</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>dif_selic_over</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>dif_cdi</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -615,56 +575,48 @@
         <v>6.25</v>
       </c>
       <c r="C2" t="n">
-        <v>0.022184</v>
+        <v>0.022435</v>
       </c>
       <c r="D2" t="n">
-        <v>0.022184</v>
+        <v>-0.64</v>
       </c>
       <c r="E2" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.64</v>
+        <v>96.96513</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2</v>
+        <v>97.10777</v>
       </c>
       <c r="H2" t="n">
-        <v>96.96513</v>
+        <v>5.4394</v>
       </c>
       <c r="I2" t="n">
-        <v>97.10777</v>
+        <v>5.4388</v>
       </c>
       <c r="J2" t="n">
-        <v>5.4394</v>
+        <v>1894119</v>
       </c>
       <c r="K2" t="n">
-        <v>5.4388</v>
+        <v>2546936</v>
       </c>
       <c r="L2" t="n">
-        <v>4441056</v>
+        <v>2.34</v>
       </c>
       <c r="M2" t="n">
-        <v>1894119</v>
+        <v>1.43</v>
       </c>
       <c r="N2" t="n">
-        <v>2546936</v>
+        <v>21.42</v>
       </c>
       <c r="O2" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="R2" t="n">
-        <v>21.42</v>
-      </c>
-      <c r="S2" t="n">
         <v>368886</v>
       </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -675,14 +627,6 @@
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -695,99 +639,77 @@
         <v>0.024244</v>
       </c>
       <c r="D3" t="n">
-        <v>0.024244</v>
+        <v>0.64</v>
       </c>
       <c r="E3" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="F3" t="n">
-        <v>0.64</v>
+        <v>97.48671</v>
       </c>
       <c r="G3" t="n">
-        <v>1.16</v>
+        <v>96.53041</v>
       </c>
       <c r="H3" t="n">
-        <v>97.48671</v>
+        <v>5.643</v>
       </c>
       <c r="I3" t="n">
-        <v>96.53041</v>
+        <v>5.6424</v>
       </c>
       <c r="J3" t="n">
-        <v>5.643</v>
+        <v>1910940</v>
       </c>
       <c r="K3" t="n">
-        <v>5.6424</v>
+        <v>2601017</v>
       </c>
       <c r="L3" t="n">
-        <v>4511956</v>
+        <v>2.33</v>
       </c>
       <c r="M3" t="n">
-        <v>1910940</v>
+        <v>1.43</v>
       </c>
       <c r="N3" t="n">
-        <v>2601017</v>
+        <v>22.89</v>
       </c>
       <c r="O3" t="n">
-        <v>2.33</v>
+        <v>367927</v>
       </c>
       <c r="P3" t="n">
-        <v>1.43</v>
+        <v>0.537905</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.99</v>
+        <v>-0.594556</v>
       </c>
       <c r="R3" t="n">
-        <v>22.89</v>
+        <v>3.74306</v>
       </c>
       <c r="S3" t="n">
-        <v>367927</v>
+        <v>3.743473</v>
       </c>
       <c r="T3" t="n">
-        <v>0.537905</v>
+        <v>0.888065</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.594556</v>
+        <v>2.123375</v>
       </c>
       <c r="V3" t="n">
-        <v>3.74306</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3.743473</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.596467</v>
-      </c>
+        <v>-0.259972</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>0.888065</v>
+        <v>1.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.123375</v>
+        <v>0.001809</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.259972</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.00206</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.00206</v>
-      </c>
-      <c r="AH3" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AB3" t="n">
         <v>0</v>
       </c>
-      <c r="AJ3" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AK3" t="n">
+      <c r="AC3" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -802,99 +724,77 @@
         <v>0.029256</v>
       </c>
       <c r="D4" t="n">
-        <v>0.029256</v>
+        <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>0.95</v>
+        <v>0.84</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02</v>
+        <v>99.05526</v>
       </c>
       <c r="G4" t="n">
-        <v>0.84</v>
+        <v>97.85277000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>99.05526</v>
+        <v>5.6199</v>
       </c>
       <c r="I4" t="n">
-        <v>97.85277000000001</v>
+        <v>5.6193</v>
       </c>
       <c r="J4" t="n">
-        <v>5.6199</v>
+        <v>1933111</v>
       </c>
       <c r="K4" t="n">
-        <v>5.6193</v>
+        <v>2664395</v>
       </c>
       <c r="L4" t="n">
-        <v>4597507</v>
+        <v>2.36</v>
       </c>
       <c r="M4" t="n">
-        <v>1933111</v>
+        <v>1.46</v>
       </c>
       <c r="N4" t="n">
-        <v>2664395</v>
+        <v>23.91</v>
       </c>
       <c r="O4" t="n">
-        <v>2.36</v>
+        <v>367772</v>
       </c>
       <c r="P4" t="n">
-        <v>1.46</v>
+        <v>1.608989</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.01</v>
+        <v>1.36989</v>
       </c>
       <c r="R4" t="n">
-        <v>23.91</v>
+        <v>-0.409357</v>
       </c>
       <c r="S4" t="n">
-        <v>367772</v>
+        <v>-0.4094</v>
       </c>
       <c r="T4" t="n">
-        <v>1.608989</v>
+        <v>1.160214</v>
       </c>
       <c r="U4" t="n">
-        <v>1.36989</v>
+        <v>2.436662</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.409357</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-0.4094</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.896096</v>
-      </c>
+        <v>-0.042128</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>1.160214</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.436662</v>
+        <v>0.005012</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.042128</v>
-      </c>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.005012</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.005012</v>
-      </c>
-      <c r="AH4" t="n">
         <v>0.03</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AB4" t="n">
         <v>0.03</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK4" t="n">
+      <c r="AC4" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -909,99 +809,77 @@
         <v>0.033316</v>
       </c>
       <c r="D5" t="n">
-        <v>0.033316</v>
+        <v>0.87</v>
       </c>
       <c r="E5" t="n">
         <v>0.73</v>
       </c>
       <c r="F5" t="n">
-        <v>0.87</v>
+        <v>99.37716</v>
       </c>
       <c r="G5" t="n">
-        <v>0.73</v>
+        <v>99.32258</v>
       </c>
       <c r="H5" t="n">
-        <v>99.37716</v>
+        <v>5.5805</v>
       </c>
       <c r="I5" t="n">
-        <v>99.32258</v>
+        <v>5.5799</v>
       </c>
       <c r="J5" t="n">
-        <v>5.5805</v>
+        <v>1974391</v>
       </c>
       <c r="K5" t="n">
-        <v>5.5799</v>
+        <v>2708461</v>
       </c>
       <c r="L5" t="n">
-        <v>4682852</v>
+        <v>2.35</v>
       </c>
       <c r="M5" t="n">
-        <v>1974391</v>
+        <v>1.4</v>
       </c>
       <c r="N5" t="n">
-        <v>2708461</v>
+        <v>24.21</v>
       </c>
       <c r="O5" t="n">
-        <v>2.35</v>
+        <v>362204</v>
       </c>
       <c r="P5" t="n">
-        <v>1.4</v>
+        <v>0.32497</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.05</v>
+        <v>1.502063</v>
       </c>
       <c r="R5" t="n">
-        <v>24.21</v>
+        <v>-0.70108</v>
       </c>
       <c r="S5" t="n">
-        <v>362204</v>
+        <v>-0.701155</v>
       </c>
       <c r="T5" t="n">
-        <v>0.32497</v>
+        <v>2.135418</v>
       </c>
       <c r="U5" t="n">
-        <v>1.502063</v>
+        <v>1.653884</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.70108</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-0.701155</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.856332</v>
-      </c>
+        <v>-1.513981</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>2.135418</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.653884</v>
+        <v>0.00406</v>
       </c>
       <c r="AA5" t="n">
-        <v>-1.513981</v>
-      </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0.00406</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0.00406</v>
-      </c>
-      <c r="AH5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AB5" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK5" t="n">
+      <c r="AC5" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1016,99 +894,77 @@
         <v>0.034749</v>
       </c>
       <c r="D6" t="n">
-        <v>0.034749</v>
+        <v>1.82</v>
       </c>
       <c r="E6" t="n">
-        <v>0.54</v>
+        <v>0.67</v>
       </c>
       <c r="F6" t="n">
-        <v>1.82</v>
+        <v>97.4213</v>
       </c>
       <c r="G6" t="n">
-        <v>0.67</v>
+        <v>91.67776000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>97.4213</v>
+        <v>5.3574</v>
       </c>
       <c r="I6" t="n">
-        <v>91.67776000000001</v>
+        <v>5.3568</v>
       </c>
       <c r="J6" t="n">
-        <v>5.3574</v>
+        <v>1947035</v>
       </c>
       <c r="K6" t="n">
-        <v>5.3568</v>
+        <v>2735096</v>
       </c>
       <c r="L6" t="n">
-        <v>4682131</v>
+        <v>2.51</v>
       </c>
       <c r="M6" t="n">
-        <v>1947035</v>
+        <v>1.46</v>
       </c>
       <c r="N6" t="n">
-        <v>2735096</v>
+        <v>25.23</v>
       </c>
       <c r="O6" t="n">
-        <v>2.51</v>
+        <v>358398</v>
       </c>
       <c r="P6" t="n">
-        <v>1.46</v>
+        <v>-1.968118</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.26</v>
+        <v>-7.696961</v>
       </c>
       <c r="R6" t="n">
-        <v>25.23</v>
+        <v>-3.99785</v>
       </c>
       <c r="S6" t="n">
-        <v>358398</v>
+        <v>-3.99828</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.968118</v>
+        <v>-1.385541</v>
       </c>
       <c r="U6" t="n">
-        <v>-7.696961</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.99785</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-3.99828</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.015397</v>
-      </c>
+        <v>-1.050789</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
-        <v>-1.385541</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.001433</v>
       </c>
       <c r="AA6" t="n">
-        <v>-1.050789</v>
-      </c>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.001433</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.001433</v>
-      </c>
-      <c r="AH6" t="n">
         <v>0.16</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AB6" t="n">
         <v>0.06</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AK6" t="n">
+      <c r="AC6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1123,99 +979,77 @@
         <v>0.039598</v>
       </c>
       <c r="D7" t="n">
-        <v>0.039598</v>
+        <v>1.83</v>
       </c>
       <c r="E7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1.83</v>
+        <v>98.4804</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>95.63728999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>98.4804</v>
+        <v>5.1394</v>
       </c>
       <c r="I7" t="n">
-        <v>95.63728999999999</v>
+        <v>5.1388</v>
       </c>
       <c r="J7" t="n">
-        <v>5.1394</v>
+        <v>1971524</v>
       </c>
       <c r="K7" t="n">
-        <v>5.1388</v>
+        <v>2756295</v>
       </c>
       <c r="L7" t="n">
-        <v>4727818</v>
+        <v>2.57</v>
       </c>
       <c r="M7" t="n">
-        <v>1971524</v>
+        <v>1.44</v>
       </c>
       <c r="N7" t="n">
-        <v>2756295</v>
+        <v>25.63</v>
       </c>
       <c r="O7" t="n">
-        <v>2.57</v>
+        <v>357740</v>
       </c>
       <c r="P7" t="n">
-        <v>1.44</v>
+        <v>1.087134</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.38</v>
+        <v>4.318965</v>
       </c>
       <c r="R7" t="n">
-        <v>25.63</v>
+        <v>-4.069138</v>
       </c>
       <c r="S7" t="n">
-        <v>357740</v>
+        <v>-4.069594</v>
       </c>
       <c r="T7" t="n">
-        <v>1.087134</v>
+        <v>1.257759</v>
       </c>
       <c r="U7" t="n">
-        <v>4.318965</v>
+        <v>0.775073</v>
       </c>
       <c r="V7" t="n">
-        <v>-4.069138</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-4.069594</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.975774</v>
-      </c>
+        <v>-0.183595</v>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
       <c r="Y7" t="n">
-        <v>1.257759</v>
+        <v>1.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.775073</v>
+        <v>0.004849</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.183595</v>
-      </c>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0.004849</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0.004849</v>
-      </c>
-      <c r="AH7" t="n">
         <v>0.06</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AB7" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AJ7" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AK7" t="n">
+      <c r="AC7" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1230,99 +1064,77 @@
         <v>0.041954</v>
       </c>
       <c r="D8" t="n">
-        <v>0.041954</v>
+        <v>1.74</v>
       </c>
       <c r="E8" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="F8" t="n">
-        <v>1.74</v>
+        <v>99.54801999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>1.71</v>
+        <v>104.53237</v>
       </c>
       <c r="H8" t="n">
-        <v>99.54801999999999</v>
+        <v>4.7378</v>
       </c>
       <c r="I8" t="n">
-        <v>104.53237</v>
+        <v>4.7372</v>
       </c>
       <c r="J8" t="n">
-        <v>4.7378</v>
+        <v>1994119</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7372</v>
+        <v>2800464</v>
       </c>
       <c r="L8" t="n">
-        <v>4794583</v>
+        <v>2.66</v>
       </c>
       <c r="M8" t="n">
-        <v>1994119</v>
+        <v>1.55</v>
       </c>
       <c r="N8" t="n">
-        <v>2800464</v>
+        <v>26.54</v>
       </c>
       <c r="O8" t="n">
-        <v>2.66</v>
+        <v>353169</v>
       </c>
       <c r="P8" t="n">
-        <v>1.55</v>
+        <v>1.084094</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.45</v>
+        <v>9.300848999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>26.54</v>
+        <v>-7.814142</v>
       </c>
       <c r="S8" t="n">
-        <v>353169</v>
+        <v>-7.815054</v>
       </c>
       <c r="T8" t="n">
-        <v>1.084094</v>
+        <v>1.146068</v>
       </c>
       <c r="U8" t="n">
-        <v>9.300848999999999</v>
+        <v>1.602477</v>
       </c>
       <c r="V8" t="n">
-        <v>-7.814142</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-7.815054</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.412174</v>
-      </c>
+        <v>-1.277744</v>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
       <c r="Y8" t="n">
-        <v>1.146068</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.602477</v>
+        <v>0.002356</v>
       </c>
       <c r="AA8" t="n">
-        <v>-1.277744</v>
-      </c>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0.002356</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.002356</v>
-      </c>
-      <c r="AH8" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AB8" t="n">
         <v>0.11</v>
       </c>
-      <c r="AJ8" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK8" t="n">
+      <c r="AC8" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1337,99 +1149,77 @@
         <v>0.043739</v>
       </c>
       <c r="D9" t="n">
-        <v>0.043739</v>
+        <v>1.41</v>
       </c>
       <c r="E9" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="F9" t="n">
-        <v>1.41</v>
+        <v>99.44118</v>
       </c>
       <c r="G9" t="n">
-        <v>1.04</v>
+        <v>100.22938</v>
       </c>
       <c r="H9" t="n">
-        <v>99.44118</v>
+        <v>4.9191</v>
       </c>
       <c r="I9" t="n">
-        <v>100.22938</v>
+        <v>4.9185</v>
       </c>
       <c r="J9" t="n">
-        <v>4.9191</v>
+        <v>2003312</v>
       </c>
       <c r="K9" t="n">
-        <v>4.9185</v>
+        <v>2830420</v>
       </c>
       <c r="L9" t="n">
-        <v>4833732</v>
+        <v>2.72</v>
       </c>
       <c r="M9" t="n">
-        <v>2003312</v>
+        <v>1.57</v>
       </c>
       <c r="N9" t="n">
-        <v>2830420</v>
+        <v>27.46</v>
       </c>
       <c r="O9" t="n">
-        <v>2.72</v>
+        <v>345097</v>
       </c>
       <c r="P9" t="n">
-        <v>1.57</v>
+        <v>-0.107325</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.54</v>
+        <v>-4.116419</v>
       </c>
       <c r="R9" t="n">
-        <v>27.46</v>
+        <v>3.826671</v>
       </c>
       <c r="S9" t="n">
-        <v>345097</v>
+        <v>3.827155</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.107325</v>
+        <v>0.461006</v>
       </c>
       <c r="U9" t="n">
-        <v>-4.116419</v>
+        <v>1.06968</v>
       </c>
       <c r="V9" t="n">
-        <v>3.826671</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3.827155</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.816526</v>
-      </c>
+        <v>-2.285591</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
       <c r="Y9" t="n">
-        <v>0.461006</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.06968</v>
+        <v>0.001785</v>
       </c>
       <c r="AA9" t="n">
-        <v>-2.285591</v>
-      </c>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.001785</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.001785</v>
-      </c>
-      <c r="AH9" t="n">
         <v>0.06</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AB9" t="n">
         <v>0.02</v>
       </c>
-      <c r="AJ9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK9" t="n">
+      <c r="AC9" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1444,99 +1234,77 @@
         <v>0.046796</v>
       </c>
       <c r="D10" t="n">
-        <v>0.046796</v>
+        <v>0.52</v>
       </c>
       <c r="E10" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="F10" t="n">
-        <v>0.52</v>
+        <v>99.6454</v>
       </c>
       <c r="G10" t="n">
-        <v>0.45</v>
+        <v>99.74383</v>
       </c>
       <c r="H10" t="n">
-        <v>99.6454</v>
+        <v>4.7289</v>
       </c>
       <c r="I10" t="n">
-        <v>99.74383</v>
+        <v>4.7283</v>
       </c>
       <c r="J10" t="n">
-        <v>4.7289</v>
+        <v>2013726</v>
       </c>
       <c r="K10" t="n">
-        <v>4.7283</v>
+        <v>2875671</v>
       </c>
       <c r="L10" t="n">
-        <v>4889397</v>
+        <v>2.79</v>
       </c>
       <c r="M10" t="n">
-        <v>2013726</v>
+        <v>1.57</v>
       </c>
       <c r="N10" t="n">
-        <v>2875671</v>
+        <v>27.42</v>
       </c>
       <c r="O10" t="n">
-        <v>2.79</v>
+        <v>346415</v>
       </c>
       <c r="P10" t="n">
-        <v>1.57</v>
+        <v>0.205368</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.65</v>
+        <v>-0.484439</v>
       </c>
       <c r="R10" t="n">
-        <v>27.42</v>
+        <v>-3.866561</v>
       </c>
       <c r="S10" t="n">
-        <v>346415</v>
+        <v>-3.867033</v>
       </c>
       <c r="T10" t="n">
-        <v>0.205368</v>
+        <v>0.5198390000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.484439</v>
+        <v>1.598738</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.866561</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-3.867033</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.151595</v>
-      </c>
+        <v>0.381922</v>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
       <c r="Y10" t="n">
-        <v>0.5198390000000001</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.598738</v>
+        <v>0.003057</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.381922</v>
-      </c>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0.003057</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0.003057</v>
-      </c>
-      <c r="AH10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AB10" t="n">
         <v>0</v>
       </c>
-      <c r="AJ10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK10" t="n">
+      <c r="AC10" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1551,99 +1319,77 @@
         <v>0.048116</v>
       </c>
       <c r="D11" t="n">
-        <v>0.048116</v>
+        <v>0.59</v>
       </c>
       <c r="E11" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="F11" t="n">
-        <v>0.59</v>
+        <v>99.51048</v>
       </c>
       <c r="G11" t="n">
-        <v>0.62</v>
+        <v>99.31653</v>
       </c>
       <c r="H11" t="n">
-        <v>99.51048</v>
+        <v>5.238</v>
       </c>
       <c r="I11" t="n">
-        <v>99.31653</v>
+        <v>5.2374</v>
       </c>
       <c r="J11" t="n">
-        <v>5.238</v>
+        <v>2052569</v>
       </c>
       <c r="K11" t="n">
-        <v>5.2374</v>
+        <v>2913035</v>
       </c>
       <c r="L11" t="n">
-        <v>4965603</v>
+        <v>2.73</v>
       </c>
       <c r="M11" t="n">
-        <v>2052569</v>
+        <v>1.52</v>
       </c>
       <c r="N11" t="n">
-        <v>2913035</v>
+        <v>27.88</v>
       </c>
       <c r="O11" t="n">
-        <v>2.73</v>
+        <v>341958</v>
       </c>
       <c r="P11" t="n">
-        <v>1.52</v>
+        <v>-0.1354</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.57</v>
+        <v>-0.428397</v>
       </c>
       <c r="R11" t="n">
-        <v>27.88</v>
+        <v>10.765717</v>
       </c>
       <c r="S11" t="n">
-        <v>341958</v>
+        <v>10.767083</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1354</v>
+        <v>1.928912</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.428397</v>
+        <v>1.299314</v>
       </c>
       <c r="V11" t="n">
-        <v>10.765717</v>
-      </c>
-      <c r="W11" t="n">
-        <v>10.767083</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.558597</v>
-      </c>
+        <v>-1.286607</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
       <c r="Y11" t="n">
-        <v>1.928912</v>
+        <v>0.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.299314</v>
+        <v>0.00132</v>
       </c>
       <c r="AA11" t="n">
-        <v>-1.286607</v>
-      </c>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0.00132</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0.00132</v>
-      </c>
-      <c r="AH11" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AB11" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AJ11" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AK11" t="n">
+      <c r="AC11" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1658,99 +1404,77 @@
         <v>0.049037</v>
       </c>
       <c r="D12" t="n">
-        <v>0.049037</v>
+        <v>0.21</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.68</v>
+        <v>-0.6</v>
       </c>
       <c r="F12" t="n">
-        <v>0.21</v>
+        <v>101.43172</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6</v>
+        <v>103.95991</v>
       </c>
       <c r="H12" t="n">
-        <v>101.43172</v>
+        <v>5.1884</v>
       </c>
       <c r="I12" t="n">
-        <v>103.95991</v>
+        <v>5.1878</v>
       </c>
       <c r="J12" t="n">
-        <v>5.1884</v>
+        <v>2047038</v>
       </c>
       <c r="K12" t="n">
-        <v>5.1878</v>
+        <v>2952207</v>
       </c>
       <c r="L12" t="n">
-        <v>4999244</v>
+        <v>2.84</v>
       </c>
       <c r="M12" t="n">
-        <v>2047038</v>
+        <v>1.6</v>
       </c>
       <c r="N12" t="n">
-        <v>2952207</v>
+        <v>29.24</v>
       </c>
       <c r="O12" t="n">
-        <v>2.84</v>
+        <v>346403</v>
       </c>
       <c r="P12" t="n">
-        <v>1.6</v>
+        <v>1.930691</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.71</v>
+        <v>4.675335</v>
       </c>
       <c r="R12" t="n">
-        <v>29.24</v>
+        <v>-0.946926</v>
       </c>
       <c r="S12" t="n">
-        <v>346403</v>
+        <v>-0.947035</v>
       </c>
       <c r="T12" t="n">
-        <v>1.930691</v>
+        <v>-0.269467</v>
       </c>
       <c r="U12" t="n">
-        <v>4.675335</v>
+        <v>1.344714</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.946926</v>
-      </c>
-      <c r="W12" t="n">
-        <v>-0.947035</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.677481</v>
-      </c>
+        <v>1.299867</v>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
       <c r="Y12" t="n">
-        <v>-0.269467</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.344714</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.299867</v>
-      </c>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0.0009210000000000001</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0.0009210000000000001</v>
-      </c>
-      <c r="AH12" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AB12" t="n">
         <v>0.08</v>
       </c>
-      <c r="AJ12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AK12" t="n">
+      <c r="AC12" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -1765,105 +1489,81 @@
         <v>0.05056</v>
       </c>
       <c r="D13" t="n">
-        <v>0.05056</v>
+        <v>-0.7</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.36</v>
+        <v>-0.31</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7</v>
+        <v>101.10583</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.31</v>
+        <v>104.51156</v>
       </c>
       <c r="H13" t="n">
-        <v>101.10583</v>
+        <v>5.179</v>
       </c>
       <c r="I13" t="n">
-        <v>104.51156</v>
+        <v>5.1784</v>
       </c>
       <c r="J13" t="n">
-        <v>5.179</v>
+        <v>2064183</v>
       </c>
       <c r="K13" t="n">
-        <v>5.1784</v>
+        <v>3008528</v>
       </c>
       <c r="L13" t="n">
-        <v>5072711</v>
+        <v>2.9</v>
       </c>
       <c r="M13" t="n">
-        <v>2064183</v>
+        <v>1.62</v>
       </c>
       <c r="N13" t="n">
-        <v>3008528</v>
+        <v>28.6</v>
       </c>
       <c r="O13" t="n">
-        <v>2.9</v>
+        <v>339664</v>
       </c>
       <c r="P13" t="n">
-        <v>1.62</v>
+        <v>-0.32129</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.78</v>
+        <v>0.530637</v>
       </c>
       <c r="R13" t="n">
-        <v>28.6</v>
+        <v>-0.181173</v>
       </c>
       <c r="S13" t="n">
-        <v>339664</v>
+        <v>-0.181194</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.32129</v>
+        <v>0.837552</v>
       </c>
       <c r="U13" t="n">
-        <v>0.530637</v>
+        <v>1.907759</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.181173</v>
+        <v>-1.945422</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.181194</v>
+        <v>8.58755</v>
       </c>
       <c r="X13" t="n">
-        <v>1.469562</v>
+        <v>8.825751</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.837552</v>
+        <v>0.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.907759</v>
+        <v>0.001523</v>
       </c>
       <c r="AA13" t="n">
-        <v>-1.945422</v>
+        <v>0.06</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.727061000000001</v>
+        <v>0.02</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.58755</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>8.825751</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0.001523</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0.001523</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK13" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -1878,105 +1578,81 @@
         <v>0.050788</v>
       </c>
       <c r="D14" t="n">
-        <v>0.050788</v>
+        <v>-0.95</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.29</v>
+        <v>-0.32</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.95</v>
+        <v>101.16034</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.32</v>
+        <v>101.1889</v>
       </c>
       <c r="H14" t="n">
-        <v>101.16034</v>
+        <v>5.4066</v>
       </c>
       <c r="I14" t="n">
-        <v>101.1889</v>
+        <v>5.406</v>
       </c>
       <c r="J14" t="n">
-        <v>5.4066</v>
+        <v>2109806</v>
       </c>
       <c r="K14" t="n">
-        <v>5.406</v>
+        <v>3054969</v>
       </c>
       <c r="L14" t="n">
-        <v>5164775</v>
+        <v>2.92</v>
       </c>
       <c r="M14" t="n">
-        <v>2109806</v>
+        <v>1.65</v>
       </c>
       <c r="N14" t="n">
-        <v>3054969</v>
+        <v>28.57</v>
       </c>
       <c r="O14" t="n">
-        <v>2.92</v>
+        <v>327580</v>
       </c>
       <c r="P14" t="n">
-        <v>1.65</v>
+        <v>0.053914</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.8</v>
+        <v>-3.179227</v>
       </c>
       <c r="R14" t="n">
-        <v>28.57</v>
+        <v>4.394671</v>
       </c>
       <c r="S14" t="n">
-        <v>327580</v>
+        <v>4.39518</v>
       </c>
       <c r="T14" t="n">
-        <v>0.053914</v>
+        <v>2.210221</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.179227</v>
+        <v>1.543645</v>
       </c>
       <c r="V14" t="n">
-        <v>4.394671</v>
+        <v>-3.557633</v>
       </c>
       <c r="W14" t="n">
-        <v>4.39518</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>1.814888</v>
+        <v>7.191214</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.210221</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.543645</v>
+        <v>0.000228</v>
       </c>
       <c r="AA14" t="n">
-        <v>-3.557633</v>
+        <v>0.02</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.168596</v>
+        <v>0.03</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.248760000000001</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>7.191214</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0.000228</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0.000228</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK14" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -1991,105 +1667,81 @@
         <v>0.050788</v>
       </c>
       <c r="D15" t="n">
-        <v>0.050788</v>
+        <v>-0.97</v>
       </c>
       <c r="E15" t="n">
-        <v>0.59</v>
+        <v>0.47</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.97</v>
+        <v>101.44171</v>
       </c>
       <c r="G15" t="n">
-        <v>0.47</v>
+        <v>100.08177</v>
       </c>
       <c r="H15" t="n">
-        <v>101.44171</v>
+        <v>5.257</v>
       </c>
       <c r="I15" t="n">
-        <v>100.08177</v>
+        <v>5.2564</v>
       </c>
       <c r="J15" t="n">
-        <v>5.257</v>
+        <v>2105856</v>
       </c>
       <c r="K15" t="n">
-        <v>5.2564</v>
+        <v>3110134</v>
       </c>
       <c r="L15" t="n">
-        <v>5215990</v>
+        <v>3.04</v>
       </c>
       <c r="M15" t="n">
-        <v>2105856</v>
+        <v>1.77</v>
       </c>
       <c r="N15" t="n">
-        <v>3110134</v>
+        <v>29.68</v>
       </c>
       <c r="O15" t="n">
-        <v>3.04</v>
+        <v>325546</v>
       </c>
       <c r="P15" t="n">
-        <v>1.77</v>
+        <v>0.278143</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.89</v>
+        <v>-1.094122</v>
       </c>
       <c r="R15" t="n">
-        <v>29.68</v>
+        <v>-2.766988</v>
       </c>
       <c r="S15" t="n">
-        <v>325546</v>
+        <v>-2.767296</v>
       </c>
       <c r="T15" t="n">
-        <v>0.278143</v>
+        <v>-0.187221</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.094122</v>
+        <v>1.805747</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.766988</v>
+        <v>-0.6209170000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>-2.767296</v>
+        <v>6.517038</v>
       </c>
       <c r="X15" t="n">
-        <v>0.991621</v>
+        <v>6.460076</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.187221</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.805747</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.6209170000000001</v>
+        <v>0.12</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.470016</v>
+        <v>0.12</v>
       </c>
       <c r="AC15" t="n">
-        <v>6.517038</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>6.460076</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK15" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -2104,105 +1756,81 @@
         <v>0.050788</v>
       </c>
       <c r="D16" t="n">
-        <v>0.050788</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5600000000000001</v>
+        <v>100.7146</v>
       </c>
       <c r="G16" t="n">
-        <v>0.38</v>
+        <v>99.15031999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>100.7146</v>
+        <v>5.2941</v>
       </c>
       <c r="I16" t="n">
-        <v>99.15031999999999</v>
+        <v>5.2935</v>
       </c>
       <c r="J16" t="n">
-        <v>5.2941</v>
+        <v>2130312</v>
       </c>
       <c r="K16" t="n">
-        <v>5.2935</v>
+        <v>3155345</v>
       </c>
       <c r="L16" t="n">
-        <v>5285657</v>
+        <v>3.07</v>
       </c>
       <c r="M16" t="n">
-        <v>2130312</v>
+        <v>1.81</v>
       </c>
       <c r="N16" t="n">
-        <v>3155345</v>
+        <v>30.52</v>
       </c>
       <c r="O16" t="n">
-        <v>3.07</v>
+        <v>331505</v>
       </c>
       <c r="P16" t="n">
-        <v>1.81</v>
+        <v>-0.716776</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.92</v>
+        <v>-0.930689</v>
       </c>
       <c r="R16" t="n">
-        <v>30.52</v>
+        <v>0.705726</v>
       </c>
       <c r="S16" t="n">
-        <v>331505</v>
+        <v>0.705806</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.716776</v>
+        <v>1.161333</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.930689</v>
+        <v>1.453667</v>
       </c>
       <c r="V16" t="n">
-        <v>0.705726</v>
+        <v>1.830463</v>
       </c>
       <c r="W16" t="n">
-        <v>0.705806</v>
+        <v>5.899363</v>
       </c>
       <c r="X16" t="n">
-        <v>1.335643</v>
+        <v>5.974439</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.161333</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.453667</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.830463</v>
+        <v>0.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.900488</v>
+        <v>0.04</v>
       </c>
       <c r="AC16" t="n">
-        <v>5.899363</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>5.974439</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AK16" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2217,105 +1845,81 @@
         <v>0.050788</v>
       </c>
       <c r="D17" t="n">
-        <v>0.050788</v>
+        <v>0.45</v>
       </c>
       <c r="E17" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.45</v>
+        <v>100.58818</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6899999999999999</v>
+        <v>99.97037</v>
       </c>
       <c r="H17" t="n">
-        <v>100.58818</v>
+        <v>5.2177</v>
       </c>
       <c r="I17" t="n">
-        <v>99.97037</v>
+        <v>5.2171</v>
       </c>
       <c r="J17" t="n">
-        <v>5.2177</v>
+        <v>2178236</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2171</v>
+        <v>3187833</v>
       </c>
       <c r="L17" t="n">
-        <v>5366069</v>
+        <v>3.07</v>
       </c>
       <c r="M17" t="n">
-        <v>2178236</v>
+        <v>1.8</v>
       </c>
       <c r="N17" t="n">
-        <v>3187833</v>
+        <v>29.64</v>
       </c>
       <c r="O17" t="n">
-        <v>3.07</v>
+        <v>324703</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8</v>
+        <v>-0.125523</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.94</v>
+        <v>0.827078</v>
       </c>
       <c r="R17" t="n">
-        <v>29.64</v>
+        <v>-1.443116</v>
       </c>
       <c r="S17" t="n">
-        <v>324703</v>
+        <v>-1.443279</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.125523</v>
+        <v>2.249624</v>
       </c>
       <c r="U17" t="n">
-        <v>0.827078</v>
+        <v>1.029618</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.443116</v>
+        <v>-2.051854</v>
       </c>
       <c r="W17" t="n">
-        <v>-1.443279</v>
+        <v>5.458422</v>
       </c>
       <c r="X17" t="n">
-        <v>1.521325</v>
+        <v>5.932356</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.249624</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.029618</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
-        <v>-2.051854</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.784842</v>
+        <v>-0.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.458422</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>5.932356</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK17" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -2330,105 +1934,81 @@
         <v>0.050788</v>
       </c>
       <c r="D18" t="n">
-        <v>0.050788</v>
+        <v>0.21</v>
       </c>
       <c r="E18" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="F18" t="n">
-        <v>0.21</v>
+        <v>100.10988</v>
       </c>
       <c r="G18" t="n">
-        <v>0.46</v>
+        <v>95.09953</v>
       </c>
       <c r="H18" t="n">
-        <v>100.10988</v>
+        <v>5.0993</v>
       </c>
       <c r="I18" t="n">
-        <v>95.09953</v>
+        <v>5.0987</v>
       </c>
       <c r="J18" t="n">
-        <v>5.0993</v>
+        <v>2151399</v>
       </c>
       <c r="K18" t="n">
-        <v>5.0987</v>
+        <v>3221831</v>
       </c>
       <c r="L18" t="n">
-        <v>5373231</v>
+        <v>3.24</v>
       </c>
       <c r="M18" t="n">
-        <v>2151399</v>
+        <v>1.94</v>
       </c>
       <c r="N18" t="n">
-        <v>3221831</v>
+        <v>30.54</v>
       </c>
       <c r="O18" t="n">
-        <v>3.24</v>
+        <v>331122</v>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>-0.475503</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.11</v>
+        <v>-4.872284</v>
       </c>
       <c r="R18" t="n">
-        <v>30.54</v>
+        <v>-2.269199</v>
       </c>
       <c r="S18" t="n">
-        <v>331122</v>
+        <v>-2.26946</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.475503</v>
+        <v>-1.232052</v>
       </c>
       <c r="U18" t="n">
-        <v>-4.872284</v>
+        <v>1.066493</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.269199</v>
+        <v>1.976883</v>
       </c>
       <c r="W18" t="n">
-        <v>-2.26946</v>
+        <v>3.79089</v>
       </c>
       <c r="X18" t="n">
-        <v>0.133468</v>
+        <v>5.711379</v>
       </c>
       <c r="Y18" t="n">
-        <v>-1.232052</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.066493</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.976883</v>
+        <v>0.17</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.77432</v>
+        <v>0.14</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.79089</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>5.711379</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AK18" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2443,105 +2023,81 @@
         <v>0.050788</v>
       </c>
       <c r="D19" t="n">
-        <v>0.050788</v>
+        <v>-0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.06</v>
+        <v>103.07987</v>
       </c>
       <c r="G19" t="n">
-        <v>0.77</v>
+        <v>98.64798</v>
       </c>
       <c r="H19" t="n">
-        <v>103.07987</v>
+        <v>5.2078</v>
       </c>
       <c r="I19" t="n">
-        <v>98.64798</v>
+        <v>5.2072</v>
       </c>
       <c r="J19" t="n">
-        <v>5.2078</v>
+        <v>2136105</v>
       </c>
       <c r="K19" t="n">
-        <v>5.2072</v>
+        <v>3234845</v>
       </c>
       <c r="L19" t="n">
-        <v>5370950</v>
+        <v>3.36</v>
       </c>
       <c r="M19" t="n">
-        <v>2136105</v>
+        <v>2.17</v>
       </c>
       <c r="N19" t="n">
-        <v>3234845</v>
+        <v>30.48</v>
       </c>
       <c r="O19" t="n">
-        <v>3.36</v>
+        <v>328098</v>
       </c>
       <c r="P19" t="n">
-        <v>2.17</v>
+        <v>2.96673</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.16</v>
+        <v>3.731301</v>
       </c>
       <c r="R19" t="n">
-        <v>30.48</v>
+        <v>2.127743</v>
       </c>
       <c r="S19" t="n">
-        <v>328098</v>
+        <v>2.127993</v>
       </c>
       <c r="T19" t="n">
-        <v>2.96673</v>
+        <v>-0.710886</v>
       </c>
       <c r="U19" t="n">
-        <v>3.731301</v>
+        <v>0.403932</v>
       </c>
       <c r="V19" t="n">
-        <v>2.127743</v>
+        <v>-0.913259</v>
       </c>
       <c r="W19" t="n">
-        <v>2.127993</v>
+        <v>1.864495</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.042451</v>
+        <v>5.47065</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.710886</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.403932</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.913259</v>
+        <v>0.12</v>
       </c>
       <c r="AB19" t="n">
-        <v>5.596302</v>
+        <v>0.23</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.864495</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>5.47065</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK19" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2556,105 +2112,81 @@
         <v>0.050788</v>
       </c>
       <c r="D20" t="n">
-        <v>0.050788</v>
+        <v>0.05</v>
       </c>
       <c r="E20" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="F20" t="n">
-        <v>0.05</v>
+        <v>103.08494</v>
       </c>
       <c r="G20" t="n">
-        <v>0.64</v>
+        <v>110.61922</v>
       </c>
       <c r="H20" t="n">
-        <v>103.08494</v>
+        <v>5.0804</v>
       </c>
       <c r="I20" t="n">
-        <v>110.61922</v>
+        <v>5.0798</v>
       </c>
       <c r="J20" t="n">
-        <v>5.0804</v>
+        <v>2154900</v>
       </c>
       <c r="K20" t="n">
-        <v>5.0798</v>
+        <v>3269910</v>
       </c>
       <c r="L20" t="n">
-        <v>5424811</v>
+        <v>3.35</v>
       </c>
       <c r="M20" t="n">
-        <v>2154900</v>
+        <v>2.2</v>
       </c>
       <c r="N20" t="n">
-        <v>3269910</v>
+        <v>30.99</v>
       </c>
       <c r="O20" t="n">
-        <v>3.35</v>
+        <v>341158</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>0.004919</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.11</v>
+        <v>12.135312</v>
       </c>
       <c r="R20" t="n">
-        <v>30.99</v>
+        <v>-2.446331</v>
       </c>
       <c r="S20" t="n">
-        <v>341158</v>
+        <v>-2.446612</v>
       </c>
       <c r="T20" t="n">
-        <v>0.004919</v>
+        <v>0.879872</v>
       </c>
       <c r="U20" t="n">
-        <v>12.135312</v>
+        <v>1.083978</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.446331</v>
+        <v>3.980518</v>
       </c>
       <c r="W20" t="n">
-        <v>-2.446612</v>
+        <v>0.172427</v>
       </c>
       <c r="X20" t="n">
-        <v>1.002821</v>
+        <v>4.361088</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.879872</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.083978</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.980518</v>
+        <v>-0.01</v>
       </c>
       <c r="AB20" t="n">
-        <v>4.650694</v>
+        <v>0.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.172427</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>4.361088</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AK20" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2669,105 +2201,81 @@
         <v>0.050788</v>
       </c>
       <c r="D21" t="n">
-        <v>0.050788</v>
+        <v>-0.95</v>
       </c>
       <c r="E21" t="n">
-        <v>0.61</v>
+        <v>0.53</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.95</v>
+        <v>103.93573</v>
       </c>
       <c r="G21" t="n">
-        <v>0.53</v>
+        <v>104.04095</v>
       </c>
       <c r="H21" t="n">
-        <v>103.93573</v>
+        <v>5.0007</v>
       </c>
       <c r="I21" t="n">
-        <v>104.04095</v>
+        <v>5.0001</v>
       </c>
       <c r="J21" t="n">
-        <v>5.0007</v>
+        <v>2145000</v>
       </c>
       <c r="K21" t="n">
-        <v>5.0001</v>
+        <v>3281308</v>
       </c>
       <c r="L21" t="n">
-        <v>5426307</v>
+        <v>3.54</v>
       </c>
       <c r="M21" t="n">
-        <v>2145000</v>
+        <v>2.45</v>
       </c>
       <c r="N21" t="n">
-        <v>3281308</v>
+        <v>31.62</v>
       </c>
       <c r="O21" t="n">
-        <v>3.54</v>
+        <v>345725</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>0.825329</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.26</v>
+        <v>-5.946769</v>
       </c>
       <c r="R21" t="n">
-        <v>31.62</v>
+        <v>-1.568774</v>
       </c>
       <c r="S21" t="n">
-        <v>345725</v>
+        <v>-1.568959</v>
       </c>
       <c r="T21" t="n">
-        <v>0.825329</v>
+        <v>-0.459418</v>
       </c>
       <c r="U21" t="n">
-        <v>-5.946769</v>
+        <v>0.348572</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.568774</v>
+        <v>1.338676</v>
       </c>
       <c r="W21" t="n">
-        <v>-1.568959</v>
+        <v>-2.158772</v>
       </c>
       <c r="X21" t="n">
-        <v>0.027577</v>
+        <v>3.834324</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.459418</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.348572</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.338676</v>
+        <v>0.19</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.184706</v>
+        <v>0.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.158772</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3.834324</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AK21" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -2782,105 +2290,81 @@
         <v>0.050788</v>
       </c>
       <c r="D22" t="n">
-        <v>0.050788</v>
+        <v>-1.84</v>
       </c>
       <c r="E22" t="n">
-        <v>0.23</v>
+        <v>0.36</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.84</v>
+        <v>102.42973</v>
       </c>
       <c r="G22" t="n">
-        <v>0.36</v>
+        <v>102.71375</v>
       </c>
       <c r="H22" t="n">
-        <v>102.42973</v>
+        <v>5.0959</v>
       </c>
       <c r="I22" t="n">
-        <v>102.71375</v>
+        <v>5.0953</v>
       </c>
       <c r="J22" t="n">
-        <v>5.0959</v>
+        <v>2145530</v>
       </c>
       <c r="K22" t="n">
-        <v>5.0953</v>
+        <v>3308178</v>
       </c>
       <c r="L22" t="n">
-        <v>5453708</v>
+        <v>3.65</v>
       </c>
       <c r="M22" t="n">
-        <v>2145530</v>
+        <v>2.58</v>
       </c>
       <c r="N22" t="n">
-        <v>3308178</v>
+        <v>31.63</v>
       </c>
       <c r="O22" t="n">
-        <v>3.65</v>
+        <v>343489</v>
       </c>
       <c r="P22" t="n">
-        <v>2.58</v>
+        <v>-1.448972</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.35</v>
+        <v>-1.275652</v>
       </c>
       <c r="R22" t="n">
-        <v>31.63</v>
+        <v>1.903733</v>
       </c>
       <c r="S22" t="n">
-        <v>343489</v>
+        <v>1.903962</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.448972</v>
+        <v>0.024709</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.275652</v>
+        <v>0.818881</v>
       </c>
       <c r="V22" t="n">
-        <v>1.903733</v>
+        <v>-0.646757</v>
       </c>
       <c r="W22" t="n">
-        <v>1.903962</v>
+        <v>-4.45588</v>
       </c>
       <c r="X22" t="n">
-        <v>0.504966</v>
+        <v>3.741292</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.024709</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.818881</v>
+        <v>-0</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0.646757</v>
+        <v>0.11</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.935832</v>
+        <v>0.13</v>
       </c>
       <c r="AC22" t="n">
-        <v>-4.45588</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.741292</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK22" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -2895,105 +2379,81 @@
         <v>0.050788</v>
       </c>
       <c r="D23" t="n">
-        <v>0.050788</v>
+        <v>-1.93</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.93</v>
+        <v>102.39935</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1</v>
+        <v>102.28352</v>
       </c>
       <c r="H23" t="n">
-        <v>102.39935</v>
+        <v>4.8192</v>
       </c>
       <c r="I23" t="n">
-        <v>102.28352</v>
+        <v>4.8186</v>
       </c>
       <c r="J23" t="n">
-        <v>4.8192</v>
+        <v>2169613</v>
       </c>
       <c r="K23" t="n">
-        <v>4.8186</v>
+        <v>3309846</v>
       </c>
       <c r="L23" t="n">
-        <v>5479459</v>
+        <v>3.61</v>
       </c>
       <c r="M23" t="n">
-        <v>2169613</v>
+        <v>2.63</v>
       </c>
       <c r="N23" t="n">
-        <v>3309846</v>
+        <v>30.85</v>
       </c>
       <c r="O23" t="n">
-        <v>3.61</v>
+        <v>343620</v>
       </c>
       <c r="P23" t="n">
-        <v>2.63</v>
+        <v>-0.029659</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.25</v>
+        <v>-0.418863</v>
       </c>
       <c r="R23" t="n">
-        <v>30.85</v>
+        <v>-5.429855</v>
       </c>
       <c r="S23" t="n">
-        <v>343620</v>
+        <v>-5.430495</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.029659</v>
+        <v>1.122473</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.418863</v>
+        <v>0.050421</v>
       </c>
       <c r="V23" t="n">
-        <v>-5.429855</v>
+        <v>0.038138</v>
       </c>
       <c r="W23" t="n">
-        <v>-5.430495</v>
+        <v>-6.84947</v>
       </c>
       <c r="X23" t="n">
-        <v>0.472174</v>
+        <v>2.998957</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.122473</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.050421</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.038138</v>
+        <v>-0.04</v>
       </c>
       <c r="AB23" t="n">
-        <v>3.161501</v>
+        <v>0.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6.84947</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.998957</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AK23" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -3008,105 +2468,81 @@
         <v>0.050788</v>
       </c>
       <c r="D24" t="n">
-        <v>0.050788</v>
+        <v>-0.72</v>
       </c>
       <c r="E24" t="n">
-        <v>0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.72</v>
+        <v>102.90686</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.09</v>
+        <v>105.34474</v>
       </c>
       <c r="H24" t="n">
-        <v>102.90686</v>
+        <v>4.7415</v>
       </c>
       <c r="I24" t="n">
-        <v>105.34474</v>
+        <v>4.7409</v>
       </c>
       <c r="J24" t="n">
-        <v>4.7415</v>
+        <v>2153541</v>
       </c>
       <c r="K24" t="n">
-        <v>4.7409</v>
+        <v>3331330</v>
       </c>
       <c r="L24" t="n">
-        <v>5484871</v>
+        <v>3.63</v>
       </c>
       <c r="M24" t="n">
-        <v>2153541</v>
+        <v>2.73</v>
       </c>
       <c r="N24" t="n">
-        <v>3331330</v>
+        <v>30.43</v>
       </c>
       <c r="O24" t="n">
-        <v>3.63</v>
+        <v>345476</v>
       </c>
       <c r="P24" t="n">
-        <v>2.73</v>
+        <v>0.495618</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.22</v>
+        <v>2.992877</v>
       </c>
       <c r="R24" t="n">
-        <v>30.43</v>
+        <v>-1.612301</v>
       </c>
       <c r="S24" t="n">
-        <v>345476</v>
+        <v>-1.612502</v>
       </c>
       <c r="T24" t="n">
-        <v>0.495618</v>
+        <v>-0.740777</v>
       </c>
       <c r="U24" t="n">
-        <v>2.992877</v>
+        <v>0.6490939999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.612301</v>
+        <v>0.5401319999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>-1.612502</v>
+        <v>-7.713954</v>
       </c>
       <c r="X24" t="n">
-        <v>0.098769</v>
+        <v>3.527423</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.740777</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.6490939999999999</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.5401319999999999</v>
+        <v>0.02</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.992444</v>
+        <v>0.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>-7.713954</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3.527423</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK24" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3121,105 +2557,81 @@
         <v>0.049189</v>
       </c>
       <c r="D25" t="n">
-        <v>0.049189</v>
+        <v>-0.14</v>
       </c>
       <c r="E25" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.14</v>
+        <v>102.50239</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2</v>
+        <v>106.05687</v>
       </c>
       <c r="H25" t="n">
-        <v>102.50239</v>
+        <v>4.9219</v>
       </c>
       <c r="I25" t="n">
-        <v>106.05687</v>
+        <v>4.9213</v>
       </c>
       <c r="J25" t="n">
-        <v>4.9219</v>
+        <v>2172658</v>
       </c>
       <c r="K25" t="n">
-        <v>4.9213</v>
+        <v>3386405</v>
       </c>
       <c r="L25" t="n">
-        <v>5559063</v>
+        <v>3.61</v>
       </c>
       <c r="M25" t="n">
-        <v>2172658</v>
+        <v>2.82</v>
       </c>
       <c r="N25" t="n">
-        <v>3386405</v>
+        <v>29.92</v>
       </c>
       <c r="O25" t="n">
-        <v>3.61</v>
+        <v>344177</v>
       </c>
       <c r="P25" t="n">
-        <v>2.82</v>
+        <v>-0.393045</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.12</v>
+        <v>0.676</v>
       </c>
       <c r="R25" t="n">
-        <v>29.92</v>
+        <v>3.804703</v>
       </c>
       <c r="S25" t="n">
-        <v>344177</v>
+        <v>3.805185</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.393045</v>
+        <v>0.887701</v>
       </c>
       <c r="U25" t="n">
-        <v>0.676</v>
+        <v>1.653244</v>
       </c>
       <c r="V25" t="n">
-        <v>3.804703</v>
+        <v>-0.376003</v>
       </c>
       <c r="W25" t="n">
-        <v>3.805185</v>
+        <v>-7.193509</v>
       </c>
       <c r="X25" t="n">
-        <v>1.352666</v>
+        <v>4.057054</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.887701</v>
+        <v>-0.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.653244</v>
+        <v>-0.001599</v>
       </c>
       <c r="AA25" t="n">
-        <v>-0.376003</v>
+        <v>-0.02</v>
       </c>
       <c r="AB25" t="n">
-        <v>4.608216</v>
+        <v>0.09</v>
       </c>
       <c r="AC25" t="n">
-        <v>-7.193509</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>4.057054</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>-0.001599</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>-0.001599</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AK25" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -3234,105 +2646,81 @@
         <v>0.048422</v>
       </c>
       <c r="D26" t="n">
-        <v>0.048422</v>
+        <v>0.37</v>
       </c>
       <c r="E26" t="n">
-        <v>0.26</v>
+        <v>0.11</v>
       </c>
       <c r="F26" t="n">
-        <v>0.37</v>
+        <v>102.5153</v>
       </c>
       <c r="G26" t="n">
-        <v>0.11</v>
+        <v>101.75897</v>
       </c>
       <c r="H26" t="n">
-        <v>102.5153</v>
+        <v>5.0076</v>
       </c>
       <c r="I26" t="n">
-        <v>101.75897</v>
+        <v>5.007</v>
       </c>
       <c r="J26" t="n">
-        <v>5.0076</v>
+        <v>2215175</v>
       </c>
       <c r="K26" t="n">
-        <v>5.007</v>
+        <v>3410769</v>
       </c>
       <c r="L26" t="n">
-        <v>5625945</v>
+        <v>3.54</v>
       </c>
       <c r="M26" t="n">
-        <v>2215175</v>
+        <v>2.82</v>
       </c>
       <c r="N26" t="n">
-        <v>3410769</v>
+        <v>29.66</v>
       </c>
       <c r="O26" t="n">
-        <v>3.54</v>
+        <v>340324</v>
       </c>
       <c r="P26" t="n">
-        <v>2.82</v>
+        <v>0.012595</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>-4.052448</v>
       </c>
       <c r="R26" t="n">
-        <v>29.66</v>
+        <v>1.741198</v>
       </c>
       <c r="S26" t="n">
-        <v>340324</v>
+        <v>1.74141</v>
       </c>
       <c r="T26" t="n">
-        <v>0.012595</v>
+        <v>1.956912</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.052448</v>
+        <v>0.719465</v>
       </c>
       <c r="V26" t="n">
-        <v>1.741198</v>
+        <v>-1.119482</v>
       </c>
       <c r="W26" t="n">
-        <v>1.74141</v>
+        <v>-5.956714</v>
       </c>
       <c r="X26" t="n">
-        <v>1.203116</v>
+        <v>4.505936</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.956912</v>
+        <v>-0.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.719465</v>
+        <v>-0.000768</v>
       </c>
       <c r="AA26" t="n">
-        <v>-1.119482</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AB26" t="n">
-        <v>5.185235</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>-5.956714</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>4.505936</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>-0.000768</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>-0.000768</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK26" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -3347,105 +2735,81 @@
         <v>0.047279</v>
       </c>
       <c r="D27" t="n">
-        <v>0.047279</v>
+        <v>0.5</v>
       </c>
       <c r="E27" t="n">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5</v>
+        <v>102.83959</v>
       </c>
       <c r="G27" t="n">
-        <v>0.12</v>
+        <v>101.9338</v>
       </c>
       <c r="H27" t="n">
-        <v>102.83959</v>
+        <v>5.0575</v>
       </c>
       <c r="I27" t="n">
-        <v>101.9338</v>
+        <v>5.0569</v>
       </c>
       <c r="J27" t="n">
-        <v>5.0575</v>
+        <v>2204808</v>
       </c>
       <c r="K27" t="n">
-        <v>5.0569</v>
+        <v>3449000</v>
       </c>
       <c r="L27" t="n">
-        <v>5653808</v>
+        <v>3.56</v>
       </c>
       <c r="M27" t="n">
-        <v>2204808</v>
+        <v>2.92</v>
       </c>
       <c r="N27" t="n">
-        <v>3449000</v>
+        <v>29.24</v>
       </c>
       <c r="O27" t="n">
-        <v>3.56</v>
+        <v>340247</v>
       </c>
       <c r="P27" t="n">
-        <v>2.92</v>
+        <v>0.316333</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.97</v>
+        <v>0.171808</v>
       </c>
       <c r="R27" t="n">
-        <v>29.24</v>
+        <v>0.996485</v>
       </c>
       <c r="S27" t="n">
-        <v>340247</v>
+        <v>0.996605</v>
       </c>
       <c r="T27" t="n">
-        <v>0.316333</v>
+        <v>-0.467999</v>
       </c>
       <c r="U27" t="n">
-        <v>0.171808</v>
+        <v>1.120891</v>
       </c>
       <c r="V27" t="n">
-        <v>0.996485</v>
+        <v>-0.022625</v>
       </c>
       <c r="W27" t="n">
-        <v>0.996605</v>
+        <v>-4.560737</v>
       </c>
       <c r="X27" t="n">
-        <v>0.495259</v>
+        <v>4.141877</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.467999</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.120891</v>
+        <v>-0.001143</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.022625</v>
+        <v>0.02</v>
       </c>
       <c r="AB27" t="n">
-        <v>4.819246</v>
+        <v>0.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4.560737</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>4.141877</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>-0.001143</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>-0.001143</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK27" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3460,105 +2824,81 @@
         <v>0.045601</v>
       </c>
       <c r="D28" t="n">
-        <v>0.045601</v>
+        <v>0.59</v>
       </c>
       <c r="E28" t="n">
-        <v>0.28</v>
+        <v>0.1</v>
       </c>
       <c r="F28" t="n">
-        <v>0.59</v>
+        <v>103.59456</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1</v>
+        <v>101.68042</v>
       </c>
       <c r="H28" t="n">
-        <v>103.59456</v>
+        <v>4.9355</v>
       </c>
       <c r="I28" t="n">
-        <v>101.68042</v>
+        <v>4.9349</v>
       </c>
       <c r="J28" t="n">
-        <v>4.9355</v>
+        <v>2220766</v>
       </c>
       <c r="K28" t="n">
-        <v>4.9349</v>
+        <v>3490337</v>
       </c>
       <c r="L28" t="n">
-        <v>5711103</v>
+        <v>3.53</v>
       </c>
       <c r="M28" t="n">
-        <v>2220766</v>
+        <v>2.99</v>
       </c>
       <c r="N28" t="n">
-        <v>3490337</v>
+        <v>29.01</v>
       </c>
       <c r="O28" t="n">
-        <v>3.53</v>
+        <v>348406</v>
       </c>
       <c r="P28" t="n">
-        <v>2.99</v>
+        <v>0.734124</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.88</v>
+        <v>-0.248573</v>
       </c>
       <c r="R28" t="n">
-        <v>29.01</v>
+        <v>-2.412259</v>
       </c>
       <c r="S28" t="n">
-        <v>348406</v>
+        <v>-2.412545</v>
       </c>
       <c r="T28" t="n">
-        <v>0.734124</v>
+        <v>0.723782</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.248573</v>
+        <v>1.198521</v>
       </c>
       <c r="V28" t="n">
-        <v>-2.412259</v>
+        <v>2.397964</v>
       </c>
       <c r="W28" t="n">
-        <v>-2.412545</v>
+        <v>-3.457004</v>
       </c>
       <c r="X28" t="n">
-        <v>1.013388</v>
+        <v>3.851383</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.723782</v>
+        <v>-0.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.198521</v>
+        <v>-0.001678</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.397964</v>
+        <v>-0.03</v>
       </c>
       <c r="AB28" t="n">
-        <v>4.683537</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AC28" t="n">
-        <v>-3.457004</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>3.851383</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>-0.001678</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>-0.001678</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="AK28" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -3573,105 +2913,81 @@
         <v>0.044537</v>
       </c>
       <c r="D29" t="n">
-        <v>0.044537</v>
+        <v>0.74</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="F29" t="n">
-        <v>0.74</v>
+        <v>104.88818</v>
       </c>
       <c r="G29" t="n">
-        <v>0.55</v>
+        <v>101.68469</v>
       </c>
       <c r="H29" t="n">
-        <v>104.88818</v>
+        <v>4.8413</v>
       </c>
       <c r="I29" t="n">
-        <v>101.68469</v>
+        <v>4.8407</v>
       </c>
       <c r="J29" t="n">
-        <v>4.8413</v>
+        <v>2283485</v>
       </c>
       <c r="K29" t="n">
-        <v>4.8407</v>
+        <v>3521672</v>
       </c>
       <c r="L29" t="n">
-        <v>5805157</v>
+        <v>3.29</v>
       </c>
       <c r="M29" t="n">
-        <v>2283485</v>
+        <v>2.59</v>
       </c>
       <c r="N29" t="n">
-        <v>3521672</v>
+        <v>28.14</v>
       </c>
       <c r="O29" t="n">
-        <v>3.29</v>
+        <v>355034</v>
       </c>
       <c r="P29" t="n">
-        <v>2.59</v>
+        <v>1.248734</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.75</v>
+        <v>0.004199</v>
       </c>
       <c r="R29" t="n">
-        <v>28.14</v>
+        <v>-1.908621</v>
       </c>
       <c r="S29" t="n">
-        <v>355034</v>
+        <v>-1.908853</v>
       </c>
       <c r="T29" t="n">
-        <v>1.248734</v>
+        <v>2.824206</v>
       </c>
       <c r="U29" t="n">
-        <v>0.004199</v>
+        <v>0.897764</v>
       </c>
       <c r="V29" t="n">
-        <v>-1.908621</v>
+        <v>1.902378</v>
       </c>
       <c r="W29" t="n">
-        <v>-1.908853</v>
+        <v>-3.178284</v>
       </c>
       <c r="X29" t="n">
-        <v>1.646862</v>
+        <v>3.706988</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.824206</v>
+        <v>-0.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.897764</v>
+        <v>-0.001064</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.902378</v>
+        <v>-0.24</v>
       </c>
       <c r="AB29" t="n">
-        <v>4.621114</v>
+        <v>-0.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.178284</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>3.706988</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>-0.001064</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>-0.001064</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="AK29" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3686,105 +3002,81 @@
         <v>0.043739</v>
       </c>
       <c r="D30" t="n">
-        <v>0.043739</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>0.42</v>
+        <v>0.57</v>
       </c>
       <c r="F30" t="n">
-        <v>0.07000000000000001</v>
+        <v>104.473</v>
       </c>
       <c r="G30" t="n">
-        <v>0.57</v>
+        <v>99.29718</v>
       </c>
       <c r="H30" t="n">
-        <v>104.473</v>
+        <v>4.9535</v>
       </c>
       <c r="I30" t="n">
-        <v>99.29718</v>
+        <v>4.9529</v>
       </c>
       <c r="J30" t="n">
-        <v>4.9535</v>
+        <v>2234362</v>
       </c>
       <c r="K30" t="n">
-        <v>4.9529</v>
+        <v>3560345</v>
       </c>
       <c r="L30" t="n">
-        <v>5794707</v>
+        <v>3.38</v>
       </c>
       <c r="M30" t="n">
-        <v>2234362</v>
+        <v>2.77</v>
       </c>
       <c r="N30" t="n">
-        <v>3560345</v>
+        <v>28</v>
       </c>
       <c r="O30" t="n">
-        <v>3.38</v>
+        <v>355066</v>
       </c>
       <c r="P30" t="n">
-        <v>2.77</v>
+        <v>-0.395831</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.76</v>
+        <v>-2.347954</v>
       </c>
       <c r="R30" t="n">
-        <v>28</v>
+        <v>2.317559</v>
       </c>
       <c r="S30" t="n">
-        <v>355066</v>
+        <v>2.317847</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.395831</v>
+        <v>-2.151229</v>
       </c>
       <c r="U30" t="n">
-        <v>-2.347954</v>
+        <v>1.098143</v>
       </c>
       <c r="V30" t="n">
-        <v>2.317559</v>
+        <v>0.009013</v>
       </c>
       <c r="W30" t="n">
-        <v>2.317847</v>
+        <v>-3.31355</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.180012</v>
+        <v>3.820543</v>
       </c>
       <c r="Y30" t="n">
-        <v>-2.151229</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.098143</v>
+        <v>-0.000798</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.009013</v>
+        <v>0.09</v>
       </c>
       <c r="AB30" t="n">
-        <v>4.506637</v>
+        <v>0.18</v>
       </c>
       <c r="AC30" t="n">
-        <v>-3.31355</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>3.820543</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>-0.000798</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>-0.000798</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK30" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -3799,105 +3091,81 @@
         <v>0.041957</v>
       </c>
       <c r="D31" t="n">
-        <v>0.041957</v>
+        <v>-0.52</v>
       </c>
       <c r="E31" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.52</v>
+        <v>104.65885</v>
       </c>
       <c r="G31" t="n">
-        <v>0.8100000000000001</v>
+        <v>102.15036</v>
       </c>
       <c r="H31" t="n">
-        <v>104.65885</v>
+        <v>4.9833</v>
       </c>
       <c r="I31" t="n">
-        <v>102.15036</v>
+        <v>4.9827</v>
       </c>
       <c r="J31" t="n">
-        <v>4.9833</v>
+        <v>2235302</v>
       </c>
       <c r="K31" t="n">
-        <v>4.9827</v>
+        <v>3580652</v>
       </c>
       <c r="L31" t="n">
-        <v>5815954</v>
+        <v>3.38</v>
       </c>
       <c r="M31" t="n">
-        <v>2235302</v>
+        <v>2.76</v>
       </c>
       <c r="N31" t="n">
-        <v>3580652</v>
+        <v>27.85</v>
       </c>
       <c r="O31" t="n">
-        <v>3.38</v>
+        <v>352705</v>
       </c>
       <c r="P31" t="n">
-        <v>2.76</v>
+        <v>0.177893</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.76</v>
+        <v>2.873375</v>
       </c>
       <c r="R31" t="n">
-        <v>27.85</v>
+        <v>0.601595</v>
       </c>
       <c r="S31" t="n">
-        <v>352705</v>
+        <v>0.601668</v>
       </c>
       <c r="T31" t="n">
-        <v>0.177893</v>
+        <v>0.04207</v>
       </c>
       <c r="U31" t="n">
-        <v>2.873375</v>
+        <v>0.570366</v>
       </c>
       <c r="V31" t="n">
-        <v>0.601595</v>
+        <v>-0.664947</v>
       </c>
       <c r="W31" t="n">
-        <v>0.601668</v>
+        <v>-3.758575</v>
       </c>
       <c r="X31" t="n">
-        <v>0.366662</v>
+        <v>3.861754</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.04207</v>
+        <v>-0.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.570366</v>
+        <v>-0.001782</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.664947</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>4.496274</v>
+        <v>-0.01</v>
       </c>
       <c r="AC31" t="n">
-        <v>-3.758575</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>3.861754</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>-0.001782</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>-0.001782</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -3912,105 +3180,81 @@
         <v>0.04142</v>
       </c>
       <c r="D32" t="n">
-        <v>0.04142</v>
+        <v>-0.47</v>
       </c>
       <c r="E32" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.47</v>
+        <v>104.6738</v>
       </c>
       <c r="G32" t="n">
-        <v>0.19</v>
+        <v>109.56901</v>
       </c>
       <c r="H32" t="n">
-        <v>104.6738</v>
+        <v>4.9962</v>
       </c>
       <c r="I32" t="n">
-        <v>109.56901</v>
+        <v>4.9956</v>
       </c>
       <c r="J32" t="n">
-        <v>4.9962</v>
+        <v>2285775</v>
       </c>
       <c r="K32" t="n">
-        <v>4.9956</v>
+        <v>3613967</v>
       </c>
       <c r="L32" t="n">
-        <v>5899742</v>
+        <v>3.33</v>
       </c>
       <c r="M32" t="n">
-        <v>2285775</v>
+        <v>2.71</v>
       </c>
       <c r="N32" t="n">
-        <v>3613967</v>
+        <v>28.14</v>
       </c>
       <c r="O32" t="n">
-        <v>3.33</v>
+        <v>355008</v>
       </c>
       <c r="P32" t="n">
-        <v>2.71</v>
+        <v>0.014285</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.71</v>
+        <v>7.262481</v>
       </c>
       <c r="R32" t="n">
-        <v>28.14</v>
+        <v>0.258865</v>
       </c>
       <c r="S32" t="n">
-        <v>355008</v>
+        <v>0.258896</v>
       </c>
       <c r="T32" t="n">
-        <v>0.014285</v>
+        <v>2.257995</v>
       </c>
       <c r="U32" t="n">
-        <v>7.262481</v>
+        <v>0.930417</v>
       </c>
       <c r="V32" t="n">
-        <v>0.258865</v>
+        <v>0.652954</v>
       </c>
       <c r="W32" t="n">
-        <v>0.258896</v>
+        <v>-4.25878</v>
       </c>
       <c r="X32" t="n">
-        <v>1.440658</v>
+        <v>3.397348</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.257995</v>
+        <v>-0.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.930417</v>
+        <v>-0.000537</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.652954</v>
+        <v>-0.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>3.925596</v>
+        <v>-0.05</v>
       </c>
       <c r="AC32" t="n">
-        <v>-4.25878</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3.397348</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>-0.000537</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>-0.000537</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AK32" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -4025,105 +3269,81 @@
         <v>0.040168</v>
       </c>
       <c r="D33" t="n">
-        <v>0.040168</v>
+        <v>0.31</v>
       </c>
       <c r="E33" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="F33" t="n">
-        <v>0.31</v>
+        <v>104.62771</v>
       </c>
       <c r="G33" t="n">
-        <v>0.37</v>
+        <v>109.2572</v>
       </c>
       <c r="H33" t="n">
-        <v>104.62771</v>
+        <v>5.1718</v>
       </c>
       <c r="I33" t="n">
-        <v>109.2572</v>
+        <v>5.1712</v>
       </c>
       <c r="J33" t="n">
-        <v>5.1718</v>
+        <v>2268879</v>
       </c>
       <c r="K33" t="n">
-        <v>5.1712</v>
+        <v>3646659</v>
       </c>
       <c r="L33" t="n">
-        <v>5915538</v>
+        <v>3.37</v>
       </c>
       <c r="M33" t="n">
-        <v>2268879</v>
+        <v>2.76</v>
       </c>
       <c r="N33" t="n">
-        <v>3646659</v>
+        <v>27.86</v>
       </c>
       <c r="O33" t="n">
-        <v>3.37</v>
+        <v>351599</v>
       </c>
       <c r="P33" t="n">
-        <v>2.76</v>
+        <v>-0.044032</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.75</v>
+        <v>-0.284579</v>
       </c>
       <c r="R33" t="n">
-        <v>27.86</v>
+        <v>3.514671</v>
       </c>
       <c r="S33" t="n">
-        <v>351599</v>
+        <v>3.515093</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.044032</v>
+        <v>-0.7391799999999999</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.284579</v>
+        <v>0.904602</v>
       </c>
       <c r="V33" t="n">
-        <v>3.514671</v>
+        <v>-0.96026</v>
       </c>
       <c r="W33" t="n">
-        <v>3.515093</v>
+        <v>-3.040871</v>
       </c>
       <c r="X33" t="n">
-        <v>0.267741</v>
+        <v>3.232784</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.7391799999999999</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.904602</v>
+        <v>-0.001252</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.96026</v>
+        <v>0.04</v>
       </c>
       <c r="AB33" t="n">
-        <v>3.688016</v>
+        <v>0.05</v>
       </c>
       <c r="AC33" t="n">
-        <v>-3.040871</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>3.232784</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>-0.001252</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>-0.001252</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK33" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -4138,105 +3358,81 @@
         <v>0.039484</v>
       </c>
       <c r="D34" t="n">
-        <v>0.039484</v>
+        <v>0.89</v>
       </c>
       <c r="E34" t="n">
         <v>0.46</v>
       </c>
       <c r="F34" t="n">
-        <v>0.89</v>
+        <v>105.60427</v>
       </c>
       <c r="G34" t="n">
-        <v>0.46</v>
+        <v>104.71213</v>
       </c>
       <c r="H34" t="n">
-        <v>105.60427</v>
+        <v>5.2416</v>
       </c>
       <c r="I34" t="n">
-        <v>104.71213</v>
+        <v>5.241</v>
       </c>
       <c r="J34" t="n">
-        <v>5.2416</v>
+        <v>2278309</v>
       </c>
       <c r="K34" t="n">
-        <v>5.241</v>
+        <v>3675652</v>
       </c>
       <c r="L34" t="n">
-        <v>5953960</v>
+        <v>3.43</v>
       </c>
       <c r="M34" t="n">
-        <v>2278309</v>
+        <v>2.8</v>
       </c>
       <c r="N34" t="n">
-        <v>3675652</v>
+        <v>27.75</v>
       </c>
       <c r="O34" t="n">
-        <v>3.43</v>
+        <v>355560</v>
       </c>
       <c r="P34" t="n">
-        <v>2.8</v>
+        <v>0.9333669999999999</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.82</v>
+        <v>-4.159973</v>
       </c>
       <c r="R34" t="n">
-        <v>27.75</v>
+        <v>1.349627</v>
       </c>
       <c r="S34" t="n">
-        <v>355560</v>
+        <v>1.349783</v>
       </c>
       <c r="T34" t="n">
-        <v>0.9333669999999999</v>
+        <v>0.415624</v>
       </c>
       <c r="U34" t="n">
-        <v>-4.159973</v>
+        <v>0.795057</v>
       </c>
       <c r="V34" t="n">
-        <v>1.349627</v>
+        <v>1.126567</v>
       </c>
       <c r="W34" t="n">
-        <v>1.349783</v>
+        <v>-0.344269</v>
       </c>
       <c r="X34" t="n">
-        <v>0.64951</v>
+        <v>3.335647</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.415624</v>
+        <v>-0.25</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.795057</v>
+        <v>-0.000684</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.126567</v>
+        <v>0.06</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.925952</v>
+        <v>0.04</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.344269</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>3.335647</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>-0.000684</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>-0.000684</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK34" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -4251,105 +3447,81 @@
         <v>0.03927</v>
       </c>
       <c r="D35" t="n">
-        <v>0.03927</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8100000000000001</v>
+        <v>106.5891</v>
       </c>
       <c r="G35" t="n">
-        <v>0.25</v>
+        <v>105.86915</v>
       </c>
       <c r="H35" t="n">
-        <v>106.5891</v>
+        <v>5.5589</v>
       </c>
       <c r="I35" t="n">
-        <v>105.86915</v>
+        <v>5.5583</v>
       </c>
       <c r="J35" t="n">
-        <v>5.5589</v>
+        <v>2336858</v>
       </c>
       <c r="K35" t="n">
-        <v>5.5583</v>
+        <v>3705041</v>
       </c>
       <c r="L35" t="n">
-        <v>6041898</v>
+        <v>3.29</v>
       </c>
       <c r="M35" t="n">
-        <v>2336858</v>
+        <v>2.64</v>
       </c>
       <c r="N35" t="n">
-        <v>3705041</v>
+        <v>27.81</v>
       </c>
       <c r="O35" t="n">
-        <v>3.29</v>
+        <v>357827</v>
       </c>
       <c r="P35" t="n">
-        <v>2.64</v>
+        <v>0.932566</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.71</v>
+        <v>1.104953</v>
       </c>
       <c r="R35" t="n">
-        <v>27.81</v>
+        <v>6.053495</v>
       </c>
       <c r="S35" t="n">
-        <v>357827</v>
+        <v>6.054188</v>
       </c>
       <c r="T35" t="n">
-        <v>0.932566</v>
+        <v>2.569845</v>
       </c>
       <c r="U35" t="n">
-        <v>1.104953</v>
+        <v>0.799559</v>
       </c>
       <c r="V35" t="n">
-        <v>6.053495</v>
+        <v>0.637586</v>
       </c>
       <c r="W35" t="n">
-        <v>6.054188</v>
+        <v>2.440035</v>
       </c>
       <c r="X35" t="n">
-        <v>1.476967</v>
+        <v>3.697684</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.569845</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.799559</v>
+        <v>-0.000214</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.637586</v>
+        <v>-0.14</v>
       </c>
       <c r="AB35" t="n">
-        <v>4.227578</v>
+        <v>-0.16</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.440035</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>3.697684</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>-0.000214</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>-0.000214</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="AK35" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -4364,105 +3536,81 @@
         <v>0.03927</v>
       </c>
       <c r="D36" t="n">
-        <v>0.03927</v>
+        <v>0.61</v>
       </c>
       <c r="E36" t="n">
-        <v>0.38</v>
+        <v>0.26</v>
       </c>
       <c r="F36" t="n">
-        <v>0.61</v>
+        <v>107.06237</v>
       </c>
       <c r="G36" t="n">
-        <v>0.26</v>
+        <v>111.509</v>
       </c>
       <c r="H36" t="n">
-        <v>107.06237</v>
+        <v>5.6621</v>
       </c>
       <c r="I36" t="n">
-        <v>111.509</v>
+        <v>5.6615</v>
       </c>
       <c r="J36" t="n">
-        <v>5.6621</v>
+        <v>2323362</v>
       </c>
       <c r="K36" t="n">
-        <v>5.6615</v>
+        <v>3745844</v>
       </c>
       <c r="L36" t="n">
-        <v>6069205</v>
+        <v>3.3</v>
       </c>
       <c r="M36" t="n">
-        <v>2323362</v>
+        <v>2.52</v>
       </c>
       <c r="N36" t="n">
-        <v>3745844</v>
+        <v>27.74</v>
       </c>
       <c r="O36" t="n">
-        <v>3.3</v>
+        <v>363282</v>
       </c>
       <c r="P36" t="n">
-        <v>2.52</v>
+        <v>0.444014</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.78</v>
+        <v>5.327189</v>
       </c>
       <c r="R36" t="n">
-        <v>27.74</v>
+        <v>1.856482</v>
       </c>
       <c r="S36" t="n">
-        <v>363282</v>
+        <v>1.856683</v>
       </c>
       <c r="T36" t="n">
-        <v>0.444014</v>
+        <v>-0.577528</v>
       </c>
       <c r="U36" t="n">
-        <v>5.327189</v>
+        <v>1.101283</v>
       </c>
       <c r="V36" t="n">
-        <v>1.856482</v>
+        <v>1.52448</v>
       </c>
       <c r="W36" t="n">
-        <v>1.856683</v>
+        <v>3.812368</v>
       </c>
       <c r="X36" t="n">
-        <v>0.451961</v>
+        <v>4.060953</v>
       </c>
       <c r="Y36" t="n">
-        <v>-0.577528</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.101283</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.52448</v>
+        <v>0.01</v>
       </c>
       <c r="AB36" t="n">
-        <v>4.498245</v>
+        <v>-0.12</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.812368</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>4.060953</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK36" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -4477,105 +3625,81 @@
         <v>0.03927</v>
       </c>
       <c r="D37" t="n">
-        <v>0.03927</v>
+        <v>0.29</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.02</v>
+        <v>-0.14</v>
       </c>
       <c r="F37" t="n">
-        <v>0.29</v>
+        <v>107.19174</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.14</v>
+        <v>110.06254</v>
       </c>
       <c r="H37" t="n">
-        <v>107.19174</v>
+        <v>5.6562</v>
       </c>
       <c r="I37" t="n">
-        <v>110.06254</v>
+        <v>5.6556</v>
       </c>
       <c r="J37" t="n">
-        <v>5.6562</v>
+        <v>2344397</v>
       </c>
       <c r="K37" t="n">
-        <v>5.6556</v>
+        <v>3790900</v>
       </c>
       <c r="L37" t="n">
-        <v>6135298</v>
+        <v>3.33</v>
       </c>
       <c r="M37" t="n">
-        <v>2344397</v>
+        <v>2.55</v>
       </c>
       <c r="N37" t="n">
-        <v>3790900</v>
+        <v>27.59</v>
       </c>
       <c r="O37" t="n">
-        <v>3.33</v>
+        <v>369214</v>
       </c>
       <c r="P37" t="n">
-        <v>2.55</v>
+        <v>0.120836</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.82</v>
+        <v>-1.297169</v>
       </c>
       <c r="R37" t="n">
-        <v>27.59</v>
+        <v>-0.104202</v>
       </c>
       <c r="S37" t="n">
-        <v>369214</v>
+        <v>-0.104213</v>
       </c>
       <c r="T37" t="n">
-        <v>0.120836</v>
+        <v>0.905369</v>
       </c>
       <c r="U37" t="n">
-        <v>-1.297169</v>
+        <v>1.202826</v>
       </c>
       <c r="V37" t="n">
-        <v>-0.104202</v>
+        <v>1.632891</v>
       </c>
       <c r="W37" t="n">
-        <v>-0.104213</v>
+        <v>4.259387</v>
       </c>
       <c r="X37" t="n">
-        <v>1.088989</v>
+        <v>3.707852</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.905369</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.202826</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.632891</v>
+        <v>0.03</v>
       </c>
       <c r="AB37" t="n">
-        <v>4.237599</v>
+        <v>0.03</v>
       </c>
       <c r="AC37" t="n">
-        <v>4.259387</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>3.707852</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK37" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4590,105 +3714,81 @@
         <v>0.039612</v>
       </c>
       <c r="D38" t="n">
-        <v>0.039612</v>
+        <v>0.62</v>
       </c>
       <c r="E38" t="n">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="F38" t="n">
-        <v>0.62</v>
+        <v>108.04382</v>
       </c>
       <c r="G38" t="n">
-        <v>0.48</v>
+        <v>107.07852</v>
       </c>
       <c r="H38" t="n">
-        <v>108.04382</v>
+        <v>5.4481</v>
       </c>
       <c r="I38" t="n">
-        <v>107.07852</v>
+        <v>5.4475</v>
       </c>
       <c r="J38" t="n">
-        <v>5.4481</v>
+        <v>2384828</v>
       </c>
       <c r="K38" t="n">
-        <v>5.4475</v>
+        <v>3831700</v>
       </c>
       <c r="L38" t="n">
-        <v>6216528</v>
+        <v>3.34</v>
       </c>
       <c r="M38" t="n">
-        <v>2384828</v>
+        <v>2.56</v>
       </c>
       <c r="N38" t="n">
-        <v>3831700</v>
+        <v>27.49</v>
       </c>
       <c r="O38" t="n">
-        <v>3.34</v>
+        <v>372016</v>
       </c>
       <c r="P38" t="n">
-        <v>2.56</v>
+        <v>0.794912</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.83</v>
+        <v>-2.711204</v>
       </c>
       <c r="R38" t="n">
-        <v>27.49</v>
+        <v>-3.679149</v>
       </c>
       <c r="S38" t="n">
-        <v>372016</v>
+        <v>-3.679539</v>
       </c>
       <c r="T38" t="n">
-        <v>0.794912</v>
+        <v>1.72458</v>
       </c>
       <c r="U38" t="n">
-        <v>-2.711204</v>
+        <v>1.076262</v>
       </c>
       <c r="V38" t="n">
-        <v>-3.679149</v>
+        <v>0.7589089999999999</v>
       </c>
       <c r="W38" t="n">
-        <v>-3.679539</v>
+        <v>4.519075</v>
       </c>
       <c r="X38" t="n">
-        <v>1.323978</v>
+        <v>4.091149</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.72458</v>
+        <v>0.25</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.076262</v>
+        <v>0.000342</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.7589089999999999</v>
+        <v>0.01</v>
       </c>
       <c r="AB38" t="n">
-        <v>4.42474</v>
+        <v>0.01</v>
       </c>
       <c r="AC38" t="n">
-        <v>4.519075</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>4.091149</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0.000342</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0.000342</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK38" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -4703,105 +3803,81 @@
         <v>0.040168</v>
       </c>
       <c r="D39" t="n">
-        <v>0.040168</v>
+        <v>1.52</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="F39" t="n">
-        <v>1.52</v>
+        <v>108.2446</v>
       </c>
       <c r="G39" t="n">
-        <v>0.61</v>
+        <v>109.18379</v>
       </c>
       <c r="H39" t="n">
-        <v>108.2446</v>
+        <v>5.7779</v>
       </c>
       <c r="I39" t="n">
-        <v>109.18379</v>
+        <v>5.7773</v>
       </c>
       <c r="J39" t="n">
-        <v>5.7779</v>
+        <v>2397533</v>
       </c>
       <c r="K39" t="n">
-        <v>5.7773</v>
+        <v>3877584</v>
       </c>
       <c r="L39" t="n">
-        <v>6275117</v>
+        <v>3.3</v>
       </c>
       <c r="M39" t="n">
-        <v>2397533</v>
+        <v>2.52</v>
       </c>
       <c r="N39" t="n">
-        <v>3877584</v>
+        <v>27.94</v>
       </c>
       <c r="O39" t="n">
-        <v>3.3</v>
+        <v>366096</v>
       </c>
       <c r="P39" t="n">
-        <v>2.52</v>
+        <v>0.185832</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.79</v>
+        <v>1.966099</v>
       </c>
       <c r="R39" t="n">
-        <v>27.94</v>
+        <v>6.053487</v>
       </c>
       <c r="S39" t="n">
-        <v>366096</v>
+        <v>6.054153</v>
       </c>
       <c r="T39" t="n">
-        <v>0.185832</v>
+        <v>0.532743</v>
       </c>
       <c r="U39" t="n">
-        <v>1.966099</v>
+        <v>1.197484</v>
       </c>
       <c r="V39" t="n">
-        <v>6.053487</v>
+        <v>-1.591329</v>
       </c>
       <c r="W39" t="n">
-        <v>6.054153</v>
+        <v>5.579866</v>
       </c>
       <c r="X39" t="n">
-        <v>0.9424709999999999</v>
+        <v>4.600584</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.532743</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.197484</v>
+        <v>0.000556</v>
       </c>
       <c r="AA39" t="n">
-        <v>-1.591329</v>
+        <v>-0.04</v>
       </c>
       <c r="AB39" t="n">
-        <v>4.758099</v>
+        <v>-0.04</v>
       </c>
       <c r="AC39" t="n">
-        <v>5.579866</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>4.600584</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0.000556</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0.000556</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AK39" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -4816,105 +3892,81 @@
         <v>0.04158</v>
       </c>
       <c r="D40" t="n">
-        <v>0.04158</v>
+        <v>1.3</v>
       </c>
       <c r="E40" t="n">
-        <v>0.39</v>
+        <v>0.33</v>
       </c>
       <c r="F40" t="n">
-        <v>1.3</v>
+        <v>108.00109</v>
       </c>
       <c r="G40" t="n">
-        <v>0.33</v>
+        <v>105.49006</v>
       </c>
       <c r="H40" t="n">
-        <v>108.00109</v>
+        <v>6.0535</v>
       </c>
       <c r="I40" t="n">
-        <v>105.49006</v>
+        <v>6.0529</v>
       </c>
       <c r="J40" t="n">
-        <v>6.0535</v>
+        <v>2436022</v>
       </c>
       <c r="K40" t="n">
-        <v>6.0529</v>
+        <v>3929668</v>
       </c>
       <c r="L40" t="n">
-        <v>6365690</v>
+        <v>3.27</v>
       </c>
       <c r="M40" t="n">
-        <v>2436022</v>
+        <v>2.5</v>
       </c>
       <c r="N40" t="n">
-        <v>3929668</v>
+        <v>28.45</v>
       </c>
       <c r="O40" t="n">
-        <v>3.27</v>
+        <v>363003</v>
       </c>
       <c r="P40" t="n">
-        <v>2.5</v>
+        <v>-0.224963</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.75</v>
+        <v>-3.383039</v>
       </c>
       <c r="R40" t="n">
-        <v>28.45</v>
+        <v>4.769899</v>
       </c>
       <c r="S40" t="n">
-        <v>363003</v>
+        <v>4.770394</v>
       </c>
       <c r="T40" t="n">
-        <v>-0.224963</v>
+        <v>1.605359</v>
       </c>
       <c r="U40" t="n">
-        <v>-3.383039</v>
+        <v>1.343208</v>
       </c>
       <c r="V40" t="n">
-        <v>4.769899</v>
+        <v>-0.8448600000000001</v>
       </c>
       <c r="W40" t="n">
-        <v>4.770394</v>
+        <v>6.325086</v>
       </c>
       <c r="X40" t="n">
-        <v>1.443368</v>
+        <v>4.840925</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.605359</v>
+        <v>0.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.343208</v>
+        <v>0.001412</v>
       </c>
       <c r="AA40" t="n">
-        <v>-0.8448600000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="AB40" t="n">
-        <v>4.873011</v>
+        <v>-0.02</v>
       </c>
       <c r="AC40" t="n">
-        <v>6.325086</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>4.840925</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0.001412</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0.001412</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AK40" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4929,105 +3981,81 @@
         <v>0.044158</v>
       </c>
       <c r="D41" t="n">
-        <v>0.044158</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>0.52</v>
+        <v>0.48</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9399999999999999</v>
+        <v>107.37012</v>
       </c>
       <c r="G41" t="n">
-        <v>0.48</v>
+        <v>104.15552</v>
       </c>
       <c r="H41" t="n">
-        <v>107.37012</v>
+        <v>6.1923</v>
       </c>
       <c r="I41" t="n">
-        <v>104.15552</v>
+        <v>6.1917</v>
       </c>
       <c r="J41" t="n">
-        <v>6.1923</v>
+        <v>2499177</v>
       </c>
       <c r="K41" t="n">
-        <v>6.1917</v>
+        <v>3965425</v>
       </c>
       <c r="L41" t="n">
-        <v>6464602</v>
+        <v>3.08</v>
       </c>
       <c r="M41" t="n">
-        <v>2499177</v>
+        <v>2.21</v>
       </c>
       <c r="N41" t="n">
-        <v>3965425</v>
+        <v>28.5</v>
       </c>
       <c r="O41" t="n">
-        <v>3.08</v>
+        <v>329730</v>
       </c>
       <c r="P41" t="n">
-        <v>2.21</v>
+        <v>-0.584226</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.63</v>
+        <v>-1.265086</v>
       </c>
       <c r="R41" t="n">
-        <v>28.5</v>
+        <v>2.292888</v>
       </c>
       <c r="S41" t="n">
-        <v>329730</v>
+        <v>2.293116</v>
       </c>
       <c r="T41" t="n">
-        <v>-0.584226</v>
+        <v>2.592546</v>
       </c>
       <c r="U41" t="n">
-        <v>-1.265086</v>
+        <v>0.909924</v>
       </c>
       <c r="V41" t="n">
-        <v>2.292888</v>
+        <v>-9.166040000000001</v>
       </c>
       <c r="W41" t="n">
-        <v>2.293116</v>
+        <v>6.536174</v>
       </c>
       <c r="X41" t="n">
-        <v>1.55383</v>
+        <v>4.767938</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.592546</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.909924</v>
+        <v>0.002578</v>
       </c>
       <c r="AA41" t="n">
-        <v>-9.166040000000001</v>
+        <v>-0.19</v>
       </c>
       <c r="AB41" t="n">
-        <v>4.831296</v>
+        <v>-0.29</v>
       </c>
       <c r="AC41" t="n">
-        <v>6.536174</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>4.767938</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>0.002578</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>0.002578</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK41" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -5042,105 +4070,81 @@
         <v>0.045833</v>
       </c>
       <c r="D42" t="n">
-        <v>0.045833</v>
+        <v>0.27</v>
       </c>
       <c r="E42" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.27</v>
+        <v>108.09524</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>102.62949</v>
       </c>
       <c r="H42" t="n">
-        <v>108.09524</v>
+        <v>5.8301</v>
       </c>
       <c r="I42" t="n">
-        <v>102.62949</v>
+        <v>5.8295</v>
       </c>
       <c r="J42" t="n">
-        <v>5.8301</v>
+        <v>2451957</v>
       </c>
       <c r="K42" t="n">
-        <v>5.8295</v>
+        <v>4013059</v>
       </c>
       <c r="L42" t="n">
-        <v>6465016</v>
+        <v>3.34</v>
       </c>
       <c r="M42" t="n">
-        <v>2451957</v>
+        <v>2.43</v>
       </c>
       <c r="N42" t="n">
-        <v>4013059</v>
+        <v>29.88</v>
       </c>
       <c r="O42" t="n">
-        <v>3.34</v>
+        <v>328303</v>
       </c>
       <c r="P42" t="n">
-        <v>2.43</v>
+        <v>0.675346</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.89</v>
+        <v>-1.465146</v>
       </c>
       <c r="R42" t="n">
-        <v>29.88</v>
+        <v>-5.8492</v>
       </c>
       <c r="S42" t="n">
-        <v>328303</v>
+        <v>-5.849767</v>
       </c>
       <c r="T42" t="n">
-        <v>0.675346</v>
+        <v>-1.889422</v>
       </c>
       <c r="U42" t="n">
-        <v>-1.465146</v>
+        <v>1.201233</v>
       </c>
       <c r="V42" t="n">
-        <v>-5.8492</v>
+        <v>-0.432778</v>
       </c>
       <c r="W42" t="n">
-        <v>-5.849767</v>
+        <v>6.749097</v>
       </c>
       <c r="X42" t="n">
-        <v>0.006404</v>
+        <v>4.174145</v>
       </c>
       <c r="Y42" t="n">
-        <v>-1.889422</v>
+        <v>1</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.201233</v>
+        <v>0.001675</v>
       </c>
       <c r="AA42" t="n">
-        <v>-0.432778</v>
+        <v>0.26</v>
       </c>
       <c r="AB42" t="n">
-        <v>4.559874</v>
+        <v>0.22</v>
       </c>
       <c r="AC42" t="n">
-        <v>6.749097</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>4.174145</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0.001675</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0.001675</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK42" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -5155,105 +4159,81 @@
         <v>0.049037</v>
       </c>
       <c r="D43" t="n">
-        <v>0.049037</v>
+        <v>1.06</v>
       </c>
       <c r="E43" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="F43" t="n">
-        <v>1.06</v>
+        <v>108.62006</v>
       </c>
       <c r="G43" t="n">
-        <v>1.48</v>
+        <v>106.82599</v>
       </c>
       <c r="H43" t="n">
-        <v>108.62006</v>
+        <v>5.8488</v>
       </c>
       <c r="I43" t="n">
-        <v>106.82599</v>
+        <v>5.8482</v>
       </c>
       <c r="J43" t="n">
-        <v>5.8488</v>
+        <v>2477151</v>
       </c>
       <c r="K43" t="n">
-        <v>5.8482</v>
+        <v>4034293</v>
       </c>
       <c r="L43" t="n">
-        <v>6511444</v>
+        <v>3.41</v>
       </c>
       <c r="M43" t="n">
-        <v>2477151</v>
+        <v>2.52</v>
       </c>
       <c r="N43" t="n">
-        <v>4034293</v>
+        <v>30.53</v>
       </c>
       <c r="O43" t="n">
-        <v>3.41</v>
+        <v>332508</v>
       </c>
       <c r="P43" t="n">
-        <v>2.52</v>
+        <v>0.485516</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.96</v>
+        <v>4.088981</v>
       </c>
       <c r="R43" t="n">
-        <v>30.53</v>
+        <v>0.320749</v>
       </c>
       <c r="S43" t="n">
-        <v>332508</v>
+        <v>0.320782</v>
       </c>
       <c r="T43" t="n">
-        <v>0.485516</v>
+        <v>1.027506</v>
       </c>
       <c r="U43" t="n">
-        <v>4.088981</v>
+        <v>0.529123</v>
       </c>
       <c r="V43" t="n">
-        <v>0.320749</v>
+        <v>1.280829</v>
       </c>
       <c r="W43" t="n">
-        <v>0.320782</v>
+        <v>8.444549</v>
       </c>
       <c r="X43" t="n">
-        <v>0.7181419999999999</v>
+        <v>4.866504</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.027506</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.529123</v>
+        <v>0.003204</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.280829</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AB43" t="n">
-        <v>5.05763</v>
+        <v>0.09</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.444549</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>4.866504</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0.003204</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0.003204</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK43" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -5268,105 +4248,81 @@
         <v>0.050508</v>
       </c>
       <c r="D44" t="n">
-        <v>0.050508</v>
+        <v>-0.34</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.34</v>
+        <v>110.03287</v>
       </c>
       <c r="G44" t="n">
-        <v>0.51</v>
+        <v>114.02067</v>
       </c>
       <c r="H44" t="n">
-        <v>110.03287</v>
+        <v>5.7422</v>
       </c>
       <c r="I44" t="n">
-        <v>114.02067</v>
+        <v>5.7416</v>
       </c>
       <c r="J44" t="n">
-        <v>5.7422</v>
+        <v>2498262</v>
       </c>
       <c r="K44" t="n">
-        <v>5.7416</v>
+        <v>4078202</v>
       </c>
       <c r="L44" t="n">
-        <v>6576464</v>
+        <v>3.44</v>
       </c>
       <c r="M44" t="n">
-        <v>2498262</v>
+        <v>2.49</v>
       </c>
       <c r="N44" t="n">
-        <v>4078202</v>
+        <v>31.34</v>
       </c>
       <c r="O44" t="n">
-        <v>3.44</v>
+        <v>336157</v>
       </c>
       <c r="P44" t="n">
-        <v>2.49</v>
+        <v>1.30069</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.03</v>
+        <v>6.734953</v>
       </c>
       <c r="R44" t="n">
-        <v>31.34</v>
+        <v>-1.822596</v>
       </c>
       <c r="S44" t="n">
-        <v>336157</v>
+        <v>-1.822783</v>
       </c>
       <c r="T44" t="n">
-        <v>1.30069</v>
+        <v>0.852229</v>
       </c>
       <c r="U44" t="n">
-        <v>6.734953</v>
+        <v>1.088394</v>
       </c>
       <c r="V44" t="n">
-        <v>-1.822596</v>
+        <v>1.097417</v>
       </c>
       <c r="W44" t="n">
-        <v>-1.822783</v>
+        <v>8.586193</v>
       </c>
       <c r="X44" t="n">
-        <v>0.99855</v>
+        <v>5.201441</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.852229</v>
+        <v>1</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.088394</v>
+        <v>0.001471</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.097417</v>
+        <v>0.03</v>
       </c>
       <c r="AB44" t="n">
-        <v>5.47719</v>
+        <v>-0.03</v>
       </c>
       <c r="AC44" t="n">
-        <v>8.586193</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>5.201441</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>0.001471</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0.001471</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK44" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -5381,105 +4337,81 @@
         <v>0.052531</v>
       </c>
       <c r="D45" t="n">
-        <v>0.052531</v>
+        <v>0.24</v>
       </c>
       <c r="E45" t="n">
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
       <c r="F45" t="n">
-        <v>0.24</v>
+        <v>109.52766</v>
       </c>
       <c r="G45" t="n">
-        <v>0.48</v>
+        <v>112.59512</v>
       </c>
       <c r="H45" t="n">
-        <v>109.52766</v>
+        <v>5.6608</v>
       </c>
       <c r="I45" t="n">
-        <v>112.59512</v>
+        <v>5.6602</v>
       </c>
       <c r="J45" t="n">
-        <v>5.6608</v>
+        <v>2512426</v>
       </c>
       <c r="K45" t="n">
-        <v>5.6602</v>
+        <v>4111522</v>
       </c>
       <c r="L45" t="n">
-        <v>6623948</v>
+        <v>3.67</v>
       </c>
       <c r="M45" t="n">
-        <v>2512426</v>
+        <v>2.72</v>
       </c>
       <c r="N45" t="n">
-        <v>4111522</v>
+        <v>31.63</v>
       </c>
       <c r="O45" t="n">
-        <v>3.67</v>
+        <v>340789</v>
       </c>
       <c r="P45" t="n">
-        <v>2.72</v>
+        <v>-0.459145</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.25</v>
+        <v>-1.250256</v>
       </c>
       <c r="R45" t="n">
-        <v>31.63</v>
+        <v>-1.417575</v>
       </c>
       <c r="S45" t="n">
-        <v>340789</v>
+        <v>-1.417723</v>
       </c>
       <c r="T45" t="n">
-        <v>-0.459145</v>
+        <v>0.566954</v>
       </c>
       <c r="U45" t="n">
-        <v>-1.250256</v>
+        <v>0.8170269999999999</v>
       </c>
       <c r="V45" t="n">
-        <v>-1.417575</v>
+        <v>1.377928</v>
       </c>
       <c r="W45" t="n">
-        <v>-1.417723</v>
+        <v>8.510418</v>
       </c>
       <c r="X45" t="n">
-        <v>0.722029</v>
+        <v>5.316736</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.566954</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.8170269999999999</v>
+        <v>0.002023</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.377928</v>
+        <v>0.23</v>
       </c>
       <c r="AB45" t="n">
-        <v>5.529729</v>
+        <v>0.23</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.510418</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>5.316736</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AK45" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -5494,105 +4426,81 @@
         <v>0.053936</v>
       </c>
       <c r="D46" t="n">
-        <v>0.053936</v>
+        <v>-0.49</v>
       </c>
       <c r="E46" t="n">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.49</v>
+        <v>108.8862</v>
       </c>
       <c r="G46" t="n">
-        <v>0.35</v>
+        <v>108.55704</v>
       </c>
       <c r="H46" t="n">
-        <v>108.8862</v>
+        <v>5.7087</v>
       </c>
       <c r="I46" t="n">
-        <v>108.55704</v>
+        <v>5.7081</v>
       </c>
       <c r="J46" t="n">
-        <v>5.7087</v>
+        <v>2532708</v>
       </c>
       <c r="K46" t="n">
-        <v>5.7081</v>
+        <v>4133579</v>
       </c>
       <c r="L46" t="n">
-        <v>6666287</v>
+        <v>3.72</v>
       </c>
       <c r="M46" t="n">
-        <v>2532708</v>
+        <v>2.67</v>
       </c>
       <c r="N46" t="n">
-        <v>4133579</v>
+        <v>31.7</v>
       </c>
       <c r="O46" t="n">
-        <v>3.72</v>
+        <v>341459</v>
       </c>
       <c r="P46" t="n">
-        <v>2.67</v>
+        <v>-0.58566</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.36</v>
+        <v>-3.586372</v>
       </c>
       <c r="R46" t="n">
-        <v>31.7</v>
+        <v>0.84617</v>
       </c>
       <c r="S46" t="n">
-        <v>341459</v>
+        <v>0.84626</v>
       </c>
       <c r="T46" t="n">
-        <v>-0.58566</v>
+        <v>0.807268</v>
       </c>
       <c r="U46" t="n">
-        <v>-3.586372</v>
+        <v>0.5364679999999999</v>
       </c>
       <c r="V46" t="n">
-        <v>0.84617</v>
+        <v>0.196603</v>
       </c>
       <c r="W46" t="n">
-        <v>0.84626</v>
+        <v>7.026183</v>
       </c>
       <c r="X46" t="n">
-        <v>0.639181</v>
+        <v>5.201418</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.807268</v>
+        <v>0.5</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.5364679999999999</v>
+        <v>0.001405</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.196603</v>
+        <v>0.05</v>
       </c>
       <c r="AB46" t="n">
-        <v>5.319636</v>
+        <v>-0.05</v>
       </c>
       <c r="AC46" t="n">
-        <v>7.026183</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>5.201418</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0.001405</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>0.001405</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK46" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5607,105 +4515,81 @@
         <v>0.054569</v>
       </c>
       <c r="D47" t="n">
-        <v>0.054569</v>
+        <v>-1.67</v>
       </c>
       <c r="E47" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.67</v>
+        <v>108.80376</v>
       </c>
       <c r="G47" t="n">
-        <v>0.23</v>
+        <v>107.36219</v>
       </c>
       <c r="H47" t="n">
-        <v>108.80376</v>
+        <v>5.4571</v>
       </c>
       <c r="I47" t="n">
-        <v>107.36219</v>
+        <v>5.4565</v>
       </c>
       <c r="J47" t="n">
-        <v>5.4571</v>
+        <v>2547693</v>
       </c>
       <c r="K47" t="n">
-        <v>5.4565</v>
+        <v>4155970</v>
       </c>
       <c r="L47" t="n">
-        <v>6703663</v>
+        <v>3.75</v>
       </c>
       <c r="M47" t="n">
-        <v>2547693</v>
+        <v>2.67</v>
       </c>
       <c r="N47" t="n">
-        <v>4155970</v>
+        <v>31.85</v>
       </c>
       <c r="O47" t="n">
-        <v>3.75</v>
+        <v>344440</v>
       </c>
       <c r="P47" t="n">
-        <v>2.67</v>
+        <v>-0.075712</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.41</v>
+        <v>-1.100666</v>
       </c>
       <c r="R47" t="n">
-        <v>31.85</v>
+        <v>-4.407308</v>
       </c>
       <c r="S47" t="n">
-        <v>344440</v>
+        <v>-4.407771</v>
       </c>
       <c r="T47" t="n">
-        <v>-0.075712</v>
+        <v>0.591659</v>
       </c>
       <c r="U47" t="n">
-        <v>-1.100666</v>
+        <v>0.541686</v>
       </c>
       <c r="V47" t="n">
-        <v>-4.407308</v>
+        <v>0.873018</v>
       </c>
       <c r="W47" t="n">
-        <v>-4.407771</v>
+        <v>4.393261</v>
       </c>
       <c r="X47" t="n">
-        <v>0.5606719999999999</v>
+        <v>5.18043</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.591659</v>
+        <v>0.25</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.541686</v>
+        <v>0.000633</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.873018</v>
+        <v>0.03</v>
       </c>
       <c r="AB47" t="n">
-        <v>5.351165</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>4.393261</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>5.18043</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>0.000633</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>0.000633</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK47" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5720,105 +4604,81 @@
         <v>0.055131</v>
       </c>
       <c r="D48" t="n">
-        <v>0.055131</v>
+        <v>-0.77</v>
       </c>
       <c r="E48" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.77</v>
+        <v>108.49869</v>
       </c>
       <c r="G48" t="n">
+        <v>113.10928</v>
+      </c>
+      <c r="H48" t="n">
+        <v>5.6021</v>
+      </c>
+      <c r="I48" t="n">
+        <v>5.6015</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2544400</v>
+      </c>
+      <c r="K48" t="n">
+        <v>4188808</v>
+      </c>
+      <c r="L48" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="M48" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="N48" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="O48" t="n">
+        <v>345111</v>
+      </c>
+      <c r="P48" t="n">
+        <v>-0.280386</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>5.352993</v>
+      </c>
+      <c r="R48" t="n">
+        <v>2.657089</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.657381</v>
+      </c>
+      <c r="T48" t="n">
+        <v>-0.129254</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0.79014</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0.194809</v>
+      </c>
+      <c r="W48" t="n">
+        <v>2.961368</v>
+      </c>
+      <c r="X48" t="n">
+        <v>5.127976</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0.000562</v>
+      </c>
+      <c r="AA48" t="n">
         <v>0.21</v>
       </c>
-      <c r="H48" t="n">
-        <v>108.49869</v>
-      </c>
-      <c r="I48" t="n">
-        <v>113.10928</v>
-      </c>
-      <c r="J48" t="n">
-        <v>5.6021</v>
-      </c>
-      <c r="K48" t="n">
-        <v>5.6015</v>
-      </c>
-      <c r="L48" t="n">
-        <v>6733209</v>
-      </c>
-      <c r="M48" t="n">
-        <v>2544400</v>
-      </c>
-      <c r="N48" t="n">
-        <v>4188808</v>
-      </c>
-      <c r="O48" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="R48" t="n">
-        <v>31.75</v>
-      </c>
-      <c r="S48" t="n">
-        <v>345111</v>
-      </c>
-      <c r="T48" t="n">
-        <v>-0.280386</v>
-      </c>
-      <c r="U48" t="n">
-        <v>5.352993</v>
-      </c>
-      <c r="V48" t="n">
-        <v>2.657089</v>
-      </c>
-      <c r="W48" t="n">
-        <v>2.657381</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0.440744</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>-0.129254</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0.79014</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0.194809</v>
-      </c>
       <c r="AB48" t="n">
-        <v>5.225222</v>
+        <v>0.12</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.961368</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>5.127976</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>0.000562</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>0.000562</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK48" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -5833,105 +4693,81 @@
         <v>0.055131</v>
       </c>
       <c r="D49" t="n">
-        <v>0.055131</v>
+        <v>0.36</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.11</v>
+        <v>-0.21</v>
       </c>
       <c r="F49" t="n">
-        <v>0.36</v>
+        <v>108.82893</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.21</v>
+        <v>110.38054</v>
       </c>
       <c r="H49" t="n">
-        <v>108.82893</v>
+        <v>5.4264</v>
       </c>
       <c r="I49" t="n">
-        <v>110.38054</v>
+        <v>5.4258</v>
       </c>
       <c r="J49" t="n">
-        <v>5.4264</v>
+        <v>2546265</v>
       </c>
       <c r="K49" t="n">
-        <v>5.4258</v>
+        <v>4228171</v>
       </c>
       <c r="L49" t="n">
-        <v>6774436</v>
+        <v>4.14</v>
       </c>
       <c r="M49" t="n">
-        <v>2546265</v>
+        <v>2.85</v>
       </c>
       <c r="N49" t="n">
-        <v>4228171</v>
+        <v>31.87</v>
       </c>
       <c r="O49" t="n">
-        <v>4.14</v>
+        <v>350767</v>
       </c>
       <c r="P49" t="n">
-        <v>2.85</v>
+        <v>0.304372</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.92</v>
+        <v>-2.412481</v>
       </c>
       <c r="R49" t="n">
-        <v>31.87</v>
+        <v>-3.136324</v>
       </c>
       <c r="S49" t="n">
-        <v>350767</v>
+        <v>-3.13666</v>
       </c>
       <c r="T49" t="n">
-        <v>0.304372</v>
+        <v>0.073298</v>
       </c>
       <c r="U49" t="n">
-        <v>-2.412481</v>
+        <v>0.9397180000000001</v>
       </c>
       <c r="V49" t="n">
-        <v>-3.136324</v>
+        <v>1.638893</v>
       </c>
       <c r="W49" t="n">
-        <v>-3.13666</v>
+        <v>3.033233</v>
       </c>
       <c r="X49" t="n">
-        <v>0.612293</v>
+        <v>5.054283</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.073298</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.9397180000000001</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.638893</v>
+        <v>0.18</v>
       </c>
       <c r="AB49" t="n">
-        <v>5.130501</v>
+        <v>0.06</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.033233</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>5.054283</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK49" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5946,105 +4782,81 @@
         <v>0.055131</v>
       </c>
       <c r="D50" t="n">
-        <v>0.055131</v>
+        <v>0.42</v>
       </c>
       <c r="E50" t="n">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="F50" t="n">
-        <v>0.42</v>
+        <v>108.73548</v>
       </c>
       <c r="G50" t="n">
-        <v>0.52</v>
+        <v>109.48375</v>
       </c>
       <c r="H50" t="n">
-        <v>108.73548</v>
+        <v>5.3186</v>
       </c>
       <c r="I50" t="n">
-        <v>109.48375</v>
+        <v>5.318</v>
       </c>
       <c r="J50" t="n">
-        <v>5.3186</v>
+        <v>2589817</v>
       </c>
       <c r="K50" t="n">
-        <v>5.318</v>
+        <v>4262888</v>
       </c>
       <c r="L50" t="n">
-        <v>6852705</v>
+        <v>4.09</v>
       </c>
       <c r="M50" t="n">
-        <v>2589817</v>
+        <v>2.77</v>
       </c>
       <c r="N50" t="n">
-        <v>4262888</v>
+        <v>31.47</v>
       </c>
       <c r="O50" t="n">
-        <v>4.09</v>
+        <v>356582</v>
       </c>
       <c r="P50" t="n">
-        <v>2.77</v>
+        <v>-0.085869</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.89</v>
+        <v>-0.812453</v>
       </c>
       <c r="R50" t="n">
-        <v>31.47</v>
+        <v>-1.986584</v>
       </c>
       <c r="S50" t="n">
-        <v>356582</v>
+        <v>-1.986804</v>
       </c>
       <c r="T50" t="n">
-        <v>-0.085869</v>
+        <v>1.710427</v>
       </c>
       <c r="U50" t="n">
-        <v>-0.812453</v>
+        <v>0.821088</v>
       </c>
       <c r="V50" t="n">
-        <v>-1.986584</v>
+        <v>1.657796</v>
       </c>
       <c r="W50" t="n">
-        <v>-1.986804</v>
+        <v>2.828436</v>
       </c>
       <c r="X50" t="n">
-        <v>1.155358</v>
+        <v>5.096104</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.710427</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.821088</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.657796</v>
+        <v>-0.05</v>
       </c>
       <c r="AB50" t="n">
-        <v>5.172369</v>
+        <v>-0.08</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.828436</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>5.096104</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK50" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -6059,105 +4871,81 @@
         <v>0.055131</v>
       </c>
       <c r="D51" t="n">
-        <v>0.055131</v>
+        <v>-0.36</v>
       </c>
       <c r="E51" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F51" t="n">
+        <v>108.75326</v>
+      </c>
+      <c r="G51" t="n">
+        <v>110.07682</v>
+      </c>
+      <c r="H51" t="n">
+        <v>5.3843</v>
+      </c>
+      <c r="I51" t="n">
+        <v>5.3837</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2597630</v>
+      </c>
+      <c r="K51" t="n">
+        <v>4326256</v>
+      </c>
+      <c r="L51" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="M51" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="N51" t="n">
+        <v>32.04</v>
+      </c>
+      <c r="O51" t="n">
+        <v>357103</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.016352</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.541697</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.235287</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1.235427</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.301682</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.486504</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0.146109</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0.924206</v>
+      </c>
+      <c r="X51" t="n">
+        <v>4.490243</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
         <v>0.09</v>
       </c>
-      <c r="F51" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H51" t="n">
-        <v>108.75326</v>
-      </c>
-      <c r="I51" t="n">
-        <v>110.07682</v>
-      </c>
-      <c r="J51" t="n">
-        <v>5.3843</v>
-      </c>
-      <c r="K51" t="n">
-        <v>5.3837</v>
-      </c>
-      <c r="L51" t="n">
-        <v>6923886</v>
-      </c>
-      <c r="M51" t="n">
-        <v>2597630</v>
-      </c>
-      <c r="N51" t="n">
-        <v>4326256</v>
-      </c>
-      <c r="O51" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="P51" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="R51" t="n">
-        <v>32.04</v>
-      </c>
-      <c r="S51" t="n">
-        <v>357103</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0.016352</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0.541697</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.235287</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.235427</v>
-      </c>
-      <c r="X51" t="n">
-        <v>1.038729</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0.301682</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.486504</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0.146109</v>
-      </c>
       <c r="AB51" t="n">
-        <v>4.680811</v>
+        <v>0.05</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.924206</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>4.490243</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK51" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -6172,105 +4960,81 @@
         <v>0.055131</v>
       </c>
       <c r="D52" t="n">
-        <v>0.055131</v>
+        <v>0.27</v>
       </c>
       <c r="E52" t="n">
-        <v>0.18</v>
+        <v>0.03</v>
       </c>
       <c r="F52" t="n">
-        <v>0.27</v>
+        <v>109.25005</v>
       </c>
       <c r="G52" t="n">
-        <v>0.03</v>
+        <v>106.59892</v>
       </c>
       <c r="H52" t="n">
-        <v>109.25005</v>
+        <v>5.3338</v>
       </c>
       <c r="I52" t="n">
-        <v>106.59892</v>
+        <v>5.3332</v>
       </c>
       <c r="J52" t="n">
-        <v>5.3338</v>
+        <v>2616902</v>
       </c>
       <c r="K52" t="n">
-        <v>5.3332</v>
+        <v>4387321</v>
       </c>
       <c r="L52" t="n">
-        <v>7004223</v>
+        <v>4.24</v>
       </c>
       <c r="M52" t="n">
-        <v>2616902</v>
+        <v>2.75</v>
       </c>
       <c r="N52" t="n">
-        <v>4387321</v>
+        <v>32.2</v>
       </c>
       <c r="O52" t="n">
-        <v>4.24</v>
+        <v>360578</v>
       </c>
       <c r="P52" t="n">
-        <v>2.75</v>
+        <v>0.456805</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.12</v>
+        <v>-3.159521</v>
       </c>
       <c r="R52" t="n">
-        <v>32.2</v>
+        <v>-0.937912</v>
       </c>
       <c r="S52" t="n">
-        <v>360578</v>
+        <v>-0.938017</v>
       </c>
       <c r="T52" t="n">
-        <v>0.456805</v>
+        <v>0.741907</v>
       </c>
       <c r="U52" t="n">
-        <v>-3.159521</v>
+        <v>1.411498</v>
       </c>
       <c r="V52" t="n">
-        <v>-0.937912</v>
+        <v>0.973109</v>
       </c>
       <c r="W52" t="n">
-        <v>-0.938017</v>
+        <v>-0.101973</v>
       </c>
       <c r="X52" t="n">
-        <v>1.160288</v>
+        <v>4.177803</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.741907</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.411498</v>
+        <v>-0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.973109</v>
+        <v>0.06</v>
       </c>
       <c r="AB52" t="n">
-        <v>4.461836</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC52" t="n">
-        <v>-0.101973</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>4.177803</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AK52" t="n">
         <v>0.16</v>
       </c>
     </row>
@@ -6285,105 +5049,81 @@
         <v>0.055131</v>
       </c>
       <c r="D53" t="n">
-        <v>0.055131</v>
+        <v>-0.01</v>
       </c>
       <c r="E53" t="n">
-        <v>0.33</v>
+        <v>0.21</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.01</v>
+        <v>109.4528</v>
       </c>
       <c r="G53" t="n">
-        <v>0.21</v>
+        <v>107.18417</v>
       </c>
       <c r="H53" t="n">
-        <v>109.4528</v>
+        <v>5.5024</v>
       </c>
       <c r="I53" t="n">
-        <v>107.18417</v>
+        <v>5.5018</v>
       </c>
       <c r="J53" t="n">
-        <v>5.5024</v>
+        <v>2701735</v>
       </c>
       <c r="K53" t="n">
-        <v>5.5018</v>
+        <v>4435517</v>
       </c>
       <c r="L53" t="n">
-        <v>7137252</v>
+        <v>4.2</v>
       </c>
       <c r="M53" t="n">
-        <v>2701735</v>
+        <v>2.7</v>
       </c>
       <c r="N53" t="n">
-        <v>4435517</v>
+        <v>31.87</v>
       </c>
       <c r="O53" t="n">
-        <v>4.2</v>
+        <v>358234</v>
       </c>
       <c r="P53" t="n">
-        <v>2.7</v>
+        <v>0.185583</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.12</v>
+        <v>0.549021</v>
       </c>
       <c r="R53" t="n">
-        <v>31.87</v>
+        <v>3.160973</v>
       </c>
       <c r="S53" t="n">
-        <v>358234</v>
+        <v>3.161329</v>
       </c>
       <c r="T53" t="n">
-        <v>0.185583</v>
+        <v>3.241734</v>
       </c>
       <c r="U53" t="n">
-        <v>0.549021</v>
+        <v>1.098529</v>
       </c>
       <c r="V53" t="n">
-        <v>3.160973</v>
+        <v>-0.650067</v>
       </c>
       <c r="W53" t="n">
-        <v>3.161329</v>
+        <v>-1.042167</v>
       </c>
       <c r="X53" t="n">
-        <v>1.899268</v>
+        <v>3.897866</v>
       </c>
       <c r="Y53" t="n">
-        <v>3.241734</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.098529</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>-0.650067</v>
+        <v>-0.04</v>
       </c>
       <c r="AB53" t="n">
-        <v>4.264385</v>
+        <v>-0.05</v>
       </c>
       <c r="AC53" t="n">
-        <v>-1.042167</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>3.897866</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -6398,105 +5138,81 @@
         <v>0.055131</v>
       </c>
       <c r="D54" t="n">
-        <v>0.055131</v>
+        <v>0.41</v>
       </c>
       <c r="E54" t="n">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
       <c r="F54" t="n">
-        <v>0.41</v>
+        <v>110.04992</v>
       </c>
       <c r="G54" t="n">
-        <v>0.39</v>
+        <v>103.77761</v>
       </c>
       <c r="H54" t="n">
-        <v>110.04992</v>
+        <v>5.2301</v>
       </c>
       <c r="I54" t="n">
-        <v>103.77761</v>
+        <v>5.2295</v>
       </c>
       <c r="J54" t="n">
-        <v>5.2301</v>
+        <v>2654220</v>
       </c>
       <c r="K54" t="n">
-        <v>5.2295</v>
+        <v>4476542</v>
       </c>
       <c r="L54" t="n">
-        <v>7130762</v>
+        <v>4.44</v>
       </c>
       <c r="M54" t="n">
-        <v>2654220</v>
+        <v>2.87</v>
       </c>
       <c r="N54" t="n">
-        <v>4476542</v>
+        <v>32.45</v>
       </c>
       <c r="O54" t="n">
-        <v>4.44</v>
+        <v>364367</v>
       </c>
       <c r="P54" t="n">
-        <v>2.87</v>
+        <v>0.54555</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.38</v>
+        <v>-3.178231</v>
       </c>
       <c r="R54" t="n">
-        <v>32.45</v>
+        <v>-4.94875</v>
       </c>
       <c r="S54" t="n">
-        <v>364367</v>
+        <v>-4.949289</v>
       </c>
       <c r="T54" t="n">
-        <v>0.54555</v>
+        <v>-1.758685</v>
       </c>
       <c r="U54" t="n">
-        <v>-3.178231</v>
+        <v>0.92492</v>
       </c>
       <c r="V54" t="n">
-        <v>-4.94875</v>
+        <v>1.712009</v>
       </c>
       <c r="W54" t="n">
-        <v>-4.949289</v>
+        <v>-0.903999</v>
       </c>
       <c r="X54" t="n">
-        <v>-0.090931</v>
+        <v>4.303068</v>
       </c>
       <c r="Y54" t="n">
-        <v>-1.758685</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.92492</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.712009</v>
+        <v>0.24</v>
       </c>
       <c r="AB54" t="n">
-        <v>4.441351</v>
+        <v>0.17</v>
       </c>
       <c r="AC54" t="n">
-        <v>-0.903999</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>4.303068</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK54" t="n">
         <v>0.58</v>
       </c>
     </row>
@@ -6511,105 +5227,81 @@
         <v>0.055131</v>
       </c>
       <c r="D55" t="n">
-        <v>0.055131</v>
+        <v>-0.73</v>
       </c>
       <c r="E55" t="n">
-        <v>0.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.73</v>
+        <v>110.7366</v>
       </c>
       <c r="G55" t="n">
-        <v>0.5600000000000001</v>
+        <v>106.76075</v>
       </c>
       <c r="H55" t="n">
-        <v>110.7366</v>
+        <v>5.1495</v>
       </c>
       <c r="I55" t="n">
-        <v>106.76075</v>
+        <v>5.1489</v>
       </c>
       <c r="J55" t="n">
-        <v>5.1495</v>
+        <v>2656484</v>
       </c>
       <c r="K55" t="n">
-        <v>5.1489</v>
+        <v>4501299</v>
       </c>
       <c r="L55" t="n">
-        <v>7157783</v>
+        <v>4.64</v>
       </c>
       <c r="M55" t="n">
-        <v>2656484</v>
+        <v>3.07</v>
       </c>
       <c r="N55" t="n">
-        <v>4501299</v>
+        <v>32.63</v>
       </c>
       <c r="O55" t="n">
-        <v>4.64</v>
+        <v>371074</v>
       </c>
       <c r="P55" t="n">
-        <v>3.07</v>
+        <v>0.6239710000000001</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.56</v>
+        <v>2.874551</v>
       </c>
       <c r="R55" t="n">
-        <v>32.63</v>
+        <v>-1.54108</v>
       </c>
       <c r="S55" t="n">
-        <v>371074</v>
+        <v>-1.541256</v>
       </c>
       <c r="T55" t="n">
-        <v>0.6239710000000001</v>
+        <v>0.085298</v>
       </c>
       <c r="U55" t="n">
-        <v>2.874551</v>
+        <v>0.553038</v>
       </c>
       <c r="V55" t="n">
-        <v>-1.54108</v>
+        <v>1.840727</v>
       </c>
       <c r="W55" t="n">
-        <v>-1.541256</v>
+        <v>-2.659212</v>
       </c>
       <c r="X55" t="n">
-        <v>0.378936</v>
+        <v>3.357475</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.085298</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.553038</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.840727</v>
+        <v>0.2</v>
       </c>
       <c r="AB55" t="n">
-        <v>3.812497</v>
+        <v>0.2</v>
       </c>
       <c r="AC55" t="n">
-        <v>-2.659212</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>3.357475</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AK55" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -6624,105 +5316,81 @@
         <v>0.054777</v>
       </c>
       <c r="D56" t="n">
-        <v>0.054777</v>
+        <v>0.52</v>
       </c>
       <c r="E56" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="F56" t="n">
-        <v>0.52</v>
+        <v>110.58808</v>
       </c>
       <c r="G56" t="n">
-        <v>0.91</v>
+        <v>118.01719</v>
       </c>
       <c r="H56" t="n">
-        <v>110.58808</v>
+        <v>5.2194</v>
       </c>
       <c r="I56" t="n">
-        <v>118.01719</v>
+        <v>5.2188</v>
       </c>
       <c r="J56" t="n">
-        <v>5.2194</v>
+        <v>2687535</v>
       </c>
       <c r="K56" t="n">
-        <v>5.2188</v>
+        <v>4553022</v>
       </c>
       <c r="L56" t="n">
-        <v>7240557</v>
+        <v>4.52</v>
       </c>
       <c r="M56" t="n">
-        <v>2687535</v>
+        <v>3.06</v>
       </c>
       <c r="N56" t="n">
-        <v>4553022</v>
+        <v>32.84</v>
       </c>
       <c r="O56" t="n">
-        <v>4.52</v>
+        <v>362002</v>
       </c>
       <c r="P56" t="n">
-        <v>3.06</v>
+        <v>-0.13412</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.39</v>
+        <v>10.543613</v>
       </c>
       <c r="R56" t="n">
-        <v>32.84</v>
+        <v>1.357413</v>
       </c>
       <c r="S56" t="n">
-        <v>362002</v>
+        <v>1.357572</v>
       </c>
       <c r="T56" t="n">
-        <v>-0.13412</v>
+        <v>1.168876</v>
       </c>
       <c r="U56" t="n">
-        <v>10.543613</v>
+        <v>1.149068</v>
       </c>
       <c r="V56" t="n">
-        <v>1.357413</v>
+        <v>-2.444795</v>
       </c>
       <c r="W56" t="n">
-        <v>1.357572</v>
+        <v>-1.819225</v>
       </c>
       <c r="X56" t="n">
-        <v>1.15642</v>
+        <v>3.768807</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.168876</v>
+        <v>-0.25</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.149068</v>
+        <v>-0.000354</v>
       </c>
       <c r="AA56" t="n">
-        <v>-2.444795</v>
+        <v>-0.12</v>
       </c>
       <c r="AB56" t="n">
-        <v>4.142847</v>
+        <v>-0.01</v>
       </c>
       <c r="AC56" t="n">
-        <v>-1.819225</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>3.768807</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>-0.000354</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>-0.000354</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="AK56" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -6737,105 +5405,81 @@
         <v>0.054223</v>
       </c>
       <c r="D57" t="n">
-        <v>0.054223</v>
+        <v>2.73</v>
       </c>
       <c r="E57" t="n">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>2.73</v>
+        <v>110.90009</v>
       </c>
       <c r="G57" t="n">
-        <v>0.8100000000000001</v>
+        <v>113.99295</v>
       </c>
       <c r="H57" t="n">
-        <v>110.90009</v>
+        <v>4.9886</v>
       </c>
       <c r="I57" t="n">
-        <v>113.99295</v>
+        <v>4.988</v>
       </c>
       <c r="J57" t="n">
-        <v>4.9886</v>
+        <v>2685397</v>
       </c>
       <c r="K57" t="n">
-        <v>4.988</v>
+        <v>4574368</v>
       </c>
       <c r="L57" t="n">
-        <v>7259766</v>
+        <v>4.64</v>
       </c>
       <c r="M57" t="n">
-        <v>2685397</v>
+        <v>3.15</v>
       </c>
       <c r="N57" t="n">
-        <v>4574368</v>
+        <v>33.36</v>
       </c>
       <c r="O57" t="n">
-        <v>4.64</v>
+        <v>366913</v>
       </c>
       <c r="P57" t="n">
-        <v>3.15</v>
+        <v>0.282137</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.51</v>
+        <v>-3.409876</v>
       </c>
       <c r="R57" t="n">
-        <v>33.36</v>
+        <v>-4.421964</v>
       </c>
       <c r="S57" t="n">
-        <v>366913</v>
+        <v>-4.422473</v>
       </c>
       <c r="T57" t="n">
-        <v>0.282137</v>
+        <v>-0.079552</v>
       </c>
       <c r="U57" t="n">
-        <v>-3.409876</v>
+        <v>0.468831</v>
       </c>
       <c r="V57" t="n">
-        <v>-4.421964</v>
+        <v>1.356622</v>
       </c>
       <c r="W57" t="n">
-        <v>-4.422473</v>
+        <v>0.619623</v>
       </c>
       <c r="X57" t="n">
-        <v>0.265297</v>
+        <v>4.109608</v>
       </c>
       <c r="Y57" t="n">
-        <v>-0.079552</v>
+        <v>-0.25</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.468831</v>
+        <v>-0.000554</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.356622</v>
+        <v>0.12</v>
       </c>
       <c r="AB57" t="n">
-        <v>4.39172</v>
+        <v>0.09</v>
       </c>
       <c r="AC57" t="n">
-        <v>0.619623</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>4.109608</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>-0.000554</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>-0.000554</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AK57" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -6850,105 +5494,81 @@
         <v>0.0534</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0534</v>
+        <v>0.84</v>
       </c>
       <c r="E58" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="F58" t="n">
-        <v>0.84</v>
+        <v>111.13846</v>
       </c>
       <c r="G58" t="n">
-        <v>0.65</v>
+        <v>109.65479</v>
       </c>
       <c r="H58" t="n">
-        <v>111.13846</v>
+        <v>5.0569</v>
       </c>
       <c r="I58" t="n">
-        <v>109.65479</v>
+        <v>5.0563</v>
       </c>
       <c r="J58" t="n">
-        <v>5.0569</v>
+        <v>2708154</v>
       </c>
       <c r="K58" t="n">
-        <v>5.0563</v>
+        <v>4597152</v>
       </c>
       <c r="L58" t="n">
-        <v>7305306</v>
+        <v>4.74</v>
       </c>
       <c r="M58" t="n">
-        <v>2708154</v>
+        <v>3.25</v>
       </c>
       <c r="N58" t="n">
-        <v>4597152</v>
+        <v>33.1</v>
       </c>
       <c r="O58" t="n">
-        <v>4.74</v>
+        <v>371137</v>
       </c>
       <c r="P58" t="n">
-        <v>3.25</v>
+        <v>0.214941</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.62</v>
+        <v>-3.805639</v>
       </c>
       <c r="R58" t="n">
-        <v>33.1</v>
+        <v>1.369122</v>
       </c>
       <c r="S58" t="n">
-        <v>371137</v>
+        <v>1.369286</v>
       </c>
       <c r="T58" t="n">
-        <v>0.214941</v>
+        <v>0.847435</v>
       </c>
       <c r="U58" t="n">
-        <v>-3.805639</v>
+        <v>0.49808</v>
       </c>
       <c r="V58" t="n">
-        <v>1.369122</v>
+        <v>1.151227</v>
       </c>
       <c r="W58" t="n">
-        <v>1.369286</v>
+        <v>1.964454</v>
       </c>
       <c r="X58" t="n">
-        <v>0.627293</v>
+        <v>4.420848</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.847435</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.49808</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.151227</v>
+        <v>0.1</v>
       </c>
       <c r="AB58" t="n">
-        <v>4.724907</v>
+        <v>0.1</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.964454</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>4.420848</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>-0.0008229999999999999</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>-0.0008229999999999999</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK58" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -6963,105 +5583,81 @@
         <v>0.053028</v>
       </c>
       <c r="D59" t="n">
-        <v>0.053028</v>
+        <v>-0.5</v>
       </c>
       <c r="E59" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.5</v>
+        <v>110.15775</v>
       </c>
       <c r="G59" t="n">
-        <v>0.14</v>
+        <v>109.94156</v>
       </c>
       <c r="H59" t="n">
-        <v>110.15775</v>
+        <v>5.1766</v>
       </c>
       <c r="I59" t="n">
-        <v>109.94156</v>
+        <v>5.176</v>
       </c>
       <c r="J59" t="n">
-        <v>5.1766</v>
+        <v>2750625</v>
       </c>
       <c r="K59" t="n">
-        <v>5.176</v>
+        <v>4602668</v>
       </c>
       <c r="L59" t="n">
-        <v>7353293</v>
+        <v>4.58</v>
       </c>
       <c r="M59" t="n">
-        <v>2750625</v>
+        <v>3.18</v>
       </c>
       <c r="N59" t="n">
-        <v>4602668</v>
+        <v>33.33</v>
       </c>
       <c r="O59" t="n">
-        <v>4.58</v>
+        <v>367558</v>
       </c>
       <c r="P59" t="n">
-        <v>3.18</v>
+        <v>-0.882422</v>
       </c>
       <c r="Q59" t="n">
-        <v>5.42</v>
+        <v>0.261521</v>
       </c>
       <c r="R59" t="n">
-        <v>33.33</v>
+        <v>2.367063</v>
       </c>
       <c r="S59" t="n">
-        <v>367558</v>
+        <v>2.367344</v>
       </c>
       <c r="T59" t="n">
-        <v>-0.882422</v>
+        <v>1.568264</v>
       </c>
       <c r="U59" t="n">
-        <v>0.261521</v>
+        <v>0.119987</v>
       </c>
       <c r="V59" t="n">
-        <v>2.367063</v>
+        <v>-0.964334</v>
       </c>
       <c r="W59" t="n">
-        <v>2.367344</v>
+        <v>3.177699</v>
       </c>
       <c r="X59" t="n">
-        <v>0.656879</v>
+        <v>4.327084</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.568264</v>
+        <v>-0.25</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.119987</v>
+        <v>-0.000372</v>
       </c>
       <c r="AA59" t="n">
-        <v>-0.964334</v>
+        <v>-0.16</v>
       </c>
       <c r="AB59" t="n">
-        <v>4.641328</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC59" t="n">
-        <v>3.177699</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>4.327084</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>-0.000372</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>-0.000372</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AK59" t="n">
         <v>0.23</v>
       </c>
     </row>
@@ -7076,105 +5672,81 @@
         <v>0.052531</v>
       </c>
       <c r="D60" t="n">
-        <v>0.052531</v>
+        <v>-1.16</v>
       </c>
       <c r="E60" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.16</v>
+        <v>109.91611</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.01</v>
+        <v>114.40189</v>
       </c>
       <c r="H60" t="n">
-        <v>109.91611</v>
+        <v>5.0773</v>
       </c>
       <c r="I60" t="n">
-        <v>114.40189</v>
+        <v>5.0767</v>
       </c>
       <c r="J60" t="n">
-        <v>5.0773</v>
+        <v>2731513</v>
       </c>
       <c r="K60" t="n">
-        <v>5.0767</v>
+        <v>4640730</v>
       </c>
       <c r="L60" t="n">
-        <v>7372243</v>
+        <v>4.88</v>
       </c>
       <c r="M60" t="n">
-        <v>2731513</v>
+        <v>3.31</v>
       </c>
       <c r="N60" t="n">
-        <v>4640730</v>
+        <v>32.08</v>
       </c>
       <c r="O60" t="n">
-        <v>4.88</v>
+        <v>369742</v>
       </c>
       <c r="P60" t="n">
-        <v>3.31</v>
+        <v>-0.219358</v>
       </c>
       <c r="Q60" t="n">
-        <v>5.81</v>
+        <v>4.057001</v>
       </c>
       <c r="R60" t="n">
-        <v>32.08</v>
+        <v>-1.918247</v>
       </c>
       <c r="S60" t="n">
-        <v>369742</v>
+        <v>-1.91847</v>
       </c>
       <c r="T60" t="n">
-        <v>-0.219358</v>
+        <v>-0.694824</v>
       </c>
       <c r="U60" t="n">
-        <v>4.057001</v>
+        <v>0.826955</v>
       </c>
       <c r="V60" t="n">
-        <v>-1.918247</v>
+        <v>0.5941920000000001</v>
       </c>
       <c r="W60" t="n">
-        <v>-1.91847</v>
+        <v>2.772183</v>
       </c>
       <c r="X60" t="n">
-        <v>0.257708</v>
+        <v>4.098046</v>
       </c>
       <c r="Y60" t="n">
-        <v>-0.694824</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.826955</v>
+        <v>-0.000497</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.5941920000000001</v>
+        <v>0.3</v>
       </c>
       <c r="AB60" t="n">
-        <v>4.443025</v>
+        <v>0.13</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.772183</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>4.098046</v>
-      </c>
-      <c r="AE60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>-0.000497</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>-0.000497</v>
-      </c>
-      <c r="AH60" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="AK60" t="n">
         <v>-1.25</v>
       </c>
     </row>
@@ -7189,71 +5761,55 @@
         <v>0.051784</v>
       </c>
       <c r="D61" t="n">
-        <v>0.051784</v>
+        <v>-0.22</v>
       </c>
       <c r="E61" t="n">
         <v>-0.32</v>
       </c>
-      <c r="F61" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="G61" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="n">
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="n">
         <v>5.1816</v>
       </c>
-      <c r="K61" t="n">
+      <c r="I61" t="n">
         <v>5.181</v>
       </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
+      <c r="O61" t="n">
+        <v>372616</v>
+      </c>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
+      <c r="R61" t="n">
+        <v>2.054241</v>
+      </c>
       <c r="S61" t="n">
-        <v>372616</v>
+        <v>2.054484</v>
       </c>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="n">
-        <v>2.054241</v>
+        <v>0.777299</v>
       </c>
       <c r="W61" t="n">
-        <v>2.054484</v>
-      </c>
-      <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
-      <c r="AA61" t="n">
-        <v>0.777299</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>4.223453</v>
-      </c>
-      <c r="AC61" t="n">
         <v>2.178243</v>
       </c>
-      <c r="AD61" t="n">
+      <c r="X61" t="n">
         <v>3.983297</v>
       </c>
-      <c r="AE61" t="n">
+      <c r="Y61" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AF61" t="n">
+      <c r="Z61" t="n">
         <v>-0.0007470000000000001</v>
       </c>
-      <c r="AG61" t="n">
-        <v>-0.0007470000000000001</v>
-      </c>
-      <c r="AH61" t="inlineStr"/>
-      <c r="AI61" t="inlineStr"/>
-      <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -7263,58 +5819,46 @@
         <v>13.75</v>
       </c>
       <c r="C62" t="n">
-        <v>0.05166</v>
-      </c>
-      <c r="D62" t="n">
-        <v>0.05166</v>
-      </c>
+        <v>0.051587</v>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="n">
-        <v>5.1527</v>
-      </c>
-      <c r="K62" t="n">
-        <v>5.152</v>
-      </c>
+      <c r="H62" t="n">
+        <v>5.1521</v>
+      </c>
+      <c r="I62" t="n">
+        <v>5.1515</v>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
+      <c r="R62" t="n">
+        <v>-0.569322</v>
+      </c>
+      <c r="S62" t="n">
+        <v>-0.569388</v>
+      </c>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
-      <c r="V62" t="n">
-        <v>-0.557743</v>
-      </c>
-      <c r="W62" t="n">
-        <v>-0.559738</v>
-      </c>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
+      <c r="Y62" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-0.000197</v>
+      </c>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr"/>
-      <c r="AD62" t="inlineStr"/>
-      <c r="AE62" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>-0.000124</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>-0.000124</v>
-      </c>
-      <c r="AH62" t="inlineStr"/>
-      <c r="AI62" t="inlineStr"/>
-      <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AI62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -433,135 +433,165 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>cdi</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ipca</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>igp_m</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>inpc</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ibc_br_sa</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>ibc_br</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>cambio_venda_usd</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>cambio_compra_usd</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>saldo_credito_total</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>saldo_credito_pj</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>saldo_credito_pf</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inadimplencia_total</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inadimplencia_pj</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
         <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>var_pct_ibc_br</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>var_pct_saldo_credito_total</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>ipca_acum_12m</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
         <is>
           <t>igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>inpc_acum_12m</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>dif_selic_over</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dif_cdi</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -578,44 +608,50 @@
         <v>0.022435</v>
       </c>
       <c r="D2" t="n">
+        <v>0.022435</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F2" t="n">
         <v>-0.64</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>1.2</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>96.96513</v>
       </c>
-      <c r="G2" t="n">
-        <v>97.10777</v>
-      </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>5.4394</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>5.4388</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
+        <v>4441056</v>
+      </c>
+      <c r="L2" t="n">
         <v>1894119</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>2546936</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>2.34</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>1.43</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="Q2" t="n">
         <v>21.42</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
         <v>368886</v>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
@@ -627,6 +663,12 @@
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -639,77 +681,93 @@
         <v>0.024244</v>
       </c>
       <c r="D3" t="n">
+        <v>0.024244</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.64</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>1.16</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>97.48671</v>
       </c>
-      <c r="G3" t="n">
-        <v>96.53041</v>
-      </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>5.643</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>5.6424</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
+        <v>4511956</v>
+      </c>
+      <c r="L3" t="n">
         <v>1910940</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>2601017</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>2.33</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>1.43</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Q3" t="n">
         <v>22.89</v>
       </c>
-      <c r="O3" t="n">
+      <c r="R3" t="n">
         <v>367927</v>
       </c>
-      <c r="P3" t="n">
+      <c r="S3" t="n">
         <v>0.537905</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-0.594556</v>
-      </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>3.74306</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>3.743473</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
+        <v>1.596467</v>
+      </c>
+      <c r="W3" t="n">
         <v>0.888065</v>
       </c>
-      <c r="U3" t="n">
+      <c r="X3" t="n">
         <v>2.123375</v>
       </c>
-      <c r="V3" t="n">
+      <c r="Y3" t="n">
         <v>-0.259972</v>
       </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="n">
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AD3" t="n">
         <v>0.001809</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AE3" t="n">
+        <v>0.001809</v>
+      </c>
+      <c r="AF3" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AI3" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -724,77 +782,93 @@
         <v>0.029256</v>
       </c>
       <c r="D4" t="n">
+        <v>0.029256</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F4" t="n">
         <v>0.02</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>0.84</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>99.05526</v>
       </c>
-      <c r="G4" t="n">
-        <v>97.85277000000001</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>5.6199</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>5.6193</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
+        <v>4597507</v>
+      </c>
+      <c r="L4" t="n">
         <v>1933111</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>2664395</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>2.36</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>1.46</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="Q4" t="n">
         <v>23.91</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>367772</v>
       </c>
-      <c r="P4" t="n">
+      <c r="S4" t="n">
         <v>1.608989</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.36989</v>
-      </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>-0.409357</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>-0.4094</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
+        <v>1.896096</v>
+      </c>
+      <c r="W4" t="n">
         <v>1.160214</v>
       </c>
-      <c r="U4" t="n">
+      <c r="X4" t="n">
         <v>2.436662</v>
       </c>
-      <c r="V4" t="n">
+      <c r="Y4" t="n">
         <v>-0.042128</v>
       </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
         <v>0.005012</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AE4" t="n">
+        <v>0.005012</v>
+      </c>
+      <c r="AF4" t="n">
         <v>0.03</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AG4" t="n">
         <v>0.03</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AH4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AI4" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -809,77 +883,93 @@
         <v>0.033316</v>
       </c>
       <c r="D5" t="n">
-        <v>0.87</v>
+        <v>0.033316</v>
       </c>
       <c r="E5" t="n">
         <v>0.73</v>
       </c>
       <c r="F5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H5" t="n">
         <v>99.37716</v>
       </c>
-      <c r="G5" t="n">
-        <v>99.32258</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>5.5805</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>5.5799</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
+        <v>4682852</v>
+      </c>
+      <c r="L5" t="n">
         <v>1974391</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>2708461</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>2.35</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>1.4</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q5" t="n">
         <v>24.21</v>
       </c>
-      <c r="O5" t="n">
+      <c r="R5" t="n">
         <v>362204</v>
       </c>
-      <c r="P5" t="n">
+      <c r="S5" t="n">
         <v>0.32497</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1.502063</v>
-      </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>-0.70108</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>-0.701155</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
+        <v>1.856332</v>
+      </c>
+      <c r="W5" t="n">
         <v>2.135418</v>
       </c>
-      <c r="U5" t="n">
+      <c r="X5" t="n">
         <v>1.653884</v>
       </c>
-      <c r="V5" t="n">
+      <c r="Y5" t="n">
         <v>-1.513981</v>
       </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="n">
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AD5" t="n">
         <v>0.00406</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AE5" t="n">
+        <v>0.00406</v>
+      </c>
+      <c r="AF5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AG5" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AH5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AI5" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -894,77 +984,93 @@
         <v>0.034749</v>
       </c>
       <c r="D6" t="n">
+        <v>0.034749</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F6" t="n">
         <v>1.82</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>0.67</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
         <v>97.4213</v>
       </c>
-      <c r="G6" t="n">
-        <v>91.67776000000001</v>
-      </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>5.3574</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>5.3568</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
+        <v>4682131</v>
+      </c>
+      <c r="L6" t="n">
         <v>1947035</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>2735096</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>2.51</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>1.46</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="Q6" t="n">
         <v>25.23</v>
       </c>
-      <c r="O6" t="n">
+      <c r="R6" t="n">
         <v>358398</v>
       </c>
-      <c r="P6" t="n">
+      <c r="S6" t="n">
         <v>-1.968118</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-7.696961</v>
-      </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>-3.99785</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>-3.99828</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
+        <v>-0.015397</v>
+      </c>
+      <c r="W6" t="n">
         <v>-1.385541</v>
       </c>
-      <c r="U6" t="n">
+      <c r="X6" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="V6" t="n">
+      <c r="Y6" t="n">
         <v>-1.050789</v>
       </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
         <v>0.001433</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AE6" t="n">
+        <v>0.001433</v>
+      </c>
+      <c r="AF6" t="n">
         <v>0.16</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AG6" t="n">
         <v>0.06</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AH6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AI6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -979,77 +1085,93 @@
         <v>0.039598</v>
       </c>
       <c r="D7" t="n">
+        <v>0.039598</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F7" t="n">
         <v>1.83</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>1</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
         <v>98.4804</v>
       </c>
-      <c r="G7" t="n">
-        <v>95.63728999999999</v>
-      </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>5.1394</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>5.1388</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
+        <v>4727818</v>
+      </c>
+      <c r="L7" t="n">
         <v>1971524</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>2756295</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>2.57</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>1.44</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="Q7" t="n">
         <v>25.63</v>
       </c>
-      <c r="O7" t="n">
+      <c r="R7" t="n">
         <v>357740</v>
       </c>
-      <c r="P7" t="n">
+      <c r="S7" t="n">
         <v>1.087134</v>
       </c>
-      <c r="Q7" t="n">
-        <v>4.318965</v>
-      </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>-4.069138</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>-4.069594</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
+        <v>0.975774</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.257759</v>
       </c>
-      <c r="U7" t="n">
+      <c r="X7" t="n">
         <v>0.775073</v>
       </c>
-      <c r="V7" t="n">
+      <c r="Y7" t="n">
         <v>-0.183595</v>
       </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="n">
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AD7" t="n">
         <v>0.004849</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AE7" t="n">
+        <v>0.004849</v>
+      </c>
+      <c r="AF7" t="n">
         <v>0.06</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AG7" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AH7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AI7" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1064,77 +1186,93 @@
         <v>0.041954</v>
       </c>
       <c r="D8" t="n">
+        <v>0.041954</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F8" t="n">
         <v>1.74</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>1.71</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
         <v>99.54801999999999</v>
       </c>
-      <c r="G8" t="n">
-        <v>104.53237</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>4.7378</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>4.7372</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
+        <v>4794583</v>
+      </c>
+      <c r="L8" t="n">
         <v>1994119</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>2800464</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>2.66</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>1.55</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Q8" t="n">
         <v>26.54</v>
       </c>
-      <c r="O8" t="n">
+      <c r="R8" t="n">
         <v>353169</v>
       </c>
-      <c r="P8" t="n">
+      <c r="S8" t="n">
         <v>1.084094</v>
       </c>
-      <c r="Q8" t="n">
-        <v>9.300848999999999</v>
-      </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>-7.814142</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>-7.815054</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
+        <v>1.412174</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.146068</v>
       </c>
-      <c r="U8" t="n">
+      <c r="X8" t="n">
         <v>1.602477</v>
       </c>
-      <c r="V8" t="n">
+      <c r="Y8" t="n">
         <v>-1.277744</v>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="n">
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="n">
         <v>1</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AD8" t="n">
         <v>0.002356</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AE8" t="n">
+        <v>0.002356</v>
+      </c>
+      <c r="AF8" t="n">
         <v>0.09</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AG8" t="n">
         <v>0.11</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AH8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AI8" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1149,77 +1287,93 @@
         <v>0.043739</v>
       </c>
       <c r="D9" t="n">
+        <v>0.043739</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="F9" t="n">
         <v>1.41</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
         <v>1.04</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="n">
         <v>99.44118</v>
       </c>
-      <c r="G9" t="n">
-        <v>100.22938</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>4.9191</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>4.9185</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
+        <v>4833732</v>
+      </c>
+      <c r="L9" t="n">
         <v>2003312</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>2830420</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>2.72</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>1.57</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="Q9" t="n">
         <v>27.46</v>
       </c>
-      <c r="O9" t="n">
+      <c r="R9" t="n">
         <v>345097</v>
       </c>
-      <c r="P9" t="n">
+      <c r="S9" t="n">
         <v>-0.107325</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-4.116419</v>
-      </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>3.826671</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>3.827155</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
+        <v>0.816526</v>
+      </c>
+      <c r="W9" t="n">
         <v>0.461006</v>
       </c>
-      <c r="U9" t="n">
+      <c r="X9" t="n">
         <v>1.06968</v>
       </c>
-      <c r="V9" t="n">
+      <c r="Y9" t="n">
         <v>-2.285591</v>
       </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
         <v>0.001785</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AE9" t="n">
+        <v>0.001785</v>
+      </c>
+      <c r="AF9" t="n">
         <v>0.06</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AG9" t="n">
         <v>0.02</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AH9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AI9" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1234,77 +1388,93 @@
         <v>0.046796</v>
       </c>
       <c r="D10" t="n">
+        <v>0.046796</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F10" t="n">
         <v>0.52</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
         <v>0.45</v>
       </c>
-      <c r="F10" t="n">
+      <c r="H10" t="n">
         <v>99.6454</v>
       </c>
-      <c r="G10" t="n">
-        <v>99.74383</v>
-      </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>4.7289</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>4.7283</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
+        <v>4889397</v>
+      </c>
+      <c r="L10" t="n">
         <v>2013726</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>2875671</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>2.79</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>1.57</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Q10" t="n">
         <v>27.42</v>
       </c>
-      <c r="O10" t="n">
+      <c r="R10" t="n">
         <v>346415</v>
       </c>
-      <c r="P10" t="n">
+      <c r="S10" t="n">
         <v>0.205368</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-0.484439</v>
-      </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>-3.866561</v>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>-3.867033</v>
       </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
+        <v>1.151595</v>
+      </c>
+      <c r="W10" t="n">
         <v>0.5198390000000001</v>
       </c>
-      <c r="U10" t="n">
+      <c r="X10" t="n">
         <v>1.598738</v>
       </c>
-      <c r="V10" t="n">
+      <c r="Y10" t="n">
         <v>0.381922</v>
       </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="n">
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="n">
         <v>1</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AD10" t="n">
         <v>0.003057</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AE10" t="n">
+        <v>0.003057</v>
+      </c>
+      <c r="AF10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AI10" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1319,77 +1489,93 @@
         <v>0.048116</v>
       </c>
       <c r="D11" t="n">
+        <v>0.048116</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F11" t="n">
         <v>0.59</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
         <v>0.62</v>
       </c>
-      <c r="F11" t="n">
+      <c r="H11" t="n">
         <v>99.51048</v>
       </c>
-      <c r="G11" t="n">
-        <v>99.31653</v>
-      </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>5.238</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>5.2374</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
+        <v>4965603</v>
+      </c>
+      <c r="L11" t="n">
         <v>2052569</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>2913035</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>2.73</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>1.52</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="Q11" t="n">
         <v>27.88</v>
       </c>
-      <c r="O11" t="n">
+      <c r="R11" t="n">
         <v>341958</v>
       </c>
-      <c r="P11" t="n">
+      <c r="S11" t="n">
         <v>-0.1354</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-0.428397</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>10.765717</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>10.767083</v>
       </c>
-      <c r="T11" t="n">
+      <c r="V11" t="n">
+        <v>1.558597</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.928912</v>
       </c>
-      <c r="U11" t="n">
+      <c r="X11" t="n">
         <v>1.299314</v>
       </c>
-      <c r="V11" t="n">
+      <c r="Y11" t="n">
         <v>-1.286607</v>
       </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="n">
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AD11" t="n">
         <v>0.00132</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AE11" t="n">
+        <v>0.00132</v>
+      </c>
+      <c r="AF11" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AG11" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AH11" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AI11" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1404,77 +1590,93 @@
         <v>0.049037</v>
       </c>
       <c r="D12" t="n">
+        <v>0.049037</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="F12" t="n">
         <v>0.21</v>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
         <v>-0.6</v>
       </c>
-      <c r="F12" t="n">
+      <c r="H12" t="n">
         <v>101.43172</v>
       </c>
-      <c r="G12" t="n">
-        <v>103.95991</v>
-      </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>5.1884</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>5.1878</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
+        <v>4999244</v>
+      </c>
+      <c r="L12" t="n">
         <v>2047038</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>2952207</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>2.84</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>1.6</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="Q12" t="n">
         <v>29.24</v>
       </c>
-      <c r="O12" t="n">
+      <c r="R12" t="n">
         <v>346403</v>
       </c>
-      <c r="P12" t="n">
+      <c r="S12" t="n">
         <v>1.930691</v>
       </c>
-      <c r="Q12" t="n">
-        <v>4.675335</v>
-      </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>-0.946926</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>-0.947035</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
+        <v>0.677481</v>
+      </c>
+      <c r="W12" t="n">
         <v>-0.269467</v>
       </c>
-      <c r="U12" t="n">
+      <c r="X12" t="n">
         <v>1.344714</v>
       </c>
-      <c r="V12" t="n">
+      <c r="Y12" t="n">
         <v>1.299867</v>
       </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AE12" t="n">
+        <v>0.0009210000000000001</v>
+      </c>
+      <c r="AF12" t="n">
         <v>0.11</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AG12" t="n">
         <v>0.08</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AH12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AI12" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -1489,81 +1691,99 @@
         <v>0.05056</v>
       </c>
       <c r="D13" t="n">
+        <v>0.05056</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="F13" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E13" t="n">
+      <c r="G13" t="n">
         <v>-0.31</v>
       </c>
-      <c r="F13" t="n">
+      <c r="H13" t="n">
         <v>101.10583</v>
       </c>
-      <c r="G13" t="n">
-        <v>104.51156</v>
-      </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>5.179</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>5.1784</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
+        <v>5072711</v>
+      </c>
+      <c r="L13" t="n">
         <v>2064183</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>3008528</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>2.9</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>1.62</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="Q13" t="n">
         <v>28.6</v>
       </c>
-      <c r="O13" t="n">
+      <c r="R13" t="n">
         <v>339664</v>
       </c>
-      <c r="P13" t="n">
+      <c r="S13" t="n">
         <v>-0.32129</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0.530637</v>
-      </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>-0.181173</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>-0.181194</v>
       </c>
-      <c r="T13" t="n">
+      <c r="V13" t="n">
+        <v>1.469562</v>
+      </c>
+      <c r="W13" t="n">
         <v>0.837552</v>
       </c>
-      <c r="U13" t="n">
+      <c r="X13" t="n">
         <v>1.907759</v>
       </c>
-      <c r="V13" t="n">
+      <c r="Y13" t="n">
         <v>-1.945422</v>
       </c>
-      <c r="W13" t="n">
+      <c r="Z13" t="n">
+        <v>8.727061000000001</v>
+      </c>
+      <c r="AA13" t="n">
         <v>8.58755</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AB13" t="n">
         <v>8.825751</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AC13" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AD13" t="n">
         <v>0.001523</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AE13" t="n">
+        <v>0.001523</v>
+      </c>
+      <c r="AF13" t="n">
         <v>0.06</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AG13" t="n">
         <v>0.02</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AH13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AI13" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -1578,81 +1798,99 @@
         <v>0.050788</v>
       </c>
       <c r="D14" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="F14" t="n">
         <v>-0.95</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
         <v>-0.32</v>
       </c>
-      <c r="F14" t="n">
+      <c r="H14" t="n">
         <v>101.16034</v>
       </c>
-      <c r="G14" t="n">
-        <v>101.1889</v>
-      </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>5.4066</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>5.406</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
+        <v>5164775</v>
+      </c>
+      <c r="L14" t="n">
         <v>2109806</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>3054969</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>2.92</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>1.65</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q14" t="n">
         <v>28.57</v>
       </c>
-      <c r="O14" t="n">
+      <c r="R14" t="n">
         <v>327580</v>
       </c>
-      <c r="P14" t="n">
+      <c r="S14" t="n">
         <v>0.053914</v>
       </c>
-      <c r="Q14" t="n">
-        <v>-3.179227</v>
-      </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>4.394671</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>4.39518</v>
       </c>
-      <c r="T14" t="n">
+      <c r="V14" t="n">
+        <v>1.814888</v>
+      </c>
+      <c r="W14" t="n">
         <v>2.210221</v>
       </c>
-      <c r="U14" t="n">
+      <c r="X14" t="n">
         <v>1.543645</v>
       </c>
-      <c r="V14" t="n">
+      <c r="Y14" t="n">
         <v>-3.557633</v>
       </c>
-      <c r="W14" t="n">
+      <c r="Z14" t="n">
+        <v>7.168596</v>
+      </c>
+      <c r="AA14" t="n">
         <v>8.248760000000001</v>
       </c>
-      <c r="X14" t="n">
+      <c r="AB14" t="n">
         <v>7.191214</v>
       </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
         <v>0.000228</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AE14" t="n">
+        <v>0.000228</v>
+      </c>
+      <c r="AF14" t="n">
         <v>0.02</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AG14" t="n">
         <v>0.03</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AH14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AI14" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -1667,81 +1905,99 @@
         <v>0.050788</v>
       </c>
       <c r="D15" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F15" t="n">
         <v>-0.97</v>
       </c>
-      <c r="E15" t="n">
+      <c r="G15" t="n">
         <v>0.47</v>
       </c>
-      <c r="F15" t="n">
+      <c r="H15" t="n">
         <v>101.44171</v>
       </c>
-      <c r="G15" t="n">
-        <v>100.08177</v>
-      </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>5.257</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>5.2564</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
+        <v>5215990</v>
+      </c>
+      <c r="L15" t="n">
         <v>2105856</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>3110134</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>3.04</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>1.77</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="Q15" t="n">
         <v>29.68</v>
       </c>
-      <c r="O15" t="n">
+      <c r="R15" t="n">
         <v>325546</v>
       </c>
-      <c r="P15" t="n">
+      <c r="S15" t="n">
         <v>0.278143</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-1.094122</v>
-      </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>-2.766988</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>-2.767296</v>
       </c>
-      <c r="T15" t="n">
+      <c r="V15" t="n">
+        <v>0.991621</v>
+      </c>
+      <c r="W15" t="n">
         <v>-0.187221</v>
       </c>
-      <c r="U15" t="n">
+      <c r="X15" t="n">
         <v>1.805747</v>
       </c>
-      <c r="V15" t="n">
+      <c r="Y15" t="n">
         <v>-0.6209170000000001</v>
       </c>
-      <c r="W15" t="n">
+      <c r="Z15" t="n">
+        <v>6.470016</v>
+      </c>
+      <c r="AA15" t="n">
         <v>6.517038</v>
       </c>
-      <c r="X15" t="n">
+      <c r="AB15" t="n">
         <v>6.460076</v>
       </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
         <v>0.12</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AG15" t="n">
         <v>0.12</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AH15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AI15" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -1756,81 +2012,99 @@
         <v>0.050788</v>
       </c>
       <c r="D16" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F16" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="E16" t="n">
+      <c r="G16" t="n">
         <v>0.38</v>
       </c>
-      <c r="F16" t="n">
+      <c r="H16" t="n">
         <v>100.7146</v>
       </c>
-      <c r="G16" t="n">
-        <v>99.15031999999999</v>
-      </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>5.2941</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>5.2935</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
+        <v>5285657</v>
+      </c>
+      <c r="L16" t="n">
         <v>2130312</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>3155345</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>3.07</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>1.81</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="Q16" t="n">
         <v>30.52</v>
       </c>
-      <c r="O16" t="n">
+      <c r="R16" t="n">
         <v>331505</v>
       </c>
-      <c r="P16" t="n">
+      <c r="S16" t="n">
         <v>-0.716776</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-0.930689</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>0.705726</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>0.705806</v>
       </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
+        <v>1.335643</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.161333</v>
       </c>
-      <c r="U16" t="n">
+      <c r="X16" t="n">
         <v>1.453667</v>
       </c>
-      <c r="V16" t="n">
+      <c r="Y16" t="n">
         <v>1.830463</v>
       </c>
-      <c r="W16" t="n">
+      <c r="Z16" t="n">
+        <v>5.900488</v>
+      </c>
+      <c r="AA16" t="n">
         <v>5.899363</v>
       </c>
-      <c r="X16" t="n">
+      <c r="AB16" t="n">
         <v>5.974439</v>
       </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
         <v>0.03</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AG16" t="n">
         <v>0.04</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AH16" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AI16" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -1845,81 +2119,99 @@
         <v>0.050788</v>
       </c>
       <c r="D17" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F17" t="n">
         <v>0.45</v>
       </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="F17" t="n">
+      <c r="H17" t="n">
         <v>100.58818</v>
       </c>
-      <c r="G17" t="n">
-        <v>99.97037</v>
-      </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>5.2177</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>5.2171</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
+        <v>5366069</v>
+      </c>
+      <c r="L17" t="n">
         <v>2178236</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>3187833</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>3.07</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>1.8</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="Q17" t="n">
         <v>29.64</v>
       </c>
-      <c r="O17" t="n">
+      <c r="R17" t="n">
         <v>324703</v>
       </c>
-      <c r="P17" t="n">
+      <c r="S17" t="n">
         <v>-0.125523</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0.827078</v>
-      </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>-1.443116</v>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
         <v>-1.443279</v>
       </c>
-      <c r="T17" t="n">
+      <c r="V17" t="n">
+        <v>1.521325</v>
+      </c>
+      <c r="W17" t="n">
         <v>2.249624</v>
       </c>
-      <c r="U17" t="n">
+      <c r="X17" t="n">
         <v>1.029618</v>
       </c>
-      <c r="V17" t="n">
+      <c r="Y17" t="n">
         <v>-2.051854</v>
       </c>
-      <c r="W17" t="n">
+      <c r="Z17" t="n">
+        <v>5.784842</v>
+      </c>
+      <c r="AA17" t="n">
         <v>5.458422</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AB17" t="n">
         <v>5.932356</v>
       </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
         <v>-0</v>
       </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="AE17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AH17" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AI17" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -1934,81 +2226,99 @@
         <v>0.050788</v>
       </c>
       <c r="D18" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F18" t="n">
         <v>0.21</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
         <v>0.46</v>
       </c>
-      <c r="F18" t="n">
+      <c r="H18" t="n">
         <v>100.10988</v>
       </c>
-      <c r="G18" t="n">
-        <v>95.09953</v>
-      </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>5.0993</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>5.0987</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
+        <v>5373231</v>
+      </c>
+      <c r="L18" t="n">
         <v>2151399</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>3221831</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>3.24</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>1.94</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="Q18" t="n">
         <v>30.54</v>
       </c>
-      <c r="O18" t="n">
+      <c r="R18" t="n">
         <v>331122</v>
       </c>
-      <c r="P18" t="n">
+      <c r="S18" t="n">
         <v>-0.475503</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-4.872284</v>
-      </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>-2.269199</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>-2.26946</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
+        <v>0.133468</v>
+      </c>
+      <c r="W18" t="n">
         <v>-1.232052</v>
       </c>
-      <c r="U18" t="n">
+      <c r="X18" t="n">
         <v>1.066493</v>
       </c>
-      <c r="V18" t="n">
+      <c r="Y18" t="n">
         <v>1.976883</v>
       </c>
-      <c r="W18" t="n">
+      <c r="Z18" t="n">
+        <v>5.77432</v>
+      </c>
+      <c r="AA18" t="n">
         <v>3.79089</v>
       </c>
-      <c r="X18" t="n">
+      <c r="AB18" t="n">
         <v>5.711379</v>
       </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
         <v>0.17</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AG18" t="n">
         <v>0.14</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AH18" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AI18" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2023,81 +2333,99 @@
         <v>0.050788</v>
       </c>
       <c r="D19" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F19" t="n">
         <v>-0.06</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
         <v>0.77</v>
       </c>
-      <c r="F19" t="n">
+      <c r="H19" t="n">
         <v>103.07987</v>
       </c>
-      <c r="G19" t="n">
-        <v>98.64798</v>
-      </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>5.2078</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>5.2072</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
+        <v>5370950</v>
+      </c>
+      <c r="L19" t="n">
         <v>2136105</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>3234845</v>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
         <v>3.36</v>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>2.17</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="Q19" t="n">
         <v>30.48</v>
       </c>
-      <c r="O19" t="n">
+      <c r="R19" t="n">
         <v>328098</v>
       </c>
-      <c r="P19" t="n">
+      <c r="S19" t="n">
         <v>2.96673</v>
       </c>
-      <c r="Q19" t="n">
-        <v>3.731301</v>
-      </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>2.127743</v>
       </c>
-      <c r="S19" t="n">
+      <c r="U19" t="n">
         <v>2.127993</v>
       </c>
-      <c r="T19" t="n">
+      <c r="V19" t="n">
+        <v>-0.042451</v>
+      </c>
+      <c r="W19" t="n">
         <v>-0.710886</v>
       </c>
-      <c r="U19" t="n">
+      <c r="X19" t="n">
         <v>0.403932</v>
       </c>
-      <c r="V19" t="n">
+      <c r="Y19" t="n">
         <v>-0.913259</v>
       </c>
-      <c r="W19" t="n">
+      <c r="Z19" t="n">
+        <v>5.596302</v>
+      </c>
+      <c r="AA19" t="n">
         <v>1.864495</v>
       </c>
-      <c r="X19" t="n">
+      <c r="AB19" t="n">
         <v>5.47065</v>
       </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
         <v>0.12</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AG19" t="n">
         <v>0.23</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AH19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AI19" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2112,81 +2440,99 @@
         <v>0.050788</v>
       </c>
       <c r="D20" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F20" t="n">
         <v>0.05</v>
       </c>
-      <c r="E20" t="n">
+      <c r="G20" t="n">
         <v>0.64</v>
       </c>
-      <c r="F20" t="n">
+      <c r="H20" t="n">
         <v>103.08494</v>
       </c>
-      <c r="G20" t="n">
-        <v>110.61922</v>
-      </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>5.0804</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>5.0798</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
+        <v>5424811</v>
+      </c>
+      <c r="L20" t="n">
         <v>2154900</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>3269910</v>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
         <v>3.35</v>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
         <v>2.2</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="Q20" t="n">
         <v>30.99</v>
       </c>
-      <c r="O20" t="n">
+      <c r="R20" t="n">
         <v>341158</v>
       </c>
-      <c r="P20" t="n">
+      <c r="S20" t="n">
         <v>0.004919</v>
       </c>
-      <c r="Q20" t="n">
-        <v>12.135312</v>
-      </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>-2.446331</v>
       </c>
-      <c r="S20" t="n">
+      <c r="U20" t="n">
         <v>-2.446612</v>
       </c>
-      <c r="T20" t="n">
+      <c r="V20" t="n">
+        <v>1.002821</v>
+      </c>
+      <c r="W20" t="n">
         <v>0.879872</v>
       </c>
-      <c r="U20" t="n">
+      <c r="X20" t="n">
         <v>1.083978</v>
       </c>
-      <c r="V20" t="n">
+      <c r="Y20" t="n">
         <v>3.980518</v>
       </c>
-      <c r="W20" t="n">
+      <c r="Z20" t="n">
+        <v>4.650694</v>
+      </c>
+      <c r="AA20" t="n">
         <v>0.172427</v>
       </c>
-      <c r="X20" t="n">
+      <c r="AB20" t="n">
         <v>4.361088</v>
       </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AG20" t="n">
         <v>0.03</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AH20" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI20" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2201,81 +2547,99 @@
         <v>0.050788</v>
       </c>
       <c r="D21" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="F21" t="n">
         <v>-0.95</v>
       </c>
-      <c r="E21" t="n">
+      <c r="G21" t="n">
         <v>0.53</v>
       </c>
-      <c r="F21" t="n">
+      <c r="H21" t="n">
         <v>103.93573</v>
       </c>
-      <c r="G21" t="n">
-        <v>104.04095</v>
-      </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>5.0007</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>5.0001</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
+        <v>5426307</v>
+      </c>
+      <c r="L21" t="n">
         <v>2145000</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>3281308</v>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
         <v>3.54</v>
       </c>
-      <c r="M21" t="n">
+      <c r="O21" t="n">
         <v>2.45</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="Q21" t="n">
         <v>31.62</v>
       </c>
-      <c r="O21" t="n">
+      <c r="R21" t="n">
         <v>345725</v>
       </c>
-      <c r="P21" t="n">
+      <c r="S21" t="n">
         <v>0.825329</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-5.946769</v>
-      </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>-1.568774</v>
       </c>
-      <c r="S21" t="n">
+      <c r="U21" t="n">
         <v>-1.568959</v>
       </c>
-      <c r="T21" t="n">
+      <c r="V21" t="n">
+        <v>0.027577</v>
+      </c>
+      <c r="W21" t="n">
         <v>-0.459418</v>
       </c>
-      <c r="U21" t="n">
+      <c r="X21" t="n">
         <v>0.348572</v>
       </c>
-      <c r="V21" t="n">
+      <c r="Y21" t="n">
         <v>1.338676</v>
       </c>
-      <c r="W21" t="n">
+      <c r="Z21" t="n">
+        <v>4.184706</v>
+      </c>
+      <c r="AA21" t="n">
         <v>-2.158772</v>
       </c>
-      <c r="X21" t="n">
+      <c r="AB21" t="n">
         <v>3.834324</v>
       </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
         <v>0.19</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AG21" t="n">
         <v>0.25</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AH21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI21" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -2290,81 +2654,99 @@
         <v>0.050788</v>
       </c>
       <c r="D22" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F22" t="n">
         <v>-1.84</v>
       </c>
-      <c r="E22" t="n">
+      <c r="G22" t="n">
         <v>0.36</v>
       </c>
-      <c r="F22" t="n">
+      <c r="H22" t="n">
         <v>102.42973</v>
       </c>
-      <c r="G22" t="n">
-        <v>102.71375</v>
-      </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>5.0959</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>5.0953</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
+        <v>5453708</v>
+      </c>
+      <c r="L22" t="n">
         <v>2145530</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>3308178</v>
       </c>
-      <c r="L22" t="n">
+      <c r="N22" t="n">
         <v>3.65</v>
       </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
         <v>2.58</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="Q22" t="n">
         <v>31.63</v>
       </c>
-      <c r="O22" t="n">
+      <c r="R22" t="n">
         <v>343489</v>
       </c>
-      <c r="P22" t="n">
+      <c r="S22" t="n">
         <v>-1.448972</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-1.275652</v>
-      </c>
-      <c r="R22" t="n">
+      <c r="T22" t="n">
         <v>1.903733</v>
       </c>
-      <c r="S22" t="n">
+      <c r="U22" t="n">
         <v>1.903962</v>
       </c>
-      <c r="T22" t="n">
+      <c r="V22" t="n">
+        <v>0.504966</v>
+      </c>
+      <c r="W22" t="n">
         <v>0.024709</v>
       </c>
-      <c r="U22" t="n">
+      <c r="X22" t="n">
         <v>0.818881</v>
       </c>
-      <c r="V22" t="n">
+      <c r="Y22" t="n">
         <v>-0.646757</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Z22" t="n">
+        <v>3.935832</v>
+      </c>
+      <c r="AA22" t="n">
         <v>-4.45588</v>
       </c>
-      <c r="X22" t="n">
+      <c r="AB22" t="n">
         <v>3.741292</v>
       </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
         <v>-0</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AE22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF22" t="n">
         <v>0.11</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AG22" t="n">
         <v>0.13</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AH22" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AI22" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -2379,81 +2761,99 @@
         <v>0.050788</v>
       </c>
       <c r="D23" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="F23" t="n">
         <v>-1.93</v>
       </c>
-      <c r="E23" t="n">
+      <c r="G23" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F23" t="n">
+      <c r="H23" t="n">
         <v>102.39935</v>
       </c>
-      <c r="G23" t="n">
-        <v>102.28352</v>
-      </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>4.8192</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>4.8186</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
+        <v>5479459</v>
+      </c>
+      <c r="L23" t="n">
         <v>2169613</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>3309846</v>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
         <v>3.61</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>2.63</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q23" t="n">
         <v>30.85</v>
       </c>
-      <c r="O23" t="n">
+      <c r="R23" t="n">
         <v>343620</v>
       </c>
-      <c r="P23" t="n">
+      <c r="S23" t="n">
         <v>-0.029659</v>
       </c>
-      <c r="Q23" t="n">
-        <v>-0.418863</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>-5.429855</v>
       </c>
-      <c r="S23" t="n">
+      <c r="U23" t="n">
         <v>-5.430495</v>
       </c>
-      <c r="T23" t="n">
+      <c r="V23" t="n">
+        <v>0.472174</v>
+      </c>
+      <c r="W23" t="n">
         <v>1.122473</v>
       </c>
-      <c r="U23" t="n">
+      <c r="X23" t="n">
         <v>0.050421</v>
       </c>
-      <c r="V23" t="n">
+      <c r="Y23" t="n">
         <v>0.038138</v>
       </c>
-      <c r="W23" t="n">
+      <c r="Z23" t="n">
+        <v>3.161501</v>
+      </c>
+      <c r="AA23" t="n">
         <v>-6.84947</v>
       </c>
-      <c r="X23" t="n">
+      <c r="AB23" t="n">
         <v>2.998957</v>
       </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AG23" t="n">
         <v>0.05</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AH23" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AI23" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -2468,81 +2868,99 @@
         <v>0.050788</v>
       </c>
       <c r="D24" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F24" t="n">
         <v>-0.72</v>
       </c>
-      <c r="E24" t="n">
+      <c r="G24" t="n">
         <v>-0.09</v>
       </c>
-      <c r="F24" t="n">
+      <c r="H24" t="n">
         <v>102.90686</v>
       </c>
-      <c r="G24" t="n">
-        <v>105.34474</v>
-      </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>4.7415</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>4.7409</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
+        <v>5484871</v>
+      </c>
+      <c r="L24" t="n">
         <v>2153541</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>3331330</v>
       </c>
-      <c r="L24" t="n">
+      <c r="N24" t="n">
         <v>3.63</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>2.73</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="Q24" t="n">
         <v>30.43</v>
       </c>
-      <c r="O24" t="n">
+      <c r="R24" t="n">
         <v>345476</v>
       </c>
-      <c r="P24" t="n">
+      <c r="S24" t="n">
         <v>0.495618</v>
       </c>
-      <c r="Q24" t="n">
-        <v>2.992877</v>
-      </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>-1.612301</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>-1.612502</v>
       </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
+        <v>0.098769</v>
+      </c>
+      <c r="W24" t="n">
         <v>-0.740777</v>
       </c>
-      <c r="U24" t="n">
+      <c r="X24" t="n">
         <v>0.6490939999999999</v>
       </c>
-      <c r="V24" t="n">
+      <c r="Y24" t="n">
         <v>0.5401319999999999</v>
       </c>
-      <c r="W24" t="n">
+      <c r="Z24" t="n">
+        <v>3.992444</v>
+      </c>
+      <c r="AA24" t="n">
         <v>-7.713954</v>
       </c>
-      <c r="X24" t="n">
+      <c r="AB24" t="n">
         <v>3.527423</v>
       </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
         <v>0.02</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AG24" t="n">
         <v>0.1</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AH24" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AI24" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -2557,81 +2975,99 @@
         <v>0.049189</v>
       </c>
       <c r="D25" t="n">
+        <v>0.049189</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F25" t="n">
         <v>-0.14</v>
       </c>
-      <c r="E25" t="n">
+      <c r="G25" t="n">
         <v>0.2</v>
       </c>
-      <c r="F25" t="n">
+      <c r="H25" t="n">
         <v>102.50239</v>
       </c>
-      <c r="G25" t="n">
-        <v>106.05687</v>
-      </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>4.9219</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>4.9213</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
+        <v>5559063</v>
+      </c>
+      <c r="L25" t="n">
         <v>2172658</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>3386405</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>3.61</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>2.82</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="Q25" t="n">
         <v>29.92</v>
       </c>
-      <c r="O25" t="n">
+      <c r="R25" t="n">
         <v>344177</v>
       </c>
-      <c r="P25" t="n">
+      <c r="S25" t="n">
         <v>-0.393045</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>3.804703</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>3.805185</v>
       </c>
-      <c r="T25" t="n">
+      <c r="V25" t="n">
+        <v>1.352666</v>
+      </c>
+      <c r="W25" t="n">
         <v>0.887701</v>
       </c>
-      <c r="U25" t="n">
+      <c r="X25" t="n">
         <v>1.653244</v>
       </c>
-      <c r="V25" t="n">
+      <c r="Y25" t="n">
         <v>-0.376003</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Z25" t="n">
+        <v>4.608216</v>
+      </c>
+      <c r="AA25" t="n">
         <v>-7.193509</v>
       </c>
-      <c r="X25" t="n">
+      <c r="AB25" t="n">
         <v>4.057054</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AC25" t="n">
         <v>-0.5</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AD25" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AE25" t="n">
+        <v>-0.001599</v>
+      </c>
+      <c r="AF25" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AG25" t="n">
         <v>0.09</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AH25" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AI25" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -2646,81 +3082,99 @@
         <v>0.048422</v>
       </c>
       <c r="D26" t="n">
+        <v>0.048422</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F26" t="n">
         <v>0.37</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
         <v>0.11</v>
       </c>
-      <c r="F26" t="n">
+      <c r="H26" t="n">
         <v>102.5153</v>
       </c>
-      <c r="G26" t="n">
-        <v>101.75897</v>
-      </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>5.0076</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>5.007</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
+        <v>5625945</v>
+      </c>
+      <c r="L26" t="n">
         <v>2215175</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>3410769</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>3.54</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>2.82</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q26" t="n">
         <v>29.66</v>
       </c>
-      <c r="O26" t="n">
+      <c r="R26" t="n">
         <v>340324</v>
       </c>
-      <c r="P26" t="n">
+      <c r="S26" t="n">
         <v>0.012595</v>
       </c>
-      <c r="Q26" t="n">
-        <v>-4.052448</v>
-      </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>1.741198</v>
       </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
         <v>1.74141</v>
       </c>
-      <c r="T26" t="n">
+      <c r="V26" t="n">
+        <v>1.203116</v>
+      </c>
+      <c r="W26" t="n">
         <v>1.956912</v>
       </c>
-      <c r="U26" t="n">
+      <c r="X26" t="n">
         <v>0.719465</v>
       </c>
-      <c r="V26" t="n">
+      <c r="Y26" t="n">
         <v>-1.119482</v>
       </c>
-      <c r="W26" t="n">
+      <c r="Z26" t="n">
+        <v>5.185235</v>
+      </c>
+      <c r="AA26" t="n">
         <v>-5.956714</v>
       </c>
-      <c r="X26" t="n">
+      <c r="AB26" t="n">
         <v>4.505936</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AC26" t="n">
         <v>-0.5</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AD26" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AE26" t="n">
+        <v>-0.000768</v>
+      </c>
+      <c r="AF26" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AI26" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -2735,81 +3189,99 @@
         <v>0.047279</v>
       </c>
       <c r="D27" t="n">
+        <v>0.047279</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F27" t="n">
         <v>0.5</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>0.12</v>
       </c>
-      <c r="F27" t="n">
+      <c r="H27" t="n">
         <v>102.83959</v>
       </c>
-      <c r="G27" t="n">
-        <v>101.9338</v>
-      </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>5.0575</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>5.0569</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
+        <v>5653808</v>
+      </c>
+      <c r="L27" t="n">
         <v>2204808</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>3449000</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>3.56</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>2.92</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="Q27" t="n">
         <v>29.24</v>
       </c>
-      <c r="O27" t="n">
+      <c r="R27" t="n">
         <v>340247</v>
       </c>
-      <c r="P27" t="n">
+      <c r="S27" t="n">
         <v>0.316333</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0.171808</v>
-      </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>0.996485</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
         <v>0.996605</v>
       </c>
-      <c r="T27" t="n">
+      <c r="V27" t="n">
+        <v>0.495259</v>
+      </c>
+      <c r="W27" t="n">
         <v>-0.467999</v>
       </c>
-      <c r="U27" t="n">
+      <c r="X27" t="n">
         <v>1.120891</v>
       </c>
-      <c r="V27" t="n">
+      <c r="Y27" t="n">
         <v>-0.022625</v>
       </c>
-      <c r="W27" t="n">
+      <c r="Z27" t="n">
+        <v>4.819246</v>
+      </c>
+      <c r="AA27" t="n">
         <v>-4.560737</v>
       </c>
-      <c r="X27" t="n">
+      <c r="AB27" t="n">
         <v>4.141877</v>
       </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AE27" t="n">
+        <v>-0.001143</v>
+      </c>
+      <c r="AF27" t="n">
         <v>0.02</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AG27" t="n">
         <v>0.1</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AH27" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AI27" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -2824,81 +3296,99 @@
         <v>0.045601</v>
       </c>
       <c r="D28" t="n">
+        <v>0.045601</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F28" t="n">
         <v>0.59</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
         <v>0.1</v>
       </c>
-      <c r="F28" t="n">
+      <c r="H28" t="n">
         <v>103.59456</v>
       </c>
-      <c r="G28" t="n">
-        <v>101.68042</v>
-      </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>4.9355</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>4.9349</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
+        <v>5711103</v>
+      </c>
+      <c r="L28" t="n">
         <v>2220766</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
         <v>3490337</v>
       </c>
-      <c r="L28" t="n">
+      <c r="N28" t="n">
         <v>3.53</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>2.99</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="Q28" t="n">
         <v>29.01</v>
       </c>
-      <c r="O28" t="n">
+      <c r="R28" t="n">
         <v>348406</v>
       </c>
-      <c r="P28" t="n">
+      <c r="S28" t="n">
         <v>0.734124</v>
       </c>
-      <c r="Q28" t="n">
-        <v>-0.248573</v>
-      </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>-2.412259</v>
       </c>
-      <c r="S28" t="n">
+      <c r="U28" t="n">
         <v>-2.412545</v>
       </c>
-      <c r="T28" t="n">
+      <c r="V28" t="n">
+        <v>1.013388</v>
+      </c>
+      <c r="W28" t="n">
         <v>0.723782</v>
       </c>
-      <c r="U28" t="n">
+      <c r="X28" t="n">
         <v>1.198521</v>
       </c>
-      <c r="V28" t="n">
+      <c r="Y28" t="n">
         <v>2.397964</v>
       </c>
-      <c r="W28" t="n">
+      <c r="Z28" t="n">
+        <v>4.683537</v>
+      </c>
+      <c r="AA28" t="n">
         <v>-3.457004</v>
       </c>
-      <c r="X28" t="n">
+      <c r="AB28" t="n">
         <v>3.851383</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AC28" t="n">
         <v>-0.5</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AD28" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AE28" t="n">
+        <v>-0.001678</v>
+      </c>
+      <c r="AF28" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AG28" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AH28" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="AI28" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -2913,81 +3403,99 @@
         <v>0.044537</v>
       </c>
       <c r="D29" t="n">
+        <v>0.044537</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F29" t="n">
         <v>0.74</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
         <v>0.55</v>
       </c>
-      <c r="F29" t="n">
+      <c r="H29" t="n">
         <v>104.88818</v>
       </c>
-      <c r="G29" t="n">
-        <v>101.68469</v>
-      </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>4.8413</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>4.8407</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
+        <v>5805157</v>
+      </c>
+      <c r="L29" t="n">
         <v>2283485</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>3521672</v>
       </c>
-      <c r="L29" t="n">
+      <c r="N29" t="n">
         <v>3.29</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>2.59</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Q29" t="n">
         <v>28.14</v>
       </c>
-      <c r="O29" t="n">
+      <c r="R29" t="n">
         <v>355034</v>
       </c>
-      <c r="P29" t="n">
+      <c r="S29" t="n">
         <v>1.248734</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0.004199</v>
-      </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>-1.908621</v>
       </c>
-      <c r="S29" t="n">
+      <c r="U29" t="n">
         <v>-1.908853</v>
       </c>
-      <c r="T29" t="n">
+      <c r="V29" t="n">
+        <v>1.646862</v>
+      </c>
+      <c r="W29" t="n">
         <v>2.824206</v>
       </c>
-      <c r="U29" t="n">
+      <c r="X29" t="n">
         <v>0.897764</v>
       </c>
-      <c r="V29" t="n">
+      <c r="Y29" t="n">
         <v>1.902378</v>
       </c>
-      <c r="W29" t="n">
+      <c r="Z29" t="n">
+        <v>4.621114</v>
+      </c>
+      <c r="AA29" t="n">
         <v>-3.178284</v>
       </c>
-      <c r="X29" t="n">
+      <c r="AB29" t="n">
         <v>3.706988</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AC29" t="n">
         <v>-0.5</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AD29" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AE29" t="n">
+        <v>-0.001064</v>
+      </c>
+      <c r="AF29" t="n">
         <v>-0.24</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AG29" t="n">
         <v>-0.4</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AH29" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="AI29" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3002,81 +3510,99 @@
         <v>0.043739</v>
       </c>
       <c r="D30" t="n">
+        <v>0.043739</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F30" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="E30" t="n">
+      <c r="G30" t="n">
         <v>0.57</v>
       </c>
-      <c r="F30" t="n">
+      <c r="H30" t="n">
         <v>104.473</v>
       </c>
-      <c r="G30" t="n">
-        <v>99.29718</v>
-      </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>4.9535</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>4.9529</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
+        <v>5794707</v>
+      </c>
+      <c r="L30" t="n">
         <v>2234362</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>3560345</v>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>3.38</v>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>2.77</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="Q30" t="n">
         <v>28</v>
       </c>
-      <c r="O30" t="n">
+      <c r="R30" t="n">
         <v>355066</v>
       </c>
-      <c r="P30" t="n">
+      <c r="S30" t="n">
         <v>-0.395831</v>
       </c>
-      <c r="Q30" t="n">
-        <v>-2.347954</v>
-      </c>
-      <c r="R30" t="n">
+      <c r="T30" t="n">
         <v>2.317559</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>2.317847</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
+        <v>-0.180012</v>
+      </c>
+      <c r="W30" t="n">
         <v>-2.151229</v>
       </c>
-      <c r="U30" t="n">
+      <c r="X30" t="n">
         <v>1.098143</v>
       </c>
-      <c r="V30" t="n">
+      <c r="Y30" t="n">
         <v>0.009013</v>
       </c>
-      <c r="W30" t="n">
+      <c r="Z30" t="n">
+        <v>4.506637</v>
+      </c>
+      <c r="AA30" t="n">
         <v>-3.31355</v>
       </c>
-      <c r="X30" t="n">
+      <c r="AB30" t="n">
         <v>3.820543</v>
       </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AE30" t="n">
+        <v>-0.000798</v>
+      </c>
+      <c r="AF30" t="n">
         <v>0.09</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AG30" t="n">
         <v>0.18</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AH30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AI30" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -3091,81 +3617,99 @@
         <v>0.041957</v>
       </c>
       <c r="D31" t="n">
+        <v>0.041957</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F31" t="n">
         <v>-0.52</v>
       </c>
-      <c r="E31" t="n">
+      <c r="G31" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="F31" t="n">
+      <c r="H31" t="n">
         <v>104.65885</v>
       </c>
-      <c r="G31" t="n">
-        <v>102.15036</v>
-      </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>4.9833</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>4.9827</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
+        <v>5815954</v>
+      </c>
+      <c r="L31" t="n">
         <v>2235302</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>3580652</v>
       </c>
-      <c r="L31" t="n">
+      <c r="N31" t="n">
         <v>3.38</v>
       </c>
-      <c r="M31" t="n">
+      <c r="O31" t="n">
         <v>2.76</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="Q31" t="n">
         <v>27.85</v>
       </c>
-      <c r="O31" t="n">
+      <c r="R31" t="n">
         <v>352705</v>
       </c>
-      <c r="P31" t="n">
+      <c r="S31" t="n">
         <v>0.177893</v>
       </c>
-      <c r="Q31" t="n">
-        <v>2.873375</v>
-      </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
         <v>0.601595</v>
       </c>
-      <c r="S31" t="n">
+      <c r="U31" t="n">
         <v>0.601668</v>
       </c>
-      <c r="T31" t="n">
+      <c r="V31" t="n">
+        <v>0.366662</v>
+      </c>
+      <c r="W31" t="n">
         <v>0.04207</v>
       </c>
-      <c r="U31" t="n">
+      <c r="X31" t="n">
         <v>0.570366</v>
       </c>
-      <c r="V31" t="n">
+      <c r="Y31" t="n">
         <v>-0.664947</v>
       </c>
-      <c r="W31" t="n">
+      <c r="Z31" t="n">
+        <v>4.496274</v>
+      </c>
+      <c r="AA31" t="n">
         <v>-3.758575</v>
       </c>
-      <c r="X31" t="n">
+      <c r="AB31" t="n">
         <v>3.861754</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AC31" t="n">
         <v>-0.5</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AD31" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
+      <c r="AE31" t="n">
+        <v>-0.001782</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -3180,81 +3724,99 @@
         <v>0.04142</v>
       </c>
       <c r="D32" t="n">
+        <v>0.04142</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F32" t="n">
         <v>-0.47</v>
       </c>
-      <c r="E32" t="n">
+      <c r="G32" t="n">
         <v>0.19</v>
       </c>
-      <c r="F32" t="n">
+      <c r="H32" t="n">
         <v>104.6738</v>
       </c>
-      <c r="G32" t="n">
-        <v>109.56901</v>
-      </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>4.9962</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>4.9956</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
+        <v>5899742</v>
+      </c>
+      <c r="L32" t="n">
         <v>2285775</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>3613967</v>
       </c>
-      <c r="L32" t="n">
+      <c r="N32" t="n">
         <v>3.33</v>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>2.71</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="Q32" t="n">
         <v>28.14</v>
       </c>
-      <c r="O32" t="n">
+      <c r="R32" t="n">
         <v>355008</v>
       </c>
-      <c r="P32" t="n">
+      <c r="S32" t="n">
         <v>0.014285</v>
       </c>
-      <c r="Q32" t="n">
-        <v>7.262481</v>
-      </c>
-      <c r="R32" t="n">
+      <c r="T32" t="n">
         <v>0.258865</v>
       </c>
-      <c r="S32" t="n">
+      <c r="U32" t="n">
         <v>0.258896</v>
       </c>
-      <c r="T32" t="n">
+      <c r="V32" t="n">
+        <v>1.440658</v>
+      </c>
+      <c r="W32" t="n">
         <v>2.257995</v>
       </c>
-      <c r="U32" t="n">
+      <c r="X32" t="n">
         <v>0.930417</v>
       </c>
-      <c r="V32" t="n">
+      <c r="Y32" t="n">
         <v>0.652954</v>
       </c>
-      <c r="W32" t="n">
+      <c r="Z32" t="n">
+        <v>3.925596</v>
+      </c>
+      <c r="AA32" t="n">
         <v>-4.25878</v>
       </c>
-      <c r="X32" t="n">
+      <c r="AB32" t="n">
         <v>3.397348</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AC32" t="n">
         <v>-0.5</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AD32" t="n">
         <v>-0.000537</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AE32" t="n">
+        <v>-0.000537</v>
+      </c>
+      <c r="AF32" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AG32" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AH32" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI32" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -3269,81 +3831,99 @@
         <v>0.040168</v>
       </c>
       <c r="D33" t="n">
+        <v>0.040168</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F33" t="n">
         <v>0.31</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>0.37</v>
       </c>
-      <c r="F33" t="n">
+      <c r="H33" t="n">
         <v>104.62771</v>
       </c>
-      <c r="G33" t="n">
-        <v>109.2572</v>
-      </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>5.1718</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>5.1712</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
+        <v>5915538</v>
+      </c>
+      <c r="L33" t="n">
         <v>2268879</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>3646659</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>3.37</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>2.76</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Q33" t="n">
         <v>27.86</v>
       </c>
-      <c r="O33" t="n">
+      <c r="R33" t="n">
         <v>351599</v>
       </c>
-      <c r="P33" t="n">
+      <c r="S33" t="n">
         <v>-0.044032</v>
       </c>
-      <c r="Q33" t="n">
-        <v>-0.284579</v>
-      </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
         <v>3.514671</v>
       </c>
-      <c r="S33" t="n">
+      <c r="U33" t="n">
         <v>3.515093</v>
       </c>
-      <c r="T33" t="n">
+      <c r="V33" t="n">
+        <v>0.267741</v>
+      </c>
+      <c r="W33" t="n">
         <v>-0.7391799999999999</v>
       </c>
-      <c r="U33" t="n">
+      <c r="X33" t="n">
         <v>0.904602</v>
       </c>
-      <c r="V33" t="n">
+      <c r="Y33" t="n">
         <v>-0.96026</v>
       </c>
-      <c r="W33" t="n">
+      <c r="Z33" t="n">
+        <v>3.688016</v>
+      </c>
+      <c r="AA33" t="n">
         <v>-3.040871</v>
       </c>
-      <c r="X33" t="n">
+      <c r="AB33" t="n">
         <v>3.232784</v>
       </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
         <v>-0.001252</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AE33" t="n">
+        <v>-0.001252</v>
+      </c>
+      <c r="AF33" t="n">
         <v>0.04</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AG33" t="n">
         <v>0.05</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AH33" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AI33" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -3358,81 +3938,99 @@
         <v>0.039484</v>
       </c>
       <c r="D34" t="n">
-        <v>0.89</v>
+        <v>0.039484</v>
       </c>
       <c r="E34" t="n">
         <v>0.46</v>
       </c>
       <c r="F34" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H34" t="n">
         <v>105.60427</v>
       </c>
-      <c r="G34" t="n">
-        <v>104.71213</v>
-      </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>5.2416</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>5.241</v>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
+        <v>5953960</v>
+      </c>
+      <c r="L34" t="n">
         <v>2278309</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>3675652</v>
       </c>
-      <c r="L34" t="n">
+      <c r="N34" t="n">
         <v>3.43</v>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>2.8</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="Q34" t="n">
         <v>27.75</v>
       </c>
-      <c r="O34" t="n">
+      <c r="R34" t="n">
         <v>355560</v>
       </c>
-      <c r="P34" t="n">
+      <c r="S34" t="n">
         <v>0.9333669999999999</v>
       </c>
-      <c r="Q34" t="n">
-        <v>-4.159973</v>
-      </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
         <v>1.349627</v>
       </c>
-      <c r="S34" t="n">
+      <c r="U34" t="n">
         <v>1.349783</v>
       </c>
-      <c r="T34" t="n">
+      <c r="V34" t="n">
+        <v>0.64951</v>
+      </c>
+      <c r="W34" t="n">
         <v>0.415624</v>
       </c>
-      <c r="U34" t="n">
+      <c r="X34" t="n">
         <v>0.795057</v>
       </c>
-      <c r="V34" t="n">
+      <c r="Y34" t="n">
         <v>1.126567</v>
       </c>
-      <c r="W34" t="n">
+      <c r="Z34" t="n">
+        <v>3.925952</v>
+      </c>
+      <c r="AA34" t="n">
         <v>-0.344269</v>
       </c>
-      <c r="X34" t="n">
+      <c r="AB34" t="n">
         <v>3.335647</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="AC34" t="n">
         <v>-0.25</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AD34" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AE34" t="n">
+        <v>-0.000684</v>
+      </c>
+      <c r="AF34" t="n">
         <v>0.06</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AG34" t="n">
         <v>0.04</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AH34" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AI34" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -3447,81 +4045,99 @@
         <v>0.03927</v>
       </c>
       <c r="D35" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F35" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
         <v>0.25</v>
       </c>
-      <c r="F35" t="n">
+      <c r="H35" t="n">
         <v>106.5891</v>
       </c>
-      <c r="G35" t="n">
-        <v>105.86915</v>
-      </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>5.5589</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>5.5583</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
+        <v>6041898</v>
+      </c>
+      <c r="L35" t="n">
         <v>2336858</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>3705041</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>3.29</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>2.64</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="Q35" t="n">
         <v>27.81</v>
       </c>
-      <c r="O35" t="n">
+      <c r="R35" t="n">
         <v>357827</v>
       </c>
-      <c r="P35" t="n">
+      <c r="S35" t="n">
         <v>0.932566</v>
       </c>
-      <c r="Q35" t="n">
-        <v>1.104953</v>
-      </c>
-      <c r="R35" t="n">
+      <c r="T35" t="n">
         <v>6.053495</v>
       </c>
-      <c r="S35" t="n">
+      <c r="U35" t="n">
         <v>6.054188</v>
       </c>
-      <c r="T35" t="n">
+      <c r="V35" t="n">
+        <v>1.476967</v>
+      </c>
+      <c r="W35" t="n">
         <v>2.569845</v>
       </c>
-      <c r="U35" t="n">
+      <c r="X35" t="n">
         <v>0.799559</v>
       </c>
-      <c r="V35" t="n">
+      <c r="Y35" t="n">
         <v>0.637586</v>
       </c>
-      <c r="W35" t="n">
+      <c r="Z35" t="n">
+        <v>4.227578</v>
+      </c>
+      <c r="AA35" t="n">
         <v>2.440035</v>
       </c>
-      <c r="X35" t="n">
+      <c r="AB35" t="n">
         <v>3.697684</v>
       </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AE35" t="n">
+        <v>-0.000214</v>
+      </c>
+      <c r="AF35" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AG35" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AH35" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AI35" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -3536,81 +4152,99 @@
         <v>0.03927</v>
       </c>
       <c r="D36" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F36" t="n">
         <v>0.61</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
         <v>0.26</v>
       </c>
-      <c r="F36" t="n">
+      <c r="H36" t="n">
         <v>107.06237</v>
       </c>
-      <c r="G36" t="n">
-        <v>111.509</v>
-      </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>5.6621</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>5.6615</v>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
+        <v>6069205</v>
+      </c>
+      <c r="L36" t="n">
         <v>2323362</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>3745844</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>3.3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>2.52</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="Q36" t="n">
         <v>27.74</v>
       </c>
-      <c r="O36" t="n">
+      <c r="R36" t="n">
         <v>363282</v>
       </c>
-      <c r="P36" t="n">
+      <c r="S36" t="n">
         <v>0.444014</v>
       </c>
-      <c r="Q36" t="n">
-        <v>5.327189</v>
-      </c>
-      <c r="R36" t="n">
+      <c r="T36" t="n">
         <v>1.856482</v>
       </c>
-      <c r="S36" t="n">
+      <c r="U36" t="n">
         <v>1.856683</v>
       </c>
-      <c r="T36" t="n">
+      <c r="V36" t="n">
+        <v>0.451961</v>
+      </c>
+      <c r="W36" t="n">
         <v>-0.577528</v>
       </c>
-      <c r="U36" t="n">
+      <c r="X36" t="n">
         <v>1.101283</v>
       </c>
-      <c r="V36" t="n">
+      <c r="Y36" t="n">
         <v>1.52448</v>
       </c>
-      <c r="W36" t="n">
+      <c r="Z36" t="n">
+        <v>4.498245</v>
+      </c>
+      <c r="AA36" t="n">
         <v>3.812368</v>
       </c>
-      <c r="X36" t="n">
+      <c r="AB36" t="n">
         <v>4.060953</v>
       </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
         <v>0.01</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AG36" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AH36" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AI36" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -3625,81 +4259,99 @@
         <v>0.03927</v>
       </c>
       <c r="D37" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F37" t="n">
         <v>0.29</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
         <v>-0.14</v>
       </c>
-      <c r="F37" t="n">
+      <c r="H37" t="n">
         <v>107.19174</v>
       </c>
-      <c r="G37" t="n">
-        <v>110.06254</v>
-      </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>5.6562</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>5.6556</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
+        <v>6135298</v>
+      </c>
+      <c r="L37" t="n">
         <v>2344397</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>3790900</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>3.33</v>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>2.55</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="Q37" t="n">
         <v>27.59</v>
       </c>
-      <c r="O37" t="n">
+      <c r="R37" t="n">
         <v>369214</v>
       </c>
-      <c r="P37" t="n">
+      <c r="S37" t="n">
         <v>0.120836</v>
       </c>
-      <c r="Q37" t="n">
-        <v>-1.297169</v>
-      </c>
-      <c r="R37" t="n">
+      <c r="T37" t="n">
         <v>-0.104202</v>
       </c>
-      <c r="S37" t="n">
+      <c r="U37" t="n">
         <v>-0.104213</v>
       </c>
-      <c r="T37" t="n">
+      <c r="V37" t="n">
+        <v>1.088989</v>
+      </c>
+      <c r="W37" t="n">
         <v>0.905369</v>
       </c>
-      <c r="U37" t="n">
+      <c r="X37" t="n">
         <v>1.202826</v>
       </c>
-      <c r="V37" t="n">
+      <c r="Y37" t="n">
         <v>1.632891</v>
       </c>
-      <c r="W37" t="n">
+      <c r="Z37" t="n">
+        <v>4.237599</v>
+      </c>
+      <c r="AA37" t="n">
         <v>4.259387</v>
       </c>
-      <c r="X37" t="n">
+      <c r="AB37" t="n">
         <v>3.707852</v>
       </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
         <v>0.03</v>
       </c>
-      <c r="AB37" t="n">
+      <c r="AG37" t="n">
         <v>0.03</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AH37" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AI37" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -3714,81 +4366,99 @@
         <v>0.039612</v>
       </c>
       <c r="D38" t="n">
+        <v>0.039612</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F38" t="n">
         <v>0.62</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>0.48</v>
       </c>
-      <c r="F38" t="n">
+      <c r="H38" t="n">
         <v>108.04382</v>
       </c>
-      <c r="G38" t="n">
-        <v>107.07852</v>
-      </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>5.4481</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>5.4475</v>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
+        <v>6216528</v>
+      </c>
+      <c r="L38" t="n">
         <v>2384828</v>
       </c>
-      <c r="K38" t="n">
+      <c r="M38" t="n">
         <v>3831700</v>
       </c>
-      <c r="L38" t="n">
+      <c r="N38" t="n">
         <v>3.34</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>2.56</v>
       </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="Q38" t="n">
         <v>27.49</v>
       </c>
-      <c r="O38" t="n">
+      <c r="R38" t="n">
         <v>372016</v>
       </c>
-      <c r="P38" t="n">
+      <c r="S38" t="n">
         <v>0.794912</v>
       </c>
-      <c r="Q38" t="n">
-        <v>-2.711204</v>
-      </c>
-      <c r="R38" t="n">
+      <c r="T38" t="n">
         <v>-3.679149</v>
       </c>
-      <c r="S38" t="n">
+      <c r="U38" t="n">
         <v>-3.679539</v>
       </c>
-      <c r="T38" t="n">
+      <c r="V38" t="n">
+        <v>1.323978</v>
+      </c>
+      <c r="W38" t="n">
         <v>1.72458</v>
       </c>
-      <c r="U38" t="n">
+      <c r="X38" t="n">
         <v>1.076262</v>
       </c>
-      <c r="V38" t="n">
+      <c r="Y38" t="n">
         <v>0.7589089999999999</v>
       </c>
-      <c r="W38" t="n">
+      <c r="Z38" t="n">
+        <v>4.42474</v>
+      </c>
+      <c r="AA38" t="n">
         <v>4.519075</v>
       </c>
-      <c r="X38" t="n">
+      <c r="AB38" t="n">
         <v>4.091149</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="AC38" t="n">
         <v>0.25</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AD38" t="n">
         <v>0.000342</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AE38" t="n">
+        <v>0.000342</v>
+      </c>
+      <c r="AF38" t="n">
         <v>0.01</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AG38" t="n">
         <v>0.01</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AH38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AI38" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -3803,81 +4473,99 @@
         <v>0.040168</v>
       </c>
       <c r="D39" t="n">
+        <v>0.040168</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F39" t="n">
         <v>1.52</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
         <v>0.61</v>
       </c>
-      <c r="F39" t="n">
+      <c r="H39" t="n">
         <v>108.2446</v>
       </c>
-      <c r="G39" t="n">
-        <v>109.18379</v>
-      </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>5.7779</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>5.7773</v>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
+        <v>6275117</v>
+      </c>
+      <c r="L39" t="n">
         <v>2397533</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>3877584</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>3.3</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>2.52</v>
       </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="Q39" t="n">
         <v>27.94</v>
       </c>
-      <c r="O39" t="n">
+      <c r="R39" t="n">
         <v>366096</v>
       </c>
-      <c r="P39" t="n">
+      <c r="S39" t="n">
         <v>0.185832</v>
       </c>
-      <c r="Q39" t="n">
-        <v>1.966099</v>
-      </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
         <v>6.053487</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>6.054153</v>
       </c>
-      <c r="T39" t="n">
+      <c r="V39" t="n">
+        <v>0.9424709999999999</v>
+      </c>
+      <c r="W39" t="n">
         <v>0.532743</v>
       </c>
-      <c r="U39" t="n">
+      <c r="X39" t="n">
         <v>1.197484</v>
       </c>
-      <c r="V39" t="n">
+      <c r="Y39" t="n">
         <v>-1.591329</v>
       </c>
-      <c r="W39" t="n">
+      <c r="Z39" t="n">
+        <v>4.758099</v>
+      </c>
+      <c r="AA39" t="n">
         <v>5.579866</v>
       </c>
-      <c r="X39" t="n">
+      <c r="AB39" t="n">
         <v>4.600584</v>
       </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
         <v>0.000556</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AE39" t="n">
+        <v>0.000556</v>
+      </c>
+      <c r="AF39" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AB39" t="n">
+      <c r="AG39" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AC39" t="n">
+      <c r="AH39" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AI39" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -3892,81 +4580,99 @@
         <v>0.04158</v>
       </c>
       <c r="D40" t="n">
+        <v>0.04158</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F40" t="n">
         <v>1.3</v>
       </c>
-      <c r="E40" t="n">
+      <c r="G40" t="n">
         <v>0.33</v>
       </c>
-      <c r="F40" t="n">
+      <c r="H40" t="n">
         <v>108.00109</v>
       </c>
-      <c r="G40" t="n">
-        <v>105.49006</v>
-      </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>6.0535</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>6.0529</v>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
+        <v>6365690</v>
+      </c>
+      <c r="L40" t="n">
         <v>2436022</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>3929668</v>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
         <v>3.27</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>2.5</v>
       </c>
-      <c r="N40" t="n">
+      <c r="P40" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Q40" t="n">
         <v>28.45</v>
       </c>
-      <c r="O40" t="n">
+      <c r="R40" t="n">
         <v>363003</v>
       </c>
-      <c r="P40" t="n">
+      <c r="S40" t="n">
         <v>-0.224963</v>
       </c>
-      <c r="Q40" t="n">
-        <v>-3.383039</v>
-      </c>
-      <c r="R40" t="n">
+      <c r="T40" t="n">
         <v>4.769899</v>
       </c>
-      <c r="S40" t="n">
+      <c r="U40" t="n">
         <v>4.770394</v>
       </c>
-      <c r="T40" t="n">
+      <c r="V40" t="n">
+        <v>1.443368</v>
+      </c>
+      <c r="W40" t="n">
         <v>1.605359</v>
       </c>
-      <c r="U40" t="n">
+      <c r="X40" t="n">
         <v>1.343208</v>
       </c>
-      <c r="V40" t="n">
+      <c r="Y40" t="n">
         <v>-0.8448600000000001</v>
       </c>
-      <c r="W40" t="n">
+      <c r="Z40" t="n">
+        <v>4.873011</v>
+      </c>
+      <c r="AA40" t="n">
         <v>6.325086</v>
       </c>
-      <c r="X40" t="n">
+      <c r="AB40" t="n">
         <v>4.840925</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="AC40" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AD40" t="n">
         <v>0.001412</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AE40" t="n">
+        <v>0.001412</v>
+      </c>
+      <c r="AF40" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AG40" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AH40" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AI40" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -3981,81 +4687,99 @@
         <v>0.044158</v>
       </c>
       <c r="D41" t="n">
+        <v>0.044158</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F41" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E41" t="n">
+      <c r="G41" t="n">
         <v>0.48</v>
       </c>
-      <c r="F41" t="n">
+      <c r="H41" t="n">
         <v>107.37012</v>
       </c>
-      <c r="G41" t="n">
-        <v>104.15552</v>
-      </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>6.1923</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>6.1917</v>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
+        <v>6464602</v>
+      </c>
+      <c r="L41" t="n">
         <v>2499177</v>
       </c>
-      <c r="K41" t="n">
+      <c r="M41" t="n">
         <v>3965425</v>
       </c>
-      <c r="L41" t="n">
+      <c r="N41" t="n">
         <v>3.08</v>
       </c>
-      <c r="M41" t="n">
+      <c r="O41" t="n">
         <v>2.21</v>
       </c>
-      <c r="N41" t="n">
+      <c r="P41" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="Q41" t="n">
         <v>28.5</v>
       </c>
-      <c r="O41" t="n">
+      <c r="R41" t="n">
         <v>329730</v>
       </c>
-      <c r="P41" t="n">
+      <c r="S41" t="n">
         <v>-0.584226</v>
       </c>
-      <c r="Q41" t="n">
-        <v>-1.265086</v>
-      </c>
-      <c r="R41" t="n">
+      <c r="T41" t="n">
         <v>2.292888</v>
       </c>
-      <c r="S41" t="n">
+      <c r="U41" t="n">
         <v>2.293116</v>
       </c>
-      <c r="T41" t="n">
+      <c r="V41" t="n">
+        <v>1.55383</v>
+      </c>
+      <c r="W41" t="n">
         <v>2.592546</v>
       </c>
-      <c r="U41" t="n">
+      <c r="X41" t="n">
         <v>0.909924</v>
       </c>
-      <c r="V41" t="n">
+      <c r="Y41" t="n">
         <v>-9.166040000000001</v>
       </c>
-      <c r="W41" t="n">
+      <c r="Z41" t="n">
+        <v>4.831296</v>
+      </c>
+      <c r="AA41" t="n">
         <v>6.536174</v>
       </c>
-      <c r="X41" t="n">
+      <c r="AB41" t="n">
         <v>4.767938</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="AC41" t="n">
         <v>1</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AD41" t="n">
         <v>0.002578</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AE41" t="n">
+        <v>0.002578</v>
+      </c>
+      <c r="AF41" t="n">
         <v>-0.19</v>
       </c>
-      <c r="AB41" t="n">
+      <c r="AG41" t="n">
         <v>-0.29</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AH41" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AI41" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -4070,81 +4794,99 @@
         <v>0.045833</v>
       </c>
       <c r="D42" t="n">
+        <v>0.045833</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F42" t="n">
         <v>0.27</v>
       </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" t="n">
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
         <v>108.09524</v>
       </c>
-      <c r="G42" t="n">
-        <v>102.62949</v>
-      </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>5.8301</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>5.8295</v>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
+        <v>6465016</v>
+      </c>
+      <c r="L42" t="n">
         <v>2451957</v>
       </c>
-      <c r="K42" t="n">
+      <c r="M42" t="n">
         <v>4013059</v>
       </c>
-      <c r="L42" t="n">
+      <c r="N42" t="n">
         <v>3.34</v>
       </c>
-      <c r="M42" t="n">
+      <c r="O42" t="n">
         <v>2.43</v>
       </c>
-      <c r="N42" t="n">
+      <c r="P42" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="Q42" t="n">
         <v>29.88</v>
       </c>
-      <c r="O42" t="n">
+      <c r="R42" t="n">
         <v>328303</v>
       </c>
-      <c r="P42" t="n">
+      <c r="S42" t="n">
         <v>0.675346</v>
       </c>
-      <c r="Q42" t="n">
-        <v>-1.465146</v>
-      </c>
-      <c r="R42" t="n">
+      <c r="T42" t="n">
         <v>-5.8492</v>
       </c>
-      <c r="S42" t="n">
+      <c r="U42" t="n">
         <v>-5.849767</v>
       </c>
-      <c r="T42" t="n">
+      <c r="V42" t="n">
+        <v>0.006404</v>
+      </c>
+      <c r="W42" t="n">
         <v>-1.889422</v>
       </c>
-      <c r="U42" t="n">
+      <c r="X42" t="n">
         <v>1.201233</v>
       </c>
-      <c r="V42" t="n">
+      <c r="Y42" t="n">
         <v>-0.432778</v>
       </c>
-      <c r="W42" t="n">
+      <c r="Z42" t="n">
+        <v>4.559874</v>
+      </c>
+      <c r="AA42" t="n">
         <v>6.749097</v>
       </c>
-      <c r="X42" t="n">
+      <c r="AB42" t="n">
         <v>4.174145</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="AC42" t="n">
         <v>1</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AD42" t="n">
         <v>0.001675</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AE42" t="n">
+        <v>0.001675</v>
+      </c>
+      <c r="AF42" t="n">
         <v>0.26</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AG42" t="n">
         <v>0.22</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AH42" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AI42" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -4159,81 +4901,99 @@
         <v>0.049037</v>
       </c>
       <c r="D43" t="n">
+        <v>0.049037</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="F43" t="n">
         <v>1.06</v>
       </c>
-      <c r="E43" t="n">
+      <c r="G43" t="n">
         <v>1.48</v>
       </c>
-      <c r="F43" t="n">
+      <c r="H43" t="n">
         <v>108.62006</v>
       </c>
-      <c r="G43" t="n">
-        <v>106.82599</v>
-      </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>5.8488</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>5.8482</v>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
+        <v>6511444</v>
+      </c>
+      <c r="L43" t="n">
         <v>2477151</v>
       </c>
-      <c r="K43" t="n">
+      <c r="M43" t="n">
         <v>4034293</v>
       </c>
-      <c r="L43" t="n">
+      <c r="N43" t="n">
         <v>3.41</v>
       </c>
-      <c r="M43" t="n">
+      <c r="O43" t="n">
         <v>2.52</v>
       </c>
-      <c r="N43" t="n">
+      <c r="P43" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Q43" t="n">
         <v>30.53</v>
       </c>
-      <c r="O43" t="n">
+      <c r="R43" t="n">
         <v>332508</v>
       </c>
-      <c r="P43" t="n">
+      <c r="S43" t="n">
         <v>0.485516</v>
       </c>
-      <c r="Q43" t="n">
-        <v>4.088981</v>
-      </c>
-      <c r="R43" t="n">
+      <c r="T43" t="n">
         <v>0.320749</v>
       </c>
-      <c r="S43" t="n">
+      <c r="U43" t="n">
         <v>0.320782</v>
       </c>
-      <c r="T43" t="n">
+      <c r="V43" t="n">
+        <v>0.7181419999999999</v>
+      </c>
+      <c r="W43" t="n">
         <v>1.027506</v>
       </c>
-      <c r="U43" t="n">
+      <c r="X43" t="n">
         <v>0.529123</v>
       </c>
-      <c r="V43" t="n">
+      <c r="Y43" t="n">
         <v>1.280829</v>
       </c>
-      <c r="W43" t="n">
+      <c r="Z43" t="n">
+        <v>5.05763</v>
+      </c>
+      <c r="AA43" t="n">
         <v>8.444549</v>
       </c>
-      <c r="X43" t="n">
+      <c r="AB43" t="n">
         <v>4.866504</v>
       </c>
-      <c r="Y43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" t="n">
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.003204</v>
       </c>
-      <c r="AA43" t="n">
+      <c r="AE43" t="n">
+        <v>0.003204</v>
+      </c>
+      <c r="AF43" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AB43" t="n">
+      <c r="AG43" t="n">
         <v>0.09</v>
       </c>
-      <c r="AC43" t="n">
+      <c r="AH43" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AI43" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -4248,81 +5008,99 @@
         <v>0.050508</v>
       </c>
       <c r="D44" t="n">
+        <v>0.050508</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F44" t="n">
         <v>-0.34</v>
       </c>
-      <c r="E44" t="n">
+      <c r="G44" t="n">
         <v>0.51</v>
       </c>
-      <c r="F44" t="n">
+      <c r="H44" t="n">
         <v>110.03287</v>
       </c>
-      <c r="G44" t="n">
-        <v>114.02067</v>
-      </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>5.7422</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>5.7416</v>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
+        <v>6576464</v>
+      </c>
+      <c r="L44" t="n">
         <v>2498262</v>
       </c>
-      <c r="K44" t="n">
+      <c r="M44" t="n">
         <v>4078202</v>
       </c>
-      <c r="L44" t="n">
+      <c r="N44" t="n">
         <v>3.44</v>
       </c>
-      <c r="M44" t="n">
+      <c r="O44" t="n">
         <v>2.49</v>
       </c>
-      <c r="N44" t="n">
+      <c r="P44" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="Q44" t="n">
         <v>31.34</v>
       </c>
-      <c r="O44" t="n">
+      <c r="R44" t="n">
         <v>336157</v>
       </c>
-      <c r="P44" t="n">
+      <c r="S44" t="n">
         <v>1.30069</v>
       </c>
-      <c r="Q44" t="n">
-        <v>6.734953</v>
-      </c>
-      <c r="R44" t="n">
+      <c r="T44" t="n">
         <v>-1.822596</v>
       </c>
-      <c r="S44" t="n">
+      <c r="U44" t="n">
         <v>-1.822783</v>
       </c>
-      <c r="T44" t="n">
+      <c r="V44" t="n">
+        <v>0.99855</v>
+      </c>
+      <c r="W44" t="n">
         <v>0.852229</v>
       </c>
-      <c r="U44" t="n">
+      <c r="X44" t="n">
         <v>1.088394</v>
       </c>
-      <c r="V44" t="n">
+      <c r="Y44" t="n">
         <v>1.097417</v>
       </c>
-      <c r="W44" t="n">
+      <c r="Z44" t="n">
+        <v>5.47719</v>
+      </c>
+      <c r="AA44" t="n">
         <v>8.586193</v>
       </c>
-      <c r="X44" t="n">
+      <c r="AB44" t="n">
         <v>5.201441</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="AC44" t="n">
         <v>1</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AD44" t="n">
         <v>0.001471</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AE44" t="n">
+        <v>0.001471</v>
+      </c>
+      <c r="AF44" t="n">
         <v>0.03</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="AG44" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AH44" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AI44" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -4337,81 +5115,99 @@
         <v>0.052531</v>
       </c>
       <c r="D45" t="n">
+        <v>0.052531</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F45" t="n">
         <v>0.24</v>
       </c>
-      <c r="E45" t="n">
+      <c r="G45" t="n">
         <v>0.48</v>
       </c>
-      <c r="F45" t="n">
+      <c r="H45" t="n">
         <v>109.52766</v>
       </c>
-      <c r="G45" t="n">
-        <v>112.59512</v>
-      </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>5.6608</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>5.6602</v>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
+        <v>6623948</v>
+      </c>
+      <c r="L45" t="n">
         <v>2512426</v>
       </c>
-      <c r="K45" t="n">
+      <c r="M45" t="n">
         <v>4111522</v>
       </c>
-      <c r="L45" t="n">
+      <c r="N45" t="n">
         <v>3.67</v>
       </c>
-      <c r="M45" t="n">
+      <c r="O45" t="n">
         <v>2.72</v>
       </c>
-      <c r="N45" t="n">
+      <c r="P45" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q45" t="n">
         <v>31.63</v>
       </c>
-      <c r="O45" t="n">
+      <c r="R45" t="n">
         <v>340789</v>
       </c>
-      <c r="P45" t="n">
+      <c r="S45" t="n">
         <v>-0.459145</v>
       </c>
-      <c r="Q45" t="n">
-        <v>-1.250256</v>
-      </c>
-      <c r="R45" t="n">
+      <c r="T45" t="n">
         <v>-1.417575</v>
       </c>
-      <c r="S45" t="n">
+      <c r="U45" t="n">
         <v>-1.417723</v>
       </c>
-      <c r="T45" t="n">
+      <c r="V45" t="n">
+        <v>0.722029</v>
+      </c>
+      <c r="W45" t="n">
         <v>0.566954</v>
       </c>
-      <c r="U45" t="n">
+      <c r="X45" t="n">
         <v>0.8170269999999999</v>
       </c>
-      <c r="V45" t="n">
+      <c r="Y45" t="n">
         <v>1.377928</v>
       </c>
-      <c r="W45" t="n">
+      <c r="Z45" t="n">
+        <v>5.529729</v>
+      </c>
+      <c r="AA45" t="n">
         <v>8.510418</v>
       </c>
-      <c r="X45" t="n">
+      <c r="AB45" t="n">
         <v>5.316736</v>
       </c>
-      <c r="Y45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="n">
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
         <v>0.002023</v>
       </c>
-      <c r="AA45" t="n">
+      <c r="AE45" t="n">
+        <v>0.002023</v>
+      </c>
+      <c r="AF45" t="n">
         <v>0.23</v>
       </c>
-      <c r="AB45" t="n">
+      <c r="AG45" t="n">
         <v>0.23</v>
       </c>
-      <c r="AC45" t="n">
+      <c r="AH45" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AI45" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -4426,81 +5222,99 @@
         <v>0.053936</v>
       </c>
       <c r="D46" t="n">
+        <v>0.053936</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F46" t="n">
         <v>-0.49</v>
       </c>
-      <c r="E46" t="n">
+      <c r="G46" t="n">
         <v>0.35</v>
       </c>
-      <c r="F46" t="n">
+      <c r="H46" t="n">
         <v>108.8862</v>
       </c>
-      <c r="G46" t="n">
-        <v>108.55704</v>
-      </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>5.7087</v>
       </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
         <v>5.7081</v>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
+        <v>6666287</v>
+      </c>
+      <c r="L46" t="n">
         <v>2532708</v>
       </c>
-      <c r="K46" t="n">
+      <c r="M46" t="n">
         <v>4133579</v>
       </c>
-      <c r="L46" t="n">
+      <c r="N46" t="n">
         <v>3.72</v>
       </c>
-      <c r="M46" t="n">
+      <c r="O46" t="n">
         <v>2.67</v>
       </c>
-      <c r="N46" t="n">
+      <c r="P46" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="Q46" t="n">
         <v>31.7</v>
       </c>
-      <c r="O46" t="n">
+      <c r="R46" t="n">
         <v>341459</v>
       </c>
-      <c r="P46" t="n">
+      <c r="S46" t="n">
         <v>-0.58566</v>
       </c>
-      <c r="Q46" t="n">
-        <v>-3.586372</v>
-      </c>
-      <c r="R46" t="n">
+      <c r="T46" t="n">
         <v>0.84617</v>
       </c>
-      <c r="S46" t="n">
+      <c r="U46" t="n">
         <v>0.84626</v>
       </c>
-      <c r="T46" t="n">
+      <c r="V46" t="n">
+        <v>0.639181</v>
+      </c>
+      <c r="W46" t="n">
         <v>0.807268</v>
       </c>
-      <c r="U46" t="n">
+      <c r="X46" t="n">
         <v>0.5364679999999999</v>
       </c>
-      <c r="V46" t="n">
+      <c r="Y46" t="n">
         <v>0.196603</v>
       </c>
-      <c r="W46" t="n">
+      <c r="Z46" t="n">
+        <v>5.319636</v>
+      </c>
+      <c r="AA46" t="n">
         <v>7.026183</v>
       </c>
-      <c r="X46" t="n">
+      <c r="AB46" t="n">
         <v>5.201418</v>
       </c>
-      <c r="Y46" t="n">
+      <c r="AC46" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z46" t="n">
+      <c r="AD46" t="n">
         <v>0.001405</v>
       </c>
-      <c r="AA46" t="n">
+      <c r="AE46" t="n">
+        <v>0.001405</v>
+      </c>
+      <c r="AF46" t="n">
         <v>0.05</v>
       </c>
-      <c r="AB46" t="n">
+      <c r="AG46" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AC46" t="n">
+      <c r="AH46" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AI46" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -4515,81 +5329,99 @@
         <v>0.054569</v>
       </c>
       <c r="D47" t="n">
+        <v>0.054569</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F47" t="n">
         <v>-1.67</v>
       </c>
-      <c r="E47" t="n">
+      <c r="G47" t="n">
         <v>0.23</v>
       </c>
-      <c r="F47" t="n">
+      <c r="H47" t="n">
         <v>108.80376</v>
       </c>
-      <c r="G47" t="n">
-        <v>107.36219</v>
-      </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>5.4571</v>
       </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
         <v>5.4565</v>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
+        <v>6703663</v>
+      </c>
+      <c r="L47" t="n">
         <v>2547693</v>
       </c>
-      <c r="K47" t="n">
+      <c r="M47" t="n">
         <v>4155970</v>
       </c>
-      <c r="L47" t="n">
+      <c r="N47" t="n">
         <v>3.75</v>
       </c>
-      <c r="M47" t="n">
+      <c r="O47" t="n">
         <v>2.67</v>
       </c>
-      <c r="N47" t="n">
+      <c r="P47" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="Q47" t="n">
         <v>31.85</v>
       </c>
-      <c r="O47" t="n">
+      <c r="R47" t="n">
         <v>344440</v>
       </c>
-      <c r="P47" t="n">
+      <c r="S47" t="n">
         <v>-0.075712</v>
       </c>
-      <c r="Q47" t="n">
-        <v>-1.100666</v>
-      </c>
-      <c r="R47" t="n">
+      <c r="T47" t="n">
         <v>-4.407308</v>
       </c>
-      <c r="S47" t="n">
+      <c r="U47" t="n">
         <v>-4.407771</v>
       </c>
-      <c r="T47" t="n">
+      <c r="V47" t="n">
+        <v>0.5606719999999999</v>
+      </c>
+      <c r="W47" t="n">
         <v>0.591659</v>
       </c>
-      <c r="U47" t="n">
+      <c r="X47" t="n">
         <v>0.541686</v>
       </c>
-      <c r="V47" t="n">
+      <c r="Y47" t="n">
         <v>0.873018</v>
       </c>
-      <c r="W47" t="n">
+      <c r="Z47" t="n">
+        <v>5.351165</v>
+      </c>
+      <c r="AA47" t="n">
         <v>4.393261</v>
       </c>
-      <c r="X47" t="n">
+      <c r="AB47" t="n">
         <v>5.18043</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="AC47" t="n">
         <v>0.25</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="AD47" t="n">
         <v>0.000633</v>
       </c>
-      <c r="AA47" t="n">
+      <c r="AE47" t="n">
+        <v>0.000633</v>
+      </c>
+      <c r="AF47" t="n">
         <v>0.03</v>
       </c>
-      <c r="AB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC47" t="n">
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AI47" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -4604,81 +5436,99 @@
         <v>0.055131</v>
       </c>
       <c r="D48" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F48" t="n">
         <v>-0.77</v>
       </c>
-      <c r="E48" t="n">
+      <c r="G48" t="n">
         <v>0.21</v>
       </c>
-      <c r="F48" t="n">
+      <c r="H48" t="n">
         <v>108.49869</v>
       </c>
-      <c r="G48" t="n">
-        <v>113.10928</v>
-      </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>5.6021</v>
       </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
         <v>5.6015</v>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
+        <v>6733209</v>
+      </c>
+      <c r="L48" t="n">
         <v>2544400</v>
       </c>
-      <c r="K48" t="n">
+      <c r="M48" t="n">
         <v>4188808</v>
       </c>
-      <c r="L48" t="n">
+      <c r="N48" t="n">
         <v>3.96</v>
       </c>
-      <c r="M48" t="n">
+      <c r="O48" t="n">
         <v>2.79</v>
       </c>
-      <c r="N48" t="n">
+      <c r="P48" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="Q48" t="n">
         <v>31.75</v>
       </c>
-      <c r="O48" t="n">
+      <c r="R48" t="n">
         <v>345111</v>
       </c>
-      <c r="P48" t="n">
+      <c r="S48" t="n">
         <v>-0.280386</v>
       </c>
-      <c r="Q48" t="n">
-        <v>5.352993</v>
-      </c>
-      <c r="R48" t="n">
+      <c r="T48" t="n">
         <v>2.657089</v>
       </c>
-      <c r="S48" t="n">
+      <c r="U48" t="n">
         <v>2.657381</v>
       </c>
-      <c r="T48" t="n">
+      <c r="V48" t="n">
+        <v>0.440744</v>
+      </c>
+      <c r="W48" t="n">
         <v>-0.129254</v>
       </c>
-      <c r="U48" t="n">
+      <c r="X48" t="n">
         <v>0.79014</v>
       </c>
-      <c r="V48" t="n">
+      <c r="Y48" t="n">
         <v>0.194809</v>
       </c>
-      <c r="W48" t="n">
+      <c r="Z48" t="n">
+        <v>5.225222</v>
+      </c>
+      <c r="AA48" t="n">
         <v>2.961368</v>
       </c>
-      <c r="X48" t="n">
+      <c r="AB48" t="n">
         <v>5.127976</v>
       </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
         <v>0.000562</v>
       </c>
-      <c r="AA48" t="n">
+      <c r="AE48" t="n">
+        <v>0.000562</v>
+      </c>
+      <c r="AF48" t="n">
         <v>0.21</v>
       </c>
-      <c r="AB48" t="n">
+      <c r="AG48" t="n">
         <v>0.12</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AH48" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AI48" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -4693,81 +5543,99 @@
         <v>0.055131</v>
       </c>
       <c r="D49" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="F49" t="n">
         <v>0.36</v>
       </c>
-      <c r="E49" t="n">
+      <c r="G49" t="n">
         <v>-0.21</v>
       </c>
-      <c r="F49" t="n">
+      <c r="H49" t="n">
         <v>108.82893</v>
       </c>
-      <c r="G49" t="n">
-        <v>110.38054</v>
-      </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>5.4264</v>
       </c>
-      <c r="I49" t="n">
+      <c r="J49" t="n">
         <v>5.4258</v>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
+        <v>6774436</v>
+      </c>
+      <c r="L49" t="n">
         <v>2546265</v>
       </c>
-      <c r="K49" t="n">
+      <c r="M49" t="n">
         <v>4228171</v>
       </c>
-      <c r="L49" t="n">
+      <c r="N49" t="n">
         <v>4.14</v>
       </c>
-      <c r="M49" t="n">
+      <c r="O49" t="n">
         <v>2.85</v>
       </c>
-      <c r="N49" t="n">
+      <c r="P49" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="Q49" t="n">
         <v>31.87</v>
       </c>
-      <c r="O49" t="n">
+      <c r="R49" t="n">
         <v>350767</v>
       </c>
-      <c r="P49" t="n">
+      <c r="S49" t="n">
         <v>0.304372</v>
       </c>
-      <c r="Q49" t="n">
-        <v>-2.412481</v>
-      </c>
-      <c r="R49" t="n">
+      <c r="T49" t="n">
         <v>-3.136324</v>
       </c>
-      <c r="S49" t="n">
+      <c r="U49" t="n">
         <v>-3.13666</v>
       </c>
-      <c r="T49" t="n">
+      <c r="V49" t="n">
+        <v>0.612293</v>
+      </c>
+      <c r="W49" t="n">
         <v>0.073298</v>
       </c>
-      <c r="U49" t="n">
+      <c r="X49" t="n">
         <v>0.9397180000000001</v>
       </c>
-      <c r="V49" t="n">
+      <c r="Y49" t="n">
         <v>1.638893</v>
       </c>
-      <c r="W49" t="n">
+      <c r="Z49" t="n">
+        <v>5.130501</v>
+      </c>
+      <c r="AA49" t="n">
         <v>3.033233</v>
       </c>
-      <c r="X49" t="n">
+      <c r="AB49" t="n">
         <v>5.054283</v>
       </c>
-      <c r="Y49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA49" t="n">
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
         <v>0.18</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AG49" t="n">
         <v>0.06</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AH49" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AI49" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -4782,81 +5650,99 @@
         <v>0.055131</v>
       </c>
       <c r="D50" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F50" t="n">
         <v>0.42</v>
       </c>
-      <c r="E50" t="n">
+      <c r="G50" t="n">
         <v>0.52</v>
       </c>
-      <c r="F50" t="n">
+      <c r="H50" t="n">
         <v>108.73548</v>
       </c>
-      <c r="G50" t="n">
-        <v>109.48375</v>
-      </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>5.3186</v>
       </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
         <v>5.318</v>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
+        <v>6852705</v>
+      </c>
+      <c r="L50" t="n">
         <v>2589817</v>
       </c>
-      <c r="K50" t="n">
+      <c r="M50" t="n">
         <v>4262888</v>
       </c>
-      <c r="L50" t="n">
+      <c r="N50" t="n">
         <v>4.09</v>
       </c>
-      <c r="M50" t="n">
+      <c r="O50" t="n">
         <v>2.77</v>
       </c>
-      <c r="N50" t="n">
+      <c r="P50" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="Q50" t="n">
         <v>31.47</v>
       </c>
-      <c r="O50" t="n">
+      <c r="R50" t="n">
         <v>356582</v>
       </c>
-      <c r="P50" t="n">
+      <c r="S50" t="n">
         <v>-0.085869</v>
       </c>
-      <c r="Q50" t="n">
-        <v>-0.812453</v>
-      </c>
-      <c r="R50" t="n">
+      <c r="T50" t="n">
         <v>-1.986584</v>
       </c>
-      <c r="S50" t="n">
+      <c r="U50" t="n">
         <v>-1.986804</v>
       </c>
-      <c r="T50" t="n">
+      <c r="V50" t="n">
+        <v>1.155358</v>
+      </c>
+      <c r="W50" t="n">
         <v>1.710427</v>
       </c>
-      <c r="U50" t="n">
+      <c r="X50" t="n">
         <v>0.821088</v>
       </c>
-      <c r="V50" t="n">
+      <c r="Y50" t="n">
         <v>1.657796</v>
       </c>
-      <c r="W50" t="n">
+      <c r="Z50" t="n">
+        <v>5.172369</v>
+      </c>
+      <c r="AA50" t="n">
         <v>2.828436</v>
       </c>
-      <c r="X50" t="n">
+      <c r="AB50" t="n">
         <v>5.096104</v>
       </c>
-      <c r="Y50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA50" t="n">
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AB50" t="n">
+      <c r="AG50" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AC50" t="n">
+      <c r="AH50" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AI50" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -4871,81 +5757,99 @@
         <v>0.055131</v>
       </c>
       <c r="D51" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F51" t="n">
         <v>-0.36</v>
       </c>
-      <c r="E51" t="n">
+      <c r="G51" t="n">
         <v>0.03</v>
       </c>
-      <c r="F51" t="n">
+      <c r="H51" t="n">
         <v>108.75326</v>
       </c>
-      <c r="G51" t="n">
-        <v>110.07682</v>
-      </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>5.3843</v>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
         <v>5.3837</v>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
+        <v>6923886</v>
+      </c>
+      <c r="L51" t="n">
         <v>2597630</v>
       </c>
-      <c r="K51" t="n">
+      <c r="M51" t="n">
         <v>4326256</v>
       </c>
-      <c r="L51" t="n">
+      <c r="N51" t="n">
         <v>4.18</v>
       </c>
-      <c r="M51" t="n">
+      <c r="O51" t="n">
         <v>2.82</v>
       </c>
-      <c r="N51" t="n">
+      <c r="P51" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="Q51" t="n">
         <v>32.04</v>
       </c>
-      <c r="O51" t="n">
+      <c r="R51" t="n">
         <v>357103</v>
       </c>
-      <c r="P51" t="n">
+      <c r="S51" t="n">
         <v>0.016352</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0.541697</v>
-      </c>
-      <c r="R51" t="n">
+      <c r="T51" t="n">
         <v>1.235287</v>
       </c>
-      <c r="S51" t="n">
+      <c r="U51" t="n">
         <v>1.235427</v>
       </c>
-      <c r="T51" t="n">
+      <c r="V51" t="n">
+        <v>1.038729</v>
+      </c>
+      <c r="W51" t="n">
         <v>0.301682</v>
       </c>
-      <c r="U51" t="n">
+      <c r="X51" t="n">
         <v>1.486504</v>
       </c>
-      <c r="V51" t="n">
+      <c r="Y51" t="n">
         <v>0.146109</v>
       </c>
-      <c r="W51" t="n">
+      <c r="Z51" t="n">
+        <v>4.680811</v>
+      </c>
+      <c r="AA51" t="n">
         <v>0.924206</v>
       </c>
-      <c r="X51" t="n">
+      <c r="AB51" t="n">
         <v>4.490243</v>
       </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
         <v>0.09</v>
       </c>
-      <c r="AB51" t="n">
+      <c r="AG51" t="n">
         <v>0.05</v>
       </c>
-      <c r="AC51" t="n">
+      <c r="AH51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AI51" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -4960,81 +5864,99 @@
         <v>0.055131</v>
       </c>
       <c r="D52" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F52" t="n">
         <v>0.27</v>
       </c>
-      <c r="E52" t="n">
+      <c r="G52" t="n">
         <v>0.03</v>
       </c>
-      <c r="F52" t="n">
+      <c r="H52" t="n">
         <v>109.25005</v>
       </c>
-      <c r="G52" t="n">
-        <v>106.59892</v>
-      </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>5.3338</v>
       </c>
-      <c r="I52" t="n">
+      <c r="J52" t="n">
         <v>5.3332</v>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
+        <v>7004223</v>
+      </c>
+      <c r="L52" t="n">
         <v>2616902</v>
       </c>
-      <c r="K52" t="n">
+      <c r="M52" t="n">
         <v>4387321</v>
       </c>
-      <c r="L52" t="n">
+      <c r="N52" t="n">
         <v>4.24</v>
       </c>
-      <c r="M52" t="n">
+      <c r="O52" t="n">
         <v>2.75</v>
       </c>
-      <c r="N52" t="n">
+      <c r="P52" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="Q52" t="n">
         <v>32.2</v>
       </c>
-      <c r="O52" t="n">
+      <c r="R52" t="n">
         <v>360578</v>
       </c>
-      <c r="P52" t="n">
+      <c r="S52" t="n">
         <v>0.456805</v>
       </c>
-      <c r="Q52" t="n">
-        <v>-3.159521</v>
-      </c>
-      <c r="R52" t="n">
+      <c r="T52" t="n">
         <v>-0.937912</v>
       </c>
-      <c r="S52" t="n">
+      <c r="U52" t="n">
         <v>-0.938017</v>
       </c>
-      <c r="T52" t="n">
+      <c r="V52" t="n">
+        <v>1.160288</v>
+      </c>
+      <c r="W52" t="n">
         <v>0.741907</v>
       </c>
-      <c r="U52" t="n">
+      <c r="X52" t="n">
         <v>1.411498</v>
       </c>
-      <c r="V52" t="n">
+      <c r="Y52" t="n">
         <v>0.973109</v>
       </c>
-      <c r="W52" t="n">
+      <c r="Z52" t="n">
+        <v>4.461836</v>
+      </c>
+      <c r="AA52" t="n">
         <v>-0.101973</v>
       </c>
-      <c r="X52" t="n">
+      <c r="AB52" t="n">
         <v>4.177803</v>
       </c>
-      <c r="Y52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z52" t="n">
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
         <v>-0</v>
       </c>
-      <c r="AA52" t="n">
+      <c r="AE52" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF52" t="n">
         <v>0.06</v>
       </c>
-      <c r="AB52" t="n">
+      <c r="AG52" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AC52" t="n">
+      <c r="AH52" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AI52" t="n">
         <v>0.16</v>
       </c>
     </row>
@@ -5049,81 +5971,99 @@
         <v>0.055131</v>
       </c>
       <c r="D53" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F53" t="n">
         <v>-0.01</v>
       </c>
-      <c r="E53" t="n">
+      <c r="G53" t="n">
         <v>0.21</v>
       </c>
-      <c r="F53" t="n">
+      <c r="H53" t="n">
         <v>109.4528</v>
       </c>
-      <c r="G53" t="n">
-        <v>107.18417</v>
-      </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>5.5024</v>
       </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
         <v>5.5018</v>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
+        <v>7137252</v>
+      </c>
+      <c r="L53" t="n">
         <v>2701735</v>
       </c>
-      <c r="K53" t="n">
+      <c r="M53" t="n">
         <v>4435517</v>
       </c>
-      <c r="L53" t="n">
+      <c r="N53" t="n">
         <v>4.2</v>
       </c>
-      <c r="M53" t="n">
+      <c r="O53" t="n">
         <v>2.7</v>
       </c>
-      <c r="N53" t="n">
+      <c r="P53" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="Q53" t="n">
         <v>31.87</v>
       </c>
-      <c r="O53" t="n">
+      <c r="R53" t="n">
         <v>358234</v>
       </c>
-      <c r="P53" t="n">
+      <c r="S53" t="n">
         <v>0.185583</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0.549021</v>
-      </c>
-      <c r="R53" t="n">
+      <c r="T53" t="n">
         <v>3.160973</v>
       </c>
-      <c r="S53" t="n">
+      <c r="U53" t="n">
         <v>3.161329</v>
       </c>
-      <c r="T53" t="n">
+      <c r="V53" t="n">
+        <v>1.899268</v>
+      </c>
+      <c r="W53" t="n">
         <v>3.241734</v>
       </c>
-      <c r="U53" t="n">
+      <c r="X53" t="n">
         <v>1.098529</v>
       </c>
-      <c r="V53" t="n">
+      <c r="Y53" t="n">
         <v>-0.650067</v>
       </c>
-      <c r="W53" t="n">
+      <c r="Z53" t="n">
+        <v>4.264385</v>
+      </c>
+      <c r="AA53" t="n">
         <v>-1.042167</v>
       </c>
-      <c r="X53" t="n">
+      <c r="AB53" t="n">
         <v>3.897866</v>
       </c>
-      <c r="Y53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA53" t="n">
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AB53" t="n">
+      <c r="AG53" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AC53" t="n">
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -5138,81 +6078,99 @@
         <v>0.055131</v>
       </c>
       <c r="D54" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F54" t="n">
         <v>0.41</v>
       </c>
-      <c r="E54" t="n">
+      <c r="G54" t="n">
         <v>0.39</v>
       </c>
-      <c r="F54" t="n">
+      <c r="H54" t="n">
         <v>110.04992</v>
       </c>
-      <c r="G54" t="n">
-        <v>103.77761</v>
-      </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>5.2301</v>
       </c>
-      <c r="I54" t="n">
+      <c r="J54" t="n">
         <v>5.2295</v>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
+        <v>7130762</v>
+      </c>
+      <c r="L54" t="n">
         <v>2654220</v>
       </c>
-      <c r="K54" t="n">
+      <c r="M54" t="n">
         <v>4476542</v>
       </c>
-      <c r="L54" t="n">
+      <c r="N54" t="n">
         <v>4.44</v>
       </c>
-      <c r="M54" t="n">
+      <c r="O54" t="n">
         <v>2.87</v>
       </c>
-      <c r="N54" t="n">
+      <c r="P54" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="Q54" t="n">
         <v>32.45</v>
       </c>
-      <c r="O54" t="n">
+      <c r="R54" t="n">
         <v>364367</v>
       </c>
-      <c r="P54" t="n">
+      <c r="S54" t="n">
         <v>0.54555</v>
       </c>
-      <c r="Q54" t="n">
-        <v>-3.178231</v>
-      </c>
-      <c r="R54" t="n">
+      <c r="T54" t="n">
         <v>-4.94875</v>
       </c>
-      <c r="S54" t="n">
+      <c r="U54" t="n">
         <v>-4.949289</v>
       </c>
-      <c r="T54" t="n">
+      <c r="V54" t="n">
+        <v>-0.090931</v>
+      </c>
+      <c r="W54" t="n">
         <v>-1.758685</v>
       </c>
-      <c r="U54" t="n">
+      <c r="X54" t="n">
         <v>0.92492</v>
       </c>
-      <c r="V54" t="n">
+      <c r="Y54" t="n">
         <v>1.712009</v>
       </c>
-      <c r="W54" t="n">
+      <c r="Z54" t="n">
+        <v>4.441351</v>
+      </c>
+      <c r="AA54" t="n">
         <v>-0.903999</v>
       </c>
-      <c r="X54" t="n">
+      <c r="AB54" t="n">
         <v>4.303068</v>
       </c>
-      <c r="Y54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA54" t="n">
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
         <v>0.24</v>
       </c>
-      <c r="AB54" t="n">
+      <c r="AG54" t="n">
         <v>0.17</v>
       </c>
-      <c r="AC54" t="n">
+      <c r="AH54" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AI54" t="n">
         <v>0.58</v>
       </c>
     </row>
@@ -5227,81 +6185,99 @@
         <v>0.055131</v>
       </c>
       <c r="D55" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F55" t="n">
         <v>-0.73</v>
       </c>
-      <c r="E55" t="n">
+      <c r="G55" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="F55" t="n">
+      <c r="H55" t="n">
         <v>110.7366</v>
       </c>
-      <c r="G55" t="n">
-        <v>106.76075</v>
-      </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>5.1495</v>
       </c>
-      <c r="I55" t="n">
+      <c r="J55" t="n">
         <v>5.1489</v>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
+        <v>7157783</v>
+      </c>
+      <c r="L55" t="n">
         <v>2656484</v>
       </c>
-      <c r="K55" t="n">
+      <c r="M55" t="n">
         <v>4501299</v>
       </c>
-      <c r="L55" t="n">
+      <c r="N55" t="n">
         <v>4.64</v>
       </c>
-      <c r="M55" t="n">
+      <c r="O55" t="n">
         <v>3.07</v>
       </c>
-      <c r="N55" t="n">
+      <c r="P55" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="Q55" t="n">
         <v>32.63</v>
       </c>
-      <c r="O55" t="n">
+      <c r="R55" t="n">
         <v>371074</v>
       </c>
-      <c r="P55" t="n">
+      <c r="S55" t="n">
         <v>0.6239710000000001</v>
       </c>
-      <c r="Q55" t="n">
-        <v>2.874551</v>
-      </c>
-      <c r="R55" t="n">
+      <c r="T55" t="n">
         <v>-1.54108</v>
       </c>
-      <c r="S55" t="n">
+      <c r="U55" t="n">
         <v>-1.541256</v>
       </c>
-      <c r="T55" t="n">
+      <c r="V55" t="n">
+        <v>0.378936</v>
+      </c>
+      <c r="W55" t="n">
         <v>0.085298</v>
       </c>
-      <c r="U55" t="n">
+      <c r="X55" t="n">
         <v>0.553038</v>
       </c>
-      <c r="V55" t="n">
+      <c r="Y55" t="n">
         <v>1.840727</v>
       </c>
-      <c r="W55" t="n">
+      <c r="Z55" t="n">
+        <v>3.812497</v>
+      </c>
+      <c r="AA55" t="n">
         <v>-2.659212</v>
       </c>
-      <c r="X55" t="n">
+      <c r="AB55" t="n">
         <v>3.357475</v>
       </c>
-      <c r="Y55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" t="n">
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="n">
         <v>0.2</v>
       </c>
-      <c r="AB55" t="n">
+      <c r="AG55" t="n">
         <v>0.2</v>
       </c>
-      <c r="AC55" t="n">
+      <c r="AH55" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AI55" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -5316,81 +6292,99 @@
         <v>0.054777</v>
       </c>
       <c r="D56" t="n">
+        <v>0.054777</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F56" t="n">
         <v>0.52</v>
       </c>
-      <c r="E56" t="n">
+      <c r="G56" t="n">
         <v>0.91</v>
       </c>
-      <c r="F56" t="n">
+      <c r="H56" t="n">
         <v>110.58808</v>
       </c>
-      <c r="G56" t="n">
-        <v>118.01719</v>
-      </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
         <v>5.2194</v>
       </c>
-      <c r="I56" t="n">
+      <c r="J56" t="n">
         <v>5.2188</v>
       </c>
-      <c r="J56" t="n">
+      <c r="K56" t="n">
+        <v>7240557</v>
+      </c>
+      <c r="L56" t="n">
         <v>2687535</v>
       </c>
-      <c r="K56" t="n">
+      <c r="M56" t="n">
         <v>4553022</v>
       </c>
-      <c r="L56" t="n">
+      <c r="N56" t="n">
         <v>4.52</v>
       </c>
-      <c r="M56" t="n">
+      <c r="O56" t="n">
         <v>3.06</v>
       </c>
-      <c r="N56" t="n">
+      <c r="P56" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="Q56" t="n">
         <v>32.84</v>
       </c>
-      <c r="O56" t="n">
+      <c r="R56" t="n">
         <v>362002</v>
       </c>
-      <c r="P56" t="n">
+      <c r="S56" t="n">
         <v>-0.13412</v>
       </c>
-      <c r="Q56" t="n">
-        <v>10.543613</v>
-      </c>
-      <c r="R56" t="n">
+      <c r="T56" t="n">
         <v>1.357413</v>
       </c>
-      <c r="S56" t="n">
+      <c r="U56" t="n">
         <v>1.357572</v>
       </c>
-      <c r="T56" t="n">
+      <c r="V56" t="n">
+        <v>1.15642</v>
+      </c>
+      <c r="W56" t="n">
         <v>1.168876</v>
       </c>
-      <c r="U56" t="n">
+      <c r="X56" t="n">
         <v>1.149068</v>
       </c>
-      <c r="V56" t="n">
+      <c r="Y56" t="n">
         <v>-2.444795</v>
       </c>
-      <c r="W56" t="n">
+      <c r="Z56" t="n">
+        <v>4.142847</v>
+      </c>
+      <c r="AA56" t="n">
         <v>-1.819225</v>
       </c>
-      <c r="X56" t="n">
+      <c r="AB56" t="n">
         <v>3.768807</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="AC56" t="n">
         <v>-0.25</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="AD56" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="AA56" t="n">
+      <c r="AE56" t="n">
+        <v>-0.000354</v>
+      </c>
+      <c r="AF56" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AB56" t="n">
+      <c r="AG56" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AC56" t="n">
+      <c r="AH56" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="AI56" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -5405,81 +6399,99 @@
         <v>0.054223</v>
       </c>
       <c r="D57" t="n">
+        <v>0.054223</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F57" t="n">
         <v>2.73</v>
       </c>
-      <c r="E57" t="n">
+      <c r="G57" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="F57" t="n">
+      <c r="H57" t="n">
         <v>110.90009</v>
       </c>
-      <c r="G57" t="n">
-        <v>113.99295</v>
-      </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>4.9886</v>
       </c>
-      <c r="I57" t="n">
+      <c r="J57" t="n">
         <v>4.988</v>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
+        <v>7259766</v>
+      </c>
+      <c r="L57" t="n">
         <v>2685397</v>
       </c>
-      <c r="K57" t="n">
+      <c r="M57" t="n">
         <v>4574368</v>
       </c>
-      <c r="L57" t="n">
+      <c r="N57" t="n">
         <v>4.64</v>
       </c>
-      <c r="M57" t="n">
+      <c r="O57" t="n">
         <v>3.15</v>
       </c>
-      <c r="N57" t="n">
+      <c r="P57" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="Q57" t="n">
         <v>33.36</v>
       </c>
-      <c r="O57" t="n">
+      <c r="R57" t="n">
         <v>366913</v>
       </c>
-      <c r="P57" t="n">
+      <c r="S57" t="n">
         <v>0.282137</v>
       </c>
-      <c r="Q57" t="n">
-        <v>-3.409876</v>
-      </c>
-      <c r="R57" t="n">
+      <c r="T57" t="n">
         <v>-4.421964</v>
       </c>
-      <c r="S57" t="n">
+      <c r="U57" t="n">
         <v>-4.422473</v>
       </c>
-      <c r="T57" t="n">
+      <c r="V57" t="n">
+        <v>0.265297</v>
+      </c>
+      <c r="W57" t="n">
         <v>-0.079552</v>
       </c>
-      <c r="U57" t="n">
+      <c r="X57" t="n">
         <v>0.468831</v>
       </c>
-      <c r="V57" t="n">
+      <c r="Y57" t="n">
         <v>1.356622</v>
       </c>
-      <c r="W57" t="n">
+      <c r="Z57" t="n">
+        <v>4.39172</v>
+      </c>
+      <c r="AA57" t="n">
         <v>0.619623</v>
       </c>
-      <c r="X57" t="n">
+      <c r="AB57" t="n">
         <v>4.109608</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="AC57" t="n">
         <v>-0.25</v>
       </c>
-      <c r="Z57" t="n">
+      <c r="AD57" t="n">
         <v>-0.000554</v>
       </c>
-      <c r="AA57" t="n">
+      <c r="AE57" t="n">
+        <v>-0.000554</v>
+      </c>
+      <c r="AF57" t="n">
         <v>0.12</v>
       </c>
-      <c r="AB57" t="n">
+      <c r="AG57" t="n">
         <v>0.09</v>
       </c>
-      <c r="AC57" t="n">
+      <c r="AH57" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AI57" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -5494,81 +6506,99 @@
         <v>0.0534</v>
       </c>
       <c r="D58" t="n">
+        <v>0.0534</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F58" t="n">
         <v>0.84</v>
       </c>
-      <c r="E58" t="n">
+      <c r="G58" t="n">
         <v>0.65</v>
       </c>
-      <c r="F58" t="n">
+      <c r="H58" t="n">
         <v>111.13846</v>
       </c>
-      <c r="G58" t="n">
-        <v>109.65479</v>
-      </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>5.0569</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>5.0563</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
+        <v>7305306</v>
+      </c>
+      <c r="L58" t="n">
         <v>2708154</v>
       </c>
-      <c r="K58" t="n">
+      <c r="M58" t="n">
         <v>4597152</v>
       </c>
-      <c r="L58" t="n">
+      <c r="N58" t="n">
         <v>4.74</v>
       </c>
-      <c r="M58" t="n">
+      <c r="O58" t="n">
         <v>3.25</v>
       </c>
-      <c r="N58" t="n">
+      <c r="P58" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="Q58" t="n">
         <v>33.1</v>
       </c>
-      <c r="O58" t="n">
+      <c r="R58" t="n">
         <v>371137</v>
       </c>
-      <c r="P58" t="n">
+      <c r="S58" t="n">
         <v>0.214941</v>
       </c>
-      <c r="Q58" t="n">
-        <v>-3.805639</v>
-      </c>
-      <c r="R58" t="n">
+      <c r="T58" t="n">
         <v>1.369122</v>
       </c>
-      <c r="S58" t="n">
+      <c r="U58" t="n">
         <v>1.369286</v>
       </c>
-      <c r="T58" t="n">
+      <c r="V58" t="n">
+        <v>0.627293</v>
+      </c>
+      <c r="W58" t="n">
         <v>0.847435</v>
       </c>
-      <c r="U58" t="n">
+      <c r="X58" t="n">
         <v>0.49808</v>
       </c>
-      <c r="V58" t="n">
+      <c r="Y58" t="n">
         <v>1.151227</v>
       </c>
-      <c r="W58" t="n">
+      <c r="Z58" t="n">
+        <v>4.724907</v>
+      </c>
+      <c r="AA58" t="n">
         <v>1.964454</v>
       </c>
-      <c r="X58" t="n">
+      <c r="AB58" t="n">
         <v>4.420848</v>
       </c>
-      <c r="Y58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z58" t="n">
+      <c r="AC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" t="n">
         <v>-0.0008229999999999999</v>
       </c>
-      <c r="AA58" t="n">
+      <c r="AE58" t="n">
+        <v>-0.0008229999999999999</v>
+      </c>
+      <c r="AF58" t="n">
         <v>0.1</v>
       </c>
-      <c r="AB58" t="n">
+      <c r="AG58" t="n">
         <v>0.1</v>
       </c>
-      <c r="AC58" t="n">
+      <c r="AH58" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AI58" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -5583,81 +6613,99 @@
         <v>0.053028</v>
       </c>
       <c r="D59" t="n">
+        <v>0.053028</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F59" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E59" t="n">
+      <c r="G59" t="n">
         <v>0.14</v>
       </c>
-      <c r="F59" t="n">
+      <c r="H59" t="n">
         <v>110.15775</v>
       </c>
-      <c r="G59" t="n">
-        <v>109.94156</v>
-      </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
         <v>5.1766</v>
       </c>
-      <c r="I59" t="n">
+      <c r="J59" t="n">
         <v>5.176</v>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
+        <v>7353293</v>
+      </c>
+      <c r="L59" t="n">
         <v>2750625</v>
       </c>
-      <c r="K59" t="n">
+      <c r="M59" t="n">
         <v>4602668</v>
       </c>
-      <c r="L59" t="n">
+      <c r="N59" t="n">
         <v>4.58</v>
       </c>
-      <c r="M59" t="n">
+      <c r="O59" t="n">
         <v>3.18</v>
       </c>
-      <c r="N59" t="n">
+      <c r="P59" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="Q59" t="n">
         <v>33.33</v>
       </c>
-      <c r="O59" t="n">
+      <c r="R59" t="n">
         <v>367558</v>
       </c>
-      <c r="P59" t="n">
+      <c r="S59" t="n">
         <v>-0.882422</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0.261521</v>
-      </c>
-      <c r="R59" t="n">
+      <c r="T59" t="n">
         <v>2.367063</v>
       </c>
-      <c r="S59" t="n">
+      <c r="U59" t="n">
         <v>2.367344</v>
       </c>
-      <c r="T59" t="n">
+      <c r="V59" t="n">
+        <v>0.656879</v>
+      </c>
+      <c r="W59" t="n">
         <v>1.568264</v>
       </c>
-      <c r="U59" t="n">
+      <c r="X59" t="n">
         <v>0.119987</v>
       </c>
-      <c r="V59" t="n">
+      <c r="Y59" t="n">
         <v>-0.964334</v>
       </c>
-      <c r="W59" t="n">
+      <c r="Z59" t="n">
+        <v>4.641328</v>
+      </c>
+      <c r="AA59" t="n">
         <v>3.177699</v>
       </c>
-      <c r="X59" t="n">
+      <c r="AB59" t="n">
         <v>4.327084</v>
       </c>
-      <c r="Y59" t="n">
+      <c r="AC59" t="n">
         <v>-0.25</v>
       </c>
-      <c r="Z59" t="n">
+      <c r="AD59" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AA59" t="n">
+      <c r="AE59" t="n">
+        <v>-0.000372</v>
+      </c>
+      <c r="AF59" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AB59" t="n">
+      <c r="AG59" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AC59" t="n">
+      <c r="AH59" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AI59" t="n">
         <v>0.23</v>
       </c>
     </row>
@@ -5672,81 +6720,99 @@
         <v>0.052531</v>
       </c>
       <c r="D60" t="n">
+        <v>0.052531</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F60" t="n">
         <v>-1.16</v>
       </c>
-      <c r="E60" t="n">
+      <c r="G60" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F60" t="n">
+      <c r="H60" t="n">
         <v>109.91611</v>
       </c>
-      <c r="G60" t="n">
-        <v>114.40189</v>
-      </c>
-      <c r="H60" t="n">
+      <c r="I60" t="n">
         <v>5.0773</v>
       </c>
-      <c r="I60" t="n">
+      <c r="J60" t="n">
         <v>5.0767</v>
       </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
+        <v>7372243</v>
+      </c>
+      <c r="L60" t="n">
         <v>2731513</v>
       </c>
-      <c r="K60" t="n">
+      <c r="M60" t="n">
         <v>4640730</v>
       </c>
-      <c r="L60" t="n">
+      <c r="N60" t="n">
         <v>4.88</v>
       </c>
-      <c r="M60" t="n">
+      <c r="O60" t="n">
         <v>3.31</v>
       </c>
-      <c r="N60" t="n">
+      <c r="P60" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="Q60" t="n">
         <v>32.08</v>
       </c>
-      <c r="O60" t="n">
+      <c r="R60" t="n">
         <v>369742</v>
       </c>
-      <c r="P60" t="n">
+      <c r="S60" t="n">
         <v>-0.219358</v>
       </c>
-      <c r="Q60" t="n">
-        <v>4.057001</v>
-      </c>
-      <c r="R60" t="n">
+      <c r="T60" t="n">
         <v>-1.918247</v>
       </c>
-      <c r="S60" t="n">
+      <c r="U60" t="n">
         <v>-1.91847</v>
       </c>
-      <c r="T60" t="n">
+      <c r="V60" t="n">
+        <v>0.257708</v>
+      </c>
+      <c r="W60" t="n">
         <v>-0.694824</v>
       </c>
-      <c r="U60" t="n">
+      <c r="X60" t="n">
         <v>0.826955</v>
       </c>
-      <c r="V60" t="n">
+      <c r="Y60" t="n">
         <v>0.5941920000000001</v>
       </c>
-      <c r="W60" t="n">
+      <c r="Z60" t="n">
+        <v>4.443025</v>
+      </c>
+      <c r="AA60" t="n">
         <v>2.772183</v>
       </c>
-      <c r="X60" t="n">
+      <c r="AB60" t="n">
         <v>4.098046</v>
       </c>
-      <c r="Y60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z60" t="n">
+      <c r="AC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="AA60" t="n">
+      <c r="AE60" t="n">
+        <v>-0.000497</v>
+      </c>
+      <c r="AF60" t="n">
         <v>0.3</v>
       </c>
-      <c r="AB60" t="n">
+      <c r="AG60" t="n">
         <v>0.13</v>
       </c>
-      <c r="AC60" t="n">
+      <c r="AH60" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AI60" t="n">
         <v>-1.25</v>
       </c>
     </row>
@@ -5761,55 +6827,69 @@
         <v>0.051784</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.22</v>
+        <v>0.051784</v>
       </c>
       <c r="E61" t="n">
         <v>-0.32</v>
       </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="n">
+      <c r="F61" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="n">
         <v>5.1816</v>
       </c>
-      <c r="I61" t="n">
+      <c r="J61" t="n">
         <v>5.181</v>
       </c>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
-      <c r="O61" t="n">
-        <v>372616</v>
-      </c>
+      <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="n">
+        <v>372616</v>
+      </c>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="n">
         <v>2.054241</v>
       </c>
-      <c r="S61" t="n">
+      <c r="U61" t="n">
         <v>2.054484</v>
       </c>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="n">
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="n">
         <v>0.777299</v>
       </c>
-      <c r="W61" t="n">
+      <c r="Z61" t="n">
+        <v>4.223453</v>
+      </c>
+      <c r="AA61" t="n">
         <v>2.178243</v>
       </c>
-      <c r="X61" t="n">
+      <c r="AB61" t="n">
         <v>3.983297</v>
       </c>
-      <c r="Y61" t="n">
+      <c r="AC61" t="n">
         <v>-0.25</v>
       </c>
-      <c r="Z61" t="n">
+      <c r="AD61" t="n">
         <v>-0.0007470000000000001</v>
       </c>
-      <c r="AA61" t="inlineStr"/>
-      <c r="AB61" t="inlineStr"/>
-      <c r="AC61" t="inlineStr"/>
+      <c r="AE61" t="n">
+        <v>-0.0007470000000000001</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -5819,19 +6899,21 @@
         <v>13.75</v>
       </c>
       <c r="C62" t="n">
+        <v>0.051526</v>
+      </c>
+      <c r="D62" t="n">
         <v>0.051587</v>
       </c>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="n">
-        <v>5.1521</v>
-      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>5.1515</v>
-      </c>
-      <c r="J62" t="inlineStr"/>
+        <v>5.1575</v>
+      </c>
+      <c r="J62" t="n">
+        <v>5.1569</v>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -5839,26 +6921,34 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="n">
-        <v>-0.569322</v>
-      </c>
-      <c r="S62" t="n">
-        <v>-0.569388</v>
-      </c>
-      <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="n">
+        <v>-0.465107</v>
+      </c>
+      <c r="U62" t="n">
+        <v>-0.465161</v>
+      </c>
       <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
-      <c r="Y62" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>-0.000197</v>
-      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr"/>
-      <c r="AC62" t="inlineStr"/>
+      <c r="AC62" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>-0.000259</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>-0.000197</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI62"/>
+  <dimension ref="A1:AK62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,135 +463,145 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>ibc_br</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>cambio_venda_usd</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>cambio_compra_usd</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>saldo_credito_total</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>saldo_credito_pj</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>saldo_credito_pf</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inadimplencia_total</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inadimplencia_pj</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inadimplencia_pf</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>var_pct_ibc_br</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ipca_acum_12m</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>inpc_acum_12m</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>dif_selic_over</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>dif_cdi</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -623,36 +633,38 @@
         <v>96.96513</v>
       </c>
       <c r="I2" t="n">
+        <v>97.10777</v>
+      </c>
+      <c r="J2" t="n">
         <v>5.4394</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>5.4388</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>4441056</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>1894119</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>2546936</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>2.34</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1.43</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>3.01</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>21.42</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>368886</v>
       </c>
-      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -669,6 +681,8 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -696,78 +710,84 @@
         <v>97.48671</v>
       </c>
       <c r="I3" t="n">
+        <v>96.53041</v>
+      </c>
+      <c r="J3" t="n">
         <v>5.643</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>5.6424</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>4511956</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>1910940</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>2601017</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>2.33</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>1.43</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>2.99</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>22.89</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>367927</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>0.537905</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
+        <v>-0.594556</v>
+      </c>
+      <c r="V3" t="n">
         <v>3.74306</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>3.743473</v>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
         <v>1.596467</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>0.888065</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>2.123375</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AA3" t="n">
         <v>-0.259972</v>
       </c>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="n">
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AF3" t="n">
         <v>0.001809</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AG3" t="n">
         <v>0.001809</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AH3" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AK3" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -797,78 +817,84 @@
         <v>99.05526</v>
       </c>
       <c r="I4" t="n">
+        <v>97.85277000000001</v>
+      </c>
+      <c r="J4" t="n">
         <v>5.6199</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>5.6193</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>4597507</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>1933111</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2664395</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>2.36</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>1.46</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>3.01</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>23.91</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>367772</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>1.608989</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
+        <v>1.36989</v>
+      </c>
+      <c r="V4" t="n">
         <v>-0.409357</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>-0.4094</v>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>1.896096</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Y4" t="n">
         <v>1.160214</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Z4" t="n">
         <v>2.436662</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AA4" t="n">
         <v>-0.042128</v>
       </c>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
         <v>0.005012</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AG4" t="n">
         <v>0.005012</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AH4" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AI4" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AJ4" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AK4" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -898,78 +924,84 @@
         <v>99.37716</v>
       </c>
       <c r="I5" t="n">
+        <v>99.32258</v>
+      </c>
+      <c r="J5" t="n">
         <v>5.5805</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>5.5799</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>4682852</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>1974391</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>2708461</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>2.35</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>1.4</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>3.05</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>24.21</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>362204</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>0.32497</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
+        <v>1.502063</v>
+      </c>
+      <c r="V5" t="n">
         <v>-0.70108</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>-0.701155</v>
       </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
         <v>1.856332</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Y5" t="n">
         <v>2.135418</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>1.653884</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AA5" t="n">
         <v>-1.513981</v>
       </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="n">
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AF5" t="n">
         <v>0.00406</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AG5" t="n">
         <v>0.00406</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AH5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AI5" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AJ5" t="n">
         <v>0.04</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AK5" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -999,78 +1031,84 @@
         <v>97.4213</v>
       </c>
       <c r="I6" t="n">
+        <v>91.67776000000001</v>
+      </c>
+      <c r="J6" t="n">
         <v>5.3574</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>5.3568</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>4682131</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>1947035</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>2735096</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>2.51</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>1.46</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>3.26</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>25.23</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>358398</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>-1.968118</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
+        <v>-7.696961</v>
+      </c>
+      <c r="V6" t="n">
         <v>-3.99785</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>-3.99828</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>-0.015397</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
         <v>-1.385541</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Z6" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AA6" t="n">
         <v>-1.050789</v>
       </c>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
         <v>0.001433</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AG6" t="n">
         <v>0.001433</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AH6" t="n">
         <v>0.16</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AI6" t="n">
         <v>0.06</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AJ6" t="n">
         <v>0.21</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AK6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1100,78 +1138,84 @@
         <v>98.4804</v>
       </c>
       <c r="I7" t="n">
+        <v>95.63728999999999</v>
+      </c>
+      <c r="J7" t="n">
         <v>5.1394</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>5.1388</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>4727818</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>1971524</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>2756295</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>2.57</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>1.44</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>3.38</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>25.63</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>357740</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>1.087134</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
+        <v>4.318965</v>
+      </c>
+      <c r="V7" t="n">
         <v>-4.069138</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>-4.069594</v>
       </c>
-      <c r="V7" t="n">
+      <c r="X7" t="n">
         <v>0.975774</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
         <v>1.257759</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>0.775073</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AA7" t="n">
         <v>-0.183595</v>
       </c>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="n">
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AF7" t="n">
         <v>0.004849</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AG7" t="n">
         <v>0.004849</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AH7" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AI7" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AJ7" t="n">
         <v>0.12</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AK7" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1201,78 +1245,84 @@
         <v>99.54801999999999</v>
       </c>
       <c r="I8" t="n">
+        <v>104.53237</v>
+      </c>
+      <c r="J8" t="n">
         <v>4.7378</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>4.7372</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>4794583</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>1994119</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>2800464</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>2.66</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>1.55</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>3.45</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>26.54</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>353169</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>1.084094</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
+        <v>9.300848999999999</v>
+      </c>
+      <c r="V8" t="n">
         <v>-7.814142</v>
       </c>
-      <c r="U8" t="n">
+      <c r="W8" t="n">
         <v>-7.815054</v>
       </c>
-      <c r="V8" t="n">
+      <c r="X8" t="n">
         <v>1.412174</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Y8" t="n">
         <v>1.146068</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Z8" t="n">
         <v>1.602477</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AA8" t="n">
         <v>-1.277744</v>
       </c>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="n">
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="n">
         <v>1</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AF8" t="n">
         <v>0.002356</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AG8" t="n">
         <v>0.002356</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AH8" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AI8" t="n">
         <v>0.11</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AJ8" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AK8" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1302,78 +1352,84 @@
         <v>99.44118</v>
       </c>
       <c r="I9" t="n">
+        <v>100.22938</v>
+      </c>
+      <c r="J9" t="n">
         <v>4.9191</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>4.9185</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>4833732</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>2003312</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>2830420</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>2.72</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>1.57</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>3.54</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>27.46</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>345097</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>-0.107325</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
+        <v>-4.116419</v>
+      </c>
+      <c r="V9" t="n">
         <v>3.826671</v>
       </c>
-      <c r="U9" t="n">
+      <c r="W9" t="n">
         <v>3.827155</v>
       </c>
-      <c r="V9" t="n">
+      <c r="X9" t="n">
         <v>0.816526</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Y9" t="n">
         <v>0.461006</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Z9" t="n">
         <v>1.06968</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AA9" t="n">
         <v>-2.285591</v>
       </c>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
         <v>0.001785</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AG9" t="n">
         <v>0.001785</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AH9" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AI9" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AJ9" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AK9" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1403,78 +1459,84 @@
         <v>99.6454</v>
       </c>
       <c r="I10" t="n">
+        <v>99.74383</v>
+      </c>
+      <c r="J10" t="n">
         <v>4.7289</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>4.7283</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4889397</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>2013726</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>2875671</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>2.79</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>1.57</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>27.42</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>346415</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>0.205368</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
+        <v>-0.484439</v>
+      </c>
+      <c r="V10" t="n">
         <v>-3.866561</v>
       </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
         <v>-3.867033</v>
       </c>
-      <c r="V10" t="n">
+      <c r="X10" t="n">
         <v>1.151595</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Y10" t="n">
         <v>0.5198390000000001</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Z10" t="n">
         <v>1.598738</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AA10" t="n">
         <v>0.381922</v>
       </c>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="n">
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="n">
         <v>1</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AF10" t="n">
         <v>0.003057</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AG10" t="n">
         <v>0.003057</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AH10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AK10" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1504,78 +1566,84 @@
         <v>99.51048</v>
       </c>
       <c r="I11" t="n">
+        <v>99.31653</v>
+      </c>
+      <c r="J11" t="n">
         <v>5.238</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>5.2374</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>4965603</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>2052569</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>2913035</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>2.73</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>1.52</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>3.57</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>27.88</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>341958</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>-0.1354</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
+        <v>-0.428397</v>
+      </c>
+      <c r="V11" t="n">
         <v>10.765717</v>
       </c>
-      <c r="U11" t="n">
+      <c r="W11" t="n">
         <v>10.767083</v>
       </c>
-      <c r="V11" t="n">
+      <c r="X11" t="n">
         <v>1.558597</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Y11" t="n">
         <v>1.928912</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Z11" t="n">
         <v>1.299314</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AA11" t="n">
         <v>-1.286607</v>
       </c>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="n">
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AF11" t="n">
         <v>0.00132</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AG11" t="n">
         <v>0.00132</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AH11" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AI11" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AJ11" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AK11" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1605,78 +1673,84 @@
         <v>101.43172</v>
       </c>
       <c r="I12" t="n">
+        <v>103.95991</v>
+      </c>
+      <c r="J12" t="n">
         <v>5.1884</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>5.1878</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>4999244</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>2047038</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>2952207</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>2.84</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>1.6</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>29.24</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>346403</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>1.930691</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
+        <v>4.675335</v>
+      </c>
+      <c r="V12" t="n">
         <v>-0.946926</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>-0.947035</v>
       </c>
-      <c r="V12" t="n">
+      <c r="X12" t="n">
         <v>0.677481</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Y12" t="n">
         <v>-0.269467</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Z12" t="n">
         <v>1.344714</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AA12" t="n">
         <v>1.299867</v>
       </c>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AG12" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AH12" t="n">
         <v>0.11</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AI12" t="n">
         <v>0.08</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AJ12" t="n">
         <v>0.14</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AK12" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -1706,84 +1780,90 @@
         <v>101.10583</v>
       </c>
       <c r="I13" t="n">
+        <v>104.51156</v>
+      </c>
+      <c r="J13" t="n">
         <v>5.179</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>5.1784</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>5072711</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>2064183</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>3008528</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>2.9</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>1.62</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>3.78</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>28.6</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>339664</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>-0.32129</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
+        <v>0.530637</v>
+      </c>
+      <c r="V13" t="n">
         <v>-0.181173</v>
       </c>
-      <c r="U13" t="n">
+      <c r="W13" t="n">
         <v>-0.181194</v>
       </c>
-      <c r="V13" t="n">
+      <c r="X13" t="n">
         <v>1.469562</v>
       </c>
-      <c r="W13" t="n">
+      <c r="Y13" t="n">
         <v>0.837552</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Z13" t="n">
         <v>1.907759</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AA13" t="n">
         <v>-1.945422</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AB13" t="n">
         <v>8.727061000000001</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AC13" t="n">
         <v>8.58755</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AD13" t="n">
         <v>8.825751</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AE13" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AF13" t="n">
         <v>0.001523</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AG13" t="n">
         <v>0.001523</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AH13" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AI13" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AJ13" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AK13" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -1813,84 +1893,90 @@
         <v>101.16034</v>
       </c>
       <c r="I14" t="n">
+        <v>101.1889</v>
+      </c>
+      <c r="J14" t="n">
         <v>5.4066</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>5.406</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>5164775</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>2109806</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3054969</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>2.92</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>1.65</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>3.8</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>28.57</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>327580</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>0.053914</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
+        <v>-3.179227</v>
+      </c>
+      <c r="V14" t="n">
         <v>4.394671</v>
       </c>
-      <c r="U14" t="n">
+      <c r="W14" t="n">
         <v>4.39518</v>
       </c>
-      <c r="V14" t="n">
+      <c r="X14" t="n">
         <v>1.814888</v>
       </c>
-      <c r="W14" t="n">
+      <c r="Y14" t="n">
         <v>2.210221</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Z14" t="n">
         <v>1.543645</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AA14" t="n">
         <v>-3.557633</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AB14" t="n">
         <v>7.168596</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AC14" t="n">
         <v>8.248760000000001</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AD14" t="n">
         <v>7.191214</v>
       </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
         <v>0.000228</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AG14" t="n">
         <v>0.000228</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0.03</v>
       </c>
       <c r="AH14" t="n">
         <v>0.02</v>
       </c>
       <c r="AI14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AK14" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -1920,84 +2006,90 @@
         <v>101.44171</v>
       </c>
       <c r="I15" t="n">
+        <v>100.08177</v>
+      </c>
+      <c r="J15" t="n">
         <v>5.257</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>5.2564</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>5215990</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>2105856</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>3110134</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>3.04</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>1.77</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>3.89</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>29.68</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>325546</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>0.278143</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
+        <v>-1.094122</v>
+      </c>
+      <c r="V15" t="n">
         <v>-2.766988</v>
       </c>
-      <c r="U15" t="n">
+      <c r="W15" t="n">
         <v>-2.767296</v>
       </c>
-      <c r="V15" t="n">
+      <c r="X15" t="n">
         <v>0.991621</v>
       </c>
-      <c r="W15" t="n">
+      <c r="Y15" t="n">
         <v>-0.187221</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Z15" t="n">
         <v>1.805747</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AA15" t="n">
         <v>-0.6209170000000001</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AB15" t="n">
         <v>6.470016</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AC15" t="n">
         <v>6.517038</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AD15" t="n">
         <v>6.460076</v>
       </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
       <c r="AE15" t="n">
         <v>0</v>
       </c>
       <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
         <v>0.12</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AI15" t="n">
         <v>0.12</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AJ15" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AK15" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -2027,84 +2119,90 @@
         <v>100.7146</v>
       </c>
       <c r="I16" t="n">
+        <v>99.15031999999999</v>
+      </c>
+      <c r="J16" t="n">
         <v>5.2941</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>5.2935</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>5285657</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>2130312</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>3155345</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>3.07</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>1.81</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>3.92</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>30.52</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>331505</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>-0.716776</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
+        <v>-0.930689</v>
+      </c>
+      <c r="V16" t="n">
         <v>0.705726</v>
       </c>
-      <c r="U16" t="n">
+      <c r="W16" t="n">
         <v>0.705806</v>
       </c>
-      <c r="V16" t="n">
+      <c r="X16" t="n">
         <v>1.335643</v>
       </c>
-      <c r="W16" t="n">
+      <c r="Y16" t="n">
         <v>1.161333</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Z16" t="n">
         <v>1.453667</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AA16" t="n">
         <v>1.830463</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AB16" t="n">
         <v>5.900488</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AC16" t="n">
         <v>5.899363</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AD16" t="n">
         <v>5.974439</v>
       </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
       <c r="AE16" t="n">
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
         <v>0.03</v>
       </c>
       <c r="AI16" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AK16" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2134,84 +2232,90 @@
         <v>100.58818</v>
       </c>
       <c r="I17" t="n">
+        <v>99.97037</v>
+      </c>
+      <c r="J17" t="n">
         <v>5.2177</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>5.2171</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>5366069</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>2178236</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>3187833</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>3.07</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>1.8</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>3.94</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>29.64</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>324703</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>-0.125523</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
+        <v>0.827078</v>
+      </c>
+      <c r="V17" t="n">
         <v>-1.443116</v>
       </c>
-      <c r="U17" t="n">
+      <c r="W17" t="n">
         <v>-1.443279</v>
       </c>
-      <c r="V17" t="n">
+      <c r="X17" t="n">
         <v>1.521325</v>
       </c>
-      <c r="W17" t="n">
+      <c r="Y17" t="n">
         <v>2.249624</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Z17" t="n">
         <v>1.029618</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AA17" t="n">
         <v>-2.051854</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AB17" t="n">
         <v>5.784842</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AC17" t="n">
         <v>5.458422</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AD17" t="n">
         <v>5.932356</v>
       </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
         <v>-0</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AG17" t="n">
         <v>-0</v>
       </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AJ17" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AK17" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -2241,84 +2345,90 @@
         <v>100.10988</v>
       </c>
       <c r="I18" t="n">
+        <v>95.09953</v>
+      </c>
+      <c r="J18" t="n">
         <v>5.0993</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>5.0987</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>5373231</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>2151399</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>3221831</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>3.24</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>1.94</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>4.11</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>30.54</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>331122</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>-0.475503</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
+        <v>-4.872284</v>
+      </c>
+      <c r="V18" t="n">
         <v>-2.269199</v>
       </c>
-      <c r="U18" t="n">
+      <c r="W18" t="n">
         <v>-2.26946</v>
       </c>
-      <c r="V18" t="n">
+      <c r="X18" t="n">
         <v>0.133468</v>
       </c>
-      <c r="W18" t="n">
+      <c r="Y18" t="n">
         <v>-1.232052</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Z18" t="n">
         <v>1.066493</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AA18" t="n">
         <v>1.976883</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AB18" t="n">
         <v>5.77432</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AC18" t="n">
         <v>3.79089</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AD18" t="n">
         <v>5.711379</v>
       </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
         <v>0.17</v>
       </c>
       <c r="AI18" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AK18" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2348,84 +2458,90 @@
         <v>103.07987</v>
       </c>
       <c r="I19" t="n">
+        <v>98.64798</v>
+      </c>
+      <c r="J19" t="n">
         <v>5.2078</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>5.2072</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>5370950</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>2136105</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>3234845</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>3.36</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>2.17</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>4.16</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>30.48</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>328098</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>2.96673</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
+        <v>3.731301</v>
+      </c>
+      <c r="V19" t="n">
         <v>2.127743</v>
       </c>
-      <c r="U19" t="n">
+      <c r="W19" t="n">
         <v>2.127993</v>
       </c>
-      <c r="V19" t="n">
+      <c r="X19" t="n">
         <v>-0.042451</v>
       </c>
-      <c r="W19" t="n">
+      <c r="Y19" t="n">
         <v>-0.710886</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Z19" t="n">
         <v>0.403932</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AA19" t="n">
         <v>-0.913259</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AB19" t="n">
         <v>5.596302</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AC19" t="n">
         <v>1.864495</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AD19" t="n">
         <v>5.47065</v>
       </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
       <c r="AE19" t="n">
         <v>0</v>
       </c>
       <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
         <v>0.12</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AI19" t="n">
         <v>0.23</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AJ19" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AK19" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2455,84 +2571,90 @@
         <v>103.08494</v>
       </c>
       <c r="I20" t="n">
+        <v>110.61922</v>
+      </c>
+      <c r="J20" t="n">
         <v>5.0804</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>5.0798</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>5424811</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>2154900</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>3269910</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>3.35</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>2.2</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>4.11</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>30.99</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>341158</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>0.004919</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
+        <v>12.135312</v>
+      </c>
+      <c r="V20" t="n">
         <v>-2.446331</v>
       </c>
-      <c r="U20" t="n">
+      <c r="W20" t="n">
         <v>-2.446612</v>
       </c>
-      <c r="V20" t="n">
+      <c r="X20" t="n">
         <v>1.002821</v>
       </c>
-      <c r="W20" t="n">
+      <c r="Y20" t="n">
         <v>0.879872</v>
       </c>
-      <c r="X20" t="n">
+      <c r="Z20" t="n">
         <v>1.083978</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AA20" t="n">
         <v>3.980518</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AB20" t="n">
         <v>4.650694</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AC20" t="n">
         <v>0.172427</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AD20" t="n">
         <v>4.361088</v>
       </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
       <c r="AE20" t="n">
         <v>0</v>
       </c>
       <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AI20" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AJ20" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AK20" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2562,84 +2684,90 @@
         <v>103.93573</v>
       </c>
       <c r="I21" t="n">
+        <v>104.04095</v>
+      </c>
+      <c r="J21" t="n">
         <v>5.0007</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>5.0001</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>5426307</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>2145000</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>3281308</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>3.54</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>2.45</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>4.26</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>31.62</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>345725</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>0.825329</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
+        <v>-5.946769</v>
+      </c>
+      <c r="V21" t="n">
         <v>-1.568774</v>
       </c>
-      <c r="U21" t="n">
+      <c r="W21" t="n">
         <v>-1.568959</v>
       </c>
-      <c r="V21" t="n">
+      <c r="X21" t="n">
         <v>0.027577</v>
       </c>
-      <c r="W21" t="n">
+      <c r="Y21" t="n">
         <v>-0.459418</v>
       </c>
-      <c r="X21" t="n">
+      <c r="Z21" t="n">
         <v>0.348572</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AA21" t="n">
         <v>1.338676</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AB21" t="n">
         <v>4.184706</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AC21" t="n">
         <v>-2.158772</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AD21" t="n">
         <v>3.834324</v>
       </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
       <c r="AE21" t="n">
         <v>0</v>
       </c>
       <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
         <v>0.19</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AI21" t="n">
         <v>0.25</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AJ21" t="n">
         <v>0.15</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AK21" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -2669,84 +2797,90 @@
         <v>102.42973</v>
       </c>
       <c r="I22" t="n">
+        <v>102.71375</v>
+      </c>
+      <c r="J22" t="n">
         <v>5.0959</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>5.0953</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>5453708</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>2145530</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>3308178</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>3.65</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>2.58</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>4.35</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>31.63</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>343489</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>-1.448972</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
+        <v>-1.275652</v>
+      </c>
+      <c r="V22" t="n">
         <v>1.903733</v>
       </c>
-      <c r="U22" t="n">
+      <c r="W22" t="n">
         <v>1.903962</v>
       </c>
-      <c r="V22" t="n">
+      <c r="X22" t="n">
         <v>0.504966</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Y22" t="n">
         <v>0.024709</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Z22" t="n">
         <v>0.818881</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AA22" t="n">
         <v>-0.646757</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AB22" t="n">
         <v>3.935832</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AC22" t="n">
         <v>-4.45588</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AD22" t="n">
         <v>3.741292</v>
       </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
         <v>-0</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AG22" t="n">
         <v>-0</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AH22" t="n">
         <v>0.11</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AI22" t="n">
         <v>0.13</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AJ22" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI22" t="n">
+      <c r="AK22" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -2776,84 +2910,90 @@
         <v>102.39935</v>
       </c>
       <c r="I23" t="n">
+        <v>102.28352</v>
+      </c>
+      <c r="J23" t="n">
         <v>4.8192</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>4.8186</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>5479459</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>2169613</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>3309846</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>3.61</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>2.63</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>4.25</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>30.85</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>343620</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>-0.029659</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
+        <v>-0.418863</v>
+      </c>
+      <c r="V23" t="n">
         <v>-5.429855</v>
       </c>
-      <c r="U23" t="n">
+      <c r="W23" t="n">
         <v>-5.430495</v>
       </c>
-      <c r="V23" t="n">
+      <c r="X23" t="n">
         <v>0.472174</v>
       </c>
-      <c r="W23" t="n">
+      <c r="Y23" t="n">
         <v>1.122473</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Z23" t="n">
         <v>0.050421</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AA23" t="n">
         <v>0.038138</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AB23" t="n">
         <v>3.161501</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AC23" t="n">
         <v>-6.84947</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AD23" t="n">
         <v>2.998957</v>
       </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
       <c r="AE23" t="n">
         <v>0</v>
       </c>
       <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AI23" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AJ23" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AK23" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -2883,84 +3023,90 @@
         <v>102.90686</v>
       </c>
       <c r="I24" t="n">
+        <v>105.34474</v>
+      </c>
+      <c r="J24" t="n">
         <v>4.7415</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>4.7409</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>5484871</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>2153541</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>3331330</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>3.63</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>2.73</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>4.22</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>30.43</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>345476</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>0.495618</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
+        <v>2.992877</v>
+      </c>
+      <c r="V24" t="n">
         <v>-1.612301</v>
       </c>
-      <c r="U24" t="n">
+      <c r="W24" t="n">
         <v>-1.612502</v>
       </c>
-      <c r="V24" t="n">
+      <c r="X24" t="n">
         <v>0.098769</v>
       </c>
-      <c r="W24" t="n">
+      <c r="Y24" t="n">
         <v>-0.740777</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Z24" t="n">
         <v>0.6490939999999999</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AA24" t="n">
         <v>0.5401319999999999</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AB24" t="n">
         <v>3.992444</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AC24" t="n">
         <v>-7.713954</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AD24" t="n">
         <v>3.527423</v>
       </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
       <c r="AE24" t="n">
         <v>0</v>
       </c>
       <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AI24" t="n">
         <v>0.1</v>
       </c>
-      <c r="AH24" t="n">
+      <c r="AJ24" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AK24" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -2990,84 +3136,90 @@
         <v>102.50239</v>
       </c>
       <c r="I25" t="n">
+        <v>106.05687</v>
+      </c>
+      <c r="J25" t="n">
         <v>4.9219</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>4.9213</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5559063</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>2172658</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>3386405</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>3.61</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>2.82</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>4.12</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>29.92</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>344177</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>-0.393045</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="V25" t="n">
         <v>3.804703</v>
       </c>
-      <c r="U25" t="n">
+      <c r="W25" t="n">
         <v>3.805185</v>
       </c>
-      <c r="V25" t="n">
+      <c r="X25" t="n">
         <v>1.352666</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Y25" t="n">
         <v>0.887701</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Z25" t="n">
         <v>1.653244</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AA25" t="n">
         <v>-0.376003</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AB25" t="n">
         <v>4.608216</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AC25" t="n">
         <v>-7.193509</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AD25" t="n">
         <v>4.057054</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AE25" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AF25" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AG25" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AH25" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AI25" t="n">
         <v>0.09</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AJ25" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="AK25" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -3097,84 +3249,90 @@
         <v>102.5153</v>
       </c>
       <c r="I26" t="n">
+        <v>101.75897</v>
+      </c>
+      <c r="J26" t="n">
         <v>5.0076</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>5.007</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>5625945</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>2215175</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>3410769</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>3.54</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>2.82</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>4</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>29.66</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>340324</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>0.012595</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
+        <v>-4.052448</v>
+      </c>
+      <c r="V26" t="n">
         <v>1.741198</v>
       </c>
-      <c r="U26" t="n">
+      <c r="W26" t="n">
         <v>1.74141</v>
       </c>
-      <c r="V26" t="n">
+      <c r="X26" t="n">
         <v>1.203116</v>
       </c>
-      <c r="W26" t="n">
+      <c r="Y26" t="n">
         <v>1.956912</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Z26" t="n">
         <v>0.719465</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AA26" t="n">
         <v>-1.119482</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AB26" t="n">
         <v>5.185235</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AC26" t="n">
         <v>-5.956714</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AD26" t="n">
         <v>4.505936</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AE26" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AF26" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AG26" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="AF26" t="n">
+      <c r="AH26" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AK26" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -3204,84 +3362,90 @@
         <v>102.83959</v>
       </c>
       <c r="I27" t="n">
+        <v>101.9338</v>
+      </c>
+      <c r="J27" t="n">
         <v>5.0575</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>5.0569</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>5653808</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>2204808</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>3449000</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>3.56</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>2.92</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>3.97</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>29.24</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>340247</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>0.316333</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
+        <v>0.171808</v>
+      </c>
+      <c r="V27" t="n">
         <v>0.996485</v>
       </c>
-      <c r="U27" t="n">
+      <c r="W27" t="n">
         <v>0.996605</v>
       </c>
-      <c r="V27" t="n">
+      <c r="X27" t="n">
         <v>0.495259</v>
       </c>
-      <c r="W27" t="n">
+      <c r="Y27" t="n">
         <v>-0.467999</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Z27" t="n">
         <v>1.120891</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AA27" t="n">
         <v>-0.022625</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AB27" t="n">
         <v>4.819246</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AC27" t="n">
         <v>-4.560737</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AD27" t="n">
         <v>4.141877</v>
       </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AG27" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AH27" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AI27" t="n">
         <v>0.1</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="AJ27" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AK27" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3311,84 +3475,90 @@
         <v>103.59456</v>
       </c>
       <c r="I28" t="n">
+        <v>101.68042</v>
+      </c>
+      <c r="J28" t="n">
         <v>4.9355</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>4.9349</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>5711103</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>2220766</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>3490337</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>3.53</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>2.99</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>3.88</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>29.01</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>348406</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>0.734124</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
+        <v>-0.248573</v>
+      </c>
+      <c r="V28" t="n">
         <v>-2.412259</v>
       </c>
-      <c r="U28" t="n">
+      <c r="W28" t="n">
         <v>-2.412545</v>
       </c>
-      <c r="V28" t="n">
+      <c r="X28" t="n">
         <v>1.013388</v>
       </c>
-      <c r="W28" t="n">
+      <c r="Y28" t="n">
         <v>0.723782</v>
       </c>
-      <c r="X28" t="n">
+      <c r="Z28" t="n">
         <v>1.198521</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AA28" t="n">
         <v>2.397964</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AB28" t="n">
         <v>4.683537</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AC28" t="n">
         <v>-3.457004</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AD28" t="n">
         <v>3.851383</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AE28" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AF28" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AG28" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AH28" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AI28" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AH28" t="n">
+      <c r="AJ28" t="n">
         <v>-0.09</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AK28" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -3418,84 +3588,90 @@
         <v>104.88818</v>
       </c>
       <c r="I29" t="n">
+        <v>101.68469</v>
+      </c>
+      <c r="J29" t="n">
         <v>4.8413</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>4.8407</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>5805157</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>2283485</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>3521672</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>3.29</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>2.59</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>28.14</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>355034</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>1.248734</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
+        <v>0.004199</v>
+      </c>
+      <c r="V29" t="n">
         <v>-1.908621</v>
       </c>
-      <c r="U29" t="n">
+      <c r="W29" t="n">
         <v>-1.908853</v>
       </c>
-      <c r="V29" t="n">
+      <c r="X29" t="n">
         <v>1.646862</v>
       </c>
-      <c r="W29" t="n">
+      <c r="Y29" t="n">
         <v>2.824206</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Z29" t="n">
         <v>0.897764</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AA29" t="n">
         <v>1.902378</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AB29" t="n">
         <v>4.621114</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AC29" t="n">
         <v>-3.178284</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AD29" t="n">
         <v>3.706988</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AE29" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AF29" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AG29" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AH29" t="n">
         <v>-0.24</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AI29" t="n">
         <v>-0.4</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AJ29" t="n">
         <v>-0.13</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AK29" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3525,84 +3701,90 @@
         <v>104.473</v>
       </c>
       <c r="I30" t="n">
+        <v>99.29718</v>
+      </c>
+      <c r="J30" t="n">
         <v>4.9535</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>4.9529</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>5794707</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>2234362</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3560345</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>3.38</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2.77</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>3.76</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>28</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>355066</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>-0.395831</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
+        <v>-2.347954</v>
+      </c>
+      <c r="V30" t="n">
         <v>2.317559</v>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>2.317847</v>
       </c>
-      <c r="V30" t="n">
+      <c r="X30" t="n">
         <v>-0.180012</v>
       </c>
-      <c r="W30" t="n">
+      <c r="Y30" t="n">
         <v>-2.151229</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Z30" t="n">
         <v>1.098143</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AA30" t="n">
         <v>0.009013</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AB30" t="n">
         <v>4.506637</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AC30" t="n">
         <v>-3.31355</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AD30" t="n">
         <v>3.820543</v>
       </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AG30" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AH30" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AI30" t="n">
         <v>0.18</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AJ30" t="n">
         <v>0.01</v>
       </c>
-      <c r="AI30" t="n">
+      <c r="AK30" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -3632,84 +3814,90 @@
         <v>104.65885</v>
       </c>
       <c r="I31" t="n">
+        <v>102.15036</v>
+      </c>
+      <c r="J31" t="n">
         <v>4.9833</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>4.9827</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>5815954</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>2235302</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>3580652</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>3.38</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>2.76</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>3.76</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>27.85</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>352705</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>0.177893</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
+        <v>2.873375</v>
+      </c>
+      <c r="V31" t="n">
         <v>0.601595</v>
       </c>
-      <c r="U31" t="n">
+      <c r="W31" t="n">
         <v>0.601668</v>
       </c>
-      <c r="V31" t="n">
+      <c r="X31" t="n">
         <v>0.366662</v>
       </c>
-      <c r="W31" t="n">
+      <c r="Y31" t="n">
         <v>0.04207</v>
       </c>
-      <c r="X31" t="n">
+      <c r="Z31" t="n">
         <v>0.570366</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AA31" t="n">
         <v>-0.664947</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AB31" t="n">
         <v>4.496274</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AC31" t="n">
         <v>-3.758575</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AD31" t="n">
         <v>3.861754</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AE31" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AF31" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AG31" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -3739,84 +3927,90 @@
         <v>104.6738</v>
       </c>
       <c r="I32" t="n">
+        <v>109.56901</v>
+      </c>
+      <c r="J32" t="n">
         <v>4.9962</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>4.9956</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>5899742</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>2285775</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>3613967</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>3.33</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>2.71</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>28.14</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>355008</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>0.014285</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
+        <v>7.262481</v>
+      </c>
+      <c r="V32" t="n">
         <v>0.258865</v>
       </c>
-      <c r="U32" t="n">
+      <c r="W32" t="n">
         <v>0.258896</v>
       </c>
-      <c r="V32" t="n">
+      <c r="X32" t="n">
         <v>1.440658</v>
       </c>
-      <c r="W32" t="n">
+      <c r="Y32" t="n">
         <v>2.257995</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Z32" t="n">
         <v>0.930417</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AA32" t="n">
         <v>0.652954</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AB32" t="n">
         <v>3.925596</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AC32" t="n">
         <v>-4.25878</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AD32" t="n">
         <v>3.397348</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AE32" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AF32" t="n">
         <v>-0.000537</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AG32" t="n">
         <v>-0.000537</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>-0.05</v>
       </c>
       <c r="AH32" t="n">
         <v>-0.05</v>
       </c>
       <c r="AI32" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK32" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -3846,84 +4040,90 @@
         <v>104.62771</v>
       </c>
       <c r="I33" t="n">
+        <v>109.2572</v>
+      </c>
+      <c r="J33" t="n">
         <v>5.1718</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>5.1712</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5915538</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>2268879</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3646659</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>3.37</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>2.76</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>27.86</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>351599</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>-0.044032</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
+        <v>-0.284579</v>
+      </c>
+      <c r="V33" t="n">
         <v>3.514671</v>
       </c>
-      <c r="U33" t="n">
+      <c r="W33" t="n">
         <v>3.515093</v>
       </c>
-      <c r="V33" t="n">
+      <c r="X33" t="n">
         <v>0.267741</v>
       </c>
-      <c r="W33" t="n">
+      <c r="Y33" t="n">
         <v>-0.7391799999999999</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Z33" t="n">
         <v>0.904602</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AA33" t="n">
         <v>-0.96026</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AB33" t="n">
         <v>3.688016</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AC33" t="n">
         <v>-3.040871</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AD33" t="n">
         <v>3.232784</v>
       </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
         <v>-0.001252</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AG33" t="n">
         <v>-0.001252</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0.05</v>
       </c>
       <c r="AH33" t="n">
         <v>0.04</v>
       </c>
       <c r="AI33" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK33" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -3953,84 +4153,90 @@
         <v>105.60427</v>
       </c>
       <c r="I34" t="n">
+        <v>104.71213</v>
+      </c>
+      <c r="J34" t="n">
         <v>5.2416</v>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>5.241</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>5953960</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>2278309</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>3675652</v>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>3.43</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>2.8</v>
       </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
         <v>3.82</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>27.75</v>
       </c>
-      <c r="R34" t="n">
+      <c r="S34" t="n">
         <v>355560</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>0.9333669999999999</v>
       </c>
-      <c r="T34" t="n">
+      <c r="U34" t="n">
+        <v>-4.159973</v>
+      </c>
+      <c r="V34" t="n">
         <v>1.349627</v>
       </c>
-      <c r="U34" t="n">
+      <c r="W34" t="n">
         <v>1.349783</v>
       </c>
-      <c r="V34" t="n">
+      <c r="X34" t="n">
         <v>0.64951</v>
       </c>
-      <c r="W34" t="n">
+      <c r="Y34" t="n">
         <v>0.415624</v>
       </c>
-      <c r="X34" t="n">
+      <c r="Z34" t="n">
         <v>0.795057</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="AA34" t="n">
         <v>1.126567</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AB34" t="n">
         <v>3.925952</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AC34" t="n">
         <v>-0.344269</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AD34" t="n">
         <v>3.335647</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AE34" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AF34" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="AE34" t="n">
+      <c r="AG34" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="AF34" t="n">
+      <c r="AH34" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG34" t="n">
+      <c r="AI34" t="n">
         <v>0.04</v>
       </c>
-      <c r="AH34" t="n">
+      <c r="AJ34" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI34" t="n">
+      <c r="AK34" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -4060,84 +4266,90 @@
         <v>106.5891</v>
       </c>
       <c r="I35" t="n">
+        <v>105.86915</v>
+      </c>
+      <c r="J35" t="n">
         <v>5.5589</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>5.5583</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>6041898</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>2336858</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>3705041</v>
       </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>3.29</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>2.64</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>27.81</v>
       </c>
-      <c r="R35" t="n">
+      <c r="S35" t="n">
         <v>357827</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>0.932566</v>
       </c>
-      <c r="T35" t="n">
+      <c r="U35" t="n">
+        <v>1.104953</v>
+      </c>
+      <c r="V35" t="n">
         <v>6.053495</v>
       </c>
-      <c r="U35" t="n">
+      <c r="W35" t="n">
         <v>6.054188</v>
       </c>
-      <c r="V35" t="n">
+      <c r="X35" t="n">
         <v>1.476967</v>
       </c>
-      <c r="W35" t="n">
+      <c r="Y35" t="n">
         <v>2.569845</v>
       </c>
-      <c r="X35" t="n">
+      <c r="Z35" t="n">
         <v>0.799559</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="AA35" t="n">
         <v>0.637586</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AB35" t="n">
         <v>4.227578</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AC35" t="n">
         <v>2.440035</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AD35" t="n">
         <v>3.697684</v>
       </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="AE35" t="n">
+      <c r="AG35" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="AF35" t="n">
+      <c r="AH35" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AI35" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AH35" t="n">
+      <c r="AJ35" t="n">
         <v>-0.11</v>
       </c>
-      <c r="AI35" t="n">
+      <c r="AK35" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -4167,84 +4379,90 @@
         <v>107.06237</v>
       </c>
       <c r="I36" t="n">
+        <v>111.509</v>
+      </c>
+      <c r="J36" t="n">
         <v>5.6621</v>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>5.6615</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>6069205</v>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>2323362</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>3745844</v>
       </c>
-      <c r="N36" t="n">
+      <c r="O36" t="n">
         <v>3.3</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>2.52</v>
       </c>
-      <c r="P36" t="n">
+      <c r="Q36" t="n">
         <v>3.78</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>27.74</v>
       </c>
-      <c r="R36" t="n">
+      <c r="S36" t="n">
         <v>363282</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>0.444014</v>
       </c>
-      <c r="T36" t="n">
+      <c r="U36" t="n">
+        <v>5.327189</v>
+      </c>
+      <c r="V36" t="n">
         <v>1.856482</v>
       </c>
-      <c r="U36" t="n">
+      <c r="W36" t="n">
         <v>1.856683</v>
       </c>
-      <c r="V36" t="n">
+      <c r="X36" t="n">
         <v>0.451961</v>
       </c>
-      <c r="W36" t="n">
+      <c r="Y36" t="n">
         <v>-0.577528</v>
       </c>
-      <c r="X36" t="n">
+      <c r="Z36" t="n">
         <v>1.101283</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="AA36" t="n">
         <v>1.52448</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AB36" t="n">
         <v>4.498245</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AC36" t="n">
         <v>3.812368</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AD36" t="n">
         <v>4.060953</v>
       </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
       <c r="AE36" t="n">
         <v>0</v>
       </c>
       <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
         <v>0.01</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AI36" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AH36" t="n">
+      <c r="AJ36" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI36" t="n">
+      <c r="AK36" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -4274,84 +4492,90 @@
         <v>107.19174</v>
       </c>
       <c r="I37" t="n">
+        <v>110.06254</v>
+      </c>
+      <c r="J37" t="n">
         <v>5.6562</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>5.6556</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6135298</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>2344397</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>3790900</v>
       </c>
-      <c r="N37" t="n">
+      <c r="O37" t="n">
         <v>3.33</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>2.55</v>
       </c>
-      <c r="P37" t="n">
+      <c r="Q37" t="n">
         <v>3.82</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>27.59</v>
       </c>
-      <c r="R37" t="n">
+      <c r="S37" t="n">
         <v>369214</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>0.120836</v>
       </c>
-      <c r="T37" t="n">
+      <c r="U37" t="n">
+        <v>-1.297169</v>
+      </c>
+      <c r="V37" t="n">
         <v>-0.104202</v>
       </c>
-      <c r="U37" t="n">
+      <c r="W37" t="n">
         <v>-0.104213</v>
       </c>
-      <c r="V37" t="n">
+      <c r="X37" t="n">
         <v>1.088989</v>
       </c>
-      <c r="W37" t="n">
+      <c r="Y37" t="n">
         <v>0.905369</v>
       </c>
-      <c r="X37" t="n">
+      <c r="Z37" t="n">
         <v>1.202826</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="AA37" t="n">
         <v>1.632891</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AB37" t="n">
         <v>4.237599</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AC37" t="n">
         <v>4.259387</v>
       </c>
-      <c r="AB37" t="n">
+      <c r="AD37" t="n">
         <v>3.707852</v>
       </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
       <c r="AE37" t="n">
         <v>0</v>
       </c>
       <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AI37" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH37" t="n">
+      <c r="AJ37" t="n">
         <v>0.04</v>
       </c>
-      <c r="AI37" t="n">
+      <c r="AK37" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4381,84 +4605,90 @@
         <v>108.04382</v>
       </c>
       <c r="I38" t="n">
+        <v>107.07852</v>
+      </c>
+      <c r="J38" t="n">
         <v>5.4481</v>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>5.4475</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>6216528</v>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>2384828</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>3831700</v>
       </c>
-      <c r="N38" t="n">
+      <c r="O38" t="n">
         <v>3.34</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>2.56</v>
       </c>
-      <c r="P38" t="n">
+      <c r="Q38" t="n">
         <v>3.83</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>27.49</v>
       </c>
-      <c r="R38" t="n">
+      <c r="S38" t="n">
         <v>372016</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>0.794912</v>
       </c>
-      <c r="T38" t="n">
+      <c r="U38" t="n">
+        <v>-2.711204</v>
+      </c>
+      <c r="V38" t="n">
         <v>-3.679149</v>
       </c>
-      <c r="U38" t="n">
+      <c r="W38" t="n">
         <v>-3.679539</v>
       </c>
-      <c r="V38" t="n">
+      <c r="X38" t="n">
         <v>1.323978</v>
       </c>
-      <c r="W38" t="n">
+      <c r="Y38" t="n">
         <v>1.72458</v>
       </c>
-      <c r="X38" t="n">
+      <c r="Z38" t="n">
         <v>1.076262</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="AA38" t="n">
         <v>0.7589089999999999</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AB38" t="n">
         <v>4.42474</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AC38" t="n">
         <v>4.519075</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AD38" t="n">
         <v>4.091149</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AE38" t="n">
         <v>0.25</v>
       </c>
-      <c r="AD38" t="n">
+      <c r="AF38" t="n">
         <v>0.000342</v>
       </c>
-      <c r="AE38" t="n">
+      <c r="AG38" t="n">
         <v>0.000342</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0.01</v>
       </c>
       <c r="AH38" t="n">
         <v>0.01</v>
       </c>
       <c r="AI38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AK38" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -4488,84 +4718,90 @@
         <v>108.2446</v>
       </c>
       <c r="I39" t="n">
+        <v>109.18379</v>
+      </c>
+      <c r="J39" t="n">
         <v>5.7779</v>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>5.7773</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>6275117</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>2397533</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>3877584</v>
       </c>
-      <c r="N39" t="n">
+      <c r="O39" t="n">
         <v>3.3</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>2.52</v>
       </c>
-      <c r="P39" t="n">
+      <c r="Q39" t="n">
         <v>3.79</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>27.94</v>
       </c>
-      <c r="R39" t="n">
+      <c r="S39" t="n">
         <v>366096</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>0.185832</v>
       </c>
-      <c r="T39" t="n">
+      <c r="U39" t="n">
+        <v>1.966099</v>
+      </c>
+      <c r="V39" t="n">
         <v>6.053487</v>
       </c>
-      <c r="U39" t="n">
+      <c r="W39" t="n">
         <v>6.054153</v>
       </c>
-      <c r="V39" t="n">
+      <c r="X39" t="n">
         <v>0.9424709999999999</v>
       </c>
-      <c r="W39" t="n">
+      <c r="Y39" t="n">
         <v>0.532743</v>
       </c>
-      <c r="X39" t="n">
+      <c r="Z39" t="n">
         <v>1.197484</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="AA39" t="n">
         <v>-1.591329</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AB39" t="n">
         <v>4.758099</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AC39" t="n">
         <v>5.579866</v>
       </c>
-      <c r="AB39" t="n">
+      <c r="AD39" t="n">
         <v>4.600584</v>
       </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
         <v>0.000556</v>
       </c>
-      <c r="AE39" t="n">
+      <c r="AG39" t="n">
         <v>0.000556</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>-0.04</v>
       </c>
       <c r="AH39" t="n">
         <v>-0.04</v>
       </c>
       <c r="AI39" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AK39" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -4595,84 +4831,90 @@
         <v>108.00109</v>
       </c>
       <c r="I40" t="n">
+        <v>105.49006</v>
+      </c>
+      <c r="J40" t="n">
         <v>6.0535</v>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>6.0529</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>6365690</v>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
         <v>2436022</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>3929668</v>
       </c>
-      <c r="N40" t="n">
+      <c r="O40" t="n">
         <v>3.27</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>2.5</v>
       </c>
-      <c r="P40" t="n">
+      <c r="Q40" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>28.45</v>
       </c>
-      <c r="R40" t="n">
+      <c r="S40" t="n">
         <v>363003</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>-0.224963</v>
       </c>
-      <c r="T40" t="n">
+      <c r="U40" t="n">
+        <v>-3.383039</v>
+      </c>
+      <c r="V40" t="n">
         <v>4.769899</v>
       </c>
-      <c r="U40" t="n">
+      <c r="W40" t="n">
         <v>4.770394</v>
       </c>
-      <c r="V40" t="n">
+      <c r="X40" t="n">
         <v>1.443368</v>
       </c>
-      <c r="W40" t="n">
+      <c r="Y40" t="n">
         <v>1.605359</v>
       </c>
-      <c r="X40" t="n">
+      <c r="Z40" t="n">
         <v>1.343208</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="AA40" t="n">
         <v>-0.8448600000000001</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AB40" t="n">
         <v>4.873011</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AC40" t="n">
         <v>6.325086</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AD40" t="n">
         <v>4.840925</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AE40" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AF40" t="n">
         <v>0.001412</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AG40" t="n">
         <v>0.001412</v>
       </c>
-      <c r="AF40" t="n">
+      <c r="AH40" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG40" t="n">
+      <c r="AI40" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AH40" t="n">
+      <c r="AJ40" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AI40" t="n">
+      <c r="AK40" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4702,84 +4944,90 @@
         <v>107.37012</v>
       </c>
       <c r="I41" t="n">
+        <v>104.15552</v>
+      </c>
+      <c r="J41" t="n">
         <v>6.1923</v>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>6.1917</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>6464602</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>2499177</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>3965425</v>
       </c>
-      <c r="N41" t="n">
+      <c r="O41" t="n">
         <v>3.08</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>2.21</v>
       </c>
-      <c r="P41" t="n">
+      <c r="Q41" t="n">
         <v>3.63</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>28.5</v>
       </c>
-      <c r="R41" t="n">
+      <c r="S41" t="n">
         <v>329730</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>-0.584226</v>
       </c>
-      <c r="T41" t="n">
+      <c r="U41" t="n">
+        <v>-1.265086</v>
+      </c>
+      <c r="V41" t="n">
         <v>2.292888</v>
       </c>
-      <c r="U41" t="n">
+      <c r="W41" t="n">
         <v>2.293116</v>
       </c>
-      <c r="V41" t="n">
+      <c r="X41" t="n">
         <v>1.55383</v>
       </c>
-      <c r="W41" t="n">
+      <c r="Y41" t="n">
         <v>2.592546</v>
       </c>
-      <c r="X41" t="n">
+      <c r="Z41" t="n">
         <v>0.909924</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="AA41" t="n">
         <v>-9.166040000000001</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AB41" t="n">
         <v>4.831296</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AC41" t="n">
         <v>6.536174</v>
       </c>
-      <c r="AB41" t="n">
+      <c r="AD41" t="n">
         <v>4.767938</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AE41" t="n">
         <v>1</v>
       </c>
-      <c r="AD41" t="n">
+      <c r="AF41" t="n">
         <v>0.002578</v>
       </c>
-      <c r="AE41" t="n">
+      <c r="AG41" t="n">
         <v>0.002578</v>
       </c>
-      <c r="AF41" t="n">
+      <c r="AH41" t="n">
         <v>-0.19</v>
       </c>
-      <c r="AG41" t="n">
+      <c r="AI41" t="n">
         <v>-0.29</v>
       </c>
-      <c r="AH41" t="n">
+      <c r="AJ41" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AI41" t="n">
+      <c r="AK41" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -4809,84 +5057,90 @@
         <v>108.09524</v>
       </c>
       <c r="I42" t="n">
+        <v>102.62949</v>
+      </c>
+      <c r="J42" t="n">
         <v>5.8301</v>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>5.8295</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>6465016</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>2451957</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>4013059</v>
       </c>
-      <c r="N42" t="n">
+      <c r="O42" t="n">
         <v>3.34</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>2.43</v>
       </c>
-      <c r="P42" t="n">
+      <c r="Q42" t="n">
         <v>3.89</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>29.88</v>
       </c>
-      <c r="R42" t="n">
+      <c r="S42" t="n">
         <v>328303</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>0.675346</v>
       </c>
-      <c r="T42" t="n">
+      <c r="U42" t="n">
+        <v>-1.465146</v>
+      </c>
+      <c r="V42" t="n">
         <v>-5.8492</v>
       </c>
-      <c r="U42" t="n">
+      <c r="W42" t="n">
         <v>-5.849767</v>
       </c>
-      <c r="V42" t="n">
+      <c r="X42" t="n">
         <v>0.006404</v>
       </c>
-      <c r="W42" t="n">
+      <c r="Y42" t="n">
         <v>-1.889422</v>
       </c>
-      <c r="X42" t="n">
+      <c r="Z42" t="n">
         <v>1.201233</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="AA42" t="n">
         <v>-0.432778</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AB42" t="n">
         <v>4.559874</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AC42" t="n">
         <v>6.749097</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AD42" t="n">
         <v>4.174145</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AE42" t="n">
         <v>1</v>
       </c>
-      <c r="AD42" t="n">
+      <c r="AF42" t="n">
         <v>0.001675</v>
       </c>
-      <c r="AE42" t="n">
+      <c r="AG42" t="n">
         <v>0.001675</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0.22</v>
       </c>
       <c r="AH42" t="n">
         <v>0.26</v>
       </c>
       <c r="AI42" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AK42" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -4916,84 +5170,90 @@
         <v>108.62006</v>
       </c>
       <c r="I43" t="n">
+        <v>106.82599</v>
+      </c>
+      <c r="J43" t="n">
         <v>5.8488</v>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
         <v>5.8482</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>6511444</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>2477151</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>4034293</v>
       </c>
-      <c r="N43" t="n">
+      <c r="O43" t="n">
         <v>3.41</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2.52</v>
       </c>
-      <c r="P43" t="n">
+      <c r="Q43" t="n">
         <v>3.96</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>30.53</v>
       </c>
-      <c r="R43" t="n">
+      <c r="S43" t="n">
         <v>332508</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>0.485516</v>
       </c>
-      <c r="T43" t="n">
+      <c r="U43" t="n">
+        <v>4.088981</v>
+      </c>
+      <c r="V43" t="n">
         <v>0.320749</v>
       </c>
-      <c r="U43" t="n">
+      <c r="W43" t="n">
         <v>0.320782</v>
       </c>
-      <c r="V43" t="n">
+      <c r="X43" t="n">
         <v>0.7181419999999999</v>
       </c>
-      <c r="W43" t="n">
+      <c r="Y43" t="n">
         <v>1.027506</v>
       </c>
-      <c r="X43" t="n">
+      <c r="Z43" t="n">
         <v>0.529123</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="AA43" t="n">
         <v>1.280829</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="AB43" t="n">
         <v>5.05763</v>
       </c>
-      <c r="AA43" t="n">
+      <c r="AC43" t="n">
         <v>8.444549</v>
       </c>
-      <c r="AB43" t="n">
+      <c r="AD43" t="n">
         <v>4.866504</v>
       </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
         <v>0.003204</v>
       </c>
-      <c r="AE43" t="n">
+      <c r="AG43" t="n">
         <v>0.003204</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0.09</v>
       </c>
       <c r="AH43" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AI43" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AK43" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -5023,84 +5283,90 @@
         <v>110.03287</v>
       </c>
       <c r="I44" t="n">
+        <v>114.02067</v>
+      </c>
+      <c r="J44" t="n">
         <v>5.7422</v>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>5.7416</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>6576464</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>2498262</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>4078202</v>
       </c>
-      <c r="N44" t="n">
+      <c r="O44" t="n">
         <v>3.44</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>2.49</v>
       </c>
-      <c r="P44" t="n">
+      <c r="Q44" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>31.34</v>
       </c>
-      <c r="R44" t="n">
+      <c r="S44" t="n">
         <v>336157</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>1.30069</v>
       </c>
-      <c r="T44" t="n">
+      <c r="U44" t="n">
+        <v>6.734953</v>
+      </c>
+      <c r="V44" t="n">
         <v>-1.822596</v>
       </c>
-      <c r="U44" t="n">
+      <c r="W44" t="n">
         <v>-1.822783</v>
       </c>
-      <c r="V44" t="n">
+      <c r="X44" t="n">
         <v>0.99855</v>
       </c>
-      <c r="W44" t="n">
+      <c r="Y44" t="n">
         <v>0.852229</v>
       </c>
-      <c r="X44" t="n">
+      <c r="Z44" t="n">
         <v>1.088394</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="AA44" t="n">
         <v>1.097417</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AB44" t="n">
         <v>5.47719</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AC44" t="n">
         <v>8.586193</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="AD44" t="n">
         <v>5.201441</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AE44" t="n">
         <v>1</v>
       </c>
-      <c r="AD44" t="n">
+      <c r="AF44" t="n">
         <v>0.001471</v>
       </c>
-      <c r="AE44" t="n">
+      <c r="AG44" t="n">
         <v>0.001471</v>
       </c>
-      <c r="AF44" t="n">
+      <c r="AH44" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG44" t="n">
+      <c r="AI44" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AH44" t="n">
+      <c r="AJ44" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI44" t="n">
+      <c r="AK44" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -5130,84 +5396,90 @@
         <v>109.52766</v>
       </c>
       <c r="I45" t="n">
+        <v>112.59512</v>
+      </c>
+      <c r="J45" t="n">
         <v>5.6608</v>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>5.6602</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>6623948</v>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" t="n">
         <v>2512426</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>4111522</v>
       </c>
-      <c r="N45" t="n">
+      <c r="O45" t="n">
         <v>3.67</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>2.72</v>
       </c>
-      <c r="P45" t="n">
+      <c r="Q45" t="n">
         <v>4.25</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>31.63</v>
       </c>
-      <c r="R45" t="n">
+      <c r="S45" t="n">
         <v>340789</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>-0.459145</v>
       </c>
-      <c r="T45" t="n">
+      <c r="U45" t="n">
+        <v>-1.250256</v>
+      </c>
+      <c r="V45" t="n">
         <v>-1.417575</v>
       </c>
-      <c r="U45" t="n">
+      <c r="W45" t="n">
         <v>-1.417723</v>
       </c>
-      <c r="V45" t="n">
+      <c r="X45" t="n">
         <v>0.722029</v>
       </c>
-      <c r="W45" t="n">
+      <c r="Y45" t="n">
         <v>0.566954</v>
       </c>
-      <c r="X45" t="n">
+      <c r="Z45" t="n">
         <v>0.8170269999999999</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="AA45" t="n">
         <v>1.377928</v>
       </c>
-      <c r="Z45" t="n">
+      <c r="AB45" t="n">
         <v>5.529729</v>
       </c>
-      <c r="AA45" t="n">
+      <c r="AC45" t="n">
         <v>8.510418</v>
       </c>
-      <c r="AB45" t="n">
+      <c r="AD45" t="n">
         <v>5.316736</v>
       </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
         <v>0.002023</v>
       </c>
-      <c r="AE45" t="n">
+      <c r="AG45" t="n">
         <v>0.002023</v>
       </c>
-      <c r="AF45" t="n">
+      <c r="AH45" t="n">
         <v>0.23</v>
       </c>
-      <c r="AG45" t="n">
+      <c r="AI45" t="n">
         <v>0.23</v>
       </c>
-      <c r="AH45" t="n">
+      <c r="AJ45" t="n">
         <v>0.22</v>
       </c>
-      <c r="AI45" t="n">
+      <c r="AK45" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -5237,84 +5509,90 @@
         <v>108.8862</v>
       </c>
       <c r="I46" t="n">
+        <v>108.55704</v>
+      </c>
+      <c r="J46" t="n">
         <v>5.7087</v>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>5.7081</v>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
         <v>6666287</v>
       </c>
-      <c r="L46" t="n">
+      <c r="M46" t="n">
         <v>2532708</v>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
         <v>4133579</v>
       </c>
-      <c r="N46" t="n">
+      <c r="O46" t="n">
         <v>3.72</v>
       </c>
-      <c r="O46" t="n">
+      <c r="P46" t="n">
         <v>2.67</v>
       </c>
-      <c r="P46" t="n">
+      <c r="Q46" t="n">
         <v>4.36</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="R46" t="n">
         <v>31.7</v>
       </c>
-      <c r="R46" t="n">
+      <c r="S46" t="n">
         <v>341459</v>
       </c>
-      <c r="S46" t="n">
+      <c r="T46" t="n">
         <v>-0.58566</v>
       </c>
-      <c r="T46" t="n">
+      <c r="U46" t="n">
+        <v>-3.586372</v>
+      </c>
+      <c r="V46" t="n">
         <v>0.84617</v>
       </c>
-      <c r="U46" t="n">
+      <c r="W46" t="n">
         <v>0.84626</v>
       </c>
-      <c r="V46" t="n">
+      <c r="X46" t="n">
         <v>0.639181</v>
       </c>
-      <c r="W46" t="n">
+      <c r="Y46" t="n">
         <v>0.807268</v>
       </c>
-      <c r="X46" t="n">
+      <c r="Z46" t="n">
         <v>0.5364679999999999</v>
       </c>
-      <c r="Y46" t="n">
+      <c r="AA46" t="n">
         <v>0.196603</v>
       </c>
-      <c r="Z46" t="n">
+      <c r="AB46" t="n">
         <v>5.319636</v>
       </c>
-      <c r="AA46" t="n">
+      <c r="AC46" t="n">
         <v>7.026183</v>
       </c>
-      <c r="AB46" t="n">
+      <c r="AD46" t="n">
         <v>5.201418</v>
       </c>
-      <c r="AC46" t="n">
+      <c r="AE46" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD46" t="n">
+      <c r="AF46" t="n">
         <v>0.001405</v>
       </c>
-      <c r="AE46" t="n">
+      <c r="AG46" t="n">
         <v>0.001405</v>
       </c>
-      <c r="AF46" t="n">
+      <c r="AH46" t="n">
         <v>0.05</v>
       </c>
-      <c r="AG46" t="n">
+      <c r="AI46" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH46" t="n">
+      <c r="AJ46" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI46" t="n">
+      <c r="AK46" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5344,84 +5622,90 @@
         <v>108.80376</v>
       </c>
       <c r="I47" t="n">
+        <v>107.36219</v>
+      </c>
+      <c r="J47" t="n">
         <v>5.4571</v>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>5.4565</v>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>6703663</v>
       </c>
-      <c r="L47" t="n">
+      <c r="M47" t="n">
         <v>2547693</v>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
         <v>4155970</v>
       </c>
-      <c r="N47" t="n">
+      <c r="O47" t="n">
         <v>3.75</v>
       </c>
-      <c r="O47" t="n">
+      <c r="P47" t="n">
         <v>2.67</v>
       </c>
-      <c r="P47" t="n">
+      <c r="Q47" t="n">
         <v>4.41</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="R47" t="n">
         <v>31.85</v>
       </c>
-      <c r="R47" t="n">
+      <c r="S47" t="n">
         <v>344440</v>
       </c>
-      <c r="S47" t="n">
+      <c r="T47" t="n">
         <v>-0.075712</v>
       </c>
-      <c r="T47" t="n">
+      <c r="U47" t="n">
+        <v>-1.100666</v>
+      </c>
+      <c r="V47" t="n">
         <v>-4.407308</v>
       </c>
-      <c r="U47" t="n">
+      <c r="W47" t="n">
         <v>-4.407771</v>
       </c>
-      <c r="V47" t="n">
+      <c r="X47" t="n">
         <v>0.5606719999999999</v>
       </c>
-      <c r="W47" t="n">
+      <c r="Y47" t="n">
         <v>0.591659</v>
       </c>
-      <c r="X47" t="n">
+      <c r="Z47" t="n">
         <v>0.541686</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="AA47" t="n">
         <v>0.873018</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="AB47" t="n">
         <v>5.351165</v>
       </c>
-      <c r="AA47" t="n">
+      <c r="AC47" t="n">
         <v>4.393261</v>
       </c>
-      <c r="AB47" t="n">
+      <c r="AD47" t="n">
         <v>5.18043</v>
       </c>
-      <c r="AC47" t="n">
+      <c r="AE47" t="n">
         <v>0.25</v>
       </c>
-      <c r="AD47" t="n">
+      <c r="AF47" t="n">
         <v>0.000633</v>
       </c>
-      <c r="AE47" t="n">
+      <c r="AG47" t="n">
         <v>0.000633</v>
       </c>
-      <c r="AF47" t="n">
+      <c r="AH47" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="n">
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI47" t="n">
+      <c r="AK47" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5451,84 +5735,90 @@
         <v>108.49869</v>
       </c>
       <c r="I48" t="n">
+        <v>113.10928</v>
+      </c>
+      <c r="J48" t="n">
         <v>5.6021</v>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
         <v>5.6015</v>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" t="n">
         <v>6733209</v>
       </c>
-      <c r="L48" t="n">
+      <c r="M48" t="n">
         <v>2544400</v>
       </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
         <v>4188808</v>
       </c>
-      <c r="N48" t="n">
+      <c r="O48" t="n">
         <v>3.96</v>
       </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
         <v>2.79</v>
       </c>
-      <c r="P48" t="n">
+      <c r="Q48" t="n">
         <v>4.66</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="R48" t="n">
         <v>31.75</v>
       </c>
-      <c r="R48" t="n">
+      <c r="S48" t="n">
         <v>345111</v>
       </c>
-      <c r="S48" t="n">
+      <c r="T48" t="n">
         <v>-0.280386</v>
       </c>
-      <c r="T48" t="n">
+      <c r="U48" t="n">
+        <v>5.352993</v>
+      </c>
+      <c r="V48" t="n">
         <v>2.657089</v>
       </c>
-      <c r="U48" t="n">
+      <c r="W48" t="n">
         <v>2.657381</v>
       </c>
-      <c r="V48" t="n">
+      <c r="X48" t="n">
         <v>0.440744</v>
       </c>
-      <c r="W48" t="n">
+      <c r="Y48" t="n">
         <v>-0.129254</v>
       </c>
-      <c r="X48" t="n">
+      <c r="Z48" t="n">
         <v>0.79014</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="AA48" t="n">
         <v>0.194809</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="AB48" t="n">
         <v>5.225222</v>
       </c>
-      <c r="AA48" t="n">
+      <c r="AC48" t="n">
         <v>2.961368</v>
       </c>
-      <c r="AB48" t="n">
+      <c r="AD48" t="n">
         <v>5.127976</v>
       </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
         <v>0.000562</v>
       </c>
-      <c r="AE48" t="n">
+      <c r="AG48" t="n">
         <v>0.000562</v>
       </c>
-      <c r="AF48" t="n">
+      <c r="AH48" t="n">
         <v>0.21</v>
       </c>
-      <c r="AG48" t="n">
+      <c r="AI48" t="n">
         <v>0.12</v>
       </c>
-      <c r="AH48" t="n">
+      <c r="AJ48" t="n">
         <v>0.25</v>
       </c>
-      <c r="AI48" t="n">
+      <c r="AK48" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -5558,84 +5848,90 @@
         <v>108.82893</v>
       </c>
       <c r="I49" t="n">
+        <v>110.38054</v>
+      </c>
+      <c r="J49" t="n">
         <v>5.4264</v>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
         <v>5.4258</v>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
         <v>6774436</v>
       </c>
-      <c r="L49" t="n">
+      <c r="M49" t="n">
         <v>2546265</v>
       </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
         <v>4228171</v>
       </c>
-      <c r="N49" t="n">
+      <c r="O49" t="n">
         <v>4.14</v>
       </c>
-      <c r="O49" t="n">
+      <c r="P49" t="n">
         <v>2.85</v>
       </c>
-      <c r="P49" t="n">
+      <c r="Q49" t="n">
         <v>4.92</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="R49" t="n">
         <v>31.87</v>
       </c>
-      <c r="R49" t="n">
+      <c r="S49" t="n">
         <v>350767</v>
       </c>
-      <c r="S49" t="n">
+      <c r="T49" t="n">
         <v>0.304372</v>
       </c>
-      <c r="T49" t="n">
+      <c r="U49" t="n">
+        <v>-2.412481</v>
+      </c>
+      <c r="V49" t="n">
         <v>-3.136324</v>
       </c>
-      <c r="U49" t="n">
+      <c r="W49" t="n">
         <v>-3.13666</v>
       </c>
-      <c r="V49" t="n">
+      <c r="X49" t="n">
         <v>0.612293</v>
       </c>
-      <c r="W49" t="n">
+      <c r="Y49" t="n">
         <v>0.073298</v>
       </c>
-      <c r="X49" t="n">
+      <c r="Z49" t="n">
         <v>0.9397180000000001</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="AA49" t="n">
         <v>1.638893</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="AB49" t="n">
         <v>5.130501</v>
       </c>
-      <c r="AA49" t="n">
+      <c r="AC49" t="n">
         <v>3.033233</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AD49" t="n">
         <v>5.054283</v>
       </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
       <c r="AE49" t="n">
         <v>0</v>
       </c>
       <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
         <v>0.18</v>
       </c>
-      <c r="AG49" t="n">
+      <c r="AI49" t="n">
         <v>0.06</v>
       </c>
-      <c r="AH49" t="n">
+      <c r="AJ49" t="n">
         <v>0.26</v>
       </c>
-      <c r="AI49" t="n">
+      <c r="AK49" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5665,84 +5961,90 @@
         <v>108.73548</v>
       </c>
       <c r="I50" t="n">
+        <v>109.48375</v>
+      </c>
+      <c r="J50" t="n">
         <v>5.3186</v>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
         <v>5.318</v>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" t="n">
         <v>6852705</v>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" t="n">
         <v>2589817</v>
       </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
         <v>4262888</v>
       </c>
-      <c r="N50" t="n">
+      <c r="O50" t="n">
         <v>4.09</v>
       </c>
-      <c r="O50" t="n">
+      <c r="P50" t="n">
         <v>2.77</v>
       </c>
-      <c r="P50" t="n">
+      <c r="Q50" t="n">
         <v>4.89</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="R50" t="n">
         <v>31.47</v>
       </c>
-      <c r="R50" t="n">
+      <c r="S50" t="n">
         <v>356582</v>
       </c>
-      <c r="S50" t="n">
+      <c r="T50" t="n">
         <v>-0.085869</v>
       </c>
-      <c r="T50" t="n">
+      <c r="U50" t="n">
+        <v>-0.812453</v>
+      </c>
+      <c r="V50" t="n">
         <v>-1.986584</v>
       </c>
-      <c r="U50" t="n">
+      <c r="W50" t="n">
         <v>-1.986804</v>
       </c>
-      <c r="V50" t="n">
+      <c r="X50" t="n">
         <v>1.155358</v>
       </c>
-      <c r="W50" t="n">
+      <c r="Y50" t="n">
         <v>1.710427</v>
       </c>
-      <c r="X50" t="n">
+      <c r="Z50" t="n">
         <v>0.821088</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="AA50" t="n">
         <v>1.657796</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="AB50" t="n">
         <v>5.172369</v>
       </c>
-      <c r="AA50" t="n">
+      <c r="AC50" t="n">
         <v>2.828436</v>
       </c>
-      <c r="AB50" t="n">
+      <c r="AD50" t="n">
         <v>5.096104</v>
       </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
       <c r="AE50" t="n">
         <v>0</v>
       </c>
       <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AG50" t="n">
+      <c r="AI50" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AH50" t="n">
+      <c r="AJ50" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI50" t="n">
+      <c r="AK50" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -5772,84 +6074,90 @@
         <v>108.75326</v>
       </c>
       <c r="I51" t="n">
+        <v>110.07682</v>
+      </c>
+      <c r="J51" t="n">
         <v>5.3843</v>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
         <v>5.3837</v>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
         <v>6923886</v>
       </c>
-      <c r="L51" t="n">
+      <c r="M51" t="n">
         <v>2597630</v>
       </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
         <v>4326256</v>
       </c>
-      <c r="N51" t="n">
+      <c r="O51" t="n">
         <v>4.18</v>
       </c>
-      <c r="O51" t="n">
+      <c r="P51" t="n">
         <v>2.82</v>
       </c>
-      <c r="P51" t="n">
+      <c r="Q51" t="n">
         <v>4.99</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="R51" t="n">
         <v>32.04</v>
       </c>
-      <c r="R51" t="n">
+      <c r="S51" t="n">
         <v>357103</v>
       </c>
-      <c r="S51" t="n">
+      <c r="T51" t="n">
         <v>0.016352</v>
       </c>
-      <c r="T51" t="n">
+      <c r="U51" t="n">
+        <v>0.541697</v>
+      </c>
+      <c r="V51" t="n">
         <v>1.235287</v>
       </c>
-      <c r="U51" t="n">
+      <c r="W51" t="n">
         <v>1.235427</v>
       </c>
-      <c r="V51" t="n">
+      <c r="X51" t="n">
         <v>1.038729</v>
       </c>
-      <c r="W51" t="n">
+      <c r="Y51" t="n">
         <v>0.301682</v>
       </c>
-      <c r="X51" t="n">
+      <c r="Z51" t="n">
         <v>1.486504</v>
       </c>
-      <c r="Y51" t="n">
+      <c r="AA51" t="n">
         <v>0.146109</v>
       </c>
-      <c r="Z51" t="n">
+      <c r="AB51" t="n">
         <v>4.680811</v>
       </c>
-      <c r="AA51" t="n">
+      <c r="AC51" t="n">
         <v>0.924206</v>
       </c>
-      <c r="AB51" t="n">
+      <c r="AD51" t="n">
         <v>4.490243</v>
       </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
       <c r="AE51" t="n">
         <v>0</v>
       </c>
       <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG51" t="n">
+      <c r="AI51" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH51" t="n">
+      <c r="AJ51" t="n">
         <v>0.1</v>
       </c>
-      <c r="AI51" t="n">
+      <c r="AK51" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -5879,84 +6187,90 @@
         <v>109.25005</v>
       </c>
       <c r="I52" t="n">
+        <v>106.59892</v>
+      </c>
+      <c r="J52" t="n">
         <v>5.3338</v>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
         <v>5.3332</v>
       </c>
-      <c r="K52" t="n">
+      <c r="L52" t="n">
         <v>7004223</v>
       </c>
-      <c r="L52" t="n">
+      <c r="M52" t="n">
         <v>2616902</v>
       </c>
-      <c r="M52" t="n">
+      <c r="N52" t="n">
         <v>4387321</v>
       </c>
-      <c r="N52" t="n">
+      <c r="O52" t="n">
         <v>4.24</v>
       </c>
-      <c r="O52" t="n">
+      <c r="P52" t="n">
         <v>2.75</v>
       </c>
-      <c r="P52" t="n">
+      <c r="Q52" t="n">
         <v>5.12</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="R52" t="n">
         <v>32.2</v>
       </c>
-      <c r="R52" t="n">
+      <c r="S52" t="n">
         <v>360578</v>
       </c>
-      <c r="S52" t="n">
+      <c r="T52" t="n">
         <v>0.456805</v>
       </c>
-      <c r="T52" t="n">
+      <c r="U52" t="n">
+        <v>-3.159521</v>
+      </c>
+      <c r="V52" t="n">
         <v>-0.937912</v>
       </c>
-      <c r="U52" t="n">
+      <c r="W52" t="n">
         <v>-0.938017</v>
       </c>
-      <c r="V52" t="n">
+      <c r="X52" t="n">
         <v>1.160288</v>
       </c>
-      <c r="W52" t="n">
+      <c r="Y52" t="n">
         <v>0.741907</v>
       </c>
-      <c r="X52" t="n">
+      <c r="Z52" t="n">
         <v>1.411498</v>
       </c>
-      <c r="Y52" t="n">
+      <c r="AA52" t="n">
         <v>0.973109</v>
       </c>
-      <c r="Z52" t="n">
+      <c r="AB52" t="n">
         <v>4.461836</v>
       </c>
-      <c r="AA52" t="n">
+      <c r="AC52" t="n">
         <v>-0.101973</v>
       </c>
-      <c r="AB52" t="n">
+      <c r="AD52" t="n">
         <v>4.177803</v>
       </c>
-      <c r="AC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" t="n">
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="n">
         <v>-0</v>
       </c>
-      <c r="AE52" t="n">
+      <c r="AG52" t="n">
         <v>-0</v>
       </c>
-      <c r="AF52" t="n">
+      <c r="AH52" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG52" t="n">
+      <c r="AI52" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AH52" t="n">
+      <c r="AJ52" t="n">
         <v>0.13</v>
       </c>
-      <c r="AI52" t="n">
+      <c r="AK52" t="n">
         <v>0.16</v>
       </c>
     </row>
@@ -5986,84 +6300,90 @@
         <v>109.4528</v>
       </c>
       <c r="I53" t="n">
+        <v>107.18417</v>
+      </c>
+      <c r="J53" t="n">
         <v>5.5024</v>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>5.5018</v>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" t="n">
         <v>7137252</v>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" t="n">
         <v>2701735</v>
       </c>
-      <c r="M53" t="n">
+      <c r="N53" t="n">
         <v>4435517</v>
       </c>
-      <c r="N53" t="n">
+      <c r="O53" t="n">
         <v>4.2</v>
       </c>
-      <c r="O53" t="n">
+      <c r="P53" t="n">
         <v>2.7</v>
       </c>
-      <c r="P53" t="n">
+      <c r="Q53" t="n">
         <v>5.12</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="R53" t="n">
         <v>31.87</v>
       </c>
-      <c r="R53" t="n">
+      <c r="S53" t="n">
         <v>358234</v>
       </c>
-      <c r="S53" t="n">
+      <c r="T53" t="n">
         <v>0.185583</v>
       </c>
-      <c r="T53" t="n">
+      <c r="U53" t="n">
+        <v>0.549021</v>
+      </c>
+      <c r="V53" t="n">
         <v>3.160973</v>
       </c>
-      <c r="U53" t="n">
+      <c r="W53" t="n">
         <v>3.161329</v>
       </c>
-      <c r="V53" t="n">
+      <c r="X53" t="n">
         <v>1.899268</v>
       </c>
-      <c r="W53" t="n">
+      <c r="Y53" t="n">
         <v>3.241734</v>
       </c>
-      <c r="X53" t="n">
+      <c r="Z53" t="n">
         <v>1.098529</v>
       </c>
-      <c r="Y53" t="n">
+      <c r="AA53" t="n">
         <v>-0.650067</v>
       </c>
-      <c r="Z53" t="n">
+      <c r="AB53" t="n">
         <v>4.264385</v>
       </c>
-      <c r="AA53" t="n">
+      <c r="AC53" t="n">
         <v>-1.042167</v>
       </c>
-      <c r="AB53" t="n">
+      <c r="AD53" t="n">
         <v>3.897866</v>
       </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
       <c r="AE53" t="n">
         <v>0</v>
       </c>
       <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AG53" t="n">
+      <c r="AI53" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI53" t="n">
+      <c r="AJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -6093,84 +6413,90 @@
         <v>110.04992</v>
       </c>
       <c r="I54" t="n">
+        <v>103.77761</v>
+      </c>
+      <c r="J54" t="n">
         <v>5.2301</v>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
         <v>5.2295</v>
       </c>
-      <c r="K54" t="n">
+      <c r="L54" t="n">
         <v>7130762</v>
       </c>
-      <c r="L54" t="n">
+      <c r="M54" t="n">
         <v>2654220</v>
       </c>
-      <c r="M54" t="n">
+      <c r="N54" t="n">
         <v>4476542</v>
       </c>
-      <c r="N54" t="n">
+      <c r="O54" t="n">
         <v>4.44</v>
       </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
         <v>2.87</v>
       </c>
-      <c r="P54" t="n">
+      <c r="Q54" t="n">
         <v>5.38</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="R54" t="n">
         <v>32.45</v>
       </c>
-      <c r="R54" t="n">
+      <c r="S54" t="n">
         <v>364367</v>
       </c>
-      <c r="S54" t="n">
+      <c r="T54" t="n">
         <v>0.54555</v>
       </c>
-      <c r="T54" t="n">
+      <c r="U54" t="n">
+        <v>-3.178231</v>
+      </c>
+      <c r="V54" t="n">
         <v>-4.94875</v>
       </c>
-      <c r="U54" t="n">
+      <c r="W54" t="n">
         <v>-4.949289</v>
       </c>
-      <c r="V54" t="n">
+      <c r="X54" t="n">
         <v>-0.090931</v>
       </c>
-      <c r="W54" t="n">
+      <c r="Y54" t="n">
         <v>-1.758685</v>
       </c>
-      <c r="X54" t="n">
+      <c r="Z54" t="n">
         <v>0.92492</v>
       </c>
-      <c r="Y54" t="n">
+      <c r="AA54" t="n">
         <v>1.712009</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="AB54" t="n">
         <v>4.441351</v>
       </c>
-      <c r="AA54" t="n">
+      <c r="AC54" t="n">
         <v>-0.903999</v>
       </c>
-      <c r="AB54" t="n">
+      <c r="AD54" t="n">
         <v>4.303068</v>
       </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>0</v>
-      </c>
       <c r="AE54" t="n">
         <v>0</v>
       </c>
       <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
         <v>0.24</v>
       </c>
-      <c r="AG54" t="n">
+      <c r="AI54" t="n">
         <v>0.17</v>
       </c>
-      <c r="AH54" t="n">
+      <c r="AJ54" t="n">
         <v>0.26</v>
       </c>
-      <c r="AI54" t="n">
+      <c r="AK54" t="n">
         <v>0.58</v>
       </c>
     </row>
@@ -6200,84 +6526,90 @@
         <v>110.7366</v>
       </c>
       <c r="I55" t="n">
+        <v>106.76075</v>
+      </c>
+      <c r="J55" t="n">
         <v>5.1495</v>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>5.1489</v>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" t="n">
         <v>7157783</v>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" t="n">
         <v>2656484</v>
       </c>
-      <c r="M55" t="n">
+      <c r="N55" t="n">
         <v>4501299</v>
       </c>
-      <c r="N55" t="n">
+      <c r="O55" t="n">
         <v>4.64</v>
       </c>
-      <c r="O55" t="n">
+      <c r="P55" t="n">
         <v>3.07</v>
       </c>
-      <c r="P55" t="n">
+      <c r="Q55" t="n">
         <v>5.56</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="R55" t="n">
         <v>32.63</v>
       </c>
-      <c r="R55" t="n">
+      <c r="S55" t="n">
         <v>371074</v>
       </c>
-      <c r="S55" t="n">
+      <c r="T55" t="n">
         <v>0.6239710000000001</v>
       </c>
-      <c r="T55" t="n">
+      <c r="U55" t="n">
+        <v>2.874551</v>
+      </c>
+      <c r="V55" t="n">
         <v>-1.54108</v>
       </c>
-      <c r="U55" t="n">
+      <c r="W55" t="n">
         <v>-1.541256</v>
       </c>
-      <c r="V55" t="n">
+      <c r="X55" t="n">
         <v>0.378936</v>
       </c>
-      <c r="W55" t="n">
+      <c r="Y55" t="n">
         <v>0.085298</v>
       </c>
-      <c r="X55" t="n">
+      <c r="Z55" t="n">
         <v>0.553038</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="AA55" t="n">
         <v>1.840727</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="AB55" t="n">
         <v>3.812497</v>
       </c>
-      <c r="AA55" t="n">
+      <c r="AC55" t="n">
         <v>-2.659212</v>
       </c>
-      <c r="AB55" t="n">
+      <c r="AD55" t="n">
         <v>3.357475</v>
       </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
       <c r="AE55" t="n">
         <v>0</v>
       </c>
       <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
         <v>0.2</v>
       </c>
-      <c r="AG55" t="n">
+      <c r="AI55" t="n">
         <v>0.2</v>
       </c>
-      <c r="AH55" t="n">
+      <c r="AJ55" t="n">
         <v>0.18</v>
       </c>
-      <c r="AI55" t="n">
+      <c r="AK55" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -6307,84 +6639,90 @@
         <v>110.58808</v>
       </c>
       <c r="I56" t="n">
+        <v>118.01719</v>
+      </c>
+      <c r="J56" t="n">
         <v>5.2194</v>
       </c>
-      <c r="J56" t="n">
+      <c r="K56" t="n">
         <v>5.2188</v>
       </c>
-      <c r="K56" t="n">
+      <c r="L56" t="n">
         <v>7240557</v>
       </c>
-      <c r="L56" t="n">
+      <c r="M56" t="n">
         <v>2687535</v>
       </c>
-      <c r="M56" t="n">
+      <c r="N56" t="n">
         <v>4553022</v>
       </c>
-      <c r="N56" t="n">
+      <c r="O56" t="n">
         <v>4.52</v>
       </c>
-      <c r="O56" t="n">
+      <c r="P56" t="n">
         <v>3.06</v>
       </c>
-      <c r="P56" t="n">
+      <c r="Q56" t="n">
         <v>5.39</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="R56" t="n">
         <v>32.84</v>
       </c>
-      <c r="R56" t="n">
+      <c r="S56" t="n">
         <v>362002</v>
       </c>
-      <c r="S56" t="n">
+      <c r="T56" t="n">
         <v>-0.13412</v>
       </c>
-      <c r="T56" t="n">
+      <c r="U56" t="n">
+        <v>10.543613</v>
+      </c>
+      <c r="V56" t="n">
         <v>1.357413</v>
       </c>
-      <c r="U56" t="n">
+      <c r="W56" t="n">
         <v>1.357572</v>
       </c>
-      <c r="V56" t="n">
+      <c r="X56" t="n">
         <v>1.15642</v>
       </c>
-      <c r="W56" t="n">
+      <c r="Y56" t="n">
         <v>1.168876</v>
       </c>
-      <c r="X56" t="n">
+      <c r="Z56" t="n">
         <v>1.149068</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="AA56" t="n">
         <v>-2.444795</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="AB56" t="n">
         <v>4.142847</v>
       </c>
-      <c r="AA56" t="n">
+      <c r="AC56" t="n">
         <v>-1.819225</v>
       </c>
-      <c r="AB56" t="n">
+      <c r="AD56" t="n">
         <v>3.768807</v>
       </c>
-      <c r="AC56" t="n">
+      <c r="AE56" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD56" t="n">
+      <c r="AF56" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="AE56" t="n">
+      <c r="AG56" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="AF56" t="n">
+      <c r="AH56" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AG56" t="n">
+      <c r="AI56" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH56" t="n">
+      <c r="AJ56" t="n">
         <v>-0.17</v>
       </c>
-      <c r="AI56" t="n">
+      <c r="AK56" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -6414,84 +6752,90 @@
         <v>110.90009</v>
       </c>
       <c r="I57" t="n">
+        <v>113.99295</v>
+      </c>
+      <c r="J57" t="n">
         <v>4.9886</v>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
         <v>4.988</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
         <v>7259766</v>
       </c>
-      <c r="L57" t="n">
+      <c r="M57" t="n">
         <v>2685397</v>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
         <v>4574368</v>
       </c>
-      <c r="N57" t="n">
+      <c r="O57" t="n">
         <v>4.64</v>
       </c>
-      <c r="O57" t="n">
+      <c r="P57" t="n">
         <v>3.15</v>
       </c>
-      <c r="P57" t="n">
+      <c r="Q57" t="n">
         <v>5.51</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="R57" t="n">
         <v>33.36</v>
       </c>
-      <c r="R57" t="n">
+      <c r="S57" t="n">
         <v>366913</v>
       </c>
-      <c r="S57" t="n">
+      <c r="T57" t="n">
         <v>0.282137</v>
       </c>
-      <c r="T57" t="n">
+      <c r="U57" t="n">
+        <v>-3.409876</v>
+      </c>
+      <c r="V57" t="n">
         <v>-4.421964</v>
       </c>
-      <c r="U57" t="n">
+      <c r="W57" t="n">
         <v>-4.422473</v>
       </c>
-      <c r="V57" t="n">
+      <c r="X57" t="n">
         <v>0.265297</v>
       </c>
-      <c r="W57" t="n">
+      <c r="Y57" t="n">
         <v>-0.079552</v>
       </c>
-      <c r="X57" t="n">
+      <c r="Z57" t="n">
         <v>0.468831</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="AA57" t="n">
         <v>1.356622</v>
       </c>
-      <c r="Z57" t="n">
+      <c r="AB57" t="n">
         <v>4.39172</v>
       </c>
-      <c r="AA57" t="n">
+      <c r="AC57" t="n">
         <v>0.619623</v>
       </c>
-      <c r="AB57" t="n">
+      <c r="AD57" t="n">
         <v>4.109608</v>
       </c>
-      <c r="AC57" t="n">
+      <c r="AE57" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD57" t="n">
+      <c r="AF57" t="n">
         <v>-0.000554</v>
       </c>
-      <c r="AE57" t="n">
+      <c r="AG57" t="n">
         <v>-0.000554</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>0.09</v>
       </c>
       <c r="AH57" t="n">
         <v>0.12</v>
       </c>
       <c r="AI57" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AK57" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -6521,84 +6865,90 @@
         <v>111.13846</v>
       </c>
       <c r="I58" t="n">
+        <v>109.65479</v>
+      </c>
+      <c r="J58" t="n">
         <v>5.0569</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>5.0563</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>7305306</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>2708154</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>4597152</v>
       </c>
-      <c r="N58" t="n">
+      <c r="O58" t="n">
         <v>4.74</v>
       </c>
-      <c r="O58" t="n">
+      <c r="P58" t="n">
         <v>3.25</v>
       </c>
-      <c r="P58" t="n">
+      <c r="Q58" t="n">
         <v>5.62</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="R58" t="n">
         <v>33.1</v>
       </c>
-      <c r="R58" t="n">
+      <c r="S58" t="n">
         <v>371137</v>
       </c>
-      <c r="S58" t="n">
+      <c r="T58" t="n">
         <v>0.214941</v>
       </c>
-      <c r="T58" t="n">
+      <c r="U58" t="n">
+        <v>-3.805639</v>
+      </c>
+      <c r="V58" t="n">
         <v>1.369122</v>
       </c>
-      <c r="U58" t="n">
+      <c r="W58" t="n">
         <v>1.369286</v>
       </c>
-      <c r="V58" t="n">
+      <c r="X58" t="n">
         <v>0.627293</v>
       </c>
-      <c r="W58" t="n">
+      <c r="Y58" t="n">
         <v>0.847435</v>
       </c>
-      <c r="X58" t="n">
+      <c r="Z58" t="n">
         <v>0.49808</v>
       </c>
-      <c r="Y58" t="n">
+      <c r="AA58" t="n">
         <v>1.151227</v>
       </c>
-      <c r="Z58" t="n">
+      <c r="AB58" t="n">
         <v>4.724907</v>
       </c>
-      <c r="AA58" t="n">
+      <c r="AC58" t="n">
         <v>1.964454</v>
       </c>
-      <c r="AB58" t="n">
+      <c r="AD58" t="n">
         <v>4.420848</v>
       </c>
-      <c r="AC58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD58" t="n">
+      <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="n">
         <v>-0.0008229999999999999</v>
       </c>
-      <c r="AE58" t="n">
+      <c r="AG58" t="n">
         <v>-0.0008229999999999999</v>
       </c>
-      <c r="AF58" t="n">
+      <c r="AH58" t="n">
         <v>0.1</v>
       </c>
-      <c r="AG58" t="n">
+      <c r="AI58" t="n">
         <v>0.1</v>
       </c>
-      <c r="AH58" t="n">
+      <c r="AJ58" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI58" t="n">
+      <c r="AK58" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -6628,84 +6978,90 @@
         <v>110.15775</v>
       </c>
       <c r="I59" t="n">
+        <v>109.94156</v>
+      </c>
+      <c r="J59" t="n">
         <v>5.1766</v>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
         <v>5.176</v>
       </c>
-      <c r="K59" t="n">
+      <c r="L59" t="n">
         <v>7353293</v>
       </c>
-      <c r="L59" t="n">
+      <c r="M59" t="n">
         <v>2750625</v>
       </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
         <v>4602668</v>
       </c>
-      <c r="N59" t="n">
+      <c r="O59" t="n">
         <v>4.58</v>
       </c>
-      <c r="O59" t="n">
+      <c r="P59" t="n">
         <v>3.18</v>
       </c>
-      <c r="P59" t="n">
+      <c r="Q59" t="n">
         <v>5.42</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="R59" t="n">
         <v>33.33</v>
       </c>
-      <c r="R59" t="n">
+      <c r="S59" t="n">
         <v>367558</v>
       </c>
-      <c r="S59" t="n">
+      <c r="T59" t="n">
         <v>-0.882422</v>
       </c>
-      <c r="T59" t="n">
+      <c r="U59" t="n">
+        <v>0.261521</v>
+      </c>
+      <c r="V59" t="n">
         <v>2.367063</v>
       </c>
-      <c r="U59" t="n">
+      <c r="W59" t="n">
         <v>2.367344</v>
       </c>
-      <c r="V59" t="n">
+      <c r="X59" t="n">
         <v>0.656879</v>
       </c>
-      <c r="W59" t="n">
+      <c r="Y59" t="n">
         <v>1.568264</v>
       </c>
-      <c r="X59" t="n">
+      <c r="Z59" t="n">
         <v>0.119987</v>
       </c>
-      <c r="Y59" t="n">
+      <c r="AA59" t="n">
         <v>-0.964334</v>
       </c>
-      <c r="Z59" t="n">
+      <c r="AB59" t="n">
         <v>4.641328</v>
       </c>
-      <c r="AA59" t="n">
+      <c r="AC59" t="n">
         <v>3.177699</v>
       </c>
-      <c r="AB59" t="n">
+      <c r="AD59" t="n">
         <v>4.327084</v>
       </c>
-      <c r="AC59" t="n">
+      <c r="AE59" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD59" t="n">
+      <c r="AF59" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AE59" t="n">
+      <c r="AG59" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AF59" t="n">
+      <c r="AH59" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AG59" t="n">
+      <c r="AI59" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AH59" t="n">
+      <c r="AJ59" t="n">
         <v>-0.2</v>
       </c>
-      <c r="AI59" t="n">
+      <c r="AK59" t="n">
         <v>0.23</v>
       </c>
     </row>
@@ -6735,84 +7091,90 @@
         <v>109.91611</v>
       </c>
       <c r="I60" t="n">
+        <v>114.40189</v>
+      </c>
+      <c r="J60" t="n">
         <v>5.0773</v>
       </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
         <v>5.0767</v>
       </c>
-      <c r="K60" t="n">
+      <c r="L60" t="n">
         <v>7372243</v>
       </c>
-      <c r="L60" t="n">
+      <c r="M60" t="n">
         <v>2731513</v>
       </c>
-      <c r="M60" t="n">
+      <c r="N60" t="n">
         <v>4640730</v>
       </c>
-      <c r="N60" t="n">
+      <c r="O60" t="n">
         <v>4.88</v>
       </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
         <v>3.31</v>
       </c>
-      <c r="P60" t="n">
+      <c r="Q60" t="n">
         <v>5.81</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="R60" t="n">
         <v>32.08</v>
       </c>
-      <c r="R60" t="n">
+      <c r="S60" t="n">
         <v>369742</v>
       </c>
-      <c r="S60" t="n">
+      <c r="T60" t="n">
         <v>-0.219358</v>
       </c>
-      <c r="T60" t="n">
+      <c r="U60" t="n">
+        <v>4.057001</v>
+      </c>
+      <c r="V60" t="n">
         <v>-1.918247</v>
       </c>
-      <c r="U60" t="n">
+      <c r="W60" t="n">
         <v>-1.91847</v>
       </c>
-      <c r="V60" t="n">
+      <c r="X60" t="n">
         <v>0.257708</v>
       </c>
-      <c r="W60" t="n">
+      <c r="Y60" t="n">
         <v>-0.694824</v>
       </c>
-      <c r="X60" t="n">
+      <c r="Z60" t="n">
         <v>0.826955</v>
       </c>
-      <c r="Y60" t="n">
+      <c r="AA60" t="n">
         <v>0.5941920000000001</v>
       </c>
-      <c r="Z60" t="n">
+      <c r="AB60" t="n">
         <v>4.443025</v>
       </c>
-      <c r="AA60" t="n">
+      <c r="AC60" t="n">
         <v>2.772183</v>
       </c>
-      <c r="AB60" t="n">
+      <c r="AD60" t="n">
         <v>4.098046</v>
       </c>
-      <c r="AC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" t="n">
+      <c r="AE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="AE60" t="n">
+      <c r="AG60" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="AF60" t="n">
+      <c r="AH60" t="n">
         <v>0.3</v>
       </c>
-      <c r="AG60" t="n">
+      <c r="AI60" t="n">
         <v>0.13</v>
       </c>
-      <c r="AH60" t="n">
+      <c r="AJ60" t="n">
         <v>0.39</v>
       </c>
-      <c r="AI60" t="n">
+      <c r="AK60" t="n">
         <v>-1.25</v>
       </c>
     </row>
@@ -6839,57 +7201,59 @@
         <v>-0.32</v>
       </c>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="n">
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="n">
         <v>5.1816</v>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
         <v>5.181</v>
       </c>
-      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="n">
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="n">
         <v>372616</v>
       </c>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="n">
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="n">
         <v>2.054241</v>
       </c>
-      <c r="U61" t="n">
+      <c r="W61" t="n">
         <v>2.054484</v>
       </c>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="n">
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="n">
         <v>0.777299</v>
       </c>
-      <c r="Z61" t="n">
+      <c r="AB61" t="n">
         <v>4.223453</v>
       </c>
-      <c r="AA61" t="n">
+      <c r="AC61" t="n">
         <v>2.178243</v>
       </c>
-      <c r="AB61" t="n">
+      <c r="AD61" t="n">
         <v>3.983297</v>
       </c>
-      <c r="AC61" t="n">
+      <c r="AE61" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD61" t="n">
+      <c r="AF61" t="n">
         <v>-0.0007470000000000001</v>
       </c>
-      <c r="AE61" t="n">
+      <c r="AG61" t="n">
         <v>-0.0007470000000000001</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -6908,13 +7272,13 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="n">
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="n">
         <v>5.1575</v>
       </c>
-      <c r="J62" t="n">
+      <c r="K62" t="n">
         <v>5.1569</v>
       </c>
-      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -6923,32 +7287,34 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
-      <c r="T62" t="n">
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="n">
         <v>-0.465107</v>
       </c>
-      <c r="U62" t="n">
+      <c r="W62" t="n">
         <v>-0.465161</v>
       </c>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr"/>
-      <c r="AC62" t="n">
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD62" t="n">
+      <c r="AF62" t="n">
         <v>-0.000259</v>
       </c>
-      <c r="AE62" t="n">
+      <c r="AG62" t="n">
         <v>-0.000197</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
-      <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK62"/>
+  <dimension ref="A1:AI62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,155 +453,145 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>inpc</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
           <t>ibc_br_sa</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ibc_br</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>cambio_venda_usd</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>cambio_compra_usd</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>saldo_credito_total</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>saldo_credito_pj</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>saldo_credito_pf</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inadimplencia_total</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inadimplencia_pj</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inadimplencia_pf</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>ipca_acum_12m</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>inpc_acum_12m</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>dif_selic_over</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dif_cdi</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -615,10 +605,10 @@
         <v>6.25</v>
       </c>
       <c r="C2" t="n">
-        <v>0.022435</v>
+        <v>0.022748</v>
       </c>
       <c r="D2" t="n">
-        <v>0.022435</v>
+        <v>0.022748</v>
       </c>
       <c r="E2" t="n">
         <v>1.16</v>
@@ -627,44 +617,42 @@
         <v>-0.64</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2</v>
+        <v>96.96513</v>
       </c>
       <c r="H2" t="n">
-        <v>96.96513</v>
+        <v>97.10777</v>
       </c>
       <c r="I2" t="n">
-        <v>97.10777</v>
+        <v>5.4394</v>
       </c>
       <c r="J2" t="n">
-        <v>5.4394</v>
+        <v>5.4388</v>
       </c>
       <c r="K2" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="L2" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="M2" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="N2" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="O2" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="P2" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="R2" t="n">
-        <v>21.42</v>
-      </c>
-      <c r="S2" t="n">
         <v>368886</v>
       </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -681,8 +669,6 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -704,90 +690,86 @@
         <v>0.64</v>
       </c>
       <c r="G3" t="n">
-        <v>1.16</v>
+        <v>97.48671</v>
       </c>
       <c r="H3" t="n">
-        <v>97.48671</v>
+        <v>96.53041</v>
       </c>
       <c r="I3" t="n">
-        <v>96.53041</v>
+        <v>5.643</v>
       </c>
       <c r="J3" t="n">
-        <v>5.643</v>
+        <v>5.6424</v>
       </c>
       <c r="K3" t="n">
-        <v>5.6424</v>
+        <v>4511956</v>
       </c>
       <c r="L3" t="n">
-        <v>4511956</v>
+        <v>1910940</v>
       </c>
       <c r="M3" t="n">
-        <v>1910940</v>
+        <v>2601017</v>
       </c>
       <c r="N3" t="n">
-        <v>2601017</v>
+        <v>2.33</v>
       </c>
       <c r="O3" t="n">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="R3" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="S3" t="n">
-        <v>367927</v>
+        <v>0.537905</v>
       </c>
       <c r="T3" t="n">
-        <v>0.537905</v>
+        <v>-0.594556</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.594556</v>
+        <v>3.74306</v>
       </c>
       <c r="V3" t="n">
-        <v>3.74306</v>
+        <v>3.743473</v>
       </c>
       <c r="W3" t="n">
-        <v>3.743473</v>
+        <v>1.596467</v>
       </c>
       <c r="X3" t="n">
-        <v>1.596467</v>
+        <v>0.888065</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.888065</v>
+        <v>2.123375</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.123375</v>
-      </c>
-      <c r="AA3" t="n">
         <v>-0.259972</v>
       </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.001496</v>
+      </c>
       <c r="AE3" t="n">
-        <v>1.5</v>
+        <v>0.001496</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.001809</v>
+        <v>-0.01</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.001809</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AK3" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -811,90 +793,86 @@
         <v>0.02</v>
       </c>
       <c r="G4" t="n">
-        <v>0.84</v>
+        <v>99.05526</v>
       </c>
       <c r="H4" t="n">
-        <v>99.05526</v>
+        <v>97.85277000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>97.85277000000001</v>
+        <v>5.6199</v>
       </c>
       <c r="J4" t="n">
-        <v>5.6199</v>
+        <v>5.6193</v>
       </c>
       <c r="K4" t="n">
-        <v>5.6193</v>
+        <v>4597507</v>
       </c>
       <c r="L4" t="n">
-        <v>4597507</v>
+        <v>1933111</v>
       </c>
       <c r="M4" t="n">
-        <v>1933111</v>
+        <v>2664395</v>
       </c>
       <c r="N4" t="n">
-        <v>2664395</v>
+        <v>2.36</v>
       </c>
       <c r="O4" t="n">
-        <v>2.36</v>
+        <v>1.46</v>
       </c>
       <c r="P4" t="n">
-        <v>1.46</v>
+        <v>3.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.01</v>
+        <v>23.91</v>
       </c>
       <c r="R4" t="n">
-        <v>23.91</v>
+        <v>367772</v>
       </c>
       <c r="S4" t="n">
-        <v>367772</v>
+        <v>1.608989</v>
       </c>
       <c r="T4" t="n">
-        <v>1.608989</v>
+        <v>1.36989</v>
       </c>
       <c r="U4" t="n">
-        <v>1.36989</v>
+        <v>-0.409357</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.409357</v>
+        <v>-0.4094</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.4094</v>
+        <v>1.896096</v>
       </c>
       <c r="X4" t="n">
-        <v>1.896096</v>
+        <v>1.160214</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.160214</v>
+        <v>2.436662</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.436662</v>
-      </c>
-      <c r="AA4" t="n">
         <v>-0.042128</v>
       </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.005012</v>
+      </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>0.005012</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.005012</v>
+        <v>0.03</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.005012</v>
+        <v>0.03</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK4" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -918,90 +896,86 @@
         <v>0.87</v>
       </c>
       <c r="G5" t="n">
-        <v>0.73</v>
+        <v>99.37716</v>
       </c>
       <c r="H5" t="n">
-        <v>99.37716</v>
+        <v>99.32258</v>
       </c>
       <c r="I5" t="n">
-        <v>99.32258</v>
+        <v>5.5805</v>
       </c>
       <c r="J5" t="n">
-        <v>5.5805</v>
+        <v>5.5799</v>
       </c>
       <c r="K5" t="n">
-        <v>5.5799</v>
+        <v>4682852</v>
       </c>
       <c r="L5" t="n">
-        <v>4682852</v>
+        <v>1974391</v>
       </c>
       <c r="M5" t="n">
-        <v>1974391</v>
+        <v>2708461</v>
       </c>
       <c r="N5" t="n">
-        <v>2708461</v>
+        <v>2.35</v>
       </c>
       <c r="O5" t="n">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="P5" t="n">
-        <v>1.4</v>
+        <v>3.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.05</v>
+        <v>24.21</v>
       </c>
       <c r="R5" t="n">
-        <v>24.21</v>
+        <v>362204</v>
       </c>
       <c r="S5" t="n">
-        <v>362204</v>
+        <v>0.32497</v>
       </c>
       <c r="T5" t="n">
-        <v>0.32497</v>
+        <v>1.502063</v>
       </c>
       <c r="U5" t="n">
-        <v>1.502063</v>
+        <v>-0.70108</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.70108</v>
+        <v>-0.701155</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.701155</v>
+        <v>1.856332</v>
       </c>
       <c r="X5" t="n">
-        <v>1.856332</v>
+        <v>2.135418</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.135418</v>
+        <v>1.653884</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.653884</v>
-      </c>
-      <c r="AA5" t="n">
         <v>-1.513981</v>
       </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.00406</v>
+      </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>0.00406</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.00406</v>
+        <v>-0.01</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.00406</v>
+        <v>-0.06</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK5" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1025,90 +999,86 @@
         <v>1.82</v>
       </c>
       <c r="G6" t="n">
-        <v>0.67</v>
+        <v>97.4213</v>
       </c>
       <c r="H6" t="n">
-        <v>97.4213</v>
+        <v>91.67776000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>91.67776000000001</v>
+        <v>5.3574</v>
       </c>
       <c r="J6" t="n">
-        <v>5.3574</v>
+        <v>5.3568</v>
       </c>
       <c r="K6" t="n">
-        <v>5.3568</v>
+        <v>4682131</v>
       </c>
       <c r="L6" t="n">
-        <v>4682131</v>
+        <v>1947035</v>
       </c>
       <c r="M6" t="n">
-        <v>1947035</v>
+        <v>2735096</v>
       </c>
       <c r="N6" t="n">
-        <v>2735096</v>
+        <v>2.51</v>
       </c>
       <c r="O6" t="n">
-        <v>2.51</v>
+        <v>1.46</v>
       </c>
       <c r="P6" t="n">
-        <v>1.46</v>
+        <v>3.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.26</v>
+        <v>25.23</v>
       </c>
       <c r="R6" t="n">
-        <v>25.23</v>
+        <v>358398</v>
       </c>
       <c r="S6" t="n">
-        <v>358398</v>
+        <v>-1.968118</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.968118</v>
+        <v>-7.696961</v>
       </c>
       <c r="U6" t="n">
-        <v>-7.696961</v>
+        <v>-3.99785</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.99785</v>
+        <v>-3.99828</v>
       </c>
       <c r="W6" t="n">
-        <v>-3.99828</v>
+        <v>-0.015397</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.015397</v>
+        <v>-1.385541</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.385541</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.9834000000000001</v>
-      </c>
-      <c r="AA6" t="n">
         <v>-1.050789</v>
       </c>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.001433</v>
+      </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>0.001433</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.001433</v>
+        <v>0.16</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.001433</v>
+        <v>0.06</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AK6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1132,90 +1102,86 @@
         <v>1.83</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>98.4804</v>
       </c>
       <c r="H7" t="n">
-        <v>98.4804</v>
+        <v>95.63728999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>95.63728999999999</v>
+        <v>5.1394</v>
       </c>
       <c r="J7" t="n">
-        <v>5.1394</v>
+        <v>5.1388</v>
       </c>
       <c r="K7" t="n">
-        <v>5.1388</v>
+        <v>4727818</v>
       </c>
       <c r="L7" t="n">
-        <v>4727818</v>
+        <v>1971524</v>
       </c>
       <c r="M7" t="n">
-        <v>1971524</v>
+        <v>2756295</v>
       </c>
       <c r="N7" t="n">
-        <v>2756295</v>
+        <v>2.57</v>
       </c>
       <c r="O7" t="n">
-        <v>2.57</v>
+        <v>1.44</v>
       </c>
       <c r="P7" t="n">
-        <v>1.44</v>
+        <v>3.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.38</v>
+        <v>25.63</v>
       </c>
       <c r="R7" t="n">
-        <v>25.63</v>
+        <v>357740</v>
       </c>
       <c r="S7" t="n">
-        <v>357740</v>
+        <v>1.087134</v>
       </c>
       <c r="T7" t="n">
-        <v>1.087134</v>
+        <v>4.318965</v>
       </c>
       <c r="U7" t="n">
-        <v>4.318965</v>
+        <v>-4.069138</v>
       </c>
       <c r="V7" t="n">
-        <v>-4.069138</v>
+        <v>-4.069594</v>
       </c>
       <c r="W7" t="n">
-        <v>-4.069594</v>
+        <v>0.975774</v>
       </c>
       <c r="X7" t="n">
-        <v>0.975774</v>
+        <v>1.257759</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.257759</v>
+        <v>0.775073</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.775073</v>
-      </c>
-      <c r="AA7" t="n">
         <v>-0.183595</v>
       </c>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.004849</v>
+      </c>
       <c r="AE7" t="n">
-        <v>1.5</v>
+        <v>0.004849</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.004849</v>
+        <v>0.06</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.004849</v>
+        <v>-0.02</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AK7" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1239,90 +1205,86 @@
         <v>1.74</v>
       </c>
       <c r="G8" t="n">
-        <v>1.71</v>
+        <v>99.54801999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>99.54801999999999</v>
+        <v>104.53237</v>
       </c>
       <c r="I8" t="n">
-        <v>104.53237</v>
+        <v>4.7378</v>
       </c>
       <c r="J8" t="n">
-        <v>4.7378</v>
+        <v>4.7372</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7372</v>
+        <v>4794583</v>
       </c>
       <c r="L8" t="n">
-        <v>4794583</v>
+        <v>1994119</v>
       </c>
       <c r="M8" t="n">
-        <v>1994119</v>
+        <v>2800464</v>
       </c>
       <c r="N8" t="n">
-        <v>2800464</v>
+        <v>2.66</v>
       </c>
       <c r="O8" t="n">
-        <v>2.66</v>
+        <v>1.55</v>
       </c>
       <c r="P8" t="n">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.45</v>
+        <v>26.54</v>
       </c>
       <c r="R8" t="n">
-        <v>26.54</v>
+        <v>353169</v>
       </c>
       <c r="S8" t="n">
-        <v>353169</v>
+        <v>1.084094</v>
       </c>
       <c r="T8" t="n">
-        <v>1.084094</v>
+        <v>9.300848999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>9.300848999999999</v>
+        <v>-7.814142</v>
       </c>
       <c r="V8" t="n">
-        <v>-7.814142</v>
+        <v>-7.815054</v>
       </c>
       <c r="W8" t="n">
-        <v>-7.815054</v>
+        <v>1.412174</v>
       </c>
       <c r="X8" t="n">
-        <v>1.412174</v>
+        <v>1.146068</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.146068</v>
+        <v>1.602477</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.602477</v>
-      </c>
-      <c r="AA8" t="n">
         <v>-1.277744</v>
       </c>
+      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.002356</v>
+      </c>
       <c r="AE8" t="n">
-        <v>1</v>
+        <v>0.002356</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.002356</v>
+        <v>0.09</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.002356</v>
+        <v>0.11</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK8" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1346,90 +1308,86 @@
         <v>1.41</v>
       </c>
       <c r="G9" t="n">
-        <v>1.04</v>
+        <v>99.44118</v>
       </c>
       <c r="H9" t="n">
-        <v>99.44118</v>
+        <v>100.22938</v>
       </c>
       <c r="I9" t="n">
-        <v>100.22938</v>
+        <v>4.9191</v>
       </c>
       <c r="J9" t="n">
-        <v>4.9191</v>
+        <v>4.9185</v>
       </c>
       <c r="K9" t="n">
-        <v>4.9185</v>
+        <v>4833732</v>
       </c>
       <c r="L9" t="n">
-        <v>4833732</v>
+        <v>2003312</v>
       </c>
       <c r="M9" t="n">
-        <v>2003312</v>
+        <v>2830420</v>
       </c>
       <c r="N9" t="n">
-        <v>2830420</v>
+        <v>2.72</v>
       </c>
       <c r="O9" t="n">
-        <v>2.72</v>
+        <v>1.57</v>
       </c>
       <c r="P9" t="n">
-        <v>1.57</v>
+        <v>3.54</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.54</v>
+        <v>27.46</v>
       </c>
       <c r="R9" t="n">
-        <v>27.46</v>
+        <v>345097</v>
       </c>
       <c r="S9" t="n">
-        <v>345097</v>
+        <v>-0.107325</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.107325</v>
+        <v>-4.116419</v>
       </c>
       <c r="U9" t="n">
-        <v>-4.116419</v>
+        <v>3.826671</v>
       </c>
       <c r="V9" t="n">
-        <v>3.826671</v>
+        <v>3.827155</v>
       </c>
       <c r="W9" t="n">
-        <v>3.827155</v>
+        <v>0.816526</v>
       </c>
       <c r="X9" t="n">
-        <v>0.816526</v>
+        <v>0.461006</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.461006</v>
+        <v>1.06968</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.06968</v>
-      </c>
-      <c r="AA9" t="n">
         <v>-2.285591</v>
       </c>
+      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.001785</v>
+      </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>0.001785</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.001785</v>
+        <v>0.06</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001785</v>
+        <v>0.02</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK9" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1453,90 +1411,86 @@
         <v>0.52</v>
       </c>
       <c r="G10" t="n">
-        <v>0.45</v>
+        <v>99.6454</v>
       </c>
       <c r="H10" t="n">
-        <v>99.6454</v>
+        <v>99.74383</v>
       </c>
       <c r="I10" t="n">
-        <v>99.74383</v>
+        <v>4.7289</v>
       </c>
       <c r="J10" t="n">
-        <v>4.7289</v>
+        <v>4.7283</v>
       </c>
       <c r="K10" t="n">
-        <v>4.7283</v>
+        <v>4889397</v>
       </c>
       <c r="L10" t="n">
-        <v>4889397</v>
+        <v>2013726</v>
       </c>
       <c r="M10" t="n">
-        <v>2013726</v>
+        <v>2875671</v>
       </c>
       <c r="N10" t="n">
-        <v>2875671</v>
+        <v>2.79</v>
       </c>
       <c r="O10" t="n">
-        <v>2.79</v>
+        <v>1.57</v>
       </c>
       <c r="P10" t="n">
-        <v>1.57</v>
+        <v>3.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.65</v>
+        <v>27.42</v>
       </c>
       <c r="R10" t="n">
-        <v>27.42</v>
+        <v>346415</v>
       </c>
       <c r="S10" t="n">
-        <v>346415</v>
+        <v>0.205368</v>
       </c>
       <c r="T10" t="n">
-        <v>0.205368</v>
+        <v>-0.484439</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.484439</v>
+        <v>-3.866561</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.866561</v>
+        <v>-3.867033</v>
       </c>
       <c r="W10" t="n">
-        <v>-3.867033</v>
+        <v>1.151595</v>
       </c>
       <c r="X10" t="n">
-        <v>1.151595</v>
+        <v>0.5198390000000001</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5198390000000001</v>
+        <v>1.598738</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.598738</v>
-      </c>
-      <c r="AA10" t="n">
         <v>0.381922</v>
       </c>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.003057</v>
+      </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>0.003057</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.003057</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.003057</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK10" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1560,90 +1514,86 @@
         <v>0.59</v>
       </c>
       <c r="G11" t="n">
-        <v>0.62</v>
+        <v>99.51048</v>
       </c>
       <c r="H11" t="n">
-        <v>99.51048</v>
+        <v>99.31653</v>
       </c>
       <c r="I11" t="n">
-        <v>99.31653</v>
+        <v>5.238</v>
       </c>
       <c r="J11" t="n">
-        <v>5.238</v>
+        <v>5.2374</v>
       </c>
       <c r="K11" t="n">
-        <v>5.2374</v>
+        <v>4965603</v>
       </c>
       <c r="L11" t="n">
-        <v>4965603</v>
+        <v>2052569</v>
       </c>
       <c r="M11" t="n">
-        <v>2052569</v>
+        <v>2913035</v>
       </c>
       <c r="N11" t="n">
-        <v>2913035</v>
+        <v>2.73</v>
       </c>
       <c r="O11" t="n">
-        <v>2.73</v>
+        <v>1.52</v>
       </c>
       <c r="P11" t="n">
-        <v>1.52</v>
+        <v>3.57</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.57</v>
+        <v>27.88</v>
       </c>
       <c r="R11" t="n">
-        <v>27.88</v>
+        <v>341958</v>
       </c>
       <c r="S11" t="n">
-        <v>341958</v>
+        <v>-0.1354</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1354</v>
+        <v>-0.428397</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.428397</v>
+        <v>10.765717</v>
       </c>
       <c r="V11" t="n">
-        <v>10.765717</v>
+        <v>10.767083</v>
       </c>
       <c r="W11" t="n">
-        <v>10.767083</v>
+        <v>1.558597</v>
       </c>
       <c r="X11" t="n">
-        <v>1.558597</v>
+        <v>1.928912</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.928912</v>
+        <v>1.299314</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.299314</v>
-      </c>
-      <c r="AA11" t="n">
         <v>-1.286607</v>
       </c>
+      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.00132</v>
+      </c>
       <c r="AE11" t="n">
-        <v>0.5</v>
+        <v>0.00132</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.00132</v>
+        <v>-0.06</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.00132</v>
+        <v>-0.05</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AK11" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1667,90 +1617,86 @@
         <v>0.21</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6</v>
+        <v>101.43172</v>
       </c>
       <c r="H12" t="n">
-        <v>101.43172</v>
+        <v>103.95991</v>
       </c>
       <c r="I12" t="n">
-        <v>103.95991</v>
+        <v>5.1884</v>
       </c>
       <c r="J12" t="n">
-        <v>5.1884</v>
+        <v>5.1878</v>
       </c>
       <c r="K12" t="n">
-        <v>5.1878</v>
+        <v>4999244</v>
       </c>
       <c r="L12" t="n">
-        <v>4999244</v>
+        <v>2047038</v>
       </c>
       <c r="M12" t="n">
-        <v>2047038</v>
+        <v>2952207</v>
       </c>
       <c r="N12" t="n">
-        <v>2952207</v>
+        <v>2.84</v>
       </c>
       <c r="O12" t="n">
-        <v>2.84</v>
+        <v>1.6</v>
       </c>
       <c r="P12" t="n">
-        <v>1.6</v>
+        <v>3.71</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.71</v>
+        <v>29.24</v>
       </c>
       <c r="R12" t="n">
-        <v>29.24</v>
+        <v>346403</v>
       </c>
       <c r="S12" t="n">
-        <v>346403</v>
+        <v>1.930691</v>
       </c>
       <c r="T12" t="n">
-        <v>1.930691</v>
+        <v>4.675335</v>
       </c>
       <c r="U12" t="n">
-        <v>4.675335</v>
+        <v>-0.946926</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.946926</v>
+        <v>-0.947035</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.947035</v>
+        <v>0.677481</v>
       </c>
       <c r="X12" t="n">
-        <v>0.677481</v>
+        <v>-0.269467</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.269467</v>
+        <v>1.344714</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.344714</v>
-      </c>
-      <c r="AA12" t="n">
         <v>1.299867</v>
       </c>
+      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.0009210000000000001</v>
+      </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AK12" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -1774,96 +1720,90 @@
         <v>-0.7</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.31</v>
+        <v>101.10583</v>
       </c>
       <c r="H13" t="n">
-        <v>101.10583</v>
+        <v>104.51156</v>
       </c>
       <c r="I13" t="n">
-        <v>104.51156</v>
+        <v>5.179</v>
       </c>
       <c r="J13" t="n">
-        <v>5.179</v>
+        <v>5.1784</v>
       </c>
       <c r="K13" t="n">
-        <v>5.1784</v>
+        <v>5072711</v>
       </c>
       <c r="L13" t="n">
-        <v>5072711</v>
+        <v>2064183</v>
       </c>
       <c r="M13" t="n">
-        <v>2064183</v>
+        <v>3008528</v>
       </c>
       <c r="N13" t="n">
-        <v>3008528</v>
+        <v>2.9</v>
       </c>
       <c r="O13" t="n">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="P13" t="n">
-        <v>1.62</v>
+        <v>3.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.78</v>
+        <v>28.6</v>
       </c>
       <c r="R13" t="n">
-        <v>28.6</v>
+        <v>339664</v>
       </c>
       <c r="S13" t="n">
-        <v>339664</v>
+        <v>-0.32129</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.32129</v>
+        <v>0.530637</v>
       </c>
       <c r="U13" t="n">
-        <v>0.530637</v>
+        <v>-0.181173</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.181173</v>
+        <v>-0.181194</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.181194</v>
+        <v>1.469562</v>
       </c>
       <c r="X13" t="n">
-        <v>1.469562</v>
+        <v>0.837552</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.837552</v>
+        <v>1.907759</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.907759</v>
+        <v>-1.945422</v>
       </c>
       <c r="AA13" t="n">
-        <v>-1.945422</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.727061000000001</v>
+        <v>8.58755</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.58755</v>
+        <v>0.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>8.825751</v>
+        <v>0.001523</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.5</v>
+        <v>0.001523</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.001523</v>
+        <v>0.06</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.001523</v>
+        <v>0.02</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK13" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -1887,96 +1827,90 @@
         <v>-0.95</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.32</v>
+        <v>101.16034</v>
       </c>
       <c r="H14" t="n">
-        <v>101.16034</v>
+        <v>101.1889</v>
       </c>
       <c r="I14" t="n">
-        <v>101.1889</v>
+        <v>5.4066</v>
       </c>
       <c r="J14" t="n">
-        <v>5.4066</v>
+        <v>5.406</v>
       </c>
       <c r="K14" t="n">
-        <v>5.406</v>
+        <v>5164775</v>
       </c>
       <c r="L14" t="n">
-        <v>5164775</v>
+        <v>2109806</v>
       </c>
       <c r="M14" t="n">
-        <v>2109806</v>
+        <v>3054969</v>
       </c>
       <c r="N14" t="n">
-        <v>3054969</v>
+        <v>2.92</v>
       </c>
       <c r="O14" t="n">
-        <v>2.92</v>
+        <v>1.65</v>
       </c>
       <c r="P14" t="n">
-        <v>1.65</v>
+        <v>3.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.8</v>
+        <v>28.57</v>
       </c>
       <c r="R14" t="n">
-        <v>28.57</v>
+        <v>327580</v>
       </c>
       <c r="S14" t="n">
-        <v>327580</v>
+        <v>0.053914</v>
       </c>
       <c r="T14" t="n">
-        <v>0.053914</v>
+        <v>-3.179227</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.179227</v>
+        <v>4.394671</v>
       </c>
       <c r="V14" t="n">
-        <v>4.394671</v>
+        <v>4.39518</v>
       </c>
       <c r="W14" t="n">
-        <v>4.39518</v>
+        <v>1.814888</v>
       </c>
       <c r="X14" t="n">
-        <v>1.814888</v>
+        <v>2.210221</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.210221</v>
+        <v>1.543645</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.543645</v>
+        <v>-3.557633</v>
       </c>
       <c r="AA14" t="n">
-        <v>-3.557633</v>
+        <v>7.168596</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.168596</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.248760000000001</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>7.191214</v>
+        <v>0.000228</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>0.000228</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.000228</v>
+        <v>0.02</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.000228</v>
+        <v>0.03</v>
       </c>
       <c r="AH14" t="n">
         <v>0.02</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK14" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -2000,96 +1934,90 @@
         <v>-0.97</v>
       </c>
       <c r="G15" t="n">
-        <v>0.47</v>
+        <v>101.44171</v>
       </c>
       <c r="H15" t="n">
-        <v>101.44171</v>
+        <v>100.08177</v>
       </c>
       <c r="I15" t="n">
-        <v>100.08177</v>
+        <v>5.257</v>
       </c>
       <c r="J15" t="n">
-        <v>5.257</v>
+        <v>5.2564</v>
       </c>
       <c r="K15" t="n">
-        <v>5.2564</v>
+        <v>5215990</v>
       </c>
       <c r="L15" t="n">
-        <v>5215990</v>
+        <v>2105856</v>
       </c>
       <c r="M15" t="n">
-        <v>2105856</v>
+        <v>3110134</v>
       </c>
       <c r="N15" t="n">
-        <v>3110134</v>
+        <v>3.04</v>
       </c>
       <c r="O15" t="n">
-        <v>3.04</v>
+        <v>1.77</v>
       </c>
       <c r="P15" t="n">
-        <v>1.77</v>
+        <v>3.89</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.89</v>
+        <v>29.68</v>
       </c>
       <c r="R15" t="n">
-        <v>29.68</v>
+        <v>325546</v>
       </c>
       <c r="S15" t="n">
-        <v>325546</v>
+        <v>0.278143</v>
       </c>
       <c r="T15" t="n">
-        <v>0.278143</v>
+        <v>-1.094122</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.094122</v>
+        <v>-2.766988</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.766988</v>
+        <v>-2.767296</v>
       </c>
       <c r="W15" t="n">
-        <v>-2.767296</v>
+        <v>0.991621</v>
       </c>
       <c r="X15" t="n">
-        <v>0.991621</v>
+        <v>-0.187221</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.187221</v>
+        <v>1.805747</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.805747</v>
+        <v>-0.6209170000000001</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.6209170000000001</v>
+        <v>6.470016</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.470016</v>
+        <v>6.517038</v>
       </c>
       <c r="AC15" t="n">
-        <v>6.517038</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.460076</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK15" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -2113,96 +2041,90 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.38</v>
+        <v>100.7146</v>
       </c>
       <c r="H16" t="n">
-        <v>100.7146</v>
+        <v>99.15031999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>99.15031999999999</v>
+        <v>5.2941</v>
       </c>
       <c r="J16" t="n">
-        <v>5.2941</v>
+        <v>5.2935</v>
       </c>
       <c r="K16" t="n">
-        <v>5.2935</v>
+        <v>5285657</v>
       </c>
       <c r="L16" t="n">
-        <v>5285657</v>
+        <v>2130312</v>
       </c>
       <c r="M16" t="n">
-        <v>2130312</v>
+        <v>3155345</v>
       </c>
       <c r="N16" t="n">
-        <v>3155345</v>
+        <v>3.07</v>
       </c>
       <c r="O16" t="n">
-        <v>3.07</v>
+        <v>1.81</v>
       </c>
       <c r="P16" t="n">
-        <v>1.81</v>
+        <v>3.92</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.92</v>
+        <v>30.52</v>
       </c>
       <c r="R16" t="n">
-        <v>30.52</v>
+        <v>331505</v>
       </c>
       <c r="S16" t="n">
-        <v>331505</v>
+        <v>-0.716776</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.716776</v>
+        <v>-0.930689</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.930689</v>
+        <v>0.705726</v>
       </c>
       <c r="V16" t="n">
-        <v>0.705726</v>
+        <v>0.705806</v>
       </c>
       <c r="W16" t="n">
-        <v>0.705806</v>
+        <v>1.335643</v>
       </c>
       <c r="X16" t="n">
-        <v>1.335643</v>
+        <v>1.161333</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.161333</v>
+        <v>1.453667</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.453667</v>
+        <v>1.830463</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.830463</v>
+        <v>5.900488</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.900488</v>
+        <v>5.899363</v>
       </c>
       <c r="AC16" t="n">
-        <v>5.899363</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>5.974439</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AH16" t="n">
         <v>0.03</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AK16" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2226,96 +2148,90 @@
         <v>0.45</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6899999999999999</v>
+        <v>100.58818</v>
       </c>
       <c r="H17" t="n">
-        <v>100.58818</v>
+        <v>99.97037</v>
       </c>
       <c r="I17" t="n">
-        <v>99.97037</v>
+        <v>5.2177</v>
       </c>
       <c r="J17" t="n">
-        <v>5.2177</v>
+        <v>5.2171</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2171</v>
+        <v>5366069</v>
       </c>
       <c r="L17" t="n">
-        <v>5366069</v>
+        <v>2178236</v>
       </c>
       <c r="M17" t="n">
-        <v>2178236</v>
+        <v>3187833</v>
       </c>
       <c r="N17" t="n">
-        <v>3187833</v>
+        <v>3.07</v>
       </c>
       <c r="O17" t="n">
-        <v>3.07</v>
+        <v>1.8</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8</v>
+        <v>3.94</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.94</v>
+        <v>29.64</v>
       </c>
       <c r="R17" t="n">
-        <v>29.64</v>
+        <v>324703</v>
       </c>
       <c r="S17" t="n">
-        <v>324703</v>
+        <v>-0.125523</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.125523</v>
+        <v>0.827078</v>
       </c>
       <c r="U17" t="n">
-        <v>0.827078</v>
+        <v>-1.443116</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.443116</v>
+        <v>-1.443279</v>
       </c>
       <c r="W17" t="n">
-        <v>-1.443279</v>
+        <v>1.521325</v>
       </c>
       <c r="X17" t="n">
-        <v>1.521325</v>
+        <v>2.249624</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.249624</v>
+        <v>1.029618</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.029618</v>
+        <v>-2.051854</v>
       </c>
       <c r="AA17" t="n">
-        <v>-2.051854</v>
+        <v>5.784842</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.784842</v>
+        <v>5.458422</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.458422</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>5.932356</v>
+        <v>-0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AI17" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK17" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -2339,96 +2255,90 @@
         <v>0.21</v>
       </c>
       <c r="G18" t="n">
-        <v>0.46</v>
+        <v>100.10988</v>
       </c>
       <c r="H18" t="n">
-        <v>100.10988</v>
+        <v>95.09953</v>
       </c>
       <c r="I18" t="n">
-        <v>95.09953</v>
+        <v>5.0993</v>
       </c>
       <c r="J18" t="n">
-        <v>5.0993</v>
+        <v>5.0987</v>
       </c>
       <c r="K18" t="n">
-        <v>5.0987</v>
+        <v>5373231</v>
       </c>
       <c r="L18" t="n">
-        <v>5373231</v>
+        <v>2151399</v>
       </c>
       <c r="M18" t="n">
-        <v>2151399</v>
+        <v>3221831</v>
       </c>
       <c r="N18" t="n">
-        <v>3221831</v>
+        <v>3.24</v>
       </c>
       <c r="O18" t="n">
-        <v>3.24</v>
+        <v>1.94</v>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>4.11</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.11</v>
+        <v>30.54</v>
       </c>
       <c r="R18" t="n">
-        <v>30.54</v>
+        <v>331122</v>
       </c>
       <c r="S18" t="n">
-        <v>331122</v>
+        <v>-0.475503</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.475503</v>
+        <v>-4.872284</v>
       </c>
       <c r="U18" t="n">
-        <v>-4.872284</v>
+        <v>-2.269199</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.269199</v>
+        <v>-2.26946</v>
       </c>
       <c r="W18" t="n">
-        <v>-2.26946</v>
+        <v>0.133468</v>
       </c>
       <c r="X18" t="n">
-        <v>0.133468</v>
+        <v>-1.232052</v>
       </c>
       <c r="Y18" t="n">
-        <v>-1.232052</v>
+        <v>1.066493</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.066493</v>
+        <v>1.976883</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.976883</v>
+        <v>5.77432</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.77432</v>
+        <v>3.79089</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.79089</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>5.711379</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AH18" t="n">
         <v>0.17</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AK18" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2452,96 +2362,90 @@
         <v>-0.06</v>
       </c>
       <c r="G19" t="n">
-        <v>0.77</v>
+        <v>103.07987</v>
       </c>
       <c r="H19" t="n">
-        <v>103.07987</v>
+        <v>98.64798</v>
       </c>
       <c r="I19" t="n">
-        <v>98.64798</v>
+        <v>5.2078</v>
       </c>
       <c r="J19" t="n">
-        <v>5.2078</v>
+        <v>5.2072</v>
       </c>
       <c r="K19" t="n">
-        <v>5.2072</v>
+        <v>5370950</v>
       </c>
       <c r="L19" t="n">
-        <v>5370950</v>
+        <v>2136105</v>
       </c>
       <c r="M19" t="n">
-        <v>2136105</v>
+        <v>3234845</v>
       </c>
       <c r="N19" t="n">
-        <v>3234845</v>
+        <v>3.36</v>
       </c>
       <c r="O19" t="n">
-        <v>3.36</v>
+        <v>2.17</v>
       </c>
       <c r="P19" t="n">
-        <v>2.17</v>
+        <v>4.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.16</v>
+        <v>30.48</v>
       </c>
       <c r="R19" t="n">
-        <v>30.48</v>
+        <v>328098</v>
       </c>
       <c r="S19" t="n">
-        <v>328098</v>
+        <v>2.96673</v>
       </c>
       <c r="T19" t="n">
-        <v>2.96673</v>
+        <v>3.731301</v>
       </c>
       <c r="U19" t="n">
-        <v>3.731301</v>
+        <v>2.127743</v>
       </c>
       <c r="V19" t="n">
-        <v>2.127743</v>
+        <v>2.127993</v>
       </c>
       <c r="W19" t="n">
-        <v>2.127993</v>
+        <v>-0.042451</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.042451</v>
+        <v>-0.710886</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.710886</v>
+        <v>0.403932</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.403932</v>
+        <v>-0.913259</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.913259</v>
+        <v>5.596302</v>
       </c>
       <c r="AB19" t="n">
-        <v>5.596302</v>
+        <v>1.864495</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.864495</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>5.47065</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK19" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2565,96 +2469,90 @@
         <v>0.05</v>
       </c>
       <c r="G20" t="n">
-        <v>0.64</v>
+        <v>103.08494</v>
       </c>
       <c r="H20" t="n">
-        <v>103.08494</v>
+        <v>110.61922</v>
       </c>
       <c r="I20" t="n">
-        <v>110.61922</v>
+        <v>5.0804</v>
       </c>
       <c r="J20" t="n">
-        <v>5.0804</v>
+        <v>5.0798</v>
       </c>
       <c r="K20" t="n">
-        <v>5.0798</v>
+        <v>5424811</v>
       </c>
       <c r="L20" t="n">
-        <v>5424811</v>
+        <v>2154900</v>
       </c>
       <c r="M20" t="n">
-        <v>2154900</v>
+        <v>3269910</v>
       </c>
       <c r="N20" t="n">
-        <v>3269910</v>
+        <v>3.35</v>
       </c>
       <c r="O20" t="n">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>4.11</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.11</v>
+        <v>30.99</v>
       </c>
       <c r="R20" t="n">
-        <v>30.99</v>
+        <v>341158</v>
       </c>
       <c r="S20" t="n">
-        <v>341158</v>
+        <v>0.004919</v>
       </c>
       <c r="T20" t="n">
-        <v>0.004919</v>
+        <v>12.135312</v>
       </c>
       <c r="U20" t="n">
-        <v>12.135312</v>
+        <v>-2.446331</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.446331</v>
+        <v>-2.446612</v>
       </c>
       <c r="W20" t="n">
-        <v>-2.446612</v>
+        <v>1.002821</v>
       </c>
       <c r="X20" t="n">
-        <v>1.002821</v>
+        <v>0.879872</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.879872</v>
+        <v>1.083978</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.083978</v>
+        <v>3.980518</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.980518</v>
+        <v>4.650694</v>
       </c>
       <c r="AB20" t="n">
-        <v>4.650694</v>
+        <v>0.172427</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.172427</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.361088</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AK20" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2678,96 +2576,90 @@
         <v>-0.95</v>
       </c>
       <c r="G21" t="n">
-        <v>0.53</v>
+        <v>103.93573</v>
       </c>
       <c r="H21" t="n">
-        <v>103.93573</v>
+        <v>104.04095</v>
       </c>
       <c r="I21" t="n">
-        <v>104.04095</v>
+        <v>5.0007</v>
       </c>
       <c r="J21" t="n">
-        <v>5.0007</v>
+        <v>5.0001</v>
       </c>
       <c r="K21" t="n">
-        <v>5.0001</v>
+        <v>5426307</v>
       </c>
       <c r="L21" t="n">
-        <v>5426307</v>
+        <v>2145000</v>
       </c>
       <c r="M21" t="n">
-        <v>2145000</v>
+        <v>3281308</v>
       </c>
       <c r="N21" t="n">
-        <v>3281308</v>
+        <v>3.54</v>
       </c>
       <c r="O21" t="n">
-        <v>3.54</v>
+        <v>2.45</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>4.26</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.26</v>
+        <v>31.62</v>
       </c>
       <c r="R21" t="n">
-        <v>31.62</v>
+        <v>345725</v>
       </c>
       <c r="S21" t="n">
-        <v>345725</v>
+        <v>0.825329</v>
       </c>
       <c r="T21" t="n">
-        <v>0.825329</v>
+        <v>-5.946769</v>
       </c>
       <c r="U21" t="n">
-        <v>-5.946769</v>
+        <v>-1.568774</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.568774</v>
+        <v>-1.568959</v>
       </c>
       <c r="W21" t="n">
-        <v>-1.568959</v>
+        <v>0.027577</v>
       </c>
       <c r="X21" t="n">
-        <v>0.027577</v>
+        <v>-0.459418</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.459418</v>
+        <v>0.348572</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.348572</v>
+        <v>1.338676</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.338676</v>
+        <v>4.184706</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.184706</v>
+        <v>-2.158772</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.158772</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.834324</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AK21" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -2791,96 +2683,90 @@
         <v>-1.84</v>
       </c>
       <c r="G22" t="n">
-        <v>0.36</v>
+        <v>102.42973</v>
       </c>
       <c r="H22" t="n">
-        <v>102.42973</v>
+        <v>102.71375</v>
       </c>
       <c r="I22" t="n">
-        <v>102.71375</v>
+        <v>5.0959</v>
       </c>
       <c r="J22" t="n">
-        <v>5.0959</v>
+        <v>5.0953</v>
       </c>
       <c r="K22" t="n">
-        <v>5.0953</v>
+        <v>5453708</v>
       </c>
       <c r="L22" t="n">
-        <v>5453708</v>
+        <v>2145530</v>
       </c>
       <c r="M22" t="n">
-        <v>2145530</v>
+        <v>3308178</v>
       </c>
       <c r="N22" t="n">
-        <v>3308178</v>
+        <v>3.65</v>
       </c>
       <c r="O22" t="n">
-        <v>3.65</v>
+        <v>2.58</v>
       </c>
       <c r="P22" t="n">
-        <v>2.58</v>
+        <v>4.35</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.35</v>
+        <v>31.63</v>
       </c>
       <c r="R22" t="n">
-        <v>31.63</v>
+        <v>343489</v>
       </c>
       <c r="S22" t="n">
-        <v>343489</v>
+        <v>-1.448972</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.448972</v>
+        <v>-1.275652</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.275652</v>
+        <v>1.903733</v>
       </c>
       <c r="V22" t="n">
-        <v>1.903733</v>
+        <v>1.903962</v>
       </c>
       <c r="W22" t="n">
-        <v>1.903962</v>
+        <v>0.504966</v>
       </c>
       <c r="X22" t="n">
-        <v>0.504966</v>
+        <v>0.024709</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.024709</v>
+        <v>0.818881</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.818881</v>
+        <v>-0.646757</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0.646757</v>
+        <v>3.935832</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.935832</v>
+        <v>-4.45588</v>
       </c>
       <c r="AC22" t="n">
-        <v>-4.45588</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.741292</v>
+        <v>-0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0</v>
+        <v>0.11</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK22" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -2904,96 +2790,90 @@
         <v>-1.93</v>
       </c>
       <c r="G23" t="n">
+        <v>102.39935</v>
+      </c>
+      <c r="H23" t="n">
+        <v>102.28352</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4.8192</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4.8186</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5479459</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2169613</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3309846</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P23" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>30.85</v>
+      </c>
+      <c r="R23" t="n">
+        <v>343620</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.029659</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.418863</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-5.429855</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-5.430495</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.472174</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.122473</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.050421</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.038138</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.161501</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-6.84947</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AH23" t="n">
         <v>-0.1</v>
       </c>
-      <c r="H23" t="n">
-        <v>102.39935</v>
-      </c>
-      <c r="I23" t="n">
-        <v>102.28352</v>
-      </c>
-      <c r="J23" t="n">
-        <v>4.8192</v>
-      </c>
-      <c r="K23" t="n">
-        <v>4.8186</v>
-      </c>
-      <c r="L23" t="n">
-        <v>5479459</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2169613</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3309846</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="R23" t="n">
-        <v>30.85</v>
-      </c>
-      <c r="S23" t="n">
-        <v>343620</v>
-      </c>
-      <c r="T23" t="n">
-        <v>-0.029659</v>
-      </c>
-      <c r="U23" t="n">
-        <v>-0.418863</v>
-      </c>
-      <c r="V23" t="n">
-        <v>-5.429855</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-5.430495</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0.472174</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.122473</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0.050421</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.038138</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>3.161501</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>-6.84947</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.998957</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>-0.04</v>
-      </c>
       <c r="AI23" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AK23" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -3017,96 +2897,90 @@
         <v>-0.72</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.09</v>
+        <v>102.90686</v>
       </c>
       <c r="H24" t="n">
-        <v>102.90686</v>
+        <v>105.34474</v>
       </c>
       <c r="I24" t="n">
-        <v>105.34474</v>
+        <v>4.7415</v>
       </c>
       <c r="J24" t="n">
-        <v>4.7415</v>
+        <v>4.7409</v>
       </c>
       <c r="K24" t="n">
-        <v>4.7409</v>
+        <v>5484871</v>
       </c>
       <c r="L24" t="n">
-        <v>5484871</v>
+        <v>2153541</v>
       </c>
       <c r="M24" t="n">
-        <v>2153541</v>
+        <v>3331330</v>
       </c>
       <c r="N24" t="n">
-        <v>3331330</v>
+        <v>3.63</v>
       </c>
       <c r="O24" t="n">
-        <v>3.63</v>
+        <v>2.73</v>
       </c>
       <c r="P24" t="n">
-        <v>2.73</v>
+        <v>4.22</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.22</v>
+        <v>30.43</v>
       </c>
       <c r="R24" t="n">
-        <v>30.43</v>
+        <v>345476</v>
       </c>
       <c r="S24" t="n">
-        <v>345476</v>
+        <v>0.495618</v>
       </c>
       <c r="T24" t="n">
-        <v>0.495618</v>
+        <v>2.992877</v>
       </c>
       <c r="U24" t="n">
-        <v>2.992877</v>
+        <v>-1.612301</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.612301</v>
+        <v>-1.612502</v>
       </c>
       <c r="W24" t="n">
-        <v>-1.612502</v>
+        <v>0.098769</v>
       </c>
       <c r="X24" t="n">
-        <v>0.098769</v>
+        <v>-0.740777</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.740777</v>
+        <v>0.6490939999999999</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.6490939999999999</v>
+        <v>0.5401319999999999</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.5401319999999999</v>
+        <v>3.992444</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.992444</v>
+        <v>-7.713954</v>
       </c>
       <c r="AC24" t="n">
-        <v>-7.713954</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.527423</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK24" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3130,96 +3004,90 @@
         <v>-0.14</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2</v>
+        <v>102.50239</v>
       </c>
       <c r="H25" t="n">
-        <v>102.50239</v>
+        <v>106.05687</v>
       </c>
       <c r="I25" t="n">
-        <v>106.05687</v>
+        <v>4.9219</v>
       </c>
       <c r="J25" t="n">
-        <v>4.9219</v>
+        <v>4.9213</v>
       </c>
       <c r="K25" t="n">
-        <v>4.9213</v>
+        <v>5559063</v>
       </c>
       <c r="L25" t="n">
-        <v>5559063</v>
+        <v>2172658</v>
       </c>
       <c r="M25" t="n">
-        <v>2172658</v>
+        <v>3386405</v>
       </c>
       <c r="N25" t="n">
-        <v>3386405</v>
+        <v>3.61</v>
       </c>
       <c r="O25" t="n">
-        <v>3.61</v>
+        <v>2.82</v>
       </c>
       <c r="P25" t="n">
-        <v>2.82</v>
+        <v>4.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.12</v>
+        <v>29.92</v>
       </c>
       <c r="R25" t="n">
-        <v>29.92</v>
+        <v>344177</v>
       </c>
       <c r="S25" t="n">
-        <v>344177</v>
+        <v>-0.393045</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.393045</v>
+        <v>0.676</v>
       </c>
       <c r="U25" t="n">
-        <v>0.676</v>
+        <v>3.804703</v>
       </c>
       <c r="V25" t="n">
-        <v>3.804703</v>
+        <v>3.805185</v>
       </c>
       <c r="W25" t="n">
-        <v>3.805185</v>
+        <v>1.352666</v>
       </c>
       <c r="X25" t="n">
-        <v>1.352666</v>
+        <v>0.887701</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.887701</v>
+        <v>1.653244</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.653244</v>
+        <v>-0.376003</v>
       </c>
       <c r="AA25" t="n">
-        <v>-0.376003</v>
+        <v>4.608216</v>
       </c>
       <c r="AB25" t="n">
-        <v>4.608216</v>
+        <v>-7.193509</v>
       </c>
       <c r="AC25" t="n">
-        <v>-7.193509</v>
+        <v>-0.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.057054</v>
+        <v>-0.001599</v>
       </c>
       <c r="AE25" t="n">
-        <v>-0.5</v>
+        <v>-0.001599</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.001599</v>
+        <v>-0.02</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.001599</v>
+        <v>0.09</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AK25" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -3243,96 +3111,90 @@
         <v>0.37</v>
       </c>
       <c r="G26" t="n">
-        <v>0.11</v>
+        <v>102.5153</v>
       </c>
       <c r="H26" t="n">
-        <v>102.5153</v>
+        <v>101.75897</v>
       </c>
       <c r="I26" t="n">
-        <v>101.75897</v>
+        <v>5.0076</v>
       </c>
       <c r="J26" t="n">
-        <v>5.0076</v>
+        <v>5.007</v>
       </c>
       <c r="K26" t="n">
-        <v>5.007</v>
+        <v>5625945</v>
       </c>
       <c r="L26" t="n">
-        <v>5625945</v>
+        <v>2215175</v>
       </c>
       <c r="M26" t="n">
-        <v>2215175</v>
+        <v>3410769</v>
       </c>
       <c r="N26" t="n">
-        <v>3410769</v>
+        <v>3.54</v>
       </c>
       <c r="O26" t="n">
-        <v>3.54</v>
+        <v>2.82</v>
       </c>
       <c r="P26" t="n">
-        <v>2.82</v>
+        <v>4</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>29.66</v>
       </c>
       <c r="R26" t="n">
-        <v>29.66</v>
+        <v>340324</v>
       </c>
       <c r="S26" t="n">
-        <v>340324</v>
+        <v>0.012595</v>
       </c>
       <c r="T26" t="n">
-        <v>0.012595</v>
+        <v>-4.052448</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.052448</v>
+        <v>1.741198</v>
       </c>
       <c r="V26" t="n">
-        <v>1.741198</v>
+        <v>1.74141</v>
       </c>
       <c r="W26" t="n">
-        <v>1.74141</v>
+        <v>1.203116</v>
       </c>
       <c r="X26" t="n">
-        <v>1.203116</v>
+        <v>1.956912</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.956912</v>
+        <v>0.719465</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.719465</v>
+        <v>-1.119482</v>
       </c>
       <c r="AA26" t="n">
-        <v>-1.119482</v>
+        <v>5.185235</v>
       </c>
       <c r="AB26" t="n">
-        <v>5.185235</v>
+        <v>-5.956714</v>
       </c>
       <c r="AC26" t="n">
-        <v>-5.956714</v>
+        <v>-0.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>4.505936</v>
+        <v>-0.000768</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.5</v>
+        <v>-0.000768</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.000768</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.000768</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK26" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -3356,96 +3218,90 @@
         <v>0.5</v>
       </c>
       <c r="G27" t="n">
-        <v>0.12</v>
+        <v>102.83959</v>
       </c>
       <c r="H27" t="n">
-        <v>102.83959</v>
+        <v>101.9338</v>
       </c>
       <c r="I27" t="n">
-        <v>101.9338</v>
+        <v>5.0575</v>
       </c>
       <c r="J27" t="n">
-        <v>5.0575</v>
+        <v>5.0569</v>
       </c>
       <c r="K27" t="n">
-        <v>5.0569</v>
+        <v>5653808</v>
       </c>
       <c r="L27" t="n">
-        <v>5653808</v>
+        <v>2204808</v>
       </c>
       <c r="M27" t="n">
-        <v>2204808</v>
+        <v>3449000</v>
       </c>
       <c r="N27" t="n">
-        <v>3449000</v>
+        <v>3.56</v>
       </c>
       <c r="O27" t="n">
-        <v>3.56</v>
+        <v>2.92</v>
       </c>
       <c r="P27" t="n">
-        <v>2.92</v>
+        <v>3.97</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.97</v>
+        <v>29.24</v>
       </c>
       <c r="R27" t="n">
-        <v>29.24</v>
+        <v>340247</v>
       </c>
       <c r="S27" t="n">
-        <v>340247</v>
+        <v>0.316333</v>
       </c>
       <c r="T27" t="n">
-        <v>0.316333</v>
+        <v>0.171808</v>
       </c>
       <c r="U27" t="n">
-        <v>0.171808</v>
+        <v>0.996485</v>
       </c>
       <c r="V27" t="n">
-        <v>0.996485</v>
+        <v>0.996605</v>
       </c>
       <c r="W27" t="n">
-        <v>0.996605</v>
+        <v>0.495259</v>
       </c>
       <c r="X27" t="n">
-        <v>0.495259</v>
+        <v>-0.467999</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.467999</v>
+        <v>1.120891</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.120891</v>
+        <v>-0.022625</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.022625</v>
+        <v>4.819246</v>
       </c>
       <c r="AB27" t="n">
-        <v>4.819246</v>
+        <v>-4.560737</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4.560737</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.141877</v>
+        <v>-0.001143</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>-0.001143</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.001143</v>
+        <v>0.02</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.001143</v>
+        <v>0.1</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK27" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3469,96 +3325,90 @@
         <v>0.59</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1</v>
+        <v>103.59456</v>
       </c>
       <c r="H28" t="n">
-        <v>103.59456</v>
+        <v>101.68042</v>
       </c>
       <c r="I28" t="n">
-        <v>101.68042</v>
+        <v>4.9355</v>
       </c>
       <c r="J28" t="n">
-        <v>4.9355</v>
+        <v>4.9349</v>
       </c>
       <c r="K28" t="n">
-        <v>4.9349</v>
+        <v>5711103</v>
       </c>
       <c r="L28" t="n">
-        <v>5711103</v>
+        <v>2220766</v>
       </c>
       <c r="M28" t="n">
-        <v>2220766</v>
+        <v>3490337</v>
       </c>
       <c r="N28" t="n">
-        <v>3490337</v>
+        <v>3.53</v>
       </c>
       <c r="O28" t="n">
-        <v>3.53</v>
+        <v>2.99</v>
       </c>
       <c r="P28" t="n">
-        <v>2.99</v>
+        <v>3.88</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.88</v>
+        <v>29.01</v>
       </c>
       <c r="R28" t="n">
-        <v>29.01</v>
+        <v>348406</v>
       </c>
       <c r="S28" t="n">
-        <v>348406</v>
+        <v>0.734124</v>
       </c>
       <c r="T28" t="n">
-        <v>0.734124</v>
+        <v>-0.248573</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.248573</v>
+        <v>-2.412259</v>
       </c>
       <c r="V28" t="n">
-        <v>-2.412259</v>
+        <v>-2.412545</v>
       </c>
       <c r="W28" t="n">
-        <v>-2.412545</v>
+        <v>1.013388</v>
       </c>
       <c r="X28" t="n">
-        <v>1.013388</v>
+        <v>0.723782</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.723782</v>
+        <v>1.198521</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.198521</v>
+        <v>2.397964</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.397964</v>
+        <v>4.683537</v>
       </c>
       <c r="AB28" t="n">
-        <v>4.683537</v>
+        <v>-3.457004</v>
       </c>
       <c r="AC28" t="n">
-        <v>-3.457004</v>
+        <v>-0.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.851383</v>
+        <v>-0.001678</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.5</v>
+        <v>-0.001678</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.001678</v>
+        <v>-0.03</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.001678</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AH28" t="n">
-        <v>-0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="AK28" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -3582,96 +3432,90 @@
         <v>0.74</v>
       </c>
       <c r="G29" t="n">
-        <v>0.55</v>
+        <v>104.88818</v>
       </c>
       <c r="H29" t="n">
-        <v>104.88818</v>
+        <v>101.68469</v>
       </c>
       <c r="I29" t="n">
-        <v>101.68469</v>
+        <v>4.8413</v>
       </c>
       <c r="J29" t="n">
-        <v>4.8413</v>
+        <v>4.8407</v>
       </c>
       <c r="K29" t="n">
-        <v>4.8407</v>
+        <v>5805157</v>
       </c>
       <c r="L29" t="n">
-        <v>5805157</v>
+        <v>2283485</v>
       </c>
       <c r="M29" t="n">
-        <v>2283485</v>
+        <v>3521672</v>
       </c>
       <c r="N29" t="n">
-        <v>3521672</v>
+        <v>3.29</v>
       </c>
       <c r="O29" t="n">
-        <v>3.29</v>
+        <v>2.59</v>
       </c>
       <c r="P29" t="n">
-        <v>2.59</v>
+        <v>3.75</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.75</v>
+        <v>28.14</v>
       </c>
       <c r="R29" t="n">
-        <v>28.14</v>
+        <v>355034</v>
       </c>
       <c r="S29" t="n">
-        <v>355034</v>
+        <v>1.248734</v>
       </c>
       <c r="T29" t="n">
-        <v>1.248734</v>
+        <v>0.004199</v>
       </c>
       <c r="U29" t="n">
-        <v>0.004199</v>
+        <v>-1.908621</v>
       </c>
       <c r="V29" t="n">
-        <v>-1.908621</v>
+        <v>-1.908853</v>
       </c>
       <c r="W29" t="n">
-        <v>-1.908853</v>
+        <v>1.646862</v>
       </c>
       <c r="X29" t="n">
-        <v>1.646862</v>
+        <v>2.824206</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.824206</v>
+        <v>0.897764</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.897764</v>
+        <v>1.902378</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.902378</v>
+        <v>4.621114</v>
       </c>
       <c r="AB29" t="n">
-        <v>4.621114</v>
+        <v>-3.178284</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.178284</v>
+        <v>-0.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.706988</v>
+        <v>-0.001064</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.5</v>
+        <v>-0.001064</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.001064</v>
+        <v>-0.24</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.001064</v>
+        <v>-0.4</v>
       </c>
       <c r="AH29" t="n">
-        <v>-0.24</v>
+        <v>-0.13</v>
       </c>
       <c r="AI29" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="AK29" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3695,96 +3539,90 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>0.57</v>
+        <v>104.473</v>
       </c>
       <c r="H30" t="n">
-        <v>104.473</v>
+        <v>99.29718</v>
       </c>
       <c r="I30" t="n">
-        <v>99.29718</v>
+        <v>4.9535</v>
       </c>
       <c r="J30" t="n">
-        <v>4.9535</v>
+        <v>4.9529</v>
       </c>
       <c r="K30" t="n">
-        <v>4.9529</v>
+        <v>5794707</v>
       </c>
       <c r="L30" t="n">
-        <v>5794707</v>
+        <v>2234362</v>
       </c>
       <c r="M30" t="n">
-        <v>2234362</v>
+        <v>3560345</v>
       </c>
       <c r="N30" t="n">
-        <v>3560345</v>
+        <v>3.38</v>
       </c>
       <c r="O30" t="n">
-        <v>3.38</v>
+        <v>2.77</v>
       </c>
       <c r="P30" t="n">
-        <v>2.77</v>
+        <v>3.76</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.76</v>
+        <v>28</v>
       </c>
       <c r="R30" t="n">
-        <v>28</v>
+        <v>355066</v>
       </c>
       <c r="S30" t="n">
-        <v>355066</v>
+        <v>-0.395831</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.395831</v>
+        <v>-2.347954</v>
       </c>
       <c r="U30" t="n">
-        <v>-2.347954</v>
+        <v>2.317559</v>
       </c>
       <c r="V30" t="n">
-        <v>2.317559</v>
+        <v>2.317847</v>
       </c>
       <c r="W30" t="n">
-        <v>2.317847</v>
+        <v>-0.180012</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.180012</v>
+        <v>-2.151229</v>
       </c>
       <c r="Y30" t="n">
-        <v>-2.151229</v>
+        <v>1.098143</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.098143</v>
+        <v>0.009013</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.009013</v>
+        <v>4.506637</v>
       </c>
       <c r="AB30" t="n">
-        <v>4.506637</v>
+        <v>-3.31355</v>
       </c>
       <c r="AC30" t="n">
-        <v>-3.31355</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.820543</v>
+        <v>-0.000798</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>-0.000798</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.000798</v>
+        <v>0.09</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.000798</v>
+        <v>0.18</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK30" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -3808,96 +3646,90 @@
         <v>-0.52</v>
       </c>
       <c r="G31" t="n">
-        <v>0.8100000000000001</v>
+        <v>104.65885</v>
       </c>
       <c r="H31" t="n">
-        <v>104.65885</v>
+        <v>102.15036</v>
       </c>
       <c r="I31" t="n">
-        <v>102.15036</v>
+        <v>4.9833</v>
       </c>
       <c r="J31" t="n">
-        <v>4.9833</v>
+        <v>4.9827</v>
       </c>
       <c r="K31" t="n">
-        <v>4.9827</v>
+        <v>5815954</v>
       </c>
       <c r="L31" t="n">
-        <v>5815954</v>
+        <v>2235302</v>
       </c>
       <c r="M31" t="n">
-        <v>2235302</v>
+        <v>3580652</v>
       </c>
       <c r="N31" t="n">
-        <v>3580652</v>
+        <v>3.38</v>
       </c>
       <c r="O31" t="n">
-        <v>3.38</v>
+        <v>2.76</v>
       </c>
       <c r="P31" t="n">
-        <v>2.76</v>
+        <v>3.76</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.76</v>
+        <v>27.85</v>
       </c>
       <c r="R31" t="n">
-        <v>27.85</v>
+        <v>352705</v>
       </c>
       <c r="S31" t="n">
-        <v>352705</v>
+        <v>0.177893</v>
       </c>
       <c r="T31" t="n">
-        <v>0.177893</v>
+        <v>2.873375</v>
       </c>
       <c r="U31" t="n">
-        <v>2.873375</v>
+        <v>0.601595</v>
       </c>
       <c r="V31" t="n">
-        <v>0.601595</v>
+        <v>0.601668</v>
       </c>
       <c r="W31" t="n">
-        <v>0.601668</v>
+        <v>0.366662</v>
       </c>
       <c r="X31" t="n">
-        <v>0.366662</v>
+        <v>0.04207</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.04207</v>
+        <v>0.570366</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.570366</v>
+        <v>-0.664947</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.664947</v>
+        <v>4.496274</v>
       </c>
       <c r="AB31" t="n">
-        <v>4.496274</v>
+        <v>-3.758575</v>
       </c>
       <c r="AC31" t="n">
-        <v>-3.758575</v>
+        <v>-0.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.861754</v>
+        <v>-0.001782</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.5</v>
+        <v>-0.001782</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.001782</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.001782</v>
+        <v>-0.01</v>
       </c>
       <c r="AH31" t="n">
         <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -3921,96 +3753,90 @@
         <v>-0.47</v>
       </c>
       <c r="G32" t="n">
-        <v>0.19</v>
+        <v>104.6738</v>
       </c>
       <c r="H32" t="n">
-        <v>104.6738</v>
+        <v>109.56901</v>
       </c>
       <c r="I32" t="n">
-        <v>109.56901</v>
+        <v>4.9962</v>
       </c>
       <c r="J32" t="n">
-        <v>4.9962</v>
+        <v>4.9956</v>
       </c>
       <c r="K32" t="n">
-        <v>4.9956</v>
+        <v>5899742</v>
       </c>
       <c r="L32" t="n">
-        <v>5899742</v>
+        <v>2285775</v>
       </c>
       <c r="M32" t="n">
-        <v>2285775</v>
+        <v>3613967</v>
       </c>
       <c r="N32" t="n">
-        <v>3613967</v>
+        <v>3.33</v>
       </c>
       <c r="O32" t="n">
-        <v>3.33</v>
+        <v>2.71</v>
       </c>
       <c r="P32" t="n">
-        <v>2.71</v>
+        <v>3.71</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.71</v>
+        <v>28.14</v>
       </c>
       <c r="R32" t="n">
-        <v>28.14</v>
+        <v>355008</v>
       </c>
       <c r="S32" t="n">
-        <v>355008</v>
+        <v>0.014285</v>
       </c>
       <c r="T32" t="n">
-        <v>0.014285</v>
+        <v>7.262481</v>
       </c>
       <c r="U32" t="n">
-        <v>7.262481</v>
+        <v>0.258865</v>
       </c>
       <c r="V32" t="n">
-        <v>0.258865</v>
+        <v>0.258896</v>
       </c>
       <c r="W32" t="n">
-        <v>0.258896</v>
+        <v>1.440658</v>
       </c>
       <c r="X32" t="n">
-        <v>1.440658</v>
+        <v>2.257995</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.257995</v>
+        <v>0.930417</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.930417</v>
+        <v>0.652954</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.652954</v>
+        <v>3.925596</v>
       </c>
       <c r="AB32" t="n">
-        <v>3.925596</v>
+        <v>-4.25878</v>
       </c>
       <c r="AC32" t="n">
-        <v>-4.25878</v>
+        <v>-0.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.397348</v>
+        <v>-0.000537</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.5</v>
+        <v>-0.000537</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="AH32" t="n">
         <v>-0.05</v>
       </c>
       <c r="AI32" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AK32" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -4034,96 +3860,90 @@
         <v>0.31</v>
       </c>
       <c r="G33" t="n">
-        <v>0.37</v>
+        <v>104.62771</v>
       </c>
       <c r="H33" t="n">
-        <v>104.62771</v>
+        <v>109.2572</v>
       </c>
       <c r="I33" t="n">
-        <v>109.2572</v>
+        <v>5.1718</v>
       </c>
       <c r="J33" t="n">
-        <v>5.1718</v>
+        <v>5.1712</v>
       </c>
       <c r="K33" t="n">
-        <v>5.1712</v>
+        <v>5915538</v>
       </c>
       <c r="L33" t="n">
-        <v>5915538</v>
+        <v>2268879</v>
       </c>
       <c r="M33" t="n">
-        <v>2268879</v>
+        <v>3646659</v>
       </c>
       <c r="N33" t="n">
-        <v>3646659</v>
+        <v>3.37</v>
       </c>
       <c r="O33" t="n">
-        <v>3.37</v>
+        <v>2.76</v>
       </c>
       <c r="P33" t="n">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.75</v>
+        <v>27.86</v>
       </c>
       <c r="R33" t="n">
-        <v>27.86</v>
+        <v>351599</v>
       </c>
       <c r="S33" t="n">
-        <v>351599</v>
+        <v>-0.044032</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.044032</v>
+        <v>-0.284579</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.284579</v>
+        <v>3.514671</v>
       </c>
       <c r="V33" t="n">
-        <v>3.514671</v>
+        <v>3.515093</v>
       </c>
       <c r="W33" t="n">
-        <v>3.515093</v>
+        <v>0.267741</v>
       </c>
       <c r="X33" t="n">
-        <v>0.267741</v>
+        <v>-0.7391799999999999</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.7391799999999999</v>
+        <v>0.904602</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.904602</v>
+        <v>-0.96026</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.96026</v>
+        <v>3.688016</v>
       </c>
       <c r="AB33" t="n">
-        <v>3.688016</v>
+        <v>-3.040871</v>
       </c>
       <c r="AC33" t="n">
-        <v>-3.040871</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.232784</v>
+        <v>-0.001252</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>-0.001252</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.001252</v>
+        <v>0.04</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.001252</v>
+        <v>0.05</v>
       </c>
       <c r="AH33" t="n">
         <v>0.04</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK33" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -4147,96 +3967,90 @@
         <v>0.89</v>
       </c>
       <c r="G34" t="n">
-        <v>0.46</v>
+        <v>105.60427</v>
       </c>
       <c r="H34" t="n">
-        <v>105.60427</v>
+        <v>104.71213</v>
       </c>
       <c r="I34" t="n">
-        <v>104.71213</v>
+        <v>5.2416</v>
       </c>
       <c r="J34" t="n">
-        <v>5.2416</v>
+        <v>5.241</v>
       </c>
       <c r="K34" t="n">
-        <v>5.241</v>
+        <v>5953960</v>
       </c>
       <c r="L34" t="n">
-        <v>5953960</v>
+        <v>2278309</v>
       </c>
       <c r="M34" t="n">
-        <v>2278309</v>
+        <v>3675652</v>
       </c>
       <c r="N34" t="n">
-        <v>3675652</v>
+        <v>3.43</v>
       </c>
       <c r="O34" t="n">
-        <v>3.43</v>
+        <v>2.8</v>
       </c>
       <c r="P34" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.82</v>
+        <v>27.75</v>
       </c>
       <c r="R34" t="n">
-        <v>27.75</v>
+        <v>355560</v>
       </c>
       <c r="S34" t="n">
-        <v>355560</v>
+        <v>0.9333669999999999</v>
       </c>
       <c r="T34" t="n">
-        <v>0.9333669999999999</v>
+        <v>-4.159973</v>
       </c>
       <c r="U34" t="n">
-        <v>-4.159973</v>
+        <v>1.349627</v>
       </c>
       <c r="V34" t="n">
-        <v>1.349627</v>
+        <v>1.349783</v>
       </c>
       <c r="W34" t="n">
-        <v>1.349783</v>
+        <v>0.64951</v>
       </c>
       <c r="X34" t="n">
-        <v>0.64951</v>
+        <v>0.415624</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.415624</v>
+        <v>0.795057</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.795057</v>
+        <v>1.126567</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.126567</v>
+        <v>3.925952</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.925952</v>
+        <v>-0.344269</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.344269</v>
+        <v>-0.25</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.335647</v>
+        <v>-0.000684</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.25</v>
+        <v>-0.000684</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.000684</v>
+        <v>0.06</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.000684</v>
+        <v>0.04</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK34" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -4260,96 +4074,90 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>0.25</v>
+        <v>106.5891</v>
       </c>
       <c r="H35" t="n">
-        <v>106.5891</v>
+        <v>105.86915</v>
       </c>
       <c r="I35" t="n">
-        <v>105.86915</v>
+        <v>5.5589</v>
       </c>
       <c r="J35" t="n">
-        <v>5.5589</v>
+        <v>5.5583</v>
       </c>
       <c r="K35" t="n">
-        <v>5.5583</v>
+        <v>6041898</v>
       </c>
       <c r="L35" t="n">
-        <v>6041898</v>
+        <v>2336858</v>
       </c>
       <c r="M35" t="n">
-        <v>2336858</v>
+        <v>3705041</v>
       </c>
       <c r="N35" t="n">
-        <v>3705041</v>
+        <v>3.29</v>
       </c>
       <c r="O35" t="n">
-        <v>3.29</v>
+        <v>2.64</v>
       </c>
       <c r="P35" t="n">
-        <v>2.64</v>
+        <v>3.71</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.71</v>
+        <v>27.81</v>
       </c>
       <c r="R35" t="n">
-        <v>27.81</v>
+        <v>357827</v>
       </c>
       <c r="S35" t="n">
-        <v>357827</v>
+        <v>0.932566</v>
       </c>
       <c r="T35" t="n">
-        <v>0.932566</v>
+        <v>1.104953</v>
       </c>
       <c r="U35" t="n">
-        <v>1.104953</v>
+        <v>6.053495</v>
       </c>
       <c r="V35" t="n">
-        <v>6.053495</v>
+        <v>6.054188</v>
       </c>
       <c r="W35" t="n">
-        <v>6.054188</v>
+        <v>1.476967</v>
       </c>
       <c r="X35" t="n">
-        <v>1.476967</v>
+        <v>2.569845</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.569845</v>
+        <v>0.799559</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.799559</v>
+        <v>0.637586</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.637586</v>
+        <v>4.227578</v>
       </c>
       <c r="AB35" t="n">
-        <v>4.227578</v>
+        <v>2.440035</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.440035</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.697684</v>
+        <v>-0.000214</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>-0.000214</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.000214</v>
+        <v>-0.14</v>
       </c>
       <c r="AG35" t="n">
-        <v>-0.000214</v>
+        <v>-0.16</v>
       </c>
       <c r="AH35" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="AI35" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="AK35" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -4373,96 +4181,90 @@
         <v>0.61</v>
       </c>
       <c r="G36" t="n">
-        <v>0.26</v>
+        <v>107.06237</v>
       </c>
       <c r="H36" t="n">
-        <v>107.06237</v>
+        <v>111.509</v>
       </c>
       <c r="I36" t="n">
-        <v>111.509</v>
+        <v>5.6621</v>
       </c>
       <c r="J36" t="n">
-        <v>5.6621</v>
+        <v>5.6615</v>
       </c>
       <c r="K36" t="n">
-        <v>5.6615</v>
+        <v>6069205</v>
       </c>
       <c r="L36" t="n">
-        <v>6069205</v>
+        <v>2323362</v>
       </c>
       <c r="M36" t="n">
-        <v>2323362</v>
+        <v>3745844</v>
       </c>
       <c r="N36" t="n">
-        <v>3745844</v>
+        <v>3.3</v>
       </c>
       <c r="O36" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="P36" t="n">
-        <v>2.52</v>
+        <v>3.78</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.78</v>
+        <v>27.74</v>
       </c>
       <c r="R36" t="n">
-        <v>27.74</v>
+        <v>363282</v>
       </c>
       <c r="S36" t="n">
-        <v>363282</v>
+        <v>0.444014</v>
       </c>
       <c r="T36" t="n">
-        <v>0.444014</v>
+        <v>5.327189</v>
       </c>
       <c r="U36" t="n">
-        <v>5.327189</v>
+        <v>1.856482</v>
       </c>
       <c r="V36" t="n">
-        <v>1.856482</v>
+        <v>1.856683</v>
       </c>
       <c r="W36" t="n">
-        <v>1.856683</v>
+        <v>0.451961</v>
       </c>
       <c r="X36" t="n">
-        <v>0.451961</v>
+        <v>-0.577528</v>
       </c>
       <c r="Y36" t="n">
-        <v>-0.577528</v>
+        <v>1.101283</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.101283</v>
+        <v>1.52448</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.52448</v>
+        <v>4.498245</v>
       </c>
       <c r="AB36" t="n">
-        <v>4.498245</v>
+        <v>3.812368</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.812368</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>4.060953</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI36" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK36" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -4486,96 +4288,90 @@
         <v>0.29</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.14</v>
+        <v>107.19174</v>
       </c>
       <c r="H37" t="n">
-        <v>107.19174</v>
+        <v>110.06254</v>
       </c>
       <c r="I37" t="n">
-        <v>110.06254</v>
+        <v>5.6562</v>
       </c>
       <c r="J37" t="n">
-        <v>5.6562</v>
+        <v>5.6556</v>
       </c>
       <c r="K37" t="n">
-        <v>5.6556</v>
+        <v>6135298</v>
       </c>
       <c r="L37" t="n">
-        <v>6135298</v>
+        <v>2344397</v>
       </c>
       <c r="M37" t="n">
-        <v>2344397</v>
+        <v>3790900</v>
       </c>
       <c r="N37" t="n">
-        <v>3790900</v>
+        <v>3.33</v>
       </c>
       <c r="O37" t="n">
-        <v>3.33</v>
+        <v>2.55</v>
       </c>
       <c r="P37" t="n">
-        <v>2.55</v>
+        <v>3.82</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.82</v>
+        <v>27.59</v>
       </c>
       <c r="R37" t="n">
-        <v>27.59</v>
+        <v>369214</v>
       </c>
       <c r="S37" t="n">
-        <v>369214</v>
+        <v>0.120836</v>
       </c>
       <c r="T37" t="n">
-        <v>0.120836</v>
+        <v>-1.297169</v>
       </c>
       <c r="U37" t="n">
-        <v>-1.297169</v>
+        <v>-0.104202</v>
       </c>
       <c r="V37" t="n">
-        <v>-0.104202</v>
+        <v>-0.104213</v>
       </c>
       <c r="W37" t="n">
-        <v>-0.104213</v>
+        <v>1.088989</v>
       </c>
       <c r="X37" t="n">
-        <v>1.088989</v>
+        <v>0.905369</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.905369</v>
+        <v>1.202826</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.202826</v>
+        <v>1.632891</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.632891</v>
+        <v>4.237599</v>
       </c>
       <c r="AB37" t="n">
-        <v>4.237599</v>
+        <v>4.259387</v>
       </c>
       <c r="AC37" t="n">
-        <v>4.259387</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.707852</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK37" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4599,96 +4395,90 @@
         <v>0.62</v>
       </c>
       <c r="G38" t="n">
-        <v>0.48</v>
+        <v>108.04382</v>
       </c>
       <c r="H38" t="n">
-        <v>108.04382</v>
+        <v>107.07852</v>
       </c>
       <c r="I38" t="n">
-        <v>107.07852</v>
+        <v>5.4481</v>
       </c>
       <c r="J38" t="n">
-        <v>5.4481</v>
+        <v>5.4475</v>
       </c>
       <c r="K38" t="n">
-        <v>5.4475</v>
+        <v>6216528</v>
       </c>
       <c r="L38" t="n">
-        <v>6216528</v>
+        <v>2384828</v>
       </c>
       <c r="M38" t="n">
-        <v>2384828</v>
+        <v>3831700</v>
       </c>
       <c r="N38" t="n">
-        <v>3831700</v>
+        <v>3.34</v>
       </c>
       <c r="O38" t="n">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="P38" t="n">
-        <v>2.56</v>
+        <v>3.83</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.83</v>
+        <v>27.49</v>
       </c>
       <c r="R38" t="n">
-        <v>27.49</v>
+        <v>372016</v>
       </c>
       <c r="S38" t="n">
-        <v>372016</v>
+        <v>0.794912</v>
       </c>
       <c r="T38" t="n">
-        <v>0.794912</v>
+        <v>-2.711204</v>
       </c>
       <c r="U38" t="n">
-        <v>-2.711204</v>
+        <v>-3.679149</v>
       </c>
       <c r="V38" t="n">
-        <v>-3.679149</v>
+        <v>-3.679539</v>
       </c>
       <c r="W38" t="n">
-        <v>-3.679539</v>
+        <v>1.323978</v>
       </c>
       <c r="X38" t="n">
-        <v>1.323978</v>
+        <v>1.72458</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.72458</v>
+        <v>1.076262</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.076262</v>
+        <v>0.7589089999999999</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.7589089999999999</v>
+        <v>4.42474</v>
       </c>
       <c r="AB38" t="n">
-        <v>4.42474</v>
+        <v>4.519075</v>
       </c>
       <c r="AC38" t="n">
-        <v>4.519075</v>
+        <v>0.25</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.091149</v>
+        <v>0.000342</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.25</v>
+        <v>0.000342</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="AH38" t="n">
         <v>0.01</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK38" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -4712,96 +4502,90 @@
         <v>1.52</v>
       </c>
       <c r="G39" t="n">
-        <v>0.61</v>
+        <v>108.2446</v>
       </c>
       <c r="H39" t="n">
-        <v>108.2446</v>
+        <v>109.18379</v>
       </c>
       <c r="I39" t="n">
-        <v>109.18379</v>
+        <v>5.7779</v>
       </c>
       <c r="J39" t="n">
-        <v>5.7779</v>
+        <v>5.7773</v>
       </c>
       <c r="K39" t="n">
-        <v>5.7773</v>
+        <v>6275117</v>
       </c>
       <c r="L39" t="n">
-        <v>6275117</v>
+        <v>2397533</v>
       </c>
       <c r="M39" t="n">
-        <v>2397533</v>
+        <v>3877584</v>
       </c>
       <c r="N39" t="n">
-        <v>3877584</v>
+        <v>3.3</v>
       </c>
       <c r="O39" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="P39" t="n">
-        <v>2.52</v>
+        <v>3.79</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.79</v>
+        <v>27.94</v>
       </c>
       <c r="R39" t="n">
-        <v>27.94</v>
+        <v>366096</v>
       </c>
       <c r="S39" t="n">
-        <v>366096</v>
+        <v>0.185832</v>
       </c>
       <c r="T39" t="n">
-        <v>0.185832</v>
+        <v>1.966099</v>
       </c>
       <c r="U39" t="n">
-        <v>1.966099</v>
+        <v>6.053487</v>
       </c>
       <c r="V39" t="n">
-        <v>6.053487</v>
+        <v>6.054153</v>
       </c>
       <c r="W39" t="n">
-        <v>6.054153</v>
+        <v>0.9424709999999999</v>
       </c>
       <c r="X39" t="n">
-        <v>0.9424709999999999</v>
+        <v>0.532743</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.532743</v>
+        <v>1.197484</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.197484</v>
+        <v>-1.591329</v>
       </c>
       <c r="AA39" t="n">
-        <v>-1.591329</v>
+        <v>4.758099</v>
       </c>
       <c r="AB39" t="n">
-        <v>4.758099</v>
+        <v>5.579866</v>
       </c>
       <c r="AC39" t="n">
-        <v>5.579866</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>4.600584</v>
+        <v>0.000556</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>0.000556</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="AH39" t="n">
         <v>-0.04</v>
       </c>
       <c r="AI39" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AK39" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -4825,96 +4609,90 @@
         <v>1.3</v>
       </c>
       <c r="G40" t="n">
-        <v>0.33</v>
+        <v>108.00109</v>
       </c>
       <c r="H40" t="n">
-        <v>108.00109</v>
+        <v>105.49006</v>
       </c>
       <c r="I40" t="n">
-        <v>105.49006</v>
+        <v>6.0535</v>
       </c>
       <c r="J40" t="n">
-        <v>6.0535</v>
+        <v>6.0529</v>
       </c>
       <c r="K40" t="n">
-        <v>6.0529</v>
+        <v>6365690</v>
       </c>
       <c r="L40" t="n">
-        <v>6365690</v>
+        <v>2436022</v>
       </c>
       <c r="M40" t="n">
-        <v>2436022</v>
+        <v>3929668</v>
       </c>
       <c r="N40" t="n">
-        <v>3929668</v>
+        <v>3.27</v>
       </c>
       <c r="O40" t="n">
-        <v>3.27</v>
+        <v>2.5</v>
       </c>
       <c r="P40" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.75</v>
+        <v>28.45</v>
       </c>
       <c r="R40" t="n">
-        <v>28.45</v>
+        <v>363003</v>
       </c>
       <c r="S40" t="n">
-        <v>363003</v>
+        <v>-0.224963</v>
       </c>
       <c r="T40" t="n">
-        <v>-0.224963</v>
+        <v>-3.383039</v>
       </c>
       <c r="U40" t="n">
-        <v>-3.383039</v>
+        <v>4.769899</v>
       </c>
       <c r="V40" t="n">
-        <v>4.769899</v>
+        <v>4.770394</v>
       </c>
       <c r="W40" t="n">
-        <v>4.770394</v>
+        <v>1.443368</v>
       </c>
       <c r="X40" t="n">
-        <v>1.443368</v>
+        <v>1.605359</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.605359</v>
+        <v>1.343208</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.343208</v>
+        <v>-0.8448600000000001</v>
       </c>
       <c r="AA40" t="n">
-        <v>-0.8448600000000001</v>
+        <v>4.873011</v>
       </c>
       <c r="AB40" t="n">
-        <v>4.873011</v>
+        <v>6.325086</v>
       </c>
       <c r="AC40" t="n">
-        <v>6.325086</v>
+        <v>0.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.840925</v>
+        <v>0.001412</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.5</v>
+        <v>0.001412</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.001412</v>
+        <v>-0.03</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.001412</v>
+        <v>-0.02</v>
       </c>
       <c r="AH40" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="AI40" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AK40" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4938,96 +4716,90 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>0.48</v>
+        <v>107.37012</v>
       </c>
       <c r="H41" t="n">
-        <v>107.37012</v>
+        <v>104.15552</v>
       </c>
       <c r="I41" t="n">
-        <v>104.15552</v>
+        <v>6.1923</v>
       </c>
       <c r="J41" t="n">
-        <v>6.1923</v>
+        <v>6.1917</v>
       </c>
       <c r="K41" t="n">
-        <v>6.1917</v>
+        <v>6464602</v>
       </c>
       <c r="L41" t="n">
-        <v>6464602</v>
+        <v>2499177</v>
       </c>
       <c r="M41" t="n">
-        <v>2499177</v>
+        <v>3965425</v>
       </c>
       <c r="N41" t="n">
-        <v>3965425</v>
+        <v>3.08</v>
       </c>
       <c r="O41" t="n">
-        <v>3.08</v>
+        <v>2.21</v>
       </c>
       <c r="P41" t="n">
-        <v>2.21</v>
+        <v>3.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.63</v>
+        <v>28.5</v>
       </c>
       <c r="R41" t="n">
-        <v>28.5</v>
+        <v>329730</v>
       </c>
       <c r="S41" t="n">
-        <v>329730</v>
+        <v>-0.584226</v>
       </c>
       <c r="T41" t="n">
-        <v>-0.584226</v>
+        <v>-1.265086</v>
       </c>
       <c r="U41" t="n">
-        <v>-1.265086</v>
+        <v>2.292888</v>
       </c>
       <c r="V41" t="n">
-        <v>2.292888</v>
+        <v>2.293116</v>
       </c>
       <c r="W41" t="n">
-        <v>2.293116</v>
+        <v>1.55383</v>
       </c>
       <c r="X41" t="n">
-        <v>1.55383</v>
+        <v>2.592546</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.592546</v>
+        <v>0.909924</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.909924</v>
+        <v>-9.166040000000001</v>
       </c>
       <c r="AA41" t="n">
-        <v>-9.166040000000001</v>
+        <v>4.831296</v>
       </c>
       <c r="AB41" t="n">
-        <v>4.831296</v>
+        <v>6.536174</v>
       </c>
       <c r="AC41" t="n">
-        <v>6.536174</v>
+        <v>1</v>
       </c>
       <c r="AD41" t="n">
-        <v>4.767938</v>
+        <v>0.002578</v>
       </c>
       <c r="AE41" t="n">
-        <v>1</v>
+        <v>0.002578</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.002578</v>
+        <v>-0.19</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.002578</v>
+        <v>-0.29</v>
       </c>
       <c r="AH41" t="n">
-        <v>-0.19</v>
+        <v>-0.12</v>
       </c>
       <c r="AI41" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK41" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -5051,96 +4823,90 @@
         <v>0.27</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>108.09524</v>
       </c>
       <c r="H42" t="n">
-        <v>108.09524</v>
+        <v>102.62949</v>
       </c>
       <c r="I42" t="n">
-        <v>102.62949</v>
+        <v>5.8301</v>
       </c>
       <c r="J42" t="n">
-        <v>5.8301</v>
+        <v>5.8295</v>
       </c>
       <c r="K42" t="n">
-        <v>5.8295</v>
+        <v>6465016</v>
       </c>
       <c r="L42" t="n">
-        <v>6465016</v>
+        <v>2451957</v>
       </c>
       <c r="M42" t="n">
-        <v>2451957</v>
+        <v>4013059</v>
       </c>
       <c r="N42" t="n">
-        <v>4013059</v>
+        <v>3.34</v>
       </c>
       <c r="O42" t="n">
-        <v>3.34</v>
+        <v>2.43</v>
       </c>
       <c r="P42" t="n">
-        <v>2.43</v>
+        <v>3.89</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.89</v>
+        <v>29.88</v>
       </c>
       <c r="R42" t="n">
-        <v>29.88</v>
+        <v>328303</v>
       </c>
       <c r="S42" t="n">
-        <v>328303</v>
+        <v>0.675346</v>
       </c>
       <c r="T42" t="n">
-        <v>0.675346</v>
+        <v>-1.465146</v>
       </c>
       <c r="U42" t="n">
-        <v>-1.465146</v>
+        <v>-5.8492</v>
       </c>
       <c r="V42" t="n">
-        <v>-5.8492</v>
+        <v>-5.849767</v>
       </c>
       <c r="W42" t="n">
-        <v>-5.849767</v>
+        <v>0.006404</v>
       </c>
       <c r="X42" t="n">
-        <v>0.006404</v>
+        <v>-1.889422</v>
       </c>
       <c r="Y42" t="n">
-        <v>-1.889422</v>
+        <v>1.201233</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.201233</v>
+        <v>-0.432778</v>
       </c>
       <c r="AA42" t="n">
-        <v>-0.432778</v>
+        <v>4.559874</v>
       </c>
       <c r="AB42" t="n">
-        <v>4.559874</v>
+        <v>6.749097</v>
       </c>
       <c r="AC42" t="n">
-        <v>6.749097</v>
+        <v>1</v>
       </c>
       <c r="AD42" t="n">
-        <v>4.174145</v>
+        <v>0.001675</v>
       </c>
       <c r="AE42" t="n">
-        <v>1</v>
+        <v>0.001675</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.001675</v>
+        <v>0.26</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.001675</v>
+        <v>0.22</v>
       </c>
       <c r="AH42" t="n">
         <v>0.26</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK42" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -5164,96 +4930,90 @@
         <v>1.06</v>
       </c>
       <c r="G43" t="n">
-        <v>1.48</v>
+        <v>108.62006</v>
       </c>
       <c r="H43" t="n">
-        <v>108.62006</v>
+        <v>106.82599</v>
       </c>
       <c r="I43" t="n">
-        <v>106.82599</v>
+        <v>5.8488</v>
       </c>
       <c r="J43" t="n">
-        <v>5.8488</v>
+        <v>5.8482</v>
       </c>
       <c r="K43" t="n">
-        <v>5.8482</v>
+        <v>6511444</v>
       </c>
       <c r="L43" t="n">
-        <v>6511444</v>
+        <v>2477151</v>
       </c>
       <c r="M43" t="n">
-        <v>2477151</v>
+        <v>4034293</v>
       </c>
       <c r="N43" t="n">
-        <v>4034293</v>
+        <v>3.41</v>
       </c>
       <c r="O43" t="n">
-        <v>3.41</v>
+        <v>2.52</v>
       </c>
       <c r="P43" t="n">
-        <v>2.52</v>
+        <v>3.96</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.96</v>
+        <v>30.53</v>
       </c>
       <c r="R43" t="n">
-        <v>30.53</v>
+        <v>332508</v>
       </c>
       <c r="S43" t="n">
-        <v>332508</v>
+        <v>0.485516</v>
       </c>
       <c r="T43" t="n">
-        <v>0.485516</v>
+        <v>4.088981</v>
       </c>
       <c r="U43" t="n">
-        <v>4.088981</v>
+        <v>0.320749</v>
       </c>
       <c r="V43" t="n">
-        <v>0.320749</v>
+        <v>0.320782</v>
       </c>
       <c r="W43" t="n">
-        <v>0.320782</v>
+        <v>0.7181419999999999</v>
       </c>
       <c r="X43" t="n">
-        <v>0.7181419999999999</v>
+        <v>1.027506</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.027506</v>
+        <v>0.529123</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.529123</v>
+        <v>1.280829</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.280829</v>
+        <v>5.05763</v>
       </c>
       <c r="AB43" t="n">
-        <v>5.05763</v>
+        <v>8.444549</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.444549</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>4.866504</v>
+        <v>0.003204</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>0.003204</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.003204</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.003204</v>
+        <v>0.09</v>
       </c>
       <c r="AH43" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK43" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -5277,96 +5037,90 @@
         <v>-0.34</v>
       </c>
       <c r="G44" t="n">
-        <v>0.51</v>
+        <v>110.03287</v>
       </c>
       <c r="H44" t="n">
-        <v>110.03287</v>
+        <v>114.02067</v>
       </c>
       <c r="I44" t="n">
-        <v>114.02067</v>
+        <v>5.7422</v>
       </c>
       <c r="J44" t="n">
-        <v>5.7422</v>
+        <v>5.7416</v>
       </c>
       <c r="K44" t="n">
-        <v>5.7416</v>
+        <v>6576464</v>
       </c>
       <c r="L44" t="n">
-        <v>6576464</v>
+        <v>2498262</v>
       </c>
       <c r="M44" t="n">
-        <v>2498262</v>
+        <v>4078202</v>
       </c>
       <c r="N44" t="n">
-        <v>4078202</v>
+        <v>3.44</v>
       </c>
       <c r="O44" t="n">
-        <v>3.44</v>
+        <v>2.49</v>
       </c>
       <c r="P44" t="n">
-        <v>2.49</v>
+        <v>4.03</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.03</v>
+        <v>31.34</v>
       </c>
       <c r="R44" t="n">
-        <v>31.34</v>
+        <v>336157</v>
       </c>
       <c r="S44" t="n">
-        <v>336157</v>
+        <v>1.30069</v>
       </c>
       <c r="T44" t="n">
-        <v>1.30069</v>
+        <v>6.734953</v>
       </c>
       <c r="U44" t="n">
-        <v>6.734953</v>
+        <v>-1.822596</v>
       </c>
       <c r="V44" t="n">
-        <v>-1.822596</v>
+        <v>-1.822783</v>
       </c>
       <c r="W44" t="n">
-        <v>-1.822783</v>
+        <v>0.99855</v>
       </c>
       <c r="X44" t="n">
-        <v>0.99855</v>
+        <v>0.852229</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.852229</v>
+        <v>1.088394</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.088394</v>
+        <v>1.097417</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.097417</v>
+        <v>5.47719</v>
       </c>
       <c r="AB44" t="n">
-        <v>5.47719</v>
+        <v>8.586193</v>
       </c>
       <c r="AC44" t="n">
-        <v>8.586193</v>
+        <v>1</v>
       </c>
       <c r="AD44" t="n">
-        <v>5.201441</v>
+        <v>0.001471</v>
       </c>
       <c r="AE44" t="n">
-        <v>1</v>
+        <v>0.001471</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.001471</v>
+        <v>0.03</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.001471</v>
+        <v>-0.03</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI44" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK44" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -5390,96 +5144,90 @@
         <v>0.24</v>
       </c>
       <c r="G45" t="n">
-        <v>0.48</v>
+        <v>109.52766</v>
       </c>
       <c r="H45" t="n">
-        <v>109.52766</v>
+        <v>112.59512</v>
       </c>
       <c r="I45" t="n">
-        <v>112.59512</v>
+        <v>5.6608</v>
       </c>
       <c r="J45" t="n">
-        <v>5.6608</v>
+        <v>5.6602</v>
       </c>
       <c r="K45" t="n">
-        <v>5.6602</v>
+        <v>6623948</v>
       </c>
       <c r="L45" t="n">
-        <v>6623948</v>
+        <v>2512426</v>
       </c>
       <c r="M45" t="n">
-        <v>2512426</v>
+        <v>4111522</v>
       </c>
       <c r="N45" t="n">
-        <v>4111522</v>
+        <v>3.67</v>
       </c>
       <c r="O45" t="n">
-        <v>3.67</v>
+        <v>2.72</v>
       </c>
       <c r="P45" t="n">
-        <v>2.72</v>
+        <v>4.25</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.25</v>
+        <v>31.63</v>
       </c>
       <c r="R45" t="n">
-        <v>31.63</v>
+        <v>340789</v>
       </c>
       <c r="S45" t="n">
-        <v>340789</v>
+        <v>-0.459145</v>
       </c>
       <c r="T45" t="n">
-        <v>-0.459145</v>
+        <v>-1.250256</v>
       </c>
       <c r="U45" t="n">
-        <v>-1.250256</v>
+        <v>-1.417575</v>
       </c>
       <c r="V45" t="n">
-        <v>-1.417575</v>
+        <v>-1.417723</v>
       </c>
       <c r="W45" t="n">
-        <v>-1.417723</v>
+        <v>0.722029</v>
       </c>
       <c r="X45" t="n">
-        <v>0.722029</v>
+        <v>0.566954</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.566954</v>
+        <v>0.8170269999999999</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.8170269999999999</v>
+        <v>1.377928</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.377928</v>
+        <v>5.529729</v>
       </c>
       <c r="AB45" t="n">
-        <v>5.529729</v>
+        <v>8.510418</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.510418</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>5.316736</v>
+        <v>0.002023</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>0.002023</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AK45" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -5503,96 +5251,90 @@
         <v>-0.49</v>
       </c>
       <c r="G46" t="n">
-        <v>0.35</v>
+        <v>108.8862</v>
       </c>
       <c r="H46" t="n">
-        <v>108.8862</v>
+        <v>108.55704</v>
       </c>
       <c r="I46" t="n">
-        <v>108.55704</v>
+        <v>5.7087</v>
       </c>
       <c r="J46" t="n">
-        <v>5.7087</v>
+        <v>5.7081</v>
       </c>
       <c r="K46" t="n">
-        <v>5.7081</v>
+        <v>6666287</v>
       </c>
       <c r="L46" t="n">
-        <v>6666287</v>
+        <v>2532708</v>
       </c>
       <c r="M46" t="n">
-        <v>2532708</v>
+        <v>4133579</v>
       </c>
       <c r="N46" t="n">
-        <v>4133579</v>
+        <v>3.72</v>
       </c>
       <c r="O46" t="n">
-        <v>3.72</v>
+        <v>2.67</v>
       </c>
       <c r="P46" t="n">
-        <v>2.67</v>
+        <v>4.36</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.36</v>
+        <v>31.7</v>
       </c>
       <c r="R46" t="n">
-        <v>31.7</v>
+        <v>341459</v>
       </c>
       <c r="S46" t="n">
-        <v>341459</v>
+        <v>-0.58566</v>
       </c>
       <c r="T46" t="n">
-        <v>-0.58566</v>
+        <v>-3.586372</v>
       </c>
       <c r="U46" t="n">
-        <v>-3.586372</v>
+        <v>0.84617</v>
       </c>
       <c r="V46" t="n">
-        <v>0.84617</v>
+        <v>0.84626</v>
       </c>
       <c r="W46" t="n">
-        <v>0.84626</v>
+        <v>0.639181</v>
       </c>
       <c r="X46" t="n">
-        <v>0.639181</v>
+        <v>0.807268</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.807268</v>
+        <v>0.5364679999999999</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.5364679999999999</v>
+        <v>0.196603</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.196603</v>
+        <v>5.319636</v>
       </c>
       <c r="AB46" t="n">
-        <v>5.319636</v>
+        <v>7.026183</v>
       </c>
       <c r="AC46" t="n">
-        <v>7.026183</v>
+        <v>0.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>5.201418</v>
+        <v>0.001405</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.5</v>
+        <v>0.001405</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.001405</v>
+        <v>0.05</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.001405</v>
+        <v>-0.05</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="AI46" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK46" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5616,96 +5358,90 @@
         <v>-1.67</v>
       </c>
       <c r="G47" t="n">
-        <v>0.23</v>
+        <v>108.80376</v>
       </c>
       <c r="H47" t="n">
-        <v>108.80376</v>
+        <v>107.36219</v>
       </c>
       <c r="I47" t="n">
-        <v>107.36219</v>
+        <v>5.4571</v>
       </c>
       <c r="J47" t="n">
-        <v>5.4571</v>
+        <v>5.4565</v>
       </c>
       <c r="K47" t="n">
-        <v>5.4565</v>
+        <v>6703663</v>
       </c>
       <c r="L47" t="n">
-        <v>6703663</v>
+        <v>2547693</v>
       </c>
       <c r="M47" t="n">
-        <v>2547693</v>
+        <v>4155970</v>
       </c>
       <c r="N47" t="n">
-        <v>4155970</v>
+        <v>3.75</v>
       </c>
       <c r="O47" t="n">
-        <v>3.75</v>
+        <v>2.67</v>
       </c>
       <c r="P47" t="n">
-        <v>2.67</v>
+        <v>4.41</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.41</v>
+        <v>31.85</v>
       </c>
       <c r="R47" t="n">
-        <v>31.85</v>
+        <v>344440</v>
       </c>
       <c r="S47" t="n">
-        <v>344440</v>
+        <v>-0.075712</v>
       </c>
       <c r="T47" t="n">
-        <v>-0.075712</v>
+        <v>-1.100666</v>
       </c>
       <c r="U47" t="n">
-        <v>-1.100666</v>
+        <v>-4.407308</v>
       </c>
       <c r="V47" t="n">
-        <v>-4.407308</v>
+        <v>-4.407771</v>
       </c>
       <c r="W47" t="n">
-        <v>-4.407771</v>
+        <v>0.5606719999999999</v>
       </c>
       <c r="X47" t="n">
-        <v>0.5606719999999999</v>
+        <v>0.591659</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.591659</v>
+        <v>0.541686</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.541686</v>
+        <v>0.873018</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.873018</v>
+        <v>5.351165</v>
       </c>
       <c r="AB47" t="n">
-        <v>5.351165</v>
+        <v>4.393261</v>
       </c>
       <c r="AC47" t="n">
-        <v>4.393261</v>
+        <v>0.25</v>
       </c>
       <c r="AD47" t="n">
-        <v>5.18043</v>
+        <v>0.000633</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.25</v>
+        <v>0.000633</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.000633</v>
+        <v>0.03</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.000633</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK47" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5729,96 +5465,90 @@
         <v>-0.77</v>
       </c>
       <c r="G48" t="n">
+        <v>108.49869</v>
+      </c>
+      <c r="H48" t="n">
+        <v>113.10928</v>
+      </c>
+      <c r="I48" t="n">
+        <v>5.6021</v>
+      </c>
+      <c r="J48" t="n">
+        <v>5.6015</v>
+      </c>
+      <c r="K48" t="n">
+        <v>6733209</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2544400</v>
+      </c>
+      <c r="M48" t="n">
+        <v>4188808</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="O48" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="P48" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="R48" t="n">
+        <v>345111</v>
+      </c>
+      <c r="S48" t="n">
+        <v>-0.280386</v>
+      </c>
+      <c r="T48" t="n">
+        <v>5.352993</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2.657089</v>
+      </c>
+      <c r="V48" t="n">
+        <v>2.657381</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0.440744</v>
+      </c>
+      <c r="X48" t="n">
+        <v>-0.129254</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0.79014</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0.194809</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>5.225222</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>2.961368</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.000562</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0.000562</v>
+      </c>
+      <c r="AF48" t="n">
         <v>0.21</v>
       </c>
-      <c r="H48" t="n">
-        <v>108.49869</v>
-      </c>
-      <c r="I48" t="n">
-        <v>113.10928</v>
-      </c>
-      <c r="J48" t="n">
-        <v>5.6021</v>
-      </c>
-      <c r="K48" t="n">
-        <v>5.6015</v>
-      </c>
-      <c r="L48" t="n">
-        <v>6733209</v>
-      </c>
-      <c r="M48" t="n">
-        <v>2544400</v>
-      </c>
-      <c r="N48" t="n">
-        <v>4188808</v>
-      </c>
-      <c r="O48" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="R48" t="n">
-        <v>31.75</v>
-      </c>
-      <c r="S48" t="n">
-        <v>345111</v>
-      </c>
-      <c r="T48" t="n">
-        <v>-0.280386</v>
-      </c>
-      <c r="U48" t="n">
-        <v>5.352993</v>
-      </c>
-      <c r="V48" t="n">
-        <v>2.657089</v>
-      </c>
-      <c r="W48" t="n">
-        <v>2.657381</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0.440744</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>-0.129254</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0.79014</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0.194809</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>5.225222</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>2.961368</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>5.127976</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>0.000562</v>
-      </c>
       <c r="AG48" t="n">
-        <v>0.000562</v>
+        <v>0.12</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="AI48" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK48" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -5842,96 +5572,90 @@
         <v>0.36</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.21</v>
+        <v>108.82893</v>
       </c>
       <c r="H49" t="n">
-        <v>108.82893</v>
+        <v>110.38054</v>
       </c>
       <c r="I49" t="n">
-        <v>110.38054</v>
+        <v>5.4264</v>
       </c>
       <c r="J49" t="n">
-        <v>5.4264</v>
+        <v>5.4258</v>
       </c>
       <c r="K49" t="n">
-        <v>5.4258</v>
+        <v>6774436</v>
       </c>
       <c r="L49" t="n">
-        <v>6774436</v>
+        <v>2546265</v>
       </c>
       <c r="M49" t="n">
-        <v>2546265</v>
+        <v>4228171</v>
       </c>
       <c r="N49" t="n">
-        <v>4228171</v>
+        <v>4.14</v>
       </c>
       <c r="O49" t="n">
-        <v>4.14</v>
+        <v>2.85</v>
       </c>
       <c r="P49" t="n">
-        <v>2.85</v>
+        <v>4.92</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.92</v>
+        <v>31.87</v>
       </c>
       <c r="R49" t="n">
-        <v>31.87</v>
+        <v>350767</v>
       </c>
       <c r="S49" t="n">
-        <v>350767</v>
+        <v>0.304372</v>
       </c>
       <c r="T49" t="n">
-        <v>0.304372</v>
+        <v>-2.412481</v>
       </c>
       <c r="U49" t="n">
-        <v>-2.412481</v>
+        <v>-3.136324</v>
       </c>
       <c r="V49" t="n">
-        <v>-3.136324</v>
+        <v>-3.13666</v>
       </c>
       <c r="W49" t="n">
-        <v>-3.13666</v>
+        <v>0.612293</v>
       </c>
       <c r="X49" t="n">
-        <v>0.612293</v>
+        <v>0.073298</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.073298</v>
+        <v>0.9397180000000001</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.9397180000000001</v>
+        <v>1.638893</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.638893</v>
+        <v>5.130501</v>
       </c>
       <c r="AB49" t="n">
-        <v>5.130501</v>
+        <v>3.033233</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.033233</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>5.054283</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK49" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5955,96 +5679,90 @@
         <v>0.42</v>
       </c>
       <c r="G50" t="n">
-        <v>0.52</v>
+        <v>108.73548</v>
       </c>
       <c r="H50" t="n">
-        <v>108.73548</v>
+        <v>109.48375</v>
       </c>
       <c r="I50" t="n">
-        <v>109.48375</v>
+        <v>5.3186</v>
       </c>
       <c r="J50" t="n">
-        <v>5.3186</v>
+        <v>5.318</v>
       </c>
       <c r="K50" t="n">
-        <v>5.318</v>
+        <v>6852705</v>
       </c>
       <c r="L50" t="n">
-        <v>6852705</v>
+        <v>2589817</v>
       </c>
       <c r="M50" t="n">
-        <v>2589817</v>
+        <v>4262888</v>
       </c>
       <c r="N50" t="n">
-        <v>4262888</v>
+        <v>4.09</v>
       </c>
       <c r="O50" t="n">
-        <v>4.09</v>
+        <v>2.77</v>
       </c>
       <c r="P50" t="n">
-        <v>2.77</v>
+        <v>4.89</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.89</v>
+        <v>31.47</v>
       </c>
       <c r="R50" t="n">
-        <v>31.47</v>
+        <v>356582</v>
       </c>
       <c r="S50" t="n">
-        <v>356582</v>
+        <v>-0.085869</v>
       </c>
       <c r="T50" t="n">
-        <v>-0.085869</v>
+        <v>-0.812453</v>
       </c>
       <c r="U50" t="n">
-        <v>-0.812453</v>
+        <v>-1.986584</v>
       </c>
       <c r="V50" t="n">
-        <v>-1.986584</v>
+        <v>-1.986804</v>
       </c>
       <c r="W50" t="n">
-        <v>-1.986804</v>
+        <v>1.155358</v>
       </c>
       <c r="X50" t="n">
-        <v>1.155358</v>
+        <v>1.710427</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.710427</v>
+        <v>0.821088</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.821088</v>
+        <v>1.657796</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.657796</v>
+        <v>5.172369</v>
       </c>
       <c r="AB50" t="n">
-        <v>5.172369</v>
+        <v>2.828436</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.828436</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>5.096104</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="AH50" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="AI50" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK50" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -6068,96 +5786,90 @@
         <v>-0.36</v>
       </c>
       <c r="G51" t="n">
-        <v>0.03</v>
+        <v>108.75326</v>
       </c>
       <c r="H51" t="n">
-        <v>108.75326</v>
+        <v>110.07682</v>
       </c>
       <c r="I51" t="n">
-        <v>110.07682</v>
+        <v>5.3843</v>
       </c>
       <c r="J51" t="n">
-        <v>5.3843</v>
+        <v>5.3837</v>
       </c>
       <c r="K51" t="n">
-        <v>5.3837</v>
+        <v>6923886</v>
       </c>
       <c r="L51" t="n">
-        <v>6923886</v>
+        <v>2597630</v>
       </c>
       <c r="M51" t="n">
-        <v>2597630</v>
+        <v>4326256</v>
       </c>
       <c r="N51" t="n">
-        <v>4326256</v>
+        <v>4.18</v>
       </c>
       <c r="O51" t="n">
-        <v>4.18</v>
+        <v>2.82</v>
       </c>
       <c r="P51" t="n">
-        <v>2.82</v>
+        <v>4.99</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.99</v>
+        <v>32.04</v>
       </c>
       <c r="R51" t="n">
-        <v>32.04</v>
+        <v>357103</v>
       </c>
       <c r="S51" t="n">
-        <v>357103</v>
+        <v>0.016352</v>
       </c>
       <c r="T51" t="n">
-        <v>0.016352</v>
+        <v>0.541697</v>
       </c>
       <c r="U51" t="n">
-        <v>0.541697</v>
+        <v>1.235287</v>
       </c>
       <c r="V51" t="n">
-        <v>1.235287</v>
+        <v>1.235427</v>
       </c>
       <c r="W51" t="n">
-        <v>1.235427</v>
+        <v>1.038729</v>
       </c>
       <c r="X51" t="n">
-        <v>1.038729</v>
+        <v>0.301682</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.301682</v>
+        <v>1.486504</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.486504</v>
+        <v>0.146109</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.146109</v>
+        <v>4.680811</v>
       </c>
       <c r="AB51" t="n">
-        <v>4.680811</v>
+        <v>0.924206</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.924206</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>4.490243</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK51" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -6181,96 +5893,90 @@
         <v>0.27</v>
       </c>
       <c r="G52" t="n">
-        <v>0.03</v>
+        <v>109.25005</v>
       </c>
       <c r="H52" t="n">
-        <v>109.25005</v>
+        <v>106.59892</v>
       </c>
       <c r="I52" t="n">
-        <v>106.59892</v>
+        <v>5.3338</v>
       </c>
       <c r="J52" t="n">
-        <v>5.3338</v>
+        <v>5.3332</v>
       </c>
       <c r="K52" t="n">
-        <v>5.3332</v>
+        <v>7004223</v>
       </c>
       <c r="L52" t="n">
-        <v>7004223</v>
+        <v>2616902</v>
       </c>
       <c r="M52" t="n">
-        <v>2616902</v>
+        <v>4387321</v>
       </c>
       <c r="N52" t="n">
-        <v>4387321</v>
+        <v>4.24</v>
       </c>
       <c r="O52" t="n">
-        <v>4.24</v>
+        <v>2.75</v>
       </c>
       <c r="P52" t="n">
-        <v>2.75</v>
+        <v>5.12</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.12</v>
+        <v>32.2</v>
       </c>
       <c r="R52" t="n">
-        <v>32.2</v>
+        <v>360578</v>
       </c>
       <c r="S52" t="n">
-        <v>360578</v>
+        <v>0.456805</v>
       </c>
       <c r="T52" t="n">
-        <v>0.456805</v>
+        <v>-3.159521</v>
       </c>
       <c r="U52" t="n">
-        <v>-3.159521</v>
+        <v>-0.937912</v>
       </c>
       <c r="V52" t="n">
-        <v>-0.937912</v>
+        <v>-0.938017</v>
       </c>
       <c r="W52" t="n">
-        <v>-0.938017</v>
+        <v>1.160288</v>
       </c>
       <c r="X52" t="n">
-        <v>1.160288</v>
+        <v>0.741907</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.741907</v>
+        <v>1.411498</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.411498</v>
+        <v>0.973109</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.973109</v>
+        <v>4.461836</v>
       </c>
       <c r="AB52" t="n">
-        <v>4.461836</v>
+        <v>-0.101973</v>
       </c>
       <c r="AC52" t="n">
-        <v>-0.101973</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>4.177803</v>
+        <v>-0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF52" t="n">
-        <v>-0</v>
+        <v>0.06</v>
       </c>
       <c r="AG52" t="n">
-        <v>-0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AH52" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="AI52" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AK52" t="n">
         <v>0.16</v>
       </c>
     </row>
@@ -6294,96 +6000,90 @@
         <v>-0.01</v>
       </c>
       <c r="G53" t="n">
-        <v>0.21</v>
+        <v>109.4528</v>
       </c>
       <c r="H53" t="n">
-        <v>109.4528</v>
+        <v>107.18417</v>
       </c>
       <c r="I53" t="n">
-        <v>107.18417</v>
+        <v>5.5024</v>
       </c>
       <c r="J53" t="n">
-        <v>5.5024</v>
+        <v>5.5018</v>
       </c>
       <c r="K53" t="n">
-        <v>5.5018</v>
+        <v>7137252</v>
       </c>
       <c r="L53" t="n">
-        <v>7137252</v>
+        <v>2701735</v>
       </c>
       <c r="M53" t="n">
-        <v>2701735</v>
+        <v>4435517</v>
       </c>
       <c r="N53" t="n">
-        <v>4435517</v>
+        <v>4.2</v>
       </c>
       <c r="O53" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="P53" t="n">
-        <v>2.7</v>
+        <v>5.12</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.12</v>
+        <v>31.87</v>
       </c>
       <c r="R53" t="n">
-        <v>31.87</v>
+        <v>358234</v>
       </c>
       <c r="S53" t="n">
-        <v>358234</v>
+        <v>0.185583</v>
       </c>
       <c r="T53" t="n">
-        <v>0.185583</v>
+        <v>0.549021</v>
       </c>
       <c r="U53" t="n">
-        <v>0.549021</v>
+        <v>3.160973</v>
       </c>
       <c r="V53" t="n">
-        <v>3.160973</v>
+        <v>3.161329</v>
       </c>
       <c r="W53" t="n">
-        <v>3.161329</v>
+        <v>1.899268</v>
       </c>
       <c r="X53" t="n">
-        <v>1.899268</v>
+        <v>3.241734</v>
       </c>
       <c r="Y53" t="n">
-        <v>3.241734</v>
+        <v>1.098529</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.098529</v>
+        <v>-0.650067</v>
       </c>
       <c r="AA53" t="n">
-        <v>-0.650067</v>
+        <v>4.264385</v>
       </c>
       <c r="AB53" t="n">
-        <v>4.264385</v>
+        <v>-1.042167</v>
       </c>
       <c r="AC53" t="n">
-        <v>-1.042167</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>3.897866</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AH53" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -6407,96 +6107,90 @@
         <v>0.41</v>
       </c>
       <c r="G54" t="n">
-        <v>0.39</v>
+        <v>110.04992</v>
       </c>
       <c r="H54" t="n">
-        <v>110.04992</v>
+        <v>103.77761</v>
       </c>
       <c r="I54" t="n">
-        <v>103.77761</v>
+        <v>5.2301</v>
       </c>
       <c r="J54" t="n">
-        <v>5.2301</v>
+        <v>5.2295</v>
       </c>
       <c r="K54" t="n">
-        <v>5.2295</v>
+        <v>7130762</v>
       </c>
       <c r="L54" t="n">
-        <v>7130762</v>
+        <v>2654220</v>
       </c>
       <c r="M54" t="n">
-        <v>2654220</v>
+        <v>4476542</v>
       </c>
       <c r="N54" t="n">
-        <v>4476542</v>
+        <v>4.44</v>
       </c>
       <c r="O54" t="n">
-        <v>4.44</v>
+        <v>2.87</v>
       </c>
       <c r="P54" t="n">
-        <v>2.87</v>
+        <v>5.38</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.38</v>
+        <v>32.45</v>
       </c>
       <c r="R54" t="n">
-        <v>32.45</v>
+        <v>364367</v>
       </c>
       <c r="S54" t="n">
-        <v>364367</v>
+        <v>0.54555</v>
       </c>
       <c r="T54" t="n">
-        <v>0.54555</v>
+        <v>-3.178231</v>
       </c>
       <c r="U54" t="n">
-        <v>-3.178231</v>
+        <v>-4.94875</v>
       </c>
       <c r="V54" t="n">
-        <v>-4.94875</v>
+        <v>-4.949289</v>
       </c>
       <c r="W54" t="n">
-        <v>-4.949289</v>
+        <v>-0.090931</v>
       </c>
       <c r="X54" t="n">
-        <v>-0.090931</v>
+        <v>-1.758685</v>
       </c>
       <c r="Y54" t="n">
-        <v>-1.758685</v>
+        <v>0.92492</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.92492</v>
+        <v>1.712009</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.712009</v>
+        <v>4.441351</v>
       </c>
       <c r="AB54" t="n">
-        <v>4.441351</v>
+        <v>-0.903999</v>
       </c>
       <c r="AC54" t="n">
-        <v>-0.903999</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>4.303068</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
         <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AH54" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="AI54" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK54" t="n">
         <v>0.58</v>
       </c>
     </row>
@@ -6520,96 +6214,90 @@
         <v>-0.73</v>
       </c>
       <c r="G55" t="n">
-        <v>0.5600000000000001</v>
+        <v>110.7366</v>
       </c>
       <c r="H55" t="n">
-        <v>110.7366</v>
+        <v>106.76075</v>
       </c>
       <c r="I55" t="n">
-        <v>106.76075</v>
+        <v>5.1495</v>
       </c>
       <c r="J55" t="n">
-        <v>5.1495</v>
+        <v>5.1489</v>
       </c>
       <c r="K55" t="n">
-        <v>5.1489</v>
+        <v>7157783</v>
       </c>
       <c r="L55" t="n">
-        <v>7157783</v>
+        <v>2656484</v>
       </c>
       <c r="M55" t="n">
-        <v>2656484</v>
+        <v>4501299</v>
       </c>
       <c r="N55" t="n">
-        <v>4501299</v>
+        <v>4.64</v>
       </c>
       <c r="O55" t="n">
-        <v>4.64</v>
+        <v>3.07</v>
       </c>
       <c r="P55" t="n">
-        <v>3.07</v>
+        <v>5.56</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.56</v>
+        <v>32.63</v>
       </c>
       <c r="R55" t="n">
-        <v>32.63</v>
+        <v>371074</v>
       </c>
       <c r="S55" t="n">
-        <v>371074</v>
+        <v>0.6239710000000001</v>
       </c>
       <c r="T55" t="n">
-        <v>0.6239710000000001</v>
+        <v>2.874551</v>
       </c>
       <c r="U55" t="n">
-        <v>2.874551</v>
+        <v>-1.54108</v>
       </c>
       <c r="V55" t="n">
-        <v>-1.54108</v>
+        <v>-1.541256</v>
       </c>
       <c r="W55" t="n">
-        <v>-1.541256</v>
+        <v>0.378936</v>
       </c>
       <c r="X55" t="n">
-        <v>0.378936</v>
+        <v>0.085298</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.085298</v>
+        <v>0.553038</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.553038</v>
+        <v>1.840727</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.840727</v>
+        <v>3.812497</v>
       </c>
       <c r="AB55" t="n">
-        <v>3.812497</v>
+        <v>-2.659212</v>
       </c>
       <c r="AC55" t="n">
-        <v>-2.659212</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.357475</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
         <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AH55" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AI55" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AK55" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -6633,96 +6321,90 @@
         <v>0.52</v>
       </c>
       <c r="G56" t="n">
-        <v>0.91</v>
+        <v>110.58808</v>
       </c>
       <c r="H56" t="n">
-        <v>110.58808</v>
+        <v>118.01719</v>
       </c>
       <c r="I56" t="n">
-        <v>118.01719</v>
+        <v>5.2194</v>
       </c>
       <c r="J56" t="n">
-        <v>5.2194</v>
+        <v>5.2188</v>
       </c>
       <c r="K56" t="n">
-        <v>5.2188</v>
+        <v>7240557</v>
       </c>
       <c r="L56" t="n">
-        <v>7240557</v>
+        <v>2687535</v>
       </c>
       <c r="M56" t="n">
-        <v>2687535</v>
+        <v>4553022</v>
       </c>
       <c r="N56" t="n">
-        <v>4553022</v>
+        <v>4.52</v>
       </c>
       <c r="O56" t="n">
-        <v>4.52</v>
+        <v>3.06</v>
       </c>
       <c r="P56" t="n">
-        <v>3.06</v>
+        <v>5.39</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.39</v>
+        <v>32.84</v>
       </c>
       <c r="R56" t="n">
-        <v>32.84</v>
+        <v>362002</v>
       </c>
       <c r="S56" t="n">
-        <v>362002</v>
+        <v>-0.13412</v>
       </c>
       <c r="T56" t="n">
-        <v>-0.13412</v>
+        <v>10.543613</v>
       </c>
       <c r="U56" t="n">
-        <v>10.543613</v>
+        <v>1.357413</v>
       </c>
       <c r="V56" t="n">
-        <v>1.357413</v>
+        <v>1.357572</v>
       </c>
       <c r="W56" t="n">
-        <v>1.357572</v>
+        <v>1.15642</v>
       </c>
       <c r="X56" t="n">
-        <v>1.15642</v>
+        <v>1.168876</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.168876</v>
+        <v>1.149068</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.149068</v>
+        <v>-2.444795</v>
       </c>
       <c r="AA56" t="n">
-        <v>-2.444795</v>
+        <v>4.142847</v>
       </c>
       <c r="AB56" t="n">
-        <v>4.142847</v>
+        <v>-1.819225</v>
       </c>
       <c r="AC56" t="n">
-        <v>-1.819225</v>
+        <v>-0.25</v>
       </c>
       <c r="AD56" t="n">
-        <v>3.768807</v>
+        <v>-0.000354</v>
       </c>
       <c r="AE56" t="n">
-        <v>-0.25</v>
+        <v>-0.000354</v>
       </c>
       <c r="AF56" t="n">
-        <v>-0.000354</v>
+        <v>-0.12</v>
       </c>
       <c r="AG56" t="n">
-        <v>-0.000354</v>
+        <v>-0.01</v>
       </c>
       <c r="AH56" t="n">
-        <v>-0.12</v>
+        <v>-0.17</v>
       </c>
       <c r="AI56" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="AK56" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -6746,96 +6428,90 @@
         <v>2.73</v>
       </c>
       <c r="G57" t="n">
-        <v>0.8100000000000001</v>
+        <v>110.90009</v>
       </c>
       <c r="H57" t="n">
-        <v>110.90009</v>
+        <v>113.99295</v>
       </c>
       <c r="I57" t="n">
-        <v>113.99295</v>
+        <v>4.9886</v>
       </c>
       <c r="J57" t="n">
-        <v>4.9886</v>
+        <v>4.988</v>
       </c>
       <c r="K57" t="n">
-        <v>4.988</v>
+        <v>7259766</v>
       </c>
       <c r="L57" t="n">
-        <v>7259766</v>
+        <v>2685397</v>
       </c>
       <c r="M57" t="n">
-        <v>2685397</v>
+        <v>4574368</v>
       </c>
       <c r="N57" t="n">
-        <v>4574368</v>
+        <v>4.64</v>
       </c>
       <c r="O57" t="n">
-        <v>4.64</v>
+        <v>3.15</v>
       </c>
       <c r="P57" t="n">
-        <v>3.15</v>
+        <v>5.51</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.51</v>
+        <v>33.36</v>
       </c>
       <c r="R57" t="n">
-        <v>33.36</v>
+        <v>366913</v>
       </c>
       <c r="S57" t="n">
-        <v>366913</v>
+        <v>0.282137</v>
       </c>
       <c r="T57" t="n">
-        <v>0.282137</v>
+        <v>-3.409876</v>
       </c>
       <c r="U57" t="n">
-        <v>-3.409876</v>
+        <v>-4.421964</v>
       </c>
       <c r="V57" t="n">
-        <v>-4.421964</v>
+        <v>-4.422473</v>
       </c>
       <c r="W57" t="n">
-        <v>-4.422473</v>
+        <v>0.265297</v>
       </c>
       <c r="X57" t="n">
-        <v>0.265297</v>
+        <v>-0.079552</v>
       </c>
       <c r="Y57" t="n">
-        <v>-0.079552</v>
+        <v>0.468831</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.468831</v>
+        <v>1.356622</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.356622</v>
+        <v>4.39172</v>
       </c>
       <c r="AB57" t="n">
-        <v>4.39172</v>
+        <v>0.619623</v>
       </c>
       <c r="AC57" t="n">
-        <v>0.619623</v>
+        <v>-0.25</v>
       </c>
       <c r="AD57" t="n">
-        <v>4.109608</v>
+        <v>-0.000554</v>
       </c>
       <c r="AE57" t="n">
-        <v>-0.25</v>
+        <v>-0.000554</v>
       </c>
       <c r="AF57" t="n">
-        <v>-0.000554</v>
+        <v>0.12</v>
       </c>
       <c r="AG57" t="n">
-        <v>-0.000554</v>
+        <v>0.09</v>
       </c>
       <c r="AH57" t="n">
         <v>0.12</v>
       </c>
       <c r="AI57" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AK57" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -6859,96 +6535,90 @@
         <v>0.84</v>
       </c>
       <c r="G58" t="n">
-        <v>0.65</v>
+        <v>111.13846</v>
       </c>
       <c r="H58" t="n">
-        <v>111.13846</v>
+        <v>109.65479</v>
       </c>
       <c r="I58" t="n">
-        <v>109.65479</v>
+        <v>5.0569</v>
       </c>
       <c r="J58" t="n">
-        <v>5.0569</v>
+        <v>5.0563</v>
       </c>
       <c r="K58" t="n">
-        <v>5.0563</v>
+        <v>7305306</v>
       </c>
       <c r="L58" t="n">
-        <v>7305306</v>
+        <v>2708154</v>
       </c>
       <c r="M58" t="n">
-        <v>2708154</v>
+        <v>4597152</v>
       </c>
       <c r="N58" t="n">
-        <v>4597152</v>
+        <v>4.74</v>
       </c>
       <c r="O58" t="n">
-        <v>4.74</v>
+        <v>3.25</v>
       </c>
       <c r="P58" t="n">
-        <v>3.25</v>
+        <v>5.62</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.62</v>
+        <v>33.1</v>
       </c>
       <c r="R58" t="n">
-        <v>33.1</v>
+        <v>371137</v>
       </c>
       <c r="S58" t="n">
-        <v>371137</v>
+        <v>0.214941</v>
       </c>
       <c r="T58" t="n">
-        <v>0.214941</v>
+        <v>-3.805639</v>
       </c>
       <c r="U58" t="n">
-        <v>-3.805639</v>
+        <v>1.369122</v>
       </c>
       <c r="V58" t="n">
-        <v>1.369122</v>
+        <v>1.369286</v>
       </c>
       <c r="W58" t="n">
-        <v>1.369286</v>
+        <v>0.627293</v>
       </c>
       <c r="X58" t="n">
-        <v>0.627293</v>
+        <v>0.847435</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.847435</v>
+        <v>0.49808</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.49808</v>
+        <v>1.151227</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.151227</v>
+        <v>4.724907</v>
       </c>
       <c r="AB58" t="n">
-        <v>4.724907</v>
+        <v>1.964454</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.964454</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>4.420848</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="AF58" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="AG58" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="AH58" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="AI58" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK58" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -6972,96 +6642,90 @@
         <v>-0.5</v>
       </c>
       <c r="G59" t="n">
-        <v>0.14</v>
+        <v>110.15775</v>
       </c>
       <c r="H59" t="n">
-        <v>110.15775</v>
+        <v>109.94156</v>
       </c>
       <c r="I59" t="n">
-        <v>109.94156</v>
+        <v>5.1766</v>
       </c>
       <c r="J59" t="n">
-        <v>5.1766</v>
+        <v>5.176</v>
       </c>
       <c r="K59" t="n">
-        <v>5.176</v>
+        <v>7353293</v>
       </c>
       <c r="L59" t="n">
-        <v>7353293</v>
+        <v>2750625</v>
       </c>
       <c r="M59" t="n">
-        <v>2750625</v>
+        <v>4602668</v>
       </c>
       <c r="N59" t="n">
-        <v>4602668</v>
+        <v>4.58</v>
       </c>
       <c r="O59" t="n">
-        <v>4.58</v>
+        <v>3.18</v>
       </c>
       <c r="P59" t="n">
-        <v>3.18</v>
+        <v>5.42</v>
       </c>
       <c r="Q59" t="n">
-        <v>5.42</v>
+        <v>33.33</v>
       </c>
       <c r="R59" t="n">
-        <v>33.33</v>
+        <v>367558</v>
       </c>
       <c r="S59" t="n">
-        <v>367558</v>
+        <v>-0.882422</v>
       </c>
       <c r="T59" t="n">
-        <v>-0.882422</v>
+        <v>0.261521</v>
       </c>
       <c r="U59" t="n">
-        <v>0.261521</v>
+        <v>2.367063</v>
       </c>
       <c r="V59" t="n">
-        <v>2.367063</v>
+        <v>2.367344</v>
       </c>
       <c r="W59" t="n">
-        <v>2.367344</v>
+        <v>0.656879</v>
       </c>
       <c r="X59" t="n">
-        <v>0.656879</v>
+        <v>1.568264</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.568264</v>
+        <v>0.119987</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.119987</v>
+        <v>-0.964334</v>
       </c>
       <c r="AA59" t="n">
-        <v>-0.964334</v>
+        <v>4.641328</v>
       </c>
       <c r="AB59" t="n">
-        <v>4.641328</v>
+        <v>3.177699</v>
       </c>
       <c r="AC59" t="n">
-        <v>3.177699</v>
+        <v>-0.25</v>
       </c>
       <c r="AD59" t="n">
-        <v>4.327084</v>
+        <v>-0.000372</v>
       </c>
       <c r="AE59" t="n">
-        <v>-0.25</v>
+        <v>-0.000372</v>
       </c>
       <c r="AF59" t="n">
-        <v>-0.000372</v>
+        <v>-0.16</v>
       </c>
       <c r="AG59" t="n">
-        <v>-0.000372</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AH59" t="n">
-        <v>-0.16</v>
+        <v>-0.2</v>
       </c>
       <c r="AI59" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AK59" t="n">
         <v>0.23</v>
       </c>
     </row>
@@ -7085,96 +6749,90 @@
         <v>-1.16</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.01</v>
+        <v>109.91611</v>
       </c>
       <c r="H60" t="n">
-        <v>109.91611</v>
+        <v>114.40189</v>
       </c>
       <c r="I60" t="n">
-        <v>114.40189</v>
+        <v>5.0773</v>
       </c>
       <c r="J60" t="n">
-        <v>5.0773</v>
+        <v>5.0767</v>
       </c>
       <c r="K60" t="n">
-        <v>5.0767</v>
+        <v>7372243</v>
       </c>
       <c r="L60" t="n">
-        <v>7372243</v>
+        <v>2731513</v>
       </c>
       <c r="M60" t="n">
-        <v>2731513</v>
+        <v>4640730</v>
       </c>
       <c r="N60" t="n">
-        <v>4640730</v>
+        <v>4.88</v>
       </c>
       <c r="O60" t="n">
-        <v>4.88</v>
+        <v>3.31</v>
       </c>
       <c r="P60" t="n">
-        <v>3.31</v>
+        <v>5.81</v>
       </c>
       <c r="Q60" t="n">
-        <v>5.81</v>
+        <v>32.08</v>
       </c>
       <c r="R60" t="n">
-        <v>32.08</v>
+        <v>369742</v>
       </c>
       <c r="S60" t="n">
-        <v>369742</v>
+        <v>-0.219358</v>
       </c>
       <c r="T60" t="n">
-        <v>-0.219358</v>
+        <v>4.057001</v>
       </c>
       <c r="U60" t="n">
-        <v>4.057001</v>
+        <v>-1.918247</v>
       </c>
       <c r="V60" t="n">
-        <v>-1.918247</v>
+        <v>-1.91847</v>
       </c>
       <c r="W60" t="n">
-        <v>-1.91847</v>
+        <v>0.257708</v>
       </c>
       <c r="X60" t="n">
-        <v>0.257708</v>
+        <v>-0.694824</v>
       </c>
       <c r="Y60" t="n">
-        <v>-0.694824</v>
+        <v>0.826955</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.826955</v>
+        <v>0.5941920000000001</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.5941920000000001</v>
+        <v>4.443025</v>
       </c>
       <c r="AB60" t="n">
-        <v>4.443025</v>
+        <v>2.772183</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.772183</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>4.098046</v>
+        <v>-0.000497</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>-0.000497</v>
       </c>
       <c r="AF60" t="n">
-        <v>-0.000497</v>
+        <v>0.3</v>
       </c>
       <c r="AG60" t="n">
-        <v>-0.000497</v>
+        <v>0.13</v>
       </c>
       <c r="AH60" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="AI60" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="AK60" t="n">
         <v>-1.25</v>
       </c>
     </row>
@@ -7197,63 +6855,57 @@
       <c r="F61" t="n">
         <v>-0.22</v>
       </c>
-      <c r="G61" t="n">
-        <v>-0.32</v>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="n">
+        <v>5.1816</v>
+      </c>
       <c r="J61" t="n">
-        <v>5.1816</v>
-      </c>
-      <c r="K61" t="n">
         <v>5.181</v>
       </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="n">
+      <c r="R61" t="n">
         <v>372616</v>
       </c>
+      <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
+      <c r="U61" t="n">
+        <v>2.054241</v>
+      </c>
       <c r="V61" t="n">
-        <v>2.054241</v>
-      </c>
-      <c r="W61" t="n">
         <v>2.054484</v>
       </c>
+      <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
+      <c r="Z61" t="n">
+        <v>0.777299</v>
+      </c>
       <c r="AA61" t="n">
-        <v>0.777299</v>
+        <v>4.223453</v>
       </c>
       <c r="AB61" t="n">
-        <v>4.223453</v>
+        <v>2.178243</v>
       </c>
       <c r="AC61" t="n">
-        <v>2.178243</v>
+        <v>-0.25</v>
       </c>
       <c r="AD61" t="n">
-        <v>3.983297</v>
+        <v>-0.0007470000000000001</v>
       </c>
       <c r="AE61" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AF61" t="n">
         <v>-0.0007470000000000001</v>
       </c>
-      <c r="AG61" t="n">
-        <v>-0.0007470000000000001</v>
-      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="inlineStr"/>
-      <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -7266,19 +6918,19 @@
         <v>0.051526</v>
       </c>
       <c r="D62" t="n">
-        <v>0.051587</v>
+        <v>0.051526</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="n">
+        <v>5.1575</v>
+      </c>
       <c r="J62" t="n">
-        <v>5.1575</v>
-      </c>
-      <c r="K62" t="n">
         <v>5.1569</v>
       </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -7288,33 +6940,31 @@
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
+      <c r="U62" t="n">
+        <v>-0.465107</v>
+      </c>
       <c r="V62" t="n">
-        <v>-0.465107</v>
-      </c>
-      <c r="W62" t="n">
         <v>-0.465161</v>
       </c>
+      <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr"/>
-      <c r="AC62" t="inlineStr"/>
-      <c r="AD62" t="inlineStr"/>
+      <c r="AC62" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>-0.000259</v>
+      </c>
       <c r="AE62" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AF62" t="n">
         <v>-0.000259</v>
       </c>
-      <c r="AG62" t="n">
-        <v>-0.000197</v>
-      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
-      <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI62"/>
+  <dimension ref="A1:AK62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,145 +453,155 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>inpc</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>ibc_br_sa</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ibc_br</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>cambio_venda_usd</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>cambio_compra_usd</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>saldo_credito_total</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>saldo_credito_pj</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>saldo_credito_pf</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inadimplencia_total</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inadimplencia_pj</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inadimplencia_pf</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ipca_acum_12m</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>inpc_acum_12m</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>dif_selic_over</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>dif_cdi</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -605,10 +615,10 @@
         <v>6.25</v>
       </c>
       <c r="C2" t="n">
-        <v>0.022748</v>
+        <v>0.02315</v>
       </c>
       <c r="D2" t="n">
-        <v>0.022748</v>
+        <v>0.02315</v>
       </c>
       <c r="E2" t="n">
         <v>1.16</v>
@@ -617,42 +627,44 @@
         <v>-0.64</v>
       </c>
       <c r="G2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H2" t="n">
         <v>96.96513</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>97.10777</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>5.4394</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>5.4388</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>4441056</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>1894119</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>2546936</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>2.34</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1.43</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>3.01</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>21.42</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>368886</v>
       </c>
-      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -669,6 +681,8 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -690,86 +704,90 @@
         <v>0.64</v>
       </c>
       <c r="G3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H3" t="n">
         <v>97.48671</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>96.53041</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>5.643</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>5.6424</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>4511956</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>1910940</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>2601017</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>2.33</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>1.43</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>2.99</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>22.89</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>367927</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>0.537905</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>-0.594556</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>3.74306</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>3.743473</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>1.596467</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>0.888065</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>2.123375</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>-0.259972</v>
       </c>
-      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="n">
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD3" t="n">
-        <v>0.001496</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0.001496</v>
-      </c>
       <c r="AF3" t="n">
+        <v>0.001094</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.001094</v>
+      </c>
+      <c r="AH3" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AK3" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -793,86 +811,90 @@
         <v>0.02</v>
       </c>
       <c r="G4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H4" t="n">
         <v>99.05526</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>97.85277000000001</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>5.6199</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>5.6193</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>4597507</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>1933111</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2664395</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>2.36</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>1.46</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>3.01</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>23.91</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>367772</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>1.608989</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>1.36989</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>-0.409357</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>-0.4094</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>1.896096</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>1.160214</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>2.436662</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>-0.042128</v>
       </c>
-      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
         <v>0.005012</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AG4" t="n">
         <v>0.005012</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AH4" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AI4" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AJ4" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AK4" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -896,86 +918,90 @@
         <v>0.87</v>
       </c>
       <c r="G5" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H5" t="n">
         <v>99.37716</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>99.32258</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>5.5805</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>5.5799</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>4682852</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>1974391</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>2708461</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>2.35</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>1.4</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>3.05</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>24.21</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>362204</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>0.32497</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>1.502063</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>-0.70108</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>-0.701155</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>1.856332</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>2.135418</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>1.653884</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>-1.513981</v>
       </c>
-      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="n">
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AF5" t="n">
         <v>0.00406</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AG5" t="n">
         <v>0.00406</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AH5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AI5" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AJ5" t="n">
         <v>0.04</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AK5" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -999,86 +1025,90 @@
         <v>1.82</v>
       </c>
       <c r="G6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H6" t="n">
         <v>97.4213</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>91.67776000000001</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>5.3574</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>5.3568</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>4682131</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>1947035</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>2735096</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>2.51</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>1.46</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>3.26</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>25.23</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>358398</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>-1.968118</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>-7.696961</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>-3.99785</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>-3.99828</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>-0.015397</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>-1.385541</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>-1.050789</v>
       </c>
-      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
         <v>0.001433</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AG6" t="n">
         <v>0.001433</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AH6" t="n">
         <v>0.16</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AI6" t="n">
         <v>0.06</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AJ6" t="n">
         <v>0.21</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AK6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1102,86 +1132,90 @@
         <v>1.83</v>
       </c>
       <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
         <v>98.4804</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>95.63728999999999</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>5.1394</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>5.1388</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>4727818</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>1971524</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>2756295</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>2.57</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>1.44</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>3.38</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>25.63</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>357740</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>1.087134</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>4.318965</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>-4.069138</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>-4.069594</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>0.975774</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>1.257759</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>0.775073</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>-0.183595</v>
       </c>
-      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="n">
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AF7" t="n">
         <v>0.004849</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AG7" t="n">
         <v>0.004849</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AH7" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AI7" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AJ7" t="n">
         <v>0.12</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AK7" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1205,86 +1239,90 @@
         <v>1.74</v>
       </c>
       <c r="G8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H8" t="n">
         <v>99.54801999999999</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>104.53237</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>4.7378</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>4.7372</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>4794583</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>1994119</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>2800464</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>2.66</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>1.55</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>3.45</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>26.54</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>353169</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>1.084094</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>9.300848999999999</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>-7.814142</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>-7.815054</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>1.412174</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>1.146068</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>1.602477</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>-1.277744</v>
       </c>
-      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="n">
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="n">
         <v>1</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AF8" t="n">
         <v>0.002356</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AG8" t="n">
         <v>0.002356</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AH8" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AI8" t="n">
         <v>0.11</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AJ8" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AK8" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1308,86 +1346,90 @@
         <v>1.41</v>
       </c>
       <c r="G9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H9" t="n">
         <v>99.44118</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>100.22938</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>4.9191</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>4.9185</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>4833732</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>2003312</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>2830420</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>2.72</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>1.57</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>3.54</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>27.46</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>345097</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>-0.107325</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>-4.116419</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>3.826671</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>3.827155</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>0.816526</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>0.461006</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>1.06968</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>-2.285591</v>
       </c>
-      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
         <v>0.001785</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AG9" t="n">
         <v>0.001785</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AH9" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AI9" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AJ9" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AK9" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1411,86 +1453,90 @@
         <v>0.52</v>
       </c>
       <c r="G10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H10" t="n">
         <v>99.6454</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>99.74383</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>4.7289</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>4.7283</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4889397</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>2013726</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>2875671</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>2.79</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>1.57</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>27.42</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>346415</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>0.205368</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>-0.484439</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>-3.866561</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>-3.867033</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>1.151595</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
         <v>0.5198390000000001</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>1.598738</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
         <v>0.381922</v>
       </c>
-      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="n">
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="n">
         <v>1</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AF10" t="n">
         <v>0.003057</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AG10" t="n">
         <v>0.003057</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AH10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AK10" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1514,86 +1560,90 @@
         <v>0.59</v>
       </c>
       <c r="G11" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H11" t="n">
         <v>99.51048</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>99.31653</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>5.238</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>5.2374</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>4965603</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>2052569</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>2913035</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>2.73</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>1.52</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>3.57</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>27.88</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>341958</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>-0.1354</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>-0.428397</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>10.765717</v>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>10.767083</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>1.558597</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
         <v>1.928912</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>1.299314</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
         <v>-1.286607</v>
       </c>
-      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="n">
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AF11" t="n">
         <v>0.00132</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AG11" t="n">
         <v>0.00132</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AH11" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AI11" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AJ11" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AK11" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1617,86 +1667,90 @@
         <v>0.21</v>
       </c>
       <c r="G12" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="H12" t="n">
         <v>101.43172</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>103.95991</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>5.1884</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>5.1878</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>4999244</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>2047038</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>2952207</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>2.84</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>1.6</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>29.24</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>346403</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>1.930691</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>4.675335</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>-0.946926</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>-0.947035</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>0.677481</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Y12" t="n">
         <v>-0.269467</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>1.344714</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="n">
         <v>1.299867</v>
       </c>
-      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AG12" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AH12" t="n">
         <v>0.11</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AI12" t="n">
         <v>0.08</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AJ12" t="n">
         <v>0.14</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AK12" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -1720,90 +1774,96 @@
         <v>-0.7</v>
       </c>
       <c r="G13" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="H13" t="n">
         <v>101.10583</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>104.51156</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>5.179</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>5.1784</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>5072711</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>2064183</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>3008528</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>2.9</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>1.62</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>3.78</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>28.6</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>339664</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>-0.32129</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>0.530637</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>-0.181173</v>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>-0.181194</v>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>1.469562</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Y13" t="n">
         <v>0.837552</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>1.907759</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AA13" t="n">
         <v>-1.945422</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AB13" t="n">
         <v>8.727061000000001</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AC13" t="n">
         <v>8.58755</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AD13" t="n">
+        <v>8.825751</v>
+      </c>
+      <c r="AE13" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AF13" t="n">
         <v>0.001523</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AG13" t="n">
         <v>0.001523</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AH13" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AI13" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AJ13" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AK13" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -1827,90 +1887,96 @@
         <v>-0.95</v>
       </c>
       <c r="G14" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="H14" t="n">
         <v>101.16034</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>101.1889</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>5.4066</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>5.406</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>5164775</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>2109806</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3054969</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>2.92</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>1.65</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>3.8</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>28.57</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>327580</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>0.053914</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>-3.179227</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>4.394671</v>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>4.39518</v>
       </c>
-      <c r="W14" t="n">
+      <c r="X14" t="n">
         <v>1.814888</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Y14" t="n">
         <v>2.210221</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Z14" t="n">
         <v>1.543645</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AA14" t="n">
         <v>-3.557633</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AB14" t="n">
         <v>7.168596</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AC14" t="n">
         <v>8.248760000000001</v>
       </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
       <c r="AD14" t="n">
+        <v>7.191214</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
         <v>0.000228</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AG14" t="n">
         <v>0.000228</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0.03</v>
       </c>
       <c r="AH14" t="n">
         <v>0.02</v>
       </c>
       <c r="AI14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AK14" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -1934,90 +2000,96 @@
         <v>-0.97</v>
       </c>
       <c r="G15" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H15" t="n">
         <v>101.44171</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>100.08177</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>5.257</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>5.2564</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>5215990</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>2105856</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>3110134</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>3.04</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>1.77</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>3.89</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>29.68</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>325546</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>0.278143</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>-1.094122</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>-2.766988</v>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>-2.767296</v>
       </c>
-      <c r="W15" t="n">
+      <c r="X15" t="n">
         <v>0.991621</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Y15" t="n">
         <v>-0.187221</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Z15" t="n">
         <v>1.805747</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AA15" t="n">
         <v>-0.6209170000000001</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AB15" t="n">
         <v>6.470016</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AC15" t="n">
         <v>6.517038</v>
       </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>6.460076</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
       </c>
       <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
         <v>0.12</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AI15" t="n">
         <v>0.12</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AJ15" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AK15" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -2041,90 +2113,96 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="G16" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H16" t="n">
         <v>100.7146</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>99.15031999999999</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>5.2941</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>5.2935</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>5285657</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>2130312</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>3155345</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>3.07</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>1.81</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>3.92</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>30.52</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>331505</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>-0.716776</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>-0.930689</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>0.705726</v>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
         <v>0.705806</v>
       </c>
-      <c r="W16" t="n">
+      <c r="X16" t="n">
         <v>1.335643</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Y16" t="n">
         <v>1.161333</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Z16" t="n">
         <v>1.453667</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AA16" t="n">
         <v>1.830463</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AB16" t="n">
         <v>5.900488</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AC16" t="n">
         <v>5.899363</v>
       </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>5.974439</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
         <v>0.03</v>
       </c>
       <c r="AI16" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AK16" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2148,90 +2226,96 @@
         <v>0.45</v>
       </c>
       <c r="G17" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H17" t="n">
         <v>100.58818</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>99.97037</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>5.2177</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>5.2171</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>5366069</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>2178236</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>3187833</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>3.07</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>1.8</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>3.94</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>29.64</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>324703</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>-0.125523</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>0.827078</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>-1.443116</v>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
         <v>-1.443279</v>
       </c>
-      <c r="W17" t="n">
+      <c r="X17" t="n">
         <v>1.521325</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Y17" t="n">
         <v>2.249624</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Z17" t="n">
         <v>1.029618</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AA17" t="n">
         <v>-2.051854</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AB17" t="n">
         <v>5.784842</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AC17" t="n">
         <v>5.458422</v>
       </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
       <c r="AD17" t="n">
+        <v>5.932356</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
         <v>-0</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AG17" t="n">
         <v>-0</v>
       </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AJ17" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AK17" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -2255,90 +2339,96 @@
         <v>0.21</v>
       </c>
       <c r="G18" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H18" t="n">
         <v>100.10988</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>95.09953</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>5.0993</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>5.0987</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>5373231</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>2151399</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>3221831</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>3.24</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>1.94</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>4.11</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>30.54</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>331122</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>-0.475503</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>-4.872284</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>-2.269199</v>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>-2.26946</v>
       </c>
-      <c r="W18" t="n">
+      <c r="X18" t="n">
         <v>0.133468</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Y18" t="n">
         <v>-1.232052</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Z18" t="n">
         <v>1.066493</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AA18" t="n">
         <v>1.976883</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AB18" t="n">
         <v>5.77432</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AC18" t="n">
         <v>3.79089</v>
       </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>5.711379</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
         <v>0.17</v>
       </c>
       <c r="AI18" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AK18" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2362,90 +2452,96 @@
         <v>-0.06</v>
       </c>
       <c r="G19" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H19" t="n">
         <v>103.07987</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>98.64798</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>5.2078</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>5.2072</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>5370950</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>2136105</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>3234845</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>3.36</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>2.17</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>4.16</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>30.48</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>328098</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>2.96673</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>3.731301</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>2.127743</v>
       </c>
-      <c r="V19" t="n">
+      <c r="W19" t="n">
         <v>2.127993</v>
       </c>
-      <c r="W19" t="n">
+      <c r="X19" t="n">
         <v>-0.042451</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Y19" t="n">
         <v>-0.710886</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="Z19" t="n">
         <v>0.403932</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AA19" t="n">
         <v>-0.913259</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AB19" t="n">
         <v>5.596302</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AC19" t="n">
         <v>1.864495</v>
       </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>5.47065</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
       </c>
       <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
         <v>0.12</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AI19" t="n">
         <v>0.23</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AJ19" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AK19" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2469,90 +2565,96 @@
         <v>0.05</v>
       </c>
       <c r="G20" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H20" t="n">
         <v>103.08494</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>110.61922</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>5.0804</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>5.0798</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>5424811</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>2154900</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>3269910</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>3.35</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>2.2</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>4.11</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>30.99</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>341158</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>0.004919</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>12.135312</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>-2.446331</v>
       </c>
-      <c r="V20" t="n">
+      <c r="W20" t="n">
         <v>-2.446612</v>
       </c>
-      <c r="W20" t="n">
+      <c r="X20" t="n">
         <v>1.002821</v>
       </c>
-      <c r="X20" t="n">
+      <c r="Y20" t="n">
         <v>0.879872</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="Z20" t="n">
         <v>1.083978</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AA20" t="n">
         <v>3.980518</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AB20" t="n">
         <v>4.650694</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AC20" t="n">
         <v>0.172427</v>
       </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>4.361088</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
       </c>
       <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AI20" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AJ20" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AK20" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2576,90 +2678,96 @@
         <v>-0.95</v>
       </c>
       <c r="G21" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H21" t="n">
         <v>103.93573</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>104.04095</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>5.0007</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>5.0001</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>5426307</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>2145000</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>3281308</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>3.54</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>2.45</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>4.26</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>31.62</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>345725</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>0.825329</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>-5.946769</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>-1.568774</v>
       </c>
-      <c r="V21" t="n">
+      <c r="W21" t="n">
         <v>-1.568959</v>
       </c>
-      <c r="W21" t="n">
+      <c r="X21" t="n">
         <v>0.027577</v>
       </c>
-      <c r="X21" t="n">
+      <c r="Y21" t="n">
         <v>-0.459418</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="Z21" t="n">
         <v>0.348572</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AA21" t="n">
         <v>1.338676</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AB21" t="n">
         <v>4.184706</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AC21" t="n">
         <v>-2.158772</v>
       </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.834324</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
       </c>
       <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
         <v>0.19</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AI21" t="n">
         <v>0.25</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AJ21" t="n">
         <v>0.15</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AK21" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -2683,90 +2791,96 @@
         <v>-1.84</v>
       </c>
       <c r="G22" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H22" t="n">
         <v>102.42973</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>102.71375</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>5.0959</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>5.0953</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>5453708</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>2145530</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>3308178</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>3.65</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>2.58</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>4.35</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>31.63</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>343489</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>-1.448972</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>-1.275652</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>1.903733</v>
       </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
         <v>1.903962</v>
       </c>
-      <c r="W22" t="n">
+      <c r="X22" t="n">
         <v>0.504966</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Y22" t="n">
         <v>0.024709</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="Z22" t="n">
         <v>0.818881</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AA22" t="n">
         <v>-0.646757</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AB22" t="n">
         <v>3.935832</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AC22" t="n">
         <v>-4.45588</v>
       </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
       <c r="AD22" t="n">
+        <v>3.741292</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
         <v>-0</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AG22" t="n">
         <v>-0</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AH22" t="n">
         <v>0.11</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AI22" t="n">
         <v>0.13</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AJ22" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI22" t="n">
+      <c r="AK22" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -2790,90 +2904,96 @@
         <v>-1.93</v>
       </c>
       <c r="G23" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="H23" t="n">
         <v>102.39935</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>102.28352</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>4.8192</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>4.8186</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>5479459</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>2169613</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>3309846</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>3.61</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>2.63</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>4.25</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>30.85</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>343620</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>-0.029659</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>-0.418863</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>-5.429855</v>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
         <v>-5.430495</v>
       </c>
-      <c r="W23" t="n">
+      <c r="X23" t="n">
         <v>0.472174</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Y23" t="n">
         <v>1.122473</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="Z23" t="n">
         <v>0.050421</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AA23" t="n">
         <v>0.038138</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AB23" t="n">
         <v>3.161501</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AC23" t="n">
         <v>-6.84947</v>
       </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.998957</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
       </c>
       <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AI23" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AJ23" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AK23" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -2897,90 +3017,96 @@
         <v>-0.72</v>
       </c>
       <c r="G24" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="H24" t="n">
         <v>102.90686</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>105.34474</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>4.7415</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>4.7409</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>5484871</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>2153541</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>3331330</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>3.63</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>2.73</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>4.22</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>30.43</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>345476</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>0.495618</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>2.992877</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>-1.612301</v>
       </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
         <v>-1.612502</v>
       </c>
-      <c r="W24" t="n">
+      <c r="X24" t="n">
         <v>0.098769</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Y24" t="n">
         <v>-0.740777</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="Z24" t="n">
         <v>0.6490939999999999</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AA24" t="n">
         <v>0.5401319999999999</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AB24" t="n">
         <v>3.992444</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AC24" t="n">
         <v>-7.713954</v>
       </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>3.527423</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
       </c>
       <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AI24" t="n">
         <v>0.1</v>
       </c>
-      <c r="AH24" t="n">
+      <c r="AJ24" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AK24" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3004,90 +3130,96 @@
         <v>-0.14</v>
       </c>
       <c r="G25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H25" t="n">
         <v>102.50239</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>106.05687</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>4.9219</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>4.9213</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5559063</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>2172658</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>3386405</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>3.61</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>2.82</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>4.12</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>29.92</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>344177</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>-0.393045</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>0.676</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>3.804703</v>
       </c>
-      <c r="V25" t="n">
+      <c r="W25" t="n">
         <v>3.805185</v>
       </c>
-      <c r="W25" t="n">
+      <c r="X25" t="n">
         <v>1.352666</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Y25" t="n">
         <v>0.887701</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="Z25" t="n">
         <v>1.653244</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AA25" t="n">
         <v>-0.376003</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AB25" t="n">
         <v>4.608216</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AC25" t="n">
         <v>-7.193509</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AD25" t="n">
+        <v>4.057054</v>
+      </c>
+      <c r="AE25" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AF25" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AG25" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AH25" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AI25" t="n">
         <v>0.09</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AJ25" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="AK25" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -3111,90 +3243,96 @@
         <v>0.37</v>
       </c>
       <c r="G26" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H26" t="n">
         <v>102.5153</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>101.75897</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>5.0076</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>5.007</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>5625945</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>2215175</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>3410769</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>3.54</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>2.82</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>4</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>29.66</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>340324</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>0.012595</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>-4.052448</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>1.741198</v>
       </c>
-      <c r="V26" t="n">
+      <c r="W26" t="n">
         <v>1.74141</v>
       </c>
-      <c r="W26" t="n">
+      <c r="X26" t="n">
         <v>1.203116</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Y26" t="n">
         <v>1.956912</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="Z26" t="n">
         <v>0.719465</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AA26" t="n">
         <v>-1.119482</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AB26" t="n">
         <v>5.185235</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AC26" t="n">
         <v>-5.956714</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AD26" t="n">
+        <v>4.505936</v>
+      </c>
+      <c r="AE26" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AF26" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AG26" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="AF26" t="n">
+      <c r="AH26" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AK26" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -3218,90 +3356,96 @@
         <v>0.5</v>
       </c>
       <c r="G27" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H27" t="n">
         <v>102.83959</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>101.9338</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>5.0575</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>5.0569</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>5653808</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>2204808</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>3449000</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>3.56</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>2.92</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>3.97</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>29.24</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>340247</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>0.316333</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>0.171808</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>0.996485</v>
       </c>
-      <c r="V27" t="n">
+      <c r="W27" t="n">
         <v>0.996605</v>
       </c>
-      <c r="W27" t="n">
+      <c r="X27" t="n">
         <v>0.495259</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Y27" t="n">
         <v>-0.467999</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="Z27" t="n">
         <v>1.120891</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AA27" t="n">
         <v>-0.022625</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AB27" t="n">
         <v>4.819246</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AC27" t="n">
         <v>-4.560737</v>
       </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
       <c r="AD27" t="n">
+        <v>4.141877</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AG27" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AH27" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AI27" t="n">
         <v>0.1</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="AJ27" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AK27" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3325,90 +3469,96 @@
         <v>0.59</v>
       </c>
       <c r="G28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H28" t="n">
         <v>103.59456</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>101.68042</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>4.9355</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>4.9349</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>5711103</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>2220766</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>3490337</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>3.53</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>2.99</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>3.88</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>29.01</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>348406</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>0.734124</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>-0.248573</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>-2.412259</v>
       </c>
-      <c r="V28" t="n">
+      <c r="W28" t="n">
         <v>-2.412545</v>
       </c>
-      <c r="W28" t="n">
+      <c r="X28" t="n">
         <v>1.013388</v>
       </c>
-      <c r="X28" t="n">
+      <c r="Y28" t="n">
         <v>0.723782</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="Z28" t="n">
         <v>1.198521</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AA28" t="n">
         <v>2.397964</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AB28" t="n">
         <v>4.683537</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AC28" t="n">
         <v>-3.457004</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AD28" t="n">
+        <v>3.851383</v>
+      </c>
+      <c r="AE28" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AF28" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AG28" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AH28" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AI28" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AH28" t="n">
+      <c r="AJ28" t="n">
         <v>-0.09</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AK28" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -3432,90 +3582,96 @@
         <v>0.74</v>
       </c>
       <c r="G29" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H29" t="n">
         <v>104.88818</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>101.68469</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>4.8413</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>4.8407</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>5805157</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>2283485</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>3521672</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>3.29</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>2.59</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>28.14</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>355034</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>1.248734</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>0.004199</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>-1.908621</v>
       </c>
-      <c r="V29" t="n">
+      <c r="W29" t="n">
         <v>-1.908853</v>
       </c>
-      <c r="W29" t="n">
+      <c r="X29" t="n">
         <v>1.646862</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Y29" t="n">
         <v>2.824206</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="Z29" t="n">
         <v>0.897764</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AA29" t="n">
         <v>1.902378</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AB29" t="n">
         <v>4.621114</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AC29" t="n">
         <v>-3.178284</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AD29" t="n">
+        <v>3.706988</v>
+      </c>
+      <c r="AE29" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AF29" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AG29" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AH29" t="n">
         <v>-0.24</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AI29" t="n">
         <v>-0.4</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AJ29" t="n">
         <v>-0.13</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AK29" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3539,90 +3695,96 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G30" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H30" t="n">
         <v>104.473</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>99.29718</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>4.9535</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>4.9529</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>5794707</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>2234362</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3560345</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>3.38</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2.77</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>3.76</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>28</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>355066</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>-0.395831</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>-2.347954</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>2.317559</v>
       </c>
-      <c r="V30" t="n">
+      <c r="W30" t="n">
         <v>2.317847</v>
       </c>
-      <c r="W30" t="n">
+      <c r="X30" t="n">
         <v>-0.180012</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Y30" t="n">
         <v>-2.151229</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="Z30" t="n">
         <v>1.098143</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AA30" t="n">
         <v>0.009013</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AB30" t="n">
         <v>4.506637</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AC30" t="n">
         <v>-3.31355</v>
       </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
       <c r="AD30" t="n">
+        <v>3.820543</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AG30" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AH30" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AI30" t="n">
         <v>0.18</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AJ30" t="n">
         <v>0.01</v>
       </c>
-      <c r="AI30" t="n">
+      <c r="AK30" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -3646,90 +3808,96 @@
         <v>-0.52</v>
       </c>
       <c r="G31" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H31" t="n">
         <v>104.65885</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>102.15036</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>4.9833</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>4.9827</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>5815954</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>2235302</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>3580652</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>3.38</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>2.76</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>3.76</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>27.85</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>352705</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>0.177893</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>2.873375</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>0.601595</v>
       </c>
-      <c r="V31" t="n">
+      <c r="W31" t="n">
         <v>0.601668</v>
       </c>
-      <c r="W31" t="n">
+      <c r="X31" t="n">
         <v>0.366662</v>
       </c>
-      <c r="X31" t="n">
+      <c r="Y31" t="n">
         <v>0.04207</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="Z31" t="n">
         <v>0.570366</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AA31" t="n">
         <v>-0.664947</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AB31" t="n">
         <v>4.496274</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AC31" t="n">
         <v>-3.758575</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AD31" t="n">
+        <v>3.861754</v>
+      </c>
+      <c r="AE31" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AF31" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AG31" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -3753,90 +3921,96 @@
         <v>-0.47</v>
       </c>
       <c r="G32" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H32" t="n">
         <v>104.6738</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>109.56901</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>4.9962</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>4.9956</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>5899742</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>2285775</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>3613967</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>3.33</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>2.71</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>28.14</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>355008</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>0.014285</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>7.262481</v>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
         <v>0.258865</v>
       </c>
-      <c r="V32" t="n">
+      <c r="W32" t="n">
         <v>0.258896</v>
       </c>
-      <c r="W32" t="n">
+      <c r="X32" t="n">
         <v>1.440658</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Y32" t="n">
         <v>2.257995</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="Z32" t="n">
         <v>0.930417</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AA32" t="n">
         <v>0.652954</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AB32" t="n">
         <v>3.925596</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AC32" t="n">
         <v>-4.25878</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AD32" t="n">
+        <v>3.397348</v>
+      </c>
+      <c r="AE32" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AF32" t="n">
         <v>-0.000537</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AG32" t="n">
         <v>-0.000537</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>-0.05</v>
       </c>
       <c r="AH32" t="n">
         <v>-0.05</v>
       </c>
       <c r="AI32" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK32" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -3860,90 +4034,96 @@
         <v>0.31</v>
       </c>
       <c r="G33" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H33" t="n">
         <v>104.62771</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>109.2572</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>5.1718</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>5.1712</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5915538</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>2268879</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3646659</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>3.37</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>2.76</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>27.86</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>351599</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>-0.044032</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
         <v>-0.284579</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>3.514671</v>
       </c>
-      <c r="V33" t="n">
+      <c r="W33" t="n">
         <v>3.515093</v>
       </c>
-      <c r="W33" t="n">
+      <c r="X33" t="n">
         <v>0.267741</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Y33" t="n">
         <v>-0.7391799999999999</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="Z33" t="n">
         <v>0.904602</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AA33" t="n">
         <v>-0.96026</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AB33" t="n">
         <v>3.688016</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AC33" t="n">
         <v>-3.040871</v>
       </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
       <c r="AD33" t="n">
+        <v>3.232784</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
         <v>-0.001252</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AG33" t="n">
         <v>-0.001252</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0.05</v>
       </c>
       <c r="AH33" t="n">
         <v>0.04</v>
       </c>
       <c r="AI33" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK33" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -3967,90 +4147,96 @@
         <v>0.89</v>
       </c>
       <c r="G34" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H34" t="n">
         <v>105.60427</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>104.71213</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>5.2416</v>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>5.241</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>5953960</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>2278309</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>3675652</v>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>3.43</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>2.8</v>
       </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
         <v>3.82</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>27.75</v>
       </c>
-      <c r="R34" t="n">
+      <c r="S34" t="n">
         <v>355560</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>0.9333669999999999</v>
       </c>
-      <c r="T34" t="n">
+      <c r="U34" t="n">
         <v>-4.159973</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>1.349627</v>
       </c>
-      <c r="V34" t="n">
+      <c r="W34" t="n">
         <v>1.349783</v>
       </c>
-      <c r="W34" t="n">
+      <c r="X34" t="n">
         <v>0.64951</v>
       </c>
-      <c r="X34" t="n">
+      <c r="Y34" t="n">
         <v>0.415624</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="Z34" t="n">
         <v>0.795057</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AA34" t="n">
         <v>1.126567</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AB34" t="n">
         <v>3.925952</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AC34" t="n">
         <v>-0.344269</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AD34" t="n">
+        <v>3.335647</v>
+      </c>
+      <c r="AE34" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AF34" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="AE34" t="n">
+      <c r="AG34" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="AF34" t="n">
+      <c r="AH34" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG34" t="n">
+      <c r="AI34" t="n">
         <v>0.04</v>
       </c>
-      <c r="AH34" t="n">
+      <c r="AJ34" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI34" t="n">
+      <c r="AK34" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -4074,90 +4260,96 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="G35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H35" t="n">
         <v>106.5891</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>105.86915</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>5.5589</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>5.5583</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>6041898</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>2336858</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>3705041</v>
       </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>3.29</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>2.64</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>27.81</v>
       </c>
-      <c r="R35" t="n">
+      <c r="S35" t="n">
         <v>357827</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>0.932566</v>
       </c>
-      <c r="T35" t="n">
+      <c r="U35" t="n">
         <v>1.104953</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>6.053495</v>
       </c>
-      <c r="V35" t="n">
+      <c r="W35" t="n">
         <v>6.054188</v>
       </c>
-      <c r="W35" t="n">
+      <c r="X35" t="n">
         <v>1.476967</v>
       </c>
-      <c r="X35" t="n">
+      <c r="Y35" t="n">
         <v>2.569845</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="Z35" t="n">
         <v>0.799559</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AA35" t="n">
         <v>0.637586</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AB35" t="n">
         <v>4.227578</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AC35" t="n">
         <v>2.440035</v>
       </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
       <c r="AD35" t="n">
+        <v>3.697684</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="AE35" t="n">
+      <c r="AG35" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="AF35" t="n">
+      <c r="AH35" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AI35" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AH35" t="n">
+      <c r="AJ35" t="n">
         <v>-0.11</v>
       </c>
-      <c r="AI35" t="n">
+      <c r="AK35" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -4181,90 +4373,96 @@
         <v>0.61</v>
       </c>
       <c r="G36" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H36" t="n">
         <v>107.06237</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>111.509</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>5.6621</v>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>5.6615</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>6069205</v>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>2323362</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>3745844</v>
       </c>
-      <c r="N36" t="n">
+      <c r="O36" t="n">
         <v>3.3</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>2.52</v>
       </c>
-      <c r="P36" t="n">
+      <c r="Q36" t="n">
         <v>3.78</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>27.74</v>
       </c>
-      <c r="R36" t="n">
+      <c r="S36" t="n">
         <v>363282</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>0.444014</v>
       </c>
-      <c r="T36" t="n">
+      <c r="U36" t="n">
         <v>5.327189</v>
       </c>
-      <c r="U36" t="n">
+      <c r="V36" t="n">
         <v>1.856482</v>
       </c>
-      <c r="V36" t="n">
+      <c r="W36" t="n">
         <v>1.856683</v>
       </c>
-      <c r="W36" t="n">
+      <c r="X36" t="n">
         <v>0.451961</v>
       </c>
-      <c r="X36" t="n">
+      <c r="Y36" t="n">
         <v>-0.577528</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="Z36" t="n">
         <v>1.101283</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AA36" t="n">
         <v>1.52448</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AB36" t="n">
         <v>4.498245</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AC36" t="n">
         <v>3.812368</v>
       </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>4.060953</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
       </c>
       <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
         <v>0.01</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AI36" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AH36" t="n">
+      <c r="AJ36" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI36" t="n">
+      <c r="AK36" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -4288,90 +4486,96 @@
         <v>0.29</v>
       </c>
       <c r="G37" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="H37" t="n">
         <v>107.19174</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>110.06254</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>5.6562</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>5.6556</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6135298</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>2344397</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>3790900</v>
       </c>
-      <c r="N37" t="n">
+      <c r="O37" t="n">
         <v>3.33</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>2.55</v>
       </c>
-      <c r="P37" t="n">
+      <c r="Q37" t="n">
         <v>3.82</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>27.59</v>
       </c>
-      <c r="R37" t="n">
+      <c r="S37" t="n">
         <v>369214</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>0.120836</v>
       </c>
-      <c r="T37" t="n">
+      <c r="U37" t="n">
         <v>-1.297169</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>-0.104202</v>
       </c>
-      <c r="V37" t="n">
+      <c r="W37" t="n">
         <v>-0.104213</v>
       </c>
-      <c r="W37" t="n">
+      <c r="X37" t="n">
         <v>1.088989</v>
       </c>
-      <c r="X37" t="n">
+      <c r="Y37" t="n">
         <v>0.905369</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="Z37" t="n">
         <v>1.202826</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AA37" t="n">
         <v>1.632891</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AB37" t="n">
         <v>4.237599</v>
       </c>
-      <c r="AB37" t="n">
+      <c r="AC37" t="n">
         <v>4.259387</v>
       </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>3.707852</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
       </c>
       <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AI37" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH37" t="n">
+      <c r="AJ37" t="n">
         <v>0.04</v>
       </c>
-      <c r="AI37" t="n">
+      <c r="AK37" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4395,90 +4599,96 @@
         <v>0.62</v>
       </c>
       <c r="G38" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H38" t="n">
         <v>108.04382</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>107.07852</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>5.4481</v>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>5.4475</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>6216528</v>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>2384828</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>3831700</v>
       </c>
-      <c r="N38" t="n">
+      <c r="O38" t="n">
         <v>3.34</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>2.56</v>
       </c>
-      <c r="P38" t="n">
+      <c r="Q38" t="n">
         <v>3.83</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>27.49</v>
       </c>
-      <c r="R38" t="n">
+      <c r="S38" t="n">
         <v>372016</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>0.794912</v>
       </c>
-      <c r="T38" t="n">
+      <c r="U38" t="n">
         <v>-2.711204</v>
       </c>
-      <c r="U38" t="n">
+      <c r="V38" t="n">
         <v>-3.679149</v>
       </c>
-      <c r="V38" t="n">
+      <c r="W38" t="n">
         <v>-3.679539</v>
       </c>
-      <c r="W38" t="n">
+      <c r="X38" t="n">
         <v>1.323978</v>
       </c>
-      <c r="X38" t="n">
+      <c r="Y38" t="n">
         <v>1.72458</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="Z38" t="n">
         <v>1.076262</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AA38" t="n">
         <v>0.7589089999999999</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AB38" t="n">
         <v>4.42474</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AC38" t="n">
         <v>4.519075</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AD38" t="n">
+        <v>4.091149</v>
+      </c>
+      <c r="AE38" t="n">
         <v>0.25</v>
       </c>
-      <c r="AD38" t="n">
+      <c r="AF38" t="n">
         <v>0.000342</v>
       </c>
-      <c r="AE38" t="n">
+      <c r="AG38" t="n">
         <v>0.000342</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0.01</v>
       </c>
       <c r="AH38" t="n">
         <v>0.01</v>
       </c>
       <c r="AI38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AK38" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -4502,90 +4712,96 @@
         <v>1.52</v>
       </c>
       <c r="G39" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H39" t="n">
         <v>108.2446</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>109.18379</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>5.7779</v>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>5.7773</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>6275117</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>2397533</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>3877584</v>
       </c>
-      <c r="N39" t="n">
+      <c r="O39" t="n">
         <v>3.3</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>2.52</v>
       </c>
-      <c r="P39" t="n">
+      <c r="Q39" t="n">
         <v>3.79</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>27.94</v>
       </c>
-      <c r="R39" t="n">
+      <c r="S39" t="n">
         <v>366096</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>0.185832</v>
       </c>
-      <c r="T39" t="n">
+      <c r="U39" t="n">
         <v>1.966099</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>6.053487</v>
       </c>
-      <c r="V39" t="n">
+      <c r="W39" t="n">
         <v>6.054153</v>
       </c>
-      <c r="W39" t="n">
+      <c r="X39" t="n">
         <v>0.9424709999999999</v>
       </c>
-      <c r="X39" t="n">
+      <c r="Y39" t="n">
         <v>0.532743</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="Z39" t="n">
         <v>1.197484</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AA39" t="n">
         <v>-1.591329</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AB39" t="n">
         <v>4.758099</v>
       </c>
-      <c r="AB39" t="n">
+      <c r="AC39" t="n">
         <v>5.579866</v>
       </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
       <c r="AD39" t="n">
+        <v>4.600584</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
         <v>0.000556</v>
       </c>
-      <c r="AE39" t="n">
+      <c r="AG39" t="n">
         <v>0.000556</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>-0.04</v>
       </c>
       <c r="AH39" t="n">
         <v>-0.04</v>
       </c>
       <c r="AI39" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AK39" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -4609,90 +4825,96 @@
         <v>1.3</v>
       </c>
       <c r="G40" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H40" t="n">
         <v>108.00109</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>105.49006</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>6.0535</v>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>6.0529</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>6365690</v>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
         <v>2436022</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>3929668</v>
       </c>
-      <c r="N40" t="n">
+      <c r="O40" t="n">
         <v>3.27</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>2.5</v>
       </c>
-      <c r="P40" t="n">
+      <c r="Q40" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>28.45</v>
       </c>
-      <c r="R40" t="n">
+      <c r="S40" t="n">
         <v>363003</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>-0.224963</v>
       </c>
-      <c r="T40" t="n">
+      <c r="U40" t="n">
         <v>-3.383039</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>4.769899</v>
       </c>
-      <c r="V40" t="n">
+      <c r="W40" t="n">
         <v>4.770394</v>
       </c>
-      <c r="W40" t="n">
+      <c r="X40" t="n">
         <v>1.443368</v>
       </c>
-      <c r="X40" t="n">
+      <c r="Y40" t="n">
         <v>1.605359</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="Z40" t="n">
         <v>1.343208</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AA40" t="n">
         <v>-0.8448600000000001</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AB40" t="n">
         <v>4.873011</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AC40" t="n">
         <v>6.325086</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AD40" t="n">
+        <v>4.840925</v>
+      </c>
+      <c r="AE40" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AF40" t="n">
         <v>0.001412</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AG40" t="n">
         <v>0.001412</v>
       </c>
-      <c r="AF40" t="n">
+      <c r="AH40" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG40" t="n">
+      <c r="AI40" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AH40" t="n">
+      <c r="AJ40" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AI40" t="n">
+      <c r="AK40" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4716,90 +4938,96 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="G41" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H41" t="n">
         <v>107.37012</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>104.15552</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>6.1923</v>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>6.1917</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>6464602</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>2499177</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>3965425</v>
       </c>
-      <c r="N41" t="n">
+      <c r="O41" t="n">
         <v>3.08</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>2.21</v>
       </c>
-      <c r="P41" t="n">
+      <c r="Q41" t="n">
         <v>3.63</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>28.5</v>
       </c>
-      <c r="R41" t="n">
+      <c r="S41" t="n">
         <v>329730</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>-0.584226</v>
       </c>
-      <c r="T41" t="n">
+      <c r="U41" t="n">
         <v>-1.265086</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>2.292888</v>
       </c>
-      <c r="V41" t="n">
+      <c r="W41" t="n">
         <v>2.293116</v>
       </c>
-      <c r="W41" t="n">
+      <c r="X41" t="n">
         <v>1.55383</v>
       </c>
-      <c r="X41" t="n">
+      <c r="Y41" t="n">
         <v>2.592546</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="Z41" t="n">
         <v>0.909924</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AA41" t="n">
         <v>-9.166040000000001</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AB41" t="n">
         <v>4.831296</v>
       </c>
-      <c r="AB41" t="n">
+      <c r="AC41" t="n">
         <v>6.536174</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AD41" t="n">
+        <v>4.767938</v>
+      </c>
+      <c r="AE41" t="n">
         <v>1</v>
       </c>
-      <c r="AD41" t="n">
+      <c r="AF41" t="n">
         <v>0.002578</v>
       </c>
-      <c r="AE41" t="n">
+      <c r="AG41" t="n">
         <v>0.002578</v>
       </c>
-      <c r="AF41" t="n">
+      <c r="AH41" t="n">
         <v>-0.19</v>
       </c>
-      <c r="AG41" t="n">
+      <c r="AI41" t="n">
         <v>-0.29</v>
       </c>
-      <c r="AH41" t="n">
+      <c r="AJ41" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AI41" t="n">
+      <c r="AK41" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -4823,90 +5051,96 @@
         <v>0.27</v>
       </c>
       <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
         <v>108.09524</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>102.62949</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>5.8301</v>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>5.8295</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>6465016</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>2451957</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>4013059</v>
       </c>
-      <c r="N42" t="n">
+      <c r="O42" t="n">
         <v>3.34</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>2.43</v>
       </c>
-      <c r="P42" t="n">
+      <c r="Q42" t="n">
         <v>3.89</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>29.88</v>
       </c>
-      <c r="R42" t="n">
+      <c r="S42" t="n">
         <v>328303</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>0.675346</v>
       </c>
-      <c r="T42" t="n">
+      <c r="U42" t="n">
         <v>-1.465146</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>-5.8492</v>
       </c>
-      <c r="V42" t="n">
+      <c r="W42" t="n">
         <v>-5.849767</v>
       </c>
-      <c r="W42" t="n">
+      <c r="X42" t="n">
         <v>0.006404</v>
       </c>
-      <c r="X42" t="n">
+      <c r="Y42" t="n">
         <v>-1.889422</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="Z42" t="n">
         <v>1.201233</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AA42" t="n">
         <v>-0.432778</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AB42" t="n">
         <v>4.559874</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AC42" t="n">
         <v>6.749097</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AD42" t="n">
+        <v>4.174145</v>
+      </c>
+      <c r="AE42" t="n">
         <v>1</v>
       </c>
-      <c r="AD42" t="n">
+      <c r="AF42" t="n">
         <v>0.001675</v>
       </c>
-      <c r="AE42" t="n">
+      <c r="AG42" t="n">
         <v>0.001675</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0.22</v>
       </c>
       <c r="AH42" t="n">
         <v>0.26</v>
       </c>
       <c r="AI42" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AK42" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -4930,90 +5164,96 @@
         <v>1.06</v>
       </c>
       <c r="G43" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H43" t="n">
         <v>108.62006</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>106.82599</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>5.8488</v>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
         <v>5.8482</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>6511444</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>2477151</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>4034293</v>
       </c>
-      <c r="N43" t="n">
+      <c r="O43" t="n">
         <v>3.41</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2.52</v>
       </c>
-      <c r="P43" t="n">
+      <c r="Q43" t="n">
         <v>3.96</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>30.53</v>
       </c>
-      <c r="R43" t="n">
+      <c r="S43" t="n">
         <v>332508</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>0.485516</v>
       </c>
-      <c r="T43" t="n">
+      <c r="U43" t="n">
         <v>4.088981</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>0.320749</v>
       </c>
-      <c r="V43" t="n">
+      <c r="W43" t="n">
         <v>0.320782</v>
       </c>
-      <c r="W43" t="n">
+      <c r="X43" t="n">
         <v>0.7181419999999999</v>
       </c>
-      <c r="X43" t="n">
+      <c r="Y43" t="n">
         <v>1.027506</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="Z43" t="n">
         <v>0.529123</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="AA43" t="n">
         <v>1.280829</v>
       </c>
-      <c r="AA43" t="n">
+      <c r="AB43" t="n">
         <v>5.05763</v>
       </c>
-      <c r="AB43" t="n">
+      <c r="AC43" t="n">
         <v>8.444549</v>
       </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
       <c r="AD43" t="n">
+        <v>4.866504</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
         <v>0.003204</v>
       </c>
-      <c r="AE43" t="n">
+      <c r="AG43" t="n">
         <v>0.003204</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0.09</v>
       </c>
       <c r="AH43" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AI43" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AK43" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -5037,90 +5277,96 @@
         <v>-0.34</v>
       </c>
       <c r="G44" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H44" t="n">
         <v>110.03287</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>114.02067</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>5.7422</v>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>5.7416</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>6576464</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>2498262</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>4078202</v>
       </c>
-      <c r="N44" t="n">
+      <c r="O44" t="n">
         <v>3.44</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>2.49</v>
       </c>
-      <c r="P44" t="n">
+      <c r="Q44" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>31.34</v>
       </c>
-      <c r="R44" t="n">
+      <c r="S44" t="n">
         <v>336157</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>1.30069</v>
       </c>
-      <c r="T44" t="n">
+      <c r="U44" t="n">
         <v>6.734953</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>-1.822596</v>
       </c>
-      <c r="V44" t="n">
+      <c r="W44" t="n">
         <v>-1.822783</v>
       </c>
-      <c r="W44" t="n">
+      <c r="X44" t="n">
         <v>0.99855</v>
       </c>
-      <c r="X44" t="n">
+      <c r="Y44" t="n">
         <v>0.852229</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="Z44" t="n">
         <v>1.088394</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AA44" t="n">
         <v>1.097417</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AB44" t="n">
         <v>5.47719</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="AC44" t="n">
         <v>8.586193</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AD44" t="n">
+        <v>5.201441</v>
+      </c>
+      <c r="AE44" t="n">
         <v>1</v>
       </c>
-      <c r="AD44" t="n">
+      <c r="AF44" t="n">
         <v>0.001471</v>
       </c>
-      <c r="AE44" t="n">
+      <c r="AG44" t="n">
         <v>0.001471</v>
       </c>
-      <c r="AF44" t="n">
+      <c r="AH44" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG44" t="n">
+      <c r="AI44" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AH44" t="n">
+      <c r="AJ44" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI44" t="n">
+      <c r="AK44" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -5144,90 +5390,96 @@
         <v>0.24</v>
       </c>
       <c r="G45" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H45" t="n">
         <v>109.52766</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>112.59512</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>5.6608</v>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>5.6602</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>6623948</v>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" t="n">
         <v>2512426</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>4111522</v>
       </c>
-      <c r="N45" t="n">
+      <c r="O45" t="n">
         <v>3.67</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>2.72</v>
       </c>
-      <c r="P45" t="n">
+      <c r="Q45" t="n">
         <v>4.25</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>31.63</v>
       </c>
-      <c r="R45" t="n">
+      <c r="S45" t="n">
         <v>340789</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>-0.459145</v>
       </c>
-      <c r="T45" t="n">
+      <c r="U45" t="n">
         <v>-1.250256</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>-1.417575</v>
       </c>
-      <c r="V45" t="n">
+      <c r="W45" t="n">
         <v>-1.417723</v>
       </c>
-      <c r="W45" t="n">
+      <c r="X45" t="n">
         <v>0.722029</v>
       </c>
-      <c r="X45" t="n">
+      <c r="Y45" t="n">
         <v>0.566954</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="Z45" t="n">
         <v>0.8170269999999999</v>
       </c>
-      <c r="Z45" t="n">
+      <c r="AA45" t="n">
         <v>1.377928</v>
       </c>
-      <c r="AA45" t="n">
+      <c r="AB45" t="n">
         <v>5.529729</v>
       </c>
-      <c r="AB45" t="n">
+      <c r="AC45" t="n">
         <v>8.510418</v>
       </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
       <c r="AD45" t="n">
+        <v>5.316736</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
         <v>0.002023</v>
       </c>
-      <c r="AE45" t="n">
+      <c r="AG45" t="n">
         <v>0.002023</v>
       </c>
-      <c r="AF45" t="n">
+      <c r="AH45" t="n">
         <v>0.23</v>
       </c>
-      <c r="AG45" t="n">
+      <c r="AI45" t="n">
         <v>0.23</v>
       </c>
-      <c r="AH45" t="n">
+      <c r="AJ45" t="n">
         <v>0.22</v>
       </c>
-      <c r="AI45" t="n">
+      <c r="AK45" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -5251,90 +5503,96 @@
         <v>-0.49</v>
       </c>
       <c r="G46" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H46" t="n">
         <v>108.8862</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>108.55704</v>
       </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
         <v>5.7087</v>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>5.7081</v>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
         <v>6666287</v>
       </c>
-      <c r="L46" t="n">
+      <c r="M46" t="n">
         <v>2532708</v>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
         <v>4133579</v>
       </c>
-      <c r="N46" t="n">
+      <c r="O46" t="n">
         <v>3.72</v>
       </c>
-      <c r="O46" t="n">
+      <c r="P46" t="n">
         <v>2.67</v>
       </c>
-      <c r="P46" t="n">
+      <c r="Q46" t="n">
         <v>4.36</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="R46" t="n">
         <v>31.7</v>
       </c>
-      <c r="R46" t="n">
+      <c r="S46" t="n">
         <v>341459</v>
       </c>
-      <c r="S46" t="n">
+      <c r="T46" t="n">
         <v>-0.58566</v>
       </c>
-      <c r="T46" t="n">
+      <c r="U46" t="n">
         <v>-3.586372</v>
       </c>
-      <c r="U46" t="n">
+      <c r="V46" t="n">
         <v>0.84617</v>
       </c>
-      <c r="V46" t="n">
+      <c r="W46" t="n">
         <v>0.84626</v>
       </c>
-      <c r="W46" t="n">
+      <c r="X46" t="n">
         <v>0.639181</v>
       </c>
-      <c r="X46" t="n">
+      <c r="Y46" t="n">
         <v>0.807268</v>
       </c>
-      <c r="Y46" t="n">
+      <c r="Z46" t="n">
         <v>0.5364679999999999</v>
       </c>
-      <c r="Z46" t="n">
+      <c r="AA46" t="n">
         <v>0.196603</v>
       </c>
-      <c r="AA46" t="n">
+      <c r="AB46" t="n">
         <v>5.319636</v>
       </c>
-      <c r="AB46" t="n">
+      <c r="AC46" t="n">
         <v>7.026183</v>
       </c>
-      <c r="AC46" t="n">
+      <c r="AD46" t="n">
+        <v>5.201418</v>
+      </c>
+      <c r="AE46" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD46" t="n">
+      <c r="AF46" t="n">
         <v>0.001405</v>
       </c>
-      <c r="AE46" t="n">
+      <c r="AG46" t="n">
         <v>0.001405</v>
       </c>
-      <c r="AF46" t="n">
+      <c r="AH46" t="n">
         <v>0.05</v>
       </c>
-      <c r="AG46" t="n">
+      <c r="AI46" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH46" t="n">
+      <c r="AJ46" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI46" t="n">
+      <c r="AK46" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5358,90 +5616,96 @@
         <v>-1.67</v>
       </c>
       <c r="G47" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H47" t="n">
         <v>108.80376</v>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>107.36219</v>
       </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
         <v>5.4571</v>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>5.4565</v>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>6703663</v>
       </c>
-      <c r="L47" t="n">
+      <c r="M47" t="n">
         <v>2547693</v>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
         <v>4155970</v>
       </c>
-      <c r="N47" t="n">
+      <c r="O47" t="n">
         <v>3.75</v>
       </c>
-      <c r="O47" t="n">
+      <c r="P47" t="n">
         <v>2.67</v>
       </c>
-      <c r="P47" t="n">
+      <c r="Q47" t="n">
         <v>4.41</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="R47" t="n">
         <v>31.85</v>
       </c>
-      <c r="R47" t="n">
+      <c r="S47" t="n">
         <v>344440</v>
       </c>
-      <c r="S47" t="n">
+      <c r="T47" t="n">
         <v>-0.075712</v>
       </c>
-      <c r="T47" t="n">
+      <c r="U47" t="n">
         <v>-1.100666</v>
       </c>
-      <c r="U47" t="n">
+      <c r="V47" t="n">
         <v>-4.407308</v>
       </c>
-      <c r="V47" t="n">
+      <c r="W47" t="n">
         <v>-4.407771</v>
       </c>
-      <c r="W47" t="n">
+      <c r="X47" t="n">
         <v>0.5606719999999999</v>
       </c>
-      <c r="X47" t="n">
+      <c r="Y47" t="n">
         <v>0.591659</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="Z47" t="n">
         <v>0.541686</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="AA47" t="n">
         <v>0.873018</v>
       </c>
-      <c r="AA47" t="n">
+      <c r="AB47" t="n">
         <v>5.351165</v>
       </c>
-      <c r="AB47" t="n">
+      <c r="AC47" t="n">
         <v>4.393261</v>
       </c>
-      <c r="AC47" t="n">
+      <c r="AD47" t="n">
+        <v>5.18043</v>
+      </c>
+      <c r="AE47" t="n">
         <v>0.25</v>
       </c>
-      <c r="AD47" t="n">
+      <c r="AF47" t="n">
         <v>0.000633</v>
       </c>
-      <c r="AE47" t="n">
+      <c r="AG47" t="n">
         <v>0.000633</v>
       </c>
-      <c r="AF47" t="n">
+      <c r="AH47" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="n">
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI47" t="n">
+      <c r="AK47" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5465,90 +5729,96 @@
         <v>-0.77</v>
       </c>
       <c r="G48" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H48" t="n">
         <v>108.49869</v>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>113.10928</v>
       </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
         <v>5.6021</v>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
         <v>5.6015</v>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" t="n">
         <v>6733209</v>
       </c>
-      <c r="L48" t="n">
+      <c r="M48" t="n">
         <v>2544400</v>
       </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
         <v>4188808</v>
       </c>
-      <c r="N48" t="n">
+      <c r="O48" t="n">
         <v>3.96</v>
       </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
         <v>2.79</v>
       </c>
-      <c r="P48" t="n">
+      <c r="Q48" t="n">
         <v>4.66</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="R48" t="n">
         <v>31.75</v>
       </c>
-      <c r="R48" t="n">
+      <c r="S48" t="n">
         <v>345111</v>
       </c>
-      <c r="S48" t="n">
+      <c r="T48" t="n">
         <v>-0.280386</v>
       </c>
-      <c r="T48" t="n">
+      <c r="U48" t="n">
         <v>5.352993</v>
       </c>
-      <c r="U48" t="n">
+      <c r="V48" t="n">
         <v>2.657089</v>
       </c>
-      <c r="V48" t="n">
+      <c r="W48" t="n">
         <v>2.657381</v>
       </c>
-      <c r="W48" t="n">
+      <c r="X48" t="n">
         <v>0.440744</v>
       </c>
-      <c r="X48" t="n">
+      <c r="Y48" t="n">
         <v>-0.129254</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="Z48" t="n">
         <v>0.79014</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="AA48" t="n">
         <v>0.194809</v>
       </c>
-      <c r="AA48" t="n">
+      <c r="AB48" t="n">
         <v>5.225222</v>
       </c>
-      <c r="AB48" t="n">
+      <c r="AC48" t="n">
         <v>2.961368</v>
       </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
       <c r="AD48" t="n">
+        <v>5.127976</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
         <v>0.000562</v>
       </c>
-      <c r="AE48" t="n">
+      <c r="AG48" t="n">
         <v>0.000562</v>
       </c>
-      <c r="AF48" t="n">
+      <c r="AH48" t="n">
         <v>0.21</v>
       </c>
-      <c r="AG48" t="n">
+      <c r="AI48" t="n">
         <v>0.12</v>
       </c>
-      <c r="AH48" t="n">
+      <c r="AJ48" t="n">
         <v>0.25</v>
       </c>
-      <c r="AI48" t="n">
+      <c r="AK48" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -5572,90 +5842,96 @@
         <v>0.36</v>
       </c>
       <c r="G49" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="H49" t="n">
         <v>108.82893</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>110.38054</v>
       </c>
-      <c r="I49" t="n">
+      <c r="J49" t="n">
         <v>5.4264</v>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
         <v>5.4258</v>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
         <v>6774436</v>
       </c>
-      <c r="L49" t="n">
+      <c r="M49" t="n">
         <v>2546265</v>
       </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
         <v>4228171</v>
       </c>
-      <c r="N49" t="n">
+      <c r="O49" t="n">
         <v>4.14</v>
       </c>
-      <c r="O49" t="n">
+      <c r="P49" t="n">
         <v>2.85</v>
       </c>
-      <c r="P49" t="n">
+      <c r="Q49" t="n">
         <v>4.92</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="R49" t="n">
         <v>31.87</v>
       </c>
-      <c r="R49" t="n">
+      <c r="S49" t="n">
         <v>350767</v>
       </c>
-      <c r="S49" t="n">
+      <c r="T49" t="n">
         <v>0.304372</v>
       </c>
-      <c r="T49" t="n">
+      <c r="U49" t="n">
         <v>-2.412481</v>
       </c>
-      <c r="U49" t="n">
+      <c r="V49" t="n">
         <v>-3.136324</v>
       </c>
-      <c r="V49" t="n">
+      <c r="W49" t="n">
         <v>-3.13666</v>
       </c>
-      <c r="W49" t="n">
+      <c r="X49" t="n">
         <v>0.612293</v>
       </c>
-      <c r="X49" t="n">
+      <c r="Y49" t="n">
         <v>0.073298</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="Z49" t="n">
         <v>0.9397180000000001</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="AA49" t="n">
         <v>1.638893</v>
       </c>
-      <c r="AA49" t="n">
+      <c r="AB49" t="n">
         <v>5.130501</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AC49" t="n">
         <v>3.033233</v>
       </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>5.054283</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
       </c>
       <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
         <v>0.18</v>
       </c>
-      <c r="AG49" t="n">
+      <c r="AI49" t="n">
         <v>0.06</v>
       </c>
-      <c r="AH49" t="n">
+      <c r="AJ49" t="n">
         <v>0.26</v>
       </c>
-      <c r="AI49" t="n">
+      <c r="AK49" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5679,90 +5955,96 @@
         <v>0.42</v>
       </c>
       <c r="G50" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H50" t="n">
         <v>108.73548</v>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>109.48375</v>
       </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
         <v>5.3186</v>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
         <v>5.318</v>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" t="n">
         <v>6852705</v>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" t="n">
         <v>2589817</v>
       </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
         <v>4262888</v>
       </c>
-      <c r="N50" t="n">
+      <c r="O50" t="n">
         <v>4.09</v>
       </c>
-      <c r="O50" t="n">
+      <c r="P50" t="n">
         <v>2.77</v>
       </c>
-      <c r="P50" t="n">
+      <c r="Q50" t="n">
         <v>4.89</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="R50" t="n">
         <v>31.47</v>
       </c>
-      <c r="R50" t="n">
+      <c r="S50" t="n">
         <v>356582</v>
       </c>
-      <c r="S50" t="n">
+      <c r="T50" t="n">
         <v>-0.085869</v>
       </c>
-      <c r="T50" t="n">
+      <c r="U50" t="n">
         <v>-0.812453</v>
       </c>
-      <c r="U50" t="n">
+      <c r="V50" t="n">
         <v>-1.986584</v>
       </c>
-      <c r="V50" t="n">
+      <c r="W50" t="n">
         <v>-1.986804</v>
       </c>
-      <c r="W50" t="n">
+      <c r="X50" t="n">
         <v>1.155358</v>
       </c>
-      <c r="X50" t="n">
+      <c r="Y50" t="n">
         <v>1.710427</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="Z50" t="n">
         <v>0.821088</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="AA50" t="n">
         <v>1.657796</v>
       </c>
-      <c r="AA50" t="n">
+      <c r="AB50" t="n">
         <v>5.172369</v>
       </c>
-      <c r="AB50" t="n">
+      <c r="AC50" t="n">
         <v>2.828436</v>
       </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>5.096104</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
       </c>
       <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AG50" t="n">
+      <c r="AI50" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AH50" t="n">
+      <c r="AJ50" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI50" t="n">
+      <c r="AK50" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -5786,90 +6068,96 @@
         <v>-0.36</v>
       </c>
       <c r="G51" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H51" t="n">
         <v>108.75326</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>110.07682</v>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
         <v>5.3843</v>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
         <v>5.3837</v>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
         <v>6923886</v>
       </c>
-      <c r="L51" t="n">
+      <c r="M51" t="n">
         <v>2597630</v>
       </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
         <v>4326256</v>
       </c>
-      <c r="N51" t="n">
+      <c r="O51" t="n">
         <v>4.18</v>
       </c>
-      <c r="O51" t="n">
+      <c r="P51" t="n">
         <v>2.82</v>
       </c>
-      <c r="P51" t="n">
+      <c r="Q51" t="n">
         <v>4.99</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="R51" t="n">
         <v>32.04</v>
       </c>
-      <c r="R51" t="n">
+      <c r="S51" t="n">
         <v>357103</v>
       </c>
-      <c r="S51" t="n">
+      <c r="T51" t="n">
         <v>0.016352</v>
       </c>
-      <c r="T51" t="n">
+      <c r="U51" t="n">
         <v>0.541697</v>
       </c>
-      <c r="U51" t="n">
+      <c r="V51" t="n">
         <v>1.235287</v>
       </c>
-      <c r="V51" t="n">
+      <c r="W51" t="n">
         <v>1.235427</v>
       </c>
-      <c r="W51" t="n">
+      <c r="X51" t="n">
         <v>1.038729</v>
       </c>
-      <c r="X51" t="n">
+      <c r="Y51" t="n">
         <v>0.301682</v>
       </c>
-      <c r="Y51" t="n">
+      <c r="Z51" t="n">
         <v>1.486504</v>
       </c>
-      <c r="Z51" t="n">
+      <c r="AA51" t="n">
         <v>0.146109</v>
       </c>
-      <c r="AA51" t="n">
+      <c r="AB51" t="n">
         <v>4.680811</v>
       </c>
-      <c r="AB51" t="n">
+      <c r="AC51" t="n">
         <v>0.924206</v>
       </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>4.490243</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
       </c>
       <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG51" t="n">
+      <c r="AI51" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH51" t="n">
+      <c r="AJ51" t="n">
         <v>0.1</v>
       </c>
-      <c r="AI51" t="n">
+      <c r="AK51" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -5893,90 +6181,96 @@
         <v>0.27</v>
       </c>
       <c r="G52" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H52" t="n">
         <v>109.25005</v>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>106.59892</v>
       </c>
-      <c r="I52" t="n">
+      <c r="J52" t="n">
         <v>5.3338</v>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
         <v>5.3332</v>
       </c>
-      <c r="K52" t="n">
+      <c r="L52" t="n">
         <v>7004223</v>
       </c>
-      <c r="L52" t="n">
+      <c r="M52" t="n">
         <v>2616902</v>
       </c>
-      <c r="M52" t="n">
+      <c r="N52" t="n">
         <v>4387321</v>
       </c>
-      <c r="N52" t="n">
+      <c r="O52" t="n">
         <v>4.24</v>
       </c>
-      <c r="O52" t="n">
+      <c r="P52" t="n">
         <v>2.75</v>
       </c>
-      <c r="P52" t="n">
+      <c r="Q52" t="n">
         <v>5.12</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="R52" t="n">
         <v>32.2</v>
       </c>
-      <c r="R52" t="n">
+      <c r="S52" t="n">
         <v>360578</v>
       </c>
-      <c r="S52" t="n">
+      <c r="T52" t="n">
         <v>0.456805</v>
       </c>
-      <c r="T52" t="n">
+      <c r="U52" t="n">
         <v>-3.159521</v>
       </c>
-      <c r="U52" t="n">
+      <c r="V52" t="n">
         <v>-0.937912</v>
       </c>
-      <c r="V52" t="n">
+      <c r="W52" t="n">
         <v>-0.938017</v>
       </c>
-      <c r="W52" t="n">
+      <c r="X52" t="n">
         <v>1.160288</v>
       </c>
-      <c r="X52" t="n">
+      <c r="Y52" t="n">
         <v>0.741907</v>
       </c>
-      <c r="Y52" t="n">
+      <c r="Z52" t="n">
         <v>1.411498</v>
       </c>
-      <c r="Z52" t="n">
+      <c r="AA52" t="n">
         <v>0.973109</v>
       </c>
-      <c r="AA52" t="n">
+      <c r="AB52" t="n">
         <v>4.461836</v>
       </c>
-      <c r="AB52" t="n">
+      <c r="AC52" t="n">
         <v>-0.101973</v>
       </c>
-      <c r="AC52" t="n">
-        <v>0</v>
-      </c>
       <c r="AD52" t="n">
+        <v>4.177803</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="n">
         <v>-0</v>
       </c>
-      <c r="AE52" t="n">
+      <c r="AG52" t="n">
         <v>-0</v>
       </c>
-      <c r="AF52" t="n">
+      <c r="AH52" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG52" t="n">
+      <c r="AI52" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AH52" t="n">
+      <c r="AJ52" t="n">
         <v>0.13</v>
       </c>
-      <c r="AI52" t="n">
+      <c r="AK52" t="n">
         <v>0.16</v>
       </c>
     </row>
@@ -6000,90 +6294,96 @@
         <v>-0.01</v>
       </c>
       <c r="G53" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H53" t="n">
         <v>109.4528</v>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>107.18417</v>
       </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
         <v>5.5024</v>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>5.5018</v>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" t="n">
         <v>7137252</v>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" t="n">
         <v>2701735</v>
       </c>
-      <c r="M53" t="n">
+      <c r="N53" t="n">
         <v>4435517</v>
       </c>
-      <c r="N53" t="n">
+      <c r="O53" t="n">
         <v>4.2</v>
       </c>
-      <c r="O53" t="n">
+      <c r="P53" t="n">
         <v>2.7</v>
       </c>
-      <c r="P53" t="n">
+      <c r="Q53" t="n">
         <v>5.12</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="R53" t="n">
         <v>31.87</v>
       </c>
-      <c r="R53" t="n">
+      <c r="S53" t="n">
         <v>358234</v>
       </c>
-      <c r="S53" t="n">
+      <c r="T53" t="n">
         <v>0.185583</v>
       </c>
-      <c r="T53" t="n">
+      <c r="U53" t="n">
         <v>0.549021</v>
       </c>
-      <c r="U53" t="n">
+      <c r="V53" t="n">
         <v>3.160973</v>
       </c>
-      <c r="V53" t="n">
+      <c r="W53" t="n">
         <v>3.161329</v>
       </c>
-      <c r="W53" t="n">
+      <c r="X53" t="n">
         <v>1.899268</v>
       </c>
-      <c r="X53" t="n">
+      <c r="Y53" t="n">
         <v>3.241734</v>
       </c>
-      <c r="Y53" t="n">
+      <c r="Z53" t="n">
         <v>1.098529</v>
       </c>
-      <c r="Z53" t="n">
+      <c r="AA53" t="n">
         <v>-0.650067</v>
       </c>
-      <c r="AA53" t="n">
+      <c r="AB53" t="n">
         <v>4.264385</v>
       </c>
-      <c r="AB53" t="n">
+      <c r="AC53" t="n">
         <v>-1.042167</v>
       </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>3.897866</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
       </c>
       <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AG53" t="n">
+      <c r="AI53" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI53" t="n">
+      <c r="AJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -6107,90 +6407,96 @@
         <v>0.41</v>
       </c>
       <c r="G54" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H54" t="n">
         <v>110.04992</v>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>103.77761</v>
       </c>
-      <c r="I54" t="n">
+      <c r="J54" t="n">
         <v>5.2301</v>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
         <v>5.2295</v>
       </c>
-      <c r="K54" t="n">
+      <c r="L54" t="n">
         <v>7130762</v>
       </c>
-      <c r="L54" t="n">
+      <c r="M54" t="n">
         <v>2654220</v>
       </c>
-      <c r="M54" t="n">
+      <c r="N54" t="n">
         <v>4476542</v>
       </c>
-      <c r="N54" t="n">
+      <c r="O54" t="n">
         <v>4.44</v>
       </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
         <v>2.87</v>
       </c>
-      <c r="P54" t="n">
+      <c r="Q54" t="n">
         <v>5.38</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="R54" t="n">
         <v>32.45</v>
       </c>
-      <c r="R54" t="n">
+      <c r="S54" t="n">
         <v>364367</v>
       </c>
-      <c r="S54" t="n">
+      <c r="T54" t="n">
         <v>0.54555</v>
       </c>
-      <c r="T54" t="n">
+      <c r="U54" t="n">
         <v>-3.178231</v>
       </c>
-      <c r="U54" t="n">
+      <c r="V54" t="n">
         <v>-4.94875</v>
       </c>
-      <c r="V54" t="n">
+      <c r="W54" t="n">
         <v>-4.949289</v>
       </c>
-      <c r="W54" t="n">
+      <c r="X54" t="n">
         <v>-0.090931</v>
       </c>
-      <c r="X54" t="n">
+      <c r="Y54" t="n">
         <v>-1.758685</v>
       </c>
-      <c r="Y54" t="n">
+      <c r="Z54" t="n">
         <v>0.92492</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="AA54" t="n">
         <v>1.712009</v>
       </c>
-      <c r="AA54" t="n">
+      <c r="AB54" t="n">
         <v>4.441351</v>
       </c>
-      <c r="AB54" t="n">
+      <c r="AC54" t="n">
         <v>-0.903999</v>
       </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>4.303068</v>
       </c>
       <c r="AE54" t="n">
         <v>0</v>
       </c>
       <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
         <v>0.24</v>
       </c>
-      <c r="AG54" t="n">
+      <c r="AI54" t="n">
         <v>0.17</v>
       </c>
-      <c r="AH54" t="n">
+      <c r="AJ54" t="n">
         <v>0.26</v>
       </c>
-      <c r="AI54" t="n">
+      <c r="AK54" t="n">
         <v>0.58</v>
       </c>
     </row>
@@ -6214,90 +6520,96 @@
         <v>-0.73</v>
       </c>
       <c r="G55" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H55" t="n">
         <v>110.7366</v>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>106.76075</v>
       </c>
-      <c r="I55" t="n">
+      <c r="J55" t="n">
         <v>5.1495</v>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>5.1489</v>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" t="n">
         <v>7157783</v>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" t="n">
         <v>2656484</v>
       </c>
-      <c r="M55" t="n">
+      <c r="N55" t="n">
         <v>4501299</v>
       </c>
-      <c r="N55" t="n">
+      <c r="O55" t="n">
         <v>4.64</v>
       </c>
-      <c r="O55" t="n">
+      <c r="P55" t="n">
         <v>3.07</v>
       </c>
-      <c r="P55" t="n">
+      <c r="Q55" t="n">
         <v>5.56</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="R55" t="n">
         <v>32.63</v>
       </c>
-      <c r="R55" t="n">
+      <c r="S55" t="n">
         <v>371074</v>
       </c>
-      <c r="S55" t="n">
+      <c r="T55" t="n">
         <v>0.6239710000000001</v>
       </c>
-      <c r="T55" t="n">
+      <c r="U55" t="n">
         <v>2.874551</v>
       </c>
-      <c r="U55" t="n">
+      <c r="V55" t="n">
         <v>-1.54108</v>
       </c>
-      <c r="V55" t="n">
+      <c r="W55" t="n">
         <v>-1.541256</v>
       </c>
-      <c r="W55" t="n">
+      <c r="X55" t="n">
         <v>0.378936</v>
       </c>
-      <c r="X55" t="n">
+      <c r="Y55" t="n">
         <v>0.085298</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="Z55" t="n">
         <v>0.553038</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="AA55" t="n">
         <v>1.840727</v>
       </c>
-      <c r="AA55" t="n">
+      <c r="AB55" t="n">
         <v>3.812497</v>
       </c>
-      <c r="AB55" t="n">
+      <c r="AC55" t="n">
         <v>-2.659212</v>
       </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>3.357475</v>
       </c>
       <c r="AE55" t="n">
         <v>0</v>
       </c>
       <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
         <v>0.2</v>
       </c>
-      <c r="AG55" t="n">
+      <c r="AI55" t="n">
         <v>0.2</v>
       </c>
-      <c r="AH55" t="n">
+      <c r="AJ55" t="n">
         <v>0.18</v>
       </c>
-      <c r="AI55" t="n">
+      <c r="AK55" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -6321,90 +6633,96 @@
         <v>0.52</v>
       </c>
       <c r="G56" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H56" t="n">
         <v>110.58808</v>
       </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
         <v>118.01719</v>
       </c>
-      <c r="I56" t="n">
+      <c r="J56" t="n">
         <v>5.2194</v>
       </c>
-      <c r="J56" t="n">
+      <c r="K56" t="n">
         <v>5.2188</v>
       </c>
-      <c r="K56" t="n">
+      <c r="L56" t="n">
         <v>7240557</v>
       </c>
-      <c r="L56" t="n">
+      <c r="M56" t="n">
         <v>2687535</v>
       </c>
-      <c r="M56" t="n">
+      <c r="N56" t="n">
         <v>4553022</v>
       </c>
-      <c r="N56" t="n">
+      <c r="O56" t="n">
         <v>4.52</v>
       </c>
-      <c r="O56" t="n">
+      <c r="P56" t="n">
         <v>3.06</v>
       </c>
-      <c r="P56" t="n">
+      <c r="Q56" t="n">
         <v>5.39</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="R56" t="n">
         <v>32.84</v>
       </c>
-      <c r="R56" t="n">
+      <c r="S56" t="n">
         <v>362002</v>
       </c>
-      <c r="S56" t="n">
+      <c r="T56" t="n">
         <v>-0.13412</v>
       </c>
-      <c r="T56" t="n">
+      <c r="U56" t="n">
         <v>10.543613</v>
       </c>
-      <c r="U56" t="n">
+      <c r="V56" t="n">
         <v>1.357413</v>
       </c>
-      <c r="V56" t="n">
+      <c r="W56" t="n">
         <v>1.357572</v>
       </c>
-      <c r="W56" t="n">
+      <c r="X56" t="n">
         <v>1.15642</v>
       </c>
-      <c r="X56" t="n">
+      <c r="Y56" t="n">
         <v>1.168876</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="Z56" t="n">
         <v>1.149068</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="AA56" t="n">
         <v>-2.444795</v>
       </c>
-      <c r="AA56" t="n">
+      <c r="AB56" t="n">
         <v>4.142847</v>
       </c>
-      <c r="AB56" t="n">
+      <c r="AC56" t="n">
         <v>-1.819225</v>
       </c>
-      <c r="AC56" t="n">
+      <c r="AD56" t="n">
+        <v>3.768807</v>
+      </c>
+      <c r="AE56" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD56" t="n">
+      <c r="AF56" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="AE56" t="n">
+      <c r="AG56" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="AF56" t="n">
+      <c r="AH56" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AG56" t="n">
+      <c r="AI56" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH56" t="n">
+      <c r="AJ56" t="n">
         <v>-0.17</v>
       </c>
-      <c r="AI56" t="n">
+      <c r="AK56" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -6428,90 +6746,96 @@
         <v>2.73</v>
       </c>
       <c r="G57" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H57" t="n">
         <v>110.90009</v>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>113.99295</v>
       </c>
-      <c r="I57" t="n">
+      <c r="J57" t="n">
         <v>4.9886</v>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
         <v>4.988</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
         <v>7259766</v>
       </c>
-      <c r="L57" t="n">
+      <c r="M57" t="n">
         <v>2685397</v>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
         <v>4574368</v>
       </c>
-      <c r="N57" t="n">
+      <c r="O57" t="n">
         <v>4.64</v>
       </c>
-      <c r="O57" t="n">
+      <c r="P57" t="n">
         <v>3.15</v>
       </c>
-      <c r="P57" t="n">
+      <c r="Q57" t="n">
         <v>5.51</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="R57" t="n">
         <v>33.36</v>
       </c>
-      <c r="R57" t="n">
+      <c r="S57" t="n">
         <v>366913</v>
       </c>
-      <c r="S57" t="n">
+      <c r="T57" t="n">
         <v>0.282137</v>
       </c>
-      <c r="T57" t="n">
+      <c r="U57" t="n">
         <v>-3.409876</v>
       </c>
-      <c r="U57" t="n">
+      <c r="V57" t="n">
         <v>-4.421964</v>
       </c>
-      <c r="V57" t="n">
+      <c r="W57" t="n">
         <v>-4.422473</v>
       </c>
-      <c r="W57" t="n">
+      <c r="X57" t="n">
         <v>0.265297</v>
       </c>
-      <c r="X57" t="n">
+      <c r="Y57" t="n">
         <v>-0.079552</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="Z57" t="n">
         <v>0.468831</v>
       </c>
-      <c r="Z57" t="n">
+      <c r="AA57" t="n">
         <v>1.356622</v>
       </c>
-      <c r="AA57" t="n">
+      <c r="AB57" t="n">
         <v>4.39172</v>
       </c>
-      <c r="AB57" t="n">
+      <c r="AC57" t="n">
         <v>0.619623</v>
       </c>
-      <c r="AC57" t="n">
+      <c r="AD57" t="n">
+        <v>4.109608</v>
+      </c>
+      <c r="AE57" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD57" t="n">
+      <c r="AF57" t="n">
         <v>-0.000554</v>
       </c>
-      <c r="AE57" t="n">
+      <c r="AG57" t="n">
         <v>-0.000554</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>0.09</v>
       </c>
       <c r="AH57" t="n">
         <v>0.12</v>
       </c>
       <c r="AI57" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AK57" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -6535,90 +6859,96 @@
         <v>0.84</v>
       </c>
       <c r="G58" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H58" t="n">
         <v>111.13846</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>109.65479</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>5.0569</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>5.0563</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>7305306</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>2708154</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>4597152</v>
       </c>
-      <c r="N58" t="n">
+      <c r="O58" t="n">
         <v>4.74</v>
       </c>
-      <c r="O58" t="n">
+      <c r="P58" t="n">
         <v>3.25</v>
       </c>
-      <c r="P58" t="n">
+      <c r="Q58" t="n">
         <v>5.62</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="R58" t="n">
         <v>33.1</v>
       </c>
-      <c r="R58" t="n">
+      <c r="S58" t="n">
         <v>371137</v>
       </c>
-      <c r="S58" t="n">
+      <c r="T58" t="n">
         <v>0.214941</v>
       </c>
-      <c r="T58" t="n">
+      <c r="U58" t="n">
         <v>-3.805639</v>
       </c>
-      <c r="U58" t="n">
+      <c r="V58" t="n">
         <v>1.369122</v>
       </c>
-      <c r="V58" t="n">
+      <c r="W58" t="n">
         <v>1.369286</v>
       </c>
-      <c r="W58" t="n">
+      <c r="X58" t="n">
         <v>0.627293</v>
       </c>
-      <c r="X58" t="n">
+      <c r="Y58" t="n">
         <v>0.847435</v>
       </c>
-      <c r="Y58" t="n">
+      <c r="Z58" t="n">
         <v>0.49808</v>
       </c>
-      <c r="Z58" t="n">
+      <c r="AA58" t="n">
         <v>1.151227</v>
       </c>
-      <c r="AA58" t="n">
+      <c r="AB58" t="n">
         <v>4.724907</v>
       </c>
-      <c r="AB58" t="n">
+      <c r="AC58" t="n">
         <v>1.964454</v>
       </c>
-      <c r="AC58" t="n">
-        <v>0</v>
-      </c>
       <c r="AD58" t="n">
+        <v>4.420848</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="n">
         <v>-0.0008229999999999999</v>
       </c>
-      <c r="AE58" t="n">
+      <c r="AG58" t="n">
         <v>-0.0008229999999999999</v>
       </c>
-      <c r="AF58" t="n">
+      <c r="AH58" t="n">
         <v>0.1</v>
       </c>
-      <c r="AG58" t="n">
+      <c r="AI58" t="n">
         <v>0.1</v>
       </c>
-      <c r="AH58" t="n">
+      <c r="AJ58" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI58" t="n">
+      <c r="AK58" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -6642,90 +6972,96 @@
         <v>-0.5</v>
       </c>
       <c r="G59" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H59" t="n">
         <v>110.15775</v>
       </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
         <v>109.94156</v>
       </c>
-      <c r="I59" t="n">
+      <c r="J59" t="n">
         <v>5.1766</v>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
         <v>5.176</v>
       </c>
-      <c r="K59" t="n">
+      <c r="L59" t="n">
         <v>7353293</v>
       </c>
-      <c r="L59" t="n">
+      <c r="M59" t="n">
         <v>2750625</v>
       </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
         <v>4602668</v>
       </c>
-      <c r="N59" t="n">
+      <c r="O59" t="n">
         <v>4.58</v>
       </c>
-      <c r="O59" t="n">
+      <c r="P59" t="n">
         <v>3.18</v>
       </c>
-      <c r="P59" t="n">
+      <c r="Q59" t="n">
         <v>5.42</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="R59" t="n">
         <v>33.33</v>
       </c>
-      <c r="R59" t="n">
+      <c r="S59" t="n">
         <v>367558</v>
       </c>
-      <c r="S59" t="n">
+      <c r="T59" t="n">
         <v>-0.882422</v>
       </c>
-      <c r="T59" t="n">
+      <c r="U59" t="n">
         <v>0.261521</v>
       </c>
-      <c r="U59" t="n">
+      <c r="V59" t="n">
         <v>2.367063</v>
       </c>
-      <c r="V59" t="n">
+      <c r="W59" t="n">
         <v>2.367344</v>
       </c>
-      <c r="W59" t="n">
+      <c r="X59" t="n">
         <v>0.656879</v>
       </c>
-      <c r="X59" t="n">
+      <c r="Y59" t="n">
         <v>1.568264</v>
       </c>
-      <c r="Y59" t="n">
+      <c r="Z59" t="n">
         <v>0.119987</v>
       </c>
-      <c r="Z59" t="n">
+      <c r="AA59" t="n">
         <v>-0.964334</v>
       </c>
-      <c r="AA59" t="n">
+      <c r="AB59" t="n">
         <v>4.641328</v>
       </c>
-      <c r="AB59" t="n">
+      <c r="AC59" t="n">
         <v>3.177699</v>
       </c>
-      <c r="AC59" t="n">
+      <c r="AD59" t="n">
+        <v>4.327084</v>
+      </c>
+      <c r="AE59" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD59" t="n">
+      <c r="AF59" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AE59" t="n">
+      <c r="AG59" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AF59" t="n">
+      <c r="AH59" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AG59" t="n">
+      <c r="AI59" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AH59" t="n">
+      <c r="AJ59" t="n">
         <v>-0.2</v>
       </c>
-      <c r="AI59" t="n">
+      <c r="AK59" t="n">
         <v>0.23</v>
       </c>
     </row>
@@ -6749,90 +7085,96 @@
         <v>-1.16</v>
       </c>
       <c r="G60" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="H60" t="n">
         <v>109.91611</v>
       </c>
-      <c r="H60" t="n">
+      <c r="I60" t="n">
         <v>114.40189</v>
       </c>
-      <c r="I60" t="n">
+      <c r="J60" t="n">
         <v>5.0773</v>
       </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
         <v>5.0767</v>
       </c>
-      <c r="K60" t="n">
+      <c r="L60" t="n">
         <v>7372243</v>
       </c>
-      <c r="L60" t="n">
+      <c r="M60" t="n">
         <v>2731513</v>
       </c>
-      <c r="M60" t="n">
+      <c r="N60" t="n">
         <v>4640730</v>
       </c>
-      <c r="N60" t="n">
+      <c r="O60" t="n">
         <v>4.88</v>
       </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
         <v>3.31</v>
       </c>
-      <c r="P60" t="n">
+      <c r="Q60" t="n">
         <v>5.81</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="R60" t="n">
         <v>32.08</v>
       </c>
-      <c r="R60" t="n">
+      <c r="S60" t="n">
         <v>369742</v>
       </c>
-      <c r="S60" t="n">
+      <c r="T60" t="n">
         <v>-0.219358</v>
       </c>
-      <c r="T60" t="n">
+      <c r="U60" t="n">
         <v>4.057001</v>
       </c>
-      <c r="U60" t="n">
+      <c r="V60" t="n">
         <v>-1.918247</v>
       </c>
-      <c r="V60" t="n">
+      <c r="W60" t="n">
         <v>-1.91847</v>
       </c>
-      <c r="W60" t="n">
+      <c r="X60" t="n">
         <v>0.257708</v>
       </c>
-      <c r="X60" t="n">
+      <c r="Y60" t="n">
         <v>-0.694824</v>
       </c>
-      <c r="Y60" t="n">
+      <c r="Z60" t="n">
         <v>0.826955</v>
       </c>
-      <c r="Z60" t="n">
+      <c r="AA60" t="n">
         <v>0.5941920000000001</v>
       </c>
-      <c r="AA60" t="n">
+      <c r="AB60" t="n">
         <v>4.443025</v>
       </c>
-      <c r="AB60" t="n">
+      <c r="AC60" t="n">
         <v>2.772183</v>
       </c>
-      <c r="AC60" t="n">
-        <v>0</v>
-      </c>
       <c r="AD60" t="n">
+        <v>4.098046</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="AE60" t="n">
+      <c r="AG60" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="AF60" t="n">
+      <c r="AH60" t="n">
         <v>0.3</v>
       </c>
-      <c r="AG60" t="n">
+      <c r="AI60" t="n">
         <v>0.13</v>
       </c>
-      <c r="AH60" t="n">
+      <c r="AJ60" t="n">
         <v>0.39</v>
       </c>
-      <c r="AI60" t="n">
+      <c r="AK60" t="n">
         <v>-1.25</v>
       </c>
     </row>
@@ -6855,57 +7197,63 @@
       <c r="F61" t="n">
         <v>-0.22</v>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="n">
+        <v>-0.32</v>
+      </c>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="n">
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="n">
         <v>5.1816</v>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
         <v>5.181</v>
       </c>
-      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="n">
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="n">
         <v>372616</v>
       </c>
-      <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="n">
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="n">
         <v>2.054241</v>
       </c>
-      <c r="V61" t="n">
+      <c r="W61" t="n">
         <v>2.054484</v>
       </c>
-      <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="n">
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="n">
         <v>0.777299</v>
       </c>
-      <c r="AA61" t="n">
+      <c r="AB61" t="n">
         <v>4.223453</v>
       </c>
-      <c r="AB61" t="n">
+      <c r="AC61" t="n">
         <v>2.178243</v>
       </c>
-      <c r="AC61" t="n">
+      <c r="AD61" t="n">
+        <v>3.983297</v>
+      </c>
+      <c r="AE61" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD61" t="n">
+      <c r="AF61" t="n">
         <v>-0.0007470000000000001</v>
       </c>
-      <c r="AE61" t="n">
+      <c r="AG61" t="n">
         <v>-0.0007470000000000001</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -6915,22 +7263,22 @@
         <v>13.75</v>
       </c>
       <c r="C62" t="n">
-        <v>0.051526</v>
+        <v>0.051473</v>
       </c>
       <c r="D62" t="n">
-        <v>0.051526</v>
+        <v>0.051473</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="n">
-        <v>5.1575</v>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>5.1569</v>
-      </c>
-      <c r="K62" t="inlineStr"/>
+        <v>5.1117</v>
+      </c>
+      <c r="K62" t="n">
+        <v>5.1111</v>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -6940,31 +7288,33 @@
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="n">
-        <v>-0.465107</v>
-      </c>
+      <c r="U62" t="inlineStr"/>
       <c r="V62" t="n">
-        <v>-0.465161</v>
-      </c>
-      <c r="W62" t="inlineStr"/>
+        <v>-1.349004</v>
+      </c>
+      <c r="W62" t="n">
+        <v>-1.34916</v>
+      </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr"/>
-      <c r="AC62" t="n">
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD62" t="n">
-        <v>-0.000259</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>-0.000259</v>
-      </c>
-      <c r="AF62" t="inlineStr"/>
-      <c r="AG62" t="inlineStr"/>
+      <c r="AF62" t="n">
+        <v>-0.000311</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>-0.000311</v>
+      </c>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK62"/>
+  <dimension ref="A1:AI62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,125 +483,115 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
           <t>saldo_credito_pf</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inadimplencia_total</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inadimplencia_pj</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inadimplencia_pf</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>var_pct_saldo_credito_pj</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ipca_acum_12m</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>inpc_acum_12m</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>dif_selic_over</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dif_cdi</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -645,26 +635,24 @@
         <v>4441056</v>
       </c>
       <c r="M2" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="N2" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="O2" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="P2" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="R2" t="n">
-        <v>21.42</v>
-      </c>
-      <c r="S2" t="n">
         <v>368886</v>
       </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -681,8 +669,6 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -722,72 +708,66 @@
         <v>4511956</v>
       </c>
       <c r="M3" t="n">
-        <v>1910940</v>
+        <v>2601017</v>
       </c>
       <c r="N3" t="n">
-        <v>2601017</v>
+        <v>2.33</v>
       </c>
       <c r="O3" t="n">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="R3" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="S3" t="n">
-        <v>367927</v>
+        <v>0.537905</v>
       </c>
       <c r="T3" t="n">
-        <v>0.537905</v>
+        <v>-0.594556</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.594556</v>
+        <v>3.74306</v>
       </c>
       <c r="V3" t="n">
-        <v>3.74306</v>
+        <v>3.743473</v>
       </c>
       <c r="W3" t="n">
-        <v>3.743473</v>
+        <v>1.596467</v>
       </c>
       <c r="X3" t="n">
-        <v>1.596467</v>
+        <v>2.123375</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.888065</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.123375</v>
-      </c>
-      <c r="AA3" t="n">
         <v>-0.259972</v>
       </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.001094</v>
+      </c>
       <c r="AE3" t="n">
-        <v>1.5</v>
+        <v>0.001094</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.001094</v>
+        <v>-0.01</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.001094</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AK3" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -829,72 +809,66 @@
         <v>4597507</v>
       </c>
       <c r="M4" t="n">
-        <v>1933111</v>
+        <v>2664395</v>
       </c>
       <c r="N4" t="n">
-        <v>2664395</v>
+        <v>2.36</v>
       </c>
       <c r="O4" t="n">
-        <v>2.36</v>
+        <v>1.46</v>
       </c>
       <c r="P4" t="n">
-        <v>1.46</v>
+        <v>3.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.01</v>
+        <v>23.91</v>
       </c>
       <c r="R4" t="n">
-        <v>23.91</v>
+        <v>367772</v>
       </c>
       <c r="S4" t="n">
-        <v>367772</v>
+        <v>1.608989</v>
       </c>
       <c r="T4" t="n">
-        <v>1.608989</v>
+        <v>1.36989</v>
       </c>
       <c r="U4" t="n">
-        <v>1.36989</v>
+        <v>-0.409357</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.409357</v>
+        <v>-0.4094</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.4094</v>
+        <v>1.896096</v>
       </c>
       <c r="X4" t="n">
-        <v>1.896096</v>
+        <v>2.436662</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.160214</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.436662</v>
-      </c>
-      <c r="AA4" t="n">
         <v>-0.042128</v>
       </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.005012</v>
+      </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>0.005012</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.005012</v>
+        <v>0.03</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.005012</v>
+        <v>0.03</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK4" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -936,72 +910,66 @@
         <v>4682852</v>
       </c>
       <c r="M5" t="n">
-        <v>1974391</v>
+        <v>2708461</v>
       </c>
       <c r="N5" t="n">
-        <v>2708461</v>
+        <v>2.35</v>
       </c>
       <c r="O5" t="n">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="P5" t="n">
-        <v>1.4</v>
+        <v>3.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.05</v>
+        <v>24.21</v>
       </c>
       <c r="R5" t="n">
-        <v>24.21</v>
+        <v>362204</v>
       </c>
       <c r="S5" t="n">
-        <v>362204</v>
+        <v>0.32497</v>
       </c>
       <c r="T5" t="n">
-        <v>0.32497</v>
+        <v>1.502063</v>
       </c>
       <c r="U5" t="n">
-        <v>1.502063</v>
+        <v>-0.70108</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.70108</v>
+        <v>-0.701155</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.701155</v>
+        <v>1.856332</v>
       </c>
       <c r="X5" t="n">
-        <v>1.856332</v>
+        <v>1.653884</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.135418</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.653884</v>
-      </c>
-      <c r="AA5" t="n">
         <v>-1.513981</v>
       </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.00406</v>
+      </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>0.00406</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.00406</v>
+        <v>-0.01</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.00406</v>
+        <v>-0.06</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK5" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1043,72 +1011,66 @@
         <v>4682131</v>
       </c>
       <c r="M6" t="n">
-        <v>1947035</v>
+        <v>2735096</v>
       </c>
       <c r="N6" t="n">
-        <v>2735096</v>
+        <v>2.51</v>
       </c>
       <c r="O6" t="n">
-        <v>2.51</v>
+        <v>1.46</v>
       </c>
       <c r="P6" t="n">
-        <v>1.46</v>
+        <v>3.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.26</v>
+        <v>25.23</v>
       </c>
       <c r="R6" t="n">
-        <v>25.23</v>
+        <v>358398</v>
       </c>
       <c r="S6" t="n">
-        <v>358398</v>
+        <v>-1.968118</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.968118</v>
+        <v>-7.696961</v>
       </c>
       <c r="U6" t="n">
-        <v>-7.696961</v>
+        <v>-3.99785</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.99785</v>
+        <v>-3.99828</v>
       </c>
       <c r="W6" t="n">
-        <v>-3.99828</v>
+        <v>-0.015397</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.015397</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.385541</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.9834000000000001</v>
-      </c>
-      <c r="AA6" t="n">
         <v>-1.050789</v>
       </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.001433</v>
+      </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>0.001433</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.001433</v>
+        <v>0.16</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.001433</v>
+        <v>0.06</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AK6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1150,72 +1112,66 @@
         <v>4727818</v>
       </c>
       <c r="M7" t="n">
-        <v>1971524</v>
+        <v>2756295</v>
       </c>
       <c r="N7" t="n">
-        <v>2756295</v>
+        <v>2.57</v>
       </c>
       <c r="O7" t="n">
-        <v>2.57</v>
+        <v>1.44</v>
       </c>
       <c r="P7" t="n">
-        <v>1.44</v>
+        <v>3.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.38</v>
+        <v>25.63</v>
       </c>
       <c r="R7" t="n">
-        <v>25.63</v>
+        <v>357740</v>
       </c>
       <c r="S7" t="n">
-        <v>357740</v>
+        <v>1.087134</v>
       </c>
       <c r="T7" t="n">
-        <v>1.087134</v>
+        <v>4.318965</v>
       </c>
       <c r="U7" t="n">
-        <v>4.318965</v>
+        <v>-4.069138</v>
       </c>
       <c r="V7" t="n">
-        <v>-4.069138</v>
+        <v>-4.069594</v>
       </c>
       <c r="W7" t="n">
-        <v>-4.069594</v>
+        <v>0.975774</v>
       </c>
       <c r="X7" t="n">
-        <v>0.975774</v>
+        <v>0.775073</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.257759</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.775073</v>
-      </c>
-      <c r="AA7" t="n">
         <v>-0.183595</v>
       </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.004849</v>
+      </c>
       <c r="AE7" t="n">
-        <v>1.5</v>
+        <v>0.004849</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.004849</v>
+        <v>0.06</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.004849</v>
+        <v>-0.02</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AK7" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1257,72 +1213,66 @@
         <v>4794583</v>
       </c>
       <c r="M8" t="n">
-        <v>1994119</v>
+        <v>2800464</v>
       </c>
       <c r="N8" t="n">
-        <v>2800464</v>
+        <v>2.66</v>
       </c>
       <c r="O8" t="n">
-        <v>2.66</v>
+        <v>1.55</v>
       </c>
       <c r="P8" t="n">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.45</v>
+        <v>26.54</v>
       </c>
       <c r="R8" t="n">
-        <v>26.54</v>
+        <v>353169</v>
       </c>
       <c r="S8" t="n">
-        <v>353169</v>
+        <v>1.084094</v>
       </c>
       <c r="T8" t="n">
-        <v>1.084094</v>
+        <v>9.300848999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>9.300848999999999</v>
+        <v>-7.814142</v>
       </c>
       <c r="V8" t="n">
-        <v>-7.814142</v>
+        <v>-7.815054</v>
       </c>
       <c r="W8" t="n">
-        <v>-7.815054</v>
+        <v>1.412174</v>
       </c>
       <c r="X8" t="n">
-        <v>1.412174</v>
+        <v>1.602477</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.146068</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.602477</v>
-      </c>
-      <c r="AA8" t="n">
         <v>-1.277744</v>
       </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.002356</v>
+      </c>
       <c r="AE8" t="n">
-        <v>1</v>
+        <v>0.002356</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.002356</v>
+        <v>0.09</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.002356</v>
+        <v>0.11</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK8" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1364,72 +1314,66 @@
         <v>4833732</v>
       </c>
       <c r="M9" t="n">
-        <v>2003312</v>
+        <v>2830420</v>
       </c>
       <c r="N9" t="n">
-        <v>2830420</v>
+        <v>2.72</v>
       </c>
       <c r="O9" t="n">
-        <v>2.72</v>
+        <v>1.57</v>
       </c>
       <c r="P9" t="n">
-        <v>1.57</v>
+        <v>3.54</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.54</v>
+        <v>27.46</v>
       </c>
       <c r="R9" t="n">
-        <v>27.46</v>
+        <v>345097</v>
       </c>
       <c r="S9" t="n">
-        <v>345097</v>
+        <v>-0.107325</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.107325</v>
+        <v>-4.116419</v>
       </c>
       <c r="U9" t="n">
-        <v>-4.116419</v>
+        <v>3.826671</v>
       </c>
       <c r="V9" t="n">
-        <v>3.826671</v>
+        <v>3.827155</v>
       </c>
       <c r="W9" t="n">
-        <v>3.827155</v>
+        <v>0.816526</v>
       </c>
       <c r="X9" t="n">
-        <v>0.816526</v>
+        <v>1.06968</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.461006</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.06968</v>
-      </c>
-      <c r="AA9" t="n">
         <v>-2.285591</v>
       </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.001785</v>
+      </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>0.001785</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.001785</v>
+        <v>0.06</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001785</v>
+        <v>0.02</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK9" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1471,72 +1415,66 @@
         <v>4889397</v>
       </c>
       <c r="M10" t="n">
-        <v>2013726</v>
+        <v>2875671</v>
       </c>
       <c r="N10" t="n">
-        <v>2875671</v>
+        <v>2.79</v>
       </c>
       <c r="O10" t="n">
-        <v>2.79</v>
+        <v>1.57</v>
       </c>
       <c r="P10" t="n">
-        <v>1.57</v>
+        <v>3.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.65</v>
+        <v>27.42</v>
       </c>
       <c r="R10" t="n">
-        <v>27.42</v>
+        <v>346415</v>
       </c>
       <c r="S10" t="n">
-        <v>346415</v>
+        <v>0.205368</v>
       </c>
       <c r="T10" t="n">
-        <v>0.205368</v>
+        <v>-0.484439</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.484439</v>
+        <v>-3.866561</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.866561</v>
+        <v>-3.867033</v>
       </c>
       <c r="W10" t="n">
-        <v>-3.867033</v>
+        <v>1.151595</v>
       </c>
       <c r="X10" t="n">
-        <v>1.151595</v>
+        <v>1.598738</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5198390000000001</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.598738</v>
-      </c>
-      <c r="AA10" t="n">
         <v>0.381922</v>
       </c>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.003057</v>
+      </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>0.003057</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.003057</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.003057</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK10" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1578,72 +1516,66 @@
         <v>4965603</v>
       </c>
       <c r="M11" t="n">
-        <v>2052569</v>
+        <v>2913035</v>
       </c>
       <c r="N11" t="n">
-        <v>2913035</v>
+        <v>2.73</v>
       </c>
       <c r="O11" t="n">
-        <v>2.73</v>
+        <v>1.52</v>
       </c>
       <c r="P11" t="n">
-        <v>1.52</v>
+        <v>3.57</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.57</v>
+        <v>27.88</v>
       </c>
       <c r="R11" t="n">
-        <v>27.88</v>
+        <v>341958</v>
       </c>
       <c r="S11" t="n">
-        <v>341958</v>
+        <v>-0.1354</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1354</v>
+        <v>-0.428397</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.428397</v>
+        <v>10.765717</v>
       </c>
       <c r="V11" t="n">
-        <v>10.765717</v>
+        <v>10.767083</v>
       </c>
       <c r="W11" t="n">
-        <v>10.767083</v>
+        <v>1.558597</v>
       </c>
       <c r="X11" t="n">
-        <v>1.558597</v>
+        <v>1.299314</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.928912</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.299314</v>
-      </c>
-      <c r="AA11" t="n">
         <v>-1.286607</v>
       </c>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.00132</v>
+      </c>
       <c r="AE11" t="n">
-        <v>0.5</v>
+        <v>0.00132</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.00132</v>
+        <v>-0.06</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.00132</v>
+        <v>-0.05</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AK11" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1685,72 +1617,66 @@
         <v>4999244</v>
       </c>
       <c r="M12" t="n">
-        <v>2047038</v>
+        <v>2952207</v>
       </c>
       <c r="N12" t="n">
-        <v>2952207</v>
+        <v>2.84</v>
       </c>
       <c r="O12" t="n">
-        <v>2.84</v>
+        <v>1.6</v>
       </c>
       <c r="P12" t="n">
-        <v>1.6</v>
+        <v>3.71</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.71</v>
+        <v>29.24</v>
       </c>
       <c r="R12" t="n">
-        <v>29.24</v>
+        <v>346403</v>
       </c>
       <c r="S12" t="n">
-        <v>346403</v>
+        <v>1.930691</v>
       </c>
       <c r="T12" t="n">
-        <v>1.930691</v>
+        <v>4.675335</v>
       </c>
       <c r="U12" t="n">
-        <v>4.675335</v>
+        <v>-0.946926</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.946926</v>
+        <v>-0.947035</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.947035</v>
+        <v>0.677481</v>
       </c>
       <c r="X12" t="n">
-        <v>0.677481</v>
+        <v>1.344714</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.269467</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.344714</v>
-      </c>
-      <c r="AA12" t="n">
         <v>1.299867</v>
       </c>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.0009210000000000001</v>
+      </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AK12" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -1792,78 +1718,72 @@
         <v>5072711</v>
       </c>
       <c r="M13" t="n">
-        <v>2064183</v>
+        <v>3008528</v>
       </c>
       <c r="N13" t="n">
-        <v>3008528</v>
+        <v>2.9</v>
       </c>
       <c r="O13" t="n">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="P13" t="n">
-        <v>1.62</v>
+        <v>3.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.78</v>
+        <v>28.6</v>
       </c>
       <c r="R13" t="n">
-        <v>28.6</v>
+        <v>339664</v>
       </c>
       <c r="S13" t="n">
-        <v>339664</v>
+        <v>-0.32129</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.32129</v>
+        <v>0.530637</v>
       </c>
       <c r="U13" t="n">
-        <v>0.530637</v>
+        <v>-0.181173</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.181173</v>
+        <v>-0.181194</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.181194</v>
+        <v>1.469562</v>
       </c>
       <c r="X13" t="n">
-        <v>1.469562</v>
+        <v>1.907759</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.837552</v>
+        <v>-1.945422</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.907759</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="AA13" t="n">
-        <v>-1.945422</v>
+        <v>8.58755</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.727061000000001</v>
+        <v>8.825751</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.58755</v>
+        <v>0.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>8.825751</v>
+        <v>0.001523</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.5</v>
+        <v>0.001523</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.001523</v>
+        <v>0.06</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.001523</v>
+        <v>0.02</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK13" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -1905,78 +1825,72 @@
         <v>5164775</v>
       </c>
       <c r="M14" t="n">
-        <v>2109806</v>
+        <v>3054969</v>
       </c>
       <c r="N14" t="n">
-        <v>3054969</v>
+        <v>2.92</v>
       </c>
       <c r="O14" t="n">
-        <v>2.92</v>
+        <v>1.65</v>
       </c>
       <c r="P14" t="n">
-        <v>1.65</v>
+        <v>3.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.8</v>
+        <v>28.57</v>
       </c>
       <c r="R14" t="n">
-        <v>28.57</v>
+        <v>327580</v>
       </c>
       <c r="S14" t="n">
-        <v>327580</v>
+        <v>0.053914</v>
       </c>
       <c r="T14" t="n">
-        <v>0.053914</v>
+        <v>-3.179227</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.179227</v>
+        <v>4.394671</v>
       </c>
       <c r="V14" t="n">
-        <v>4.394671</v>
+        <v>4.39518</v>
       </c>
       <c r="W14" t="n">
-        <v>4.39518</v>
+        <v>1.814888</v>
       </c>
       <c r="X14" t="n">
-        <v>1.814888</v>
+        <v>1.543645</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.210221</v>
+        <v>-3.557633</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.543645</v>
+        <v>7.168596</v>
       </c>
       <c r="AA14" t="n">
-        <v>-3.557633</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.168596</v>
+        <v>7.191214</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.248760000000001</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>7.191214</v>
+        <v>0.000228</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>0.000228</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.000228</v>
+        <v>0.02</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.000228</v>
+        <v>0.03</v>
       </c>
       <c r="AH14" t="n">
         <v>0.02</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK14" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -2018,78 +1932,72 @@
         <v>5215990</v>
       </c>
       <c r="M15" t="n">
-        <v>2105856</v>
+        <v>3110134</v>
       </c>
       <c r="N15" t="n">
-        <v>3110134</v>
+        <v>3.04</v>
       </c>
       <c r="O15" t="n">
-        <v>3.04</v>
+        <v>1.77</v>
       </c>
       <c r="P15" t="n">
-        <v>1.77</v>
+        <v>3.89</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.89</v>
+        <v>29.68</v>
       </c>
       <c r="R15" t="n">
-        <v>29.68</v>
+        <v>325546</v>
       </c>
       <c r="S15" t="n">
-        <v>325546</v>
+        <v>0.278143</v>
       </c>
       <c r="T15" t="n">
-        <v>0.278143</v>
+        <v>-1.094122</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.094122</v>
+        <v>-2.766988</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.766988</v>
+        <v>-2.767296</v>
       </c>
       <c r="W15" t="n">
-        <v>-2.767296</v>
+        <v>0.991621</v>
       </c>
       <c r="X15" t="n">
-        <v>0.991621</v>
+        <v>1.805747</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.187221</v>
+        <v>-0.6209170000000001</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.805747</v>
+        <v>6.470016</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.6209170000000001</v>
+        <v>6.517038</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.470016</v>
+        <v>6.460076</v>
       </c>
       <c r="AC15" t="n">
-        <v>6.517038</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.460076</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK15" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -2131,78 +2039,72 @@
         <v>5285657</v>
       </c>
       <c r="M16" t="n">
-        <v>2130312</v>
+        <v>3155345</v>
       </c>
       <c r="N16" t="n">
-        <v>3155345</v>
+        <v>3.07</v>
       </c>
       <c r="O16" t="n">
-        <v>3.07</v>
+        <v>1.81</v>
       </c>
       <c r="P16" t="n">
-        <v>1.81</v>
+        <v>3.92</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.92</v>
+        <v>30.52</v>
       </c>
       <c r="R16" t="n">
-        <v>30.52</v>
+        <v>331505</v>
       </c>
       <c r="S16" t="n">
-        <v>331505</v>
+        <v>-0.716776</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.716776</v>
+        <v>-0.930689</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.930689</v>
+        <v>0.705726</v>
       </c>
       <c r="V16" t="n">
-        <v>0.705726</v>
+        <v>0.705806</v>
       </c>
       <c r="W16" t="n">
-        <v>0.705806</v>
+        <v>1.335643</v>
       </c>
       <c r="X16" t="n">
-        <v>1.335643</v>
+        <v>1.453667</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.161333</v>
+        <v>1.830463</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.453667</v>
+        <v>5.900488</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.830463</v>
+        <v>5.899363</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.900488</v>
+        <v>5.974439</v>
       </c>
       <c r="AC16" t="n">
-        <v>5.899363</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>5.974439</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AH16" t="n">
         <v>0.03</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AK16" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2244,78 +2146,72 @@
         <v>5366069</v>
       </c>
       <c r="M17" t="n">
-        <v>2178236</v>
+        <v>3187833</v>
       </c>
       <c r="N17" t="n">
-        <v>3187833</v>
+        <v>3.07</v>
       </c>
       <c r="O17" t="n">
-        <v>3.07</v>
+        <v>1.8</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8</v>
+        <v>3.94</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.94</v>
+        <v>29.64</v>
       </c>
       <c r="R17" t="n">
-        <v>29.64</v>
+        <v>324703</v>
       </c>
       <c r="S17" t="n">
-        <v>324703</v>
+        <v>-0.125523</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.125523</v>
+        <v>0.827078</v>
       </c>
       <c r="U17" t="n">
-        <v>0.827078</v>
+        <v>-1.443116</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.443116</v>
+        <v>-1.443279</v>
       </c>
       <c r="W17" t="n">
-        <v>-1.443279</v>
+        <v>1.521325</v>
       </c>
       <c r="X17" t="n">
-        <v>1.521325</v>
+        <v>1.029618</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.249624</v>
+        <v>-2.051854</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.029618</v>
+        <v>5.784842</v>
       </c>
       <c r="AA17" t="n">
-        <v>-2.051854</v>
+        <v>5.458422</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.784842</v>
+        <v>5.932356</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.458422</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>5.932356</v>
+        <v>-0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AI17" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK17" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -2357,78 +2253,72 @@
         <v>5373231</v>
       </c>
       <c r="M18" t="n">
-        <v>2151399</v>
+        <v>3221831</v>
       </c>
       <c r="N18" t="n">
-        <v>3221831</v>
+        <v>3.24</v>
       </c>
       <c r="O18" t="n">
-        <v>3.24</v>
+        <v>1.94</v>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>4.11</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.11</v>
+        <v>30.54</v>
       </c>
       <c r="R18" t="n">
-        <v>30.54</v>
+        <v>331122</v>
       </c>
       <c r="S18" t="n">
-        <v>331122</v>
+        <v>-0.475503</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.475503</v>
+        <v>-4.872284</v>
       </c>
       <c r="U18" t="n">
-        <v>-4.872284</v>
+        <v>-2.269199</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.269199</v>
+        <v>-2.26946</v>
       </c>
       <c r="W18" t="n">
-        <v>-2.26946</v>
+        <v>0.133468</v>
       </c>
       <c r="X18" t="n">
-        <v>0.133468</v>
+        <v>1.066493</v>
       </c>
       <c r="Y18" t="n">
-        <v>-1.232052</v>
+        <v>1.976883</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.066493</v>
+        <v>5.77432</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.976883</v>
+        <v>3.79089</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.77432</v>
+        <v>5.711379</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.79089</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>5.711379</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AH18" t="n">
         <v>0.17</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AK18" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2470,78 +2360,72 @@
         <v>5370950</v>
       </c>
       <c r="M19" t="n">
-        <v>2136105</v>
+        <v>3234845</v>
       </c>
       <c r="N19" t="n">
-        <v>3234845</v>
+        <v>3.36</v>
       </c>
       <c r="O19" t="n">
-        <v>3.36</v>
+        <v>2.17</v>
       </c>
       <c r="P19" t="n">
-        <v>2.17</v>
+        <v>4.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.16</v>
+        <v>30.48</v>
       </c>
       <c r="R19" t="n">
-        <v>30.48</v>
+        <v>328098</v>
       </c>
       <c r="S19" t="n">
-        <v>328098</v>
+        <v>2.96673</v>
       </c>
       <c r="T19" t="n">
-        <v>2.96673</v>
+        <v>3.731301</v>
       </c>
       <c r="U19" t="n">
-        <v>3.731301</v>
+        <v>2.127743</v>
       </c>
       <c r="V19" t="n">
-        <v>2.127743</v>
+        <v>2.127993</v>
       </c>
       <c r="W19" t="n">
-        <v>2.127993</v>
+        <v>-0.042451</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.042451</v>
+        <v>0.403932</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.710886</v>
+        <v>-0.913259</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.403932</v>
+        <v>5.596302</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.913259</v>
+        <v>1.864495</v>
       </c>
       <c r="AB19" t="n">
-        <v>5.596302</v>
+        <v>5.47065</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.864495</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>5.47065</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK19" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2583,78 +2467,72 @@
         <v>5424811</v>
       </c>
       <c r="M20" t="n">
-        <v>2154900</v>
+        <v>3269910</v>
       </c>
       <c r="N20" t="n">
-        <v>3269910</v>
+        <v>3.35</v>
       </c>
       <c r="O20" t="n">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>4.11</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.11</v>
+        <v>30.99</v>
       </c>
       <c r="R20" t="n">
-        <v>30.99</v>
+        <v>341158</v>
       </c>
       <c r="S20" t="n">
-        <v>341158</v>
+        <v>0.004919</v>
       </c>
       <c r="T20" t="n">
-        <v>0.004919</v>
+        <v>12.135312</v>
       </c>
       <c r="U20" t="n">
-        <v>12.135312</v>
+        <v>-2.446331</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.446331</v>
+        <v>-2.446612</v>
       </c>
       <c r="W20" t="n">
-        <v>-2.446612</v>
+        <v>1.002821</v>
       </c>
       <c r="X20" t="n">
-        <v>1.002821</v>
+        <v>1.083978</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.879872</v>
+        <v>3.980518</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.083978</v>
+        <v>4.650694</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.980518</v>
+        <v>0.172427</v>
       </c>
       <c r="AB20" t="n">
-        <v>4.650694</v>
+        <v>4.361088</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.172427</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.361088</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AK20" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2696,78 +2574,72 @@
         <v>5426307</v>
       </c>
       <c r="M21" t="n">
-        <v>2145000</v>
+        <v>3281308</v>
       </c>
       <c r="N21" t="n">
-        <v>3281308</v>
+        <v>3.54</v>
       </c>
       <c r="O21" t="n">
-        <v>3.54</v>
+        <v>2.45</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>4.26</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.26</v>
+        <v>31.62</v>
       </c>
       <c r="R21" t="n">
-        <v>31.62</v>
+        <v>345725</v>
       </c>
       <c r="S21" t="n">
-        <v>345725</v>
+        <v>0.825329</v>
       </c>
       <c r="T21" t="n">
-        <v>0.825329</v>
+        <v>-5.946769</v>
       </c>
       <c r="U21" t="n">
-        <v>-5.946769</v>
+        <v>-1.568774</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.568774</v>
+        <v>-1.568959</v>
       </c>
       <c r="W21" t="n">
-        <v>-1.568959</v>
+        <v>0.027577</v>
       </c>
       <c r="X21" t="n">
-        <v>0.027577</v>
+        <v>0.348572</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.459418</v>
+        <v>1.338676</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.348572</v>
+        <v>4.184706</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.338676</v>
+        <v>-2.158772</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.184706</v>
+        <v>3.834324</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.158772</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.834324</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AK21" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -2809,78 +2681,72 @@
         <v>5453708</v>
       </c>
       <c r="M22" t="n">
-        <v>2145530</v>
+        <v>3308178</v>
       </c>
       <c r="N22" t="n">
-        <v>3308178</v>
+        <v>3.65</v>
       </c>
       <c r="O22" t="n">
-        <v>3.65</v>
+        <v>2.58</v>
       </c>
       <c r="P22" t="n">
-        <v>2.58</v>
+        <v>4.35</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.35</v>
+        <v>31.63</v>
       </c>
       <c r="R22" t="n">
-        <v>31.63</v>
+        <v>343489</v>
       </c>
       <c r="S22" t="n">
-        <v>343489</v>
+        <v>-1.448972</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.448972</v>
+        <v>-1.275652</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.275652</v>
+        <v>1.903733</v>
       </c>
       <c r="V22" t="n">
-        <v>1.903733</v>
+        <v>1.903962</v>
       </c>
       <c r="W22" t="n">
-        <v>1.903962</v>
+        <v>0.504966</v>
       </c>
       <c r="X22" t="n">
-        <v>0.504966</v>
+        <v>0.818881</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.024709</v>
+        <v>-0.646757</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.818881</v>
+        <v>3.935832</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0.646757</v>
+        <v>-4.45588</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.935832</v>
+        <v>3.741292</v>
       </c>
       <c r="AC22" t="n">
-        <v>-4.45588</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.741292</v>
+        <v>-0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0</v>
+        <v>0.11</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK22" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -2922,78 +2788,72 @@
         <v>5479459</v>
       </c>
       <c r="M23" t="n">
-        <v>2169613</v>
+        <v>3309846</v>
       </c>
       <c r="N23" t="n">
-        <v>3309846</v>
+        <v>3.61</v>
       </c>
       <c r="O23" t="n">
-        <v>3.61</v>
+        <v>2.63</v>
       </c>
       <c r="P23" t="n">
-        <v>2.63</v>
+        <v>4.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.25</v>
+        <v>30.85</v>
       </c>
       <c r="R23" t="n">
-        <v>30.85</v>
+        <v>343620</v>
       </c>
       <c r="S23" t="n">
-        <v>343620</v>
+        <v>-0.029659</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.029659</v>
+        <v>-0.418863</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.418863</v>
+        <v>-5.429855</v>
       </c>
       <c r="V23" t="n">
-        <v>-5.429855</v>
+        <v>-5.430495</v>
       </c>
       <c r="W23" t="n">
-        <v>-5.430495</v>
+        <v>0.472174</v>
       </c>
       <c r="X23" t="n">
-        <v>0.472174</v>
+        <v>0.050421</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.122473</v>
+        <v>0.038138</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.050421</v>
+        <v>3.161501</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.038138</v>
+        <v>-6.84947</v>
       </c>
       <c r="AB23" t="n">
-        <v>3.161501</v>
+        <v>2.998957</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6.84947</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.998957</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AK23" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -3035,78 +2895,72 @@
         <v>5484871</v>
       </c>
       <c r="M24" t="n">
-        <v>2153541</v>
+        <v>3331330</v>
       </c>
       <c r="N24" t="n">
-        <v>3331330</v>
+        <v>3.63</v>
       </c>
       <c r="O24" t="n">
-        <v>3.63</v>
+        <v>2.73</v>
       </c>
       <c r="P24" t="n">
-        <v>2.73</v>
+        <v>4.22</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.22</v>
+        <v>30.43</v>
       </c>
       <c r="R24" t="n">
-        <v>30.43</v>
+        <v>345476</v>
       </c>
       <c r="S24" t="n">
-        <v>345476</v>
+        <v>0.495618</v>
       </c>
       <c r="T24" t="n">
-        <v>0.495618</v>
+        <v>2.992877</v>
       </c>
       <c r="U24" t="n">
-        <v>2.992877</v>
+        <v>-1.612301</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.612301</v>
+        <v>-1.612502</v>
       </c>
       <c r="W24" t="n">
-        <v>-1.612502</v>
+        <v>0.098769</v>
       </c>
       <c r="X24" t="n">
-        <v>0.098769</v>
+        <v>0.6490939999999999</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.740777</v>
+        <v>0.5401319999999999</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.6490939999999999</v>
+        <v>3.992444</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.5401319999999999</v>
+        <v>-7.713954</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.992444</v>
+        <v>3.527423</v>
       </c>
       <c r="AC24" t="n">
-        <v>-7.713954</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.527423</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK24" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3148,78 +3002,72 @@
         <v>5559063</v>
       </c>
       <c r="M25" t="n">
-        <v>2172658</v>
+        <v>3386405</v>
       </c>
       <c r="N25" t="n">
-        <v>3386405</v>
+        <v>3.61</v>
       </c>
       <c r="O25" t="n">
-        <v>3.61</v>
+        <v>2.82</v>
       </c>
       <c r="P25" t="n">
-        <v>2.82</v>
+        <v>4.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.12</v>
+        <v>29.92</v>
       </c>
       <c r="R25" t="n">
-        <v>29.92</v>
+        <v>344177</v>
       </c>
       <c r="S25" t="n">
-        <v>344177</v>
+        <v>-0.393045</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.393045</v>
+        <v>0.676</v>
       </c>
       <c r="U25" t="n">
-        <v>0.676</v>
+        <v>3.804703</v>
       </c>
       <c r="V25" t="n">
-        <v>3.804703</v>
+        <v>3.805185</v>
       </c>
       <c r="W25" t="n">
-        <v>3.805185</v>
+        <v>1.352666</v>
       </c>
       <c r="X25" t="n">
-        <v>1.352666</v>
+        <v>1.653244</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.887701</v>
+        <v>-0.376003</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.653244</v>
+        <v>4.608216</v>
       </c>
       <c r="AA25" t="n">
-        <v>-0.376003</v>
+        <v>-7.193509</v>
       </c>
       <c r="AB25" t="n">
-        <v>4.608216</v>
+        <v>4.057054</v>
       </c>
       <c r="AC25" t="n">
-        <v>-7.193509</v>
+        <v>-0.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.057054</v>
+        <v>-0.001599</v>
       </c>
       <c r="AE25" t="n">
-        <v>-0.5</v>
+        <v>-0.001599</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.001599</v>
+        <v>-0.02</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.001599</v>
+        <v>0.09</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AK25" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -3261,78 +3109,72 @@
         <v>5625945</v>
       </c>
       <c r="M26" t="n">
-        <v>2215175</v>
+        <v>3410769</v>
       </c>
       <c r="N26" t="n">
-        <v>3410769</v>
+        <v>3.54</v>
       </c>
       <c r="O26" t="n">
-        <v>3.54</v>
+        <v>2.82</v>
       </c>
       <c r="P26" t="n">
-        <v>2.82</v>
+        <v>4</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>29.66</v>
       </c>
       <c r="R26" t="n">
-        <v>29.66</v>
+        <v>340324</v>
       </c>
       <c r="S26" t="n">
-        <v>340324</v>
+        <v>0.012595</v>
       </c>
       <c r="T26" t="n">
-        <v>0.012595</v>
+        <v>-4.052448</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.052448</v>
+        <v>1.741198</v>
       </c>
       <c r="V26" t="n">
-        <v>1.741198</v>
+        <v>1.74141</v>
       </c>
       <c r="W26" t="n">
-        <v>1.74141</v>
+        <v>1.203116</v>
       </c>
       <c r="X26" t="n">
-        <v>1.203116</v>
+        <v>0.719465</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.956912</v>
+        <v>-1.119482</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.719465</v>
+        <v>5.185235</v>
       </c>
       <c r="AA26" t="n">
-        <v>-1.119482</v>
+        <v>-5.956714</v>
       </c>
       <c r="AB26" t="n">
-        <v>5.185235</v>
+        <v>4.505936</v>
       </c>
       <c r="AC26" t="n">
-        <v>-5.956714</v>
+        <v>-0.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>4.505936</v>
+        <v>-0.000768</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.5</v>
+        <v>-0.000768</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.000768</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.000768</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK26" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -3374,78 +3216,72 @@
         <v>5653808</v>
       </c>
       <c r="M27" t="n">
-        <v>2204808</v>
+        <v>3449000</v>
       </c>
       <c r="N27" t="n">
-        <v>3449000</v>
+        <v>3.56</v>
       </c>
       <c r="O27" t="n">
-        <v>3.56</v>
+        <v>2.92</v>
       </c>
       <c r="P27" t="n">
-        <v>2.92</v>
+        <v>3.97</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.97</v>
+        <v>29.24</v>
       </c>
       <c r="R27" t="n">
-        <v>29.24</v>
+        <v>340247</v>
       </c>
       <c r="S27" t="n">
-        <v>340247</v>
+        <v>0.316333</v>
       </c>
       <c r="T27" t="n">
-        <v>0.316333</v>
+        <v>0.171808</v>
       </c>
       <c r="U27" t="n">
-        <v>0.171808</v>
+        <v>0.996485</v>
       </c>
       <c r="V27" t="n">
-        <v>0.996485</v>
+        <v>0.996605</v>
       </c>
       <c r="W27" t="n">
-        <v>0.996605</v>
+        <v>0.495259</v>
       </c>
       <c r="X27" t="n">
-        <v>0.495259</v>
+        <v>1.120891</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.467999</v>
+        <v>-0.022625</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.120891</v>
+        <v>4.819246</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.022625</v>
+        <v>-4.560737</v>
       </c>
       <c r="AB27" t="n">
-        <v>4.819246</v>
+        <v>4.141877</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4.560737</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.141877</v>
+        <v>-0.001143</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>-0.001143</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.001143</v>
+        <v>0.02</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.001143</v>
+        <v>0.1</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK27" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3487,78 +3323,72 @@
         <v>5711103</v>
       </c>
       <c r="M28" t="n">
-        <v>2220766</v>
+        <v>3490337</v>
       </c>
       <c r="N28" t="n">
-        <v>3490337</v>
+        <v>3.53</v>
       </c>
       <c r="O28" t="n">
-        <v>3.53</v>
+        <v>2.99</v>
       </c>
       <c r="P28" t="n">
-        <v>2.99</v>
+        <v>3.88</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.88</v>
+        <v>29.01</v>
       </c>
       <c r="R28" t="n">
-        <v>29.01</v>
+        <v>348406</v>
       </c>
       <c r="S28" t="n">
-        <v>348406</v>
+        <v>0.734124</v>
       </c>
       <c r="T28" t="n">
-        <v>0.734124</v>
+        <v>-0.248573</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.248573</v>
+        <v>-2.412259</v>
       </c>
       <c r="V28" t="n">
-        <v>-2.412259</v>
+        <v>-2.412545</v>
       </c>
       <c r="W28" t="n">
-        <v>-2.412545</v>
+        <v>1.013388</v>
       </c>
       <c r="X28" t="n">
-        <v>1.013388</v>
+        <v>1.198521</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.723782</v>
+        <v>2.397964</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.198521</v>
+        <v>4.683537</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.397964</v>
+        <v>-3.457004</v>
       </c>
       <c r="AB28" t="n">
-        <v>4.683537</v>
+        <v>3.851383</v>
       </c>
       <c r="AC28" t="n">
-        <v>-3.457004</v>
+        <v>-0.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.851383</v>
+        <v>-0.001678</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.5</v>
+        <v>-0.001678</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.001678</v>
+        <v>-0.03</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.001678</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AH28" t="n">
-        <v>-0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="AK28" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -3600,78 +3430,72 @@
         <v>5805157</v>
       </c>
       <c r="M29" t="n">
-        <v>2283485</v>
+        <v>3521672</v>
       </c>
       <c r="N29" t="n">
-        <v>3521672</v>
+        <v>3.29</v>
       </c>
       <c r="O29" t="n">
-        <v>3.29</v>
+        <v>2.59</v>
       </c>
       <c r="P29" t="n">
-        <v>2.59</v>
+        <v>3.75</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.75</v>
+        <v>28.14</v>
       </c>
       <c r="R29" t="n">
-        <v>28.14</v>
+        <v>355034</v>
       </c>
       <c r="S29" t="n">
-        <v>355034</v>
+        <v>1.248734</v>
       </c>
       <c r="T29" t="n">
-        <v>1.248734</v>
+        <v>0.004199</v>
       </c>
       <c r="U29" t="n">
-        <v>0.004199</v>
+        <v>-1.908621</v>
       </c>
       <c r="V29" t="n">
-        <v>-1.908621</v>
+        <v>-1.908853</v>
       </c>
       <c r="W29" t="n">
-        <v>-1.908853</v>
+        <v>1.646862</v>
       </c>
       <c r="X29" t="n">
-        <v>1.646862</v>
+        <v>0.897764</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.824206</v>
+        <v>1.902378</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.897764</v>
+        <v>4.621114</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.902378</v>
+        <v>-3.178284</v>
       </c>
       <c r="AB29" t="n">
-        <v>4.621114</v>
+        <v>3.706988</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.178284</v>
+        <v>-0.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.706988</v>
+        <v>-0.001064</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.5</v>
+        <v>-0.001064</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.001064</v>
+        <v>-0.24</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.001064</v>
+        <v>-0.4</v>
       </c>
       <c r="AH29" t="n">
-        <v>-0.24</v>
+        <v>-0.13</v>
       </c>
       <c r="AI29" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="AK29" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3713,78 +3537,72 @@
         <v>5794707</v>
       </c>
       <c r="M30" t="n">
-        <v>2234362</v>
+        <v>3560345</v>
       </c>
       <c r="N30" t="n">
-        <v>3560345</v>
+        <v>3.38</v>
       </c>
       <c r="O30" t="n">
-        <v>3.38</v>
+        <v>2.77</v>
       </c>
       <c r="P30" t="n">
-        <v>2.77</v>
+        <v>3.76</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.76</v>
+        <v>28</v>
       </c>
       <c r="R30" t="n">
-        <v>28</v>
+        <v>355066</v>
       </c>
       <c r="S30" t="n">
-        <v>355066</v>
+        <v>-0.395831</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.395831</v>
+        <v>-2.347954</v>
       </c>
       <c r="U30" t="n">
-        <v>-2.347954</v>
+        <v>2.317559</v>
       </c>
       <c r="V30" t="n">
-        <v>2.317559</v>
+        <v>2.317847</v>
       </c>
       <c r="W30" t="n">
-        <v>2.317847</v>
+        <v>-0.180012</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.180012</v>
+        <v>1.098143</v>
       </c>
       <c r="Y30" t="n">
-        <v>-2.151229</v>
+        <v>0.009013</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.098143</v>
+        <v>4.506637</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.009013</v>
+        <v>-3.31355</v>
       </c>
       <c r="AB30" t="n">
-        <v>4.506637</v>
+        <v>3.820543</v>
       </c>
       <c r="AC30" t="n">
-        <v>-3.31355</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.820543</v>
+        <v>-0.000798</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>-0.000798</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.000798</v>
+        <v>0.09</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.000798</v>
+        <v>0.18</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK30" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -3826,78 +3644,72 @@
         <v>5815954</v>
       </c>
       <c r="M31" t="n">
-        <v>2235302</v>
+        <v>3580652</v>
       </c>
       <c r="N31" t="n">
-        <v>3580652</v>
+        <v>3.38</v>
       </c>
       <c r="O31" t="n">
-        <v>3.38</v>
+        <v>2.76</v>
       </c>
       <c r="P31" t="n">
-        <v>2.76</v>
+        <v>3.76</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.76</v>
+        <v>27.85</v>
       </c>
       <c r="R31" t="n">
-        <v>27.85</v>
+        <v>352705</v>
       </c>
       <c r="S31" t="n">
-        <v>352705</v>
+        <v>0.177893</v>
       </c>
       <c r="T31" t="n">
-        <v>0.177893</v>
+        <v>2.873375</v>
       </c>
       <c r="U31" t="n">
-        <v>2.873375</v>
+        <v>0.601595</v>
       </c>
       <c r="V31" t="n">
-        <v>0.601595</v>
+        <v>0.601668</v>
       </c>
       <c r="W31" t="n">
-        <v>0.601668</v>
+        <v>0.366662</v>
       </c>
       <c r="X31" t="n">
-        <v>0.366662</v>
+        <v>0.570366</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.04207</v>
+        <v>-0.664947</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.570366</v>
+        <v>4.496274</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.664947</v>
+        <v>-3.758575</v>
       </c>
       <c r="AB31" t="n">
-        <v>4.496274</v>
+        <v>3.861754</v>
       </c>
       <c r="AC31" t="n">
-        <v>-3.758575</v>
+        <v>-0.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.861754</v>
+        <v>-0.001782</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.5</v>
+        <v>-0.001782</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.001782</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.001782</v>
+        <v>-0.01</v>
       </c>
       <c r="AH31" t="n">
         <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -3939,78 +3751,72 @@
         <v>5899742</v>
       </c>
       <c r="M32" t="n">
-        <v>2285775</v>
+        <v>3613967</v>
       </c>
       <c r="N32" t="n">
-        <v>3613967</v>
+        <v>3.33</v>
       </c>
       <c r="O32" t="n">
-        <v>3.33</v>
+        <v>2.71</v>
       </c>
       <c r="P32" t="n">
-        <v>2.71</v>
+        <v>3.71</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.71</v>
+        <v>28.14</v>
       </c>
       <c r="R32" t="n">
-        <v>28.14</v>
+        <v>355008</v>
       </c>
       <c r="S32" t="n">
-        <v>355008</v>
+        <v>0.014285</v>
       </c>
       <c r="T32" t="n">
-        <v>0.014285</v>
+        <v>7.262481</v>
       </c>
       <c r="U32" t="n">
-        <v>7.262481</v>
+        <v>0.258865</v>
       </c>
       <c r="V32" t="n">
-        <v>0.258865</v>
+        <v>0.258896</v>
       </c>
       <c r="W32" t="n">
-        <v>0.258896</v>
+        <v>1.440658</v>
       </c>
       <c r="X32" t="n">
-        <v>1.440658</v>
+        <v>0.930417</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.257995</v>
+        <v>0.652954</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.930417</v>
+        <v>3.925596</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.652954</v>
+        <v>-4.25878</v>
       </c>
       <c r="AB32" t="n">
-        <v>3.925596</v>
+        <v>3.397348</v>
       </c>
       <c r="AC32" t="n">
-        <v>-4.25878</v>
+        <v>-0.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.397348</v>
+        <v>-0.000537</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.5</v>
+        <v>-0.000537</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="AH32" t="n">
         <v>-0.05</v>
       </c>
       <c r="AI32" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AK32" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -4052,78 +3858,72 @@
         <v>5915538</v>
       </c>
       <c r="M33" t="n">
-        <v>2268879</v>
+        <v>3646659</v>
       </c>
       <c r="N33" t="n">
-        <v>3646659</v>
+        <v>3.37</v>
       </c>
       <c r="O33" t="n">
-        <v>3.37</v>
+        <v>2.76</v>
       </c>
       <c r="P33" t="n">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.75</v>
+        <v>27.86</v>
       </c>
       <c r="R33" t="n">
-        <v>27.86</v>
+        <v>351599</v>
       </c>
       <c r="S33" t="n">
-        <v>351599</v>
+        <v>-0.044032</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.044032</v>
+        <v>-0.284579</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.284579</v>
+        <v>3.514671</v>
       </c>
       <c r="V33" t="n">
-        <v>3.514671</v>
+        <v>3.515093</v>
       </c>
       <c r="W33" t="n">
-        <v>3.515093</v>
+        <v>0.267741</v>
       </c>
       <c r="X33" t="n">
-        <v>0.267741</v>
+        <v>0.904602</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.7391799999999999</v>
+        <v>-0.96026</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.904602</v>
+        <v>3.688016</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.96026</v>
+        <v>-3.040871</v>
       </c>
       <c r="AB33" t="n">
-        <v>3.688016</v>
+        <v>3.232784</v>
       </c>
       <c r="AC33" t="n">
-        <v>-3.040871</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.232784</v>
+        <v>-0.001252</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>-0.001252</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.001252</v>
+        <v>0.04</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.001252</v>
+        <v>0.05</v>
       </c>
       <c r="AH33" t="n">
         <v>0.04</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK33" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -4165,78 +3965,72 @@
         <v>5953960</v>
       </c>
       <c r="M34" t="n">
-        <v>2278309</v>
+        <v>3675652</v>
       </c>
       <c r="N34" t="n">
-        <v>3675652</v>
+        <v>3.43</v>
       </c>
       <c r="O34" t="n">
-        <v>3.43</v>
+        <v>2.8</v>
       </c>
       <c r="P34" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.82</v>
+        <v>27.75</v>
       </c>
       <c r="R34" t="n">
-        <v>27.75</v>
+        <v>355560</v>
       </c>
       <c r="S34" t="n">
-        <v>355560</v>
+        <v>0.9333669999999999</v>
       </c>
       <c r="T34" t="n">
-        <v>0.9333669999999999</v>
+        <v>-4.159973</v>
       </c>
       <c r="U34" t="n">
-        <v>-4.159973</v>
+        <v>1.349627</v>
       </c>
       <c r="V34" t="n">
-        <v>1.349627</v>
+        <v>1.349783</v>
       </c>
       <c r="W34" t="n">
-        <v>1.349783</v>
+        <v>0.64951</v>
       </c>
       <c r="X34" t="n">
-        <v>0.64951</v>
+        <v>0.795057</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.415624</v>
+        <v>1.126567</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.795057</v>
+        <v>3.925952</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.126567</v>
+        <v>-0.344269</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.925952</v>
+        <v>3.335647</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.344269</v>
+        <v>-0.25</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.335647</v>
+        <v>-0.000684</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.25</v>
+        <v>-0.000684</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.000684</v>
+        <v>0.06</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.000684</v>
+        <v>0.04</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK34" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -4278,78 +4072,72 @@
         <v>6041898</v>
       </c>
       <c r="M35" t="n">
-        <v>2336858</v>
+        <v>3705041</v>
       </c>
       <c r="N35" t="n">
-        <v>3705041</v>
+        <v>3.29</v>
       </c>
       <c r="O35" t="n">
-        <v>3.29</v>
+        <v>2.64</v>
       </c>
       <c r="P35" t="n">
-        <v>2.64</v>
+        <v>3.71</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.71</v>
+        <v>27.81</v>
       </c>
       <c r="R35" t="n">
-        <v>27.81</v>
+        <v>357827</v>
       </c>
       <c r="S35" t="n">
-        <v>357827</v>
+        <v>0.932566</v>
       </c>
       <c r="T35" t="n">
-        <v>0.932566</v>
+        <v>1.104953</v>
       </c>
       <c r="U35" t="n">
-        <v>1.104953</v>
+        <v>6.053495</v>
       </c>
       <c r="V35" t="n">
-        <v>6.053495</v>
+        <v>6.054188</v>
       </c>
       <c r="W35" t="n">
-        <v>6.054188</v>
+        <v>1.476967</v>
       </c>
       <c r="X35" t="n">
-        <v>1.476967</v>
+        <v>0.799559</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.569845</v>
+        <v>0.637586</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.799559</v>
+        <v>4.227578</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.637586</v>
+        <v>2.440035</v>
       </c>
       <c r="AB35" t="n">
-        <v>4.227578</v>
+        <v>3.697684</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.440035</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.697684</v>
+        <v>-0.000214</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>-0.000214</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.000214</v>
+        <v>-0.14</v>
       </c>
       <c r="AG35" t="n">
-        <v>-0.000214</v>
+        <v>-0.16</v>
       </c>
       <c r="AH35" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="AI35" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="AK35" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -4391,78 +4179,72 @@
         <v>6069205</v>
       </c>
       <c r="M36" t="n">
-        <v>2323362</v>
+        <v>3745844</v>
       </c>
       <c r="N36" t="n">
-        <v>3745844</v>
+        <v>3.3</v>
       </c>
       <c r="O36" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="P36" t="n">
-        <v>2.52</v>
+        <v>3.78</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.78</v>
+        <v>27.74</v>
       </c>
       <c r="R36" t="n">
-        <v>27.74</v>
+        <v>363282</v>
       </c>
       <c r="S36" t="n">
-        <v>363282</v>
+        <v>0.444014</v>
       </c>
       <c r="T36" t="n">
-        <v>0.444014</v>
+        <v>5.327189</v>
       </c>
       <c r="U36" t="n">
-        <v>5.327189</v>
+        <v>1.856482</v>
       </c>
       <c r="V36" t="n">
-        <v>1.856482</v>
+        <v>1.856683</v>
       </c>
       <c r="W36" t="n">
-        <v>1.856683</v>
+        <v>0.451961</v>
       </c>
       <c r="X36" t="n">
-        <v>0.451961</v>
+        <v>1.101283</v>
       </c>
       <c r="Y36" t="n">
-        <v>-0.577528</v>
+        <v>1.52448</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.101283</v>
+        <v>4.498245</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.52448</v>
+        <v>3.812368</v>
       </c>
       <c r="AB36" t="n">
-        <v>4.498245</v>
+        <v>4.060953</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.812368</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>4.060953</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI36" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK36" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -4504,78 +4286,72 @@
         <v>6135298</v>
       </c>
       <c r="M37" t="n">
-        <v>2344397</v>
+        <v>3790900</v>
       </c>
       <c r="N37" t="n">
-        <v>3790900</v>
+        <v>3.33</v>
       </c>
       <c r="O37" t="n">
-        <v>3.33</v>
+        <v>2.55</v>
       </c>
       <c r="P37" t="n">
-        <v>2.55</v>
+        <v>3.82</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.82</v>
+        <v>27.59</v>
       </c>
       <c r="R37" t="n">
-        <v>27.59</v>
+        <v>369214</v>
       </c>
       <c r="S37" t="n">
-        <v>369214</v>
+        <v>0.120836</v>
       </c>
       <c r="T37" t="n">
-        <v>0.120836</v>
+        <v>-1.297169</v>
       </c>
       <c r="U37" t="n">
-        <v>-1.297169</v>
+        <v>-0.104202</v>
       </c>
       <c r="V37" t="n">
-        <v>-0.104202</v>
+        <v>-0.104213</v>
       </c>
       <c r="W37" t="n">
-        <v>-0.104213</v>
+        <v>1.088989</v>
       </c>
       <c r="X37" t="n">
-        <v>1.088989</v>
+        <v>1.202826</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.905369</v>
+        <v>1.632891</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.202826</v>
+        <v>4.237599</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.632891</v>
+        <v>4.259387</v>
       </c>
       <c r="AB37" t="n">
-        <v>4.237599</v>
+        <v>3.707852</v>
       </c>
       <c r="AC37" t="n">
-        <v>4.259387</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.707852</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK37" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4617,78 +4393,72 @@
         <v>6216528</v>
       </c>
       <c r="M38" t="n">
-        <v>2384828</v>
+        <v>3831700</v>
       </c>
       <c r="N38" t="n">
-        <v>3831700</v>
+        <v>3.34</v>
       </c>
       <c r="O38" t="n">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="P38" t="n">
-        <v>2.56</v>
+        <v>3.83</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.83</v>
+        <v>27.49</v>
       </c>
       <c r="R38" t="n">
-        <v>27.49</v>
+        <v>372016</v>
       </c>
       <c r="S38" t="n">
-        <v>372016</v>
+        <v>0.794912</v>
       </c>
       <c r="T38" t="n">
-        <v>0.794912</v>
+        <v>-2.711204</v>
       </c>
       <c r="U38" t="n">
-        <v>-2.711204</v>
+        <v>-3.679149</v>
       </c>
       <c r="V38" t="n">
-        <v>-3.679149</v>
+        <v>-3.679539</v>
       </c>
       <c r="W38" t="n">
-        <v>-3.679539</v>
+        <v>1.323978</v>
       </c>
       <c r="X38" t="n">
-        <v>1.323978</v>
+        <v>1.076262</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.72458</v>
+        <v>0.7589089999999999</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.076262</v>
+        <v>4.42474</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.7589089999999999</v>
+        <v>4.519075</v>
       </c>
       <c r="AB38" t="n">
-        <v>4.42474</v>
+        <v>4.091149</v>
       </c>
       <c r="AC38" t="n">
-        <v>4.519075</v>
+        <v>0.25</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.091149</v>
+        <v>0.000342</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.25</v>
+        <v>0.000342</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="AH38" t="n">
         <v>0.01</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK38" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -4730,78 +4500,72 @@
         <v>6275117</v>
       </c>
       <c r="M39" t="n">
-        <v>2397533</v>
+        <v>3877584</v>
       </c>
       <c r="N39" t="n">
-        <v>3877584</v>
+        <v>3.3</v>
       </c>
       <c r="O39" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="P39" t="n">
-        <v>2.52</v>
+        <v>3.79</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.79</v>
+        <v>27.94</v>
       </c>
       <c r="R39" t="n">
-        <v>27.94</v>
+        <v>366096</v>
       </c>
       <c r="S39" t="n">
-        <v>366096</v>
+        <v>0.185832</v>
       </c>
       <c r="T39" t="n">
-        <v>0.185832</v>
+        <v>1.966099</v>
       </c>
       <c r="U39" t="n">
-        <v>1.966099</v>
+        <v>6.053487</v>
       </c>
       <c r="V39" t="n">
-        <v>6.053487</v>
+        <v>6.054153</v>
       </c>
       <c r="W39" t="n">
-        <v>6.054153</v>
+        <v>0.9424709999999999</v>
       </c>
       <c r="X39" t="n">
-        <v>0.9424709999999999</v>
+        <v>1.197484</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.532743</v>
+        <v>-1.591329</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.197484</v>
+        <v>4.758099</v>
       </c>
       <c r="AA39" t="n">
-        <v>-1.591329</v>
+        <v>5.579866</v>
       </c>
       <c r="AB39" t="n">
-        <v>4.758099</v>
+        <v>4.600584</v>
       </c>
       <c r="AC39" t="n">
-        <v>5.579866</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>4.600584</v>
+        <v>0.000556</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>0.000556</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="AH39" t="n">
         <v>-0.04</v>
       </c>
       <c r="AI39" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AK39" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -4843,78 +4607,72 @@
         <v>6365690</v>
       </c>
       <c r="M40" t="n">
-        <v>2436022</v>
+        <v>3929668</v>
       </c>
       <c r="N40" t="n">
-        <v>3929668</v>
+        <v>3.27</v>
       </c>
       <c r="O40" t="n">
-        <v>3.27</v>
+        <v>2.5</v>
       </c>
       <c r="P40" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.75</v>
+        <v>28.45</v>
       </c>
       <c r="R40" t="n">
-        <v>28.45</v>
+        <v>363003</v>
       </c>
       <c r="S40" t="n">
-        <v>363003</v>
+        <v>-0.224963</v>
       </c>
       <c r="T40" t="n">
-        <v>-0.224963</v>
+        <v>-3.383039</v>
       </c>
       <c r="U40" t="n">
-        <v>-3.383039</v>
+        <v>4.769899</v>
       </c>
       <c r="V40" t="n">
-        <v>4.769899</v>
+        <v>4.770394</v>
       </c>
       <c r="W40" t="n">
-        <v>4.770394</v>
+        <v>1.443368</v>
       </c>
       <c r="X40" t="n">
-        <v>1.443368</v>
+        <v>1.343208</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.605359</v>
+        <v>-0.8448600000000001</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.343208</v>
+        <v>4.873011</v>
       </c>
       <c r="AA40" t="n">
-        <v>-0.8448600000000001</v>
+        <v>6.325086</v>
       </c>
       <c r="AB40" t="n">
-        <v>4.873011</v>
+        <v>4.840925</v>
       </c>
       <c r="AC40" t="n">
-        <v>6.325086</v>
+        <v>0.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.840925</v>
+        <v>0.001412</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.5</v>
+        <v>0.001412</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.001412</v>
+        <v>-0.03</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.001412</v>
+        <v>-0.02</v>
       </c>
       <c r="AH40" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="AI40" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AK40" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4956,78 +4714,72 @@
         <v>6464602</v>
       </c>
       <c r="M41" t="n">
-        <v>2499177</v>
+        <v>3965425</v>
       </c>
       <c r="N41" t="n">
-        <v>3965425</v>
+        <v>3.08</v>
       </c>
       <c r="O41" t="n">
-        <v>3.08</v>
+        <v>2.21</v>
       </c>
       <c r="P41" t="n">
-        <v>2.21</v>
+        <v>3.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.63</v>
+        <v>28.5</v>
       </c>
       <c r="R41" t="n">
-        <v>28.5</v>
+        <v>329730</v>
       </c>
       <c r="S41" t="n">
-        <v>329730</v>
+        <v>-0.584226</v>
       </c>
       <c r="T41" t="n">
-        <v>-0.584226</v>
+        <v>-1.265086</v>
       </c>
       <c r="U41" t="n">
-        <v>-1.265086</v>
+        <v>2.292888</v>
       </c>
       <c r="V41" t="n">
-        <v>2.292888</v>
+        <v>2.293116</v>
       </c>
       <c r="W41" t="n">
-        <v>2.293116</v>
+        <v>1.55383</v>
       </c>
       <c r="X41" t="n">
-        <v>1.55383</v>
+        <v>0.909924</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.592546</v>
+        <v>-9.166040000000001</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.909924</v>
+        <v>4.831296</v>
       </c>
       <c r="AA41" t="n">
-        <v>-9.166040000000001</v>
+        <v>6.536174</v>
       </c>
       <c r="AB41" t="n">
-        <v>4.831296</v>
+        <v>4.767938</v>
       </c>
       <c r="AC41" t="n">
-        <v>6.536174</v>
+        <v>1</v>
       </c>
       <c r="AD41" t="n">
-        <v>4.767938</v>
+        <v>0.002578</v>
       </c>
       <c r="AE41" t="n">
-        <v>1</v>
+        <v>0.002578</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.002578</v>
+        <v>-0.19</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.002578</v>
+        <v>-0.29</v>
       </c>
       <c r="AH41" t="n">
-        <v>-0.19</v>
+        <v>-0.12</v>
       </c>
       <c r="AI41" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK41" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -5069,78 +4821,72 @@
         <v>6465016</v>
       </c>
       <c r="M42" t="n">
-        <v>2451957</v>
+        <v>4013059</v>
       </c>
       <c r="N42" t="n">
-        <v>4013059</v>
+        <v>3.34</v>
       </c>
       <c r="O42" t="n">
-        <v>3.34</v>
+        <v>2.43</v>
       </c>
       <c r="P42" t="n">
-        <v>2.43</v>
+        <v>3.89</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.89</v>
+        <v>29.88</v>
       </c>
       <c r="R42" t="n">
-        <v>29.88</v>
+        <v>328303</v>
       </c>
       <c r="S42" t="n">
-        <v>328303</v>
+        <v>0.675346</v>
       </c>
       <c r="T42" t="n">
-        <v>0.675346</v>
+        <v>-1.465146</v>
       </c>
       <c r="U42" t="n">
-        <v>-1.465146</v>
+        <v>-5.8492</v>
       </c>
       <c r="V42" t="n">
-        <v>-5.8492</v>
+        <v>-5.849767</v>
       </c>
       <c r="W42" t="n">
-        <v>-5.849767</v>
+        <v>0.006404</v>
       </c>
       <c r="X42" t="n">
-        <v>0.006404</v>
+        <v>1.201233</v>
       </c>
       <c r="Y42" t="n">
-        <v>-1.889422</v>
+        <v>-0.432778</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.201233</v>
+        <v>4.559874</v>
       </c>
       <c r="AA42" t="n">
-        <v>-0.432778</v>
+        <v>6.749097</v>
       </c>
       <c r="AB42" t="n">
-        <v>4.559874</v>
+        <v>4.174145</v>
       </c>
       <c r="AC42" t="n">
-        <v>6.749097</v>
+        <v>1</v>
       </c>
       <c r="AD42" t="n">
-        <v>4.174145</v>
+        <v>0.001675</v>
       </c>
       <c r="AE42" t="n">
-        <v>1</v>
+        <v>0.001675</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.001675</v>
+        <v>0.26</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.001675</v>
+        <v>0.22</v>
       </c>
       <c r="AH42" t="n">
         <v>0.26</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK42" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -5182,78 +4928,72 @@
         <v>6511444</v>
       </c>
       <c r="M43" t="n">
-        <v>2477151</v>
+        <v>4034293</v>
       </c>
       <c r="N43" t="n">
-        <v>4034293</v>
+        <v>3.41</v>
       </c>
       <c r="O43" t="n">
-        <v>3.41</v>
+        <v>2.52</v>
       </c>
       <c r="P43" t="n">
-        <v>2.52</v>
+        <v>3.96</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.96</v>
+        <v>30.53</v>
       </c>
       <c r="R43" t="n">
-        <v>30.53</v>
+        <v>332508</v>
       </c>
       <c r="S43" t="n">
-        <v>332508</v>
+        <v>0.485516</v>
       </c>
       <c r="T43" t="n">
-        <v>0.485516</v>
+        <v>4.088981</v>
       </c>
       <c r="U43" t="n">
-        <v>4.088981</v>
+        <v>0.320749</v>
       </c>
       <c r="V43" t="n">
-        <v>0.320749</v>
+        <v>0.320782</v>
       </c>
       <c r="W43" t="n">
-        <v>0.320782</v>
+        <v>0.7181419999999999</v>
       </c>
       <c r="X43" t="n">
-        <v>0.7181419999999999</v>
+        <v>0.529123</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.027506</v>
+        <v>1.280829</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.529123</v>
+        <v>5.05763</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.280829</v>
+        <v>8.444549</v>
       </c>
       <c r="AB43" t="n">
-        <v>5.05763</v>
+        <v>4.866504</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.444549</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>4.866504</v>
+        <v>0.003204</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>0.003204</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.003204</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.003204</v>
+        <v>0.09</v>
       </c>
       <c r="AH43" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK43" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -5295,78 +5035,72 @@
         <v>6576464</v>
       </c>
       <c r="M44" t="n">
-        <v>2498262</v>
+        <v>4078202</v>
       </c>
       <c r="N44" t="n">
-        <v>4078202</v>
+        <v>3.44</v>
       </c>
       <c r="O44" t="n">
-        <v>3.44</v>
+        <v>2.49</v>
       </c>
       <c r="P44" t="n">
-        <v>2.49</v>
+        <v>4.03</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.03</v>
+        <v>31.34</v>
       </c>
       <c r="R44" t="n">
-        <v>31.34</v>
+        <v>336157</v>
       </c>
       <c r="S44" t="n">
-        <v>336157</v>
+        <v>1.30069</v>
       </c>
       <c r="T44" t="n">
-        <v>1.30069</v>
+        <v>6.734953</v>
       </c>
       <c r="U44" t="n">
-        <v>6.734953</v>
+        <v>-1.822596</v>
       </c>
       <c r="V44" t="n">
-        <v>-1.822596</v>
+        <v>-1.822783</v>
       </c>
       <c r="W44" t="n">
-        <v>-1.822783</v>
+        <v>0.99855</v>
       </c>
       <c r="X44" t="n">
-        <v>0.99855</v>
+        <v>1.088394</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.852229</v>
+        <v>1.097417</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.088394</v>
+        <v>5.47719</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.097417</v>
+        <v>8.586193</v>
       </c>
       <c r="AB44" t="n">
-        <v>5.47719</v>
+        <v>5.201441</v>
       </c>
       <c r="AC44" t="n">
-        <v>8.586193</v>
+        <v>1</v>
       </c>
       <c r="AD44" t="n">
-        <v>5.201441</v>
+        <v>0.001471</v>
       </c>
       <c r="AE44" t="n">
-        <v>1</v>
+        <v>0.001471</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.001471</v>
+        <v>0.03</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.001471</v>
+        <v>-0.03</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI44" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK44" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -5408,78 +5142,72 @@
         <v>6623948</v>
       </c>
       <c r="M45" t="n">
-        <v>2512426</v>
+        <v>4111522</v>
       </c>
       <c r="N45" t="n">
-        <v>4111522</v>
+        <v>3.67</v>
       </c>
       <c r="O45" t="n">
-        <v>3.67</v>
+        <v>2.72</v>
       </c>
       <c r="P45" t="n">
-        <v>2.72</v>
+        <v>4.25</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.25</v>
+        <v>31.63</v>
       </c>
       <c r="R45" t="n">
-        <v>31.63</v>
+        <v>340789</v>
       </c>
       <c r="S45" t="n">
-        <v>340789</v>
+        <v>-0.459145</v>
       </c>
       <c r="T45" t="n">
-        <v>-0.459145</v>
+        <v>-1.250256</v>
       </c>
       <c r="U45" t="n">
-        <v>-1.250256</v>
+        <v>-1.417575</v>
       </c>
       <c r="V45" t="n">
-        <v>-1.417575</v>
+        <v>-1.417723</v>
       </c>
       <c r="W45" t="n">
-        <v>-1.417723</v>
+        <v>0.722029</v>
       </c>
       <c r="X45" t="n">
-        <v>0.722029</v>
+        <v>0.8170269999999999</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.566954</v>
+        <v>1.377928</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.8170269999999999</v>
+        <v>5.529729</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.377928</v>
+        <v>8.510418</v>
       </c>
       <c r="AB45" t="n">
-        <v>5.529729</v>
+        <v>5.316736</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.510418</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>5.316736</v>
+        <v>0.002023</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>0.002023</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AK45" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -5521,78 +5249,72 @@
         <v>6666287</v>
       </c>
       <c r="M46" t="n">
-        <v>2532708</v>
+        <v>4133579</v>
       </c>
       <c r="N46" t="n">
-        <v>4133579</v>
+        <v>3.72</v>
       </c>
       <c r="O46" t="n">
-        <v>3.72</v>
+        <v>2.67</v>
       </c>
       <c r="P46" t="n">
-        <v>2.67</v>
+        <v>4.36</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.36</v>
+        <v>31.7</v>
       </c>
       <c r="R46" t="n">
-        <v>31.7</v>
+        <v>341459</v>
       </c>
       <c r="S46" t="n">
-        <v>341459</v>
+        <v>-0.58566</v>
       </c>
       <c r="T46" t="n">
-        <v>-0.58566</v>
+        <v>-3.586372</v>
       </c>
       <c r="U46" t="n">
-        <v>-3.586372</v>
+        <v>0.84617</v>
       </c>
       <c r="V46" t="n">
-        <v>0.84617</v>
+        <v>0.84626</v>
       </c>
       <c r="W46" t="n">
-        <v>0.84626</v>
+        <v>0.639181</v>
       </c>
       <c r="X46" t="n">
-        <v>0.639181</v>
+        <v>0.5364679999999999</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.807268</v>
+        <v>0.196603</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.5364679999999999</v>
+        <v>5.319636</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.196603</v>
+        <v>7.026183</v>
       </c>
       <c r="AB46" t="n">
-        <v>5.319636</v>
+        <v>5.201418</v>
       </c>
       <c r="AC46" t="n">
-        <v>7.026183</v>
+        <v>0.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>5.201418</v>
+        <v>0.001405</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.5</v>
+        <v>0.001405</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.001405</v>
+        <v>0.05</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.001405</v>
+        <v>-0.05</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="AI46" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK46" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5634,78 +5356,72 @@
         <v>6703663</v>
       </c>
       <c r="M47" t="n">
-        <v>2547693</v>
+        <v>4155970</v>
       </c>
       <c r="N47" t="n">
-        <v>4155970</v>
+        <v>3.75</v>
       </c>
       <c r="O47" t="n">
-        <v>3.75</v>
+        <v>2.67</v>
       </c>
       <c r="P47" t="n">
-        <v>2.67</v>
+        <v>4.41</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.41</v>
+        <v>31.85</v>
       </c>
       <c r="R47" t="n">
-        <v>31.85</v>
+        <v>344440</v>
       </c>
       <c r="S47" t="n">
-        <v>344440</v>
+        <v>-0.075712</v>
       </c>
       <c r="T47" t="n">
-        <v>-0.075712</v>
+        <v>-1.100666</v>
       </c>
       <c r="U47" t="n">
-        <v>-1.100666</v>
+        <v>-4.407308</v>
       </c>
       <c r="V47" t="n">
-        <v>-4.407308</v>
+        <v>-4.407771</v>
       </c>
       <c r="W47" t="n">
-        <v>-4.407771</v>
+        <v>0.5606719999999999</v>
       </c>
       <c r="X47" t="n">
-        <v>0.5606719999999999</v>
+        <v>0.541686</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.591659</v>
+        <v>0.873018</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.541686</v>
+        <v>5.351165</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.873018</v>
+        <v>4.393261</v>
       </c>
       <c r="AB47" t="n">
-        <v>5.351165</v>
+        <v>5.18043</v>
       </c>
       <c r="AC47" t="n">
-        <v>4.393261</v>
+        <v>0.25</v>
       </c>
       <c r="AD47" t="n">
-        <v>5.18043</v>
+        <v>0.000633</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.25</v>
+        <v>0.000633</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.000633</v>
+        <v>0.03</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.000633</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK47" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5747,78 +5463,72 @@
         <v>6733209</v>
       </c>
       <c r="M48" t="n">
-        <v>2544400</v>
+        <v>4188808</v>
       </c>
       <c r="N48" t="n">
-        <v>4188808</v>
+        <v>3.96</v>
       </c>
       <c r="O48" t="n">
-        <v>3.96</v>
+        <v>2.79</v>
       </c>
       <c r="P48" t="n">
-        <v>2.79</v>
+        <v>4.66</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.66</v>
+        <v>31.75</v>
       </c>
       <c r="R48" t="n">
-        <v>31.75</v>
+        <v>345111</v>
       </c>
       <c r="S48" t="n">
-        <v>345111</v>
+        <v>-0.280386</v>
       </c>
       <c r="T48" t="n">
-        <v>-0.280386</v>
+        <v>5.352993</v>
       </c>
       <c r="U48" t="n">
-        <v>5.352993</v>
+        <v>2.657089</v>
       </c>
       <c r="V48" t="n">
-        <v>2.657089</v>
+        <v>2.657381</v>
       </c>
       <c r="W48" t="n">
-        <v>2.657381</v>
+        <v>0.440744</v>
       </c>
       <c r="X48" t="n">
-        <v>0.440744</v>
+        <v>0.79014</v>
       </c>
       <c r="Y48" t="n">
-        <v>-0.129254</v>
+        <v>0.194809</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.79014</v>
+        <v>5.225222</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.194809</v>
+        <v>2.961368</v>
       </c>
       <c r="AB48" t="n">
-        <v>5.225222</v>
+        <v>5.127976</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.961368</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>5.127976</v>
+        <v>0.000562</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>0.000562</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.000562</v>
+        <v>0.21</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.000562</v>
+        <v>0.12</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="AI48" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK48" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -5860,78 +5570,72 @@
         <v>6774436</v>
       </c>
       <c r="M49" t="n">
-        <v>2546265</v>
+        <v>4228171</v>
       </c>
       <c r="N49" t="n">
-        <v>4228171</v>
+        <v>4.14</v>
       </c>
       <c r="O49" t="n">
-        <v>4.14</v>
+        <v>2.85</v>
       </c>
       <c r="P49" t="n">
-        <v>2.85</v>
+        <v>4.92</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.92</v>
+        <v>31.87</v>
       </c>
       <c r="R49" t="n">
-        <v>31.87</v>
+        <v>350767</v>
       </c>
       <c r="S49" t="n">
-        <v>350767</v>
+        <v>0.304372</v>
       </c>
       <c r="T49" t="n">
-        <v>0.304372</v>
+        <v>-2.412481</v>
       </c>
       <c r="U49" t="n">
-        <v>-2.412481</v>
+        <v>-3.136324</v>
       </c>
       <c r="V49" t="n">
-        <v>-3.136324</v>
+        <v>-3.13666</v>
       </c>
       <c r="W49" t="n">
-        <v>-3.13666</v>
+        <v>0.612293</v>
       </c>
       <c r="X49" t="n">
-        <v>0.612293</v>
+        <v>0.9397180000000001</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.073298</v>
+        <v>1.638893</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.9397180000000001</v>
+        <v>5.130501</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.638893</v>
+        <v>3.033233</v>
       </c>
       <c r="AB49" t="n">
-        <v>5.130501</v>
+        <v>5.054283</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.033233</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>5.054283</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK49" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5973,78 +5677,72 @@
         <v>6852705</v>
       </c>
       <c r="M50" t="n">
-        <v>2589817</v>
+        <v>4262888</v>
       </c>
       <c r="N50" t="n">
-        <v>4262888</v>
+        <v>4.09</v>
       </c>
       <c r="O50" t="n">
-        <v>4.09</v>
+        <v>2.77</v>
       </c>
       <c r="P50" t="n">
-        <v>2.77</v>
+        <v>4.89</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.89</v>
+        <v>31.47</v>
       </c>
       <c r="R50" t="n">
-        <v>31.47</v>
+        <v>356582</v>
       </c>
       <c r="S50" t="n">
-        <v>356582</v>
+        <v>-0.085869</v>
       </c>
       <c r="T50" t="n">
-        <v>-0.085869</v>
+        <v>-0.812453</v>
       </c>
       <c r="U50" t="n">
-        <v>-0.812453</v>
+        <v>-1.986584</v>
       </c>
       <c r="V50" t="n">
-        <v>-1.986584</v>
+        <v>-1.986804</v>
       </c>
       <c r="W50" t="n">
-        <v>-1.986804</v>
+        <v>1.155358</v>
       </c>
       <c r="X50" t="n">
-        <v>1.155358</v>
+        <v>0.821088</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.710427</v>
+        <v>1.657796</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.821088</v>
+        <v>5.172369</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.657796</v>
+        <v>2.828436</v>
       </c>
       <c r="AB50" t="n">
-        <v>5.172369</v>
+        <v>5.096104</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.828436</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>5.096104</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="AH50" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="AI50" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK50" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -6086,78 +5784,72 @@
         <v>6923886</v>
       </c>
       <c r="M51" t="n">
-        <v>2597630</v>
+        <v>4326256</v>
       </c>
       <c r="N51" t="n">
-        <v>4326256</v>
+        <v>4.18</v>
       </c>
       <c r="O51" t="n">
-        <v>4.18</v>
+        <v>2.82</v>
       </c>
       <c r="P51" t="n">
-        <v>2.82</v>
+        <v>4.99</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.99</v>
+        <v>32.04</v>
       </c>
       <c r="R51" t="n">
-        <v>32.04</v>
+        <v>357103</v>
       </c>
       <c r="S51" t="n">
-        <v>357103</v>
+        <v>0.016352</v>
       </c>
       <c r="T51" t="n">
-        <v>0.016352</v>
+        <v>0.541697</v>
       </c>
       <c r="U51" t="n">
-        <v>0.541697</v>
+        <v>1.235287</v>
       </c>
       <c r="V51" t="n">
-        <v>1.235287</v>
+        <v>1.235427</v>
       </c>
       <c r="W51" t="n">
-        <v>1.235427</v>
+        <v>1.038729</v>
       </c>
       <c r="X51" t="n">
-        <v>1.038729</v>
+        <v>1.486504</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.301682</v>
+        <v>0.146109</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.486504</v>
+        <v>4.680811</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.146109</v>
+        <v>0.924206</v>
       </c>
       <c r="AB51" t="n">
-        <v>4.680811</v>
+        <v>4.490243</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.924206</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>4.490243</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK51" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -6199,78 +5891,72 @@
         <v>7004223</v>
       </c>
       <c r="M52" t="n">
-        <v>2616902</v>
+        <v>4387321</v>
       </c>
       <c r="N52" t="n">
-        <v>4387321</v>
+        <v>4.24</v>
       </c>
       <c r="O52" t="n">
-        <v>4.24</v>
+        <v>2.75</v>
       </c>
       <c r="P52" t="n">
-        <v>2.75</v>
+        <v>5.12</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.12</v>
+        <v>32.2</v>
       </c>
       <c r="R52" t="n">
-        <v>32.2</v>
+        <v>360578</v>
       </c>
       <c r="S52" t="n">
-        <v>360578</v>
+        <v>0.456805</v>
       </c>
       <c r="T52" t="n">
-        <v>0.456805</v>
+        <v>-3.159521</v>
       </c>
       <c r="U52" t="n">
-        <v>-3.159521</v>
+        <v>-0.937912</v>
       </c>
       <c r="V52" t="n">
-        <v>-0.937912</v>
+        <v>-0.938017</v>
       </c>
       <c r="W52" t="n">
-        <v>-0.938017</v>
+        <v>1.160288</v>
       </c>
       <c r="X52" t="n">
-        <v>1.160288</v>
+        <v>1.411498</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.741907</v>
+        <v>0.973109</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.411498</v>
+        <v>4.461836</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.973109</v>
+        <v>-0.101973</v>
       </c>
       <c r="AB52" t="n">
-        <v>4.461836</v>
+        <v>4.177803</v>
       </c>
       <c r="AC52" t="n">
-        <v>-0.101973</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>4.177803</v>
+        <v>-0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF52" t="n">
-        <v>-0</v>
+        <v>0.06</v>
       </c>
       <c r="AG52" t="n">
-        <v>-0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AH52" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="AI52" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AK52" t="n">
         <v>0.16</v>
       </c>
     </row>
@@ -6312,78 +5998,72 @@
         <v>7137252</v>
       </c>
       <c r="M53" t="n">
-        <v>2701735</v>
+        <v>4435517</v>
       </c>
       <c r="N53" t="n">
-        <v>4435517</v>
+        <v>4.2</v>
       </c>
       <c r="O53" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="P53" t="n">
-        <v>2.7</v>
+        <v>5.12</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.12</v>
+        <v>31.87</v>
       </c>
       <c r="R53" t="n">
-        <v>31.87</v>
+        <v>358234</v>
       </c>
       <c r="S53" t="n">
-        <v>358234</v>
+        <v>0.185583</v>
       </c>
       <c r="T53" t="n">
-        <v>0.185583</v>
+        <v>0.549021</v>
       </c>
       <c r="U53" t="n">
-        <v>0.549021</v>
+        <v>3.160973</v>
       </c>
       <c r="V53" t="n">
-        <v>3.160973</v>
+        <v>3.161329</v>
       </c>
       <c r="W53" t="n">
-        <v>3.161329</v>
+        <v>1.899268</v>
       </c>
       <c r="X53" t="n">
-        <v>1.899268</v>
+        <v>1.098529</v>
       </c>
       <c r="Y53" t="n">
-        <v>3.241734</v>
+        <v>-0.650067</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.098529</v>
+        <v>4.264385</v>
       </c>
       <c r="AA53" t="n">
-        <v>-0.650067</v>
+        <v>-1.042167</v>
       </c>
       <c r="AB53" t="n">
-        <v>4.264385</v>
+        <v>3.897866</v>
       </c>
       <c r="AC53" t="n">
-        <v>-1.042167</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>3.897866</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AH53" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -6425,78 +6105,72 @@
         <v>7130762</v>
       </c>
       <c r="M54" t="n">
-        <v>2654220</v>
+        <v>4476542</v>
       </c>
       <c r="N54" t="n">
-        <v>4476542</v>
+        <v>4.44</v>
       </c>
       <c r="O54" t="n">
-        <v>4.44</v>
+        <v>2.87</v>
       </c>
       <c r="P54" t="n">
-        <v>2.87</v>
+        <v>5.38</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.38</v>
+        <v>32.45</v>
       </c>
       <c r="R54" t="n">
-        <v>32.45</v>
+        <v>364367</v>
       </c>
       <c r="S54" t="n">
-        <v>364367</v>
+        <v>0.54555</v>
       </c>
       <c r="T54" t="n">
-        <v>0.54555</v>
+        <v>-3.178231</v>
       </c>
       <c r="U54" t="n">
-        <v>-3.178231</v>
+        <v>-4.94875</v>
       </c>
       <c r="V54" t="n">
-        <v>-4.94875</v>
+        <v>-4.949289</v>
       </c>
       <c r="W54" t="n">
-        <v>-4.949289</v>
+        <v>-0.090931</v>
       </c>
       <c r="X54" t="n">
-        <v>-0.090931</v>
+        <v>0.92492</v>
       </c>
       <c r="Y54" t="n">
-        <v>-1.758685</v>
+        <v>1.712009</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.92492</v>
+        <v>4.441351</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.712009</v>
+        <v>-0.903999</v>
       </c>
       <c r="AB54" t="n">
-        <v>4.441351</v>
+        <v>4.303068</v>
       </c>
       <c r="AC54" t="n">
-        <v>-0.903999</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>4.303068</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
         <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AH54" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="AI54" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK54" t="n">
         <v>0.58</v>
       </c>
     </row>
@@ -6538,78 +6212,72 @@
         <v>7157783</v>
       </c>
       <c r="M55" t="n">
-        <v>2656484</v>
+        <v>4501299</v>
       </c>
       <c r="N55" t="n">
-        <v>4501299</v>
+        <v>4.64</v>
       </c>
       <c r="O55" t="n">
-        <v>4.64</v>
+        <v>3.07</v>
       </c>
       <c r="P55" t="n">
-        <v>3.07</v>
+        <v>5.56</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.56</v>
+        <v>32.63</v>
       </c>
       <c r="R55" t="n">
-        <v>32.63</v>
+        <v>371074</v>
       </c>
       <c r="S55" t="n">
-        <v>371074</v>
+        <v>0.6239710000000001</v>
       </c>
       <c r="T55" t="n">
-        <v>0.6239710000000001</v>
+        <v>2.874551</v>
       </c>
       <c r="U55" t="n">
-        <v>2.874551</v>
+        <v>-1.54108</v>
       </c>
       <c r="V55" t="n">
-        <v>-1.54108</v>
+        <v>-1.541256</v>
       </c>
       <c r="W55" t="n">
-        <v>-1.541256</v>
+        <v>0.378936</v>
       </c>
       <c r="X55" t="n">
-        <v>0.378936</v>
+        <v>0.553038</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.085298</v>
+        <v>1.840727</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.553038</v>
+        <v>3.812497</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.840727</v>
+        <v>-2.659212</v>
       </c>
       <c r="AB55" t="n">
-        <v>3.812497</v>
+        <v>3.357475</v>
       </c>
       <c r="AC55" t="n">
-        <v>-2.659212</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.357475</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
         <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AH55" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AI55" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AK55" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -6651,78 +6319,72 @@
         <v>7240557</v>
       </c>
       <c r="M56" t="n">
-        <v>2687535</v>
+        <v>4553022</v>
       </c>
       <c r="N56" t="n">
-        <v>4553022</v>
+        <v>4.52</v>
       </c>
       <c r="O56" t="n">
-        <v>4.52</v>
+        <v>3.06</v>
       </c>
       <c r="P56" t="n">
-        <v>3.06</v>
+        <v>5.39</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.39</v>
+        <v>32.84</v>
       </c>
       <c r="R56" t="n">
-        <v>32.84</v>
+        <v>362002</v>
       </c>
       <c r="S56" t="n">
-        <v>362002</v>
+        <v>-0.13412</v>
       </c>
       <c r="T56" t="n">
-        <v>-0.13412</v>
+        <v>10.543613</v>
       </c>
       <c r="U56" t="n">
-        <v>10.543613</v>
+        <v>1.357413</v>
       </c>
       <c r="V56" t="n">
-        <v>1.357413</v>
+        <v>1.357572</v>
       </c>
       <c r="W56" t="n">
-        <v>1.357572</v>
+        <v>1.15642</v>
       </c>
       <c r="X56" t="n">
-        <v>1.15642</v>
+        <v>1.149068</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.168876</v>
+        <v>-2.444795</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.149068</v>
+        <v>4.142847</v>
       </c>
       <c r="AA56" t="n">
-        <v>-2.444795</v>
+        <v>-1.819225</v>
       </c>
       <c r="AB56" t="n">
-        <v>4.142847</v>
+        <v>3.768807</v>
       </c>
       <c r="AC56" t="n">
-        <v>-1.819225</v>
+        <v>-0.25</v>
       </c>
       <c r="AD56" t="n">
-        <v>3.768807</v>
+        <v>-0.000354</v>
       </c>
       <c r="AE56" t="n">
-        <v>-0.25</v>
+        <v>-0.000354</v>
       </c>
       <c r="AF56" t="n">
-        <v>-0.000354</v>
+        <v>-0.12</v>
       </c>
       <c r="AG56" t="n">
-        <v>-0.000354</v>
+        <v>-0.01</v>
       </c>
       <c r="AH56" t="n">
-        <v>-0.12</v>
+        <v>-0.17</v>
       </c>
       <c r="AI56" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="AK56" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -6764,78 +6426,72 @@
         <v>7259766</v>
       </c>
       <c r="M57" t="n">
-        <v>2685397</v>
+        <v>4574368</v>
       </c>
       <c r="N57" t="n">
-        <v>4574368</v>
+        <v>4.64</v>
       </c>
       <c r="O57" t="n">
-        <v>4.64</v>
+        <v>3.15</v>
       </c>
       <c r="P57" t="n">
-        <v>3.15</v>
+        <v>5.51</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.51</v>
+        <v>33.36</v>
       </c>
       <c r="R57" t="n">
-        <v>33.36</v>
+        <v>366913</v>
       </c>
       <c r="S57" t="n">
-        <v>366913</v>
+        <v>0.282137</v>
       </c>
       <c r="T57" t="n">
-        <v>0.282137</v>
+        <v>-3.409876</v>
       </c>
       <c r="U57" t="n">
-        <v>-3.409876</v>
+        <v>-4.421964</v>
       </c>
       <c r="V57" t="n">
-        <v>-4.421964</v>
+        <v>-4.422473</v>
       </c>
       <c r="W57" t="n">
-        <v>-4.422473</v>
+        <v>0.265297</v>
       </c>
       <c r="X57" t="n">
-        <v>0.265297</v>
+        <v>0.468831</v>
       </c>
       <c r="Y57" t="n">
-        <v>-0.079552</v>
+        <v>1.356622</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.468831</v>
+        <v>4.39172</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.356622</v>
+        <v>0.619623</v>
       </c>
       <c r="AB57" t="n">
-        <v>4.39172</v>
+        <v>4.109608</v>
       </c>
       <c r="AC57" t="n">
-        <v>0.619623</v>
+        <v>-0.25</v>
       </c>
       <c r="AD57" t="n">
-        <v>4.109608</v>
+        <v>-0.000554</v>
       </c>
       <c r="AE57" t="n">
-        <v>-0.25</v>
+        <v>-0.000554</v>
       </c>
       <c r="AF57" t="n">
-        <v>-0.000554</v>
+        <v>0.12</v>
       </c>
       <c r="AG57" t="n">
-        <v>-0.000554</v>
+        <v>0.09</v>
       </c>
       <c r="AH57" t="n">
         <v>0.12</v>
       </c>
       <c r="AI57" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AK57" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -6877,78 +6533,72 @@
         <v>7305306</v>
       </c>
       <c r="M58" t="n">
-        <v>2708154</v>
+        <v>4597152</v>
       </c>
       <c r="N58" t="n">
-        <v>4597152</v>
+        <v>4.74</v>
       </c>
       <c r="O58" t="n">
-        <v>4.74</v>
+        <v>3.25</v>
       </c>
       <c r="P58" t="n">
-        <v>3.25</v>
+        <v>5.62</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.62</v>
+        <v>33.1</v>
       </c>
       <c r="R58" t="n">
-        <v>33.1</v>
+        <v>371137</v>
       </c>
       <c r="S58" t="n">
-        <v>371137</v>
+        <v>0.214941</v>
       </c>
       <c r="T58" t="n">
-        <v>0.214941</v>
+        <v>-3.805639</v>
       </c>
       <c r="U58" t="n">
-        <v>-3.805639</v>
+        <v>1.369122</v>
       </c>
       <c r="V58" t="n">
-        <v>1.369122</v>
+        <v>1.369286</v>
       </c>
       <c r="W58" t="n">
-        <v>1.369286</v>
+        <v>0.627293</v>
       </c>
       <c r="X58" t="n">
-        <v>0.627293</v>
+        <v>0.49808</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.847435</v>
+        <v>1.151227</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.49808</v>
+        <v>4.724907</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.151227</v>
+        <v>1.964454</v>
       </c>
       <c r="AB58" t="n">
-        <v>4.724907</v>
+        <v>4.420848</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.964454</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>4.420848</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="AF58" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="AG58" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="AH58" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="AI58" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK58" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -6990,78 +6640,72 @@
         <v>7353293</v>
       </c>
       <c r="M59" t="n">
-        <v>2750625</v>
+        <v>4602668</v>
       </c>
       <c r="N59" t="n">
-        <v>4602668</v>
+        <v>4.58</v>
       </c>
       <c r="O59" t="n">
-        <v>4.58</v>
+        <v>3.18</v>
       </c>
       <c r="P59" t="n">
-        <v>3.18</v>
+        <v>5.42</v>
       </c>
       <c r="Q59" t="n">
-        <v>5.42</v>
+        <v>33.33</v>
       </c>
       <c r="R59" t="n">
-        <v>33.33</v>
+        <v>367558</v>
       </c>
       <c r="S59" t="n">
-        <v>367558</v>
+        <v>-0.882422</v>
       </c>
       <c r="T59" t="n">
-        <v>-0.882422</v>
+        <v>0.261521</v>
       </c>
       <c r="U59" t="n">
-        <v>0.261521</v>
+        <v>2.367063</v>
       </c>
       <c r="V59" t="n">
-        <v>2.367063</v>
+        <v>2.367344</v>
       </c>
       <c r="W59" t="n">
-        <v>2.367344</v>
+        <v>0.656879</v>
       </c>
       <c r="X59" t="n">
-        <v>0.656879</v>
+        <v>0.119987</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.568264</v>
+        <v>-0.964334</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.119987</v>
+        <v>4.641328</v>
       </c>
       <c r="AA59" t="n">
-        <v>-0.964334</v>
+        <v>3.177699</v>
       </c>
       <c r="AB59" t="n">
-        <v>4.641328</v>
+        <v>4.327084</v>
       </c>
       <c r="AC59" t="n">
-        <v>3.177699</v>
+        <v>-0.25</v>
       </c>
       <c r="AD59" t="n">
-        <v>4.327084</v>
+        <v>-0.000372</v>
       </c>
       <c r="AE59" t="n">
-        <v>-0.25</v>
+        <v>-0.000372</v>
       </c>
       <c r="AF59" t="n">
-        <v>-0.000372</v>
+        <v>-0.16</v>
       </c>
       <c r="AG59" t="n">
-        <v>-0.000372</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AH59" t="n">
-        <v>-0.16</v>
+        <v>-0.2</v>
       </c>
       <c r="AI59" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AK59" t="n">
         <v>0.23</v>
       </c>
     </row>
@@ -7103,78 +6747,72 @@
         <v>7372243</v>
       </c>
       <c r="M60" t="n">
-        <v>2731513</v>
+        <v>4640730</v>
       </c>
       <c r="N60" t="n">
-        <v>4640730</v>
+        <v>4.88</v>
       </c>
       <c r="O60" t="n">
-        <v>4.88</v>
+        <v>3.31</v>
       </c>
       <c r="P60" t="n">
-        <v>3.31</v>
+        <v>5.81</v>
       </c>
       <c r="Q60" t="n">
-        <v>5.81</v>
+        <v>32.08</v>
       </c>
       <c r="R60" t="n">
-        <v>32.08</v>
+        <v>369742</v>
       </c>
       <c r="S60" t="n">
-        <v>369742</v>
+        <v>-0.219358</v>
       </c>
       <c r="T60" t="n">
-        <v>-0.219358</v>
+        <v>4.057001</v>
       </c>
       <c r="U60" t="n">
-        <v>4.057001</v>
+        <v>-1.918247</v>
       </c>
       <c r="V60" t="n">
-        <v>-1.918247</v>
+        <v>-1.91847</v>
       </c>
       <c r="W60" t="n">
-        <v>-1.91847</v>
+        <v>0.257708</v>
       </c>
       <c r="X60" t="n">
-        <v>0.257708</v>
+        <v>0.826955</v>
       </c>
       <c r="Y60" t="n">
-        <v>-0.694824</v>
+        <v>0.5941920000000001</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.826955</v>
+        <v>4.443025</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.5941920000000001</v>
+        <v>2.772183</v>
       </c>
       <c r="AB60" t="n">
-        <v>4.443025</v>
+        <v>4.098046</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.772183</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>4.098046</v>
+        <v>-0.000497</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>-0.000497</v>
       </c>
       <c r="AF60" t="n">
-        <v>-0.000497</v>
+        <v>0.3</v>
       </c>
       <c r="AG60" t="n">
-        <v>-0.000497</v>
+        <v>0.13</v>
       </c>
       <c r="AH60" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="AI60" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="AK60" t="n">
         <v>-1.25</v>
       </c>
     </row>
@@ -7214,46 +6852,44 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="n">
+      <c r="R61" t="n">
         <v>372616</v>
       </c>
+      <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
+      <c r="U61" t="n">
+        <v>2.054241</v>
+      </c>
       <c r="V61" t="n">
-        <v>2.054241</v>
-      </c>
-      <c r="W61" t="n">
         <v>2.054484</v>
       </c>
+      <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
+      <c r="Y61" t="n">
+        <v>0.777299</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>4.223453</v>
+      </c>
       <c r="AA61" t="n">
-        <v>0.777299</v>
+        <v>2.178243</v>
       </c>
       <c r="AB61" t="n">
-        <v>4.223453</v>
+        <v>3.983297</v>
       </c>
       <c r="AC61" t="n">
-        <v>2.178243</v>
+        <v>-0.25</v>
       </c>
       <c r="AD61" t="n">
-        <v>3.983297</v>
+        <v>-0.0007470000000000001</v>
       </c>
       <c r="AE61" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AF61" t="n">
         <v>-0.0007470000000000001</v>
       </c>
-      <c r="AG61" t="n">
-        <v>-0.0007470000000000001</v>
-      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="inlineStr"/>
-      <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -7288,33 +6924,31 @@
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
+      <c r="U62" t="n">
+        <v>-1.349004</v>
+      </c>
       <c r="V62" t="n">
-        <v>-1.349004</v>
-      </c>
-      <c r="W62" t="n">
         <v>-1.34916</v>
       </c>
+      <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr"/>
-      <c r="AC62" t="inlineStr"/>
-      <c r="AD62" t="inlineStr"/>
+      <c r="AC62" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>-0.000311</v>
+      </c>
       <c r="AE62" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AF62" t="n">
         <v>-0.000311</v>
       </c>
-      <c r="AG62" t="n">
-        <v>-0.000311</v>
-      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
-      <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI62"/>
+  <dimension ref="A1:AK62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,115 +483,125 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>saldo_credito_pj</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>saldo_credito_pf</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inadimplencia_total</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inadimplencia_pj</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inadimplencia_pf</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>var_pct_saldo_credito_pj</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ipca_acum_12m</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>inpc_acum_12m</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>dif_selic_over</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>dif_cdi</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -605,10 +615,10 @@
         <v>6.25</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02315</v>
+        <v>0.023687</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02315</v>
+        <v>0.023687</v>
       </c>
       <c r="E2" t="n">
         <v>1.16</v>
@@ -635,24 +645,26 @@
         <v>4441056</v>
       </c>
       <c r="M2" t="n">
+        <v>1894119</v>
+      </c>
+      <c r="N2" t="n">
         <v>2546936</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>2.34</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1.43</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>3.01</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>21.42</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>368886</v>
       </c>
-      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -669,6 +681,8 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -708,66 +722,72 @@
         <v>4511956</v>
       </c>
       <c r="M3" t="n">
+        <v>1910940</v>
+      </c>
+      <c r="N3" t="n">
         <v>2601017</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>2.33</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>1.43</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>2.99</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>22.89</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>367927</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>0.537905</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>-0.594556</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>3.74306</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>3.743473</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>1.596467</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
+        <v>0.888065</v>
+      </c>
+      <c r="Z3" t="n">
         <v>2.123375</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AA3" t="n">
         <v>-0.259972</v>
       </c>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="n">
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD3" t="n">
-        <v>0.001094</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0.001094</v>
-      </c>
       <c r="AF3" t="n">
+        <v>0.000557</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.000557</v>
+      </c>
+      <c r="AH3" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AK3" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -809,66 +829,72 @@
         <v>4597507</v>
       </c>
       <c r="M4" t="n">
+        <v>1933111</v>
+      </c>
+      <c r="N4" t="n">
         <v>2664395</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>2.36</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>1.46</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>3.01</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>23.91</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>367772</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>1.608989</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>1.36989</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>-0.409357</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>-0.4094</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>1.896096</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
+        <v>1.160214</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.436662</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AA4" t="n">
         <v>-0.042128</v>
       </c>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
         <v>0.005012</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AG4" t="n">
         <v>0.005012</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AH4" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AI4" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AJ4" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AK4" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -910,66 +936,72 @@
         <v>4682852</v>
       </c>
       <c r="M5" t="n">
+        <v>1974391</v>
+      </c>
+      <c r="N5" t="n">
         <v>2708461</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>2.35</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>1.4</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>3.05</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>24.21</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>362204</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>0.32497</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>1.502063</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>-0.70108</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>-0.701155</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>1.856332</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
+        <v>2.135418</v>
+      </c>
+      <c r="Z5" t="n">
         <v>1.653884</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AA5" t="n">
         <v>-1.513981</v>
       </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="n">
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AF5" t="n">
         <v>0.00406</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AG5" t="n">
         <v>0.00406</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AH5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AI5" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AJ5" t="n">
         <v>0.04</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AK5" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1011,66 +1043,72 @@
         <v>4682131</v>
       </c>
       <c r="M6" t="n">
+        <v>1947035</v>
+      </c>
+      <c r="N6" t="n">
         <v>2735096</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>2.51</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>1.46</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>3.26</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>25.23</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>358398</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>-1.968118</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>-7.696961</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>-3.99785</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>-3.99828</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>-0.015397</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
+        <v>-1.385541</v>
+      </c>
+      <c r="Z6" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AA6" t="n">
         <v>-1.050789</v>
       </c>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
         <v>0.001433</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AG6" t="n">
         <v>0.001433</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AH6" t="n">
         <v>0.16</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AI6" t="n">
         <v>0.06</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AJ6" t="n">
         <v>0.21</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AK6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1112,66 +1150,72 @@
         <v>4727818</v>
       </c>
       <c r="M7" t="n">
+        <v>1971524</v>
+      </c>
+      <c r="N7" t="n">
         <v>2756295</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>2.57</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>1.44</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>3.38</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>25.63</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>357740</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>1.087134</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>4.318965</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>-4.069138</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>-4.069594</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>0.975774</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
+        <v>1.257759</v>
+      </c>
+      <c r="Z7" t="n">
         <v>0.775073</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AA7" t="n">
         <v>-0.183595</v>
       </c>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="n">
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AF7" t="n">
         <v>0.004849</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AG7" t="n">
         <v>0.004849</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AH7" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AI7" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AJ7" t="n">
         <v>0.12</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AK7" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1213,66 +1257,72 @@
         <v>4794583</v>
       </c>
       <c r="M8" t="n">
+        <v>1994119</v>
+      </c>
+      <c r="N8" t="n">
         <v>2800464</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>2.66</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>1.55</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>3.45</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>26.54</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>353169</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>1.084094</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>9.300848999999999</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>-7.814142</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>-7.815054</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>1.412174</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
+        <v>1.146068</v>
+      </c>
+      <c r="Z8" t="n">
         <v>1.602477</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AA8" t="n">
         <v>-1.277744</v>
       </c>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="n">
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="n">
         <v>1</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AF8" t="n">
         <v>0.002356</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AG8" t="n">
         <v>0.002356</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AH8" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AI8" t="n">
         <v>0.11</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AJ8" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AK8" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1314,66 +1364,72 @@
         <v>4833732</v>
       </c>
       <c r="M9" t="n">
+        <v>2003312</v>
+      </c>
+      <c r="N9" t="n">
         <v>2830420</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>2.72</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>1.57</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>3.54</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>27.46</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>345097</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>-0.107325</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>-4.116419</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>3.826671</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>3.827155</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>0.816526</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
+        <v>0.461006</v>
+      </c>
+      <c r="Z9" t="n">
         <v>1.06968</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AA9" t="n">
         <v>-2.285591</v>
       </c>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
         <v>0.001785</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AG9" t="n">
         <v>0.001785</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AH9" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AI9" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AJ9" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AK9" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1415,66 +1471,72 @@
         <v>4889397</v>
       </c>
       <c r="M10" t="n">
+        <v>2013726</v>
+      </c>
+      <c r="N10" t="n">
         <v>2875671</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>2.79</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>1.57</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>27.42</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>346415</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>0.205368</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>-0.484439</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>-3.866561</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>-3.867033</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>1.151595</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
+        <v>0.5198390000000001</v>
+      </c>
+      <c r="Z10" t="n">
         <v>1.598738</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AA10" t="n">
         <v>0.381922</v>
       </c>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="n">
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="n">
         <v>1</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AF10" t="n">
         <v>0.003057</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AG10" t="n">
         <v>0.003057</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AH10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AK10" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1516,66 +1578,72 @@
         <v>4965603</v>
       </c>
       <c r="M11" t="n">
+        <v>2052569</v>
+      </c>
+      <c r="N11" t="n">
         <v>2913035</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>2.73</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>1.52</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>3.57</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>27.88</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>341958</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>-0.1354</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>-0.428397</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>10.765717</v>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>10.767083</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>1.558597</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
+        <v>1.928912</v>
+      </c>
+      <c r="Z11" t="n">
         <v>1.299314</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AA11" t="n">
         <v>-1.286607</v>
       </c>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="n">
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AF11" t="n">
         <v>0.00132</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AG11" t="n">
         <v>0.00132</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AH11" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AI11" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AJ11" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AK11" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1617,66 +1685,72 @@
         <v>4999244</v>
       </c>
       <c r="M12" t="n">
+        <v>2047038</v>
+      </c>
+      <c r="N12" t="n">
         <v>2952207</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>2.84</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>1.6</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>29.24</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>346403</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>1.930691</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>4.675335</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>-0.946926</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>-0.947035</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>0.677481</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Y12" t="n">
+        <v>-0.269467</v>
+      </c>
+      <c r="Z12" t="n">
         <v>1.344714</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AA12" t="n">
         <v>1.299867</v>
       </c>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AG12" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AH12" t="n">
         <v>0.11</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AI12" t="n">
         <v>0.08</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AJ12" t="n">
         <v>0.14</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AK12" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -1718,72 +1792,78 @@
         <v>5072711</v>
       </c>
       <c r="M13" t="n">
+        <v>2064183</v>
+      </c>
+      <c r="N13" t="n">
         <v>3008528</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>2.9</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>1.62</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>3.78</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>28.6</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>339664</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>-0.32129</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>0.530637</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>-0.181173</v>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>-0.181194</v>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>1.469562</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Y13" t="n">
+        <v>0.837552</v>
+      </c>
+      <c r="Z13" t="n">
         <v>1.907759</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AA13" t="n">
         <v>-1.945422</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AB13" t="n">
         <v>8.727061000000001</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AC13" t="n">
         <v>8.58755</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AD13" t="n">
         <v>8.825751</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AE13" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AF13" t="n">
         <v>0.001523</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AG13" t="n">
         <v>0.001523</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AH13" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AI13" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AJ13" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AK13" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -1825,72 +1905,78 @@
         <v>5164775</v>
       </c>
       <c r="M14" t="n">
+        <v>2109806</v>
+      </c>
+      <c r="N14" t="n">
         <v>3054969</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>2.92</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>1.65</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>3.8</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>28.57</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>327580</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>0.053914</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>-3.179227</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>4.394671</v>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>4.39518</v>
       </c>
-      <c r="W14" t="n">
+      <c r="X14" t="n">
         <v>1.814888</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Y14" t="n">
+        <v>2.210221</v>
+      </c>
+      <c r="Z14" t="n">
         <v>1.543645</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AA14" t="n">
         <v>-3.557633</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AB14" t="n">
         <v>7.168596</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AC14" t="n">
         <v>8.248760000000001</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AD14" t="n">
         <v>7.191214</v>
       </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
         <v>0.000228</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AG14" t="n">
         <v>0.000228</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0.03</v>
       </c>
       <c r="AH14" t="n">
         <v>0.02</v>
       </c>
       <c r="AI14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AK14" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -1932,72 +2018,78 @@
         <v>5215990</v>
       </c>
       <c r="M15" t="n">
+        <v>2105856</v>
+      </c>
+      <c r="N15" t="n">
         <v>3110134</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>3.04</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>1.77</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>3.89</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>29.68</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>325546</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>0.278143</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>-1.094122</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>-2.766988</v>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>-2.767296</v>
       </c>
-      <c r="W15" t="n">
+      <c r="X15" t="n">
         <v>0.991621</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Y15" t="n">
+        <v>-0.187221</v>
+      </c>
+      <c r="Z15" t="n">
         <v>1.805747</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AA15" t="n">
         <v>-0.6209170000000001</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AB15" t="n">
         <v>6.470016</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AC15" t="n">
         <v>6.517038</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AD15" t="n">
         <v>6.460076</v>
       </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
       <c r="AE15" t="n">
         <v>0</v>
       </c>
       <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
         <v>0.12</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AI15" t="n">
         <v>0.12</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AJ15" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AK15" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -2039,72 +2131,78 @@
         <v>5285657</v>
       </c>
       <c r="M16" t="n">
+        <v>2130312</v>
+      </c>
+      <c r="N16" t="n">
         <v>3155345</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>3.07</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>1.81</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>3.92</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>30.52</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>331505</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>-0.716776</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>-0.930689</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>0.705726</v>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
         <v>0.705806</v>
       </c>
-      <c r="W16" t="n">
+      <c r="X16" t="n">
         <v>1.335643</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Y16" t="n">
+        <v>1.161333</v>
+      </c>
+      <c r="Z16" t="n">
         <v>1.453667</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AA16" t="n">
         <v>1.830463</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AB16" t="n">
         <v>5.900488</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AC16" t="n">
         <v>5.899363</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AD16" t="n">
         <v>5.974439</v>
       </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
       <c r="AE16" t="n">
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
         <v>0.03</v>
       </c>
       <c r="AI16" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AK16" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2146,72 +2244,78 @@
         <v>5366069</v>
       </c>
       <c r="M17" t="n">
+        <v>2178236</v>
+      </c>
+      <c r="N17" t="n">
         <v>3187833</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>3.07</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>1.8</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>3.94</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>29.64</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>324703</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>-0.125523</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>0.827078</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>-1.443116</v>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
         <v>-1.443279</v>
       </c>
-      <c r="W17" t="n">
+      <c r="X17" t="n">
         <v>1.521325</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Y17" t="n">
+        <v>2.249624</v>
+      </c>
+      <c r="Z17" t="n">
         <v>1.029618</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AA17" t="n">
         <v>-2.051854</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AB17" t="n">
         <v>5.784842</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AC17" t="n">
         <v>5.458422</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AD17" t="n">
         <v>5.932356</v>
       </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
         <v>-0</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AG17" t="n">
         <v>-0</v>
       </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AJ17" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AK17" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -2253,72 +2357,78 @@
         <v>5373231</v>
       </c>
       <c r="M18" t="n">
+        <v>2151399</v>
+      </c>
+      <c r="N18" t="n">
         <v>3221831</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>3.24</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>1.94</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>4.11</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>30.54</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>331122</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>-0.475503</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>-4.872284</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>-2.269199</v>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>-2.26946</v>
       </c>
-      <c r="W18" t="n">
+      <c r="X18" t="n">
         <v>0.133468</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Y18" t="n">
+        <v>-1.232052</v>
+      </c>
+      <c r="Z18" t="n">
         <v>1.066493</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AA18" t="n">
         <v>1.976883</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AB18" t="n">
         <v>5.77432</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AC18" t="n">
         <v>3.79089</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AD18" t="n">
         <v>5.711379</v>
       </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
         <v>0.17</v>
       </c>
       <c r="AI18" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AK18" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2360,72 +2470,78 @@
         <v>5370950</v>
       </c>
       <c r="M19" t="n">
+        <v>2136105</v>
+      </c>
+      <c r="N19" t="n">
         <v>3234845</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>3.36</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>2.17</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>4.16</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>30.48</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>328098</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>2.96673</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>3.731301</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>2.127743</v>
       </c>
-      <c r="V19" t="n">
+      <c r="W19" t="n">
         <v>2.127993</v>
       </c>
-      <c r="W19" t="n">
+      <c r="X19" t="n">
         <v>-0.042451</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Y19" t="n">
+        <v>-0.710886</v>
+      </c>
+      <c r="Z19" t="n">
         <v>0.403932</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AA19" t="n">
         <v>-0.913259</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AB19" t="n">
         <v>5.596302</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AC19" t="n">
         <v>1.864495</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AD19" t="n">
         <v>5.47065</v>
       </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
       <c r="AE19" t="n">
         <v>0</v>
       </c>
       <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
         <v>0.12</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AI19" t="n">
         <v>0.23</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AJ19" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AK19" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2467,72 +2583,78 @@
         <v>5424811</v>
       </c>
       <c r="M20" t="n">
+        <v>2154900</v>
+      </c>
+      <c r="N20" t="n">
         <v>3269910</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>3.35</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>2.2</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>4.11</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>30.99</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>341158</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>0.004919</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>12.135312</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>-2.446331</v>
       </c>
-      <c r="V20" t="n">
+      <c r="W20" t="n">
         <v>-2.446612</v>
       </c>
-      <c r="W20" t="n">
+      <c r="X20" t="n">
         <v>1.002821</v>
       </c>
-      <c r="X20" t="n">
+      <c r="Y20" t="n">
+        <v>0.879872</v>
+      </c>
+      <c r="Z20" t="n">
         <v>1.083978</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AA20" t="n">
         <v>3.980518</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AB20" t="n">
         <v>4.650694</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AC20" t="n">
         <v>0.172427</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AD20" t="n">
         <v>4.361088</v>
       </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
       <c r="AE20" t="n">
         <v>0</v>
       </c>
       <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AI20" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AJ20" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AK20" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2574,72 +2696,78 @@
         <v>5426307</v>
       </c>
       <c r="M21" t="n">
+        <v>2145000</v>
+      </c>
+      <c r="N21" t="n">
         <v>3281308</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>3.54</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>2.45</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>4.26</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>31.62</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>345725</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>0.825329</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>-5.946769</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>-1.568774</v>
       </c>
-      <c r="V21" t="n">
+      <c r="W21" t="n">
         <v>-1.568959</v>
       </c>
-      <c r="W21" t="n">
+      <c r="X21" t="n">
         <v>0.027577</v>
       </c>
-      <c r="X21" t="n">
+      <c r="Y21" t="n">
+        <v>-0.459418</v>
+      </c>
+      <c r="Z21" t="n">
         <v>0.348572</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AA21" t="n">
         <v>1.338676</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AB21" t="n">
         <v>4.184706</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AC21" t="n">
         <v>-2.158772</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AD21" t="n">
         <v>3.834324</v>
       </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
       <c r="AE21" t="n">
         <v>0</v>
       </c>
       <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
         <v>0.19</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AI21" t="n">
         <v>0.25</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AJ21" t="n">
         <v>0.15</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AK21" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -2681,72 +2809,78 @@
         <v>5453708</v>
       </c>
       <c r="M22" t="n">
+        <v>2145530</v>
+      </c>
+      <c r="N22" t="n">
         <v>3308178</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>3.65</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>2.58</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>4.35</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>31.63</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>343489</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>-1.448972</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>-1.275652</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>1.903733</v>
       </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
         <v>1.903962</v>
       </c>
-      <c r="W22" t="n">
+      <c r="X22" t="n">
         <v>0.504966</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Y22" t="n">
+        <v>0.024709</v>
+      </c>
+      <c r="Z22" t="n">
         <v>0.818881</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AA22" t="n">
         <v>-0.646757</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AB22" t="n">
         <v>3.935832</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AC22" t="n">
         <v>-4.45588</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AD22" t="n">
         <v>3.741292</v>
       </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
         <v>-0</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AG22" t="n">
         <v>-0</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AH22" t="n">
         <v>0.11</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AI22" t="n">
         <v>0.13</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AJ22" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI22" t="n">
+      <c r="AK22" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -2788,72 +2922,78 @@
         <v>5479459</v>
       </c>
       <c r="M23" t="n">
+        <v>2169613</v>
+      </c>
+      <c r="N23" t="n">
         <v>3309846</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>3.61</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>2.63</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>4.25</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>30.85</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>343620</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>-0.029659</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>-0.418863</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>-5.429855</v>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
         <v>-5.430495</v>
       </c>
-      <c r="W23" t="n">
+      <c r="X23" t="n">
         <v>0.472174</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Y23" t="n">
+        <v>1.122473</v>
+      </c>
+      <c r="Z23" t="n">
         <v>0.050421</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AA23" t="n">
         <v>0.038138</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AB23" t="n">
         <v>3.161501</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AC23" t="n">
         <v>-6.84947</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AD23" t="n">
         <v>2.998957</v>
       </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
       <c r="AE23" t="n">
         <v>0</v>
       </c>
       <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AI23" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AJ23" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AK23" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -2895,72 +3035,78 @@
         <v>5484871</v>
       </c>
       <c r="M24" t="n">
+        <v>2153541</v>
+      </c>
+      <c r="N24" t="n">
         <v>3331330</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>3.63</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>2.73</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>4.22</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>30.43</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>345476</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>0.495618</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>2.992877</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>-1.612301</v>
       </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
         <v>-1.612502</v>
       </c>
-      <c r="W24" t="n">
+      <c r="X24" t="n">
         <v>0.098769</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Y24" t="n">
+        <v>-0.740777</v>
+      </c>
+      <c r="Z24" t="n">
         <v>0.6490939999999999</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AA24" t="n">
         <v>0.5401319999999999</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AB24" t="n">
         <v>3.992444</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AC24" t="n">
         <v>-7.713954</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AD24" t="n">
         <v>3.527423</v>
       </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
       <c r="AE24" t="n">
         <v>0</v>
       </c>
       <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AI24" t="n">
         <v>0.1</v>
       </c>
-      <c r="AH24" t="n">
+      <c r="AJ24" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AK24" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3002,72 +3148,78 @@
         <v>5559063</v>
       </c>
       <c r="M25" t="n">
+        <v>2172658</v>
+      </c>
+      <c r="N25" t="n">
         <v>3386405</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>3.61</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>2.82</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>4.12</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>29.92</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>344177</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>-0.393045</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>0.676</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>3.804703</v>
       </c>
-      <c r="V25" t="n">
+      <c r="W25" t="n">
         <v>3.805185</v>
       </c>
-      <c r="W25" t="n">
+      <c r="X25" t="n">
         <v>1.352666</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Y25" t="n">
+        <v>0.887701</v>
+      </c>
+      <c r="Z25" t="n">
         <v>1.653244</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AA25" t="n">
         <v>-0.376003</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AB25" t="n">
         <v>4.608216</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AC25" t="n">
         <v>-7.193509</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AD25" t="n">
         <v>4.057054</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AE25" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AF25" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AG25" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AH25" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AI25" t="n">
         <v>0.09</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AJ25" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="AK25" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -3109,72 +3261,78 @@
         <v>5625945</v>
       </c>
       <c r="M26" t="n">
+        <v>2215175</v>
+      </c>
+      <c r="N26" t="n">
         <v>3410769</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>3.54</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>2.82</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>4</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>29.66</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>340324</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>0.012595</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>-4.052448</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>1.741198</v>
       </c>
-      <c r="V26" t="n">
+      <c r="W26" t="n">
         <v>1.74141</v>
       </c>
-      <c r="W26" t="n">
+      <c r="X26" t="n">
         <v>1.203116</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Y26" t="n">
+        <v>1.956912</v>
+      </c>
+      <c r="Z26" t="n">
         <v>0.719465</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AA26" t="n">
         <v>-1.119482</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AB26" t="n">
         <v>5.185235</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AC26" t="n">
         <v>-5.956714</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AD26" t="n">
         <v>4.505936</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AE26" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AF26" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AG26" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="AF26" t="n">
+      <c r="AH26" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AK26" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -3216,72 +3374,78 @@
         <v>5653808</v>
       </c>
       <c r="M27" t="n">
+        <v>2204808</v>
+      </c>
+      <c r="N27" t="n">
         <v>3449000</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>3.56</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>2.92</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>3.97</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>29.24</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>340247</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>0.316333</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>0.171808</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>0.996485</v>
       </c>
-      <c r="V27" t="n">
+      <c r="W27" t="n">
         <v>0.996605</v>
       </c>
-      <c r="W27" t="n">
+      <c r="X27" t="n">
         <v>0.495259</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Y27" t="n">
+        <v>-0.467999</v>
+      </c>
+      <c r="Z27" t="n">
         <v>1.120891</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AA27" t="n">
         <v>-0.022625</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AB27" t="n">
         <v>4.819246</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AC27" t="n">
         <v>-4.560737</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AD27" t="n">
         <v>4.141877</v>
       </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AG27" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AH27" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AI27" t="n">
         <v>0.1</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="AJ27" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AK27" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3323,72 +3487,78 @@
         <v>5711103</v>
       </c>
       <c r="M28" t="n">
+        <v>2220766</v>
+      </c>
+      <c r="N28" t="n">
         <v>3490337</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>3.53</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>2.99</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>3.88</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>29.01</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>348406</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>0.734124</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>-0.248573</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>-2.412259</v>
       </c>
-      <c r="V28" t="n">
+      <c r="W28" t="n">
         <v>-2.412545</v>
       </c>
-      <c r="W28" t="n">
+      <c r="X28" t="n">
         <v>1.013388</v>
       </c>
-      <c r="X28" t="n">
+      <c r="Y28" t="n">
+        <v>0.723782</v>
+      </c>
+      <c r="Z28" t="n">
         <v>1.198521</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AA28" t="n">
         <v>2.397964</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AB28" t="n">
         <v>4.683537</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AC28" t="n">
         <v>-3.457004</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AD28" t="n">
         <v>3.851383</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AE28" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AF28" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AG28" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AH28" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AI28" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AH28" t="n">
+      <c r="AJ28" t="n">
         <v>-0.09</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AK28" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -3430,72 +3600,78 @@
         <v>5805157</v>
       </c>
       <c r="M29" t="n">
+        <v>2283485</v>
+      </c>
+      <c r="N29" t="n">
         <v>3521672</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>3.29</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>2.59</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>28.14</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>355034</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>1.248734</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>0.004199</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>-1.908621</v>
       </c>
-      <c r="V29" t="n">
+      <c r="W29" t="n">
         <v>-1.908853</v>
       </c>
-      <c r="W29" t="n">
+      <c r="X29" t="n">
         <v>1.646862</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Y29" t="n">
+        <v>2.824206</v>
+      </c>
+      <c r="Z29" t="n">
         <v>0.897764</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AA29" t="n">
         <v>1.902378</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AB29" t="n">
         <v>4.621114</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AC29" t="n">
         <v>-3.178284</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AD29" t="n">
         <v>3.706988</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AE29" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AF29" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AG29" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AH29" t="n">
         <v>-0.24</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AI29" t="n">
         <v>-0.4</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AJ29" t="n">
         <v>-0.13</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AK29" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3537,72 +3713,78 @@
         <v>5794707</v>
       </c>
       <c r="M30" t="n">
+        <v>2234362</v>
+      </c>
+      <c r="N30" t="n">
         <v>3560345</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>3.38</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2.77</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>3.76</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>28</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>355066</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>-0.395831</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>-2.347954</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>2.317559</v>
       </c>
-      <c r="V30" t="n">
+      <c r="W30" t="n">
         <v>2.317847</v>
       </c>
-      <c r="W30" t="n">
+      <c r="X30" t="n">
         <v>-0.180012</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Y30" t="n">
+        <v>-2.151229</v>
+      </c>
+      <c r="Z30" t="n">
         <v>1.098143</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AA30" t="n">
         <v>0.009013</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AB30" t="n">
         <v>4.506637</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AC30" t="n">
         <v>-3.31355</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AD30" t="n">
         <v>3.820543</v>
       </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AG30" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AH30" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AI30" t="n">
         <v>0.18</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AJ30" t="n">
         <v>0.01</v>
       </c>
-      <c r="AI30" t="n">
+      <c r="AK30" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -3644,72 +3826,78 @@
         <v>5815954</v>
       </c>
       <c r="M31" t="n">
+        <v>2235302</v>
+      </c>
+      <c r="N31" t="n">
         <v>3580652</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>3.38</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>2.76</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>3.76</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>27.85</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>352705</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>0.177893</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>2.873375</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>0.601595</v>
       </c>
-      <c r="V31" t="n">
+      <c r="W31" t="n">
         <v>0.601668</v>
       </c>
-      <c r="W31" t="n">
+      <c r="X31" t="n">
         <v>0.366662</v>
       </c>
-      <c r="X31" t="n">
+      <c r="Y31" t="n">
+        <v>0.04207</v>
+      </c>
+      <c r="Z31" t="n">
         <v>0.570366</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AA31" t="n">
         <v>-0.664947</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AB31" t="n">
         <v>4.496274</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AC31" t="n">
         <v>-3.758575</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AD31" t="n">
         <v>3.861754</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AE31" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AF31" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AG31" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -3751,72 +3939,78 @@
         <v>5899742</v>
       </c>
       <c r="M32" t="n">
+        <v>2285775</v>
+      </c>
+      <c r="N32" t="n">
         <v>3613967</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>3.33</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>2.71</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>28.14</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>355008</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>0.014285</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>7.262481</v>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
         <v>0.258865</v>
       </c>
-      <c r="V32" t="n">
+      <c r="W32" t="n">
         <v>0.258896</v>
       </c>
-      <c r="W32" t="n">
+      <c r="X32" t="n">
         <v>1.440658</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Y32" t="n">
+        <v>2.257995</v>
+      </c>
+      <c r="Z32" t="n">
         <v>0.930417</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AA32" t="n">
         <v>0.652954</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AB32" t="n">
         <v>3.925596</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AC32" t="n">
         <v>-4.25878</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AD32" t="n">
         <v>3.397348</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AE32" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AF32" t="n">
         <v>-0.000537</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AG32" t="n">
         <v>-0.000537</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>-0.05</v>
       </c>
       <c r="AH32" t="n">
         <v>-0.05</v>
       </c>
       <c r="AI32" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK32" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -3858,72 +4052,78 @@
         <v>5915538</v>
       </c>
       <c r="M33" t="n">
+        <v>2268879</v>
+      </c>
+      <c r="N33" t="n">
         <v>3646659</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>3.37</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>2.76</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>27.86</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>351599</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>-0.044032</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
         <v>-0.284579</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>3.514671</v>
       </c>
-      <c r="V33" t="n">
+      <c r="W33" t="n">
         <v>3.515093</v>
       </c>
-      <c r="W33" t="n">
+      <c r="X33" t="n">
         <v>0.267741</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Y33" t="n">
+        <v>-0.7391799999999999</v>
+      </c>
+      <c r="Z33" t="n">
         <v>0.904602</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AA33" t="n">
         <v>-0.96026</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AB33" t="n">
         <v>3.688016</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AC33" t="n">
         <v>-3.040871</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AD33" t="n">
         <v>3.232784</v>
       </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
         <v>-0.001252</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AG33" t="n">
         <v>-0.001252</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0.05</v>
       </c>
       <c r="AH33" t="n">
         <v>0.04</v>
       </c>
       <c r="AI33" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK33" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -3965,72 +4165,78 @@
         <v>5953960</v>
       </c>
       <c r="M34" t="n">
+        <v>2278309</v>
+      </c>
+      <c r="N34" t="n">
         <v>3675652</v>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>3.43</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>2.8</v>
       </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
         <v>3.82</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>27.75</v>
       </c>
-      <c r="R34" t="n">
+      <c r="S34" t="n">
         <v>355560</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>0.9333669999999999</v>
       </c>
-      <c r="T34" t="n">
+      <c r="U34" t="n">
         <v>-4.159973</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>1.349627</v>
       </c>
-      <c r="V34" t="n">
+      <c r="W34" t="n">
         <v>1.349783</v>
       </c>
-      <c r="W34" t="n">
+      <c r="X34" t="n">
         <v>0.64951</v>
       </c>
-      <c r="X34" t="n">
+      <c r="Y34" t="n">
+        <v>0.415624</v>
+      </c>
+      <c r="Z34" t="n">
         <v>0.795057</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="AA34" t="n">
         <v>1.126567</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AB34" t="n">
         <v>3.925952</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AC34" t="n">
         <v>-0.344269</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AD34" t="n">
         <v>3.335647</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AE34" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AF34" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="AE34" t="n">
+      <c r="AG34" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="AF34" t="n">
+      <c r="AH34" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG34" t="n">
+      <c r="AI34" t="n">
         <v>0.04</v>
       </c>
-      <c r="AH34" t="n">
+      <c r="AJ34" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI34" t="n">
+      <c r="AK34" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -4072,72 +4278,78 @@
         <v>6041898</v>
       </c>
       <c r="M35" t="n">
+        <v>2336858</v>
+      </c>
+      <c r="N35" t="n">
         <v>3705041</v>
       </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>3.29</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>2.64</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>27.81</v>
       </c>
-      <c r="R35" t="n">
+      <c r="S35" t="n">
         <v>357827</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>0.932566</v>
       </c>
-      <c r="T35" t="n">
+      <c r="U35" t="n">
         <v>1.104953</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>6.053495</v>
       </c>
-      <c r="V35" t="n">
+      <c r="W35" t="n">
         <v>6.054188</v>
       </c>
-      <c r="W35" t="n">
+      <c r="X35" t="n">
         <v>1.476967</v>
       </c>
-      <c r="X35" t="n">
+      <c r="Y35" t="n">
+        <v>2.569845</v>
+      </c>
+      <c r="Z35" t="n">
         <v>0.799559</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="AA35" t="n">
         <v>0.637586</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AB35" t="n">
         <v>4.227578</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AC35" t="n">
         <v>2.440035</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AD35" t="n">
         <v>3.697684</v>
       </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="AE35" t="n">
+      <c r="AG35" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="AF35" t="n">
+      <c r="AH35" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AI35" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AH35" t="n">
+      <c r="AJ35" t="n">
         <v>-0.11</v>
       </c>
-      <c r="AI35" t="n">
+      <c r="AK35" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -4179,72 +4391,78 @@
         <v>6069205</v>
       </c>
       <c r="M36" t="n">
+        <v>2323362</v>
+      </c>
+      <c r="N36" t="n">
         <v>3745844</v>
       </c>
-      <c r="N36" t="n">
+      <c r="O36" t="n">
         <v>3.3</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>2.52</v>
       </c>
-      <c r="P36" t="n">
+      <c r="Q36" t="n">
         <v>3.78</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>27.74</v>
       </c>
-      <c r="R36" t="n">
+      <c r="S36" t="n">
         <v>363282</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>0.444014</v>
       </c>
-      <c r="T36" t="n">
+      <c r="U36" t="n">
         <v>5.327189</v>
       </c>
-      <c r="U36" t="n">
+      <c r="V36" t="n">
         <v>1.856482</v>
       </c>
-      <c r="V36" t="n">
+      <c r="W36" t="n">
         <v>1.856683</v>
       </c>
-      <c r="W36" t="n">
+      <c r="X36" t="n">
         <v>0.451961</v>
       </c>
-      <c r="X36" t="n">
+      <c r="Y36" t="n">
+        <v>-0.577528</v>
+      </c>
+      <c r="Z36" t="n">
         <v>1.101283</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="AA36" t="n">
         <v>1.52448</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AB36" t="n">
         <v>4.498245</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AC36" t="n">
         <v>3.812368</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AD36" t="n">
         <v>4.060953</v>
       </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
       <c r="AE36" t="n">
         <v>0</v>
       </c>
       <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
         <v>0.01</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AI36" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AH36" t="n">
+      <c r="AJ36" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI36" t="n">
+      <c r="AK36" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -4286,72 +4504,78 @@
         <v>6135298</v>
       </c>
       <c r="M37" t="n">
+        <v>2344397</v>
+      </c>
+      <c r="N37" t="n">
         <v>3790900</v>
       </c>
-      <c r="N37" t="n">
+      <c r="O37" t="n">
         <v>3.33</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>2.55</v>
       </c>
-      <c r="P37" t="n">
+      <c r="Q37" t="n">
         <v>3.82</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>27.59</v>
       </c>
-      <c r="R37" t="n">
+      <c r="S37" t="n">
         <v>369214</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>0.120836</v>
       </c>
-      <c r="T37" t="n">
+      <c r="U37" t="n">
         <v>-1.297169</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>-0.104202</v>
       </c>
-      <c r="V37" t="n">
+      <c r="W37" t="n">
         <v>-0.104213</v>
       </c>
-      <c r="W37" t="n">
+      <c r="X37" t="n">
         <v>1.088989</v>
       </c>
-      <c r="X37" t="n">
+      <c r="Y37" t="n">
+        <v>0.905369</v>
+      </c>
+      <c r="Z37" t="n">
         <v>1.202826</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="AA37" t="n">
         <v>1.632891</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AB37" t="n">
         <v>4.237599</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AC37" t="n">
         <v>4.259387</v>
       </c>
-      <c r="AB37" t="n">
+      <c r="AD37" t="n">
         <v>3.707852</v>
       </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
       <c r="AE37" t="n">
         <v>0</v>
       </c>
       <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AI37" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH37" t="n">
+      <c r="AJ37" t="n">
         <v>0.04</v>
       </c>
-      <c r="AI37" t="n">
+      <c r="AK37" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4393,72 +4617,78 @@
         <v>6216528</v>
       </c>
       <c r="M38" t="n">
+        <v>2384828</v>
+      </c>
+      <c r="N38" t="n">
         <v>3831700</v>
       </c>
-      <c r="N38" t="n">
+      <c r="O38" t="n">
         <v>3.34</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>2.56</v>
       </c>
-      <c r="P38" t="n">
+      <c r="Q38" t="n">
         <v>3.83</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>27.49</v>
       </c>
-      <c r="R38" t="n">
+      <c r="S38" t="n">
         <v>372016</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>0.794912</v>
       </c>
-      <c r="T38" t="n">
+      <c r="U38" t="n">
         <v>-2.711204</v>
       </c>
-      <c r="U38" t="n">
+      <c r="V38" t="n">
         <v>-3.679149</v>
       </c>
-      <c r="V38" t="n">
+      <c r="W38" t="n">
         <v>-3.679539</v>
       </c>
-      <c r="W38" t="n">
+      <c r="X38" t="n">
         <v>1.323978</v>
       </c>
-      <c r="X38" t="n">
+      <c r="Y38" t="n">
+        <v>1.72458</v>
+      </c>
+      <c r="Z38" t="n">
         <v>1.076262</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="AA38" t="n">
         <v>0.7589089999999999</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AB38" t="n">
         <v>4.42474</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AC38" t="n">
         <v>4.519075</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AD38" t="n">
         <v>4.091149</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AE38" t="n">
         <v>0.25</v>
       </c>
-      <c r="AD38" t="n">
+      <c r="AF38" t="n">
         <v>0.000342</v>
       </c>
-      <c r="AE38" t="n">
+      <c r="AG38" t="n">
         <v>0.000342</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0.01</v>
       </c>
       <c r="AH38" t="n">
         <v>0.01</v>
       </c>
       <c r="AI38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AK38" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -4500,72 +4730,78 @@
         <v>6275117</v>
       </c>
       <c r="M39" t="n">
+        <v>2397533</v>
+      </c>
+      <c r="N39" t="n">
         <v>3877584</v>
       </c>
-      <c r="N39" t="n">
+      <c r="O39" t="n">
         <v>3.3</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>2.52</v>
       </c>
-      <c r="P39" t="n">
+      <c r="Q39" t="n">
         <v>3.79</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>27.94</v>
       </c>
-      <c r="R39" t="n">
+      <c r="S39" t="n">
         <v>366096</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>0.185832</v>
       </c>
-      <c r="T39" t="n">
+      <c r="U39" t="n">
         <v>1.966099</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>6.053487</v>
       </c>
-      <c r="V39" t="n">
+      <c r="W39" t="n">
         <v>6.054153</v>
       </c>
-      <c r="W39" t="n">
+      <c r="X39" t="n">
         <v>0.9424709999999999</v>
       </c>
-      <c r="X39" t="n">
+      <c r="Y39" t="n">
+        <v>0.532743</v>
+      </c>
+      <c r="Z39" t="n">
         <v>1.197484</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="AA39" t="n">
         <v>-1.591329</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AB39" t="n">
         <v>4.758099</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AC39" t="n">
         <v>5.579866</v>
       </c>
-      <c r="AB39" t="n">
+      <c r="AD39" t="n">
         <v>4.600584</v>
       </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
         <v>0.000556</v>
       </c>
-      <c r="AE39" t="n">
+      <c r="AG39" t="n">
         <v>0.000556</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>-0.04</v>
       </c>
       <c r="AH39" t="n">
         <v>-0.04</v>
       </c>
       <c r="AI39" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AK39" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -4607,72 +4843,78 @@
         <v>6365690</v>
       </c>
       <c r="M40" t="n">
+        <v>2436022</v>
+      </c>
+      <c r="N40" t="n">
         <v>3929668</v>
       </c>
-      <c r="N40" t="n">
+      <c r="O40" t="n">
         <v>3.27</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>2.5</v>
       </c>
-      <c r="P40" t="n">
+      <c r="Q40" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>28.45</v>
       </c>
-      <c r="R40" t="n">
+      <c r="S40" t="n">
         <v>363003</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>-0.224963</v>
       </c>
-      <c r="T40" t="n">
+      <c r="U40" t="n">
         <v>-3.383039</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>4.769899</v>
       </c>
-      <c r="V40" t="n">
+      <c r="W40" t="n">
         <v>4.770394</v>
       </c>
-      <c r="W40" t="n">
+      <c r="X40" t="n">
         <v>1.443368</v>
       </c>
-      <c r="X40" t="n">
+      <c r="Y40" t="n">
+        <v>1.605359</v>
+      </c>
+      <c r="Z40" t="n">
         <v>1.343208</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="AA40" t="n">
         <v>-0.8448600000000001</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AB40" t="n">
         <v>4.873011</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AC40" t="n">
         <v>6.325086</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AD40" t="n">
         <v>4.840925</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AE40" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AF40" t="n">
         <v>0.001412</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AG40" t="n">
         <v>0.001412</v>
       </c>
-      <c r="AF40" t="n">
+      <c r="AH40" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG40" t="n">
+      <c r="AI40" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AH40" t="n">
+      <c r="AJ40" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AI40" t="n">
+      <c r="AK40" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4714,72 +4956,78 @@
         <v>6464602</v>
       </c>
       <c r="M41" t="n">
+        <v>2499177</v>
+      </c>
+      <c r="N41" t="n">
         <v>3965425</v>
       </c>
-      <c r="N41" t="n">
+      <c r="O41" t="n">
         <v>3.08</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>2.21</v>
       </c>
-      <c r="P41" t="n">
+      <c r="Q41" t="n">
         <v>3.63</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>28.5</v>
       </c>
-      <c r="R41" t="n">
+      <c r="S41" t="n">
         <v>329730</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>-0.584226</v>
       </c>
-      <c r="T41" t="n">
+      <c r="U41" t="n">
         <v>-1.265086</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>2.292888</v>
       </c>
-      <c r="V41" t="n">
+      <c r="W41" t="n">
         <v>2.293116</v>
       </c>
-      <c r="W41" t="n">
+      <c r="X41" t="n">
         <v>1.55383</v>
       </c>
-      <c r="X41" t="n">
+      <c r="Y41" t="n">
+        <v>2.592546</v>
+      </c>
+      <c r="Z41" t="n">
         <v>0.909924</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="AA41" t="n">
         <v>-9.166040000000001</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AB41" t="n">
         <v>4.831296</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AC41" t="n">
         <v>6.536174</v>
       </c>
-      <c r="AB41" t="n">
+      <c r="AD41" t="n">
         <v>4.767938</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AE41" t="n">
         <v>1</v>
       </c>
-      <c r="AD41" t="n">
+      <c r="AF41" t="n">
         <v>0.002578</v>
       </c>
-      <c r="AE41" t="n">
+      <c r="AG41" t="n">
         <v>0.002578</v>
       </c>
-      <c r="AF41" t="n">
+      <c r="AH41" t="n">
         <v>-0.19</v>
       </c>
-      <c r="AG41" t="n">
+      <c r="AI41" t="n">
         <v>-0.29</v>
       </c>
-      <c r="AH41" t="n">
+      <c r="AJ41" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AI41" t="n">
+      <c r="AK41" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -4821,72 +5069,78 @@
         <v>6465016</v>
       </c>
       <c r="M42" t="n">
+        <v>2451957</v>
+      </c>
+      <c r="N42" t="n">
         <v>4013059</v>
       </c>
-      <c r="N42" t="n">
+      <c r="O42" t="n">
         <v>3.34</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>2.43</v>
       </c>
-      <c r="P42" t="n">
+      <c r="Q42" t="n">
         <v>3.89</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>29.88</v>
       </c>
-      <c r="R42" t="n">
+      <c r="S42" t="n">
         <v>328303</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>0.675346</v>
       </c>
-      <c r="T42" t="n">
+      <c r="U42" t="n">
         <v>-1.465146</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>-5.8492</v>
       </c>
-      <c r="V42" t="n">
+      <c r="W42" t="n">
         <v>-5.849767</v>
       </c>
-      <c r="W42" t="n">
+      <c r="X42" t="n">
         <v>0.006404</v>
       </c>
-      <c r="X42" t="n">
+      <c r="Y42" t="n">
+        <v>-1.889422</v>
+      </c>
+      <c r="Z42" t="n">
         <v>1.201233</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="AA42" t="n">
         <v>-0.432778</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AB42" t="n">
         <v>4.559874</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AC42" t="n">
         <v>6.749097</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AD42" t="n">
         <v>4.174145</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AE42" t="n">
         <v>1</v>
       </c>
-      <c r="AD42" t="n">
+      <c r="AF42" t="n">
         <v>0.001675</v>
       </c>
-      <c r="AE42" t="n">
+      <c r="AG42" t="n">
         <v>0.001675</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0.22</v>
       </c>
       <c r="AH42" t="n">
         <v>0.26</v>
       </c>
       <c r="AI42" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AK42" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -4928,72 +5182,78 @@
         <v>6511444</v>
       </c>
       <c r="M43" t="n">
+        <v>2477151</v>
+      </c>
+      <c r="N43" t="n">
         <v>4034293</v>
       </c>
-      <c r="N43" t="n">
+      <c r="O43" t="n">
         <v>3.41</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2.52</v>
       </c>
-      <c r="P43" t="n">
+      <c r="Q43" t="n">
         <v>3.96</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>30.53</v>
       </c>
-      <c r="R43" t="n">
+      <c r="S43" t="n">
         <v>332508</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>0.485516</v>
       </c>
-      <c r="T43" t="n">
+      <c r="U43" t="n">
         <v>4.088981</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>0.320749</v>
       </c>
-      <c r="V43" t="n">
+      <c r="W43" t="n">
         <v>0.320782</v>
       </c>
-      <c r="W43" t="n">
+      <c r="X43" t="n">
         <v>0.7181419999999999</v>
       </c>
-      <c r="X43" t="n">
+      <c r="Y43" t="n">
+        <v>1.027506</v>
+      </c>
+      <c r="Z43" t="n">
         <v>0.529123</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="AA43" t="n">
         <v>1.280829</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="AB43" t="n">
         <v>5.05763</v>
       </c>
-      <c r="AA43" t="n">
+      <c r="AC43" t="n">
         <v>8.444549</v>
       </c>
-      <c r="AB43" t="n">
+      <c r="AD43" t="n">
         <v>4.866504</v>
       </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
         <v>0.003204</v>
       </c>
-      <c r="AE43" t="n">
+      <c r="AG43" t="n">
         <v>0.003204</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0.09</v>
       </c>
       <c r="AH43" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AI43" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AK43" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -5035,72 +5295,78 @@
         <v>6576464</v>
       </c>
       <c r="M44" t="n">
+        <v>2498262</v>
+      </c>
+      <c r="N44" t="n">
         <v>4078202</v>
       </c>
-      <c r="N44" t="n">
+      <c r="O44" t="n">
         <v>3.44</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>2.49</v>
       </c>
-      <c r="P44" t="n">
+      <c r="Q44" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>31.34</v>
       </c>
-      <c r="R44" t="n">
+      <c r="S44" t="n">
         <v>336157</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>1.30069</v>
       </c>
-      <c r="T44" t="n">
+      <c r="U44" t="n">
         <v>6.734953</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>-1.822596</v>
       </c>
-      <c r="V44" t="n">
+      <c r="W44" t="n">
         <v>-1.822783</v>
       </c>
-      <c r="W44" t="n">
+      <c r="X44" t="n">
         <v>0.99855</v>
       </c>
-      <c r="X44" t="n">
+      <c r="Y44" t="n">
+        <v>0.852229</v>
+      </c>
+      <c r="Z44" t="n">
         <v>1.088394</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="AA44" t="n">
         <v>1.097417</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AB44" t="n">
         <v>5.47719</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AC44" t="n">
         <v>8.586193</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="AD44" t="n">
         <v>5.201441</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AE44" t="n">
         <v>1</v>
       </c>
-      <c r="AD44" t="n">
+      <c r="AF44" t="n">
         <v>0.001471</v>
       </c>
-      <c r="AE44" t="n">
+      <c r="AG44" t="n">
         <v>0.001471</v>
       </c>
-      <c r="AF44" t="n">
+      <c r="AH44" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG44" t="n">
+      <c r="AI44" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AH44" t="n">
+      <c r="AJ44" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI44" t="n">
+      <c r="AK44" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -5142,72 +5408,78 @@
         <v>6623948</v>
       </c>
       <c r="M45" t="n">
+        <v>2512426</v>
+      </c>
+      <c r="N45" t="n">
         <v>4111522</v>
       </c>
-      <c r="N45" t="n">
+      <c r="O45" t="n">
         <v>3.67</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>2.72</v>
       </c>
-      <c r="P45" t="n">
+      <c r="Q45" t="n">
         <v>4.25</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>31.63</v>
       </c>
-      <c r="R45" t="n">
+      <c r="S45" t="n">
         <v>340789</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>-0.459145</v>
       </c>
-      <c r="T45" t="n">
+      <c r="U45" t="n">
         <v>-1.250256</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>-1.417575</v>
       </c>
-      <c r="V45" t="n">
+      <c r="W45" t="n">
         <v>-1.417723</v>
       </c>
-      <c r="W45" t="n">
+      <c r="X45" t="n">
         <v>0.722029</v>
       </c>
-      <c r="X45" t="n">
+      <c r="Y45" t="n">
+        <v>0.566954</v>
+      </c>
+      <c r="Z45" t="n">
         <v>0.8170269999999999</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="AA45" t="n">
         <v>1.377928</v>
       </c>
-      <c r="Z45" t="n">
+      <c r="AB45" t="n">
         <v>5.529729</v>
       </c>
-      <c r="AA45" t="n">
+      <c r="AC45" t="n">
         <v>8.510418</v>
       </c>
-      <c r="AB45" t="n">
+      <c r="AD45" t="n">
         <v>5.316736</v>
       </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
         <v>0.002023</v>
       </c>
-      <c r="AE45" t="n">
+      <c r="AG45" t="n">
         <v>0.002023</v>
       </c>
-      <c r="AF45" t="n">
+      <c r="AH45" t="n">
         <v>0.23</v>
       </c>
-      <c r="AG45" t="n">
+      <c r="AI45" t="n">
         <v>0.23</v>
       </c>
-      <c r="AH45" t="n">
+      <c r="AJ45" t="n">
         <v>0.22</v>
       </c>
-      <c r="AI45" t="n">
+      <c r="AK45" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -5249,72 +5521,78 @@
         <v>6666287</v>
       </c>
       <c r="M46" t="n">
+        <v>2532708</v>
+      </c>
+      <c r="N46" t="n">
         <v>4133579</v>
       </c>
-      <c r="N46" t="n">
+      <c r="O46" t="n">
         <v>3.72</v>
       </c>
-      <c r="O46" t="n">
+      <c r="P46" t="n">
         <v>2.67</v>
       </c>
-      <c r="P46" t="n">
+      <c r="Q46" t="n">
         <v>4.36</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="R46" t="n">
         <v>31.7</v>
       </c>
-      <c r="R46" t="n">
+      <c r="S46" t="n">
         <v>341459</v>
       </c>
-      <c r="S46" t="n">
+      <c r="T46" t="n">
         <v>-0.58566</v>
       </c>
-      <c r="T46" t="n">
+      <c r="U46" t="n">
         <v>-3.586372</v>
       </c>
-      <c r="U46" t="n">
+      <c r="V46" t="n">
         <v>0.84617</v>
       </c>
-      <c r="V46" t="n">
+      <c r="W46" t="n">
         <v>0.84626</v>
       </c>
-      <c r="W46" t="n">
+      <c r="X46" t="n">
         <v>0.639181</v>
       </c>
-      <c r="X46" t="n">
+      <c r="Y46" t="n">
+        <v>0.807268</v>
+      </c>
+      <c r="Z46" t="n">
         <v>0.5364679999999999</v>
       </c>
-      <c r="Y46" t="n">
+      <c r="AA46" t="n">
         <v>0.196603</v>
       </c>
-      <c r="Z46" t="n">
+      <c r="AB46" t="n">
         <v>5.319636</v>
       </c>
-      <c r="AA46" t="n">
+      <c r="AC46" t="n">
         <v>7.026183</v>
       </c>
-      <c r="AB46" t="n">
+      <c r="AD46" t="n">
         <v>5.201418</v>
       </c>
-      <c r="AC46" t="n">
+      <c r="AE46" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD46" t="n">
+      <c r="AF46" t="n">
         <v>0.001405</v>
       </c>
-      <c r="AE46" t="n">
+      <c r="AG46" t="n">
         <v>0.001405</v>
       </c>
-      <c r="AF46" t="n">
+      <c r="AH46" t="n">
         <v>0.05</v>
       </c>
-      <c r="AG46" t="n">
+      <c r="AI46" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH46" t="n">
+      <c r="AJ46" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI46" t="n">
+      <c r="AK46" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5356,72 +5634,78 @@
         <v>6703663</v>
       </c>
       <c r="M47" t="n">
+        <v>2547693</v>
+      </c>
+      <c r="N47" t="n">
         <v>4155970</v>
       </c>
-      <c r="N47" t="n">
+      <c r="O47" t="n">
         <v>3.75</v>
       </c>
-      <c r="O47" t="n">
+      <c r="P47" t="n">
         <v>2.67</v>
       </c>
-      <c r="P47" t="n">
+      <c r="Q47" t="n">
         <v>4.41</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="R47" t="n">
         <v>31.85</v>
       </c>
-      <c r="R47" t="n">
+      <c r="S47" t="n">
         <v>344440</v>
       </c>
-      <c r="S47" t="n">
+      <c r="T47" t="n">
         <v>-0.075712</v>
       </c>
-      <c r="T47" t="n">
+      <c r="U47" t="n">
         <v>-1.100666</v>
       </c>
-      <c r="U47" t="n">
+      <c r="V47" t="n">
         <v>-4.407308</v>
       </c>
-      <c r="V47" t="n">
+      <c r="W47" t="n">
         <v>-4.407771</v>
       </c>
-      <c r="W47" t="n">
+      <c r="X47" t="n">
         <v>0.5606719999999999</v>
       </c>
-      <c r="X47" t="n">
+      <c r="Y47" t="n">
+        <v>0.591659</v>
+      </c>
+      <c r="Z47" t="n">
         <v>0.541686</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="AA47" t="n">
         <v>0.873018</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="AB47" t="n">
         <v>5.351165</v>
       </c>
-      <c r="AA47" t="n">
+      <c r="AC47" t="n">
         <v>4.393261</v>
       </c>
-      <c r="AB47" t="n">
+      <c r="AD47" t="n">
         <v>5.18043</v>
       </c>
-      <c r="AC47" t="n">
+      <c r="AE47" t="n">
         <v>0.25</v>
       </c>
-      <c r="AD47" t="n">
+      <c r="AF47" t="n">
         <v>0.000633</v>
       </c>
-      <c r="AE47" t="n">
+      <c r="AG47" t="n">
         <v>0.000633</v>
       </c>
-      <c r="AF47" t="n">
+      <c r="AH47" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="n">
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI47" t="n">
+      <c r="AK47" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5463,72 +5747,78 @@
         <v>6733209</v>
       </c>
       <c r="M48" t="n">
+        <v>2544400</v>
+      </c>
+      <c r="N48" t="n">
         <v>4188808</v>
       </c>
-      <c r="N48" t="n">
+      <c r="O48" t="n">
         <v>3.96</v>
       </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
         <v>2.79</v>
       </c>
-      <c r="P48" t="n">
+      <c r="Q48" t="n">
         <v>4.66</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="R48" t="n">
         <v>31.75</v>
       </c>
-      <c r="R48" t="n">
+      <c r="S48" t="n">
         <v>345111</v>
       </c>
-      <c r="S48" t="n">
+      <c r="T48" t="n">
         <v>-0.280386</v>
       </c>
-      <c r="T48" t="n">
+      <c r="U48" t="n">
         <v>5.352993</v>
       </c>
-      <c r="U48" t="n">
+      <c r="V48" t="n">
         <v>2.657089</v>
       </c>
-      <c r="V48" t="n">
+      <c r="W48" t="n">
         <v>2.657381</v>
       </c>
-      <c r="W48" t="n">
+      <c r="X48" t="n">
         <v>0.440744</v>
       </c>
-      <c r="X48" t="n">
+      <c r="Y48" t="n">
+        <v>-0.129254</v>
+      </c>
+      <c r="Z48" t="n">
         <v>0.79014</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="AA48" t="n">
         <v>0.194809</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="AB48" t="n">
         <v>5.225222</v>
       </c>
-      <c r="AA48" t="n">
+      <c r="AC48" t="n">
         <v>2.961368</v>
       </c>
-      <c r="AB48" t="n">
+      <c r="AD48" t="n">
         <v>5.127976</v>
       </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
         <v>0.000562</v>
       </c>
-      <c r="AE48" t="n">
+      <c r="AG48" t="n">
         <v>0.000562</v>
       </c>
-      <c r="AF48" t="n">
+      <c r="AH48" t="n">
         <v>0.21</v>
       </c>
-      <c r="AG48" t="n">
+      <c r="AI48" t="n">
         <v>0.12</v>
       </c>
-      <c r="AH48" t="n">
+      <c r="AJ48" t="n">
         <v>0.25</v>
       </c>
-      <c r="AI48" t="n">
+      <c r="AK48" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -5570,72 +5860,78 @@
         <v>6774436</v>
       </c>
       <c r="M49" t="n">
+        <v>2546265</v>
+      </c>
+      <c r="N49" t="n">
         <v>4228171</v>
       </c>
-      <c r="N49" t="n">
+      <c r="O49" t="n">
         <v>4.14</v>
       </c>
-      <c r="O49" t="n">
+      <c r="P49" t="n">
         <v>2.85</v>
       </c>
-      <c r="P49" t="n">
+      <c r="Q49" t="n">
         <v>4.92</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="R49" t="n">
         <v>31.87</v>
       </c>
-      <c r="R49" t="n">
+      <c r="S49" t="n">
         <v>350767</v>
       </c>
-      <c r="S49" t="n">
+      <c r="T49" t="n">
         <v>0.304372</v>
       </c>
-      <c r="T49" t="n">
+      <c r="U49" t="n">
         <v>-2.412481</v>
       </c>
-      <c r="U49" t="n">
+      <c r="V49" t="n">
         <v>-3.136324</v>
       </c>
-      <c r="V49" t="n">
+      <c r="W49" t="n">
         <v>-3.13666</v>
       </c>
-      <c r="W49" t="n">
+      <c r="X49" t="n">
         <v>0.612293</v>
       </c>
-      <c r="X49" t="n">
+      <c r="Y49" t="n">
+        <v>0.073298</v>
+      </c>
+      <c r="Z49" t="n">
         <v>0.9397180000000001</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="AA49" t="n">
         <v>1.638893</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="AB49" t="n">
         <v>5.130501</v>
       </c>
-      <c r="AA49" t="n">
+      <c r="AC49" t="n">
         <v>3.033233</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AD49" t="n">
         <v>5.054283</v>
       </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
       <c r="AE49" t="n">
         <v>0</v>
       </c>
       <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
         <v>0.18</v>
       </c>
-      <c r="AG49" t="n">
+      <c r="AI49" t="n">
         <v>0.06</v>
       </c>
-      <c r="AH49" t="n">
+      <c r="AJ49" t="n">
         <v>0.26</v>
       </c>
-      <c r="AI49" t="n">
+      <c r="AK49" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5677,72 +5973,78 @@
         <v>6852705</v>
       </c>
       <c r="M50" t="n">
+        <v>2589817</v>
+      </c>
+      <c r="N50" t="n">
         <v>4262888</v>
       </c>
-      <c r="N50" t="n">
+      <c r="O50" t="n">
         <v>4.09</v>
       </c>
-      <c r="O50" t="n">
+      <c r="P50" t="n">
         <v>2.77</v>
       </c>
-      <c r="P50" t="n">
+      <c r="Q50" t="n">
         <v>4.89</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="R50" t="n">
         <v>31.47</v>
       </c>
-      <c r="R50" t="n">
+      <c r="S50" t="n">
         <v>356582</v>
       </c>
-      <c r="S50" t="n">
+      <c r="T50" t="n">
         <v>-0.085869</v>
       </c>
-      <c r="T50" t="n">
+      <c r="U50" t="n">
         <v>-0.812453</v>
       </c>
-      <c r="U50" t="n">
+      <c r="V50" t="n">
         <v>-1.986584</v>
       </c>
-      <c r="V50" t="n">
+      <c r="W50" t="n">
         <v>-1.986804</v>
       </c>
-      <c r="W50" t="n">
+      <c r="X50" t="n">
         <v>1.155358</v>
       </c>
-      <c r="X50" t="n">
+      <c r="Y50" t="n">
+        <v>1.710427</v>
+      </c>
+      <c r="Z50" t="n">
         <v>0.821088</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="AA50" t="n">
         <v>1.657796</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="AB50" t="n">
         <v>5.172369</v>
       </c>
-      <c r="AA50" t="n">
+      <c r="AC50" t="n">
         <v>2.828436</v>
       </c>
-      <c r="AB50" t="n">
+      <c r="AD50" t="n">
         <v>5.096104</v>
       </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
       <c r="AE50" t="n">
         <v>0</v>
       </c>
       <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AG50" t="n">
+      <c r="AI50" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AH50" t="n">
+      <c r="AJ50" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI50" t="n">
+      <c r="AK50" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -5784,72 +6086,78 @@
         <v>6923886</v>
       </c>
       <c r="M51" t="n">
+        <v>2597630</v>
+      </c>
+      <c r="N51" t="n">
         <v>4326256</v>
       </c>
-      <c r="N51" t="n">
+      <c r="O51" t="n">
         <v>4.18</v>
       </c>
-      <c r="O51" t="n">
+      <c r="P51" t="n">
         <v>2.82</v>
       </c>
-      <c r="P51" t="n">
+      <c r="Q51" t="n">
         <v>4.99</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="R51" t="n">
         <v>32.04</v>
       </c>
-      <c r="R51" t="n">
+      <c r="S51" t="n">
         <v>357103</v>
       </c>
-      <c r="S51" t="n">
+      <c r="T51" t="n">
         <v>0.016352</v>
       </c>
-      <c r="T51" t="n">
+      <c r="U51" t="n">
         <v>0.541697</v>
       </c>
-      <c r="U51" t="n">
+      <c r="V51" t="n">
         <v>1.235287</v>
       </c>
-      <c r="V51" t="n">
+      <c r="W51" t="n">
         <v>1.235427</v>
       </c>
-      <c r="W51" t="n">
+      <c r="X51" t="n">
         <v>1.038729</v>
       </c>
-      <c r="X51" t="n">
+      <c r="Y51" t="n">
+        <v>0.301682</v>
+      </c>
+      <c r="Z51" t="n">
         <v>1.486504</v>
       </c>
-      <c r="Y51" t="n">
+      <c r="AA51" t="n">
         <v>0.146109</v>
       </c>
-      <c r="Z51" t="n">
+      <c r="AB51" t="n">
         <v>4.680811</v>
       </c>
-      <c r="AA51" t="n">
+      <c r="AC51" t="n">
         <v>0.924206</v>
       </c>
-      <c r="AB51" t="n">
+      <c r="AD51" t="n">
         <v>4.490243</v>
       </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
       <c r="AE51" t="n">
         <v>0</v>
       </c>
       <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG51" t="n">
+      <c r="AI51" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH51" t="n">
+      <c r="AJ51" t="n">
         <v>0.1</v>
       </c>
-      <c r="AI51" t="n">
+      <c r="AK51" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -5891,72 +6199,78 @@
         <v>7004223</v>
       </c>
       <c r="M52" t="n">
+        <v>2616902</v>
+      </c>
+      <c r="N52" t="n">
         <v>4387321</v>
       </c>
-      <c r="N52" t="n">
+      <c r="O52" t="n">
         <v>4.24</v>
       </c>
-      <c r="O52" t="n">
+      <c r="P52" t="n">
         <v>2.75</v>
       </c>
-      <c r="P52" t="n">
+      <c r="Q52" t="n">
         <v>5.12</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="R52" t="n">
         <v>32.2</v>
       </c>
-      <c r="R52" t="n">
+      <c r="S52" t="n">
         <v>360578</v>
       </c>
-      <c r="S52" t="n">
+      <c r="T52" t="n">
         <v>0.456805</v>
       </c>
-      <c r="T52" t="n">
+      <c r="U52" t="n">
         <v>-3.159521</v>
       </c>
-      <c r="U52" t="n">
+      <c r="V52" t="n">
         <v>-0.937912</v>
       </c>
-      <c r="V52" t="n">
+      <c r="W52" t="n">
         <v>-0.938017</v>
       </c>
-      <c r="W52" t="n">
+      <c r="X52" t="n">
         <v>1.160288</v>
       </c>
-      <c r="X52" t="n">
+      <c r="Y52" t="n">
+        <v>0.741907</v>
+      </c>
+      <c r="Z52" t="n">
         <v>1.411498</v>
       </c>
-      <c r="Y52" t="n">
+      <c r="AA52" t="n">
         <v>0.973109</v>
       </c>
-      <c r="Z52" t="n">
+      <c r="AB52" t="n">
         <v>4.461836</v>
       </c>
-      <c r="AA52" t="n">
+      <c r="AC52" t="n">
         <v>-0.101973</v>
       </c>
-      <c r="AB52" t="n">
+      <c r="AD52" t="n">
         <v>4.177803</v>
       </c>
-      <c r="AC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" t="n">
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="n">
         <v>-0</v>
       </c>
-      <c r="AE52" t="n">
+      <c r="AG52" t="n">
         <v>-0</v>
       </c>
-      <c r="AF52" t="n">
+      <c r="AH52" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG52" t="n">
+      <c r="AI52" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AH52" t="n">
+      <c r="AJ52" t="n">
         <v>0.13</v>
       </c>
-      <c r="AI52" t="n">
+      <c r="AK52" t="n">
         <v>0.16</v>
       </c>
     </row>
@@ -5998,72 +6312,78 @@
         <v>7137252</v>
       </c>
       <c r="M53" t="n">
+        <v>2701735</v>
+      </c>
+      <c r="N53" t="n">
         <v>4435517</v>
       </c>
-      <c r="N53" t="n">
+      <c r="O53" t="n">
         <v>4.2</v>
       </c>
-      <c r="O53" t="n">
+      <c r="P53" t="n">
         <v>2.7</v>
       </c>
-      <c r="P53" t="n">
+      <c r="Q53" t="n">
         <v>5.12</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="R53" t="n">
         <v>31.87</v>
       </c>
-      <c r="R53" t="n">
+      <c r="S53" t="n">
         <v>358234</v>
       </c>
-      <c r="S53" t="n">
+      <c r="T53" t="n">
         <v>0.185583</v>
       </c>
-      <c r="T53" t="n">
+      <c r="U53" t="n">
         <v>0.549021</v>
       </c>
-      <c r="U53" t="n">
+      <c r="V53" t="n">
         <v>3.160973</v>
       </c>
-      <c r="V53" t="n">
+      <c r="W53" t="n">
         <v>3.161329</v>
       </c>
-      <c r="W53" t="n">
+      <c r="X53" t="n">
         <v>1.899268</v>
       </c>
-      <c r="X53" t="n">
+      <c r="Y53" t="n">
+        <v>3.241734</v>
+      </c>
+      <c r="Z53" t="n">
         <v>1.098529</v>
       </c>
-      <c r="Y53" t="n">
+      <c r="AA53" t="n">
         <v>-0.650067</v>
       </c>
-      <c r="Z53" t="n">
+      <c r="AB53" t="n">
         <v>4.264385</v>
       </c>
-      <c r="AA53" t="n">
+      <c r="AC53" t="n">
         <v>-1.042167</v>
       </c>
-      <c r="AB53" t="n">
+      <c r="AD53" t="n">
         <v>3.897866</v>
       </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
       <c r="AE53" t="n">
         <v>0</v>
       </c>
       <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AG53" t="n">
+      <c r="AI53" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI53" t="n">
+      <c r="AJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -6105,72 +6425,78 @@
         <v>7130762</v>
       </c>
       <c r="M54" t="n">
+        <v>2654220</v>
+      </c>
+      <c r="N54" t="n">
         <v>4476542</v>
       </c>
-      <c r="N54" t="n">
+      <c r="O54" t="n">
         <v>4.44</v>
       </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
         <v>2.87</v>
       </c>
-      <c r="P54" t="n">
+      <c r="Q54" t="n">
         <v>5.38</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="R54" t="n">
         <v>32.45</v>
       </c>
-      <c r="R54" t="n">
+      <c r="S54" t="n">
         <v>364367</v>
       </c>
-      <c r="S54" t="n">
+      <c r="T54" t="n">
         <v>0.54555</v>
       </c>
-      <c r="T54" t="n">
+      <c r="U54" t="n">
         <v>-3.178231</v>
       </c>
-      <c r="U54" t="n">
+      <c r="V54" t="n">
         <v>-4.94875</v>
       </c>
-      <c r="V54" t="n">
+      <c r="W54" t="n">
         <v>-4.949289</v>
       </c>
-      <c r="W54" t="n">
+      <c r="X54" t="n">
         <v>-0.090931</v>
       </c>
-      <c r="X54" t="n">
+      <c r="Y54" t="n">
+        <v>-1.758685</v>
+      </c>
+      <c r="Z54" t="n">
         <v>0.92492</v>
       </c>
-      <c r="Y54" t="n">
+      <c r="AA54" t="n">
         <v>1.712009</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="AB54" t="n">
         <v>4.441351</v>
       </c>
-      <c r="AA54" t="n">
+      <c r="AC54" t="n">
         <v>-0.903999</v>
       </c>
-      <c r="AB54" t="n">
+      <c r="AD54" t="n">
         <v>4.303068</v>
       </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>0</v>
-      </c>
       <c r="AE54" t="n">
         <v>0</v>
       </c>
       <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
         <v>0.24</v>
       </c>
-      <c r="AG54" t="n">
+      <c r="AI54" t="n">
         <v>0.17</v>
       </c>
-      <c r="AH54" t="n">
+      <c r="AJ54" t="n">
         <v>0.26</v>
       </c>
-      <c r="AI54" t="n">
+      <c r="AK54" t="n">
         <v>0.58</v>
       </c>
     </row>
@@ -6212,72 +6538,78 @@
         <v>7157783</v>
       </c>
       <c r="M55" t="n">
+        <v>2656484</v>
+      </c>
+      <c r="N55" t="n">
         <v>4501299</v>
       </c>
-      <c r="N55" t="n">
+      <c r="O55" t="n">
         <v>4.64</v>
       </c>
-      <c r="O55" t="n">
+      <c r="P55" t="n">
         <v>3.07</v>
       </c>
-      <c r="P55" t="n">
+      <c r="Q55" t="n">
         <v>5.56</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="R55" t="n">
         <v>32.63</v>
       </c>
-      <c r="R55" t="n">
+      <c r="S55" t="n">
         <v>371074</v>
       </c>
-      <c r="S55" t="n">
+      <c r="T55" t="n">
         <v>0.6239710000000001</v>
       </c>
-      <c r="T55" t="n">
+      <c r="U55" t="n">
         <v>2.874551</v>
       </c>
-      <c r="U55" t="n">
+      <c r="V55" t="n">
         <v>-1.54108</v>
       </c>
-      <c r="V55" t="n">
+      <c r="W55" t="n">
         <v>-1.541256</v>
       </c>
-      <c r="W55" t="n">
+      <c r="X55" t="n">
         <v>0.378936</v>
       </c>
-      <c r="X55" t="n">
+      <c r="Y55" t="n">
+        <v>0.085298</v>
+      </c>
+      <c r="Z55" t="n">
         <v>0.553038</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="AA55" t="n">
         <v>1.840727</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="AB55" t="n">
         <v>3.812497</v>
       </c>
-      <c r="AA55" t="n">
+      <c r="AC55" t="n">
         <v>-2.659212</v>
       </c>
-      <c r="AB55" t="n">
+      <c r="AD55" t="n">
         <v>3.357475</v>
       </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
       <c r="AE55" t="n">
         <v>0</v>
       </c>
       <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
         <v>0.2</v>
       </c>
-      <c r="AG55" t="n">
+      <c r="AI55" t="n">
         <v>0.2</v>
       </c>
-      <c r="AH55" t="n">
+      <c r="AJ55" t="n">
         <v>0.18</v>
       </c>
-      <c r="AI55" t="n">
+      <c r="AK55" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -6319,72 +6651,78 @@
         <v>7240557</v>
       </c>
       <c r="M56" t="n">
+        <v>2687535</v>
+      </c>
+      <c r="N56" t="n">
         <v>4553022</v>
       </c>
-      <c r="N56" t="n">
+      <c r="O56" t="n">
         <v>4.52</v>
       </c>
-      <c r="O56" t="n">
+      <c r="P56" t="n">
         <v>3.06</v>
       </c>
-      <c r="P56" t="n">
+      <c r="Q56" t="n">
         <v>5.39</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="R56" t="n">
         <v>32.84</v>
       </c>
-      <c r="R56" t="n">
+      <c r="S56" t="n">
         <v>362002</v>
       </c>
-      <c r="S56" t="n">
+      <c r="T56" t="n">
         <v>-0.13412</v>
       </c>
-      <c r="T56" t="n">
+      <c r="U56" t="n">
         <v>10.543613</v>
       </c>
-      <c r="U56" t="n">
+      <c r="V56" t="n">
         <v>1.357413</v>
       </c>
-      <c r="V56" t="n">
+      <c r="W56" t="n">
         <v>1.357572</v>
       </c>
-      <c r="W56" t="n">
+      <c r="X56" t="n">
         <v>1.15642</v>
       </c>
-      <c r="X56" t="n">
+      <c r="Y56" t="n">
+        <v>1.168876</v>
+      </c>
+      <c r="Z56" t="n">
         <v>1.149068</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="AA56" t="n">
         <v>-2.444795</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="AB56" t="n">
         <v>4.142847</v>
       </c>
-      <c r="AA56" t="n">
+      <c r="AC56" t="n">
         <v>-1.819225</v>
       </c>
-      <c r="AB56" t="n">
+      <c r="AD56" t="n">
         <v>3.768807</v>
       </c>
-      <c r="AC56" t="n">
+      <c r="AE56" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD56" t="n">
+      <c r="AF56" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="AE56" t="n">
+      <c r="AG56" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="AF56" t="n">
+      <c r="AH56" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AG56" t="n">
+      <c r="AI56" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH56" t="n">
+      <c r="AJ56" t="n">
         <v>-0.17</v>
       </c>
-      <c r="AI56" t="n">
+      <c r="AK56" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -6426,72 +6764,78 @@
         <v>7259766</v>
       </c>
       <c r="M57" t="n">
+        <v>2685397</v>
+      </c>
+      <c r="N57" t="n">
         <v>4574368</v>
       </c>
-      <c r="N57" t="n">
+      <c r="O57" t="n">
         <v>4.64</v>
       </c>
-      <c r="O57" t="n">
+      <c r="P57" t="n">
         <v>3.15</v>
       </c>
-      <c r="P57" t="n">
+      <c r="Q57" t="n">
         <v>5.51</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="R57" t="n">
         <v>33.36</v>
       </c>
-      <c r="R57" t="n">
+      <c r="S57" t="n">
         <v>366913</v>
       </c>
-      <c r="S57" t="n">
+      <c r="T57" t="n">
         <v>0.282137</v>
       </c>
-      <c r="T57" t="n">
+      <c r="U57" t="n">
         <v>-3.409876</v>
       </c>
-      <c r="U57" t="n">
+      <c r="V57" t="n">
         <v>-4.421964</v>
       </c>
-      <c r="V57" t="n">
+      <c r="W57" t="n">
         <v>-4.422473</v>
       </c>
-      <c r="W57" t="n">
+      <c r="X57" t="n">
         <v>0.265297</v>
       </c>
-      <c r="X57" t="n">
+      <c r="Y57" t="n">
+        <v>-0.079552</v>
+      </c>
+      <c r="Z57" t="n">
         <v>0.468831</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="AA57" t="n">
         <v>1.356622</v>
       </c>
-      <c r="Z57" t="n">
+      <c r="AB57" t="n">
         <v>4.39172</v>
       </c>
-      <c r="AA57" t="n">
+      <c r="AC57" t="n">
         <v>0.619623</v>
       </c>
-      <c r="AB57" t="n">
+      <c r="AD57" t="n">
         <v>4.109608</v>
       </c>
-      <c r="AC57" t="n">
+      <c r="AE57" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD57" t="n">
+      <c r="AF57" t="n">
         <v>-0.000554</v>
       </c>
-      <c r="AE57" t="n">
+      <c r="AG57" t="n">
         <v>-0.000554</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>0.09</v>
       </c>
       <c r="AH57" t="n">
         <v>0.12</v>
       </c>
       <c r="AI57" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AK57" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -6533,72 +6877,78 @@
         <v>7305306</v>
       </c>
       <c r="M58" t="n">
+        <v>2708154</v>
+      </c>
+      <c r="N58" t="n">
         <v>4597152</v>
       </c>
-      <c r="N58" t="n">
+      <c r="O58" t="n">
         <v>4.74</v>
       </c>
-      <c r="O58" t="n">
+      <c r="P58" t="n">
         <v>3.25</v>
       </c>
-      <c r="P58" t="n">
+      <c r="Q58" t="n">
         <v>5.62</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="R58" t="n">
         <v>33.1</v>
       </c>
-      <c r="R58" t="n">
+      <c r="S58" t="n">
         <v>371137</v>
       </c>
-      <c r="S58" t="n">
+      <c r="T58" t="n">
         <v>0.214941</v>
       </c>
-      <c r="T58" t="n">
+      <c r="U58" t="n">
         <v>-3.805639</v>
       </c>
-      <c r="U58" t="n">
+      <c r="V58" t="n">
         <v>1.369122</v>
       </c>
-      <c r="V58" t="n">
+      <c r="W58" t="n">
         <v>1.369286</v>
       </c>
-      <c r="W58" t="n">
+      <c r="X58" t="n">
         <v>0.627293</v>
       </c>
-      <c r="X58" t="n">
+      <c r="Y58" t="n">
+        <v>0.847435</v>
+      </c>
+      <c r="Z58" t="n">
         <v>0.49808</v>
       </c>
-      <c r="Y58" t="n">
+      <c r="AA58" t="n">
         <v>1.151227</v>
       </c>
-      <c r="Z58" t="n">
+      <c r="AB58" t="n">
         <v>4.724907</v>
       </c>
-      <c r="AA58" t="n">
+      <c r="AC58" t="n">
         <v>1.964454</v>
       </c>
-      <c r="AB58" t="n">
+      <c r="AD58" t="n">
         <v>4.420848</v>
       </c>
-      <c r="AC58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD58" t="n">
+      <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="n">
         <v>-0.0008229999999999999</v>
       </c>
-      <c r="AE58" t="n">
+      <c r="AG58" t="n">
         <v>-0.0008229999999999999</v>
       </c>
-      <c r="AF58" t="n">
+      <c r="AH58" t="n">
         <v>0.1</v>
       </c>
-      <c r="AG58" t="n">
+      <c r="AI58" t="n">
         <v>0.1</v>
       </c>
-      <c r="AH58" t="n">
+      <c r="AJ58" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI58" t="n">
+      <c r="AK58" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -6640,72 +6990,78 @@
         <v>7353293</v>
       </c>
       <c r="M59" t="n">
+        <v>2750625</v>
+      </c>
+      <c r="N59" t="n">
         <v>4602668</v>
       </c>
-      <c r="N59" t="n">
+      <c r="O59" t="n">
         <v>4.58</v>
       </c>
-      <c r="O59" t="n">
+      <c r="P59" t="n">
         <v>3.18</v>
       </c>
-      <c r="P59" t="n">
+      <c r="Q59" t="n">
         <v>5.42</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="R59" t="n">
         <v>33.33</v>
       </c>
-      <c r="R59" t="n">
+      <c r="S59" t="n">
         <v>367558</v>
       </c>
-      <c r="S59" t="n">
+      <c r="T59" t="n">
         <v>-0.882422</v>
       </c>
-      <c r="T59" t="n">
+      <c r="U59" t="n">
         <v>0.261521</v>
       </c>
-      <c r="U59" t="n">
+      <c r="V59" t="n">
         <v>2.367063</v>
       </c>
-      <c r="V59" t="n">
+      <c r="W59" t="n">
         <v>2.367344</v>
       </c>
-      <c r="W59" t="n">
+      <c r="X59" t="n">
         <v>0.656879</v>
       </c>
-      <c r="X59" t="n">
+      <c r="Y59" t="n">
+        <v>1.568264</v>
+      </c>
+      <c r="Z59" t="n">
         <v>0.119987</v>
       </c>
-      <c r="Y59" t="n">
+      <c r="AA59" t="n">
         <v>-0.964334</v>
       </c>
-      <c r="Z59" t="n">
+      <c r="AB59" t="n">
         <v>4.641328</v>
       </c>
-      <c r="AA59" t="n">
+      <c r="AC59" t="n">
         <v>3.177699</v>
       </c>
-      <c r="AB59" t="n">
+      <c r="AD59" t="n">
         <v>4.327084</v>
       </c>
-      <c r="AC59" t="n">
+      <c r="AE59" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD59" t="n">
+      <c r="AF59" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AE59" t="n">
+      <c r="AG59" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AF59" t="n">
+      <c r="AH59" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AG59" t="n">
+      <c r="AI59" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AH59" t="n">
+      <c r="AJ59" t="n">
         <v>-0.2</v>
       </c>
-      <c r="AI59" t="n">
+      <c r="AK59" t="n">
         <v>0.23</v>
       </c>
     </row>
@@ -6747,72 +7103,78 @@
         <v>7372243</v>
       </c>
       <c r="M60" t="n">
+        <v>2731513</v>
+      </c>
+      <c r="N60" t="n">
         <v>4640730</v>
       </c>
-      <c r="N60" t="n">
+      <c r="O60" t="n">
         <v>4.88</v>
       </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
         <v>3.31</v>
       </c>
-      <c r="P60" t="n">
+      <c r="Q60" t="n">
         <v>5.81</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="R60" t="n">
         <v>32.08</v>
       </c>
-      <c r="R60" t="n">
+      <c r="S60" t="n">
         <v>369742</v>
       </c>
-      <c r="S60" t="n">
+      <c r="T60" t="n">
         <v>-0.219358</v>
       </c>
-      <c r="T60" t="n">
+      <c r="U60" t="n">
         <v>4.057001</v>
       </c>
-      <c r="U60" t="n">
+      <c r="V60" t="n">
         <v>-1.918247</v>
       </c>
-      <c r="V60" t="n">
+      <c r="W60" t="n">
         <v>-1.91847</v>
       </c>
-      <c r="W60" t="n">
+      <c r="X60" t="n">
         <v>0.257708</v>
       </c>
-      <c r="X60" t="n">
+      <c r="Y60" t="n">
+        <v>-0.694824</v>
+      </c>
+      <c r="Z60" t="n">
         <v>0.826955</v>
       </c>
-      <c r="Y60" t="n">
+      <c r="AA60" t="n">
         <v>0.5941920000000001</v>
       </c>
-      <c r="Z60" t="n">
+      <c r="AB60" t="n">
         <v>4.443025</v>
       </c>
-      <c r="AA60" t="n">
+      <c r="AC60" t="n">
         <v>2.772183</v>
       </c>
-      <c r="AB60" t="n">
+      <c r="AD60" t="n">
         <v>4.098046</v>
       </c>
-      <c r="AC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" t="n">
+      <c r="AE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="AE60" t="n">
+      <c r="AG60" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="AF60" t="n">
+      <c r="AH60" t="n">
         <v>0.3</v>
       </c>
-      <c r="AG60" t="n">
+      <c r="AI60" t="n">
         <v>0.13</v>
       </c>
-      <c r="AH60" t="n">
+      <c r="AJ60" t="n">
         <v>0.39</v>
       </c>
-      <c r="AI60" t="n">
+      <c r="AK60" t="n">
         <v>-1.25</v>
       </c>
     </row>
@@ -6852,44 +7214,46 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="n">
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="n">
         <v>372616</v>
       </c>
-      <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="n">
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="n">
         <v>2.054241</v>
       </c>
-      <c r="V61" t="n">
+      <c r="W61" t="n">
         <v>2.054484</v>
       </c>
-      <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="n">
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="n">
         <v>0.777299</v>
       </c>
-      <c r="Z61" t="n">
+      <c r="AB61" t="n">
         <v>4.223453</v>
       </c>
-      <c r="AA61" t="n">
+      <c r="AC61" t="n">
         <v>2.178243</v>
       </c>
-      <c r="AB61" t="n">
+      <c r="AD61" t="n">
         <v>3.983297</v>
       </c>
-      <c r="AC61" t="n">
+      <c r="AE61" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD61" t="n">
+      <c r="AF61" t="n">
         <v>-0.0007470000000000001</v>
       </c>
-      <c r="AE61" t="n">
+      <c r="AG61" t="n">
         <v>-0.0007470000000000001</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -6899,10 +7263,10 @@
         <v>13.75</v>
       </c>
       <c r="C62" t="n">
-        <v>0.051473</v>
+        <v>0.051427</v>
       </c>
       <c r="D62" t="n">
-        <v>0.051473</v>
+        <v>0.051427</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
@@ -6910,10 +7274,10 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>5.1117</v>
+        <v>5.1161</v>
       </c>
       <c r="K62" t="n">
-        <v>5.1111</v>
+        <v>5.1155</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -6924,31 +7288,33 @@
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="n">
-        <v>-1.349004</v>
-      </c>
+      <c r="U62" t="inlineStr"/>
       <c r="V62" t="n">
-        <v>-1.34916</v>
-      </c>
-      <c r="W62" t="inlineStr"/>
+        <v>-1.264088</v>
+      </c>
+      <c r="W62" t="n">
+        <v>-1.264235</v>
+      </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr"/>
-      <c r="AC62" t="n">
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD62" t="n">
-        <v>-0.000311</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>-0.000311</v>
-      </c>
-      <c r="AF62" t="inlineStr"/>
-      <c r="AG62" t="inlineStr"/>
+      <c r="AF62" t="n">
+        <v>-0.000357</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>-0.000357</v>
+      </c>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -7263,10 +7263,10 @@
         <v>13.75</v>
       </c>
       <c r="C62" t="n">
-        <v>0.051427</v>
+        <v>0.051387</v>
       </c>
       <c r="D62" t="n">
-        <v>0.051427</v>
+        <v>0.051387</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
@@ -7274,10 +7274,10 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>5.1161</v>
+        <v>5.1414</v>
       </c>
       <c r="K62" t="n">
-        <v>5.1155</v>
+        <v>5.1408</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -7290,10 +7290,10 @@
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="n">
-        <v>-1.264088</v>
+        <v>-0.775822</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.264235</v>
+        <v>-0.775912</v>
       </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
@@ -7306,10 +7306,10 @@
         <v>-0.25</v>
       </c>
       <c r="AF62" t="n">
-        <v>-0.000357</v>
+        <v>-0.000397</v>
       </c>
       <c r="AG62" t="n">
-        <v>-0.000357</v>
+        <v>-0.000397</v>
       </c>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -7263,10 +7263,10 @@
         <v>13.75</v>
       </c>
       <c r="C62" t="n">
-        <v>0.051387</v>
+        <v>0.051352</v>
       </c>
       <c r="D62" t="n">
-        <v>0.051387</v>
+        <v>0.051352</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
@@ -7274,10 +7274,10 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>5.1414</v>
+        <v>5.1795</v>
       </c>
       <c r="K62" t="n">
-        <v>5.1408</v>
+        <v>5.1789</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -7290,10 +7290,10 @@
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="n">
-        <v>-0.775822</v>
+        <v>-0.040528</v>
       </c>
       <c r="W62" t="n">
-        <v>-0.775912</v>
+        <v>-0.040533</v>
       </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
@@ -7306,10 +7306,10 @@
         <v>-0.25</v>
       </c>
       <c r="AF62" t="n">
-        <v>-0.000397</v>
+        <v>-0.000432</v>
       </c>
       <c r="AG62" t="n">
-        <v>-0.000397</v>
+        <v>-0.000432</v>
       </c>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK62"/>
+  <dimension ref="A1:AI62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,135 +473,125 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
           <t>saldo_credito_total</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>saldo_credito_pj</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>saldo_credito_pf</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inadimplencia_total</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inadimplencia_pj</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inadimplencia_pf</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>var_pct_cambio_compra_usd</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ipca_acum_12m</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>inpc_acum_12m</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>dif_selic_over</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dif_cdi</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -639,32 +629,30 @@
         <v>5.4394</v>
       </c>
       <c r="K2" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="L2" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="M2" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="N2" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="O2" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="P2" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="R2" t="n">
-        <v>21.42</v>
-      </c>
-      <c r="S2" t="n">
         <v>368886</v>
       </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -681,8 +669,6 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -716,78 +702,72 @@
         <v>5.643</v>
       </c>
       <c r="K3" t="n">
-        <v>5.6424</v>
+        <v>4511956</v>
       </c>
       <c r="L3" t="n">
-        <v>4511956</v>
+        <v>1910940</v>
       </c>
       <c r="M3" t="n">
-        <v>1910940</v>
+        <v>2601017</v>
       </c>
       <c r="N3" t="n">
-        <v>2601017</v>
+        <v>2.33</v>
       </c>
       <c r="O3" t="n">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="R3" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="S3" t="n">
-        <v>367927</v>
+        <v>0.537905</v>
       </c>
       <c r="T3" t="n">
-        <v>0.537905</v>
+        <v>-0.594556</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.594556</v>
+        <v>3.74306</v>
       </c>
       <c r="V3" t="n">
-        <v>3.74306</v>
+        <v>1.596467</v>
       </c>
       <c r="W3" t="n">
-        <v>3.743473</v>
+        <v>0.888065</v>
       </c>
       <c r="X3" t="n">
-        <v>1.596467</v>
+        <v>2.123375</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.888065</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.123375</v>
-      </c>
-      <c r="AA3" t="n">
         <v>-0.259972</v>
       </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.000557</v>
+      </c>
       <c r="AE3" t="n">
-        <v>1.5</v>
+        <v>0.000557</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.000557</v>
+        <v>-0.01</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.000557</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AK3" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -823,78 +803,72 @@
         <v>5.6199</v>
       </c>
       <c r="K4" t="n">
-        <v>5.6193</v>
+        <v>4597507</v>
       </c>
       <c r="L4" t="n">
-        <v>4597507</v>
+        <v>1933111</v>
       </c>
       <c r="M4" t="n">
-        <v>1933111</v>
+        <v>2664395</v>
       </c>
       <c r="N4" t="n">
-        <v>2664395</v>
+        <v>2.36</v>
       </c>
       <c r="O4" t="n">
-        <v>2.36</v>
+        <v>1.46</v>
       </c>
       <c r="P4" t="n">
-        <v>1.46</v>
+        <v>3.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.01</v>
+        <v>23.91</v>
       </c>
       <c r="R4" t="n">
-        <v>23.91</v>
+        <v>367772</v>
       </c>
       <c r="S4" t="n">
-        <v>367772</v>
+        <v>1.608989</v>
       </c>
       <c r="T4" t="n">
-        <v>1.608989</v>
+        <v>1.36989</v>
       </c>
       <c r="U4" t="n">
-        <v>1.36989</v>
+        <v>-0.409357</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.409357</v>
+        <v>1.896096</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.4094</v>
+        <v>1.160214</v>
       </c>
       <c r="X4" t="n">
-        <v>1.896096</v>
+        <v>2.436662</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.160214</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.436662</v>
-      </c>
-      <c r="AA4" t="n">
         <v>-0.042128</v>
       </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.005012</v>
+      </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>0.005012</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.005012</v>
+        <v>0.03</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.005012</v>
+        <v>0.03</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK4" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -930,78 +904,72 @@
         <v>5.5805</v>
       </c>
       <c r="K5" t="n">
-        <v>5.5799</v>
+        <v>4682852</v>
       </c>
       <c r="L5" t="n">
-        <v>4682852</v>
+        <v>1974391</v>
       </c>
       <c r="M5" t="n">
-        <v>1974391</v>
+        <v>2708461</v>
       </c>
       <c r="N5" t="n">
-        <v>2708461</v>
+        <v>2.35</v>
       </c>
       <c r="O5" t="n">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="P5" t="n">
-        <v>1.4</v>
+        <v>3.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.05</v>
+        <v>24.21</v>
       </c>
       <c r="R5" t="n">
-        <v>24.21</v>
+        <v>362204</v>
       </c>
       <c r="S5" t="n">
-        <v>362204</v>
+        <v>0.32497</v>
       </c>
       <c r="T5" t="n">
-        <v>0.32497</v>
+        <v>1.502063</v>
       </c>
       <c r="U5" t="n">
-        <v>1.502063</v>
+        <v>-0.70108</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.70108</v>
+        <v>1.856332</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.701155</v>
+        <v>2.135418</v>
       </c>
       <c r="X5" t="n">
-        <v>1.856332</v>
+        <v>1.653884</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.135418</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.653884</v>
-      </c>
-      <c r="AA5" t="n">
         <v>-1.513981</v>
       </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.00406</v>
+      </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>0.00406</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.00406</v>
+        <v>-0.01</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.00406</v>
+        <v>-0.06</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK5" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1037,78 +1005,72 @@
         <v>5.3574</v>
       </c>
       <c r="K6" t="n">
-        <v>5.3568</v>
+        <v>4682131</v>
       </c>
       <c r="L6" t="n">
-        <v>4682131</v>
+        <v>1947035</v>
       </c>
       <c r="M6" t="n">
-        <v>1947035</v>
+        <v>2735096</v>
       </c>
       <c r="N6" t="n">
-        <v>2735096</v>
+        <v>2.51</v>
       </c>
       <c r="O6" t="n">
-        <v>2.51</v>
+        <v>1.46</v>
       </c>
       <c r="P6" t="n">
-        <v>1.46</v>
+        <v>3.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.26</v>
+        <v>25.23</v>
       </c>
       <c r="R6" t="n">
-        <v>25.23</v>
+        <v>358398</v>
       </c>
       <c r="S6" t="n">
-        <v>358398</v>
+        <v>-1.968118</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.968118</v>
+        <v>-7.696961</v>
       </c>
       <c r="U6" t="n">
-        <v>-7.696961</v>
+        <v>-3.99785</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.99785</v>
+        <v>-0.015397</v>
       </c>
       <c r="W6" t="n">
-        <v>-3.99828</v>
+        <v>-1.385541</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.015397</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.385541</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.9834000000000001</v>
-      </c>
-      <c r="AA6" t="n">
         <v>-1.050789</v>
       </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.001433</v>
+      </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>0.001433</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.001433</v>
+        <v>0.16</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.001433</v>
+        <v>0.06</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AK6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1144,78 +1106,72 @@
         <v>5.1394</v>
       </c>
       <c r="K7" t="n">
-        <v>5.1388</v>
+        <v>4727818</v>
       </c>
       <c r="L7" t="n">
-        <v>4727818</v>
+        <v>1971524</v>
       </c>
       <c r="M7" t="n">
-        <v>1971524</v>
+        <v>2756295</v>
       </c>
       <c r="N7" t="n">
-        <v>2756295</v>
+        <v>2.57</v>
       </c>
       <c r="O7" t="n">
-        <v>2.57</v>
+        <v>1.44</v>
       </c>
       <c r="P7" t="n">
-        <v>1.44</v>
+        <v>3.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.38</v>
+        <v>25.63</v>
       </c>
       <c r="R7" t="n">
-        <v>25.63</v>
+        <v>357740</v>
       </c>
       <c r="S7" t="n">
-        <v>357740</v>
+        <v>1.087134</v>
       </c>
       <c r="T7" t="n">
-        <v>1.087134</v>
+        <v>4.318965</v>
       </c>
       <c r="U7" t="n">
-        <v>4.318965</v>
+        <v>-4.069138</v>
       </c>
       <c r="V7" t="n">
-        <v>-4.069138</v>
+        <v>0.975774</v>
       </c>
       <c r="W7" t="n">
-        <v>-4.069594</v>
+        <v>1.257759</v>
       </c>
       <c r="X7" t="n">
-        <v>0.975774</v>
+        <v>0.775073</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.257759</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.775073</v>
-      </c>
-      <c r="AA7" t="n">
         <v>-0.183595</v>
       </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.004849</v>
+      </c>
       <c r="AE7" t="n">
-        <v>1.5</v>
+        <v>0.004849</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.004849</v>
+        <v>0.06</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.004849</v>
+        <v>-0.02</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AK7" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1251,78 +1207,72 @@
         <v>4.7378</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7372</v>
+        <v>4794583</v>
       </c>
       <c r="L8" t="n">
-        <v>4794583</v>
+        <v>1994119</v>
       </c>
       <c r="M8" t="n">
-        <v>1994119</v>
+        <v>2800464</v>
       </c>
       <c r="N8" t="n">
-        <v>2800464</v>
+        <v>2.66</v>
       </c>
       <c r="O8" t="n">
-        <v>2.66</v>
+        <v>1.55</v>
       </c>
       <c r="P8" t="n">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.45</v>
+        <v>26.54</v>
       </c>
       <c r="R8" t="n">
-        <v>26.54</v>
+        <v>353169</v>
       </c>
       <c r="S8" t="n">
-        <v>353169</v>
+        <v>1.084094</v>
       </c>
       <c r="T8" t="n">
-        <v>1.084094</v>
+        <v>9.300848999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>9.300848999999999</v>
+        <v>-7.814142</v>
       </c>
       <c r="V8" t="n">
-        <v>-7.814142</v>
+        <v>1.412174</v>
       </c>
       <c r="W8" t="n">
-        <v>-7.815054</v>
+        <v>1.146068</v>
       </c>
       <c r="X8" t="n">
-        <v>1.412174</v>
+        <v>1.602477</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.146068</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.602477</v>
-      </c>
-      <c r="AA8" t="n">
         <v>-1.277744</v>
       </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.002356</v>
+      </c>
       <c r="AE8" t="n">
-        <v>1</v>
+        <v>0.002356</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.002356</v>
+        <v>0.09</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.002356</v>
+        <v>0.11</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK8" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1358,78 +1308,72 @@
         <v>4.9191</v>
       </c>
       <c r="K9" t="n">
-        <v>4.9185</v>
+        <v>4833732</v>
       </c>
       <c r="L9" t="n">
-        <v>4833732</v>
+        <v>2003312</v>
       </c>
       <c r="M9" t="n">
-        <v>2003312</v>
+        <v>2830420</v>
       </c>
       <c r="N9" t="n">
-        <v>2830420</v>
+        <v>2.72</v>
       </c>
       <c r="O9" t="n">
-        <v>2.72</v>
+        <v>1.57</v>
       </c>
       <c r="P9" t="n">
-        <v>1.57</v>
+        <v>3.54</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.54</v>
+        <v>27.46</v>
       </c>
       <c r="R9" t="n">
-        <v>27.46</v>
+        <v>345097</v>
       </c>
       <c r="S9" t="n">
-        <v>345097</v>
+        <v>-0.107325</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.107325</v>
+        <v>-4.116419</v>
       </c>
       <c r="U9" t="n">
-        <v>-4.116419</v>
+        <v>3.826671</v>
       </c>
       <c r="V9" t="n">
-        <v>3.826671</v>
+        <v>0.816526</v>
       </c>
       <c r="W9" t="n">
-        <v>3.827155</v>
+        <v>0.461006</v>
       </c>
       <c r="X9" t="n">
-        <v>0.816526</v>
+        <v>1.06968</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.461006</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.06968</v>
-      </c>
-      <c r="AA9" t="n">
         <v>-2.285591</v>
       </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.001785</v>
+      </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>0.001785</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.001785</v>
+        <v>0.06</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001785</v>
+        <v>0.02</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK9" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1465,78 +1409,72 @@
         <v>4.7289</v>
       </c>
       <c r="K10" t="n">
-        <v>4.7283</v>
+        <v>4889397</v>
       </c>
       <c r="L10" t="n">
-        <v>4889397</v>
+        <v>2013726</v>
       </c>
       <c r="M10" t="n">
-        <v>2013726</v>
+        <v>2875671</v>
       </c>
       <c r="N10" t="n">
-        <v>2875671</v>
+        <v>2.79</v>
       </c>
       <c r="O10" t="n">
-        <v>2.79</v>
+        <v>1.57</v>
       </c>
       <c r="P10" t="n">
-        <v>1.57</v>
+        <v>3.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.65</v>
+        <v>27.42</v>
       </c>
       <c r="R10" t="n">
-        <v>27.42</v>
+        <v>346415</v>
       </c>
       <c r="S10" t="n">
-        <v>346415</v>
+        <v>0.205368</v>
       </c>
       <c r="T10" t="n">
-        <v>0.205368</v>
+        <v>-0.484439</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.484439</v>
+        <v>-3.866561</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.866561</v>
+        <v>1.151595</v>
       </c>
       <c r="W10" t="n">
-        <v>-3.867033</v>
+        <v>0.5198390000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>1.151595</v>
+        <v>1.598738</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5198390000000001</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.598738</v>
-      </c>
-      <c r="AA10" t="n">
         <v>0.381922</v>
       </c>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.003057</v>
+      </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>0.003057</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.003057</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.003057</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK10" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1572,78 +1510,72 @@
         <v>5.238</v>
       </c>
       <c r="K11" t="n">
-        <v>5.2374</v>
+        <v>4965603</v>
       </c>
       <c r="L11" t="n">
-        <v>4965603</v>
+        <v>2052569</v>
       </c>
       <c r="M11" t="n">
-        <v>2052569</v>
+        <v>2913035</v>
       </c>
       <c r="N11" t="n">
-        <v>2913035</v>
+        <v>2.73</v>
       </c>
       <c r="O11" t="n">
-        <v>2.73</v>
+        <v>1.52</v>
       </c>
       <c r="P11" t="n">
-        <v>1.52</v>
+        <v>3.57</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.57</v>
+        <v>27.88</v>
       </c>
       <c r="R11" t="n">
-        <v>27.88</v>
+        <v>341958</v>
       </c>
       <c r="S11" t="n">
-        <v>341958</v>
+        <v>-0.1354</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1354</v>
+        <v>-0.428397</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.428397</v>
+        <v>10.765717</v>
       </c>
       <c r="V11" t="n">
-        <v>10.765717</v>
+        <v>1.558597</v>
       </c>
       <c r="W11" t="n">
-        <v>10.767083</v>
+        <v>1.928912</v>
       </c>
       <c r="X11" t="n">
-        <v>1.558597</v>
+        <v>1.299314</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.928912</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.299314</v>
-      </c>
-      <c r="AA11" t="n">
         <v>-1.286607</v>
       </c>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.00132</v>
+      </c>
       <c r="AE11" t="n">
-        <v>0.5</v>
+        <v>0.00132</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.00132</v>
+        <v>-0.06</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.00132</v>
+        <v>-0.05</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AK11" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1679,78 +1611,72 @@
         <v>5.1884</v>
       </c>
       <c r="K12" t="n">
-        <v>5.1878</v>
+        <v>4999244</v>
       </c>
       <c r="L12" t="n">
-        <v>4999244</v>
+        <v>2047038</v>
       </c>
       <c r="M12" t="n">
-        <v>2047038</v>
+        <v>2952207</v>
       </c>
       <c r="N12" t="n">
-        <v>2952207</v>
+        <v>2.84</v>
       </c>
       <c r="O12" t="n">
-        <v>2.84</v>
+        <v>1.6</v>
       </c>
       <c r="P12" t="n">
-        <v>1.6</v>
+        <v>3.71</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.71</v>
+        <v>29.24</v>
       </c>
       <c r="R12" t="n">
-        <v>29.24</v>
+        <v>346403</v>
       </c>
       <c r="S12" t="n">
-        <v>346403</v>
+        <v>1.930691</v>
       </c>
       <c r="T12" t="n">
-        <v>1.930691</v>
+        <v>4.675335</v>
       </c>
       <c r="U12" t="n">
-        <v>4.675335</v>
+        <v>-0.946926</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.946926</v>
+        <v>0.677481</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.947035</v>
+        <v>-0.269467</v>
       </c>
       <c r="X12" t="n">
-        <v>0.677481</v>
+        <v>1.344714</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.269467</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.344714</v>
-      </c>
-      <c r="AA12" t="n">
         <v>1.299867</v>
       </c>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.0009210000000000001</v>
+      </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AK12" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -1786,84 +1712,78 @@
         <v>5.179</v>
       </c>
       <c r="K13" t="n">
-        <v>5.1784</v>
+        <v>5072711</v>
       </c>
       <c r="L13" t="n">
-        <v>5072711</v>
+        <v>2064183</v>
       </c>
       <c r="M13" t="n">
-        <v>2064183</v>
+        <v>3008528</v>
       </c>
       <c r="N13" t="n">
-        <v>3008528</v>
+        <v>2.9</v>
       </c>
       <c r="O13" t="n">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="P13" t="n">
-        <v>1.62</v>
+        <v>3.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.78</v>
+        <v>28.6</v>
       </c>
       <c r="R13" t="n">
-        <v>28.6</v>
+        <v>339664</v>
       </c>
       <c r="S13" t="n">
-        <v>339664</v>
+        <v>-0.32129</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.32129</v>
+        <v>0.530637</v>
       </c>
       <c r="U13" t="n">
-        <v>0.530637</v>
+        <v>-0.181173</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.181173</v>
+        <v>1.469562</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.181194</v>
+        <v>0.837552</v>
       </c>
       <c r="X13" t="n">
-        <v>1.469562</v>
+        <v>1.907759</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.837552</v>
+        <v>-1.945422</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.907759</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="AA13" t="n">
-        <v>-1.945422</v>
+        <v>8.58755</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.727061000000001</v>
+        <v>8.825751</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.58755</v>
+        <v>0.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>8.825751</v>
+        <v>0.001523</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.5</v>
+        <v>0.001523</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.001523</v>
+        <v>0.06</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.001523</v>
+        <v>0.02</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK13" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -1899,84 +1819,78 @@
         <v>5.4066</v>
       </c>
       <c r="K14" t="n">
-        <v>5.406</v>
+        <v>5164775</v>
       </c>
       <c r="L14" t="n">
-        <v>5164775</v>
+        <v>2109806</v>
       </c>
       <c r="M14" t="n">
-        <v>2109806</v>
+        <v>3054969</v>
       </c>
       <c r="N14" t="n">
-        <v>3054969</v>
+        <v>2.92</v>
       </c>
       <c r="O14" t="n">
-        <v>2.92</v>
+        <v>1.65</v>
       </c>
       <c r="P14" t="n">
-        <v>1.65</v>
+        <v>3.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.8</v>
+        <v>28.57</v>
       </c>
       <c r="R14" t="n">
-        <v>28.57</v>
+        <v>327580</v>
       </c>
       <c r="S14" t="n">
-        <v>327580</v>
+        <v>0.053914</v>
       </c>
       <c r="T14" t="n">
-        <v>0.053914</v>
+        <v>-3.179227</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.179227</v>
+        <v>4.394671</v>
       </c>
       <c r="V14" t="n">
-        <v>4.394671</v>
+        <v>1.814888</v>
       </c>
       <c r="W14" t="n">
-        <v>4.39518</v>
+        <v>2.210221</v>
       </c>
       <c r="X14" t="n">
-        <v>1.814888</v>
+        <v>1.543645</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.210221</v>
+        <v>-3.557633</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.543645</v>
+        <v>7.168596</v>
       </c>
       <c r="AA14" t="n">
-        <v>-3.557633</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.168596</v>
+        <v>7.191214</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.248760000000001</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>7.191214</v>
+        <v>0.000228</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>0.000228</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.000228</v>
+        <v>0.02</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.000228</v>
+        <v>0.03</v>
       </c>
       <c r="AH14" t="n">
         <v>0.02</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK14" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -2012,84 +1926,78 @@
         <v>5.257</v>
       </c>
       <c r="K15" t="n">
-        <v>5.2564</v>
+        <v>5215990</v>
       </c>
       <c r="L15" t="n">
-        <v>5215990</v>
+        <v>2105856</v>
       </c>
       <c r="M15" t="n">
-        <v>2105856</v>
+        <v>3110134</v>
       </c>
       <c r="N15" t="n">
-        <v>3110134</v>
+        <v>3.04</v>
       </c>
       <c r="O15" t="n">
-        <v>3.04</v>
+        <v>1.77</v>
       </c>
       <c r="P15" t="n">
-        <v>1.77</v>
+        <v>3.89</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.89</v>
+        <v>29.68</v>
       </c>
       <c r="R15" t="n">
-        <v>29.68</v>
+        <v>325546</v>
       </c>
       <c r="S15" t="n">
-        <v>325546</v>
+        <v>0.278143</v>
       </c>
       <c r="T15" t="n">
-        <v>0.278143</v>
+        <v>-1.094122</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.094122</v>
+        <v>-2.766988</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.766988</v>
+        <v>0.991621</v>
       </c>
       <c r="W15" t="n">
-        <v>-2.767296</v>
+        <v>-0.187221</v>
       </c>
       <c r="X15" t="n">
-        <v>0.991621</v>
+        <v>1.805747</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.187221</v>
+        <v>-0.6209170000000001</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.805747</v>
+        <v>6.470016</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.6209170000000001</v>
+        <v>6.517038</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.470016</v>
+        <v>6.460076</v>
       </c>
       <c r="AC15" t="n">
-        <v>6.517038</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.460076</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK15" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -2125,84 +2033,78 @@
         <v>5.2941</v>
       </c>
       <c r="K16" t="n">
-        <v>5.2935</v>
+        <v>5285657</v>
       </c>
       <c r="L16" t="n">
-        <v>5285657</v>
+        <v>2130312</v>
       </c>
       <c r="M16" t="n">
-        <v>2130312</v>
+        <v>3155345</v>
       </c>
       <c r="N16" t="n">
-        <v>3155345</v>
+        <v>3.07</v>
       </c>
       <c r="O16" t="n">
-        <v>3.07</v>
+        <v>1.81</v>
       </c>
       <c r="P16" t="n">
-        <v>1.81</v>
+        <v>3.92</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.92</v>
+        <v>30.52</v>
       </c>
       <c r="R16" t="n">
-        <v>30.52</v>
+        <v>331505</v>
       </c>
       <c r="S16" t="n">
-        <v>331505</v>
+        <v>-0.716776</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.716776</v>
+        <v>-0.930689</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.930689</v>
+        <v>0.705726</v>
       </c>
       <c r="V16" t="n">
-        <v>0.705726</v>
+        <v>1.335643</v>
       </c>
       <c r="W16" t="n">
-        <v>0.705806</v>
+        <v>1.161333</v>
       </c>
       <c r="X16" t="n">
-        <v>1.335643</v>
+        <v>1.453667</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.161333</v>
+        <v>1.830463</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.453667</v>
+        <v>5.900488</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.830463</v>
+        <v>5.899363</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.900488</v>
+        <v>5.974439</v>
       </c>
       <c r="AC16" t="n">
-        <v>5.899363</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>5.974439</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AH16" t="n">
         <v>0.03</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AK16" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2238,84 +2140,78 @@
         <v>5.2177</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2171</v>
+        <v>5366069</v>
       </c>
       <c r="L17" t="n">
-        <v>5366069</v>
+        <v>2178236</v>
       </c>
       <c r="M17" t="n">
-        <v>2178236</v>
+        <v>3187833</v>
       </c>
       <c r="N17" t="n">
-        <v>3187833</v>
+        <v>3.07</v>
       </c>
       <c r="O17" t="n">
-        <v>3.07</v>
+        <v>1.8</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8</v>
+        <v>3.94</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.94</v>
+        <v>29.64</v>
       </c>
       <c r="R17" t="n">
-        <v>29.64</v>
+        <v>324703</v>
       </c>
       <c r="S17" t="n">
-        <v>324703</v>
+        <v>-0.125523</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.125523</v>
+        <v>0.827078</v>
       </c>
       <c r="U17" t="n">
-        <v>0.827078</v>
+        <v>-1.443116</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.443116</v>
+        <v>1.521325</v>
       </c>
       <c r="W17" t="n">
-        <v>-1.443279</v>
+        <v>2.249624</v>
       </c>
       <c r="X17" t="n">
-        <v>1.521325</v>
+        <v>1.029618</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.249624</v>
+        <v>-2.051854</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.029618</v>
+        <v>5.784842</v>
       </c>
       <c r="AA17" t="n">
-        <v>-2.051854</v>
+        <v>5.458422</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.784842</v>
+        <v>5.932356</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.458422</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>5.932356</v>
+        <v>-0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AI17" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK17" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -2351,84 +2247,78 @@
         <v>5.0993</v>
       </c>
       <c r="K18" t="n">
-        <v>5.0987</v>
+        <v>5373231</v>
       </c>
       <c r="L18" t="n">
-        <v>5373231</v>
+        <v>2151399</v>
       </c>
       <c r="M18" t="n">
-        <v>2151399</v>
+        <v>3221831</v>
       </c>
       <c r="N18" t="n">
-        <v>3221831</v>
+        <v>3.24</v>
       </c>
       <c r="O18" t="n">
-        <v>3.24</v>
+        <v>1.94</v>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>4.11</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.11</v>
+        <v>30.54</v>
       </c>
       <c r="R18" t="n">
-        <v>30.54</v>
+        <v>331122</v>
       </c>
       <c r="S18" t="n">
-        <v>331122</v>
+        <v>-0.475503</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.475503</v>
+        <v>-4.872284</v>
       </c>
       <c r="U18" t="n">
-        <v>-4.872284</v>
+        <v>-2.269199</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.269199</v>
+        <v>0.133468</v>
       </c>
       <c r="W18" t="n">
-        <v>-2.26946</v>
+        <v>-1.232052</v>
       </c>
       <c r="X18" t="n">
-        <v>0.133468</v>
+        <v>1.066493</v>
       </c>
       <c r="Y18" t="n">
-        <v>-1.232052</v>
+        <v>1.976883</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.066493</v>
+        <v>5.77432</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.976883</v>
+        <v>3.79089</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.77432</v>
+        <v>5.711379</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.79089</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>5.711379</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AH18" t="n">
         <v>0.17</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AK18" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2464,84 +2354,78 @@
         <v>5.2078</v>
       </c>
       <c r="K19" t="n">
-        <v>5.2072</v>
+        <v>5370950</v>
       </c>
       <c r="L19" t="n">
-        <v>5370950</v>
+        <v>2136105</v>
       </c>
       <c r="M19" t="n">
-        <v>2136105</v>
+        <v>3234845</v>
       </c>
       <c r="N19" t="n">
-        <v>3234845</v>
+        <v>3.36</v>
       </c>
       <c r="O19" t="n">
-        <v>3.36</v>
+        <v>2.17</v>
       </c>
       <c r="P19" t="n">
-        <v>2.17</v>
+        <v>4.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.16</v>
+        <v>30.48</v>
       </c>
       <c r="R19" t="n">
-        <v>30.48</v>
+        <v>328098</v>
       </c>
       <c r="S19" t="n">
-        <v>328098</v>
+        <v>2.96673</v>
       </c>
       <c r="T19" t="n">
-        <v>2.96673</v>
+        <v>3.731301</v>
       </c>
       <c r="U19" t="n">
-        <v>3.731301</v>
+        <v>2.127743</v>
       </c>
       <c r="V19" t="n">
-        <v>2.127743</v>
+        <v>-0.042451</v>
       </c>
       <c r="W19" t="n">
-        <v>2.127993</v>
+        <v>-0.710886</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.042451</v>
+        <v>0.403932</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.710886</v>
+        <v>-0.913259</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.403932</v>
+        <v>5.596302</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.913259</v>
+        <v>1.864495</v>
       </c>
       <c r="AB19" t="n">
-        <v>5.596302</v>
+        <v>5.47065</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.864495</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>5.47065</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK19" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2577,84 +2461,78 @@
         <v>5.0804</v>
       </c>
       <c r="K20" t="n">
-        <v>5.0798</v>
+        <v>5424811</v>
       </c>
       <c r="L20" t="n">
-        <v>5424811</v>
+        <v>2154900</v>
       </c>
       <c r="M20" t="n">
-        <v>2154900</v>
+        <v>3269910</v>
       </c>
       <c r="N20" t="n">
-        <v>3269910</v>
+        <v>3.35</v>
       </c>
       <c r="O20" t="n">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>4.11</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.11</v>
+        <v>30.99</v>
       </c>
       <c r="R20" t="n">
-        <v>30.99</v>
+        <v>341158</v>
       </c>
       <c r="S20" t="n">
-        <v>341158</v>
+        <v>0.004919</v>
       </c>
       <c r="T20" t="n">
-        <v>0.004919</v>
+        <v>12.135312</v>
       </c>
       <c r="U20" t="n">
-        <v>12.135312</v>
+        <v>-2.446331</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.446331</v>
+        <v>1.002821</v>
       </c>
       <c r="W20" t="n">
-        <v>-2.446612</v>
+        <v>0.879872</v>
       </c>
       <c r="X20" t="n">
-        <v>1.002821</v>
+        <v>1.083978</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.879872</v>
+        <v>3.980518</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.083978</v>
+        <v>4.650694</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.980518</v>
+        <v>0.172427</v>
       </c>
       <c r="AB20" t="n">
-        <v>4.650694</v>
+        <v>4.361088</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.172427</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.361088</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AK20" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2690,84 +2568,78 @@
         <v>5.0007</v>
       </c>
       <c r="K21" t="n">
-        <v>5.0001</v>
+        <v>5426307</v>
       </c>
       <c r="L21" t="n">
-        <v>5426307</v>
+        <v>2145000</v>
       </c>
       <c r="M21" t="n">
-        <v>2145000</v>
+        <v>3281308</v>
       </c>
       <c r="N21" t="n">
-        <v>3281308</v>
+        <v>3.54</v>
       </c>
       <c r="O21" t="n">
-        <v>3.54</v>
+        <v>2.45</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>4.26</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.26</v>
+        <v>31.62</v>
       </c>
       <c r="R21" t="n">
-        <v>31.62</v>
+        <v>345725</v>
       </c>
       <c r="S21" t="n">
-        <v>345725</v>
+        <v>0.825329</v>
       </c>
       <c r="T21" t="n">
-        <v>0.825329</v>
+        <v>-5.946769</v>
       </c>
       <c r="U21" t="n">
-        <v>-5.946769</v>
+        <v>-1.568774</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.568774</v>
+        <v>0.027577</v>
       </c>
       <c r="W21" t="n">
-        <v>-1.568959</v>
+        <v>-0.459418</v>
       </c>
       <c r="X21" t="n">
-        <v>0.027577</v>
+        <v>0.348572</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.459418</v>
+        <v>1.338676</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.348572</v>
+        <v>4.184706</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.338676</v>
+        <v>-2.158772</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.184706</v>
+        <v>3.834324</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.158772</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.834324</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AK21" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -2803,84 +2675,78 @@
         <v>5.0959</v>
       </c>
       <c r="K22" t="n">
-        <v>5.0953</v>
+        <v>5453708</v>
       </c>
       <c r="L22" t="n">
-        <v>5453708</v>
+        <v>2145530</v>
       </c>
       <c r="M22" t="n">
-        <v>2145530</v>
+        <v>3308178</v>
       </c>
       <c r="N22" t="n">
-        <v>3308178</v>
+        <v>3.65</v>
       </c>
       <c r="O22" t="n">
-        <v>3.65</v>
+        <v>2.58</v>
       </c>
       <c r="P22" t="n">
-        <v>2.58</v>
+        <v>4.35</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.35</v>
+        <v>31.63</v>
       </c>
       <c r="R22" t="n">
-        <v>31.63</v>
+        <v>343489</v>
       </c>
       <c r="S22" t="n">
-        <v>343489</v>
+        <v>-1.448972</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.448972</v>
+        <v>-1.275652</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.275652</v>
+        <v>1.903733</v>
       </c>
       <c r="V22" t="n">
-        <v>1.903733</v>
+        <v>0.504966</v>
       </c>
       <c r="W22" t="n">
-        <v>1.903962</v>
+        <v>0.024709</v>
       </c>
       <c r="X22" t="n">
-        <v>0.504966</v>
+        <v>0.818881</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.024709</v>
+        <v>-0.646757</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.818881</v>
+        <v>3.935832</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0.646757</v>
+        <v>-4.45588</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.935832</v>
+        <v>3.741292</v>
       </c>
       <c r="AC22" t="n">
-        <v>-4.45588</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.741292</v>
+        <v>-0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0</v>
+        <v>0.11</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK22" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -2916,84 +2782,78 @@
         <v>4.8192</v>
       </c>
       <c r="K23" t="n">
-        <v>4.8186</v>
+        <v>5479459</v>
       </c>
       <c r="L23" t="n">
-        <v>5479459</v>
+        <v>2169613</v>
       </c>
       <c r="M23" t="n">
-        <v>2169613</v>
+        <v>3309846</v>
       </c>
       <c r="N23" t="n">
-        <v>3309846</v>
+        <v>3.61</v>
       </c>
       <c r="O23" t="n">
-        <v>3.61</v>
+        <v>2.63</v>
       </c>
       <c r="P23" t="n">
-        <v>2.63</v>
+        <v>4.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.25</v>
+        <v>30.85</v>
       </c>
       <c r="R23" t="n">
-        <v>30.85</v>
+        <v>343620</v>
       </c>
       <c r="S23" t="n">
-        <v>343620</v>
+        <v>-0.029659</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.029659</v>
+        <v>-0.418863</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.418863</v>
+        <v>-5.429855</v>
       </c>
       <c r="V23" t="n">
-        <v>-5.429855</v>
+        <v>0.472174</v>
       </c>
       <c r="W23" t="n">
-        <v>-5.430495</v>
+        <v>1.122473</v>
       </c>
       <c r="X23" t="n">
-        <v>0.472174</v>
+        <v>0.050421</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.122473</v>
+        <v>0.038138</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.050421</v>
+        <v>3.161501</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.038138</v>
+        <v>-6.84947</v>
       </c>
       <c r="AB23" t="n">
-        <v>3.161501</v>
+        <v>2.998957</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6.84947</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.998957</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AK23" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -3029,84 +2889,78 @@
         <v>4.7415</v>
       </c>
       <c r="K24" t="n">
-        <v>4.7409</v>
+        <v>5484871</v>
       </c>
       <c r="L24" t="n">
-        <v>5484871</v>
+        <v>2153541</v>
       </c>
       <c r="M24" t="n">
-        <v>2153541</v>
+        <v>3331330</v>
       </c>
       <c r="N24" t="n">
-        <v>3331330</v>
+        <v>3.63</v>
       </c>
       <c r="O24" t="n">
-        <v>3.63</v>
+        <v>2.73</v>
       </c>
       <c r="P24" t="n">
-        <v>2.73</v>
+        <v>4.22</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.22</v>
+        <v>30.43</v>
       </c>
       <c r="R24" t="n">
-        <v>30.43</v>
+        <v>345476</v>
       </c>
       <c r="S24" t="n">
-        <v>345476</v>
+        <v>0.495618</v>
       </c>
       <c r="T24" t="n">
-        <v>0.495618</v>
+        <v>2.992877</v>
       </c>
       <c r="U24" t="n">
-        <v>2.992877</v>
+        <v>-1.612301</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.612301</v>
+        <v>0.098769</v>
       </c>
       <c r="W24" t="n">
-        <v>-1.612502</v>
+        <v>-0.740777</v>
       </c>
       <c r="X24" t="n">
-        <v>0.098769</v>
+        <v>0.6490939999999999</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.740777</v>
+        <v>0.5401319999999999</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.6490939999999999</v>
+        <v>3.992444</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.5401319999999999</v>
+        <v>-7.713954</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.992444</v>
+        <v>3.527423</v>
       </c>
       <c r="AC24" t="n">
-        <v>-7.713954</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.527423</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK24" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3142,84 +2996,78 @@
         <v>4.9219</v>
       </c>
       <c r="K25" t="n">
-        <v>4.9213</v>
+        <v>5559063</v>
       </c>
       <c r="L25" t="n">
-        <v>5559063</v>
+        <v>2172658</v>
       </c>
       <c r="M25" t="n">
-        <v>2172658</v>
+        <v>3386405</v>
       </c>
       <c r="N25" t="n">
-        <v>3386405</v>
+        <v>3.61</v>
       </c>
       <c r="O25" t="n">
-        <v>3.61</v>
+        <v>2.82</v>
       </c>
       <c r="P25" t="n">
-        <v>2.82</v>
+        <v>4.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.12</v>
+        <v>29.92</v>
       </c>
       <c r="R25" t="n">
-        <v>29.92</v>
+        <v>344177</v>
       </c>
       <c r="S25" t="n">
-        <v>344177</v>
+        <v>-0.393045</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.393045</v>
+        <v>0.676</v>
       </c>
       <c r="U25" t="n">
-        <v>0.676</v>
+        <v>3.804703</v>
       </c>
       <c r="V25" t="n">
-        <v>3.804703</v>
+        <v>1.352666</v>
       </c>
       <c r="W25" t="n">
-        <v>3.805185</v>
+        <v>0.887701</v>
       </c>
       <c r="X25" t="n">
-        <v>1.352666</v>
+        <v>1.653244</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.887701</v>
+        <v>-0.376003</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.653244</v>
+        <v>4.608216</v>
       </c>
       <c r="AA25" t="n">
-        <v>-0.376003</v>
+        <v>-7.193509</v>
       </c>
       <c r="AB25" t="n">
-        <v>4.608216</v>
+        <v>4.057054</v>
       </c>
       <c r="AC25" t="n">
-        <v>-7.193509</v>
+        <v>-0.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.057054</v>
+        <v>-0.001599</v>
       </c>
       <c r="AE25" t="n">
-        <v>-0.5</v>
+        <v>-0.001599</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.001599</v>
+        <v>-0.02</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.001599</v>
+        <v>0.09</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AK25" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -3255,84 +3103,78 @@
         <v>5.0076</v>
       </c>
       <c r="K26" t="n">
-        <v>5.007</v>
+        <v>5625945</v>
       </c>
       <c r="L26" t="n">
-        <v>5625945</v>
+        <v>2215175</v>
       </c>
       <c r="M26" t="n">
-        <v>2215175</v>
+        <v>3410769</v>
       </c>
       <c r="N26" t="n">
-        <v>3410769</v>
+        <v>3.54</v>
       </c>
       <c r="O26" t="n">
-        <v>3.54</v>
+        <v>2.82</v>
       </c>
       <c r="P26" t="n">
-        <v>2.82</v>
+        <v>4</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>29.66</v>
       </c>
       <c r="R26" t="n">
-        <v>29.66</v>
+        <v>340324</v>
       </c>
       <c r="S26" t="n">
-        <v>340324</v>
+        <v>0.012595</v>
       </c>
       <c r="T26" t="n">
-        <v>0.012595</v>
+        <v>-4.052448</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.052448</v>
+        <v>1.741198</v>
       </c>
       <c r="V26" t="n">
-        <v>1.741198</v>
+        <v>1.203116</v>
       </c>
       <c r="W26" t="n">
-        <v>1.74141</v>
+        <v>1.956912</v>
       </c>
       <c r="X26" t="n">
-        <v>1.203116</v>
+        <v>0.719465</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.956912</v>
+        <v>-1.119482</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.719465</v>
+        <v>5.185235</v>
       </c>
       <c r="AA26" t="n">
-        <v>-1.119482</v>
+        <v>-5.956714</v>
       </c>
       <c r="AB26" t="n">
-        <v>5.185235</v>
+        <v>4.505936</v>
       </c>
       <c r="AC26" t="n">
-        <v>-5.956714</v>
+        <v>-0.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>4.505936</v>
+        <v>-0.000768</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.5</v>
+        <v>-0.000768</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.000768</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.000768</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK26" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -3368,84 +3210,78 @@
         <v>5.0575</v>
       </c>
       <c r="K27" t="n">
-        <v>5.0569</v>
+        <v>5653808</v>
       </c>
       <c r="L27" t="n">
-        <v>5653808</v>
+        <v>2204808</v>
       </c>
       <c r="M27" t="n">
-        <v>2204808</v>
+        <v>3449000</v>
       </c>
       <c r="N27" t="n">
-        <v>3449000</v>
+        <v>3.56</v>
       </c>
       <c r="O27" t="n">
-        <v>3.56</v>
+        <v>2.92</v>
       </c>
       <c r="P27" t="n">
-        <v>2.92</v>
+        <v>3.97</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.97</v>
+        <v>29.24</v>
       </c>
       <c r="R27" t="n">
-        <v>29.24</v>
+        <v>340247</v>
       </c>
       <c r="S27" t="n">
-        <v>340247</v>
+        <v>0.316333</v>
       </c>
       <c r="T27" t="n">
-        <v>0.316333</v>
+        <v>0.171808</v>
       </c>
       <c r="U27" t="n">
-        <v>0.171808</v>
+        <v>0.996485</v>
       </c>
       <c r="V27" t="n">
-        <v>0.996485</v>
+        <v>0.495259</v>
       </c>
       <c r="W27" t="n">
-        <v>0.996605</v>
+        <v>-0.467999</v>
       </c>
       <c r="X27" t="n">
-        <v>0.495259</v>
+        <v>1.120891</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.467999</v>
+        <v>-0.022625</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.120891</v>
+        <v>4.819246</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.022625</v>
+        <v>-4.560737</v>
       </c>
       <c r="AB27" t="n">
-        <v>4.819246</v>
+        <v>4.141877</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4.560737</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.141877</v>
+        <v>-0.001143</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>-0.001143</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.001143</v>
+        <v>0.02</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.001143</v>
+        <v>0.1</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK27" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3481,84 +3317,78 @@
         <v>4.9355</v>
       </c>
       <c r="K28" t="n">
-        <v>4.9349</v>
+        <v>5711103</v>
       </c>
       <c r="L28" t="n">
-        <v>5711103</v>
+        <v>2220766</v>
       </c>
       <c r="M28" t="n">
-        <v>2220766</v>
+        <v>3490337</v>
       </c>
       <c r="N28" t="n">
-        <v>3490337</v>
+        <v>3.53</v>
       </c>
       <c r="O28" t="n">
-        <v>3.53</v>
+        <v>2.99</v>
       </c>
       <c r="P28" t="n">
-        <v>2.99</v>
+        <v>3.88</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.88</v>
+        <v>29.01</v>
       </c>
       <c r="R28" t="n">
-        <v>29.01</v>
+        <v>348406</v>
       </c>
       <c r="S28" t="n">
-        <v>348406</v>
+        <v>0.734124</v>
       </c>
       <c r="T28" t="n">
-        <v>0.734124</v>
+        <v>-0.248573</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.248573</v>
+        <v>-2.412259</v>
       </c>
       <c r="V28" t="n">
-        <v>-2.412259</v>
+        <v>1.013388</v>
       </c>
       <c r="W28" t="n">
-        <v>-2.412545</v>
+        <v>0.723782</v>
       </c>
       <c r="X28" t="n">
-        <v>1.013388</v>
+        <v>1.198521</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.723782</v>
+        <v>2.397964</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.198521</v>
+        <v>4.683537</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.397964</v>
+        <v>-3.457004</v>
       </c>
       <c r="AB28" t="n">
-        <v>4.683537</v>
+        <v>3.851383</v>
       </c>
       <c r="AC28" t="n">
-        <v>-3.457004</v>
+        <v>-0.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.851383</v>
+        <v>-0.001678</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.5</v>
+        <v>-0.001678</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.001678</v>
+        <v>-0.03</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.001678</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AH28" t="n">
-        <v>-0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="AK28" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -3594,84 +3424,78 @@
         <v>4.8413</v>
       </c>
       <c r="K29" t="n">
-        <v>4.8407</v>
+        <v>5805157</v>
       </c>
       <c r="L29" t="n">
-        <v>5805157</v>
+        <v>2283485</v>
       </c>
       <c r="M29" t="n">
-        <v>2283485</v>
+        <v>3521672</v>
       </c>
       <c r="N29" t="n">
-        <v>3521672</v>
+        <v>3.29</v>
       </c>
       <c r="O29" t="n">
-        <v>3.29</v>
+        <v>2.59</v>
       </c>
       <c r="P29" t="n">
-        <v>2.59</v>
+        <v>3.75</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.75</v>
+        <v>28.14</v>
       </c>
       <c r="R29" t="n">
-        <v>28.14</v>
+        <v>355034</v>
       </c>
       <c r="S29" t="n">
-        <v>355034</v>
+        <v>1.248734</v>
       </c>
       <c r="T29" t="n">
-        <v>1.248734</v>
+        <v>0.004199</v>
       </c>
       <c r="U29" t="n">
-        <v>0.004199</v>
+        <v>-1.908621</v>
       </c>
       <c r="V29" t="n">
-        <v>-1.908621</v>
+        <v>1.646862</v>
       </c>
       <c r="W29" t="n">
-        <v>-1.908853</v>
+        <v>2.824206</v>
       </c>
       <c r="X29" t="n">
-        <v>1.646862</v>
+        <v>0.897764</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.824206</v>
+        <v>1.902378</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.897764</v>
+        <v>4.621114</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.902378</v>
+        <v>-3.178284</v>
       </c>
       <c r="AB29" t="n">
-        <v>4.621114</v>
+        <v>3.706988</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.178284</v>
+        <v>-0.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.706988</v>
+        <v>-0.001064</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.5</v>
+        <v>-0.001064</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.001064</v>
+        <v>-0.24</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.001064</v>
+        <v>-0.4</v>
       </c>
       <c r="AH29" t="n">
-        <v>-0.24</v>
+        <v>-0.13</v>
       </c>
       <c r="AI29" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="AK29" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3707,84 +3531,78 @@
         <v>4.9535</v>
       </c>
       <c r="K30" t="n">
-        <v>4.9529</v>
+        <v>5794707</v>
       </c>
       <c r="L30" t="n">
-        <v>5794707</v>
+        <v>2234362</v>
       </c>
       <c r="M30" t="n">
-        <v>2234362</v>
+        <v>3560345</v>
       </c>
       <c r="N30" t="n">
-        <v>3560345</v>
+        <v>3.38</v>
       </c>
       <c r="O30" t="n">
-        <v>3.38</v>
+        <v>2.77</v>
       </c>
       <c r="P30" t="n">
-        <v>2.77</v>
+        <v>3.76</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.76</v>
+        <v>28</v>
       </c>
       <c r="R30" t="n">
-        <v>28</v>
+        <v>355066</v>
       </c>
       <c r="S30" t="n">
-        <v>355066</v>
+        <v>-0.395831</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.395831</v>
+        <v>-2.347954</v>
       </c>
       <c r="U30" t="n">
-        <v>-2.347954</v>
+        <v>2.317559</v>
       </c>
       <c r="V30" t="n">
-        <v>2.317559</v>
+        <v>-0.180012</v>
       </c>
       <c r="W30" t="n">
-        <v>2.317847</v>
+        <v>-2.151229</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.180012</v>
+        <v>1.098143</v>
       </c>
       <c r="Y30" t="n">
-        <v>-2.151229</v>
+        <v>0.009013</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.098143</v>
+        <v>4.506637</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.009013</v>
+        <v>-3.31355</v>
       </c>
       <c r="AB30" t="n">
-        <v>4.506637</v>
+        <v>3.820543</v>
       </c>
       <c r="AC30" t="n">
-        <v>-3.31355</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.820543</v>
+        <v>-0.000798</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>-0.000798</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.000798</v>
+        <v>0.09</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.000798</v>
+        <v>0.18</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK30" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -3820,84 +3638,78 @@
         <v>4.9833</v>
       </c>
       <c r="K31" t="n">
-        <v>4.9827</v>
+        <v>5815954</v>
       </c>
       <c r="L31" t="n">
-        <v>5815954</v>
+        <v>2235302</v>
       </c>
       <c r="M31" t="n">
-        <v>2235302</v>
+        <v>3580652</v>
       </c>
       <c r="N31" t="n">
-        <v>3580652</v>
+        <v>3.38</v>
       </c>
       <c r="O31" t="n">
-        <v>3.38</v>
+        <v>2.76</v>
       </c>
       <c r="P31" t="n">
-        <v>2.76</v>
+        <v>3.76</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.76</v>
+        <v>27.85</v>
       </c>
       <c r="R31" t="n">
-        <v>27.85</v>
+        <v>352705</v>
       </c>
       <c r="S31" t="n">
-        <v>352705</v>
+        <v>0.177893</v>
       </c>
       <c r="T31" t="n">
-        <v>0.177893</v>
+        <v>2.873375</v>
       </c>
       <c r="U31" t="n">
-        <v>2.873375</v>
+        <v>0.601595</v>
       </c>
       <c r="V31" t="n">
-        <v>0.601595</v>
+        <v>0.366662</v>
       </c>
       <c r="W31" t="n">
-        <v>0.601668</v>
+        <v>0.04207</v>
       </c>
       <c r="X31" t="n">
-        <v>0.366662</v>
+        <v>0.570366</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.04207</v>
+        <v>-0.664947</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.570366</v>
+        <v>4.496274</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.664947</v>
+        <v>-3.758575</v>
       </c>
       <c r="AB31" t="n">
-        <v>4.496274</v>
+        <v>3.861754</v>
       </c>
       <c r="AC31" t="n">
-        <v>-3.758575</v>
+        <v>-0.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.861754</v>
+        <v>-0.001782</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.5</v>
+        <v>-0.001782</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.001782</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.001782</v>
+        <v>-0.01</v>
       </c>
       <c r="AH31" t="n">
         <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -3933,84 +3745,78 @@
         <v>4.9962</v>
       </c>
       <c r="K32" t="n">
-        <v>4.9956</v>
+        <v>5899742</v>
       </c>
       <c r="L32" t="n">
-        <v>5899742</v>
+        <v>2285775</v>
       </c>
       <c r="M32" t="n">
-        <v>2285775</v>
+        <v>3613967</v>
       </c>
       <c r="N32" t="n">
-        <v>3613967</v>
+        <v>3.33</v>
       </c>
       <c r="O32" t="n">
-        <v>3.33</v>
+        <v>2.71</v>
       </c>
       <c r="P32" t="n">
-        <v>2.71</v>
+        <v>3.71</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.71</v>
+        <v>28.14</v>
       </c>
       <c r="R32" t="n">
-        <v>28.14</v>
+        <v>355008</v>
       </c>
       <c r="S32" t="n">
-        <v>355008</v>
+        <v>0.014285</v>
       </c>
       <c r="T32" t="n">
-        <v>0.014285</v>
+        <v>7.262481</v>
       </c>
       <c r="U32" t="n">
-        <v>7.262481</v>
+        <v>0.258865</v>
       </c>
       <c r="V32" t="n">
-        <v>0.258865</v>
+        <v>1.440658</v>
       </c>
       <c r="W32" t="n">
-        <v>0.258896</v>
+        <v>2.257995</v>
       </c>
       <c r="X32" t="n">
-        <v>1.440658</v>
+        <v>0.930417</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.257995</v>
+        <v>0.652954</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.930417</v>
+        <v>3.925596</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.652954</v>
+        <v>-4.25878</v>
       </c>
       <c r="AB32" t="n">
-        <v>3.925596</v>
+        <v>3.397348</v>
       </c>
       <c r="AC32" t="n">
-        <v>-4.25878</v>
+        <v>-0.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.397348</v>
+        <v>-0.000537</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.5</v>
+        <v>-0.000537</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="AH32" t="n">
         <v>-0.05</v>
       </c>
       <c r="AI32" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AK32" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -4046,84 +3852,78 @@
         <v>5.1718</v>
       </c>
       <c r="K33" t="n">
-        <v>5.1712</v>
+        <v>5915538</v>
       </c>
       <c r="L33" t="n">
-        <v>5915538</v>
+        <v>2268879</v>
       </c>
       <c r="M33" t="n">
-        <v>2268879</v>
+        <v>3646659</v>
       </c>
       <c r="N33" t="n">
-        <v>3646659</v>
+        <v>3.37</v>
       </c>
       <c r="O33" t="n">
-        <v>3.37</v>
+        <v>2.76</v>
       </c>
       <c r="P33" t="n">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.75</v>
+        <v>27.86</v>
       </c>
       <c r="R33" t="n">
-        <v>27.86</v>
+        <v>351599</v>
       </c>
       <c r="S33" t="n">
-        <v>351599</v>
+        <v>-0.044032</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.044032</v>
+        <v>-0.284579</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.284579</v>
+        <v>3.514671</v>
       </c>
       <c r="V33" t="n">
-        <v>3.514671</v>
+        <v>0.267741</v>
       </c>
       <c r="W33" t="n">
-        <v>3.515093</v>
+        <v>-0.7391799999999999</v>
       </c>
       <c r="X33" t="n">
-        <v>0.267741</v>
+        <v>0.904602</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.7391799999999999</v>
+        <v>-0.96026</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.904602</v>
+        <v>3.688016</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.96026</v>
+        <v>-3.040871</v>
       </c>
       <c r="AB33" t="n">
-        <v>3.688016</v>
+        <v>3.232784</v>
       </c>
       <c r="AC33" t="n">
-        <v>-3.040871</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.232784</v>
+        <v>-0.001252</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>-0.001252</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.001252</v>
+        <v>0.04</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.001252</v>
+        <v>0.05</v>
       </c>
       <c r="AH33" t="n">
         <v>0.04</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK33" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -4159,84 +3959,78 @@
         <v>5.2416</v>
       </c>
       <c r="K34" t="n">
-        <v>5.241</v>
+        <v>5953960</v>
       </c>
       <c r="L34" t="n">
-        <v>5953960</v>
+        <v>2278309</v>
       </c>
       <c r="M34" t="n">
-        <v>2278309</v>
+        <v>3675652</v>
       </c>
       <c r="N34" t="n">
-        <v>3675652</v>
+        <v>3.43</v>
       </c>
       <c r="O34" t="n">
-        <v>3.43</v>
+        <v>2.8</v>
       </c>
       <c r="P34" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.82</v>
+        <v>27.75</v>
       </c>
       <c r="R34" t="n">
-        <v>27.75</v>
+        <v>355560</v>
       </c>
       <c r="S34" t="n">
-        <v>355560</v>
+        <v>0.9333669999999999</v>
       </c>
       <c r="T34" t="n">
-        <v>0.9333669999999999</v>
+        <v>-4.159973</v>
       </c>
       <c r="U34" t="n">
-        <v>-4.159973</v>
+        <v>1.349627</v>
       </c>
       <c r="V34" t="n">
-        <v>1.349627</v>
+        <v>0.64951</v>
       </c>
       <c r="W34" t="n">
-        <v>1.349783</v>
+        <v>0.415624</v>
       </c>
       <c r="X34" t="n">
-        <v>0.64951</v>
+        <v>0.795057</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.415624</v>
+        <v>1.126567</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.795057</v>
+        <v>3.925952</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.126567</v>
+        <v>-0.344269</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.925952</v>
+        <v>3.335647</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.344269</v>
+        <v>-0.25</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.335647</v>
+        <v>-0.000684</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.25</v>
+        <v>-0.000684</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.000684</v>
+        <v>0.06</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.000684</v>
+        <v>0.04</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK34" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -4272,84 +4066,78 @@
         <v>5.5589</v>
       </c>
       <c r="K35" t="n">
-        <v>5.5583</v>
+        <v>6041898</v>
       </c>
       <c r="L35" t="n">
-        <v>6041898</v>
+        <v>2336858</v>
       </c>
       <c r="M35" t="n">
-        <v>2336858</v>
+        <v>3705041</v>
       </c>
       <c r="N35" t="n">
-        <v>3705041</v>
+        <v>3.29</v>
       </c>
       <c r="O35" t="n">
-        <v>3.29</v>
+        <v>2.64</v>
       </c>
       <c r="P35" t="n">
-        <v>2.64</v>
+        <v>3.71</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.71</v>
+        <v>27.81</v>
       </c>
       <c r="R35" t="n">
-        <v>27.81</v>
+        <v>357827</v>
       </c>
       <c r="S35" t="n">
-        <v>357827</v>
+        <v>0.932566</v>
       </c>
       <c r="T35" t="n">
-        <v>0.932566</v>
+        <v>1.104953</v>
       </c>
       <c r="U35" t="n">
-        <v>1.104953</v>
+        <v>6.053495</v>
       </c>
       <c r="V35" t="n">
-        <v>6.053495</v>
+        <v>1.476967</v>
       </c>
       <c r="W35" t="n">
-        <v>6.054188</v>
+        <v>2.569845</v>
       </c>
       <c r="X35" t="n">
-        <v>1.476967</v>
+        <v>0.799559</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.569845</v>
+        <v>0.637586</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.799559</v>
+        <v>4.227578</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.637586</v>
+        <v>2.440035</v>
       </c>
       <c r="AB35" t="n">
-        <v>4.227578</v>
+        <v>3.697684</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.440035</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.697684</v>
+        <v>-0.000214</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>-0.000214</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.000214</v>
+        <v>-0.14</v>
       </c>
       <c r="AG35" t="n">
-        <v>-0.000214</v>
+        <v>-0.16</v>
       </c>
       <c r="AH35" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="AI35" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="AK35" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -4385,84 +4173,78 @@
         <v>5.6621</v>
       </c>
       <c r="K36" t="n">
-        <v>5.6615</v>
+        <v>6069205</v>
       </c>
       <c r="L36" t="n">
-        <v>6069205</v>
+        <v>2323362</v>
       </c>
       <c r="M36" t="n">
-        <v>2323362</v>
+        <v>3745844</v>
       </c>
       <c r="N36" t="n">
-        <v>3745844</v>
+        <v>3.3</v>
       </c>
       <c r="O36" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="P36" t="n">
-        <v>2.52</v>
+        <v>3.78</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.78</v>
+        <v>27.74</v>
       </c>
       <c r="R36" t="n">
-        <v>27.74</v>
+        <v>363282</v>
       </c>
       <c r="S36" t="n">
-        <v>363282</v>
+        <v>0.444014</v>
       </c>
       <c r="T36" t="n">
-        <v>0.444014</v>
+        <v>5.327189</v>
       </c>
       <c r="U36" t="n">
-        <v>5.327189</v>
+        <v>1.856482</v>
       </c>
       <c r="V36" t="n">
-        <v>1.856482</v>
+        <v>0.451961</v>
       </c>
       <c r="W36" t="n">
-        <v>1.856683</v>
+        <v>-0.577528</v>
       </c>
       <c r="X36" t="n">
-        <v>0.451961</v>
+        <v>1.101283</v>
       </c>
       <c r="Y36" t="n">
-        <v>-0.577528</v>
+        <v>1.52448</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.101283</v>
+        <v>4.498245</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.52448</v>
+        <v>3.812368</v>
       </c>
       <c r="AB36" t="n">
-        <v>4.498245</v>
+        <v>4.060953</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.812368</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>4.060953</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI36" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK36" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -4498,84 +4280,78 @@
         <v>5.6562</v>
       </c>
       <c r="K37" t="n">
-        <v>5.6556</v>
+        <v>6135298</v>
       </c>
       <c r="L37" t="n">
-        <v>6135298</v>
+        <v>2344397</v>
       </c>
       <c r="M37" t="n">
-        <v>2344397</v>
+        <v>3790900</v>
       </c>
       <c r="N37" t="n">
-        <v>3790900</v>
+        <v>3.33</v>
       </c>
       <c r="O37" t="n">
-        <v>3.33</v>
+        <v>2.55</v>
       </c>
       <c r="P37" t="n">
-        <v>2.55</v>
+        <v>3.82</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.82</v>
+        <v>27.59</v>
       </c>
       <c r="R37" t="n">
-        <v>27.59</v>
+        <v>369214</v>
       </c>
       <c r="S37" t="n">
-        <v>369214</v>
+        <v>0.120836</v>
       </c>
       <c r="T37" t="n">
-        <v>0.120836</v>
+        <v>-1.297169</v>
       </c>
       <c r="U37" t="n">
-        <v>-1.297169</v>
+        <v>-0.104202</v>
       </c>
       <c r="V37" t="n">
-        <v>-0.104202</v>
+        <v>1.088989</v>
       </c>
       <c r="W37" t="n">
-        <v>-0.104213</v>
+        <v>0.905369</v>
       </c>
       <c r="X37" t="n">
-        <v>1.088989</v>
+        <v>1.202826</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.905369</v>
+        <v>1.632891</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.202826</v>
+        <v>4.237599</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.632891</v>
+        <v>4.259387</v>
       </c>
       <c r="AB37" t="n">
-        <v>4.237599</v>
+        <v>3.707852</v>
       </c>
       <c r="AC37" t="n">
-        <v>4.259387</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.707852</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK37" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4611,84 +4387,78 @@
         <v>5.4481</v>
       </c>
       <c r="K38" t="n">
-        <v>5.4475</v>
+        <v>6216528</v>
       </c>
       <c r="L38" t="n">
-        <v>6216528</v>
+        <v>2384828</v>
       </c>
       <c r="M38" t="n">
-        <v>2384828</v>
+        <v>3831700</v>
       </c>
       <c r="N38" t="n">
-        <v>3831700</v>
+        <v>3.34</v>
       </c>
       <c r="O38" t="n">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="P38" t="n">
-        <v>2.56</v>
+        <v>3.83</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.83</v>
+        <v>27.49</v>
       </c>
       <c r="R38" t="n">
-        <v>27.49</v>
+        <v>372016</v>
       </c>
       <c r="S38" t="n">
-        <v>372016</v>
+        <v>0.794912</v>
       </c>
       <c r="T38" t="n">
-        <v>0.794912</v>
+        <v>-2.711204</v>
       </c>
       <c r="U38" t="n">
-        <v>-2.711204</v>
+        <v>-3.679149</v>
       </c>
       <c r="V38" t="n">
-        <v>-3.679149</v>
+        <v>1.323978</v>
       </c>
       <c r="W38" t="n">
-        <v>-3.679539</v>
+        <v>1.72458</v>
       </c>
       <c r="X38" t="n">
-        <v>1.323978</v>
+        <v>1.076262</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.72458</v>
+        <v>0.7589089999999999</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.076262</v>
+        <v>4.42474</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.7589089999999999</v>
+        <v>4.519075</v>
       </c>
       <c r="AB38" t="n">
-        <v>4.42474</v>
+        <v>4.091149</v>
       </c>
       <c r="AC38" t="n">
-        <v>4.519075</v>
+        <v>0.25</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.091149</v>
+        <v>0.000342</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.25</v>
+        <v>0.000342</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="AH38" t="n">
         <v>0.01</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK38" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -4724,84 +4494,78 @@
         <v>5.7779</v>
       </c>
       <c r="K39" t="n">
-        <v>5.7773</v>
+        <v>6275117</v>
       </c>
       <c r="L39" t="n">
-        <v>6275117</v>
+        <v>2397533</v>
       </c>
       <c r="M39" t="n">
-        <v>2397533</v>
+        <v>3877584</v>
       </c>
       <c r="N39" t="n">
-        <v>3877584</v>
+        <v>3.3</v>
       </c>
       <c r="O39" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="P39" t="n">
-        <v>2.52</v>
+        <v>3.79</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.79</v>
+        <v>27.94</v>
       </c>
       <c r="R39" t="n">
-        <v>27.94</v>
+        <v>366096</v>
       </c>
       <c r="S39" t="n">
-        <v>366096</v>
+        <v>0.185832</v>
       </c>
       <c r="T39" t="n">
-        <v>0.185832</v>
+        <v>1.966099</v>
       </c>
       <c r="U39" t="n">
-        <v>1.966099</v>
+        <v>6.053487</v>
       </c>
       <c r="V39" t="n">
-        <v>6.053487</v>
+        <v>0.9424709999999999</v>
       </c>
       <c r="W39" t="n">
-        <v>6.054153</v>
+        <v>0.532743</v>
       </c>
       <c r="X39" t="n">
-        <v>0.9424709999999999</v>
+        <v>1.197484</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.532743</v>
+        <v>-1.591329</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.197484</v>
+        <v>4.758099</v>
       </c>
       <c r="AA39" t="n">
-        <v>-1.591329</v>
+        <v>5.579866</v>
       </c>
       <c r="AB39" t="n">
-        <v>4.758099</v>
+        <v>4.600584</v>
       </c>
       <c r="AC39" t="n">
-        <v>5.579866</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>4.600584</v>
+        <v>0.000556</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>0.000556</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="AH39" t="n">
         <v>-0.04</v>
       </c>
       <c r="AI39" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AK39" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -4837,84 +4601,78 @@
         <v>6.0535</v>
       </c>
       <c r="K40" t="n">
-        <v>6.0529</v>
+        <v>6365690</v>
       </c>
       <c r="L40" t="n">
-        <v>6365690</v>
+        <v>2436022</v>
       </c>
       <c r="M40" t="n">
-        <v>2436022</v>
+        <v>3929668</v>
       </c>
       <c r="N40" t="n">
-        <v>3929668</v>
+        <v>3.27</v>
       </c>
       <c r="O40" t="n">
-        <v>3.27</v>
+        <v>2.5</v>
       </c>
       <c r="P40" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.75</v>
+        <v>28.45</v>
       </c>
       <c r="R40" t="n">
-        <v>28.45</v>
+        <v>363003</v>
       </c>
       <c r="S40" t="n">
-        <v>363003</v>
+        <v>-0.224963</v>
       </c>
       <c r="T40" t="n">
-        <v>-0.224963</v>
+        <v>-3.383039</v>
       </c>
       <c r="U40" t="n">
-        <v>-3.383039</v>
+        <v>4.769899</v>
       </c>
       <c r="V40" t="n">
-        <v>4.769899</v>
+        <v>1.443368</v>
       </c>
       <c r="W40" t="n">
-        <v>4.770394</v>
+        <v>1.605359</v>
       </c>
       <c r="X40" t="n">
-        <v>1.443368</v>
+        <v>1.343208</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.605359</v>
+        <v>-0.8448600000000001</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.343208</v>
+        <v>4.873011</v>
       </c>
       <c r="AA40" t="n">
-        <v>-0.8448600000000001</v>
+        <v>6.325086</v>
       </c>
       <c r="AB40" t="n">
-        <v>4.873011</v>
+        <v>4.840925</v>
       </c>
       <c r="AC40" t="n">
-        <v>6.325086</v>
+        <v>0.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.840925</v>
+        <v>0.001412</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.5</v>
+        <v>0.001412</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.001412</v>
+        <v>-0.03</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.001412</v>
+        <v>-0.02</v>
       </c>
       <c r="AH40" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="AI40" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AK40" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4950,84 +4708,78 @@
         <v>6.1923</v>
       </c>
       <c r="K41" t="n">
-        <v>6.1917</v>
+        <v>6464602</v>
       </c>
       <c r="L41" t="n">
-        <v>6464602</v>
+        <v>2499177</v>
       </c>
       <c r="M41" t="n">
-        <v>2499177</v>
+        <v>3965425</v>
       </c>
       <c r="N41" t="n">
-        <v>3965425</v>
+        <v>3.08</v>
       </c>
       <c r="O41" t="n">
-        <v>3.08</v>
+        <v>2.21</v>
       </c>
       <c r="P41" t="n">
-        <v>2.21</v>
+        <v>3.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.63</v>
+        <v>28.5</v>
       </c>
       <c r="R41" t="n">
-        <v>28.5</v>
+        <v>329730</v>
       </c>
       <c r="S41" t="n">
-        <v>329730</v>
+        <v>-0.584226</v>
       </c>
       <c r="T41" t="n">
-        <v>-0.584226</v>
+        <v>-1.265086</v>
       </c>
       <c r="U41" t="n">
-        <v>-1.265086</v>
+        <v>2.292888</v>
       </c>
       <c r="V41" t="n">
-        <v>2.292888</v>
+        <v>1.55383</v>
       </c>
       <c r="W41" t="n">
-        <v>2.293116</v>
+        <v>2.592546</v>
       </c>
       <c r="X41" t="n">
-        <v>1.55383</v>
+        <v>0.909924</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.592546</v>
+        <v>-9.166040000000001</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.909924</v>
+        <v>4.831296</v>
       </c>
       <c r="AA41" t="n">
-        <v>-9.166040000000001</v>
+        <v>6.536174</v>
       </c>
       <c r="AB41" t="n">
-        <v>4.831296</v>
+        <v>4.767938</v>
       </c>
       <c r="AC41" t="n">
-        <v>6.536174</v>
+        <v>1</v>
       </c>
       <c r="AD41" t="n">
-        <v>4.767938</v>
+        <v>0.002578</v>
       </c>
       <c r="AE41" t="n">
-        <v>1</v>
+        <v>0.002578</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.002578</v>
+        <v>-0.19</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.002578</v>
+        <v>-0.29</v>
       </c>
       <c r="AH41" t="n">
-        <v>-0.19</v>
+        <v>-0.12</v>
       </c>
       <c r="AI41" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK41" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -5063,84 +4815,78 @@
         <v>5.8301</v>
       </c>
       <c r="K42" t="n">
-        <v>5.8295</v>
+        <v>6465016</v>
       </c>
       <c r="L42" t="n">
-        <v>6465016</v>
+        <v>2451957</v>
       </c>
       <c r="M42" t="n">
-        <v>2451957</v>
+        <v>4013059</v>
       </c>
       <c r="N42" t="n">
-        <v>4013059</v>
+        <v>3.34</v>
       </c>
       <c r="O42" t="n">
-        <v>3.34</v>
+        <v>2.43</v>
       </c>
       <c r="P42" t="n">
-        <v>2.43</v>
+        <v>3.89</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.89</v>
+        <v>29.88</v>
       </c>
       <c r="R42" t="n">
-        <v>29.88</v>
+        <v>328303</v>
       </c>
       <c r="S42" t="n">
-        <v>328303</v>
+        <v>0.675346</v>
       </c>
       <c r="T42" t="n">
-        <v>0.675346</v>
+        <v>-1.465146</v>
       </c>
       <c r="U42" t="n">
-        <v>-1.465146</v>
+        <v>-5.8492</v>
       </c>
       <c r="V42" t="n">
-        <v>-5.8492</v>
+        <v>0.006404</v>
       </c>
       <c r="W42" t="n">
-        <v>-5.849767</v>
+        <v>-1.889422</v>
       </c>
       <c r="X42" t="n">
-        <v>0.006404</v>
+        <v>1.201233</v>
       </c>
       <c r="Y42" t="n">
-        <v>-1.889422</v>
+        <v>-0.432778</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.201233</v>
+        <v>4.559874</v>
       </c>
       <c r="AA42" t="n">
-        <v>-0.432778</v>
+        <v>6.749097</v>
       </c>
       <c r="AB42" t="n">
-        <v>4.559874</v>
+        <v>4.174145</v>
       </c>
       <c r="AC42" t="n">
-        <v>6.749097</v>
+        <v>1</v>
       </c>
       <c r="AD42" t="n">
-        <v>4.174145</v>
+        <v>0.001675</v>
       </c>
       <c r="AE42" t="n">
-        <v>1</v>
+        <v>0.001675</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.001675</v>
+        <v>0.26</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.001675</v>
+        <v>0.22</v>
       </c>
       <c r="AH42" t="n">
         <v>0.26</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK42" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -5176,84 +4922,78 @@
         <v>5.8488</v>
       </c>
       <c r="K43" t="n">
-        <v>5.8482</v>
+        <v>6511444</v>
       </c>
       <c r="L43" t="n">
-        <v>6511444</v>
+        <v>2477151</v>
       </c>
       <c r="M43" t="n">
-        <v>2477151</v>
+        <v>4034293</v>
       </c>
       <c r="N43" t="n">
-        <v>4034293</v>
+        <v>3.41</v>
       </c>
       <c r="O43" t="n">
-        <v>3.41</v>
+        <v>2.52</v>
       </c>
       <c r="P43" t="n">
-        <v>2.52</v>
+        <v>3.96</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.96</v>
+        <v>30.53</v>
       </c>
       <c r="R43" t="n">
-        <v>30.53</v>
+        <v>332508</v>
       </c>
       <c r="S43" t="n">
-        <v>332508</v>
+        <v>0.485516</v>
       </c>
       <c r="T43" t="n">
-        <v>0.485516</v>
+        <v>4.088981</v>
       </c>
       <c r="U43" t="n">
-        <v>4.088981</v>
+        <v>0.320749</v>
       </c>
       <c r="V43" t="n">
-        <v>0.320749</v>
+        <v>0.7181419999999999</v>
       </c>
       <c r="W43" t="n">
-        <v>0.320782</v>
+        <v>1.027506</v>
       </c>
       <c r="X43" t="n">
-        <v>0.7181419999999999</v>
+        <v>0.529123</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.027506</v>
+        <v>1.280829</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.529123</v>
+        <v>5.05763</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.280829</v>
+        <v>8.444549</v>
       </c>
       <c r="AB43" t="n">
-        <v>5.05763</v>
+        <v>4.866504</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.444549</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>4.866504</v>
+        <v>0.003204</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>0.003204</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.003204</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.003204</v>
+        <v>0.09</v>
       </c>
       <c r="AH43" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK43" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -5289,84 +5029,78 @@
         <v>5.7422</v>
       </c>
       <c r="K44" t="n">
-        <v>5.7416</v>
+        <v>6576464</v>
       </c>
       <c r="L44" t="n">
-        <v>6576464</v>
+        <v>2498262</v>
       </c>
       <c r="M44" t="n">
-        <v>2498262</v>
+        <v>4078202</v>
       </c>
       <c r="N44" t="n">
-        <v>4078202</v>
+        <v>3.44</v>
       </c>
       <c r="O44" t="n">
-        <v>3.44</v>
+        <v>2.49</v>
       </c>
       <c r="P44" t="n">
-        <v>2.49</v>
+        <v>4.03</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.03</v>
+        <v>31.34</v>
       </c>
       <c r="R44" t="n">
-        <v>31.34</v>
+        <v>336157</v>
       </c>
       <c r="S44" t="n">
-        <v>336157</v>
+        <v>1.30069</v>
       </c>
       <c r="T44" t="n">
-        <v>1.30069</v>
+        <v>6.734953</v>
       </c>
       <c r="U44" t="n">
-        <v>6.734953</v>
+        <v>-1.822596</v>
       </c>
       <c r="V44" t="n">
-        <v>-1.822596</v>
+        <v>0.99855</v>
       </c>
       <c r="W44" t="n">
-        <v>-1.822783</v>
+        <v>0.852229</v>
       </c>
       <c r="X44" t="n">
-        <v>0.99855</v>
+        <v>1.088394</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.852229</v>
+        <v>1.097417</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.088394</v>
+        <v>5.47719</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.097417</v>
+        <v>8.586193</v>
       </c>
       <c r="AB44" t="n">
-        <v>5.47719</v>
+        <v>5.201441</v>
       </c>
       <c r="AC44" t="n">
-        <v>8.586193</v>
+        <v>1</v>
       </c>
       <c r="AD44" t="n">
-        <v>5.201441</v>
+        <v>0.001471</v>
       </c>
       <c r="AE44" t="n">
-        <v>1</v>
+        <v>0.001471</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.001471</v>
+        <v>0.03</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.001471</v>
+        <v>-0.03</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI44" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK44" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -5402,84 +5136,78 @@
         <v>5.6608</v>
       </c>
       <c r="K45" t="n">
-        <v>5.6602</v>
+        <v>6623948</v>
       </c>
       <c r="L45" t="n">
-        <v>6623948</v>
+        <v>2512426</v>
       </c>
       <c r="M45" t="n">
-        <v>2512426</v>
+        <v>4111522</v>
       </c>
       <c r="N45" t="n">
-        <v>4111522</v>
+        <v>3.67</v>
       </c>
       <c r="O45" t="n">
-        <v>3.67</v>
+        <v>2.72</v>
       </c>
       <c r="P45" t="n">
-        <v>2.72</v>
+        <v>4.25</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.25</v>
+        <v>31.63</v>
       </c>
       <c r="R45" t="n">
-        <v>31.63</v>
+        <v>340789</v>
       </c>
       <c r="S45" t="n">
-        <v>340789</v>
+        <v>-0.459145</v>
       </c>
       <c r="T45" t="n">
-        <v>-0.459145</v>
+        <v>-1.250256</v>
       </c>
       <c r="U45" t="n">
-        <v>-1.250256</v>
+        <v>-1.417575</v>
       </c>
       <c r="V45" t="n">
-        <v>-1.417575</v>
+        <v>0.722029</v>
       </c>
       <c r="W45" t="n">
-        <v>-1.417723</v>
+        <v>0.566954</v>
       </c>
       <c r="X45" t="n">
-        <v>0.722029</v>
+        <v>0.8170269999999999</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.566954</v>
+        <v>1.377928</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.8170269999999999</v>
+        <v>5.529729</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.377928</v>
+        <v>8.510418</v>
       </c>
       <c r="AB45" t="n">
-        <v>5.529729</v>
+        <v>5.316736</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.510418</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>5.316736</v>
+        <v>0.002023</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>0.002023</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AK45" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -5515,84 +5243,78 @@
         <v>5.7087</v>
       </c>
       <c r="K46" t="n">
-        <v>5.7081</v>
+        <v>6666287</v>
       </c>
       <c r="L46" t="n">
-        <v>6666287</v>
+        <v>2532708</v>
       </c>
       <c r="M46" t="n">
-        <v>2532708</v>
+        <v>4133579</v>
       </c>
       <c r="N46" t="n">
-        <v>4133579</v>
+        <v>3.72</v>
       </c>
       <c r="O46" t="n">
-        <v>3.72</v>
+        <v>2.67</v>
       </c>
       <c r="P46" t="n">
-        <v>2.67</v>
+        <v>4.36</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.36</v>
+        <v>31.7</v>
       </c>
       <c r="R46" t="n">
-        <v>31.7</v>
+        <v>341459</v>
       </c>
       <c r="S46" t="n">
-        <v>341459</v>
+        <v>-0.58566</v>
       </c>
       <c r="T46" t="n">
-        <v>-0.58566</v>
+        <v>-3.586372</v>
       </c>
       <c r="U46" t="n">
-        <v>-3.586372</v>
+        <v>0.84617</v>
       </c>
       <c r="V46" t="n">
-        <v>0.84617</v>
+        <v>0.639181</v>
       </c>
       <c r="W46" t="n">
-        <v>0.84626</v>
+        <v>0.807268</v>
       </c>
       <c r="X46" t="n">
-        <v>0.639181</v>
+        <v>0.5364679999999999</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.807268</v>
+        <v>0.196603</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.5364679999999999</v>
+        <v>5.319636</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.196603</v>
+        <v>7.026183</v>
       </c>
       <c r="AB46" t="n">
-        <v>5.319636</v>
+        <v>5.201418</v>
       </c>
       <c r="AC46" t="n">
-        <v>7.026183</v>
+        <v>0.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>5.201418</v>
+        <v>0.001405</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.5</v>
+        <v>0.001405</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.001405</v>
+        <v>0.05</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.001405</v>
+        <v>-0.05</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="AI46" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK46" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5628,84 +5350,78 @@
         <v>5.4571</v>
       </c>
       <c r="K47" t="n">
-        <v>5.4565</v>
+        <v>6703663</v>
       </c>
       <c r="L47" t="n">
-        <v>6703663</v>
+        <v>2547693</v>
       </c>
       <c r="M47" t="n">
-        <v>2547693</v>
+        <v>4155970</v>
       </c>
       <c r="N47" t="n">
-        <v>4155970</v>
+        <v>3.75</v>
       </c>
       <c r="O47" t="n">
-        <v>3.75</v>
+        <v>2.67</v>
       </c>
       <c r="P47" t="n">
-        <v>2.67</v>
+        <v>4.41</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.41</v>
+        <v>31.85</v>
       </c>
       <c r="R47" t="n">
-        <v>31.85</v>
+        <v>344440</v>
       </c>
       <c r="S47" t="n">
-        <v>344440</v>
+        <v>-0.075712</v>
       </c>
       <c r="T47" t="n">
-        <v>-0.075712</v>
+        <v>-1.100666</v>
       </c>
       <c r="U47" t="n">
-        <v>-1.100666</v>
+        <v>-4.407308</v>
       </c>
       <c r="V47" t="n">
-        <v>-4.407308</v>
+        <v>0.5606719999999999</v>
       </c>
       <c r="W47" t="n">
-        <v>-4.407771</v>
+        <v>0.591659</v>
       </c>
       <c r="X47" t="n">
-        <v>0.5606719999999999</v>
+        <v>0.541686</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.591659</v>
+        <v>0.873018</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.541686</v>
+        <v>5.351165</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.873018</v>
+        <v>4.393261</v>
       </c>
       <c r="AB47" t="n">
-        <v>5.351165</v>
+        <v>5.18043</v>
       </c>
       <c r="AC47" t="n">
-        <v>4.393261</v>
+        <v>0.25</v>
       </c>
       <c r="AD47" t="n">
-        <v>5.18043</v>
+        <v>0.000633</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.25</v>
+        <v>0.000633</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.000633</v>
+        <v>0.03</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.000633</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK47" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5741,84 +5457,78 @@
         <v>5.6021</v>
       </c>
       <c r="K48" t="n">
-        <v>5.6015</v>
+        <v>6733209</v>
       </c>
       <c r="L48" t="n">
-        <v>6733209</v>
+        <v>2544400</v>
       </c>
       <c r="M48" t="n">
-        <v>2544400</v>
+        <v>4188808</v>
       </c>
       <c r="N48" t="n">
-        <v>4188808</v>
+        <v>3.96</v>
       </c>
       <c r="O48" t="n">
-        <v>3.96</v>
+        <v>2.79</v>
       </c>
       <c r="P48" t="n">
-        <v>2.79</v>
+        <v>4.66</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.66</v>
+        <v>31.75</v>
       </c>
       <c r="R48" t="n">
-        <v>31.75</v>
+        <v>345111</v>
       </c>
       <c r="S48" t="n">
-        <v>345111</v>
+        <v>-0.280386</v>
       </c>
       <c r="T48" t="n">
-        <v>-0.280386</v>
+        <v>5.352993</v>
       </c>
       <c r="U48" t="n">
-        <v>5.352993</v>
+        <v>2.657089</v>
       </c>
       <c r="V48" t="n">
-        <v>2.657089</v>
+        <v>0.440744</v>
       </c>
       <c r="W48" t="n">
-        <v>2.657381</v>
+        <v>-0.129254</v>
       </c>
       <c r="X48" t="n">
-        <v>0.440744</v>
+        <v>0.79014</v>
       </c>
       <c r="Y48" t="n">
-        <v>-0.129254</v>
+        <v>0.194809</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.79014</v>
+        <v>5.225222</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.194809</v>
+        <v>2.961368</v>
       </c>
       <c r="AB48" t="n">
-        <v>5.225222</v>
+        <v>5.127976</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.961368</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>5.127976</v>
+        <v>0.000562</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>0.000562</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.000562</v>
+        <v>0.21</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.000562</v>
+        <v>0.12</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="AI48" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK48" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -5854,84 +5564,78 @@
         <v>5.4264</v>
       </c>
       <c r="K49" t="n">
-        <v>5.4258</v>
+        <v>6774436</v>
       </c>
       <c r="L49" t="n">
-        <v>6774436</v>
+        <v>2546265</v>
       </c>
       <c r="M49" t="n">
-        <v>2546265</v>
+        <v>4228171</v>
       </c>
       <c r="N49" t="n">
-        <v>4228171</v>
+        <v>4.14</v>
       </c>
       <c r="O49" t="n">
-        <v>4.14</v>
+        <v>2.85</v>
       </c>
       <c r="P49" t="n">
-        <v>2.85</v>
+        <v>4.92</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.92</v>
+        <v>31.87</v>
       </c>
       <c r="R49" t="n">
-        <v>31.87</v>
+        <v>350767</v>
       </c>
       <c r="S49" t="n">
-        <v>350767</v>
+        <v>0.304372</v>
       </c>
       <c r="T49" t="n">
-        <v>0.304372</v>
+        <v>-2.412481</v>
       </c>
       <c r="U49" t="n">
-        <v>-2.412481</v>
+        <v>-3.136324</v>
       </c>
       <c r="V49" t="n">
-        <v>-3.136324</v>
+        <v>0.612293</v>
       </c>
       <c r="W49" t="n">
-        <v>-3.13666</v>
+        <v>0.073298</v>
       </c>
       <c r="X49" t="n">
-        <v>0.612293</v>
+        <v>0.9397180000000001</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.073298</v>
+        <v>1.638893</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.9397180000000001</v>
+        <v>5.130501</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.638893</v>
+        <v>3.033233</v>
       </c>
       <c r="AB49" t="n">
-        <v>5.130501</v>
+        <v>5.054283</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.033233</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>5.054283</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK49" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5967,84 +5671,78 @@
         <v>5.3186</v>
       </c>
       <c r="K50" t="n">
-        <v>5.318</v>
+        <v>6852705</v>
       </c>
       <c r="L50" t="n">
-        <v>6852705</v>
+        <v>2589817</v>
       </c>
       <c r="M50" t="n">
-        <v>2589817</v>
+        <v>4262888</v>
       </c>
       <c r="N50" t="n">
-        <v>4262888</v>
+        <v>4.09</v>
       </c>
       <c r="O50" t="n">
-        <v>4.09</v>
+        <v>2.77</v>
       </c>
       <c r="P50" t="n">
-        <v>2.77</v>
+        <v>4.89</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.89</v>
+        <v>31.47</v>
       </c>
       <c r="R50" t="n">
-        <v>31.47</v>
+        <v>356582</v>
       </c>
       <c r="S50" t="n">
-        <v>356582</v>
+        <v>-0.085869</v>
       </c>
       <c r="T50" t="n">
-        <v>-0.085869</v>
+        <v>-0.812453</v>
       </c>
       <c r="U50" t="n">
-        <v>-0.812453</v>
+        <v>-1.986584</v>
       </c>
       <c r="V50" t="n">
-        <v>-1.986584</v>
+        <v>1.155358</v>
       </c>
       <c r="W50" t="n">
-        <v>-1.986804</v>
+        <v>1.710427</v>
       </c>
       <c r="X50" t="n">
-        <v>1.155358</v>
+        <v>0.821088</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.710427</v>
+        <v>1.657796</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.821088</v>
+        <v>5.172369</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.657796</v>
+        <v>2.828436</v>
       </c>
       <c r="AB50" t="n">
-        <v>5.172369</v>
+        <v>5.096104</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.828436</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>5.096104</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="AH50" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="AI50" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK50" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -6080,84 +5778,78 @@
         <v>5.3843</v>
       </c>
       <c r="K51" t="n">
-        <v>5.3837</v>
+        <v>6923886</v>
       </c>
       <c r="L51" t="n">
-        <v>6923886</v>
+        <v>2597630</v>
       </c>
       <c r="M51" t="n">
-        <v>2597630</v>
+        <v>4326256</v>
       </c>
       <c r="N51" t="n">
-        <v>4326256</v>
+        <v>4.18</v>
       </c>
       <c r="O51" t="n">
-        <v>4.18</v>
+        <v>2.82</v>
       </c>
       <c r="P51" t="n">
-        <v>2.82</v>
+        <v>4.99</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.99</v>
+        <v>32.04</v>
       </c>
       <c r="R51" t="n">
-        <v>32.04</v>
+        <v>357103</v>
       </c>
       <c r="S51" t="n">
-        <v>357103</v>
+        <v>0.016352</v>
       </c>
       <c r="T51" t="n">
-        <v>0.016352</v>
+        <v>0.541697</v>
       </c>
       <c r="U51" t="n">
-        <v>0.541697</v>
+        <v>1.235287</v>
       </c>
       <c r="V51" t="n">
-        <v>1.235287</v>
+        <v>1.038729</v>
       </c>
       <c r="W51" t="n">
-        <v>1.235427</v>
+        <v>0.301682</v>
       </c>
       <c r="X51" t="n">
-        <v>1.038729</v>
+        <v>1.486504</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.301682</v>
+        <v>0.146109</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.486504</v>
+        <v>4.680811</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.146109</v>
+        <v>0.924206</v>
       </c>
       <c r="AB51" t="n">
-        <v>4.680811</v>
+        <v>4.490243</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.924206</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>4.490243</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK51" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -6193,84 +5885,78 @@
         <v>5.3338</v>
       </c>
       <c r="K52" t="n">
-        <v>5.3332</v>
+        <v>7004223</v>
       </c>
       <c r="L52" t="n">
-        <v>7004223</v>
+        <v>2616902</v>
       </c>
       <c r="M52" t="n">
-        <v>2616902</v>
+        <v>4387321</v>
       </c>
       <c r="N52" t="n">
-        <v>4387321</v>
+        <v>4.24</v>
       </c>
       <c r="O52" t="n">
-        <v>4.24</v>
+        <v>2.75</v>
       </c>
       <c r="P52" t="n">
-        <v>2.75</v>
+        <v>5.12</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.12</v>
+        <v>32.2</v>
       </c>
       <c r="R52" t="n">
-        <v>32.2</v>
+        <v>360578</v>
       </c>
       <c r="S52" t="n">
-        <v>360578</v>
+        <v>0.456805</v>
       </c>
       <c r="T52" t="n">
-        <v>0.456805</v>
+        <v>-3.159521</v>
       </c>
       <c r="U52" t="n">
-        <v>-3.159521</v>
+        <v>-0.937912</v>
       </c>
       <c r="V52" t="n">
-        <v>-0.937912</v>
+        <v>1.160288</v>
       </c>
       <c r="W52" t="n">
-        <v>-0.938017</v>
+        <v>0.741907</v>
       </c>
       <c r="X52" t="n">
-        <v>1.160288</v>
+        <v>1.411498</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.741907</v>
+        <v>0.973109</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.411498</v>
+        <v>4.461836</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.973109</v>
+        <v>-0.101973</v>
       </c>
       <c r="AB52" t="n">
-        <v>4.461836</v>
+        <v>4.177803</v>
       </c>
       <c r="AC52" t="n">
-        <v>-0.101973</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>4.177803</v>
+        <v>-0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF52" t="n">
-        <v>-0</v>
+        <v>0.06</v>
       </c>
       <c r="AG52" t="n">
-        <v>-0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AH52" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="AI52" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AK52" t="n">
         <v>0.16</v>
       </c>
     </row>
@@ -6306,84 +5992,78 @@
         <v>5.5024</v>
       </c>
       <c r="K53" t="n">
-        <v>5.5018</v>
+        <v>7137252</v>
       </c>
       <c r="L53" t="n">
-        <v>7137252</v>
+        <v>2701735</v>
       </c>
       <c r="M53" t="n">
-        <v>2701735</v>
+        <v>4435517</v>
       </c>
       <c r="N53" t="n">
-        <v>4435517</v>
+        <v>4.2</v>
       </c>
       <c r="O53" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="P53" t="n">
-        <v>2.7</v>
+        <v>5.12</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.12</v>
+        <v>31.87</v>
       </c>
       <c r="R53" t="n">
-        <v>31.87</v>
+        <v>358234</v>
       </c>
       <c r="S53" t="n">
-        <v>358234</v>
+        <v>0.185583</v>
       </c>
       <c r="T53" t="n">
-        <v>0.185583</v>
+        <v>0.549021</v>
       </c>
       <c r="U53" t="n">
-        <v>0.549021</v>
+        <v>3.160973</v>
       </c>
       <c r="V53" t="n">
-        <v>3.160973</v>
+        <v>1.899268</v>
       </c>
       <c r="W53" t="n">
-        <v>3.161329</v>
+        <v>3.241734</v>
       </c>
       <c r="X53" t="n">
-        <v>1.899268</v>
+        <v>1.098529</v>
       </c>
       <c r="Y53" t="n">
-        <v>3.241734</v>
+        <v>-0.650067</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.098529</v>
+        <v>4.264385</v>
       </c>
       <c r="AA53" t="n">
-        <v>-0.650067</v>
+        <v>-1.042167</v>
       </c>
       <c r="AB53" t="n">
-        <v>4.264385</v>
+        <v>3.897866</v>
       </c>
       <c r="AC53" t="n">
-        <v>-1.042167</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>3.897866</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AH53" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -6419,84 +6099,78 @@
         <v>5.2301</v>
       </c>
       <c r="K54" t="n">
-        <v>5.2295</v>
+        <v>7130762</v>
       </c>
       <c r="L54" t="n">
-        <v>7130762</v>
+        <v>2654220</v>
       </c>
       <c r="M54" t="n">
-        <v>2654220</v>
+        <v>4476542</v>
       </c>
       <c r="N54" t="n">
-        <v>4476542</v>
+        <v>4.44</v>
       </c>
       <c r="O54" t="n">
-        <v>4.44</v>
+        <v>2.87</v>
       </c>
       <c r="P54" t="n">
-        <v>2.87</v>
+        <v>5.38</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.38</v>
+        <v>32.45</v>
       </c>
       <c r="R54" t="n">
-        <v>32.45</v>
+        <v>364367</v>
       </c>
       <c r="S54" t="n">
-        <v>364367</v>
+        <v>0.54555</v>
       </c>
       <c r="T54" t="n">
-        <v>0.54555</v>
+        <v>-3.178231</v>
       </c>
       <c r="U54" t="n">
-        <v>-3.178231</v>
+        <v>-4.94875</v>
       </c>
       <c r="V54" t="n">
-        <v>-4.94875</v>
+        <v>-0.090931</v>
       </c>
       <c r="W54" t="n">
-        <v>-4.949289</v>
+        <v>-1.758685</v>
       </c>
       <c r="X54" t="n">
-        <v>-0.090931</v>
+        <v>0.92492</v>
       </c>
       <c r="Y54" t="n">
-        <v>-1.758685</v>
+        <v>1.712009</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.92492</v>
+        <v>4.441351</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.712009</v>
+        <v>-0.903999</v>
       </c>
       <c r="AB54" t="n">
-        <v>4.441351</v>
+        <v>4.303068</v>
       </c>
       <c r="AC54" t="n">
-        <v>-0.903999</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>4.303068</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
         <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AH54" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="AI54" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK54" t="n">
         <v>0.58</v>
       </c>
     </row>
@@ -6532,84 +6206,78 @@
         <v>5.1495</v>
       </c>
       <c r="K55" t="n">
-        <v>5.1489</v>
+        <v>7157783</v>
       </c>
       <c r="L55" t="n">
-        <v>7157783</v>
+        <v>2656484</v>
       </c>
       <c r="M55" t="n">
-        <v>2656484</v>
+        <v>4501299</v>
       </c>
       <c r="N55" t="n">
-        <v>4501299</v>
+        <v>4.64</v>
       </c>
       <c r="O55" t="n">
-        <v>4.64</v>
+        <v>3.07</v>
       </c>
       <c r="P55" t="n">
-        <v>3.07</v>
+        <v>5.56</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.56</v>
+        <v>32.63</v>
       </c>
       <c r="R55" t="n">
-        <v>32.63</v>
+        <v>371074</v>
       </c>
       <c r="S55" t="n">
-        <v>371074</v>
+        <v>0.6239710000000001</v>
       </c>
       <c r="T55" t="n">
-        <v>0.6239710000000001</v>
+        <v>2.874551</v>
       </c>
       <c r="U55" t="n">
-        <v>2.874551</v>
+        <v>-1.54108</v>
       </c>
       <c r="V55" t="n">
-        <v>-1.54108</v>
+        <v>0.378936</v>
       </c>
       <c r="W55" t="n">
-        <v>-1.541256</v>
+        <v>0.085298</v>
       </c>
       <c r="X55" t="n">
-        <v>0.378936</v>
+        <v>0.553038</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.085298</v>
+        <v>1.840727</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.553038</v>
+        <v>3.812497</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.840727</v>
+        <v>-2.659212</v>
       </c>
       <c r="AB55" t="n">
-        <v>3.812497</v>
+        <v>3.357475</v>
       </c>
       <c r="AC55" t="n">
-        <v>-2.659212</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.357475</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
         <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AH55" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AI55" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AK55" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -6645,84 +6313,78 @@
         <v>5.2194</v>
       </c>
       <c r="K56" t="n">
-        <v>5.2188</v>
+        <v>7240557</v>
       </c>
       <c r="L56" t="n">
-        <v>7240557</v>
+        <v>2687535</v>
       </c>
       <c r="M56" t="n">
-        <v>2687535</v>
+        <v>4553022</v>
       </c>
       <c r="N56" t="n">
-        <v>4553022</v>
+        <v>4.52</v>
       </c>
       <c r="O56" t="n">
-        <v>4.52</v>
+        <v>3.06</v>
       </c>
       <c r="P56" t="n">
-        <v>3.06</v>
+        <v>5.39</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.39</v>
+        <v>32.84</v>
       </c>
       <c r="R56" t="n">
-        <v>32.84</v>
+        <v>362002</v>
       </c>
       <c r="S56" t="n">
-        <v>362002</v>
+        <v>-0.13412</v>
       </c>
       <c r="T56" t="n">
-        <v>-0.13412</v>
+        <v>10.543613</v>
       </c>
       <c r="U56" t="n">
-        <v>10.543613</v>
+        <v>1.357413</v>
       </c>
       <c r="V56" t="n">
-        <v>1.357413</v>
+        <v>1.15642</v>
       </c>
       <c r="W56" t="n">
-        <v>1.357572</v>
+        <v>1.168876</v>
       </c>
       <c r="X56" t="n">
-        <v>1.15642</v>
+        <v>1.149068</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.168876</v>
+        <v>-2.444795</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.149068</v>
+        <v>4.142847</v>
       </c>
       <c r="AA56" t="n">
-        <v>-2.444795</v>
+        <v>-1.819225</v>
       </c>
       <c r="AB56" t="n">
-        <v>4.142847</v>
+        <v>3.768807</v>
       </c>
       <c r="AC56" t="n">
-        <v>-1.819225</v>
+        <v>-0.25</v>
       </c>
       <c r="AD56" t="n">
-        <v>3.768807</v>
+        <v>-0.000354</v>
       </c>
       <c r="AE56" t="n">
-        <v>-0.25</v>
+        <v>-0.000354</v>
       </c>
       <c r="AF56" t="n">
-        <v>-0.000354</v>
+        <v>-0.12</v>
       </c>
       <c r="AG56" t="n">
-        <v>-0.000354</v>
+        <v>-0.01</v>
       </c>
       <c r="AH56" t="n">
-        <v>-0.12</v>
+        <v>-0.17</v>
       </c>
       <c r="AI56" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="AK56" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -6758,84 +6420,78 @@
         <v>4.9886</v>
       </c>
       <c r="K57" t="n">
-        <v>4.988</v>
+        <v>7259766</v>
       </c>
       <c r="L57" t="n">
-        <v>7259766</v>
+        <v>2685397</v>
       </c>
       <c r="M57" t="n">
-        <v>2685397</v>
+        <v>4574368</v>
       </c>
       <c r="N57" t="n">
-        <v>4574368</v>
+        <v>4.64</v>
       </c>
       <c r="O57" t="n">
-        <v>4.64</v>
+        <v>3.15</v>
       </c>
       <c r="P57" t="n">
-        <v>3.15</v>
+        <v>5.51</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.51</v>
+        <v>33.36</v>
       </c>
       <c r="R57" t="n">
-        <v>33.36</v>
+        <v>366913</v>
       </c>
       <c r="S57" t="n">
-        <v>366913</v>
+        <v>0.282137</v>
       </c>
       <c r="T57" t="n">
-        <v>0.282137</v>
+        <v>-3.409876</v>
       </c>
       <c r="U57" t="n">
-        <v>-3.409876</v>
+        <v>-4.421964</v>
       </c>
       <c r="V57" t="n">
-        <v>-4.421964</v>
+        <v>0.265297</v>
       </c>
       <c r="W57" t="n">
-        <v>-4.422473</v>
+        <v>-0.079552</v>
       </c>
       <c r="X57" t="n">
-        <v>0.265297</v>
+        <v>0.468831</v>
       </c>
       <c r="Y57" t="n">
-        <v>-0.079552</v>
+        <v>1.356622</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.468831</v>
+        <v>4.39172</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.356622</v>
+        <v>0.619623</v>
       </c>
       <c r="AB57" t="n">
-        <v>4.39172</v>
+        <v>4.109608</v>
       </c>
       <c r="AC57" t="n">
-        <v>0.619623</v>
+        <v>-0.25</v>
       </c>
       <c r="AD57" t="n">
-        <v>4.109608</v>
+        <v>-0.000554</v>
       </c>
       <c r="AE57" t="n">
-        <v>-0.25</v>
+        <v>-0.000554</v>
       </c>
       <c r="AF57" t="n">
-        <v>-0.000554</v>
+        <v>0.12</v>
       </c>
       <c r="AG57" t="n">
-        <v>-0.000554</v>
+        <v>0.09</v>
       </c>
       <c r="AH57" t="n">
         <v>0.12</v>
       </c>
       <c r="AI57" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AK57" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -6871,84 +6527,78 @@
         <v>5.0569</v>
       </c>
       <c r="K58" t="n">
-        <v>5.0563</v>
+        <v>7305306</v>
       </c>
       <c r="L58" t="n">
-        <v>7305306</v>
+        <v>2708154</v>
       </c>
       <c r="M58" t="n">
-        <v>2708154</v>
+        <v>4597152</v>
       </c>
       <c r="N58" t="n">
-        <v>4597152</v>
+        <v>4.74</v>
       </c>
       <c r="O58" t="n">
-        <v>4.74</v>
+        <v>3.25</v>
       </c>
       <c r="P58" t="n">
-        <v>3.25</v>
+        <v>5.62</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.62</v>
+        <v>33.1</v>
       </c>
       <c r="R58" t="n">
-        <v>33.1</v>
+        <v>371137</v>
       </c>
       <c r="S58" t="n">
-        <v>371137</v>
+        <v>0.214941</v>
       </c>
       <c r="T58" t="n">
-        <v>0.214941</v>
+        <v>-3.805639</v>
       </c>
       <c r="U58" t="n">
-        <v>-3.805639</v>
+        <v>1.369122</v>
       </c>
       <c r="V58" t="n">
-        <v>1.369122</v>
+        <v>0.627293</v>
       </c>
       <c r="W58" t="n">
-        <v>1.369286</v>
+        <v>0.847435</v>
       </c>
       <c r="X58" t="n">
-        <v>0.627293</v>
+        <v>0.49808</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.847435</v>
+        <v>1.151227</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.49808</v>
+        <v>4.724907</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.151227</v>
+        <v>1.964454</v>
       </c>
       <c r="AB58" t="n">
-        <v>4.724907</v>
+        <v>4.420848</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.964454</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>4.420848</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="AF58" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="AG58" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="AH58" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="AI58" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK58" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -6984,84 +6634,78 @@
         <v>5.1766</v>
       </c>
       <c r="K59" t="n">
-        <v>5.176</v>
+        <v>7353293</v>
       </c>
       <c r="L59" t="n">
-        <v>7353293</v>
+        <v>2750625</v>
       </c>
       <c r="M59" t="n">
-        <v>2750625</v>
+        <v>4602668</v>
       </c>
       <c r="N59" t="n">
-        <v>4602668</v>
+        <v>4.58</v>
       </c>
       <c r="O59" t="n">
-        <v>4.58</v>
+        <v>3.18</v>
       </c>
       <c r="P59" t="n">
-        <v>3.18</v>
+        <v>5.42</v>
       </c>
       <c r="Q59" t="n">
-        <v>5.42</v>
+        <v>33.33</v>
       </c>
       <c r="R59" t="n">
-        <v>33.33</v>
+        <v>367558</v>
       </c>
       <c r="S59" t="n">
-        <v>367558</v>
+        <v>-0.882422</v>
       </c>
       <c r="T59" t="n">
-        <v>-0.882422</v>
+        <v>0.261521</v>
       </c>
       <c r="U59" t="n">
-        <v>0.261521</v>
+        <v>2.367063</v>
       </c>
       <c r="V59" t="n">
-        <v>2.367063</v>
+        <v>0.656879</v>
       </c>
       <c r="W59" t="n">
-        <v>2.367344</v>
+        <v>1.568264</v>
       </c>
       <c r="X59" t="n">
-        <v>0.656879</v>
+        <v>0.119987</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.568264</v>
+        <v>-0.964334</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.119987</v>
+        <v>4.641328</v>
       </c>
       <c r="AA59" t="n">
-        <v>-0.964334</v>
+        <v>3.177699</v>
       </c>
       <c r="AB59" t="n">
-        <v>4.641328</v>
+        <v>4.327084</v>
       </c>
       <c r="AC59" t="n">
-        <v>3.177699</v>
+        <v>-0.25</v>
       </c>
       <c r="AD59" t="n">
-        <v>4.327084</v>
+        <v>-0.000372</v>
       </c>
       <c r="AE59" t="n">
-        <v>-0.25</v>
+        <v>-0.000372</v>
       </c>
       <c r="AF59" t="n">
-        <v>-0.000372</v>
+        <v>-0.16</v>
       </c>
       <c r="AG59" t="n">
-        <v>-0.000372</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AH59" t="n">
-        <v>-0.16</v>
+        <v>-0.2</v>
       </c>
       <c r="AI59" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AK59" t="n">
         <v>0.23</v>
       </c>
     </row>
@@ -7097,84 +6741,78 @@
         <v>5.0773</v>
       </c>
       <c r="K60" t="n">
-        <v>5.0767</v>
+        <v>7372243</v>
       </c>
       <c r="L60" t="n">
-        <v>7372243</v>
+        <v>2731513</v>
       </c>
       <c r="M60" t="n">
-        <v>2731513</v>
+        <v>4640730</v>
       </c>
       <c r="N60" t="n">
-        <v>4640730</v>
+        <v>4.88</v>
       </c>
       <c r="O60" t="n">
-        <v>4.88</v>
+        <v>3.31</v>
       </c>
       <c r="P60" t="n">
-        <v>3.31</v>
+        <v>5.81</v>
       </c>
       <c r="Q60" t="n">
-        <v>5.81</v>
+        <v>32.08</v>
       </c>
       <c r="R60" t="n">
-        <v>32.08</v>
+        <v>369742</v>
       </c>
       <c r="S60" t="n">
-        <v>369742</v>
+        <v>-0.219358</v>
       </c>
       <c r="T60" t="n">
-        <v>-0.219358</v>
+        <v>4.057001</v>
       </c>
       <c r="U60" t="n">
-        <v>4.057001</v>
+        <v>-1.918247</v>
       </c>
       <c r="V60" t="n">
-        <v>-1.918247</v>
+        <v>0.257708</v>
       </c>
       <c r="W60" t="n">
-        <v>-1.91847</v>
+        <v>-0.694824</v>
       </c>
       <c r="X60" t="n">
-        <v>0.257708</v>
+        <v>0.826955</v>
       </c>
       <c r="Y60" t="n">
-        <v>-0.694824</v>
+        <v>0.5941920000000001</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.826955</v>
+        <v>4.443025</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.5941920000000001</v>
+        <v>2.772183</v>
       </c>
       <c r="AB60" t="n">
-        <v>4.443025</v>
+        <v>4.098046</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.772183</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>4.098046</v>
+        <v>-0.000497</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>-0.000497</v>
       </c>
       <c r="AF60" t="n">
-        <v>-0.000497</v>
+        <v>0.3</v>
       </c>
       <c r="AG60" t="n">
-        <v>-0.000497</v>
+        <v>0.13</v>
       </c>
       <c r="AH60" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="AI60" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="AK60" t="n">
         <v>-1.25</v>
       </c>
     </row>
@@ -7205,55 +6843,49 @@
       <c r="J61" t="n">
         <v>5.1816</v>
       </c>
-      <c r="K61" t="n">
-        <v>5.181</v>
-      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="n">
+      <c r="R61" t="n">
         <v>372616</v>
       </c>
+      <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="n">
+      <c r="U61" t="n">
         <v>2.054241</v>
       </c>
-      <c r="W61" t="n">
-        <v>2.054484</v>
-      </c>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
+      <c r="Y61" t="n">
+        <v>0.777299</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>4.223453</v>
+      </c>
       <c r="AA61" t="n">
-        <v>0.777299</v>
+        <v>2.178243</v>
       </c>
       <c r="AB61" t="n">
-        <v>4.223453</v>
+        <v>3.983297</v>
       </c>
       <c r="AC61" t="n">
-        <v>2.178243</v>
+        <v>-0.25</v>
       </c>
       <c r="AD61" t="n">
-        <v>3.983297</v>
+        <v>-0.0007470000000000001</v>
       </c>
       <c r="AE61" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AF61" t="n">
         <v>-0.0007470000000000001</v>
       </c>
-      <c r="AG61" t="n">
-        <v>-0.0007470000000000001</v>
-      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="inlineStr"/>
-      <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -7263,7 +6895,7 @@
         <v>13.75</v>
       </c>
       <c r="C62" t="n">
-        <v>0.051352</v>
+        <v>0.051321</v>
       </c>
       <c r="D62" t="n">
         <v>0.051352</v>
@@ -7274,11 +6906,9 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>5.1795</v>
-      </c>
-      <c r="K62" t="n">
-        <v>5.1789</v>
-      </c>
+        <v>5.1991</v>
+      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -7288,33 +6918,29 @@
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="n">
-        <v>-0.040528</v>
-      </c>
-      <c r="W62" t="n">
-        <v>-0.040533</v>
-      </c>
+      <c r="U62" t="n">
+        <v>0.337734</v>
+      </c>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr"/>
-      <c r="AC62" t="inlineStr"/>
-      <c r="AD62" t="inlineStr"/>
+      <c r="AC62" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>-0.000464</v>
+      </c>
       <c r="AE62" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AF62" t="n">
         <v>-0.000432</v>
       </c>
-      <c r="AG62" t="n">
-        <v>-0.000432</v>
-      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
-      <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI62"/>
+  <dimension ref="A1:AK62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,125 +473,135 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>cambio_compra_usd</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>saldo_credito_total</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>saldo_credito_pj</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>saldo_credito_pf</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inadimplencia_total</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inadimplencia_pj</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inadimplencia_pf</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>var_pct_cambio_compra_usd</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ipca_acum_12m</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>inpc_acum_12m</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>dif_selic_over</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>dif_cdi</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -629,30 +639,32 @@
         <v>5.4394</v>
       </c>
       <c r="K2" t="n">
+        <v>5.4388</v>
+      </c>
+      <c r="L2" t="n">
         <v>4441056</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>1894119</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>2546936</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>2.34</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1.43</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>3.01</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>21.42</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>368886</v>
       </c>
-      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -669,6 +681,8 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -702,72 +716,78 @@
         <v>5.643</v>
       </c>
       <c r="K3" t="n">
+        <v>5.6424</v>
+      </c>
+      <c r="L3" t="n">
         <v>4511956</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>1910940</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>2601017</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>2.33</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>1.43</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>2.99</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>22.89</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>367927</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>0.537905</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>-0.594556</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>3.74306</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
+        <v>3.743473</v>
+      </c>
+      <c r="X3" t="n">
         <v>1.596467</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>0.888065</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>2.123375</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AA3" t="n">
         <v>-0.259972</v>
       </c>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="n">
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AF3" t="n">
         <v>0.000557</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AG3" t="n">
         <v>0.000557</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AH3" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AK3" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -803,72 +823,78 @@
         <v>5.6199</v>
       </c>
       <c r="K4" t="n">
+        <v>5.6193</v>
+      </c>
+      <c r="L4" t="n">
         <v>4597507</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>1933111</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2664395</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>2.36</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>1.46</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>3.01</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>23.91</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>367772</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>1.608989</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>1.36989</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>-0.409357</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
+        <v>-0.4094</v>
+      </c>
+      <c r="X4" t="n">
         <v>1.896096</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Y4" t="n">
         <v>1.160214</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Z4" t="n">
         <v>2.436662</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AA4" t="n">
         <v>-0.042128</v>
       </c>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
         <v>0.005012</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AG4" t="n">
         <v>0.005012</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AH4" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AI4" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AJ4" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AK4" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -904,72 +930,78 @@
         <v>5.5805</v>
       </c>
       <c r="K5" t="n">
+        <v>5.5799</v>
+      </c>
+      <c r="L5" t="n">
         <v>4682852</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>1974391</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>2708461</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>2.35</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>1.4</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>3.05</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>24.21</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>362204</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>0.32497</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>1.502063</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>-0.70108</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
+        <v>-0.701155</v>
+      </c>
+      <c r="X5" t="n">
         <v>1.856332</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Y5" t="n">
         <v>2.135418</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>1.653884</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AA5" t="n">
         <v>-1.513981</v>
       </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="n">
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AF5" t="n">
         <v>0.00406</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AG5" t="n">
         <v>0.00406</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AH5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AI5" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AJ5" t="n">
         <v>0.04</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AK5" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1005,72 +1037,78 @@
         <v>5.3574</v>
       </c>
       <c r="K6" t="n">
+        <v>5.3568</v>
+      </c>
+      <c r="L6" t="n">
         <v>4682131</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>1947035</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>2735096</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>2.51</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>1.46</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>3.26</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>25.23</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>358398</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>-1.968118</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>-7.696961</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>-3.99785</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
+        <v>-3.99828</v>
+      </c>
+      <c r="X6" t="n">
         <v>-0.015397</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
         <v>-1.385541</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Z6" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AA6" t="n">
         <v>-1.050789</v>
       </c>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
         <v>0.001433</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AG6" t="n">
         <v>0.001433</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AH6" t="n">
         <v>0.16</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AI6" t="n">
         <v>0.06</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AJ6" t="n">
         <v>0.21</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AK6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1106,72 +1144,78 @@
         <v>5.1394</v>
       </c>
       <c r="K7" t="n">
+        <v>5.1388</v>
+      </c>
+      <c r="L7" t="n">
         <v>4727818</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>1971524</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>2756295</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>2.57</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>1.44</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>3.38</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>25.63</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>357740</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>1.087134</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>4.318965</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>-4.069138</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
+        <v>-4.069594</v>
+      </c>
+      <c r="X7" t="n">
         <v>0.975774</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
         <v>1.257759</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>0.775073</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AA7" t="n">
         <v>-0.183595</v>
       </c>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="n">
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AF7" t="n">
         <v>0.004849</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AG7" t="n">
         <v>0.004849</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AH7" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AI7" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AJ7" t="n">
         <v>0.12</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AK7" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1207,72 +1251,78 @@
         <v>4.7378</v>
       </c>
       <c r="K8" t="n">
+        <v>4.7372</v>
+      </c>
+      <c r="L8" t="n">
         <v>4794583</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>1994119</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>2800464</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>2.66</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>1.55</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>3.45</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>26.54</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>353169</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>1.084094</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>9.300848999999999</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>-7.814142</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
+        <v>-7.815054</v>
+      </c>
+      <c r="X8" t="n">
         <v>1.412174</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Y8" t="n">
         <v>1.146068</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Z8" t="n">
         <v>1.602477</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AA8" t="n">
         <v>-1.277744</v>
       </c>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="n">
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="n">
         <v>1</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AF8" t="n">
         <v>0.002356</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AG8" t="n">
         <v>0.002356</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AH8" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AI8" t="n">
         <v>0.11</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AJ8" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AK8" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1308,72 +1358,78 @@
         <v>4.9191</v>
       </c>
       <c r="K9" t="n">
+        <v>4.9185</v>
+      </c>
+      <c r="L9" t="n">
         <v>4833732</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>2003312</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>2830420</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>2.72</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>1.57</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>3.54</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>27.46</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>345097</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>-0.107325</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>-4.116419</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>3.826671</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
+        <v>3.827155</v>
+      </c>
+      <c r="X9" t="n">
         <v>0.816526</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Y9" t="n">
         <v>0.461006</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Z9" t="n">
         <v>1.06968</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AA9" t="n">
         <v>-2.285591</v>
       </c>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
         <v>0.001785</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AG9" t="n">
         <v>0.001785</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AH9" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AI9" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AJ9" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AK9" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1409,72 +1465,78 @@
         <v>4.7289</v>
       </c>
       <c r="K10" t="n">
+        <v>4.7283</v>
+      </c>
+      <c r="L10" t="n">
         <v>4889397</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>2013726</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>2875671</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>2.79</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>1.57</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>27.42</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>346415</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>0.205368</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>-0.484439</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>-3.866561</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
+        <v>-3.867033</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.151595</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Y10" t="n">
         <v>0.5198390000000001</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Z10" t="n">
         <v>1.598738</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AA10" t="n">
         <v>0.381922</v>
       </c>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="n">
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="n">
         <v>1</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AF10" t="n">
         <v>0.003057</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AG10" t="n">
         <v>0.003057</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AH10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AK10" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1510,72 +1572,78 @@
         <v>5.238</v>
       </c>
       <c r="K11" t="n">
+        <v>5.2374</v>
+      </c>
+      <c r="L11" t="n">
         <v>4965603</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>2052569</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>2913035</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>2.73</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>1.52</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>3.57</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>27.88</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>341958</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>-0.1354</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>-0.428397</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>10.765717</v>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
+        <v>10.767083</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.558597</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Y11" t="n">
         <v>1.928912</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Z11" t="n">
         <v>1.299314</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AA11" t="n">
         <v>-1.286607</v>
       </c>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="n">
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AF11" t="n">
         <v>0.00132</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AG11" t="n">
         <v>0.00132</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AH11" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AI11" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AJ11" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AK11" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1611,72 +1679,78 @@
         <v>5.1884</v>
       </c>
       <c r="K12" t="n">
+        <v>5.1878</v>
+      </c>
+      <c r="L12" t="n">
         <v>4999244</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>2047038</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>2952207</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>2.84</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>1.6</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>29.24</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>346403</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>1.930691</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>4.675335</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>-0.946926</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
+        <v>-0.947035</v>
+      </c>
+      <c r="X12" t="n">
         <v>0.677481</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Y12" t="n">
         <v>-0.269467</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Z12" t="n">
         <v>1.344714</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AA12" t="n">
         <v>1.299867</v>
       </c>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AG12" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AH12" t="n">
         <v>0.11</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AI12" t="n">
         <v>0.08</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AJ12" t="n">
         <v>0.14</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AK12" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -1712,78 +1786,84 @@
         <v>5.179</v>
       </c>
       <c r="K13" t="n">
+        <v>5.1784</v>
+      </c>
+      <c r="L13" t="n">
         <v>5072711</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>2064183</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>3008528</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>2.9</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>1.62</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>3.78</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>28.6</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>339664</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>-0.32129</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>0.530637</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>-0.181173</v>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
+        <v>-0.181194</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.469562</v>
       </c>
-      <c r="W13" t="n">
+      <c r="Y13" t="n">
         <v>0.837552</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Z13" t="n">
         <v>1.907759</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AA13" t="n">
         <v>-1.945422</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AB13" t="n">
         <v>8.727061000000001</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AC13" t="n">
         <v>8.58755</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AD13" t="n">
         <v>8.825751</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AE13" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AF13" t="n">
         <v>0.001523</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AG13" t="n">
         <v>0.001523</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AH13" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AI13" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AJ13" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AK13" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -1819,78 +1899,84 @@
         <v>5.4066</v>
       </c>
       <c r="K14" t="n">
+        <v>5.406</v>
+      </c>
+      <c r="L14" t="n">
         <v>5164775</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>2109806</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3054969</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>2.92</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>1.65</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>3.8</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>28.57</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>327580</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>0.053914</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>-3.179227</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>4.394671</v>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
+        <v>4.39518</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.814888</v>
       </c>
-      <c r="W14" t="n">
+      <c r="Y14" t="n">
         <v>2.210221</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Z14" t="n">
         <v>1.543645</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AA14" t="n">
         <v>-3.557633</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AB14" t="n">
         <v>7.168596</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AC14" t="n">
         <v>8.248760000000001</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AD14" t="n">
         <v>7.191214</v>
       </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
         <v>0.000228</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AG14" t="n">
         <v>0.000228</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0.03</v>
       </c>
       <c r="AH14" t="n">
         <v>0.02</v>
       </c>
       <c r="AI14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AK14" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -1926,78 +2012,84 @@
         <v>5.257</v>
       </c>
       <c r="K15" t="n">
+        <v>5.2564</v>
+      </c>
+      <c r="L15" t="n">
         <v>5215990</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>2105856</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>3110134</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>3.04</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>1.77</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>3.89</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>29.68</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>325546</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>0.278143</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>-1.094122</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>-2.766988</v>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
+        <v>-2.767296</v>
+      </c>
+      <c r="X15" t="n">
         <v>0.991621</v>
       </c>
-      <c r="W15" t="n">
+      <c r="Y15" t="n">
         <v>-0.187221</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Z15" t="n">
         <v>1.805747</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AA15" t="n">
         <v>-0.6209170000000001</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AB15" t="n">
         <v>6.470016</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AC15" t="n">
         <v>6.517038</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AD15" t="n">
         <v>6.460076</v>
       </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
       <c r="AE15" t="n">
         <v>0</v>
       </c>
       <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
         <v>0.12</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AI15" t="n">
         <v>0.12</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AJ15" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AK15" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -2033,78 +2125,84 @@
         <v>5.2941</v>
       </c>
       <c r="K16" t="n">
+        <v>5.2935</v>
+      </c>
+      <c r="L16" t="n">
         <v>5285657</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>2130312</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>3155345</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>3.07</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>1.81</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>3.92</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>30.52</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>331505</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>-0.716776</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>-0.930689</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>0.705726</v>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
+        <v>0.705806</v>
+      </c>
+      <c r="X16" t="n">
         <v>1.335643</v>
       </c>
-      <c r="W16" t="n">
+      <c r="Y16" t="n">
         <v>1.161333</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Z16" t="n">
         <v>1.453667</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AA16" t="n">
         <v>1.830463</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AB16" t="n">
         <v>5.900488</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AC16" t="n">
         <v>5.899363</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AD16" t="n">
         <v>5.974439</v>
       </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
       <c r="AE16" t="n">
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
         <v>0.03</v>
       </c>
       <c r="AI16" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AK16" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2140,78 +2238,84 @@
         <v>5.2177</v>
       </c>
       <c r="K17" t="n">
+        <v>5.2171</v>
+      </c>
+      <c r="L17" t="n">
         <v>5366069</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>2178236</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>3187833</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>3.07</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>1.8</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>3.94</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>29.64</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>324703</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>-0.125523</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>0.827078</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>-1.443116</v>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
+        <v>-1.443279</v>
+      </c>
+      <c r="X17" t="n">
         <v>1.521325</v>
       </c>
-      <c r="W17" t="n">
+      <c r="Y17" t="n">
         <v>2.249624</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Z17" t="n">
         <v>1.029618</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AA17" t="n">
         <v>-2.051854</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AB17" t="n">
         <v>5.784842</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AC17" t="n">
         <v>5.458422</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AD17" t="n">
         <v>5.932356</v>
       </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
         <v>-0</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AG17" t="n">
         <v>-0</v>
       </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AJ17" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AK17" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -2247,78 +2351,84 @@
         <v>5.0993</v>
       </c>
       <c r="K18" t="n">
+        <v>5.0987</v>
+      </c>
+      <c r="L18" t="n">
         <v>5373231</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>2151399</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>3221831</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>3.24</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>1.94</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>4.11</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>30.54</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>331122</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>-0.475503</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>-4.872284</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>-2.269199</v>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
+        <v>-2.26946</v>
+      </c>
+      <c r="X18" t="n">
         <v>0.133468</v>
       </c>
-      <c r="W18" t="n">
+      <c r="Y18" t="n">
         <v>-1.232052</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Z18" t="n">
         <v>1.066493</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AA18" t="n">
         <v>1.976883</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AB18" t="n">
         <v>5.77432</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AC18" t="n">
         <v>3.79089</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AD18" t="n">
         <v>5.711379</v>
       </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
         <v>0.17</v>
       </c>
       <c r="AI18" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AK18" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2354,78 +2464,84 @@
         <v>5.2078</v>
       </c>
       <c r="K19" t="n">
+        <v>5.2072</v>
+      </c>
+      <c r="L19" t="n">
         <v>5370950</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>2136105</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>3234845</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>3.36</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>2.17</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>4.16</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>30.48</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>328098</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>2.96673</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>3.731301</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>2.127743</v>
       </c>
-      <c r="V19" t="n">
+      <c r="W19" t="n">
+        <v>2.127993</v>
+      </c>
+      <c r="X19" t="n">
         <v>-0.042451</v>
       </c>
-      <c r="W19" t="n">
+      <c r="Y19" t="n">
         <v>-0.710886</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Z19" t="n">
         <v>0.403932</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AA19" t="n">
         <v>-0.913259</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AB19" t="n">
         <v>5.596302</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AC19" t="n">
         <v>1.864495</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AD19" t="n">
         <v>5.47065</v>
       </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
       <c r="AE19" t="n">
         <v>0</v>
       </c>
       <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
         <v>0.12</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AI19" t="n">
         <v>0.23</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AJ19" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AK19" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2461,78 +2577,84 @@
         <v>5.0804</v>
       </c>
       <c r="K20" t="n">
+        <v>5.0798</v>
+      </c>
+      <c r="L20" t="n">
         <v>5424811</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>2154900</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>3269910</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>3.35</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>2.2</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>4.11</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>30.99</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>341158</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>0.004919</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>12.135312</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>-2.446331</v>
       </c>
-      <c r="V20" t="n">
+      <c r="W20" t="n">
+        <v>-2.446612</v>
+      </c>
+      <c r="X20" t="n">
         <v>1.002821</v>
       </c>
-      <c r="W20" t="n">
+      <c r="Y20" t="n">
         <v>0.879872</v>
       </c>
-      <c r="X20" t="n">
+      <c r="Z20" t="n">
         <v>1.083978</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AA20" t="n">
         <v>3.980518</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AB20" t="n">
         <v>4.650694</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AC20" t="n">
         <v>0.172427</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AD20" t="n">
         <v>4.361088</v>
       </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
       <c r="AE20" t="n">
         <v>0</v>
       </c>
       <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AI20" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AJ20" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AK20" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2568,78 +2690,84 @@
         <v>5.0007</v>
       </c>
       <c r="K21" t="n">
+        <v>5.0001</v>
+      </c>
+      <c r="L21" t="n">
         <v>5426307</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>2145000</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>3281308</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>3.54</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>2.45</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>4.26</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>31.62</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>345725</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>0.825329</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>-5.946769</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>-1.568774</v>
       </c>
-      <c r="V21" t="n">
+      <c r="W21" t="n">
+        <v>-1.568959</v>
+      </c>
+      <c r="X21" t="n">
         <v>0.027577</v>
       </c>
-      <c r="W21" t="n">
+      <c r="Y21" t="n">
         <v>-0.459418</v>
       </c>
-      <c r="X21" t="n">
+      <c r="Z21" t="n">
         <v>0.348572</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AA21" t="n">
         <v>1.338676</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AB21" t="n">
         <v>4.184706</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AC21" t="n">
         <v>-2.158772</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AD21" t="n">
         <v>3.834324</v>
       </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
       <c r="AE21" t="n">
         <v>0</v>
       </c>
       <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
         <v>0.19</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AI21" t="n">
         <v>0.25</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AJ21" t="n">
         <v>0.15</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AK21" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -2675,78 +2803,84 @@
         <v>5.0959</v>
       </c>
       <c r="K22" t="n">
+        <v>5.0953</v>
+      </c>
+      <c r="L22" t="n">
         <v>5453708</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>2145530</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>3308178</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>3.65</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>2.58</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>4.35</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>31.63</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>343489</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>-1.448972</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>-1.275652</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>1.903733</v>
       </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
+        <v>1.903962</v>
+      </c>
+      <c r="X22" t="n">
         <v>0.504966</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Y22" t="n">
         <v>0.024709</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Z22" t="n">
         <v>0.818881</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AA22" t="n">
         <v>-0.646757</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AB22" t="n">
         <v>3.935832</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AC22" t="n">
         <v>-4.45588</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AD22" t="n">
         <v>3.741292</v>
       </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
         <v>-0</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AG22" t="n">
         <v>-0</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AH22" t="n">
         <v>0.11</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AI22" t="n">
         <v>0.13</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AJ22" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI22" t="n">
+      <c r="AK22" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -2782,78 +2916,84 @@
         <v>4.8192</v>
       </c>
       <c r="K23" t="n">
+        <v>4.8186</v>
+      </c>
+      <c r="L23" t="n">
         <v>5479459</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>2169613</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>3309846</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>3.61</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>2.63</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>4.25</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>30.85</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>343620</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>-0.029659</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>-0.418863</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>-5.429855</v>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
+        <v>-5.430495</v>
+      </c>
+      <c r="X23" t="n">
         <v>0.472174</v>
       </c>
-      <c r="W23" t="n">
+      <c r="Y23" t="n">
         <v>1.122473</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Z23" t="n">
         <v>0.050421</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AA23" t="n">
         <v>0.038138</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AB23" t="n">
         <v>3.161501</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AC23" t="n">
         <v>-6.84947</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AD23" t="n">
         <v>2.998957</v>
       </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
       <c r="AE23" t="n">
         <v>0</v>
       </c>
       <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AI23" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AJ23" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AK23" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -2889,78 +3029,84 @@
         <v>4.7415</v>
       </c>
       <c r="K24" t="n">
+        <v>4.7409</v>
+      </c>
+      <c r="L24" t="n">
         <v>5484871</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>2153541</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>3331330</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>3.63</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>2.73</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>4.22</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>30.43</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>345476</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>0.495618</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>2.992877</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>-1.612301</v>
       </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
+        <v>-1.612502</v>
+      </c>
+      <c r="X24" t="n">
         <v>0.098769</v>
       </c>
-      <c r="W24" t="n">
+      <c r="Y24" t="n">
         <v>-0.740777</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Z24" t="n">
         <v>0.6490939999999999</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AA24" t="n">
         <v>0.5401319999999999</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AB24" t="n">
         <v>3.992444</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AC24" t="n">
         <v>-7.713954</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AD24" t="n">
         <v>3.527423</v>
       </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
       <c r="AE24" t="n">
         <v>0</v>
       </c>
       <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AI24" t="n">
         <v>0.1</v>
       </c>
-      <c r="AH24" t="n">
+      <c r="AJ24" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AK24" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -2996,78 +3142,84 @@
         <v>4.9219</v>
       </c>
       <c r="K25" t="n">
+        <v>4.9213</v>
+      </c>
+      <c r="L25" t="n">
         <v>5559063</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>2172658</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>3386405</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>3.61</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>2.82</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>4.12</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>29.92</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>344177</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>-0.393045</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>0.676</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>3.804703</v>
       </c>
-      <c r="V25" t="n">
+      <c r="W25" t="n">
+        <v>3.805185</v>
+      </c>
+      <c r="X25" t="n">
         <v>1.352666</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Y25" t="n">
         <v>0.887701</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Z25" t="n">
         <v>1.653244</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AA25" t="n">
         <v>-0.376003</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AB25" t="n">
         <v>4.608216</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AC25" t="n">
         <v>-7.193509</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AD25" t="n">
         <v>4.057054</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AE25" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AF25" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AG25" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AH25" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AI25" t="n">
         <v>0.09</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AJ25" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="AK25" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -3103,78 +3255,84 @@
         <v>5.0076</v>
       </c>
       <c r="K26" t="n">
+        <v>5.007</v>
+      </c>
+      <c r="L26" t="n">
         <v>5625945</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>2215175</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>3410769</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>3.54</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>2.82</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>4</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>29.66</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>340324</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>0.012595</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>-4.052448</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>1.741198</v>
       </c>
-      <c r="V26" t="n">
+      <c r="W26" t="n">
+        <v>1.74141</v>
+      </c>
+      <c r="X26" t="n">
         <v>1.203116</v>
       </c>
-      <c r="W26" t="n">
+      <c r="Y26" t="n">
         <v>1.956912</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Z26" t="n">
         <v>0.719465</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AA26" t="n">
         <v>-1.119482</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AB26" t="n">
         <v>5.185235</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AC26" t="n">
         <v>-5.956714</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AD26" t="n">
         <v>4.505936</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AE26" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AF26" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AG26" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="AF26" t="n">
+      <c r="AH26" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AK26" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -3210,78 +3368,84 @@
         <v>5.0575</v>
       </c>
       <c r="K27" t="n">
+        <v>5.0569</v>
+      </c>
+      <c r="L27" t="n">
         <v>5653808</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>2204808</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>3449000</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>3.56</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>2.92</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>3.97</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>29.24</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>340247</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>0.316333</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>0.171808</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>0.996485</v>
       </c>
-      <c r="V27" t="n">
+      <c r="W27" t="n">
+        <v>0.996605</v>
+      </c>
+      <c r="X27" t="n">
         <v>0.495259</v>
       </c>
-      <c r="W27" t="n">
+      <c r="Y27" t="n">
         <v>-0.467999</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Z27" t="n">
         <v>1.120891</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AA27" t="n">
         <v>-0.022625</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AB27" t="n">
         <v>4.819246</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AC27" t="n">
         <v>-4.560737</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AD27" t="n">
         <v>4.141877</v>
       </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AG27" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AH27" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AI27" t="n">
         <v>0.1</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="AJ27" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AK27" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3317,78 +3481,84 @@
         <v>4.9355</v>
       </c>
       <c r="K28" t="n">
+        <v>4.9349</v>
+      </c>
+      <c r="L28" t="n">
         <v>5711103</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>2220766</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>3490337</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>3.53</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>2.99</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>3.88</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>29.01</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>348406</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>0.734124</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>-0.248573</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>-2.412259</v>
       </c>
-      <c r="V28" t="n">
+      <c r="W28" t="n">
+        <v>-2.412545</v>
+      </c>
+      <c r="X28" t="n">
         <v>1.013388</v>
       </c>
-      <c r="W28" t="n">
+      <c r="Y28" t="n">
         <v>0.723782</v>
       </c>
-      <c r="X28" t="n">
+      <c r="Z28" t="n">
         <v>1.198521</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AA28" t="n">
         <v>2.397964</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AB28" t="n">
         <v>4.683537</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AC28" t="n">
         <v>-3.457004</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AD28" t="n">
         <v>3.851383</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AE28" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AF28" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AG28" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AH28" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AI28" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AH28" t="n">
+      <c r="AJ28" t="n">
         <v>-0.09</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AK28" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -3424,78 +3594,84 @@
         <v>4.8413</v>
       </c>
       <c r="K29" t="n">
+        <v>4.8407</v>
+      </c>
+      <c r="L29" t="n">
         <v>5805157</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>2283485</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>3521672</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>3.29</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>2.59</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>28.14</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>355034</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>1.248734</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>0.004199</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>-1.908621</v>
       </c>
-      <c r="V29" t="n">
+      <c r="W29" t="n">
+        <v>-1.908853</v>
+      </c>
+      <c r="X29" t="n">
         <v>1.646862</v>
       </c>
-      <c r="W29" t="n">
+      <c r="Y29" t="n">
         <v>2.824206</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Z29" t="n">
         <v>0.897764</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AA29" t="n">
         <v>1.902378</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AB29" t="n">
         <v>4.621114</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AC29" t="n">
         <v>-3.178284</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AD29" t="n">
         <v>3.706988</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AE29" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AF29" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AG29" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AH29" t="n">
         <v>-0.24</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AI29" t="n">
         <v>-0.4</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AJ29" t="n">
         <v>-0.13</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AK29" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3531,78 +3707,84 @@
         <v>4.9535</v>
       </c>
       <c r="K30" t="n">
+        <v>4.9529</v>
+      </c>
+      <c r="L30" t="n">
         <v>5794707</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>2234362</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3560345</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>3.38</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2.77</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>3.76</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>28</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>355066</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>-0.395831</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>-2.347954</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>2.317559</v>
       </c>
-      <c r="V30" t="n">
+      <c r="W30" t="n">
+        <v>2.317847</v>
+      </c>
+      <c r="X30" t="n">
         <v>-0.180012</v>
       </c>
-      <c r="W30" t="n">
+      <c r="Y30" t="n">
         <v>-2.151229</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Z30" t="n">
         <v>1.098143</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AA30" t="n">
         <v>0.009013</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AB30" t="n">
         <v>4.506637</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AC30" t="n">
         <v>-3.31355</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AD30" t="n">
         <v>3.820543</v>
       </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AG30" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AH30" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AI30" t="n">
         <v>0.18</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AJ30" t="n">
         <v>0.01</v>
       </c>
-      <c r="AI30" t="n">
+      <c r="AK30" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -3638,78 +3820,84 @@
         <v>4.9833</v>
       </c>
       <c r="K31" t="n">
+        <v>4.9827</v>
+      </c>
+      <c r="L31" t="n">
         <v>5815954</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>2235302</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>3580652</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>3.38</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>2.76</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>3.76</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>27.85</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>352705</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>0.177893</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>2.873375</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>0.601595</v>
       </c>
-      <c r="V31" t="n">
+      <c r="W31" t="n">
+        <v>0.601668</v>
+      </c>
+      <c r="X31" t="n">
         <v>0.366662</v>
       </c>
-      <c r="W31" t="n">
+      <c r="Y31" t="n">
         <v>0.04207</v>
       </c>
-      <c r="X31" t="n">
+      <c r="Z31" t="n">
         <v>0.570366</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AA31" t="n">
         <v>-0.664947</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AB31" t="n">
         <v>4.496274</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AC31" t="n">
         <v>-3.758575</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AD31" t="n">
         <v>3.861754</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AE31" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AF31" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AG31" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -3745,78 +3933,84 @@
         <v>4.9962</v>
       </c>
       <c r="K32" t="n">
+        <v>4.9956</v>
+      </c>
+      <c r="L32" t="n">
         <v>5899742</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>2285775</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>3613967</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>3.33</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>2.71</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>28.14</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>355008</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>0.014285</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>7.262481</v>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
         <v>0.258865</v>
       </c>
-      <c r="V32" t="n">
+      <c r="W32" t="n">
+        <v>0.258896</v>
+      </c>
+      <c r="X32" t="n">
         <v>1.440658</v>
       </c>
-      <c r="W32" t="n">
+      <c r="Y32" t="n">
         <v>2.257995</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Z32" t="n">
         <v>0.930417</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AA32" t="n">
         <v>0.652954</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AB32" t="n">
         <v>3.925596</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AC32" t="n">
         <v>-4.25878</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AD32" t="n">
         <v>3.397348</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AE32" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AF32" t="n">
         <v>-0.000537</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AG32" t="n">
         <v>-0.000537</v>
-      </c>
-      <c r="AF32" t